--- a/docs/Scag-Scapes-Proforma.xlsx
+++ b/docs/Scag-Scapes-Proforma.xlsx
@@ -12,7 +12,8 @@
     <sheet name="Proforma 24 mo" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Unit economics" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Scenarios" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Sources &amp; notes" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Equipment plan" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Sources &amp; notes" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="285">
   <si>
     <t xml:space="preserve">Scag Scapes LLC - Growth Proforma - Assumptions</t>
   </si>
@@ -302,25 +303,85 @@
     <t xml:space="preserve">Left at $0 on purpose - terms to be agreed. Enter a number to see the effect.</t>
   </si>
   <si>
-    <t xml:space="preserve">CREW 2 STARTUP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equipment purchase - mini excavator, trailer, tools ($)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Used 3.5-4 ton mini-ex ~$45-55K + dump trailer + hand tools. Alternative: rent at ~$2,000/mo (Home Depot live rate in the app) for the first 90 days.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Truck for Crew 2 ($)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Used 3/4-ton.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% financed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20% down.</t>
+    <t xml:space="preserve">CREW 2 EQUIPMENT - rent first, then own (Crew 1 already owns its trailer, skid steer and mini excavator)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mini excavator (3.5-4 ton, used) - purchase price ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Used KX040 / 26G class. Crew 1's is owned; Crew 2 needs its own.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mini excavator - rental per month ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home Depot 4-week rate ~$1,700-2,000 (live in the app); Sunbelt/United quote-only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mini excavator - months rented before buying</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rent while Crew 2 proves itself; buy after it hits target twice. 0 = buy at start.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skid steer / CTL (used) - purchase price ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Used T66 / 259D class.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skid steer - rental per month ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chain 4-week rate (rate card, CALL_TO_CONFIRM).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skid steer - months rented before buying</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dump trailer 7x14 (new) - purchase price ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trailers rent badly and hold value - buy at start.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dump trailer - rental per month ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dump trailer - months rented before buying</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 = buy at Crew 2 start.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Truck 3/4-ton (used) - purchase price ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Truck - rental per month ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not rented.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Truck - months rented before buying</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hand tools, laser, compactor, PPE, phones ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bought at start.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tools - rental per month ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tools - months rented before buying</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% financed on purchases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20% down on each purchase.</t>
   </si>
   <si>
     <t xml:space="preserve">Loan rate (APR)</t>
@@ -332,18 +393,6 @@
     <t xml:space="preserve">Loan term (months)</t>
   </si>
   <si>
-    <t xml:space="preserve">Rent instead of buy for first 3 months? (1 = yes)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Safer: rent the mini-ex for months 7-9, buy when Crew 2 has hit target twice.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rental cost per month while renting ($)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home Depot 3.5-4 ton ~$439/day, ~$1,700-2,000 4-week; app shows live.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hiring + training cost for Crew 2 (one-time $)</t>
   </si>
   <si>
@@ -482,10 +531,10 @@
     <t xml:space="preserve">Marketing - content, reviews, GBP, site</t>
   </si>
   <si>
-    <t xml:space="preserve">Crew 2 - rental (months before purchase) + hiring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crew 2 - equipment + truck loan payment</t>
+    <t xml:space="preserve">Crew 2 - equipment rental (before purchase) + hiring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crew 2 - equipment + truck loan payments</t>
   </si>
   <si>
     <t xml:space="preserve">Total overhead</t>
@@ -506,7 +555,7 @@
     <t xml:space="preserve">Cash out - direct costs + overhead</t>
   </si>
   <si>
-    <t xml:space="preserve">Cash out - Crew 2 down payment (equipment + truck)</t>
+    <t xml:space="preserve">Cash out - Crew 2 down payments (20% of each purchase)</t>
   </si>
   <si>
     <t xml:space="preserve">NET CASH FLOW</t>
@@ -686,6 +735,78 @@
     <t xml:space="preserve">Stretch: pricing power from reviews + Moasure proposals lifts $/LF to $46; 140 plan customers = the sellable recurring book.</t>
   </si>
   <si>
+    <t xml:space="preserve">Path to owning Crew 2's equipment - rent first, buy on proof</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crew 1 already owns a big trailer, a skid steer and a mini excavator (no capex in this plan). Crew 2 needs its own set. Rent-to-prove, then buy; every date is driven by the Crew 2 start month on Assumptions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purchase price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rent / month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Months rented</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rent paid before buying</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purchase month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Down payment (20%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loan payment / mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loan paid off (month)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own-vs-rent break-even (months)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mini excavator (used)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skid steer / CTL (used)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dump trailer 7x14 (new)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Truck 3/4-ton (used)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tools, laser, compactor, PPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How to read it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own-vs-rent break-even: purchase price / monthly rent. A mini-ex at $50,000 vs $2,000/month breaks even at 25 months of use - so anything Crew 2 will run for more than two years should be owned; the 3-month rental is insurance against Crew 2 not working out, not a long-term plan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The purchase month is the Crew 2 start month plus the months rented. Decision rule for pulling the trigger early or late: buy when Crew 2 has installed its target LF in two consecutive months; keep renting if it has not.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Down payments hit cash in the purchase month (Proforma: 'Cash out - Crew 2 down payments'); loan payments run 60 months from there. Rent paid before buying is money spent to de-risk the purchase - budgeted, not wasted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crew 1's set is already owned: no purchases are modeled for it. Its existing payments, if any, sit in 'Existing truck / equipment payments' on Assumptions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time to full ownership of Crew 2's set: trailer, truck and tools on day one; mini-ex and skid steer bought in month start+3; all loans paid off 60 months after that (month 70 in the base case). Equity builds from the first payment; the machines outlast the loans.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sources and notes</t>
   </si>
   <si>
@@ -758,7 +879,7 @@
     <t xml:space="preserve">Model conventions</t>
   </si>
   <si>
-    <t xml:space="preserve">Revenue recognized in month of install; 30% deposit at signing, 90% of balance in month of completion, 10% the following month. Payroll burden 18% is an estimate - replace with actual workers' comp rate. No income tax modeled (pass-through LLC). Crew 2 equipment: rent 3 months then buy, 80% financed at 9% over 60 months.</t>
+    <t xml:space="preserve">Revenue recognized in month of install; 30% deposit at signing, 90% of balance in month of completion, 10% the following month. Payroll burden 18% is an estimate - replace with actual workers' comp rate. No income tax modeled (pass-through LLC). Crew 2 equipment: Crew 1 already owns its trailer, skid steer and mini excavator; Crew 2's mini-ex and skid steer are rented for 3 months then bought (80% financed, 9%, 60 months); trailer, truck and tools bought at start.</t>
   </si>
 </sst>
 </file>
@@ -928,7 +1049,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1047,6 +1168,14 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1309,7 +1438,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C72"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -1863,7 +1992,7 @@
         <v>93</v>
       </c>
       <c r="B54" s="13" t="n">
-        <v>65000</v>
+        <v>50000</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>94</v>
@@ -1874,7 +2003,7 @@
         <v>95</v>
       </c>
       <c r="B55" s="14" t="n">
-        <v>35000</v>
+        <v>2000</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>96</v>
@@ -1884,8 +2013,8 @@
       <c r="A56" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B56" s="12" t="n">
-        <v>0.8</v>
+      <c r="B56" s="6" t="n">
+        <v>3</v>
       </c>
       <c r="C56" s="7" t="s">
         <v>98</v>
@@ -1895,8 +2024,8 @@
       <c r="A57" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B57" s="12" t="n">
-        <v>0.09</v>
+      <c r="B57" s="13" t="n">
+        <v>38000</v>
       </c>
       <c r="C57" s="7" t="s">
         <v>100</v>
@@ -1906,28 +2035,28 @@
       <c r="A58" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B58" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="C58" s="7"/>
+      <c r="B58" s="14" t="n">
+        <v>1700</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B59" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>103</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="C59" s="7"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
         <v>104</v>
       </c>
       <c r="B60" s="14" t="n">
-        <v>2000</v>
+        <v>9500</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>105</v>
@@ -1938,10 +2067,119 @@
         <v>106</v>
       </c>
       <c r="B61" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="C61" s="7"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B62" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B63" s="14" t="n">
+        <v>35000</v>
+      </c>
+      <c r="C63" s="7"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B64" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B65" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="7"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B66" s="14" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B67" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="7"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B68" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" s="7"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B69" s="12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B70" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B71" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="C71" s="7"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B72" s="14" t="n">
         <v>4500</v>
       </c>
-      <c r="C61" s="7" t="s">
-        <v>107</v>
+      <c r="C72" s="7" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -1970,7 +2208,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2002,7 +2240,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2064,7 +2302,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="B4" s="16" t="n">
         <v>1</v>
@@ -2139,18 +2377,18 @@
         <v>24</v>
       </c>
       <c r="Z4" s="15" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="AA4" s="15" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="AB4" s="15" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -2182,7 +2420,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="B6" s="18" t="n">
         <f aca="false">MIN(Assumptions!$B$7,Assumptions!$B$6+(Assumptions!$B$7-Assumptions!$B$6)*(1-1)/5)</f>
@@ -2295,7 +2533,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="B7" s="18" t="n">
         <f aca="false">IF(1&lt;Assumptions!$B$8,0,MIN(Assumptions!$B$10,Assumptions!$B$9+(Assumptions!$B$10-Assumptions!$B$9)*(1-Assumptions!$B$8)/3))</f>
@@ -2408,7 +2646,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B8" s="19" t="n">
         <f aca="false">B6+B7</f>
@@ -2521,7 +2759,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -2553,7 +2791,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="B10" s="18" t="n">
         <f aca="false">Assumptions!$B$34*IF(1&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$35</f>
@@ -2666,7 +2904,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="B11" s="18" t="n">
         <f aca="false">IF(1&gt;=2,Assumptions!$B$37*IF(1&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$38,0)</f>
@@ -2779,7 +3017,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="B12" s="18" t="n">
         <f aca="false">Assumptions!$B$40*(1+Assumptions!$B$41)^(1-1)</f>
@@ -2892,7 +3130,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="B13" s="19" t="n">
         <f aca="false">B10+B11+B12</f>
@@ -3005,7 +3243,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="B14" s="18" t="n">
         <f aca="false">B10*Assumptions!$B$36+B11*Assumptions!$B$39+B12*Assumptions!$B$42</f>
@@ -3118,7 +3356,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="B15" s="18" t="n">
         <f aca="false">B14*Assumptions!$B$11</f>
@@ -3231,7 +3469,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="B16" s="19" t="n">
         <f aca="false">MIN(B15+0,B8)</f>
@@ -3344,7 +3582,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="B17" s="18" t="n">
         <f aca="false">MIN(B8*Assumptions!$B$12,MAX(0,B15+0-B16))</f>
@@ -3448,7 +3686,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="B18" s="20" t="n">
         <f aca="false">IF(B8=0,0,B16/B8)</f>
@@ -3552,7 +3790,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -3584,7 +3822,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="B20" s="21" t="n">
         <f aca="false">B16*Assumptions!$B$5</f>
@@ -3697,7 +3935,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="B21" s="18" t="n">
         <f aca="false">IF(1&lt;Assumptions!$B$26,0,B16/Assumptions!$B$11*Assumptions!$B$23+IF(1&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
@@ -3810,7 +4048,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="B22" s="18" t="n">
         <f aca="false">0+B21</f>
@@ -3914,7 +4152,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="B23" s="21" t="n">
         <f aca="false">B22/12/Assumptions!$B$22*Assumptions!$B$21</f>
@@ -4027,7 +4265,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="B24" s="22" t="n">
         <f aca="false">B20+B23</f>
@@ -4140,7 +4378,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -4172,7 +4410,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="17" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="B26" s="21" t="n">
         <f aca="false">B20*Assumptions!$B$14</f>
@@ -4285,7 +4523,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="17" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="B27" s="21" t="n">
         <f aca="false">B20*Assumptions!$B$15</f>
@@ -4398,7 +4636,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="17" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="B28" s="21" t="n">
         <f aca="false">B22/12/Assumptions!$B$22*Assumptions!$B$27</f>
@@ -4511,7 +4749,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="B29" s="22" t="n">
         <f aca="false">B26+B27+B28</f>
@@ -4624,7 +4862,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="B30" s="23" t="n">
         <f aca="false">B24-B29</f>
@@ -4737,7 +4975,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="17" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="B31" s="20" t="n">
         <f aca="false">IF(B24=0,0,B30/B24)</f>
@@ -4841,7 +5079,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -4873,7 +5111,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="17" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="B33" s="21" t="n">
         <f aca="false">Assumptions!$B$46</f>
@@ -4986,7 +5224,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="17" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="B34" s="21" t="n">
         <f aca="false">Assumptions!$B$47</f>
@@ -5099,7 +5337,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="17" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="B35" s="21" t="n">
         <f aca="false">Assumptions!$B$48</f>
@@ -5212,7 +5450,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="17" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="B36" s="21" t="n">
         <f aca="false">Assumptions!$B$49</f>
@@ -5325,7 +5563,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="17" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="B37" s="21" t="n">
         <f aca="false">Assumptions!$B$50</f>
@@ -5438,7 +5676,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="17" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="B38" s="21" t="n">
         <f aca="false">Assumptions!$B$51</f>
@@ -5551,7 +5789,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="17" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="B39" s="21" t="n">
         <f aca="false">Assumptions!$B$52</f>
@@ -5664,7 +5902,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="17" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="B40" s="21" t="n">
         <f aca="false">Assumptions!$B$34*IF(1&gt;=Assumptions!$B$8,Assumptions!$B$43,1)</f>
@@ -5777,7 +6015,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="17" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="B41" s="21" t="n">
         <f aca="false">IF(1&gt;=2,Assumptions!$B$37*IF(1&gt;=Assumptions!$B$8,Assumptions!$B$43,1),0)</f>
@@ -5890,7 +6128,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="17" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="B42" s="21" t="n">
         <f aca="false">Assumptions!$B$44</f>
@@ -6003,107 +6241,107 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="17" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="B43" s="21" t="n">
-        <f aca="false">IF(AND(Assumptions!$B$59=1,1&gt;=Assumptions!$B$8,1&lt;Assumptions!$B$8+3),Assumptions!$B$60,0)+IF(1=Assumptions!$B$8,Assumptions!$B$61,0)</f>
+        <f aca="false">IF(AND(1&gt;=Assumptions!$B$8,1&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(1&gt;=Assumptions!$B$8,1&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(1&gt;=Assumptions!$B$8,1&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(1&gt;=Assumptions!$B$8,1&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(1&gt;=Assumptions!$B$8,1&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(1=Assumptions!$B$8,Assumptions!$B$72,0)</f>
         <v>0</v>
       </c>
       <c r="C43" s="21" t="n">
-        <f aca="false">IF(AND(Assumptions!$B$59=1,2&gt;=Assumptions!$B$8,2&lt;Assumptions!$B$8+3),Assumptions!$B$60,0)+IF(2=Assumptions!$B$8,Assumptions!$B$61,0)</f>
+        <f aca="false">IF(AND(2&gt;=Assumptions!$B$8,2&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(2&gt;=Assumptions!$B$8,2&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(2&gt;=Assumptions!$B$8,2&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(2&gt;=Assumptions!$B$8,2&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(2&gt;=Assumptions!$B$8,2&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(2=Assumptions!$B$8,Assumptions!$B$72,0)</f>
         <v>0</v>
       </c>
       <c r="D43" s="21" t="n">
-        <f aca="false">IF(AND(Assumptions!$B$59=1,3&gt;=Assumptions!$B$8,3&lt;Assumptions!$B$8+3),Assumptions!$B$60,0)+IF(3=Assumptions!$B$8,Assumptions!$B$61,0)</f>
+        <f aca="false">IF(AND(3&gt;=Assumptions!$B$8,3&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(3&gt;=Assumptions!$B$8,3&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(3&gt;=Assumptions!$B$8,3&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(3&gt;=Assumptions!$B$8,3&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(3&gt;=Assumptions!$B$8,3&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(3=Assumptions!$B$8,Assumptions!$B$72,0)</f>
         <v>0</v>
       </c>
       <c r="E43" s="21" t="n">
-        <f aca="false">IF(AND(Assumptions!$B$59=1,4&gt;=Assumptions!$B$8,4&lt;Assumptions!$B$8+3),Assumptions!$B$60,0)+IF(4=Assumptions!$B$8,Assumptions!$B$61,0)</f>
+        <f aca="false">IF(AND(4&gt;=Assumptions!$B$8,4&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(4&gt;=Assumptions!$B$8,4&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(4&gt;=Assumptions!$B$8,4&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(4&gt;=Assumptions!$B$8,4&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(4&gt;=Assumptions!$B$8,4&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(4=Assumptions!$B$8,Assumptions!$B$72,0)</f>
         <v>0</v>
       </c>
       <c r="F43" s="21" t="n">
-        <f aca="false">IF(AND(Assumptions!$B$59=1,5&gt;=Assumptions!$B$8,5&lt;Assumptions!$B$8+3),Assumptions!$B$60,0)+IF(5=Assumptions!$B$8,Assumptions!$B$61,0)</f>
+        <f aca="false">IF(AND(5&gt;=Assumptions!$B$8,5&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(5&gt;=Assumptions!$B$8,5&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(5&gt;=Assumptions!$B$8,5&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(5&gt;=Assumptions!$B$8,5&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(5&gt;=Assumptions!$B$8,5&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(5=Assumptions!$B$8,Assumptions!$B$72,0)</f>
         <v>0</v>
       </c>
       <c r="G43" s="21" t="n">
-        <f aca="false">IF(AND(Assumptions!$B$59=1,6&gt;=Assumptions!$B$8,6&lt;Assumptions!$B$8+3),Assumptions!$B$60,0)+IF(6=Assumptions!$B$8,Assumptions!$B$61,0)</f>
+        <f aca="false">IF(AND(6&gt;=Assumptions!$B$8,6&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(6&gt;=Assumptions!$B$8,6&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(6&gt;=Assumptions!$B$8,6&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(6&gt;=Assumptions!$B$8,6&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(6&gt;=Assumptions!$B$8,6&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(6=Assumptions!$B$8,Assumptions!$B$72,0)</f>
         <v>0</v>
       </c>
       <c r="H43" s="21" t="n">
-        <f aca="false">IF(AND(Assumptions!$B$59=1,7&gt;=Assumptions!$B$8,7&lt;Assumptions!$B$8+3),Assumptions!$B$60,0)+IF(7=Assumptions!$B$8,Assumptions!$B$61,0)</f>
-        <v>6500</v>
+        <f aca="false">IF(AND(7&gt;=Assumptions!$B$8,7&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(7&gt;=Assumptions!$B$8,7&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(7&gt;=Assumptions!$B$8,7&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(7&gt;=Assumptions!$B$8,7&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(7&gt;=Assumptions!$B$8,7&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(7=Assumptions!$B$8,Assumptions!$B$72,0)</f>
+        <v>8200</v>
       </c>
       <c r="I43" s="21" t="n">
-        <f aca="false">IF(AND(Assumptions!$B$59=1,8&gt;=Assumptions!$B$8,8&lt;Assumptions!$B$8+3),Assumptions!$B$60,0)+IF(8=Assumptions!$B$8,Assumptions!$B$61,0)</f>
-        <v>2000</v>
+        <f aca="false">IF(AND(8&gt;=Assumptions!$B$8,8&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(8&gt;=Assumptions!$B$8,8&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(8&gt;=Assumptions!$B$8,8&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(8&gt;=Assumptions!$B$8,8&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(8&gt;=Assumptions!$B$8,8&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(8=Assumptions!$B$8,Assumptions!$B$72,0)</f>
+        <v>3700</v>
       </c>
       <c r="J43" s="21" t="n">
-        <f aca="false">IF(AND(Assumptions!$B$59=1,9&gt;=Assumptions!$B$8,9&lt;Assumptions!$B$8+3),Assumptions!$B$60,0)+IF(9=Assumptions!$B$8,Assumptions!$B$61,0)</f>
-        <v>2000</v>
+        <f aca="false">IF(AND(9&gt;=Assumptions!$B$8,9&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(9&gt;=Assumptions!$B$8,9&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(9&gt;=Assumptions!$B$8,9&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(9&gt;=Assumptions!$B$8,9&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(9&gt;=Assumptions!$B$8,9&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(9=Assumptions!$B$8,Assumptions!$B$72,0)</f>
+        <v>3700</v>
       </c>
       <c r="K43" s="21" t="n">
-        <f aca="false">IF(AND(Assumptions!$B$59=1,10&gt;=Assumptions!$B$8,10&lt;Assumptions!$B$8+3),Assumptions!$B$60,0)+IF(10=Assumptions!$B$8,Assumptions!$B$61,0)</f>
+        <f aca="false">IF(AND(10&gt;=Assumptions!$B$8,10&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(10&gt;=Assumptions!$B$8,10&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(10&gt;=Assumptions!$B$8,10&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(10&gt;=Assumptions!$B$8,10&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(10&gt;=Assumptions!$B$8,10&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(10=Assumptions!$B$8,Assumptions!$B$72,0)</f>
         <v>0</v>
       </c>
       <c r="L43" s="21" t="n">
-        <f aca="false">IF(AND(Assumptions!$B$59=1,11&gt;=Assumptions!$B$8,11&lt;Assumptions!$B$8+3),Assumptions!$B$60,0)+IF(11=Assumptions!$B$8,Assumptions!$B$61,0)</f>
+        <f aca="false">IF(AND(11&gt;=Assumptions!$B$8,11&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(11&gt;=Assumptions!$B$8,11&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(11&gt;=Assumptions!$B$8,11&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(11&gt;=Assumptions!$B$8,11&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(11&gt;=Assumptions!$B$8,11&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(11=Assumptions!$B$8,Assumptions!$B$72,0)</f>
         <v>0</v>
       </c>
       <c r="M43" s="21" t="n">
-        <f aca="false">IF(AND(Assumptions!$B$59=1,12&gt;=Assumptions!$B$8,12&lt;Assumptions!$B$8+3),Assumptions!$B$60,0)+IF(12=Assumptions!$B$8,Assumptions!$B$61,0)</f>
+        <f aca="false">IF(AND(12&gt;=Assumptions!$B$8,12&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(12&gt;=Assumptions!$B$8,12&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(12&gt;=Assumptions!$B$8,12&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(12&gt;=Assumptions!$B$8,12&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(12&gt;=Assumptions!$B$8,12&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(12=Assumptions!$B$8,Assumptions!$B$72,0)</f>
         <v>0</v>
       </c>
       <c r="N43" s="21" t="n">
-        <f aca="false">IF(AND(Assumptions!$B$59=1,13&gt;=Assumptions!$B$8,13&lt;Assumptions!$B$8+3),Assumptions!$B$60,0)+IF(13=Assumptions!$B$8,Assumptions!$B$61,0)</f>
+        <f aca="false">IF(AND(13&gt;=Assumptions!$B$8,13&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(13&gt;=Assumptions!$B$8,13&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(13&gt;=Assumptions!$B$8,13&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(13&gt;=Assumptions!$B$8,13&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(13&gt;=Assumptions!$B$8,13&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(13=Assumptions!$B$8,Assumptions!$B$72,0)</f>
         <v>0</v>
       </c>
       <c r="O43" s="21" t="n">
-        <f aca="false">IF(AND(Assumptions!$B$59=1,14&gt;=Assumptions!$B$8,14&lt;Assumptions!$B$8+3),Assumptions!$B$60,0)+IF(14=Assumptions!$B$8,Assumptions!$B$61,0)</f>
+        <f aca="false">IF(AND(14&gt;=Assumptions!$B$8,14&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(14&gt;=Assumptions!$B$8,14&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(14&gt;=Assumptions!$B$8,14&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(14&gt;=Assumptions!$B$8,14&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(14&gt;=Assumptions!$B$8,14&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(14=Assumptions!$B$8,Assumptions!$B$72,0)</f>
         <v>0</v>
       </c>
       <c r="P43" s="21" t="n">
-        <f aca="false">IF(AND(Assumptions!$B$59=1,15&gt;=Assumptions!$B$8,15&lt;Assumptions!$B$8+3),Assumptions!$B$60,0)+IF(15=Assumptions!$B$8,Assumptions!$B$61,0)</f>
+        <f aca="false">IF(AND(15&gt;=Assumptions!$B$8,15&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(15&gt;=Assumptions!$B$8,15&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(15&gt;=Assumptions!$B$8,15&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(15&gt;=Assumptions!$B$8,15&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(15&gt;=Assumptions!$B$8,15&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(15=Assumptions!$B$8,Assumptions!$B$72,0)</f>
         <v>0</v>
       </c>
       <c r="Q43" s="21" t="n">
-        <f aca="false">IF(AND(Assumptions!$B$59=1,16&gt;=Assumptions!$B$8,16&lt;Assumptions!$B$8+3),Assumptions!$B$60,0)+IF(16=Assumptions!$B$8,Assumptions!$B$61,0)</f>
+        <f aca="false">IF(AND(16&gt;=Assumptions!$B$8,16&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(16&gt;=Assumptions!$B$8,16&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(16&gt;=Assumptions!$B$8,16&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(16&gt;=Assumptions!$B$8,16&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(16&gt;=Assumptions!$B$8,16&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(16=Assumptions!$B$8,Assumptions!$B$72,0)</f>
         <v>0</v>
       </c>
       <c r="R43" s="21" t="n">
-        <f aca="false">IF(AND(Assumptions!$B$59=1,17&gt;=Assumptions!$B$8,17&lt;Assumptions!$B$8+3),Assumptions!$B$60,0)+IF(17=Assumptions!$B$8,Assumptions!$B$61,0)</f>
+        <f aca="false">IF(AND(17&gt;=Assumptions!$B$8,17&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(17&gt;=Assumptions!$B$8,17&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(17&gt;=Assumptions!$B$8,17&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(17&gt;=Assumptions!$B$8,17&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(17&gt;=Assumptions!$B$8,17&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(17=Assumptions!$B$8,Assumptions!$B$72,0)</f>
         <v>0</v>
       </c>
       <c r="S43" s="21" t="n">
-        <f aca="false">IF(AND(Assumptions!$B$59=1,18&gt;=Assumptions!$B$8,18&lt;Assumptions!$B$8+3),Assumptions!$B$60,0)+IF(18=Assumptions!$B$8,Assumptions!$B$61,0)</f>
+        <f aca="false">IF(AND(18&gt;=Assumptions!$B$8,18&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(18&gt;=Assumptions!$B$8,18&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(18&gt;=Assumptions!$B$8,18&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(18&gt;=Assumptions!$B$8,18&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(18&gt;=Assumptions!$B$8,18&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(18=Assumptions!$B$8,Assumptions!$B$72,0)</f>
         <v>0</v>
       </c>
       <c r="T43" s="21" t="n">
-        <f aca="false">IF(AND(Assumptions!$B$59=1,19&gt;=Assumptions!$B$8,19&lt;Assumptions!$B$8+3),Assumptions!$B$60,0)+IF(19=Assumptions!$B$8,Assumptions!$B$61,0)</f>
+        <f aca="false">IF(AND(19&gt;=Assumptions!$B$8,19&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(19&gt;=Assumptions!$B$8,19&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(19&gt;=Assumptions!$B$8,19&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(19&gt;=Assumptions!$B$8,19&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(19&gt;=Assumptions!$B$8,19&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(19=Assumptions!$B$8,Assumptions!$B$72,0)</f>
         <v>0</v>
       </c>
       <c r="U43" s="21" t="n">
-        <f aca="false">IF(AND(Assumptions!$B$59=1,20&gt;=Assumptions!$B$8,20&lt;Assumptions!$B$8+3),Assumptions!$B$60,0)+IF(20=Assumptions!$B$8,Assumptions!$B$61,0)</f>
+        <f aca="false">IF(AND(20&gt;=Assumptions!$B$8,20&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(20&gt;=Assumptions!$B$8,20&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(20&gt;=Assumptions!$B$8,20&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(20&gt;=Assumptions!$B$8,20&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(20&gt;=Assumptions!$B$8,20&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(20=Assumptions!$B$8,Assumptions!$B$72,0)</f>
         <v>0</v>
       </c>
       <c r="V43" s="21" t="n">
-        <f aca="false">IF(AND(Assumptions!$B$59=1,21&gt;=Assumptions!$B$8,21&lt;Assumptions!$B$8+3),Assumptions!$B$60,0)+IF(21=Assumptions!$B$8,Assumptions!$B$61,0)</f>
+        <f aca="false">IF(AND(21&gt;=Assumptions!$B$8,21&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(21&gt;=Assumptions!$B$8,21&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(21&gt;=Assumptions!$B$8,21&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(21&gt;=Assumptions!$B$8,21&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(21&gt;=Assumptions!$B$8,21&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(21=Assumptions!$B$8,Assumptions!$B$72,0)</f>
         <v>0</v>
       </c>
       <c r="W43" s="21" t="n">
-        <f aca="false">IF(AND(Assumptions!$B$59=1,22&gt;=Assumptions!$B$8,22&lt;Assumptions!$B$8+3),Assumptions!$B$60,0)+IF(22=Assumptions!$B$8,Assumptions!$B$61,0)</f>
+        <f aca="false">IF(AND(22&gt;=Assumptions!$B$8,22&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(22&gt;=Assumptions!$B$8,22&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(22&gt;=Assumptions!$B$8,22&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(22&gt;=Assumptions!$B$8,22&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(22&gt;=Assumptions!$B$8,22&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(22=Assumptions!$B$8,Assumptions!$B$72,0)</f>
         <v>0</v>
       </c>
       <c r="X43" s="21" t="n">
-        <f aca="false">IF(AND(Assumptions!$B$59=1,23&gt;=Assumptions!$B$8,23&lt;Assumptions!$B$8+3),Assumptions!$B$60,0)+IF(23=Assumptions!$B$8,Assumptions!$B$61,0)</f>
+        <f aca="false">IF(AND(23&gt;=Assumptions!$B$8,23&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(23&gt;=Assumptions!$B$8,23&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(23&gt;=Assumptions!$B$8,23&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(23&gt;=Assumptions!$B$8,23&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(23&gt;=Assumptions!$B$8,23&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(23=Assumptions!$B$8,Assumptions!$B$72,0)</f>
         <v>0</v>
       </c>
       <c r="Y43" s="21" t="n">
-        <f aca="false">IF(AND(Assumptions!$B$59=1,24&gt;=Assumptions!$B$8,24&lt;Assumptions!$B$8+3),Assumptions!$B$60,0)+IF(24=Assumptions!$B$8,Assumptions!$B$61,0)</f>
+        <f aca="false">IF(AND(24&gt;=Assumptions!$B$8,24&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(24&gt;=Assumptions!$B$8,24&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(24&gt;=Assumptions!$B$8,24&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(24&gt;=Assumptions!$B$8,24&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(24&gt;=Assumptions!$B$8,24&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(24=Assumptions!$B$8,Assumptions!$B$72,0)</f>
         <v>0</v>
       </c>
       <c r="Z43" s="21" t="n">
         <f aca="false">SUM(B43:M43)</f>
-        <v>10500</v>
+        <v>15600</v>
       </c>
       <c r="AA43" s="21" t="n">
         <f aca="false">SUM(N43:Y43)</f>
@@ -6111,125 +6349,125 @@
       </c>
       <c r="AB43" s="21" t="n">
         <f aca="false">SUM(B43:Y43)</f>
-        <v>10500</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="17" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="B44" s="21" t="n">
-        <f aca="false">IF(1&gt;=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),-PMT(Assumptions!$B$57/12,Assumptions!$B$58,(Assumptions!$B$54+Assumptions!$B$55)*Assumptions!$B$56),0)</f>
+        <f aca="false">IF(1&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(1&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(1&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(1&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(1&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
         <v>0</v>
       </c>
       <c r="C44" s="21" t="n">
-        <f aca="false">IF(2&gt;=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),-PMT(Assumptions!$B$57/12,Assumptions!$B$58,(Assumptions!$B$54+Assumptions!$B$55)*Assumptions!$B$56),0)</f>
+        <f aca="false">IF(2&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(2&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(2&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(2&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(2&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
         <v>0</v>
       </c>
       <c r="D44" s="21" t="n">
-        <f aca="false">IF(3&gt;=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),-PMT(Assumptions!$B$57/12,Assumptions!$B$58,(Assumptions!$B$54+Assumptions!$B$55)*Assumptions!$B$56),0)</f>
+        <f aca="false">IF(3&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(3&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(3&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(3&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(3&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
         <v>0</v>
       </c>
       <c r="E44" s="21" t="n">
-        <f aca="false">IF(4&gt;=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),-PMT(Assumptions!$B$57/12,Assumptions!$B$58,(Assumptions!$B$54+Assumptions!$B$55)*Assumptions!$B$56),0)</f>
+        <f aca="false">IF(4&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(4&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(4&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(4&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(4&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
         <v>0</v>
       </c>
       <c r="F44" s="21" t="n">
-        <f aca="false">IF(5&gt;=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),-PMT(Assumptions!$B$57/12,Assumptions!$B$58,(Assumptions!$B$54+Assumptions!$B$55)*Assumptions!$B$56),0)</f>
+        <f aca="false">IF(5&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(5&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(5&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(5&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(5&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
         <v>0</v>
       </c>
       <c r="G44" s="21" t="n">
-        <f aca="false">IF(6&gt;=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),-PMT(Assumptions!$B$57/12,Assumptions!$B$58,(Assumptions!$B$54+Assumptions!$B$55)*Assumptions!$B$56),0)</f>
+        <f aca="false">IF(6&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(6&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(6&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(6&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(6&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
         <v>0</v>
       </c>
       <c r="H44" s="21" t="n">
-        <f aca="false">IF(7&gt;=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),-PMT(Assumptions!$B$57/12,Assumptions!$B$58,(Assumptions!$B$54+Assumptions!$B$55)*Assumptions!$B$56),0)</f>
-        <v>0</v>
+        <f aca="false">IF(7&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(7&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(7&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(7&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(7&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
+        <v>838.637551144702</v>
       </c>
       <c r="I44" s="21" t="n">
-        <f aca="false">IF(8&gt;=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),-PMT(Assumptions!$B$57/12,Assumptions!$B$58,(Assumptions!$B$54+Assumptions!$B$55)*Assumptions!$B$56),0)</f>
-        <v>0</v>
+        <f aca="false">IF(8&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(8&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(8&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(8&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(8&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
+        <v>838.637551144702</v>
       </c>
       <c r="J44" s="21" t="n">
-        <f aca="false">IF(9&gt;=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),-PMT(Assumptions!$B$57/12,Assumptions!$B$58,(Assumptions!$B$54+Assumptions!$B$55)*Assumptions!$B$56),0)</f>
-        <v>0</v>
+        <f aca="false">IF(9&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(9&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(9&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(9&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(9&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
+        <v>838.637551144702</v>
       </c>
       <c r="K44" s="21" t="n">
-        <f aca="false">IF(10&gt;=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),-PMT(Assumptions!$B$57/12,Assumptions!$B$58,(Assumptions!$B$54+Assumptions!$B$55)*Assumptions!$B$56),0)</f>
-        <v>1660.66841810832</v>
+        <f aca="false">IF(10&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(10&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(10&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(10&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(10&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
+        <v>2300.02575908002</v>
       </c>
       <c r="L44" s="21" t="n">
-        <f aca="false">IF(11&gt;=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),-PMT(Assumptions!$B$57/12,Assumptions!$B$58,(Assumptions!$B$54+Assumptions!$B$55)*Assumptions!$B$56),0)</f>
-        <v>1660.66841810832</v>
+        <f aca="false">IF(11&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(11&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(11&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(11&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(11&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
+        <v>2300.02575908002</v>
       </c>
       <c r="M44" s="21" t="n">
-        <f aca="false">IF(12&gt;=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),-PMT(Assumptions!$B$57/12,Assumptions!$B$58,(Assumptions!$B$54+Assumptions!$B$55)*Assumptions!$B$56),0)</f>
-        <v>1660.66841810832</v>
+        <f aca="false">IF(12&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(12&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(12&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(12&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(12&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
+        <v>2300.02575908002</v>
       </c>
       <c r="N44" s="21" t="n">
-        <f aca="false">IF(13&gt;=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),-PMT(Assumptions!$B$57/12,Assumptions!$B$58,(Assumptions!$B$54+Assumptions!$B$55)*Assumptions!$B$56),0)</f>
-        <v>1660.66841810832</v>
+        <f aca="false">IF(13&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(13&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(13&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(13&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(13&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
+        <v>2300.02575908002</v>
       </c>
       <c r="O44" s="21" t="n">
-        <f aca="false">IF(14&gt;=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),-PMT(Assumptions!$B$57/12,Assumptions!$B$58,(Assumptions!$B$54+Assumptions!$B$55)*Assumptions!$B$56),0)</f>
-        <v>1660.66841810832</v>
+        <f aca="false">IF(14&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(14&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(14&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(14&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(14&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
+        <v>2300.02575908002</v>
       </c>
       <c r="P44" s="21" t="n">
-        <f aca="false">IF(15&gt;=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),-PMT(Assumptions!$B$57/12,Assumptions!$B$58,(Assumptions!$B$54+Assumptions!$B$55)*Assumptions!$B$56),0)</f>
-        <v>1660.66841810832</v>
+        <f aca="false">IF(15&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(15&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(15&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(15&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(15&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
+        <v>2300.02575908002</v>
       </c>
       <c r="Q44" s="21" t="n">
-        <f aca="false">IF(16&gt;=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),-PMT(Assumptions!$B$57/12,Assumptions!$B$58,(Assumptions!$B$54+Assumptions!$B$55)*Assumptions!$B$56),0)</f>
-        <v>1660.66841810832</v>
+        <f aca="false">IF(16&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(16&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(16&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(16&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(16&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
+        <v>2300.02575908002</v>
       </c>
       <c r="R44" s="21" t="n">
-        <f aca="false">IF(17&gt;=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),-PMT(Assumptions!$B$57/12,Assumptions!$B$58,(Assumptions!$B$54+Assumptions!$B$55)*Assumptions!$B$56),0)</f>
-        <v>1660.66841810832</v>
+        <f aca="false">IF(17&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(17&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(17&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(17&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(17&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
+        <v>2300.02575908002</v>
       </c>
       <c r="S44" s="21" t="n">
-        <f aca="false">IF(18&gt;=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),-PMT(Assumptions!$B$57/12,Assumptions!$B$58,(Assumptions!$B$54+Assumptions!$B$55)*Assumptions!$B$56),0)</f>
-        <v>1660.66841810832</v>
+        <f aca="false">IF(18&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(18&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(18&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(18&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(18&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
+        <v>2300.02575908002</v>
       </c>
       <c r="T44" s="21" t="n">
-        <f aca="false">IF(19&gt;=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),-PMT(Assumptions!$B$57/12,Assumptions!$B$58,(Assumptions!$B$54+Assumptions!$B$55)*Assumptions!$B$56),0)</f>
-        <v>1660.66841810832</v>
+        <f aca="false">IF(19&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(19&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(19&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(19&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(19&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
+        <v>2300.02575908002</v>
       </c>
       <c r="U44" s="21" t="n">
-        <f aca="false">IF(20&gt;=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),-PMT(Assumptions!$B$57/12,Assumptions!$B$58,(Assumptions!$B$54+Assumptions!$B$55)*Assumptions!$B$56),0)</f>
-        <v>1660.66841810832</v>
+        <f aca="false">IF(20&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(20&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(20&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(20&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(20&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
+        <v>2300.02575908002</v>
       </c>
       <c r="V44" s="21" t="n">
-        <f aca="false">IF(21&gt;=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),-PMT(Assumptions!$B$57/12,Assumptions!$B$58,(Assumptions!$B$54+Assumptions!$B$55)*Assumptions!$B$56),0)</f>
-        <v>1660.66841810832</v>
+        <f aca="false">IF(21&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(21&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(21&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(21&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(21&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
+        <v>2300.02575908002</v>
       </c>
       <c r="W44" s="21" t="n">
-        <f aca="false">IF(22&gt;=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),-PMT(Assumptions!$B$57/12,Assumptions!$B$58,(Assumptions!$B$54+Assumptions!$B$55)*Assumptions!$B$56),0)</f>
-        <v>1660.66841810832</v>
+        <f aca="false">IF(22&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(22&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(22&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(22&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(22&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
+        <v>2300.02575908002</v>
       </c>
       <c r="X44" s="21" t="n">
-        <f aca="false">IF(23&gt;=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),-PMT(Assumptions!$B$57/12,Assumptions!$B$58,(Assumptions!$B$54+Assumptions!$B$55)*Assumptions!$B$56),0)</f>
-        <v>1660.66841810832</v>
+        <f aca="false">IF(23&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(23&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(23&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(23&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(23&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
+        <v>2300.02575908002</v>
       </c>
       <c r="Y44" s="21" t="n">
-        <f aca="false">IF(24&gt;=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),-PMT(Assumptions!$B$57/12,Assumptions!$B$58,(Assumptions!$B$54+Assumptions!$B$55)*Assumptions!$B$56),0)</f>
-        <v>1660.66841810832</v>
+        <f aca="false">IF(24&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(24&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(24&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(24&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(24&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
+        <v>2300.02575908002</v>
       </c>
       <c r="Z44" s="21" t="n">
         <f aca="false">SUM(B44:M44)</f>
-        <v>4982.00525432496</v>
+        <v>9415.98993067418</v>
       </c>
       <c r="AA44" s="21" t="n">
         <f aca="false">SUM(N44:Y44)</f>
-        <v>19928.0210172999</v>
+        <v>27600.3091089603</v>
       </c>
       <c r="AB44" s="21" t="n">
         <f aca="false">SUM(B44:Y44)</f>
-        <v>24910.0262716248</v>
+        <v>37016.2990396345</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="B45" s="22" t="n">
         <f aca="false">SUM(B33:B44)</f>
@@ -6257,92 +6495,92 @@
       </c>
       <c r="H45" s="22" t="n">
         <f aca="false">SUM(H33:H44)</f>
-        <v>19100</v>
+        <v>21638.6375511447</v>
       </c>
       <c r="I45" s="22" t="n">
         <f aca="false">SUM(I33:I44)</f>
-        <v>14600</v>
+        <v>17138.6375511447</v>
       </c>
       <c r="J45" s="22" t="n">
         <f aca="false">SUM(J33:J44)</f>
-        <v>14600</v>
+        <v>17138.6375511447</v>
       </c>
       <c r="K45" s="22" t="n">
         <f aca="false">SUM(K33:K44)</f>
-        <v>14260.6684181083</v>
+        <v>14900.02575908</v>
       </c>
       <c r="L45" s="22" t="n">
         <f aca="false">SUM(L33:L44)</f>
-        <v>14260.6684181083</v>
+        <v>14900.02575908</v>
       </c>
       <c r="M45" s="22" t="n">
         <f aca="false">SUM(M33:M44)</f>
-        <v>14260.6684181083</v>
+        <v>14900.02575908</v>
       </c>
       <c r="N45" s="22" t="n">
         <f aca="false">SUM(N33:N44)</f>
-        <v>14260.6684181083</v>
+        <v>14900.02575908</v>
       </c>
       <c r="O45" s="22" t="n">
         <f aca="false">SUM(O33:O44)</f>
-        <v>14260.6684181083</v>
+        <v>14900.02575908</v>
       </c>
       <c r="P45" s="22" t="n">
         <f aca="false">SUM(P33:P44)</f>
-        <v>14260.6684181083</v>
+        <v>14900.02575908</v>
       </c>
       <c r="Q45" s="22" t="n">
         <f aca="false">SUM(Q33:Q44)</f>
-        <v>14260.6684181083</v>
+        <v>14900.02575908</v>
       </c>
       <c r="R45" s="22" t="n">
         <f aca="false">SUM(R33:R44)</f>
-        <v>14260.6684181083</v>
+        <v>14900.02575908</v>
       </c>
       <c r="S45" s="22" t="n">
         <f aca="false">SUM(S33:S44)</f>
-        <v>14260.6684181083</v>
+        <v>14900.02575908</v>
       </c>
       <c r="T45" s="22" t="n">
         <f aca="false">SUM(T33:T44)</f>
-        <v>14260.6684181083</v>
+        <v>14900.02575908</v>
       </c>
       <c r="U45" s="22" t="n">
         <f aca="false">SUM(U33:U44)</f>
-        <v>14260.6684181083</v>
+        <v>14900.02575908</v>
       </c>
       <c r="V45" s="22" t="n">
         <f aca="false">SUM(V33:V44)</f>
-        <v>14260.6684181083</v>
+        <v>14900.02575908</v>
       </c>
       <c r="W45" s="22" t="n">
         <f aca="false">SUM(W33:W44)</f>
-        <v>14260.6684181083</v>
+        <v>14900.02575908</v>
       </c>
       <c r="X45" s="22" t="n">
         <f aca="false">SUM(X33:X44)</f>
-        <v>14260.6684181083</v>
+        <v>14900.02575908</v>
       </c>
       <c r="Y45" s="22" t="n">
         <f aca="false">SUM(Y33:Y44)</f>
-        <v>14260.6684181083</v>
+        <v>14900.02575908</v>
       </c>
       <c r="Z45" s="23" t="n">
         <f aca="false">SUM(B45:M45)</f>
-        <v>160682.005254325</v>
+        <v>170215.989930674</v>
       </c>
       <c r="AA45" s="23" t="n">
         <f aca="false">SUM(N45:Y45)</f>
-        <v>171128.0210173</v>
+        <v>178800.30910896</v>
       </c>
       <c r="AB45" s="23" t="n">
         <f aca="false">SUM(B45:Y45)</f>
-        <v>331810.026271625</v>
+        <v>349016.299039634</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="B46" s="23" t="n">
         <f aca="false">B30-B45</f>
@@ -6370,92 +6608,92 @@
       </c>
       <c r="H46" s="23" t="n">
         <f aca="false">H30-H45</f>
-        <v>9539.26315171339</v>
+        <v>7000.62560056869</v>
       </c>
       <c r="I46" s="23" t="n">
         <f aca="false">I30-I45</f>
-        <v>16843.9523695909</v>
+        <v>14305.3148184462</v>
       </c>
       <c r="J46" s="23" t="n">
         <f aca="false">J30-J45</f>
-        <v>19655.8192149047</v>
+        <v>17117.18166376</v>
       </c>
       <c r="K46" s="23" t="n">
         <f aca="false">K30-K45</f>
-        <v>22814.147418697</v>
+        <v>22174.7900777253</v>
       </c>
       <c r="L46" s="23" t="n">
         <f aca="false">L30-L45</f>
-        <v>22944.270729785</v>
+        <v>22304.9133888133</v>
       </c>
       <c r="M46" s="23" t="n">
         <f aca="false">M30-M45</f>
-        <v>23073.5265521324</v>
+        <v>22434.1692111606</v>
       </c>
       <c r="N46" s="23" t="n">
         <f aca="false">N30-N45</f>
-        <v>23201.9206689974</v>
+        <v>22562.5633280257</v>
       </c>
       <c r="O46" s="23" t="n">
         <f aca="false">O30-O45</f>
-        <v>23329.4588250834</v>
+        <v>22690.1014841117</v>
       </c>
       <c r="P46" s="23" t="n">
         <f aca="false">P30-P45</f>
-        <v>23428.1779767954</v>
+        <v>22788.8206358237</v>
       </c>
       <c r="Q46" s="23" t="n">
         <f aca="false">Q30-Q45</f>
-        <v>23526.2390008294</v>
+        <v>22886.8816598577</v>
       </c>
       <c r="R46" s="23" t="n">
         <f aca="false">R30-R45</f>
-        <v>23623.6462847032</v>
+        <v>22984.2889437315</v>
       </c>
       <c r="S46" s="23" t="n">
         <f aca="false">S30-S45</f>
-        <v>23720.4041866844</v>
+        <v>23081.0468457127</v>
       </c>
       <c r="T46" s="23" t="n">
         <f aca="false">T30-T45</f>
-        <v>23816.5170359858</v>
+        <v>23177.1596950141</v>
       </c>
       <c r="U46" s="23" t="n">
         <f aca="false">U30-U45</f>
-        <v>23911.9891329585</v>
+        <v>23272.6317919868</v>
       </c>
       <c r="V46" s="23" t="n">
         <f aca="false">V30-V45</f>
-        <v>24006.8247492847</v>
+        <v>23367.467408313</v>
       </c>
       <c r="W46" s="23" t="n">
         <f aca="false">W30-W45</f>
-        <v>24101.0281281688</v>
+        <v>23461.6707871971</v>
       </c>
       <c r="X46" s="23" t="n">
         <f aca="false">X30-X45</f>
-        <v>24194.6034845269</v>
+        <v>23555.2461435552</v>
       </c>
       <c r="Y46" s="23" t="n">
         <f aca="false">Y30-Y45</f>
-        <v>24287.555005176</v>
+        <v>23648.1976642043</v>
       </c>
       <c r="Z46" s="23" t="n">
         <f aca="false">SUM(B46:M46)</f>
-        <v>139767.069179814</v>
+        <v>130233.084503465</v>
       </c>
       <c r="AA46" s="23" t="n">
         <f aca="false">SUM(N46:Y46)</f>
-        <v>285148.364479194</v>
+        <v>277476.076387534</v>
       </c>
       <c r="AB46" s="23" t="n">
         <f aca="false">SUM(B46:Y46)</f>
-        <v>424915.433659008</v>
+        <v>407709.160890998</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="17" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="B47" s="20" t="n">
         <f aca="false">IF(B24=0,0,B46/B24)</f>
@@ -6483,75 +6721,75 @@
       </c>
       <c r="H47" s="20" t="n">
         <f aca="false">IF(H24=0,0,H46/H24)</f>
-        <v>0.16065408613074</v>
+        <v>0.117899998177618</v>
       </c>
       <c r="I47" s="20" t="n">
         <f aca="false">IF(I24=0,0,I46/I24)</f>
-        <v>0.258580871133738</v>
+        <v>0.219608835647998</v>
       </c>
       <c r="J47" s="20" t="n">
         <f aca="false">IF(J24=0,0,J46/J24)</f>
-        <v>0.277184965371192</v>
+        <v>0.241385279079284</v>
       </c>
       <c r="K47" s="20" t="n">
         <f aca="false">IF(K24=0,0,K46/K24)</f>
-        <v>0.297467806527227</v>
+        <v>0.289131390429114</v>
       </c>
       <c r="L47" s="20" t="n">
         <f aca="false">IF(L24=0,0,L46/L24)</f>
-        <v>0.298460044457676</v>
+        <v>0.2901432571142</v>
       </c>
       <c r="M47" s="20" t="n">
         <f aca="false">IF(M24=0,0,M46/M24)</f>
-        <v>0.299441052278976</v>
+        <v>0.291143671532678</v>
       </c>
       <c r="N47" s="20" t="n">
         <f aca="false">IF(N24=0,0,N46/N24)</f>
-        <v>0.300410997994279</v>
+        <v>0.29213280501119</v>
       </c>
       <c r="O47" s="20" t="n">
         <f aca="false">IF(O24=0,0,O46/O24)</f>
-        <v>0.301370046328512</v>
+        <v>0.293110825533302</v>
       </c>
       <c r="P47" s="20" t="n">
         <f aca="false">IF(P24=0,0,P46/P24)</f>
-        <v>0.302109371629716</v>
+        <v>0.29386477639405</v>
       </c>
       <c r="Q47" s="20" t="n">
         <f aca="false">IF(Q24=0,0,Q46/Q24)</f>
-        <v>0.302841180355429</v>
+        <v>0.294611061984109</v>
       </c>
       <c r="R47" s="20" t="n">
         <f aca="false">IF(R24=0,0,R46/R24)</f>
-        <v>0.303565570431586</v>
+        <v>0.295349782166614</v>
       </c>
       <c r="S47" s="20" t="n">
         <f aca="false">IF(S24=0,0,S46/S24)</f>
-        <v>0.304282638137298</v>
+        <v>0.2960810351253</v>
       </c>
       <c r="T47" s="20" t="n">
         <f aca="false">IF(T24=0,0,T46/T24)</f>
-        <v>0.304992478139368</v>
+        <v>0.296804917399697</v>
       </c>
       <c r="U47" s="20" t="n">
         <f aca="false">IF(U24=0,0,U46/U24)</f>
-        <v>0.305695183525931</v>
+        <v>0.297521523919436</v>
       </c>
       <c r="V47" s="20" t="n">
         <f aca="false">IF(V24=0,0,V46/V24)</f>
-        <v>0.306390845839261</v>
+        <v>0.298230948037712</v>
       </c>
       <c r="W47" s="20" t="n">
         <f aca="false">IF(W24=0,0,W46/W24)</f>
-        <v>0.30707955510776</v>
+        <v>0.298933281563894</v>
       </c>
       <c r="X47" s="20" t="n">
         <f aca="false">IF(X24=0,0,X46/X24)</f>
-        <v>0.307761399877156</v>
+        <v>0.299628614795349</v>
       </c>
       <c r="Y47" s="20" t="n">
         <f aca="false">IF(Y24=0,0,Y46/Y24)</f>
-        <v>0.308436467240926</v>
+        <v>0.300317036548465</v>
       </c>
       <c r="Z47" s="2"/>
       <c r="AA47" s="2"/>
@@ -6559,7 +6797,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -6591,7 +6829,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="17" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="B49" s="21" t="n">
         <f aca="false">B20*Assumptions!$B$29+B20*(1-Assumptions!$B$29)*Assumptions!$B$30+0+B23</f>
@@ -6704,7 +6942,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="17" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="B50" s="21" t="n">
         <f aca="false">B29+B45</f>
@@ -6732,192 +6970,192 @@
       </c>
       <c r="H50" s="21" t="n">
         <f aca="false">H29+H45</f>
-        <v>49838.3934112846</v>
+        <v>52377.0309624293</v>
       </c>
       <c r="I50" s="21" t="n">
         <f aca="false">I29+I45</f>
-        <v>48296.0260663205</v>
+        <v>50834.6636174652</v>
       </c>
       <c r="J50" s="21" t="n">
         <f aca="false">J29+J45</f>
-        <v>51256.4656147672</v>
+        <v>53795.1031659119</v>
       </c>
       <c r="K50" s="21" t="n">
         <f aca="false">K29+K45</f>
-        <v>53880.3617621104</v>
+        <v>54519.7191030821</v>
       </c>
       <c r="L50" s="21" t="n">
         <f aca="false">L29+L45</f>
-        <v>53931.2479731504</v>
+        <v>54570.6053141221</v>
       </c>
       <c r="M50" s="21" t="n">
         <f aca="false">M29+M45</f>
-        <v>53981.7949427835</v>
+        <v>54621.1522837552</v>
       </c>
       <c r="N50" s="21" t="n">
         <f aca="false">N29+N45</f>
-        <v>54032.0049326189</v>
+        <v>54671.3622735907</v>
       </c>
       <c r="O50" s="21" t="n">
         <f aca="false">O29+O45</f>
-        <v>54081.8801891889</v>
+        <v>54721.2375301606</v>
       </c>
       <c r="P50" s="21" t="n">
         <f aca="false">P29+P45</f>
-        <v>54120.4854440483</v>
+        <v>54759.84278502</v>
       </c>
       <c r="Q50" s="21" t="n">
         <f aca="false">Q29+Q45</f>
-        <v>54158.8333305421</v>
+        <v>54798.1906715138</v>
       </c>
       <c r="R50" s="21" t="n">
         <f aca="false">R29+R45</f>
-        <v>54196.9255644592</v>
+        <v>54836.2829054309</v>
       </c>
       <c r="S50" s="21" t="n">
         <f aca="false">S29+S45</f>
-        <v>54234.7638501502</v>
+        <v>54874.1211911219</v>
       </c>
       <c r="T50" s="21" t="n">
         <f aca="false">T29+T45</f>
-        <v>54272.3498806032</v>
+        <v>54911.7072215749</v>
       </c>
       <c r="U50" s="21" t="n">
         <f aca="false">U29+U45</f>
-        <v>54309.6853375199</v>
+        <v>54949.0426784916</v>
       </c>
       <c r="V50" s="21" t="n">
         <f aca="false">V29+V45</f>
-        <v>54346.7718913905</v>
+        <v>54986.1292323622</v>
       </c>
       <c r="W50" s="21" t="n">
         <f aca="false">W29+W45</f>
-        <v>54383.6112015686</v>
+        <v>55022.9685425403</v>
       </c>
       <c r="X50" s="21" t="n">
         <f aca="false">X29+X45</f>
-        <v>54420.2049163456</v>
+        <v>55059.5622573173</v>
       </c>
       <c r="Y50" s="21" t="n">
         <f aca="false">Y29+Y45</f>
-        <v>54456.554673024</v>
+        <v>55095.9120139957</v>
       </c>
       <c r="Z50" s="21" t="n">
         <f aca="false">SUM(B50:M50)</f>
-        <v>482634.403077731</v>
+        <v>492168.38775408</v>
       </c>
       <c r="AA50" s="21" t="n">
         <f aca="false">SUM(N50:Y50)</f>
-        <v>651014.071211459</v>
+        <v>658686.35930312</v>
       </c>
       <c r="AB50" s="21" t="n">
         <f aca="false">SUM(B50:Y50)</f>
-        <v>1133648.47428919</v>
+        <v>1150854.7470572</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="17" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="B51" s="21" t="n">
-        <f aca="false">IF(1=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),(Assumptions!$B$54+Assumptions!$B$55)*(1-Assumptions!$B$56),0)</f>
+        <f aca="false">IF(1=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(1=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(1=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(1=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(1=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
         <v>0</v>
       </c>
       <c r="C51" s="21" t="n">
-        <f aca="false">IF(2=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),(Assumptions!$B$54+Assumptions!$B$55)*(1-Assumptions!$B$56),0)</f>
+        <f aca="false">IF(2=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(2=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(2=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(2=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(2=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
         <v>0</v>
       </c>
       <c r="D51" s="21" t="n">
-        <f aca="false">IF(3=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),(Assumptions!$B$54+Assumptions!$B$55)*(1-Assumptions!$B$56),0)</f>
+        <f aca="false">IF(3=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(3=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(3=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(3=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(3=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
         <v>0</v>
       </c>
       <c r="E51" s="21" t="n">
-        <f aca="false">IF(4=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),(Assumptions!$B$54+Assumptions!$B$55)*(1-Assumptions!$B$56),0)</f>
+        <f aca="false">IF(4=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(4=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(4=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(4=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(4=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
         <v>0</v>
       </c>
       <c r="F51" s="21" t="n">
-        <f aca="false">IF(5=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),(Assumptions!$B$54+Assumptions!$B$55)*(1-Assumptions!$B$56),0)</f>
+        <f aca="false">IF(5=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(5=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(5=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(5=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(5=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
         <v>0</v>
       </c>
       <c r="G51" s="21" t="n">
-        <f aca="false">IF(6=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),(Assumptions!$B$54+Assumptions!$B$55)*(1-Assumptions!$B$56),0)</f>
+        <f aca="false">IF(6=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(6=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(6=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(6=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(6=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
         <v>0</v>
       </c>
       <c r="H51" s="21" t="n">
-        <f aca="false">IF(7=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),(Assumptions!$B$54+Assumptions!$B$55)*(1-Assumptions!$B$56),0)</f>
-        <v>0</v>
+        <f aca="false">IF(7=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(7=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(7=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(7=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(7=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
+        <v>10100</v>
       </c>
       <c r="I51" s="21" t="n">
-        <f aca="false">IF(8=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),(Assumptions!$B$54+Assumptions!$B$55)*(1-Assumptions!$B$56),0)</f>
+        <f aca="false">IF(8=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(8=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(8=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(8=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(8=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
         <v>0</v>
       </c>
       <c r="J51" s="21" t="n">
-        <f aca="false">IF(9=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),(Assumptions!$B$54+Assumptions!$B$55)*(1-Assumptions!$B$56),0)</f>
+        <f aca="false">IF(9=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(9=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(9=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(9=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(9=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
         <v>0</v>
       </c>
       <c r="K51" s="21" t="n">
-        <f aca="false">IF(10=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),(Assumptions!$B$54+Assumptions!$B$55)*(1-Assumptions!$B$56),0)</f>
-        <v>20000</v>
+        <f aca="false">IF(10=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(10=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(10=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(10=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(10=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
+        <v>17600</v>
       </c>
       <c r="L51" s="21" t="n">
-        <f aca="false">IF(11=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),(Assumptions!$B$54+Assumptions!$B$55)*(1-Assumptions!$B$56),0)</f>
+        <f aca="false">IF(11=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(11=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(11=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(11=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(11=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
         <v>0</v>
       </c>
       <c r="M51" s="21" t="n">
-        <f aca="false">IF(12=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),(Assumptions!$B$54+Assumptions!$B$55)*(1-Assumptions!$B$56),0)</f>
+        <f aca="false">IF(12=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(12=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(12=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(12=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(12=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
         <v>0</v>
       </c>
       <c r="N51" s="21" t="n">
-        <f aca="false">IF(13=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),(Assumptions!$B$54+Assumptions!$B$55)*(1-Assumptions!$B$56),0)</f>
+        <f aca="false">IF(13=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(13=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(13=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(13=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(13=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
         <v>0</v>
       </c>
       <c r="O51" s="21" t="n">
-        <f aca="false">IF(14=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),(Assumptions!$B$54+Assumptions!$B$55)*(1-Assumptions!$B$56),0)</f>
+        <f aca="false">IF(14=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(14=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(14=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(14=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(14=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
         <v>0</v>
       </c>
       <c r="P51" s="21" t="n">
-        <f aca="false">IF(15=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),(Assumptions!$B$54+Assumptions!$B$55)*(1-Assumptions!$B$56),0)</f>
+        <f aca="false">IF(15=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(15=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(15=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(15=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(15=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
         <v>0</v>
       </c>
       <c r="Q51" s="21" t="n">
-        <f aca="false">IF(16=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),(Assumptions!$B$54+Assumptions!$B$55)*(1-Assumptions!$B$56),0)</f>
+        <f aca="false">IF(16=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(16=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(16=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(16=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(16=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
         <v>0</v>
       </c>
       <c r="R51" s="21" t="n">
-        <f aca="false">IF(17=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),(Assumptions!$B$54+Assumptions!$B$55)*(1-Assumptions!$B$56),0)</f>
+        <f aca="false">IF(17=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(17=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(17=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(17=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(17=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
         <v>0</v>
       </c>
       <c r="S51" s="21" t="n">
-        <f aca="false">IF(18=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),(Assumptions!$B$54+Assumptions!$B$55)*(1-Assumptions!$B$56),0)</f>
+        <f aca="false">IF(18=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(18=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(18=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(18=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(18=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
         <v>0</v>
       </c>
       <c r="T51" s="21" t="n">
-        <f aca="false">IF(19=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),(Assumptions!$B$54+Assumptions!$B$55)*(1-Assumptions!$B$56),0)</f>
+        <f aca="false">IF(19=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(19=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(19=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(19=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(19=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
         <v>0</v>
       </c>
       <c r="U51" s="21" t="n">
-        <f aca="false">IF(20=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),(Assumptions!$B$54+Assumptions!$B$55)*(1-Assumptions!$B$56),0)</f>
+        <f aca="false">IF(20=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(20=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(20=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(20=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(20=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
         <v>0</v>
       </c>
       <c r="V51" s="21" t="n">
-        <f aca="false">IF(21=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),(Assumptions!$B$54+Assumptions!$B$55)*(1-Assumptions!$B$56),0)</f>
+        <f aca="false">IF(21=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(21=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(21=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(21=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(21=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
         <v>0</v>
       </c>
       <c r="W51" s="21" t="n">
-        <f aca="false">IF(22=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),(Assumptions!$B$54+Assumptions!$B$55)*(1-Assumptions!$B$56),0)</f>
+        <f aca="false">IF(22=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(22=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(22=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(22=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(22=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
         <v>0</v>
       </c>
       <c r="X51" s="21" t="n">
-        <f aca="false">IF(23=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),(Assumptions!$B$54+Assumptions!$B$55)*(1-Assumptions!$B$56),0)</f>
+        <f aca="false">IF(23=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(23=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(23=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(23=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(23=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
         <v>0</v>
       </c>
       <c r="Y51" s="21" t="n">
-        <f aca="false">IF(24=Assumptions!$B$8+IF(Assumptions!$B$59=1,3,0),(Assumptions!$B$54+Assumptions!$B$55)*(1-Assumptions!$B$56),0)</f>
+        <f aca="false">IF(24=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(24=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(24=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(24=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(24=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
         <v>0</v>
       </c>
       <c r="Z51" s="21" t="n">
         <f aca="false">SUM(B51:M51)</f>
-        <v>20000</v>
+        <v>27700</v>
       </c>
       <c r="AA51" s="21" t="n">
         <f aca="false">SUM(N51:Y51)</f>
@@ -6925,12 +7163,12 @@
       </c>
       <c r="AB51" s="21" t="n">
         <f aca="false">SUM(B51:Y51)</f>
-        <v>20000</v>
+        <v>27700</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="15" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="B52" s="22" t="n">
         <f aca="false">B49-B50-B51</f>
@@ -6958,92 +7196,92 @@
       </c>
       <c r="H52" s="22" t="n">
         <f aca="false">H49-H50-H51</f>
-        <v>8069.26315171339</v>
+        <v>-4569.37439943131</v>
       </c>
       <c r="I52" s="22" t="n">
         <f aca="false">I49-I50-I51</f>
-        <v>16451.9523695909</v>
+        <v>13913.3148184462</v>
       </c>
       <c r="J52" s="22" t="n">
         <f aca="false">J49-J50-J51</f>
-        <v>19263.8192149047</v>
+        <v>16725.18166376</v>
       </c>
       <c r="K52" s="22" t="n">
         <f aca="false">K49-K50-K51</f>
-        <v>2422.14741869702</v>
+        <v>4182.79007772531</v>
       </c>
       <c r="L52" s="22" t="n">
         <f aca="false">L49-L50-L51</f>
-        <v>22944.270729785</v>
+        <v>22304.9133888133</v>
       </c>
       <c r="M52" s="22" t="n">
         <f aca="false">M49-M50-M51</f>
-        <v>23073.5265521324</v>
+        <v>22434.1692111606</v>
       </c>
       <c r="N52" s="22" t="n">
         <f aca="false">N49-N50-N51</f>
-        <v>23201.9206689974</v>
+        <v>22562.5633280257</v>
       </c>
       <c r="O52" s="22" t="n">
         <f aca="false">O49-O50-O51</f>
-        <v>23329.4588250834</v>
+        <v>22690.1014841117</v>
       </c>
       <c r="P52" s="22" t="n">
         <f aca="false">P49-P50-P51</f>
-        <v>23428.1779767954</v>
+        <v>22788.8206358237</v>
       </c>
       <c r="Q52" s="22" t="n">
         <f aca="false">Q49-Q50-Q51</f>
-        <v>23526.2390008294</v>
+        <v>22886.8816598577</v>
       </c>
       <c r="R52" s="22" t="n">
         <f aca="false">R49-R50-R51</f>
-        <v>23623.6462847032</v>
+        <v>22984.2889437315</v>
       </c>
       <c r="S52" s="22" t="n">
         <f aca="false">S49-S50-S51</f>
-        <v>23720.4041866844</v>
+        <v>23081.0468457127</v>
       </c>
       <c r="T52" s="22" t="n">
         <f aca="false">T49-T50-T51</f>
-        <v>23816.5170359858</v>
+        <v>23177.1596950141</v>
       </c>
       <c r="U52" s="22" t="n">
         <f aca="false">U49-U50-U51</f>
-        <v>23911.9891329585</v>
+        <v>23272.6317919868</v>
       </c>
       <c r="V52" s="22" t="n">
         <f aca="false">V49-V50-V51</f>
-        <v>24006.8247492847</v>
+        <v>23367.467408313</v>
       </c>
       <c r="W52" s="22" t="n">
         <f aca="false">W49-W50-W51</f>
-        <v>24101.0281281688</v>
+        <v>23461.6707871971</v>
       </c>
       <c r="X52" s="22" t="n">
         <f aca="false">X49-X50-X51</f>
-        <v>24194.6034845269</v>
+        <v>23555.2461435552</v>
       </c>
       <c r="Y52" s="22" t="n">
         <f aca="false">Y49-Y50-Y51</f>
-        <v>24287.555005176</v>
+        <v>23648.1976642043</v>
       </c>
       <c r="Z52" s="23" t="n">
         <f aca="false">SUM(B52:M52)</f>
-        <v>114475.069179814</v>
+        <v>97241.0845034648</v>
       </c>
       <c r="AA52" s="23" t="n">
         <f aca="false">SUM(N52:Y52)</f>
-        <v>285148.364479194</v>
+        <v>277476.076387534</v>
       </c>
       <c r="AB52" s="23" t="n">
         <f aca="false">SUM(B52:Y52)</f>
-        <v>399623.433659008</v>
+        <v>374717.160890998</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="B53" s="23" t="n">
         <f aca="false">Assumptions!$B$32+B52</f>
@@ -7071,75 +7309,75 @@
       </c>
       <c r="H53" s="23" t="n">
         <f aca="false">G53+H52</f>
-        <v>55319.3528947041</v>
+        <v>42680.7153435594</v>
       </c>
       <c r="I53" s="23" t="n">
         <f aca="false">H53+I52</f>
-        <v>71771.305264295</v>
+        <v>56594.0301620056</v>
       </c>
       <c r="J53" s="23" t="n">
         <f aca="false">I53+J52</f>
-        <v>91035.1244791997</v>
+        <v>73319.2118257656</v>
       </c>
       <c r="K53" s="23" t="n">
         <f aca="false">J53+K52</f>
-        <v>93457.2718978967</v>
+        <v>77502.0019034909</v>
       </c>
       <c r="L53" s="23" t="n">
         <f aca="false">K53+L52</f>
-        <v>116401.542627682</v>
+        <v>99806.9152923042</v>
       </c>
       <c r="M53" s="23" t="n">
         <f aca="false">L53+M52</f>
-        <v>139475.069179814</v>
+        <v>122241.084503465</v>
       </c>
       <c r="N53" s="23" t="n">
         <f aca="false">M53+N52</f>
-        <v>162676.989848811</v>
+        <v>144803.647831491</v>
       </c>
       <c r="O53" s="23" t="n">
         <f aca="false">N53+O52</f>
-        <v>186006.448673895</v>
+        <v>167493.749315602</v>
       </c>
       <c r="P53" s="23" t="n">
         <f aca="false">O53+P52</f>
-        <v>209434.62665069</v>
+        <v>190282.569951426</v>
       </c>
       <c r="Q53" s="23" t="n">
         <f aca="false">P53+Q52</f>
-        <v>232960.86565152</v>
+        <v>213169.451611284</v>
       </c>
       <c r="R53" s="23" t="n">
         <f aca="false">Q53+R52</f>
-        <v>256584.511936223</v>
+        <v>236153.740555015</v>
       </c>
       <c r="S53" s="23" t="n">
         <f aca="false">R53+S52</f>
-        <v>280304.916122907</v>
+        <v>259234.787400728</v>
       </c>
       <c r="T53" s="23" t="n">
         <f aca="false">S53+T52</f>
-        <v>304121.433158893</v>
+        <v>282411.947095742</v>
       </c>
       <c r="U53" s="23" t="n">
         <f aca="false">T53+U52</f>
-        <v>328033.422291852</v>
+        <v>305684.578887729</v>
       </c>
       <c r="V53" s="23" t="n">
         <f aca="false">U53+V52</f>
-        <v>352040.247041136</v>
+        <v>329052.046296042</v>
       </c>
       <c r="W53" s="23" t="n">
         <f aca="false">V53+W52</f>
-        <v>376141.275169305</v>
+        <v>352513.717083239</v>
       </c>
       <c r="X53" s="23" t="n">
         <f aca="false">W53+X52</f>
-        <v>400335.878653832</v>
+        <v>376068.963226794</v>
       </c>
       <c r="Y53" s="23" t="n">
         <f aca="false">X53+Y52</f>
-        <v>424623.433659008</v>
+        <v>399717.160890998</v>
       </c>
       <c r="Z53" s="2"/>
       <c r="AA53" s="2"/>
@@ -7147,7 +7385,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -7179,7 +7417,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="17" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="B55" s="21" t="n">
         <f aca="false">IF(B8=0,0,B20/IF(B7&gt;0,2,1))</f>
@@ -7283,7 +7521,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="17" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="B56" s="21" t="n">
         <f aca="false">IF(B13=0,0,(B40+B41+B42)/B13)</f>
@@ -7387,7 +7625,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="17" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="B57" s="21" t="n">
         <f aca="false">IF(B14=0,0,(B40+B41+B42)/B14)</f>
@@ -7491,7 +7729,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="17" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="B58" s="20" t="n">
         <f aca="false">IF(B24=0,0,B23/B24)</f>
@@ -7595,7 +7833,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="17" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="B59" s="18" t="n">
         <f aca="false">B45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
@@ -7623,75 +7861,75 @@
       </c>
       <c r="H59" s="18" t="n">
         <f aca="false">H45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>947.420634920635</v>
+        <v>1073.34511662424</v>
       </c>
       <c r="I59" s="18" t="n">
         <f aca="false">I45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>724.206349206349</v>
+        <v>850.130830909956</v>
       </c>
       <c r="J59" s="18" t="n">
         <f aca="false">J45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>724.206349206349</v>
+        <v>850.130830909956</v>
       </c>
       <c r="K59" s="18" t="n">
         <f aca="false">K45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>707.374425501405</v>
+        <v>739.088579319446</v>
       </c>
       <c r="L59" s="18" t="n">
         <f aca="false">L45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>707.374425501405</v>
+        <v>739.088579319446</v>
       </c>
       <c r="M59" s="18" t="n">
         <f aca="false">M45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>707.374425501405</v>
+        <v>739.088579319446</v>
       </c>
       <c r="N59" s="18" t="n">
         <f aca="false">N45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>707.374425501405</v>
+        <v>739.088579319446</v>
       </c>
       <c r="O59" s="18" t="n">
         <f aca="false">O45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>707.374425501405</v>
+        <v>739.088579319446</v>
       </c>
       <c r="P59" s="18" t="n">
         <f aca="false">P45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>707.374425501405</v>
+        <v>739.088579319446</v>
       </c>
       <c r="Q59" s="18" t="n">
         <f aca="false">Q45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>707.374425501405</v>
+        <v>739.088579319446</v>
       </c>
       <c r="R59" s="18" t="n">
         <f aca="false">R45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>707.374425501405</v>
+        <v>739.088579319446</v>
       </c>
       <c r="S59" s="18" t="n">
         <f aca="false">S45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>707.374425501405</v>
+        <v>739.088579319446</v>
       </c>
       <c r="T59" s="18" t="n">
         <f aca="false">T45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>707.374425501405</v>
+        <v>739.088579319446</v>
       </c>
       <c r="U59" s="18" t="n">
         <f aca="false">U45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>707.374425501405</v>
+        <v>739.088579319446</v>
       </c>
       <c r="V59" s="18" t="n">
         <f aca="false">V45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>707.374425501405</v>
+        <v>739.088579319446</v>
       </c>
       <c r="W59" s="18" t="n">
         <f aca="false">W45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>707.374425501405</v>
+        <v>739.088579319446</v>
       </c>
       <c r="X59" s="18" t="n">
         <f aca="false">X45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>707.374425501405</v>
+        <v>739.088579319446</v>
       </c>
       <c r="Y59" s="18" t="n">
         <f aca="false">Y45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>707.374425501405</v>
+        <v>739.088579319446</v>
       </c>
       <c r="Z59" s="2"/>
       <c r="AA59" s="2"/>
@@ -7723,21 +7961,21 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="B3" s="24" t="n">
         <f aca="false">Assumptions!$B$11</f>
@@ -7747,7 +7985,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="B4" s="25" t="n">
         <f aca="false">B3*Assumptions!$B$5</f>
@@ -7757,7 +7995,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="B5" s="25" t="n">
         <f aca="false">B4*Assumptions!$B$14</f>
@@ -7767,7 +8005,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="B6" s="25" t="n">
         <f aca="false">B4*Assumptions!$B$15</f>
@@ -7777,7 +8015,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="B7" s="21" t="n">
         <f aca="false">B4-B5-B6</f>
@@ -7787,7 +8025,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="B8" s="20" t="n">
         <f aca="false">B7/B4</f>
@@ -7797,7 +8035,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="B9" s="26" t="n">
         <f aca="false">B3/(Assumptions!$B$7/21)</f>
@@ -7807,14 +8045,14 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="B11" s="24" t="n">
         <f aca="false">Assumptions!$B$7</f>
@@ -7824,7 +8062,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="B12" s="25" t="n">
         <f aca="false">B11*Assumptions!$B$5</f>
@@ -7834,7 +8072,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="B13" s="25" t="n">
         <f aca="false">Assumptions!$B$18*Assumptions!$B$19*Assumptions!$B$16</f>
@@ -7844,7 +8082,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="B14" s="25" t="n">
         <f aca="false">B13*(1+Assumptions!$B$17)</f>
@@ -7854,19 +8092,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="B15" s="20" t="n">
         <f aca="false">B14/B12</f>
         <v>0.352178571428572</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="B16" s="25" t="n">
         <f aca="false">B12*(1-Assumptions!$B$14-Assumptions!$B$15)</f>
@@ -7876,14 +8114,14 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="B18" s="25" t="n">
         <f aca="false">Assumptions!$B$21</f>
@@ -7893,7 +8131,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="B19" s="25" t="n">
         <f aca="false">Assumptions!$B$27</f>
@@ -7903,7 +8141,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="B20" s="21" t="n">
         <f aca="false">B18-B19</f>
@@ -7913,7 +8151,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="B21" s="20" t="n">
         <f aca="false">B20/B18</f>
@@ -7923,7 +8161,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="B22" s="24" t="n">
         <f aca="false">5/Assumptions!$B$22</f>
@@ -7933,7 +8171,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="B23" s="21" t="n">
         <f aca="false">B20*B22</f>
@@ -7943,26 +8181,26 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="B24" s="21" t="n">
         <f aca="false">0.25*B4*(1-0.52)</f>
         <v>504</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="B26" s="25" t="n">
         <f aca="false">'Proforma 24 mo'!D45</f>
@@ -7972,7 +8210,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="B27" s="24" t="n">
         <f aca="false">B26/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
@@ -7982,7 +8220,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="B28" s="27" t="n">
         <f aca="false">B27/Assumptions!$B$7</f>
@@ -8015,7 +8253,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8023,7 +8261,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8038,18 +8276,18 @@
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="28"/>
       <c r="B4" s="28" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="B5" s="8" t="n">
         <v>700</v>
@@ -8063,7 +8301,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="B6" s="8" t="n">
         <v>1</v>
@@ -8077,7 +8315,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="B7" s="14" t="n">
         <v>38</v>
@@ -8091,7 +8329,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="B8" s="8" t="n">
         <v>40</v>
@@ -8105,7 +8343,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="B9" s="21" t="n">
         <f aca="false">B5*B6*B7</f>
@@ -8122,7 +8360,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="B10" s="21" t="n">
         <f aca="false">B8/12/Assumptions!$B$22*Assumptions!$B$21</f>
@@ -8139,7 +8377,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="B11" s="21" t="n">
         <f aca="false">B9+B10</f>
@@ -8156,7 +8394,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="B12" s="23" t="n">
         <f aca="false">B9*(1-Assumptions!$B$14-Assumptions!$B$15)+B10*(1-Assumptions!$B$27/Assumptions!$B$21)</f>
@@ -8173,7 +8411,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="B13" s="21" t="n">
         <f aca="false">IF(B6=1,'Proforma 24 mo'!D45,'Proforma 24 mo'!Y45)</f>
@@ -8181,16 +8419,16 @@
       </c>
       <c r="C13" s="21" t="n">
         <f aca="false">IF(C6=1,'Proforma 24 mo'!D45,'Proforma 24 mo'!Y45)</f>
-        <v>14260.6684181083</v>
+        <v>14900.02575908</v>
       </c>
       <c r="D13" s="21" t="n">
         <f aca="false">IF(D6=1,'Proforma 24 mo'!D45,'Proforma 24 mo'!Y45)</f>
-        <v>14260.6684181083</v>
+        <v>14900.02575908</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="B14" s="23" t="n">
         <f aca="false">B12-B13</f>
@@ -8198,16 +8436,16 @@
       </c>
       <c r="C14" s="23" t="n">
         <f aca="false">C12-C13</f>
-        <v>23369.8315818917</v>
+        <v>22730.47424092</v>
       </c>
       <c r="D14" s="23" t="n">
         <f aca="false">D12-D13</f>
-        <v>31987.664915225</v>
+        <v>31348.3075742533</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="B15" s="23" t="n">
         <f aca="false">B14*12</f>
@@ -8215,16 +8453,16 @@
       </c>
       <c r="C15" s="23" t="n">
         <f aca="false">C14*12</f>
-        <v>280437.9789827</v>
+        <v>272765.69089104</v>
       </c>
       <c r="D15" s="23" t="n">
         <f aca="false">D14*12</f>
-        <v>383851.9789827</v>
+        <v>376179.69089104</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="B16" s="20" t="n">
         <f aca="false">IF(B11=0,0,B14/B11)</f>
@@ -8232,16 +8470,16 @@
       </c>
       <c r="C16" s="20" t="n">
         <f aca="false">IF(C11=0,0,C14/C11)</f>
-        <v>0.301672721875518</v>
+        <v>0.293419488700681</v>
       </c>
       <c r="D16" s="20" t="n">
         <f aca="false">IF(D11=0,0,D14/D11)</f>
-        <v>0.337049311577104</v>
+        <v>0.33031249748963</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="B17" s="18" t="n">
         <f aca="false">B5*B6/Assumptions!$B$11/0.3</f>
@@ -8264,7 +8502,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="29" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -8272,7 +8510,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -8280,7 +8518,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -8288,7 +8526,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -8310,6 +8548,435 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="2" style="0" width="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>239</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="G4" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="H4" s="30" t="s">
+        <v>245</v>
+      </c>
+      <c r="I4" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="J4" s="30" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B5" s="25" t="n">
+        <f aca="false">Assumptions!$B$54</f>
+        <v>50000</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <f aca="false">Assumptions!$B$55</f>
+        <v>2000</v>
+      </c>
+      <c r="D5" s="24" t="n">
+        <f aca="false">Assumptions!$B$56</f>
+        <v>3</v>
+      </c>
+      <c r="E5" s="21" t="n">
+        <f aca="false">C5*D5</f>
+        <v>6000</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <f aca="false">Assumptions!$B$8+D5</f>
+        <v>10</v>
+      </c>
+      <c r="G5" s="21" t="n">
+        <f aca="false">B5*(1-Assumptions!$B$69)</f>
+        <v>10000</v>
+      </c>
+      <c r="H5" s="21" t="n">
+        <f aca="false">-PMT(Assumptions!$B$70/12,Assumptions!$B$71,B5*Assumptions!$B$69)</f>
+        <v>830.33420905416</v>
+      </c>
+      <c r="I5" s="18" t="n">
+        <f aca="false">F5+Assumptions!$B$71</f>
+        <v>70</v>
+      </c>
+      <c r="J5" s="18" t="n">
+        <f aca="false">IF(C5=0,"n/a",B5/C5)</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B6" s="25" t="n">
+        <f aca="false">Assumptions!$B$57</f>
+        <v>38000</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <f aca="false">Assumptions!$B$58</f>
+        <v>1700</v>
+      </c>
+      <c r="D6" s="24" t="n">
+        <f aca="false">Assumptions!$B$59</f>
+        <v>3</v>
+      </c>
+      <c r="E6" s="21" t="n">
+        <f aca="false">C6*D6</f>
+        <v>5100</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <f aca="false">Assumptions!$B$8+D6</f>
+        <v>10</v>
+      </c>
+      <c r="G6" s="21" t="n">
+        <f aca="false">B6*(1-Assumptions!$B$69)</f>
+        <v>7600</v>
+      </c>
+      <c r="H6" s="21" t="n">
+        <f aca="false">-PMT(Assumptions!$B$70/12,Assumptions!$B$71,B6*Assumptions!$B$69)</f>
+        <v>631.053998881162</v>
+      </c>
+      <c r="I6" s="18" t="n">
+        <f aca="false">F6+Assumptions!$B$71</f>
+        <v>70</v>
+      </c>
+      <c r="J6" s="18" t="n">
+        <f aca="false">IF(C6=0,"n/a",B6/C6)</f>
+        <v>22.3529411764706</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B7" s="25" t="n">
+        <f aca="false">Assumptions!$B$60</f>
+        <v>9500</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <f aca="false">Assumptions!$B$61</f>
+        <v>600</v>
+      </c>
+      <c r="D7" s="24" t="n">
+        <f aca="false">Assumptions!$B$62</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="21" t="n">
+        <f aca="false">C7*D7</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <f aca="false">Assumptions!$B$8+D7</f>
+        <v>7</v>
+      </c>
+      <c r="G7" s="21" t="n">
+        <f aca="false">B7*(1-Assumptions!$B$69)</f>
+        <v>1900</v>
+      </c>
+      <c r="H7" s="21" t="n">
+        <f aca="false">-PMT(Assumptions!$B$70/12,Assumptions!$B$71,B7*Assumptions!$B$69)</f>
+        <v>157.76349972029</v>
+      </c>
+      <c r="I7" s="18" t="n">
+        <f aca="false">F7+Assumptions!$B$71</f>
+        <v>67</v>
+      </c>
+      <c r="J7" s="18" t="n">
+        <f aca="false">IF(C7=0,"n/a",B7/C7)</f>
+        <v>15.8333333333333</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B8" s="25" t="n">
+        <f aca="false">Assumptions!$B$63</f>
+        <v>35000</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <f aca="false">Assumptions!$B$64</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="24" t="n">
+        <f aca="false">Assumptions!$B$65</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="21" t="n">
+        <f aca="false">C8*D8</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <f aca="false">Assumptions!$B$8+D8</f>
+        <v>7</v>
+      </c>
+      <c r="G8" s="21" t="n">
+        <f aca="false">B8*(1-Assumptions!$B$69)</f>
+        <v>7000</v>
+      </c>
+      <c r="H8" s="21" t="n">
+        <f aca="false">-PMT(Assumptions!$B$70/12,Assumptions!$B$71,B8*Assumptions!$B$69)</f>
+        <v>581.233946337912</v>
+      </c>
+      <c r="I8" s="18" t="n">
+        <f aca="false">F8+Assumptions!$B$71</f>
+        <v>67</v>
+      </c>
+      <c r="J8" s="18" t="str">
+        <f aca="false">IF(C8=0,"n/a",B8/C8)</f>
+        <v>n/a</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B9" s="25" t="n">
+        <f aca="false">Assumptions!$B$66</f>
+        <v>6000</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <f aca="false">Assumptions!$B$67</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="24" t="n">
+        <f aca="false">Assumptions!$B$68</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="21" t="n">
+        <f aca="false">C9*D9</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <f aca="false">Assumptions!$B$8+D9</f>
+        <v>7</v>
+      </c>
+      <c r="G9" s="21" t="n">
+        <f aca="false">B9*(1-Assumptions!$B$69)</f>
+        <v>1200</v>
+      </c>
+      <c r="H9" s="21" t="n">
+        <f aca="false">-PMT(Assumptions!$B$70/12,Assumptions!$B$71,B9*Assumptions!$B$69)</f>
+        <v>99.6401050864993</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <f aca="false">F9+Assumptions!$B$71</f>
+        <v>67</v>
+      </c>
+      <c r="J9" s="18" t="str">
+        <f aca="false">IF(C9=0,"n/a",B9/C9)</f>
+        <v>n/a</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="B10" s="23" t="n">
+        <f aca="false">SUM(B5:B9)</f>
+        <v>138500</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="23" t="n">
+        <f aca="false">SUM(E5:E9)</f>
+        <v>11100</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="23" t="n">
+        <f aca="false">SUM(G5:G9)</f>
+        <v>27700</v>
+      </c>
+      <c r="H10" s="23" t="n">
+        <f aca="false">SUM(H5:H9)</f>
+        <v>2300.02575908002</v>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="31" t="s">
+        <v>255</v>
+      </c>
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31"/>
+    </row>
+    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="31" t="s">
+        <v>256</v>
+      </c>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
+    </row>
+    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="31" t="s">
+        <v>257</v>
+      </c>
+      <c r="B15" s="31"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+    </row>
+    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="31" t="s">
+        <v>258</v>
+      </c>
+      <c r="B16" s="31"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
+    </row>
+    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="31" t="s">
+        <v>259</v>
+      </c>
+      <c r="B17" s="31"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A13:J13"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:J15"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A17:J17"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:B14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -8319,7 +8986,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="B1" s="2"/>
     </row>
@@ -8328,99 +8995,99 @@
       <c r="B2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="30" t="s">
-        <v>221</v>
-      </c>
-      <c r="B3" s="31" t="s">
-        <v>222</v>
+      <c r="A3" s="32" t="s">
+        <v>261</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="30" t="s">
-        <v>223</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>224</v>
+      <c r="A4" s="32" t="s">
+        <v>263</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="30" t="s">
-        <v>225</v>
-      </c>
-      <c r="B5" s="31" t="s">
-        <v>226</v>
+      <c r="A5" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="B5" s="33" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="30" t="s">
-        <v>227</v>
-      </c>
-      <c r="B6" s="31" t="s">
-        <v>228</v>
+      <c r="A6" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="30" t="s">
-        <v>229</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>230</v>
+      <c r="A7" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="B7" s="33" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="30" t="s">
-        <v>231</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>232</v>
+      <c r="A8" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="30" t="s">
-        <v>233</v>
-      </c>
-      <c r="B9" s="31" t="s">
-        <v>234</v>
+      <c r="A9" s="32" t="s">
+        <v>273</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="30" t="s">
-        <v>235</v>
-      </c>
-      <c r="B10" s="31" t="s">
-        <v>236</v>
+      <c r="A10" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="30" t="s">
-        <v>237</v>
-      </c>
-      <c r="B11" s="31" t="s">
-        <v>238</v>
+      <c r="A11" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="B12" s="31" t="s">
-        <v>240</v>
+      <c r="A12" s="32" t="s">
+        <v>279</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="B13" s="31" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="30" t="s">
-        <v>243</v>
-      </c>
-      <c r="B14" s="31" t="s">
-        <v>244</v>
+      <c r="A13" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="B14" s="33" t="s">
+        <v>284</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Scag-Scapes-Proforma.xlsx
+++ b/docs/Scag-Scapes-Proforma.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="291">
   <si>
     <t xml:space="preserve">Scag Scapes LLC - Growth Proforma - Assumptions</t>
   </si>
@@ -210,10 +210,10 @@
     <t xml:space="preserve">SearchLight Feb 2026, drain/sewer category.</t>
   </si>
   <si>
-    <t xml:space="preserve">Google LSA - lead-to-job close rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Book rate 39.5% x quote-to-sale; conservative 35% of leads become jobs.</t>
+    <t xml:space="preserve">Google LSA - leads that become an estimate visit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LSA book rate is 39.5% industry-wide (SearchLight); with 60-second text-back we assume half of leads book a visit.</t>
   </si>
   <si>
     <t xml:space="preserve">Facebook + Instagram - monthly budget ($)</t>
@@ -228,10 +228,10 @@
     <t xml:space="preserve">Middle of the landscaping range.</t>
   </si>
   <si>
-    <t xml:space="preserve">Meta - lead-to-job close rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lower intent than search; 60-second text-back is what makes these convert.</t>
+    <t xml:space="preserve">Meta - leads that become an estimate visit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lower intent than search; instant text-back is what gets them to book.</t>
   </si>
   <si>
     <t xml:space="preserve">Organic / referral / review leads per month (month 1)</t>
@@ -246,10 +246,19 @@
     <t xml:space="preserve">Review flywheel + parish pages + Facebook organic.</t>
   </si>
   <si>
-    <t xml:space="preserve">Organic / referral close rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warm leads.</t>
+    <t xml:space="preserve">Organic / referral - leads that become an estimate visit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warm leads book easily.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLOSE RATE - Charlie's number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Close rate on estimates run (quote -&gt; sold job)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charlie: about 7 of 10 quoted jobs sell. Change this one cell and every channel, the proforma and the scenarios move.</t>
   </si>
   <si>
     <t xml:space="preserve">Marketing budget multiplier once Crew 2 starts</t>
@@ -444,7 +453,10 @@
     <t xml:space="preserve">Total leads</t>
   </si>
   <si>
-    <t xml:space="preserve">Jobs sold (leads x close rate by channel)</t>
+    <t xml:space="preserve">Estimate visits booked (leads x booking rate by channel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobs sold (estimates x Charlie's close rate)</t>
   </si>
   <si>
     <t xml:space="preserve">LF demanded (jobs x average job LF)</t>
@@ -576,6 +588,9 @@
     <t xml:space="preserve">Marketing cost per job sold</t>
   </si>
   <si>
+    <t xml:space="preserve">Close rate in use (from Assumptions)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Maintenance share of revenue</t>
   </si>
   <si>
@@ -720,7 +735,10 @@
     <t xml:space="preserve">Operating margin</t>
   </si>
   <si>
-    <t xml:space="preserve">Leads needed per month (at 30% blended close, avg job LF)</t>
+    <t xml:space="preserve">Estimates needed per month (jobs / Charlie's close rate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leads needed per month (at ~45% of leads booking an estimate)</t>
   </si>
   <si>
     <t xml:space="preserve">What has to be true</t>
@@ -729,7 +747,7 @@
     <t xml:space="preserve">Conservative: one crew at 700 LF and $38/LF still clears overhead - the plan fails safe.</t>
   </si>
   <si>
-    <t xml:space="preserve">Base: two crews at 900 LF, $42/LF, 90 plan customers - Charlie's stated goal, reached in month 10-12 of the proforma.</t>
+    <t xml:space="preserve">Base: two crews at 900 LF, $42/LF, 90 plan customers - Charlie's stated goal, reached in month 10-12 of the proforma. Close rate on estimates is Charlie's 70% (Assumptions, yellow cell).</t>
   </si>
   <si>
     <t xml:space="preserve">Stretch: pricing power from reviews + Moasure proposals lifts $/LF to $46; 140 plan customers = the sellable recurring book.</t>
@@ -1438,7 +1456,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C72"/>
+  <dimension ref="A1:C74"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -1802,7 +1820,7 @@
         <v>61</v>
       </c>
       <c r="B36" s="12" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>62</v>
@@ -1835,7 +1853,7 @@
         <v>67</v>
       </c>
       <c r="B39" s="12" t="n">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>68</v>
@@ -1868,72 +1886,68 @@
         <v>73</v>
       </c>
       <c r="B42" s="12" t="n">
-        <v>0.45</v>
+        <v>0.65</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B43" s="6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>76</v>
-      </c>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B44" s="11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C44" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B44" s="14" t="n">
-        <v>300</v>
-      </c>
-      <c r="C44" s="7" t="s">
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="s">
+      <c r="B45" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C45" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B46" s="13" t="n">
-        <v>6000</v>
+      <c r="B46" s="14" t="n">
+        <v>300</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B47" s="14" t="n">
-        <v>900</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>83</v>
-      </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B48" s="13" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C48" s="7" t="s">
         <v>84</v>
-      </c>
-      <c r="B48" s="14" t="n">
-        <v>1800</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1941,7 +1955,7 @@
         <v>85</v>
       </c>
       <c r="B49" s="14" t="n">
-        <v>350</v>
+        <v>900</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>86</v>
@@ -1952,111 +1966,113 @@
         <v>87</v>
       </c>
       <c r="B50" s="14" t="n">
-        <v>250</v>
+        <v>1800</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B51" s="14" t="n">
+        <v>350</v>
+      </c>
+      <c r="C51" s="7" t="s">
         <v>89</v>
-      </c>
-      <c r="B51" s="14" t="n">
-        <v>600</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B52" s="6" t="n">
-        <v>0</v>
+      <c r="B52" s="14" t="n">
+        <v>250</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
+      <c r="B53" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B54" s="13" t="n">
-        <v>50000</v>
+      <c r="B54" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B55" s="14" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>96</v>
-      </c>
+      <c r="B55" s="5"/>
+      <c r="C55" s="5"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B56" s="13" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C56" s="7" t="s">
         <v>97</v>
-      </c>
-      <c r="B56" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B57" s="14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C57" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="B57" s="13" t="n">
-        <v>38000</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B58" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C58" s="7" t="s">
         <v>101</v>
-      </c>
-      <c r="B58" s="14" t="n">
-        <v>1700</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B59" s="13" t="n">
+        <v>38000</v>
+      </c>
+      <c r="C59" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B59" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C59" s="7"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
         <v>104</v>
       </c>
       <c r="B60" s="14" t="n">
-        <v>9500</v>
+        <v>1700</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>105</v>
@@ -2066,8 +2082,8 @@
       <c r="A61" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B61" s="14" t="n">
-        <v>600</v>
+      <c r="B61" s="6" t="n">
+        <v>3</v>
       </c>
       <c r="C61" s="7"/>
     </row>
@@ -2075,8 +2091,8 @@
       <c r="A62" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B62" s="10" t="n">
-        <v>0</v>
+      <c r="B62" s="14" t="n">
+        <v>9500</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>108</v>
@@ -2087,7 +2103,7 @@
         <v>109</v>
       </c>
       <c r="B63" s="14" t="n">
-        <v>35000</v>
+        <v>600</v>
       </c>
       <c r="C63" s="7"/>
     </row>
@@ -2106,8 +2122,8 @@
       <c r="A65" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B65" s="10" t="n">
-        <v>0</v>
+      <c r="B65" s="14" t="n">
+        <v>35000</v>
       </c>
       <c r="C65" s="7"/>
     </row>
@@ -2115,8 +2131,8 @@
       <c r="A66" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B66" s="14" t="n">
-        <v>6000</v>
+      <c r="B66" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="C66" s="7" t="s">
         <v>114</v>
@@ -2135,51 +2151,71 @@
       <c r="A68" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B68" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C68" s="7"/>
+      <c r="B68" s="14" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B69" s="12" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C69" s="7" t="s">
         <v>118</v>
       </c>
+      <c r="B69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="7"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B70" s="12" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>120</v>
-      </c>
+      <c r="B70" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="7"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B71" s="12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C71" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="B71" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="C71" s="7"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B72" s="14" t="n">
-        <v>4500</v>
+      <c r="B72" s="12" t="n">
+        <v>0.09</v>
       </c>
       <c r="C72" s="7" t="s">
         <v>123</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B73" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="C73" s="7"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B74" s="14" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -2198,7 +2234,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AB59"/>
+  <dimension ref="A1:AB61"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
@@ -2208,7 +2244,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2240,7 +2276,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2302,7 +2338,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B4" s="16" t="n">
         <v>1</v>
@@ -2377,18 +2413,18 @@
         <v>24</v>
       </c>
       <c r="Z4" s="15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="AA4" s="15" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="AB4" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -2420,7 +2456,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B6" s="18" t="n">
         <f aca="false">MIN(Assumptions!$B$7,Assumptions!$B$6+(Assumptions!$B$7-Assumptions!$B$6)*(1-1)/5)</f>
@@ -2533,7 +2569,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B7" s="18" t="n">
         <f aca="false">IF(1&lt;Assumptions!$B$8,0,MIN(Assumptions!$B$10,Assumptions!$B$9+(Assumptions!$B$10-Assumptions!$B$9)*(1-Assumptions!$B$8)/3))</f>
@@ -2646,7 +2682,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B8" s="19" t="n">
         <f aca="false">B6+B7</f>
@@ -2759,7 +2795,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -2791,102 +2827,102 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B10" s="18" t="n">
-        <f aca="false">Assumptions!$B$34*IF(1&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$35</f>
+        <f aca="false">Assumptions!$B$34*IF(1&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$35</f>
         <v>15.2542372881356</v>
       </c>
       <c r="C10" s="18" t="n">
-        <f aca="false">Assumptions!$B$34*IF(2&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$35</f>
+        <f aca="false">Assumptions!$B$34*IF(2&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$35</f>
         <v>15.2542372881356</v>
       </c>
       <c r="D10" s="18" t="n">
-        <f aca="false">Assumptions!$B$34*IF(3&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$35</f>
+        <f aca="false">Assumptions!$B$34*IF(3&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$35</f>
         <v>15.2542372881356</v>
       </c>
       <c r="E10" s="18" t="n">
-        <f aca="false">Assumptions!$B$34*IF(4&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$35</f>
+        <f aca="false">Assumptions!$B$34*IF(4&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$35</f>
         <v>15.2542372881356</v>
       </c>
       <c r="F10" s="18" t="n">
-        <f aca="false">Assumptions!$B$34*IF(5&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$35</f>
+        <f aca="false">Assumptions!$B$34*IF(5&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$35</f>
         <v>15.2542372881356</v>
       </c>
       <c r="G10" s="18" t="n">
-        <f aca="false">Assumptions!$B$34*IF(6&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$35</f>
+        <f aca="false">Assumptions!$B$34*IF(6&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$35</f>
         <v>15.2542372881356</v>
       </c>
       <c r="H10" s="18" t="n">
-        <f aca="false">Assumptions!$B$34*IF(7&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$35</f>
+        <f aca="false">Assumptions!$B$34*IF(7&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$35</f>
         <v>24.4067796610169</v>
       </c>
       <c r="I10" s="18" t="n">
-        <f aca="false">Assumptions!$B$34*IF(8&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$35</f>
+        <f aca="false">Assumptions!$B$34*IF(8&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$35</f>
         <v>24.4067796610169</v>
       </c>
       <c r="J10" s="18" t="n">
-        <f aca="false">Assumptions!$B$34*IF(9&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$35</f>
+        <f aca="false">Assumptions!$B$34*IF(9&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$35</f>
         <v>24.4067796610169</v>
       </c>
       <c r="K10" s="18" t="n">
-        <f aca="false">Assumptions!$B$34*IF(10&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$35</f>
+        <f aca="false">Assumptions!$B$34*IF(10&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$35</f>
         <v>24.4067796610169</v>
       </c>
       <c r="L10" s="18" t="n">
-        <f aca="false">Assumptions!$B$34*IF(11&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$35</f>
+        <f aca="false">Assumptions!$B$34*IF(11&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$35</f>
         <v>24.4067796610169</v>
       </c>
       <c r="M10" s="18" t="n">
-        <f aca="false">Assumptions!$B$34*IF(12&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$35</f>
+        <f aca="false">Assumptions!$B$34*IF(12&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$35</f>
         <v>24.4067796610169</v>
       </c>
       <c r="N10" s="18" t="n">
-        <f aca="false">Assumptions!$B$34*IF(13&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$35</f>
+        <f aca="false">Assumptions!$B$34*IF(13&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$35</f>
         <v>24.4067796610169</v>
       </c>
       <c r="O10" s="18" t="n">
-        <f aca="false">Assumptions!$B$34*IF(14&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$35</f>
+        <f aca="false">Assumptions!$B$34*IF(14&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$35</f>
         <v>24.4067796610169</v>
       </c>
       <c r="P10" s="18" t="n">
-        <f aca="false">Assumptions!$B$34*IF(15&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$35</f>
+        <f aca="false">Assumptions!$B$34*IF(15&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$35</f>
         <v>24.4067796610169</v>
       </c>
       <c r="Q10" s="18" t="n">
-        <f aca="false">Assumptions!$B$34*IF(16&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$35</f>
+        <f aca="false">Assumptions!$B$34*IF(16&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$35</f>
         <v>24.4067796610169</v>
       </c>
       <c r="R10" s="18" t="n">
-        <f aca="false">Assumptions!$B$34*IF(17&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$35</f>
+        <f aca="false">Assumptions!$B$34*IF(17&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$35</f>
         <v>24.4067796610169</v>
       </c>
       <c r="S10" s="18" t="n">
-        <f aca="false">Assumptions!$B$34*IF(18&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$35</f>
+        <f aca="false">Assumptions!$B$34*IF(18&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$35</f>
         <v>24.4067796610169</v>
       </c>
       <c r="T10" s="18" t="n">
-        <f aca="false">Assumptions!$B$34*IF(19&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$35</f>
+        <f aca="false">Assumptions!$B$34*IF(19&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$35</f>
         <v>24.4067796610169</v>
       </c>
       <c r="U10" s="18" t="n">
-        <f aca="false">Assumptions!$B$34*IF(20&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$35</f>
+        <f aca="false">Assumptions!$B$34*IF(20&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$35</f>
         <v>24.4067796610169</v>
       </c>
       <c r="V10" s="18" t="n">
-        <f aca="false">Assumptions!$B$34*IF(21&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$35</f>
+        <f aca="false">Assumptions!$B$34*IF(21&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$35</f>
         <v>24.4067796610169</v>
       </c>
       <c r="W10" s="18" t="n">
-        <f aca="false">Assumptions!$B$34*IF(22&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$35</f>
+        <f aca="false">Assumptions!$B$34*IF(22&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$35</f>
         <v>24.4067796610169</v>
       </c>
       <c r="X10" s="18" t="n">
-        <f aca="false">Assumptions!$B$34*IF(23&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$35</f>
+        <f aca="false">Assumptions!$B$34*IF(23&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$35</f>
         <v>24.4067796610169</v>
       </c>
       <c r="Y10" s="18" t="n">
-        <f aca="false">Assumptions!$B$34*IF(24&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$35</f>
+        <f aca="false">Assumptions!$B$34*IF(24&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$35</f>
         <v>24.4067796610169</v>
       </c>
       <c r="Z10" s="18" t="n">
@@ -2904,102 +2940,102 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B11" s="18" t="n">
-        <f aca="false">IF(1&gt;=2,Assumptions!$B$37*IF(1&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$38,0)</f>
+        <f aca="false">IF(1&gt;=2,Assumptions!$B$37*IF(1&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="C11" s="18" t="n">
-        <f aca="false">IF(2&gt;=2,Assumptions!$B$37*IF(2&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$38,0)</f>
+        <f aca="false">IF(2&gt;=2,Assumptions!$B$37*IF(2&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$38,0)</f>
         <v>10.9090909090909</v>
       </c>
       <c r="D11" s="18" t="n">
-        <f aca="false">IF(3&gt;=2,Assumptions!$B$37*IF(3&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$38,0)</f>
+        <f aca="false">IF(3&gt;=2,Assumptions!$B$37*IF(3&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$38,0)</f>
         <v>10.9090909090909</v>
       </c>
       <c r="E11" s="18" t="n">
-        <f aca="false">IF(4&gt;=2,Assumptions!$B$37*IF(4&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$38,0)</f>
+        <f aca="false">IF(4&gt;=2,Assumptions!$B$37*IF(4&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$38,0)</f>
         <v>10.9090909090909</v>
       </c>
       <c r="F11" s="18" t="n">
-        <f aca="false">IF(5&gt;=2,Assumptions!$B$37*IF(5&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$38,0)</f>
+        <f aca="false">IF(5&gt;=2,Assumptions!$B$37*IF(5&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$38,0)</f>
         <v>10.9090909090909</v>
       </c>
       <c r="G11" s="18" t="n">
-        <f aca="false">IF(6&gt;=2,Assumptions!$B$37*IF(6&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$38,0)</f>
+        <f aca="false">IF(6&gt;=2,Assumptions!$B$37*IF(6&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$38,0)</f>
         <v>10.9090909090909</v>
       </c>
       <c r="H11" s="18" t="n">
-        <f aca="false">IF(7&gt;=2,Assumptions!$B$37*IF(7&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$38,0)</f>
+        <f aca="false">IF(7&gt;=2,Assumptions!$B$37*IF(7&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$38,0)</f>
         <v>17.4545454545455</v>
       </c>
       <c r="I11" s="18" t="n">
-        <f aca="false">IF(8&gt;=2,Assumptions!$B$37*IF(8&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$38,0)</f>
+        <f aca="false">IF(8&gt;=2,Assumptions!$B$37*IF(8&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$38,0)</f>
         <v>17.4545454545455</v>
       </c>
       <c r="J11" s="18" t="n">
-        <f aca="false">IF(9&gt;=2,Assumptions!$B$37*IF(9&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$38,0)</f>
+        <f aca="false">IF(9&gt;=2,Assumptions!$B$37*IF(9&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$38,0)</f>
         <v>17.4545454545455</v>
       </c>
       <c r="K11" s="18" t="n">
-        <f aca="false">IF(10&gt;=2,Assumptions!$B$37*IF(10&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$38,0)</f>
+        <f aca="false">IF(10&gt;=2,Assumptions!$B$37*IF(10&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$38,0)</f>
         <v>17.4545454545455</v>
       </c>
       <c r="L11" s="18" t="n">
-        <f aca="false">IF(11&gt;=2,Assumptions!$B$37*IF(11&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$38,0)</f>
+        <f aca="false">IF(11&gt;=2,Assumptions!$B$37*IF(11&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$38,0)</f>
         <v>17.4545454545455</v>
       </c>
       <c r="M11" s="18" t="n">
-        <f aca="false">IF(12&gt;=2,Assumptions!$B$37*IF(12&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$38,0)</f>
+        <f aca="false">IF(12&gt;=2,Assumptions!$B$37*IF(12&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$38,0)</f>
         <v>17.4545454545455</v>
       </c>
       <c r="N11" s="18" t="n">
-        <f aca="false">IF(13&gt;=2,Assumptions!$B$37*IF(13&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$38,0)</f>
+        <f aca="false">IF(13&gt;=2,Assumptions!$B$37*IF(13&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$38,0)</f>
         <v>17.4545454545455</v>
       </c>
       <c r="O11" s="18" t="n">
-        <f aca="false">IF(14&gt;=2,Assumptions!$B$37*IF(14&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$38,0)</f>
+        <f aca="false">IF(14&gt;=2,Assumptions!$B$37*IF(14&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$38,0)</f>
         <v>17.4545454545455</v>
       </c>
       <c r="P11" s="18" t="n">
-        <f aca="false">IF(15&gt;=2,Assumptions!$B$37*IF(15&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$38,0)</f>
+        <f aca="false">IF(15&gt;=2,Assumptions!$B$37*IF(15&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$38,0)</f>
         <v>17.4545454545455</v>
       </c>
       <c r="Q11" s="18" t="n">
-        <f aca="false">IF(16&gt;=2,Assumptions!$B$37*IF(16&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$38,0)</f>
+        <f aca="false">IF(16&gt;=2,Assumptions!$B$37*IF(16&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$38,0)</f>
         <v>17.4545454545455</v>
       </c>
       <c r="R11" s="18" t="n">
-        <f aca="false">IF(17&gt;=2,Assumptions!$B$37*IF(17&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$38,0)</f>
+        <f aca="false">IF(17&gt;=2,Assumptions!$B$37*IF(17&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$38,0)</f>
         <v>17.4545454545455</v>
       </c>
       <c r="S11" s="18" t="n">
-        <f aca="false">IF(18&gt;=2,Assumptions!$B$37*IF(18&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$38,0)</f>
+        <f aca="false">IF(18&gt;=2,Assumptions!$B$37*IF(18&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$38,0)</f>
         <v>17.4545454545455</v>
       </c>
       <c r="T11" s="18" t="n">
-        <f aca="false">IF(19&gt;=2,Assumptions!$B$37*IF(19&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$38,0)</f>
+        <f aca="false">IF(19&gt;=2,Assumptions!$B$37*IF(19&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$38,0)</f>
         <v>17.4545454545455</v>
       </c>
       <c r="U11" s="18" t="n">
-        <f aca="false">IF(20&gt;=2,Assumptions!$B$37*IF(20&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$38,0)</f>
+        <f aca="false">IF(20&gt;=2,Assumptions!$B$37*IF(20&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$38,0)</f>
         <v>17.4545454545455</v>
       </c>
       <c r="V11" s="18" t="n">
-        <f aca="false">IF(21&gt;=2,Assumptions!$B$37*IF(21&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$38,0)</f>
+        <f aca="false">IF(21&gt;=2,Assumptions!$B$37*IF(21&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$38,0)</f>
         <v>17.4545454545455</v>
       </c>
       <c r="W11" s="18" t="n">
-        <f aca="false">IF(22&gt;=2,Assumptions!$B$37*IF(22&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$38,0)</f>
+        <f aca="false">IF(22&gt;=2,Assumptions!$B$37*IF(22&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$38,0)</f>
         <v>17.4545454545455</v>
       </c>
       <c r="X11" s="18" t="n">
-        <f aca="false">IF(23&gt;=2,Assumptions!$B$37*IF(23&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$38,0)</f>
+        <f aca="false">IF(23&gt;=2,Assumptions!$B$37*IF(23&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$38,0)</f>
         <v>17.4545454545455</v>
       </c>
       <c r="Y11" s="18" t="n">
-        <f aca="false">IF(24&gt;=2,Assumptions!$B$37*IF(24&gt;=Assumptions!$B$8,Assumptions!$B$43,1)/Assumptions!$B$38,0)</f>
+        <f aca="false">IF(24&gt;=2,Assumptions!$B$37*IF(24&gt;=Assumptions!$B$8,Assumptions!$B$45,1)/Assumptions!$B$38,0)</f>
         <v>17.4545454545455</v>
       </c>
       <c r="Z11" s="18" t="n">
@@ -3017,7 +3053,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B12" s="18" t="n">
         <f aca="false">Assumptions!$B$40*(1+Assumptions!$B$41)^(1-1)</f>
@@ -3130,7 +3166,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B13" s="19" t="n">
         <f aca="false">B10+B11+B12</f>
@@ -3243,4381 +3279,4390 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B14" s="18" t="n">
         <f aca="false">B10*Assumptions!$B$36+B11*Assumptions!$B$39+B12*Assumptions!$B$42</f>
-        <v>8.03898305084746</v>
+        <v>11.5271186440678</v>
       </c>
       <c r="C14" s="18" t="n">
         <f aca="false">C10*Assumptions!$B$36+C11*Assumptions!$B$39+C12*Assumptions!$B$42</f>
-        <v>10.1646194144838</v>
+        <v>15.0338459167951</v>
       </c>
       <c r="D14" s="18" t="n">
         <f aca="false">D10*Assumptions!$B$36+D11*Assumptions!$B$39+D12*Assumptions!$B$42</f>
-        <v>10.3363394144838</v>
+        <v>15.2818859167951</v>
       </c>
       <c r="E14" s="18" t="n">
         <f aca="false">E10*Assumptions!$B$36+E11*Assumptions!$B$39+E12*Assumptions!$B$42</f>
-        <v>10.5183626144838</v>
+        <v>15.5448083167951</v>
       </c>
       <c r="F14" s="18" t="n">
         <f aca="false">F10*Assumptions!$B$36+F11*Assumptions!$B$39+F12*Assumptions!$B$42</f>
-        <v>10.7113072064838</v>
+        <v>15.8235060607951</v>
       </c>
       <c r="G14" s="18" t="n">
         <f aca="false">G10*Assumptions!$B$36+G11*Assumptions!$B$39+G12*Assumptions!$B$42</f>
-        <v>10.9158284740038</v>
+        <v>16.1189256694351</v>
       </c>
       <c r="H14" s="18" t="n">
         <f aca="false">H10*Assumptions!$B$36+H11*Assumptions!$B$39+H12*Assumptions!$B$42</f>
-        <v>15.5141926662653</v>
+        <v>22.9719780046705</v>
       </c>
       <c r="I14" s="18" t="n">
         <f aca="false">I10*Assumptions!$B$36+I11*Assumptions!$B$39+I12*Assumptions!$B$42</f>
-        <v>15.7439927624508</v>
+        <v>23.3039114769384</v>
       </c>
       <c r="J14" s="18" t="n">
         <f aca="false">J10*Assumptions!$B$36+J11*Assumptions!$B$39+J12*Assumptions!$B$42</f>
-        <v>15.9875808644074</v>
+        <v>23.6557609575424</v>
       </c>
       <c r="K14" s="18" t="n">
         <f aca="false">K10*Assumptions!$B$36+K11*Assumptions!$B$39+K12*Assumptions!$B$42</f>
-        <v>16.2457842524814</v>
+        <v>24.0287214069826</v>
       </c>
       <c r="L14" s="18" t="n">
         <f aca="false">L10*Assumptions!$B$36+L11*Assumptions!$B$39+L12*Assumptions!$B$42</f>
-        <v>16.5194798438398</v>
+        <v>24.4240594833892</v>
       </c>
       <c r="M14" s="18" t="n">
         <f aca="false">M10*Assumptions!$B$36+M11*Assumptions!$B$39+M12*Assumptions!$B$42</f>
-        <v>16.8095971706798</v>
+        <v>24.8431178443803</v>
       </c>
       <c r="N14" s="18" t="n">
         <f aca="false">N10*Assumptions!$B$36+N11*Assumptions!$B$39+N12*Assumptions!$B$42</f>
-        <v>17.1171215371301</v>
+        <v>25.2873197070308</v>
       </c>
       <c r="O14" s="18" t="n">
         <f aca="false">O10*Assumptions!$B$36+O11*Assumptions!$B$39+O12*Assumptions!$B$42</f>
-        <v>17.4430973655675</v>
+        <v>25.7581736814403</v>
       </c>
       <c r="P14" s="18" t="n">
         <f aca="false">P10*Assumptions!$B$36+P11*Assumptions!$B$39+P12*Assumptions!$B$42</f>
-        <v>17.7886317437111</v>
+        <v>26.2572788943144</v>
       </c>
       <c r="Q14" s="18" t="n">
         <f aca="false">Q10*Assumptions!$B$36+Q11*Assumptions!$B$39+Q12*Assumptions!$B$42</f>
-        <v>18.1548981845433</v>
+        <v>26.7863304199609</v>
       </c>
       <c r="R14" s="18" t="n">
         <f aca="false">R10*Assumptions!$B$36+R11*Assumptions!$B$39+R12*Assumptions!$B$42</f>
-        <v>18.5431406118254</v>
+        <v>27.3471250371462</v>
       </c>
       <c r="S14" s="18" t="n">
         <f aca="false">S10*Assumptions!$B$36+S11*Assumptions!$B$39+S12*Assumptions!$B$42</f>
-        <v>18.9546775847445</v>
+        <v>27.9415673313627</v>
       </c>
       <c r="T14" s="18" t="n">
         <f aca="false">T10*Assumptions!$B$36+T11*Assumptions!$B$39+T12*Assumptions!$B$42</f>
-        <v>19.3909067760387</v>
+        <v>28.5716761632321</v>
       </c>
       <c r="U14" s="18" t="n">
         <f aca="false">U10*Assumptions!$B$36+U11*Assumptions!$B$39+U12*Assumptions!$B$42</f>
-        <v>19.8533097188106</v>
+        <v>29.2395915250137</v>
       </c>
       <c r="V14" s="18" t="n">
         <f aca="false">V10*Assumptions!$B$36+V11*Assumptions!$B$39+V12*Assumptions!$B$42</f>
-        <v>20.3434568381488</v>
+        <v>29.9475818085022</v>
       </c>
       <c r="W14" s="18" t="n">
         <f aca="false">W10*Assumptions!$B$36+W11*Assumptions!$B$39+W12*Assumptions!$B$42</f>
-        <v>20.8630127846473</v>
+        <v>30.698051509</v>
       </c>
       <c r="X14" s="18" t="n">
         <f aca="false">X10*Assumptions!$B$36+X11*Assumptions!$B$39+X12*Assumptions!$B$42</f>
-        <v>21.4137420879357</v>
+        <v>31.4935493915277</v>
       </c>
       <c r="Y14" s="18" t="n">
         <f aca="false">Y10*Assumptions!$B$36+Y11*Assumptions!$B$39+Y12*Assumptions!$B$42</f>
-        <v>21.9975151494214</v>
+        <v>32.336777147007</v>
       </c>
       <c r="Z14" s="18" t="n">
         <f aca="false">SUM(B14:M14)</f>
-        <v>157.506067734911</v>
+        <v>232.557639698587</v>
       </c>
       <c r="AA14" s="18" t="n">
         <f aca="false">SUM(N14:Y14)</f>
-        <v>231.863510382524</v>
+        <v>341.665022615538</v>
       </c>
       <c r="AB14" s="18" t="n">
         <f aca="false">SUM(B14:Y14)</f>
-        <v>389.369578117435</v>
+        <v>574.222662314125</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="B15" s="18" t="n">
-        <f aca="false">B14*Assumptions!$B$11</f>
-        <v>803.898305084746</v>
-      </c>
-      <c r="C15" s="18" t="n">
-        <f aca="false">C14*Assumptions!$B$11</f>
-        <v>1016.46194144838</v>
-      </c>
-      <c r="D15" s="18" t="n">
-        <f aca="false">D14*Assumptions!$B$11</f>
-        <v>1033.63394144838</v>
-      </c>
-      <c r="E15" s="18" t="n">
-        <f aca="false">E14*Assumptions!$B$11</f>
-        <v>1051.83626144838</v>
-      </c>
-      <c r="F15" s="18" t="n">
-        <f aca="false">F14*Assumptions!$B$11</f>
-        <v>1071.13072064838</v>
-      </c>
-      <c r="G15" s="18" t="n">
-        <f aca="false">G14*Assumptions!$B$11</f>
-        <v>1091.58284740038</v>
-      </c>
-      <c r="H15" s="18" t="n">
-        <f aca="false">H14*Assumptions!$B$11</f>
-        <v>1551.41926662653</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <f aca="false">I14*Assumptions!$B$11</f>
-        <v>1574.39927624508</v>
-      </c>
-      <c r="J15" s="18" t="n">
-        <f aca="false">J14*Assumptions!$B$11</f>
-        <v>1598.75808644074</v>
-      </c>
-      <c r="K15" s="18" t="n">
-        <f aca="false">K14*Assumptions!$B$11</f>
-        <v>1624.57842524814</v>
-      </c>
-      <c r="L15" s="18" t="n">
-        <f aca="false">L14*Assumptions!$B$11</f>
-        <v>1651.94798438398</v>
-      </c>
-      <c r="M15" s="18" t="n">
-        <f aca="false">M14*Assumptions!$B$11</f>
-        <v>1680.95971706798</v>
-      </c>
-      <c r="N15" s="18" t="n">
-        <f aca="false">N14*Assumptions!$B$11</f>
-        <v>1711.71215371301</v>
-      </c>
-      <c r="O15" s="18" t="n">
-        <f aca="false">O14*Assumptions!$B$11</f>
-        <v>1744.30973655675</v>
-      </c>
-      <c r="P15" s="18" t="n">
-        <f aca="false">P14*Assumptions!$B$11</f>
-        <v>1778.86317437111</v>
-      </c>
-      <c r="Q15" s="18" t="n">
-        <f aca="false">Q14*Assumptions!$B$11</f>
-        <v>1815.48981845433</v>
-      </c>
-      <c r="R15" s="18" t="n">
-        <f aca="false">R14*Assumptions!$B$11</f>
-        <v>1854.31406118254</v>
-      </c>
-      <c r="S15" s="18" t="n">
-        <f aca="false">S14*Assumptions!$B$11</f>
-        <v>1895.46775847445</v>
-      </c>
-      <c r="T15" s="18" t="n">
-        <f aca="false">T14*Assumptions!$B$11</f>
-        <v>1939.09067760387</v>
-      </c>
-      <c r="U15" s="18" t="n">
-        <f aca="false">U14*Assumptions!$B$11</f>
-        <v>1985.33097188106</v>
-      </c>
-      <c r="V15" s="18" t="n">
-        <f aca="false">V14*Assumptions!$B$11</f>
-        <v>2034.34568381488</v>
-      </c>
-      <c r="W15" s="18" t="n">
-        <f aca="false">W14*Assumptions!$B$11</f>
-        <v>2086.30127846473</v>
-      </c>
-      <c r="X15" s="18" t="n">
-        <f aca="false">X14*Assumptions!$B$11</f>
-        <v>2141.37420879357</v>
-      </c>
-      <c r="Y15" s="18" t="n">
-        <f aca="false">Y14*Assumptions!$B$11</f>
-        <v>2199.75151494214</v>
-      </c>
-      <c r="Z15" s="18" t="n">
+      <c r="A15" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="B15" s="19" t="n">
+        <f aca="false">B14*Assumptions!$B$44</f>
+        <v>8.06898305084746</v>
+      </c>
+      <c r="C15" s="19" t="n">
+        <f aca="false">C14*Assumptions!$B$44</f>
+        <v>10.5236921417565</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <f aca="false">D14*Assumptions!$B$44</f>
+        <v>10.6973201417565</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <f aca="false">E14*Assumptions!$B$44</f>
+        <v>10.8813658217565</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <f aca="false">F14*Assumptions!$B$44</f>
+        <v>11.0764542425565</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <f aca="false">G14*Assumptions!$B$44</f>
+        <v>11.2832479686045</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <f aca="false">H14*Assumptions!$B$44</f>
+        <v>16.0803846032694</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <f aca="false">I14*Assumptions!$B$44</f>
+        <v>16.3127380338569</v>
+      </c>
+      <c r="J15" s="19" t="n">
+        <f aca="false">J14*Assumptions!$B$44</f>
+        <v>16.5590326702797</v>
+      </c>
+      <c r="K15" s="19" t="n">
+        <f aca="false">K14*Assumptions!$B$44</f>
+        <v>16.8201049848878</v>
+      </c>
+      <c r="L15" s="19" t="n">
+        <f aca="false">L14*Assumptions!$B$44</f>
+        <v>17.0968416383725</v>
+      </c>
+      <c r="M15" s="19" t="n">
+        <f aca="false">M14*Assumptions!$B$44</f>
+        <v>17.3901824910662</v>
+      </c>
+      <c r="N15" s="19" t="n">
+        <f aca="false">N14*Assumptions!$B$44</f>
+        <v>17.7011237949215</v>
+      </c>
+      <c r="O15" s="19" t="n">
+        <f aca="false">O14*Assumptions!$B$44</f>
+        <v>18.0307215770082</v>
+      </c>
+      <c r="P15" s="19" t="n">
+        <f aca="false">P14*Assumptions!$B$44</f>
+        <v>18.3800952260201</v>
+      </c>
+      <c r="Q15" s="19" t="n">
+        <f aca="false">Q14*Assumptions!$B$44</f>
+        <v>18.7504312939726</v>
+      </c>
+      <c r="R15" s="19" t="n">
+        <f aca="false">R14*Assumptions!$B$44</f>
+        <v>19.1429875260024</v>
+      </c>
+      <c r="S15" s="19" t="n">
+        <f aca="false">S14*Assumptions!$B$44</f>
+        <v>19.5590971319539</v>
+      </c>
+      <c r="T15" s="19" t="n">
+        <f aca="false">T14*Assumptions!$B$44</f>
+        <v>20.0001733142625</v>
+      </c>
+      <c r="U15" s="19" t="n">
+        <f aca="false">U14*Assumptions!$B$44</f>
+        <v>20.4677140675096</v>
+      </c>
+      <c r="V15" s="19" t="n">
+        <f aca="false">V14*Assumptions!$B$44</f>
+        <v>20.9633072659516</v>
+      </c>
+      <c r="W15" s="19" t="n">
+        <f aca="false">W14*Assumptions!$B$44</f>
+        <v>21.4886360563</v>
+      </c>
+      <c r="X15" s="19" t="n">
+        <f aca="false">X14*Assumptions!$B$44</f>
+        <v>22.0454845740694</v>
+      </c>
+      <c r="Y15" s="19" t="n">
+        <f aca="false">Y14*Assumptions!$B$44</f>
+        <v>22.6357440029049</v>
+      </c>
+      <c r="Z15" s="19" t="n">
         <f aca="false">SUM(B15:M15)</f>
-        <v>15750.6067734911</v>
-      </c>
-      <c r="AA15" s="18" t="n">
+        <v>162.790347789011</v>
+      </c>
+      <c r="AA15" s="19" t="n">
         <f aca="false">SUM(N15:Y15)</f>
-        <v>23186.3510382524</v>
-      </c>
-      <c r="AB15" s="18" t="n">
+        <v>239.165515830877</v>
+      </c>
+      <c r="AB15" s="19" t="n">
         <f aca="false">SUM(B15:Y15)</f>
-        <v>38936.9578117435</v>
+        <v>401.955863619887</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="B16" s="19" t="n">
-        <f aca="false">MIN(B15+0,B8)</f>
+      <c r="A16" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="B16" s="18" t="n">
+        <f aca="false">B15*Assumptions!$B$11</f>
+        <v>806.898305084746</v>
+      </c>
+      <c r="C16" s="18" t="n">
+        <f aca="false">C15*Assumptions!$B$11</f>
+        <v>1052.36921417565</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <f aca="false">D15*Assumptions!$B$11</f>
+        <v>1069.73201417565</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <f aca="false">E15*Assumptions!$B$11</f>
+        <v>1088.13658217566</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <f aca="false">F15*Assumptions!$B$11</f>
+        <v>1107.64542425566</v>
+      </c>
+      <c r="G16" s="18" t="n">
+        <f aca="false">G15*Assumptions!$B$11</f>
+        <v>1128.32479686045</v>
+      </c>
+      <c r="H16" s="18" t="n">
+        <f aca="false">H15*Assumptions!$B$11</f>
+        <v>1608.03846032694</v>
+      </c>
+      <c r="I16" s="18" t="n">
+        <f aca="false">I15*Assumptions!$B$11</f>
+        <v>1631.27380338569</v>
+      </c>
+      <c r="J16" s="18" t="n">
+        <f aca="false">J15*Assumptions!$B$11</f>
+        <v>1655.90326702797</v>
+      </c>
+      <c r="K16" s="18" t="n">
+        <f aca="false">K15*Assumptions!$B$11</f>
+        <v>1682.01049848878</v>
+      </c>
+      <c r="L16" s="18" t="n">
+        <f aca="false">L15*Assumptions!$B$11</f>
+        <v>1709.68416383725</v>
+      </c>
+      <c r="M16" s="18" t="n">
+        <f aca="false">M15*Assumptions!$B$11</f>
+        <v>1739.01824910662</v>
+      </c>
+      <c r="N16" s="18" t="n">
+        <f aca="false">N15*Assumptions!$B$11</f>
+        <v>1770.11237949215</v>
+      </c>
+      <c r="O16" s="18" t="n">
+        <f aca="false">O15*Assumptions!$B$11</f>
+        <v>1803.07215770082</v>
+      </c>
+      <c r="P16" s="18" t="n">
+        <f aca="false">P15*Assumptions!$B$11</f>
+        <v>1838.00952260201</v>
+      </c>
+      <c r="Q16" s="18" t="n">
+        <f aca="false">Q15*Assumptions!$B$11</f>
+        <v>1875.04312939726</v>
+      </c>
+      <c r="R16" s="18" t="n">
+        <f aca="false">R15*Assumptions!$B$11</f>
+        <v>1914.29875260024</v>
+      </c>
+      <c r="S16" s="18" t="n">
+        <f aca="false">S15*Assumptions!$B$11</f>
+        <v>1955.90971319539</v>
+      </c>
+      <c r="T16" s="18" t="n">
+        <f aca="false">T15*Assumptions!$B$11</f>
+        <v>2000.01733142625</v>
+      </c>
+      <c r="U16" s="18" t="n">
+        <f aca="false">U15*Assumptions!$B$11</f>
+        <v>2046.77140675096</v>
+      </c>
+      <c r="V16" s="18" t="n">
+        <f aca="false">V15*Assumptions!$B$11</f>
+        <v>2096.33072659516</v>
+      </c>
+      <c r="W16" s="18" t="n">
+        <f aca="false">W15*Assumptions!$B$11</f>
+        <v>2148.86360563</v>
+      </c>
+      <c r="X16" s="18" t="n">
+        <f aca="false">X15*Assumptions!$B$11</f>
+        <v>2204.54845740694</v>
+      </c>
+      <c r="Y16" s="18" t="n">
+        <f aca="false">Y15*Assumptions!$B$11</f>
+        <v>2263.57440029049</v>
+      </c>
+      <c r="Z16" s="18" t="n">
+        <f aca="false">SUM(B16:M16)</f>
+        <v>16279.0347789011</v>
+      </c>
+      <c r="AA16" s="18" t="n">
+        <f aca="false">SUM(N16:Y16)</f>
+        <v>23916.5515830877</v>
+      </c>
+      <c r="AB16" s="18" t="n">
+        <f aca="false">SUM(B16:Y16)</f>
+        <v>40195.5863619887</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="B17" s="19" t="n">
+        <f aca="false">MIN(B16+0,B8)</f>
         <v>650</v>
       </c>
-      <c r="C16" s="19" t="n">
-        <f aca="false">MIN(C15+B17,C8)</f>
+      <c r="C17" s="19" t="n">
+        <f aca="false">MIN(C16+B18,C8)</f>
         <v>700</v>
       </c>
-      <c r="D16" s="19" t="n">
-        <f aca="false">MIN(D15+C17,D8)</f>
+      <c r="D17" s="19" t="n">
+        <f aca="false">MIN(D16+C18,D8)</f>
         <v>750</v>
       </c>
-      <c r="E16" s="19" t="n">
-        <f aca="false">MIN(E15+D17,E8)</f>
+      <c r="E17" s="19" t="n">
+        <f aca="false">MIN(E16+D18,E8)</f>
         <v>800</v>
       </c>
-      <c r="F16" s="19" t="n">
-        <f aca="false">MIN(F15+E17,F8)</f>
+      <c r="F17" s="19" t="n">
+        <f aca="false">MIN(F16+E18,F8)</f>
         <v>850</v>
       </c>
-      <c r="G16" s="19" t="n">
-        <f aca="false">MIN(G15+F17,G8)</f>
+      <c r="G17" s="19" t="n">
+        <f aca="false">MIN(G16+F18,G8)</f>
         <v>900</v>
       </c>
-      <c r="H16" s="19" t="n">
-        <f aca="false">MIN(H15+G17,H8)</f>
+      <c r="H17" s="19" t="n">
+        <f aca="false">MIN(H16+G18,H8)</f>
         <v>1400</v>
       </c>
-      <c r="I16" s="19" t="n">
-        <f aca="false">MIN(I15+H17,I8)</f>
+      <c r="I17" s="19" t="n">
+        <f aca="false">MIN(I16+H18,I8)</f>
         <v>1533.33333333333</v>
       </c>
-      <c r="J16" s="19" t="n">
-        <f aca="false">MIN(J15+I17,J8)</f>
+      <c r="J17" s="19" t="n">
+        <f aca="false">MIN(J16+I18,J8)</f>
         <v>1666.66666666667</v>
       </c>
-      <c r="K16" s="19" t="n">
-        <f aca="false">MIN(K15+J17,K8)</f>
+      <c r="K17" s="19" t="n">
+        <f aca="false">MIN(K16+J18,K8)</f>
         <v>1800</v>
       </c>
-      <c r="L16" s="19" t="n">
-        <f aca="false">MIN(L15+K17,L8)</f>
+      <c r="L17" s="19" t="n">
+        <f aca="false">MIN(L16+K18,L8)</f>
         <v>1800</v>
       </c>
-      <c r="M16" s="19" t="n">
-        <f aca="false">MIN(M15+L17,M8)</f>
+      <c r="M17" s="19" t="n">
+        <f aca="false">MIN(M16+L18,M8)</f>
         <v>1800</v>
       </c>
-      <c r="N16" s="19" t="n">
-        <f aca="false">MIN(N15+M17,N8)</f>
+      <c r="N17" s="19" t="n">
+        <f aca="false">MIN(N16+M18,N8)</f>
         <v>1800</v>
       </c>
-      <c r="O16" s="19" t="n">
-        <f aca="false">MIN(O15+N17,O8)</f>
+      <c r="O17" s="19" t="n">
+        <f aca="false">MIN(O16+N18,O8)</f>
         <v>1800</v>
       </c>
-      <c r="P16" s="19" t="n">
-        <f aca="false">MIN(P15+O17,P8)</f>
+      <c r="P17" s="19" t="n">
+        <f aca="false">MIN(P16+O18,P8)</f>
         <v>1800</v>
       </c>
-      <c r="Q16" s="19" t="n">
-        <f aca="false">MIN(Q15+P17,Q8)</f>
+      <c r="Q17" s="19" t="n">
+        <f aca="false">MIN(Q16+P18,Q8)</f>
         <v>1800</v>
       </c>
-      <c r="R16" s="19" t="n">
-        <f aca="false">MIN(R15+Q17,R8)</f>
+      <c r="R17" s="19" t="n">
+        <f aca="false">MIN(R16+Q18,R8)</f>
         <v>1800</v>
       </c>
-      <c r="S16" s="19" t="n">
-        <f aca="false">MIN(S15+R17,S8)</f>
+      <c r="S17" s="19" t="n">
+        <f aca="false">MIN(S16+R18,S8)</f>
         <v>1800</v>
       </c>
-      <c r="T16" s="19" t="n">
-        <f aca="false">MIN(T15+S17,T8)</f>
+      <c r="T17" s="19" t="n">
+        <f aca="false">MIN(T16+S18,T8)</f>
         <v>1800</v>
       </c>
-      <c r="U16" s="19" t="n">
-        <f aca="false">MIN(U15+T17,U8)</f>
+      <c r="U17" s="19" t="n">
+        <f aca="false">MIN(U16+T18,U8)</f>
         <v>1800</v>
       </c>
-      <c r="V16" s="19" t="n">
-        <f aca="false">MIN(V15+U17,V8)</f>
+      <c r="V17" s="19" t="n">
+        <f aca="false">MIN(V16+U18,V8)</f>
         <v>1800</v>
       </c>
-      <c r="W16" s="19" t="n">
-        <f aca="false">MIN(W15+V17,W8)</f>
+      <c r="W17" s="19" t="n">
+        <f aca="false">MIN(W16+V18,W8)</f>
         <v>1800</v>
       </c>
-      <c r="X16" s="19" t="n">
-        <f aca="false">MIN(X15+W17,X8)</f>
+      <c r="X17" s="19" t="n">
+        <f aca="false">MIN(X16+W18,X8)</f>
         <v>1800</v>
       </c>
-      <c r="Y16" s="19" t="n">
-        <f aca="false">MIN(Y15+X17,Y8)</f>
+      <c r="Y17" s="19" t="n">
+        <f aca="false">MIN(Y16+X18,Y8)</f>
         <v>1800</v>
       </c>
-      <c r="Z16" s="19" t="n">
-        <f aca="false">SUM(B16:M16)</f>
+      <c r="Z17" s="19" t="n">
+        <f aca="false">SUM(B17:M17)</f>
         <v>14650</v>
       </c>
-      <c r="AA16" s="19" t="n">
-        <f aca="false">SUM(N16:Y16)</f>
+      <c r="AA17" s="19" t="n">
+        <f aca="false">SUM(N17:Y17)</f>
         <v>21600</v>
       </c>
-      <c r="AB16" s="19" t="n">
-        <f aca="false">SUM(B16:Y16)</f>
+      <c r="AB17" s="19" t="n">
+        <f aca="false">SUM(B17:Y17)</f>
         <v>36250</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="B17" s="18" t="n">
-        <f aca="false">MIN(B8*Assumptions!$B$12,MAX(0,B15+0-B16))</f>
-        <v>153.898305084746</v>
-      </c>
-      <c r="C17" s="18" t="n">
-        <f aca="false">MIN(C8*Assumptions!$B$12,MAX(0,C15+B17-C16))</f>
-        <v>470.360246533128</v>
-      </c>
-      <c r="D17" s="18" t="n">
-        <f aca="false">MIN(D8*Assumptions!$B$12,MAX(0,D15+C17-D16))</f>
-        <v>750</v>
-      </c>
-      <c r="E17" s="18" t="n">
-        <f aca="false">MIN(E8*Assumptions!$B$12,MAX(0,E15+D17-E16))</f>
-        <v>800</v>
-      </c>
-      <c r="F17" s="18" t="n">
-        <f aca="false">MIN(F8*Assumptions!$B$12,MAX(0,F15+E17-F16))</f>
-        <v>850</v>
-      </c>
-      <c r="G17" s="18" t="n">
-        <f aca="false">MIN(G8*Assumptions!$B$12,MAX(0,G15+F17-G16))</f>
-        <v>900</v>
-      </c>
-      <c r="H17" s="18" t="n">
-        <f aca="false">MIN(H8*Assumptions!$B$12,MAX(0,H15+G17-H16))</f>
-        <v>1051.41926662653</v>
-      </c>
-      <c r="I17" s="18" t="n">
-        <f aca="false">MIN(I8*Assumptions!$B$12,MAX(0,I15+H17-I16))</f>
-        <v>1092.48520953828</v>
-      </c>
-      <c r="J17" s="18" t="n">
-        <f aca="false">MIN(J8*Assumptions!$B$12,MAX(0,J15+I17-J16))</f>
-        <v>1024.57662931235</v>
-      </c>
-      <c r="K17" s="18" t="n">
-        <f aca="false">MIN(K8*Assumptions!$B$12,MAX(0,K15+J17-K16))</f>
-        <v>849.155054560486</v>
-      </c>
-      <c r="L17" s="18" t="n">
-        <f aca="false">MIN(L8*Assumptions!$B$12,MAX(0,L15+K17-L16))</f>
-        <v>701.103038944468</v>
-      </c>
-      <c r="M17" s="18" t="n">
-        <f aca="false">MIN(M8*Assumptions!$B$12,MAX(0,M15+L17-M16))</f>
-        <v>582.062756012444</v>
-      </c>
-      <c r="N17" s="18" t="n">
-        <f aca="false">MIN(N8*Assumptions!$B$12,MAX(0,N15+M17-N16))</f>
-        <v>493.774909725455</v>
-      </c>
-      <c r="O17" s="18" t="n">
-        <f aca="false">MIN(O8*Assumptions!$B$12,MAX(0,O15+N17-O16))</f>
-        <v>438.084646282201</v>
-      </c>
-      <c r="P17" s="18" t="n">
-        <f aca="false">MIN(P8*Assumptions!$B$12,MAX(0,P15+O17-P16))</f>
-        <v>416.947820653307</v>
-      </c>
-      <c r="Q17" s="18" t="n">
-        <f aca="false">MIN(Q8*Assumptions!$B$12,MAX(0,Q15+P17-Q16))</f>
-        <v>432.437639107635</v>
-      </c>
-      <c r="R17" s="18" t="n">
-        <f aca="false">MIN(R8*Assumptions!$B$12,MAX(0,R15+Q17-R16))</f>
-        <v>486.751700290178</v>
-      </c>
-      <c r="S17" s="18" t="n">
-        <f aca="false">MIN(S8*Assumptions!$B$12,MAX(0,S15+R17-S16))</f>
-        <v>582.219458764629</v>
-      </c>
-      <c r="T17" s="18" t="n">
-        <f aca="false">MIN(T8*Assumptions!$B$12,MAX(0,T15+S17-T16))</f>
-        <v>721.310136368502</v>
-      </c>
-      <c r="U17" s="18" t="n">
-        <f aca="false">MIN(U8*Assumptions!$B$12,MAX(0,U15+T17-U16))</f>
-        <v>906.641108249563</v>
-      </c>
-      <c r="V17" s="18" t="n">
-        <f aca="false">MIN(V8*Assumptions!$B$12,MAX(0,V15+U17-V16))</f>
-        <v>1140.98679206444</v>
-      </c>
-      <c r="W17" s="18" t="n">
-        <f aca="false">MIN(W8*Assumptions!$B$12,MAX(0,W15+V17-W16))</f>
-        <v>1427.28807052917</v>
-      </c>
-      <c r="X17" s="18" t="n">
-        <f aca="false">MIN(X8*Assumptions!$B$12,MAX(0,X15+W17-X16))</f>
-        <v>1768.66227932274</v>
-      </c>
-      <c r="Y17" s="18" t="n">
-        <f aca="false">MIN(Y8*Assumptions!$B$12,MAX(0,Y15+X17-Y16))</f>
-        <v>1800</v>
-      </c>
-      <c r="Z17" s="2"/>
-      <c r="AA17" s="2"/>
-      <c r="AB17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="B18" s="20" t="n">
-        <f aca="false">IF(B8=0,0,B16/B8)</f>
-        <v>1</v>
-      </c>
-      <c r="C18" s="20" t="n">
-        <f aca="false">IF(C8=0,0,C16/C8)</f>
-        <v>1</v>
-      </c>
-      <c r="D18" s="20" t="n">
-        <f aca="false">IF(D8=0,0,D16/D8)</f>
-        <v>1</v>
-      </c>
-      <c r="E18" s="20" t="n">
-        <f aca="false">IF(E8=0,0,E16/E8)</f>
-        <v>1</v>
-      </c>
-      <c r="F18" s="20" t="n">
-        <f aca="false">IF(F8=0,0,F16/F8)</f>
-        <v>1</v>
-      </c>
-      <c r="G18" s="20" t="n">
-        <f aca="false">IF(G8=0,0,G16/G8)</f>
-        <v>1</v>
-      </c>
-      <c r="H18" s="20" t="n">
-        <f aca="false">IF(H8=0,0,H16/H8)</f>
-        <v>1</v>
-      </c>
-      <c r="I18" s="20" t="n">
-        <f aca="false">IF(I8=0,0,I16/I8)</f>
-        <v>1</v>
-      </c>
-      <c r="J18" s="20" t="n">
-        <f aca="false">IF(J8=0,0,J16/J8)</f>
-        <v>1</v>
-      </c>
-      <c r="K18" s="20" t="n">
-        <f aca="false">IF(K8=0,0,K16/K8)</f>
-        <v>1</v>
-      </c>
-      <c r="L18" s="20" t="n">
-        <f aca="false">IF(L8=0,0,L16/L8)</f>
-        <v>1</v>
-      </c>
-      <c r="M18" s="20" t="n">
-        <f aca="false">IF(M8=0,0,M16/M8)</f>
-        <v>1</v>
-      </c>
-      <c r="N18" s="20" t="n">
-        <f aca="false">IF(N8=0,0,N16/N8)</f>
-        <v>1</v>
-      </c>
-      <c r="O18" s="20" t="n">
-        <f aca="false">IF(O8=0,0,O16/O8)</f>
-        <v>1</v>
-      </c>
-      <c r="P18" s="20" t="n">
-        <f aca="false">IF(P8=0,0,P16/P8)</f>
-        <v>1</v>
-      </c>
-      <c r="Q18" s="20" t="n">
-        <f aca="false">IF(Q8=0,0,Q16/Q8)</f>
-        <v>1</v>
-      </c>
-      <c r="R18" s="20" t="n">
-        <f aca="false">IF(R8=0,0,R16/R8)</f>
-        <v>1</v>
-      </c>
-      <c r="S18" s="20" t="n">
-        <f aca="false">IF(S8=0,0,S16/S8)</f>
-        <v>1</v>
-      </c>
-      <c r="T18" s="20" t="n">
-        <f aca="false">IF(T8=0,0,T16/T8)</f>
-        <v>1</v>
-      </c>
-      <c r="U18" s="20" t="n">
-        <f aca="false">IF(U8=0,0,U16/U8)</f>
-        <v>1</v>
-      </c>
-      <c r="V18" s="20" t="n">
-        <f aca="false">IF(V8=0,0,V16/V8)</f>
-        <v>1</v>
-      </c>
-      <c r="W18" s="20" t="n">
-        <f aca="false">IF(W8=0,0,W16/W8)</f>
-        <v>1</v>
-      </c>
-      <c r="X18" s="20" t="n">
-        <f aca="false">IF(X8=0,0,X16/X8)</f>
-        <v>1</v>
-      </c>
-      <c r="Y18" s="20" t="n">
-        <f aca="false">IF(Y8=0,0,Y16/Y8)</f>
-        <v>1</v>
+        <v>146</v>
+      </c>
+      <c r="B18" s="18" t="n">
+        <f aca="false">MIN(B8*Assumptions!$B$12,MAX(0,B16+0-B17))</f>
+        <v>156.898305084746</v>
+      </c>
+      <c r="C18" s="18" t="n">
+        <f aca="false">MIN(C8*Assumptions!$B$12,MAX(0,C16+B18-C17))</f>
+        <v>509.267519260401</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <f aca="false">MIN(D8*Assumptions!$B$12,MAX(0,D16+C18-D17))</f>
+        <v>750</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <f aca="false">MIN(E8*Assumptions!$B$12,MAX(0,E16+D18-E17))</f>
+        <v>800</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <f aca="false">MIN(F8*Assumptions!$B$12,MAX(0,F16+E18-F17))</f>
+        <v>850</v>
+      </c>
+      <c r="G18" s="18" t="n">
+        <f aca="false">MIN(G8*Assumptions!$B$12,MAX(0,G16+F18-G17))</f>
+        <v>900</v>
+      </c>
+      <c r="H18" s="18" t="n">
+        <f aca="false">MIN(H8*Assumptions!$B$12,MAX(0,H16+G18-H17))</f>
+        <v>1108.03846032694</v>
+      </c>
+      <c r="I18" s="18" t="n">
+        <f aca="false">MIN(I8*Assumptions!$B$12,MAX(0,I16+H18-I17))</f>
+        <v>1205.97893037929</v>
+      </c>
+      <c r="J18" s="18" t="n">
+        <f aca="false">MIN(J8*Assumptions!$B$12,MAX(0,J16+I18-J17))</f>
+        <v>1195.21553074059</v>
+      </c>
+      <c r="K18" s="18" t="n">
+        <f aca="false">MIN(K8*Assumptions!$B$12,MAX(0,K16+J18-K17))</f>
+        <v>1077.22602922937</v>
+      </c>
+      <c r="L18" s="18" t="n">
+        <f aca="false">MIN(L8*Assumptions!$B$12,MAX(0,L16+K18-L17))</f>
+        <v>986.910193066621</v>
+      </c>
+      <c r="M18" s="18" t="n">
+        <f aca="false">MIN(M8*Assumptions!$B$12,MAX(0,M16+L18-M17))</f>
+        <v>925.92844217324</v>
+      </c>
+      <c r="N18" s="18" t="n">
+        <f aca="false">MIN(N8*Assumptions!$B$12,MAX(0,N16+M18-N17))</f>
+        <v>896.040821665393</v>
+      </c>
+      <c r="O18" s="18" t="n">
+        <f aca="false">MIN(O8*Assumptions!$B$12,MAX(0,O16+N18-O17))</f>
+        <v>899.112979366212</v>
+      </c>
+      <c r="P18" s="18" t="n">
+        <f aca="false">MIN(P8*Assumptions!$B$12,MAX(0,P16+O18-P17))</f>
+        <v>937.122501968218</v>
+      </c>
+      <c r="Q18" s="18" t="n">
+        <f aca="false">MIN(Q8*Assumptions!$B$12,MAX(0,Q16+P18-Q17))</f>
+        <v>1012.16563136548</v>
+      </c>
+      <c r="R18" s="18" t="n">
+        <f aca="false">MIN(R8*Assumptions!$B$12,MAX(0,R16+Q18-R17))</f>
+        <v>1126.46438396572</v>
+      </c>
+      <c r="S18" s="18" t="n">
+        <f aca="false">MIN(S8*Assumptions!$B$12,MAX(0,S16+R18-S17))</f>
+        <v>1282.37409716111</v>
+      </c>
+      <c r="T18" s="18" t="n">
+        <f aca="false">MIN(T8*Assumptions!$B$12,MAX(0,T16+S18-T17))</f>
+        <v>1482.39142858735</v>
+      </c>
+      <c r="U18" s="18" t="n">
+        <f aca="false">MIN(U8*Assumptions!$B$12,MAX(0,U16+T18-U17))</f>
+        <v>1729.16283533831</v>
+      </c>
+      <c r="V18" s="18" t="n">
+        <f aca="false">MIN(V8*Assumptions!$B$12,MAX(0,V16+U18-V17))</f>
+        <v>1800</v>
+      </c>
+      <c r="W18" s="18" t="n">
+        <f aca="false">MIN(W8*Assumptions!$B$12,MAX(0,W16+V18-W17))</f>
+        <v>1800</v>
+      </c>
+      <c r="X18" s="18" t="n">
+        <f aca="false">MIN(X8*Assumptions!$B$12,MAX(0,X16+W18-X17))</f>
+        <v>1800</v>
+      </c>
+      <c r="Y18" s="18" t="n">
+        <f aca="false">MIN(Y8*Assumptions!$B$12,MAX(0,Y16+X18-Y17))</f>
+        <v>1800</v>
       </c>
       <c r="Z18" s="2"/>
       <c r="AA18" s="2"/>
       <c r="AB18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="5"/>
-      <c r="S19" s="5"/>
-      <c r="T19" s="5"/>
-      <c r="U19" s="5"/>
-      <c r="V19" s="5"/>
-      <c r="W19" s="5"/>
-      <c r="X19" s="5"/>
-      <c r="Y19" s="5"/>
-      <c r="Z19" s="5"/>
-      <c r="AA19" s="5"/>
-      <c r="AB19" s="5"/>
+      <c r="A19" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="B19" s="20" t="n">
+        <f aca="false">IF(B8=0,0,B17/B8)</f>
+        <v>1</v>
+      </c>
+      <c r="C19" s="20" t="n">
+        <f aca="false">IF(C8=0,0,C17/C8)</f>
+        <v>1</v>
+      </c>
+      <c r="D19" s="20" t="n">
+        <f aca="false">IF(D8=0,0,D17/D8)</f>
+        <v>1</v>
+      </c>
+      <c r="E19" s="20" t="n">
+        <f aca="false">IF(E8=0,0,E17/E8)</f>
+        <v>1</v>
+      </c>
+      <c r="F19" s="20" t="n">
+        <f aca="false">IF(F8=0,0,F17/F8)</f>
+        <v>1</v>
+      </c>
+      <c r="G19" s="20" t="n">
+        <f aca="false">IF(G8=0,0,G17/G8)</f>
+        <v>1</v>
+      </c>
+      <c r="H19" s="20" t="n">
+        <f aca="false">IF(H8=0,0,H17/H8)</f>
+        <v>1</v>
+      </c>
+      <c r="I19" s="20" t="n">
+        <f aca="false">IF(I8=0,0,I17/I8)</f>
+        <v>1</v>
+      </c>
+      <c r="J19" s="20" t="n">
+        <f aca="false">IF(J8=0,0,J17/J8)</f>
+        <v>1</v>
+      </c>
+      <c r="K19" s="20" t="n">
+        <f aca="false">IF(K8=0,0,K17/K8)</f>
+        <v>1</v>
+      </c>
+      <c r="L19" s="20" t="n">
+        <f aca="false">IF(L8=0,0,L17/L8)</f>
+        <v>1</v>
+      </c>
+      <c r="M19" s="20" t="n">
+        <f aca="false">IF(M8=0,0,M17/M8)</f>
+        <v>1</v>
+      </c>
+      <c r="N19" s="20" t="n">
+        <f aca="false">IF(N8=0,0,N17/N8)</f>
+        <v>1</v>
+      </c>
+      <c r="O19" s="20" t="n">
+        <f aca="false">IF(O8=0,0,O17/O8)</f>
+        <v>1</v>
+      </c>
+      <c r="P19" s="20" t="n">
+        <f aca="false">IF(P8=0,0,P17/P8)</f>
+        <v>1</v>
+      </c>
+      <c r="Q19" s="20" t="n">
+        <f aca="false">IF(Q8=0,0,Q17/Q8)</f>
+        <v>1</v>
+      </c>
+      <c r="R19" s="20" t="n">
+        <f aca="false">IF(R8=0,0,R17/R8)</f>
+        <v>1</v>
+      </c>
+      <c r="S19" s="20" t="n">
+        <f aca="false">IF(S8=0,0,S17/S8)</f>
+        <v>1</v>
+      </c>
+      <c r="T19" s="20" t="n">
+        <f aca="false">IF(T8=0,0,T17/T8)</f>
+        <v>1</v>
+      </c>
+      <c r="U19" s="20" t="n">
+        <f aca="false">IF(U8=0,0,U17/U8)</f>
+        <v>1</v>
+      </c>
+      <c r="V19" s="20" t="n">
+        <f aca="false">IF(V8=0,0,V17/V8)</f>
+        <v>1</v>
+      </c>
+      <c r="W19" s="20" t="n">
+        <f aca="false">IF(W8=0,0,W17/W8)</f>
+        <v>1</v>
+      </c>
+      <c r="X19" s="20" t="n">
+        <f aca="false">IF(X8=0,0,X17/X8)</f>
+        <v>1</v>
+      </c>
+      <c r="Y19" s="20" t="n">
+        <f aca="false">IF(Y8=0,0,Y17/Y8)</f>
+        <v>1</v>
+      </c>
+      <c r="Z19" s="2"/>
+      <c r="AA19" s="2"/>
+      <c r="AB19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="B20" s="21" t="n">
-        <f aca="false">B16*Assumptions!$B$5</f>
-        <v>27300</v>
-      </c>
-      <c r="C20" s="21" t="n">
-        <f aca="false">C16*Assumptions!$B$5</f>
-        <v>29400</v>
-      </c>
-      <c r="D20" s="21" t="n">
-        <f aca="false">D16*Assumptions!$B$5</f>
-        <v>31500</v>
-      </c>
-      <c r="E20" s="21" t="n">
-        <f aca="false">E16*Assumptions!$B$5</f>
-        <v>33600</v>
-      </c>
-      <c r="F20" s="21" t="n">
-        <f aca="false">F16*Assumptions!$B$5</f>
-        <v>35700</v>
-      </c>
-      <c r="G20" s="21" t="n">
-        <f aca="false">G16*Assumptions!$B$5</f>
-        <v>37800</v>
-      </c>
-      <c r="H20" s="21" t="n">
-        <f aca="false">H16*Assumptions!$B$5</f>
-        <v>58800</v>
-      </c>
-      <c r="I20" s="21" t="n">
-        <f aca="false">I16*Assumptions!$B$5</f>
-        <v>64400</v>
-      </c>
-      <c r="J20" s="21" t="n">
-        <f aca="false">J16*Assumptions!$B$5</f>
-        <v>70000</v>
-      </c>
-      <c r="K20" s="21" t="n">
-        <f aca="false">K16*Assumptions!$B$5</f>
-        <v>75600</v>
-      </c>
-      <c r="L20" s="21" t="n">
-        <f aca="false">L16*Assumptions!$B$5</f>
-        <v>75600</v>
-      </c>
-      <c r="M20" s="21" t="n">
-        <f aca="false">M16*Assumptions!$B$5</f>
-        <v>75600</v>
-      </c>
-      <c r="N20" s="21" t="n">
-        <f aca="false">N16*Assumptions!$B$5</f>
-        <v>75600</v>
-      </c>
-      <c r="O20" s="21" t="n">
-        <f aca="false">O16*Assumptions!$B$5</f>
-        <v>75600</v>
-      </c>
-      <c r="P20" s="21" t="n">
-        <f aca="false">P16*Assumptions!$B$5</f>
-        <v>75600</v>
-      </c>
-      <c r="Q20" s="21" t="n">
-        <f aca="false">Q16*Assumptions!$B$5</f>
-        <v>75600</v>
-      </c>
-      <c r="R20" s="21" t="n">
-        <f aca="false">R16*Assumptions!$B$5</f>
-        <v>75600</v>
-      </c>
-      <c r="S20" s="21" t="n">
-        <f aca="false">S16*Assumptions!$B$5</f>
-        <v>75600</v>
-      </c>
-      <c r="T20" s="21" t="n">
-        <f aca="false">T16*Assumptions!$B$5</f>
-        <v>75600</v>
-      </c>
-      <c r="U20" s="21" t="n">
-        <f aca="false">U16*Assumptions!$B$5</f>
-        <v>75600</v>
-      </c>
-      <c r="V20" s="21" t="n">
-        <f aca="false">V16*Assumptions!$B$5</f>
-        <v>75600</v>
-      </c>
-      <c r="W20" s="21" t="n">
-        <f aca="false">W16*Assumptions!$B$5</f>
-        <v>75600</v>
-      </c>
-      <c r="X20" s="21" t="n">
-        <f aca="false">X16*Assumptions!$B$5</f>
-        <v>75600</v>
-      </c>
-      <c r="Y20" s="21" t="n">
-        <f aca="false">Y16*Assumptions!$B$5</f>
-        <v>75600</v>
-      </c>
-      <c r="Z20" s="21" t="n">
-        <f aca="false">SUM(B20:M20)</f>
-        <v>615300</v>
-      </c>
-      <c r="AA20" s="21" t="n">
-        <f aca="false">SUM(N20:Y20)</f>
-        <v>907200</v>
-      </c>
-      <c r="AB20" s="21" t="n">
-        <f aca="false">SUM(B20:Y20)</f>
-        <v>1522500</v>
-      </c>
+      <c r="A20" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
+      <c r="R20" s="5"/>
+      <c r="S20" s="5"/>
+      <c r="T20" s="5"/>
+      <c r="U20" s="5"/>
+      <c r="V20" s="5"/>
+      <c r="W20" s="5"/>
+      <c r="X20" s="5"/>
+      <c r="Y20" s="5"/>
+      <c r="Z20" s="5"/>
+      <c r="AA20" s="5"/>
+      <c r="AB20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="B21" s="18" t="n">
-        <f aca="false">IF(1&lt;Assumptions!$B$26,0,B16/Assumptions!$B$11*Assumptions!$B$23+IF(1&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
-        <v>0</v>
-      </c>
-      <c r="C21" s="18" t="n">
-        <f aca="false">IF(2&lt;Assumptions!$B$26,0,C16/Assumptions!$B$11*Assumptions!$B$23+IF(2&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
-        <v>0</v>
-      </c>
-      <c r="D21" s="18" t="n">
-        <f aca="false">IF(3&lt;Assumptions!$B$26,0,D16/Assumptions!$B$11*Assumptions!$B$23+IF(3&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
-        <v>4.875</v>
-      </c>
-      <c r="E21" s="18" t="n">
-        <f aca="false">IF(4&lt;Assumptions!$B$26,0,E16/Assumptions!$B$11*Assumptions!$B$23+IF(4&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
-        <v>5.075</v>
-      </c>
-      <c r="F21" s="18" t="n">
-        <f aca="false">IF(5&lt;Assumptions!$B$26,0,F16/Assumptions!$B$11*Assumptions!$B$23+IF(5&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
-        <v>5.275</v>
-      </c>
-      <c r="G21" s="18" t="n">
-        <f aca="false">IF(6&lt;Assumptions!$B$26,0,G16/Assumptions!$B$11*Assumptions!$B$23+IF(6&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
-        <v>5.475</v>
-      </c>
-      <c r="H21" s="18" t="n">
-        <f aca="false">IF(7&lt;Assumptions!$B$26,0,H16/Assumptions!$B$11*Assumptions!$B$23+IF(7&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
-        <v>7.475</v>
-      </c>
-      <c r="I21" s="18" t="n">
-        <f aca="false">IF(8&lt;Assumptions!$B$26,0,I16/Assumptions!$B$11*Assumptions!$B$23+IF(8&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
-        <v>8.00833333333334</v>
-      </c>
-      <c r="J21" s="18" t="n">
-        <f aca="false">IF(9&lt;Assumptions!$B$26,0,J16/Assumptions!$B$11*Assumptions!$B$23+IF(9&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
-        <v>8.54166666666667</v>
-      </c>
-      <c r="K21" s="18" t="n">
-        <f aca="false">IF(10&lt;Assumptions!$B$26,0,K16/Assumptions!$B$11*Assumptions!$B$23+IF(10&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
-        <v>9.075</v>
-      </c>
-      <c r="L21" s="18" t="n">
-        <f aca="false">IF(11&lt;Assumptions!$B$26,0,L16/Assumptions!$B$11*Assumptions!$B$23+IF(11&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
-        <v>9.075</v>
-      </c>
-      <c r="M21" s="18" t="n">
-        <f aca="false">IF(12&lt;Assumptions!$B$26,0,M16/Assumptions!$B$11*Assumptions!$B$23+IF(12&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
-        <v>9.075</v>
-      </c>
-      <c r="N21" s="18" t="n">
-        <f aca="false">IF(13&lt;Assumptions!$B$26,0,N16/Assumptions!$B$11*Assumptions!$B$23+IF(13&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
-        <v>9.075</v>
-      </c>
-      <c r="O21" s="18" t="n">
-        <f aca="false">IF(14&lt;Assumptions!$B$26,0,O16/Assumptions!$B$11*Assumptions!$B$23+IF(14&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
-        <v>9.075</v>
-      </c>
-      <c r="P21" s="18" t="n">
-        <f aca="false">IF(15&lt;Assumptions!$B$26,0,P16/Assumptions!$B$11*Assumptions!$B$23+IF(15&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
-        <v>7.2</v>
-      </c>
-      <c r="Q21" s="18" t="n">
-        <f aca="false">IF(16&lt;Assumptions!$B$26,0,Q16/Assumptions!$B$11*Assumptions!$B$23+IF(16&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
-        <v>7.2</v>
-      </c>
-      <c r="R21" s="18" t="n">
-        <f aca="false">IF(17&lt;Assumptions!$B$26,0,R16/Assumptions!$B$11*Assumptions!$B$23+IF(17&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
-        <v>7.2</v>
-      </c>
-      <c r="S21" s="18" t="n">
-        <f aca="false">IF(18&lt;Assumptions!$B$26,0,S16/Assumptions!$B$11*Assumptions!$B$23+IF(18&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
-        <v>7.2</v>
-      </c>
-      <c r="T21" s="18" t="n">
-        <f aca="false">IF(19&lt;Assumptions!$B$26,0,T16/Assumptions!$B$11*Assumptions!$B$23+IF(19&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
-        <v>7.2</v>
-      </c>
-      <c r="U21" s="18" t="n">
-        <f aca="false">IF(20&lt;Assumptions!$B$26,0,U16/Assumptions!$B$11*Assumptions!$B$23+IF(20&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
-        <v>7.2</v>
-      </c>
-      <c r="V21" s="18" t="n">
-        <f aca="false">IF(21&lt;Assumptions!$B$26,0,V16/Assumptions!$B$11*Assumptions!$B$23+IF(21&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
-        <v>7.2</v>
-      </c>
-      <c r="W21" s="18" t="n">
-        <f aca="false">IF(22&lt;Assumptions!$B$26,0,W16/Assumptions!$B$11*Assumptions!$B$23+IF(22&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
-        <v>7.2</v>
-      </c>
-      <c r="X21" s="18" t="n">
-        <f aca="false">IF(23&lt;Assumptions!$B$26,0,X16/Assumptions!$B$11*Assumptions!$B$23+IF(23&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
-        <v>7.2</v>
-      </c>
-      <c r="Y21" s="18" t="n">
-        <f aca="false">IF(24&lt;Assumptions!$B$26,0,Y16/Assumptions!$B$11*Assumptions!$B$23+IF(24&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
-        <v>7.2</v>
-      </c>
-      <c r="Z21" s="18" t="n">
+        <v>149</v>
+      </c>
+      <c r="B21" s="21" t="n">
+        <f aca="false">B17*Assumptions!$B$5</f>
+        <v>27300</v>
+      </c>
+      <c r="C21" s="21" t="n">
+        <f aca="false">C17*Assumptions!$B$5</f>
+        <v>29400</v>
+      </c>
+      <c r="D21" s="21" t="n">
+        <f aca="false">D17*Assumptions!$B$5</f>
+        <v>31500</v>
+      </c>
+      <c r="E21" s="21" t="n">
+        <f aca="false">E17*Assumptions!$B$5</f>
+        <v>33600</v>
+      </c>
+      <c r="F21" s="21" t="n">
+        <f aca="false">F17*Assumptions!$B$5</f>
+        <v>35700</v>
+      </c>
+      <c r="G21" s="21" t="n">
+        <f aca="false">G17*Assumptions!$B$5</f>
+        <v>37800</v>
+      </c>
+      <c r="H21" s="21" t="n">
+        <f aca="false">H17*Assumptions!$B$5</f>
+        <v>58800</v>
+      </c>
+      <c r="I21" s="21" t="n">
+        <f aca="false">I17*Assumptions!$B$5</f>
+        <v>64400</v>
+      </c>
+      <c r="J21" s="21" t="n">
+        <f aca="false">J17*Assumptions!$B$5</f>
+        <v>70000</v>
+      </c>
+      <c r="K21" s="21" t="n">
+        <f aca="false">K17*Assumptions!$B$5</f>
+        <v>75600</v>
+      </c>
+      <c r="L21" s="21" t="n">
+        <f aca="false">L17*Assumptions!$B$5</f>
+        <v>75600</v>
+      </c>
+      <c r="M21" s="21" t="n">
+        <f aca="false">M17*Assumptions!$B$5</f>
+        <v>75600</v>
+      </c>
+      <c r="N21" s="21" t="n">
+        <f aca="false">N17*Assumptions!$B$5</f>
+        <v>75600</v>
+      </c>
+      <c r="O21" s="21" t="n">
+        <f aca="false">O17*Assumptions!$B$5</f>
+        <v>75600</v>
+      </c>
+      <c r="P21" s="21" t="n">
+        <f aca="false">P17*Assumptions!$B$5</f>
+        <v>75600</v>
+      </c>
+      <c r="Q21" s="21" t="n">
+        <f aca="false">Q17*Assumptions!$B$5</f>
+        <v>75600</v>
+      </c>
+      <c r="R21" s="21" t="n">
+        <f aca="false">R17*Assumptions!$B$5</f>
+        <v>75600</v>
+      </c>
+      <c r="S21" s="21" t="n">
+        <f aca="false">S17*Assumptions!$B$5</f>
+        <v>75600</v>
+      </c>
+      <c r="T21" s="21" t="n">
+        <f aca="false">T17*Assumptions!$B$5</f>
+        <v>75600</v>
+      </c>
+      <c r="U21" s="21" t="n">
+        <f aca="false">U17*Assumptions!$B$5</f>
+        <v>75600</v>
+      </c>
+      <c r="V21" s="21" t="n">
+        <f aca="false">V17*Assumptions!$B$5</f>
+        <v>75600</v>
+      </c>
+      <c r="W21" s="21" t="n">
+        <f aca="false">W17*Assumptions!$B$5</f>
+        <v>75600</v>
+      </c>
+      <c r="X21" s="21" t="n">
+        <f aca="false">X17*Assumptions!$B$5</f>
+        <v>75600</v>
+      </c>
+      <c r="Y21" s="21" t="n">
+        <f aca="false">Y17*Assumptions!$B$5</f>
+        <v>75600</v>
+      </c>
+      <c r="Z21" s="21" t="n">
         <f aca="false">SUM(B21:M21)</f>
-        <v>71.95</v>
-      </c>
-      <c r="AA21" s="18" t="n">
+        <v>615300</v>
+      </c>
+      <c r="AA21" s="21" t="n">
         <f aca="false">SUM(N21:Y21)</f>
-        <v>90.15</v>
-      </c>
-      <c r="AB21" s="18" t="n">
+        <v>907200</v>
+      </c>
+      <c r="AB21" s="21" t="n">
         <f aca="false">SUM(B21:Y21)</f>
-        <v>162.1</v>
+        <v>1522500</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B22" s="18" t="n">
-        <f aca="false">0+B21</f>
+        <f aca="false">IF(1&lt;Assumptions!$B$26,0,B17/Assumptions!$B$11*Assumptions!$B$23+IF(1&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
         <v>0</v>
       </c>
       <c r="C22" s="18" t="n">
-        <f aca="false">B22*(1-0.08/12)+C21</f>
+        <f aca="false">IF(2&lt;Assumptions!$B$26,0,C17/Assumptions!$B$11*Assumptions!$B$23+IF(2&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
         <v>0</v>
       </c>
       <c r="D22" s="18" t="n">
-        <f aca="false">C22*(1-0.08/12)+D21</f>
+        <f aca="false">IF(3&lt;Assumptions!$B$26,0,D17/Assumptions!$B$11*Assumptions!$B$23+IF(3&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
         <v>4.875</v>
       </c>
       <c r="E22" s="18" t="n">
-        <f aca="false">D22*(1-0.08/12)+E21</f>
-        <v>9.9175</v>
+        <f aca="false">IF(4&lt;Assumptions!$B$26,0,E17/Assumptions!$B$11*Assumptions!$B$23+IF(4&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
+        <v>5.075</v>
       </c>
       <c r="F22" s="18" t="n">
-        <f aca="false">E22*(1-0.08/12)+F21</f>
-        <v>15.1263833333333</v>
+        <f aca="false">IF(5&lt;Assumptions!$B$26,0,F17/Assumptions!$B$11*Assumptions!$B$23+IF(5&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
+        <v>5.275</v>
       </c>
       <c r="G22" s="18" t="n">
-        <f aca="false">F22*(1-0.08/12)+G21</f>
-        <v>20.5005407777778</v>
+        <f aca="false">IF(6&lt;Assumptions!$B$26,0,G17/Assumptions!$B$11*Assumptions!$B$23+IF(6&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
+        <v>5.475</v>
       </c>
       <c r="H22" s="18" t="n">
-        <f aca="false">G22*(1-0.08/12)+H21</f>
-        <v>27.8388705059259</v>
+        <f aca="false">IF(7&lt;Assumptions!$B$26,0,H17/Assumptions!$B$11*Assumptions!$B$23+IF(7&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
+        <v>7.475</v>
       </c>
       <c r="I22" s="18" t="n">
-        <f aca="false">H22*(1-0.08/12)+I21</f>
-        <v>35.6616113692198</v>
+        <f aca="false">IF(8&lt;Assumptions!$B$26,0,I17/Assumptions!$B$11*Assumptions!$B$23+IF(8&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
+        <v>8.00833333333334</v>
       </c>
       <c r="J22" s="18" t="n">
-        <f aca="false">I22*(1-0.08/12)+J21</f>
-        <v>43.9655339600916</v>
+        <f aca="false">IF(9&lt;Assumptions!$B$26,0,J17/Assumptions!$B$11*Assumptions!$B$23+IF(9&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
+        <v>8.54166666666667</v>
       </c>
       <c r="K22" s="18" t="n">
-        <f aca="false">J22*(1-0.08/12)+K21</f>
-        <v>52.7474304003577</v>
+        <f aca="false">IF(10&lt;Assumptions!$B$26,0,K17/Assumptions!$B$11*Assumptions!$B$23+IF(10&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
+        <v>9.075</v>
       </c>
       <c r="L22" s="18" t="n">
-        <f aca="false">K22*(1-0.08/12)+L21</f>
-        <v>61.4707808643553</v>
+        <f aca="false">IF(11&lt;Assumptions!$B$26,0,L17/Assumptions!$B$11*Assumptions!$B$23+IF(11&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
+        <v>9.075</v>
       </c>
       <c r="M22" s="18" t="n">
-        <f aca="false">L22*(1-0.08/12)+M21</f>
-        <v>70.1359756585929</v>
+        <f aca="false">IF(12&lt;Assumptions!$B$26,0,M17/Assumptions!$B$11*Assumptions!$B$23+IF(12&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
+        <v>9.075</v>
       </c>
       <c r="N22" s="18" t="n">
-        <f aca="false">M22*(1-0.08/12)+N21</f>
-        <v>78.7434024875356</v>
+        <f aca="false">IF(13&lt;Assumptions!$B$26,0,N17/Assumptions!$B$11*Assumptions!$B$23+IF(13&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
+        <v>9.075</v>
       </c>
       <c r="O22" s="18" t="n">
-        <f aca="false">N22*(1-0.08/12)+O21</f>
-        <v>87.2934464709521</v>
+        <f aca="false">IF(14&lt;Assumptions!$B$26,0,O17/Assumptions!$B$11*Assumptions!$B$23+IF(14&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
+        <v>9.075</v>
       </c>
       <c r="P22" s="18" t="n">
-        <f aca="false">O22*(1-0.08/12)+P21</f>
-        <v>93.9114901611457</v>
+        <f aca="false">IF(15&lt;Assumptions!$B$26,0,P17/Assumptions!$B$11*Assumptions!$B$23+IF(15&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
+        <v>7.2</v>
       </c>
       <c r="Q22" s="18" t="n">
-        <f aca="false">P22*(1-0.08/12)+Q21</f>
-        <v>100.485413560071</v>
+        <f aca="false">IF(16&lt;Assumptions!$B$26,0,Q17/Assumptions!$B$11*Assumptions!$B$23+IF(16&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
+        <v>7.2</v>
       </c>
       <c r="R22" s="18" t="n">
-        <f aca="false">Q22*(1-0.08/12)+R21</f>
-        <v>107.015510803004</v>
+        <f aca="false">IF(17&lt;Assumptions!$B$26,0,R17/Assumptions!$B$11*Assumptions!$B$23+IF(17&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
+        <v>7.2</v>
       </c>
       <c r="S22" s="18" t="n">
-        <f aca="false">R22*(1-0.08/12)+S21</f>
-        <v>113.502074064318</v>
+        <f aca="false">IF(18&lt;Assumptions!$B$26,0,S17/Assumptions!$B$11*Assumptions!$B$23+IF(18&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
+        <v>7.2</v>
       </c>
       <c r="T22" s="18" t="n">
-        <f aca="false">S22*(1-0.08/12)+T21</f>
-        <v>119.945393570555</v>
+        <f aca="false">IF(19&lt;Assumptions!$B$26,0,T17/Assumptions!$B$11*Assumptions!$B$23+IF(19&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
+        <v>7.2</v>
       </c>
       <c r="U22" s="18" t="n">
-        <f aca="false">T22*(1-0.08/12)+U21</f>
-        <v>126.345757613418</v>
+        <f aca="false">IF(20&lt;Assumptions!$B$26,0,U17/Assumptions!$B$11*Assumptions!$B$23+IF(20&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
+        <v>7.2</v>
       </c>
       <c r="V22" s="18" t="n">
-        <f aca="false">U22*(1-0.08/12)+V21</f>
-        <v>132.703452562662</v>
+        <f aca="false">IF(21&lt;Assumptions!$B$26,0,V17/Assumptions!$B$11*Assumptions!$B$23+IF(21&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
+        <v>7.2</v>
       </c>
       <c r="W22" s="18" t="n">
-        <f aca="false">V22*(1-0.08/12)+W21</f>
-        <v>139.018762878911</v>
+        <f aca="false">IF(22&lt;Assumptions!$B$26,0,W17/Assumptions!$B$11*Assumptions!$B$23+IF(22&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
+        <v>7.2</v>
       </c>
       <c r="X22" s="18" t="n">
-        <f aca="false">W22*(1-0.08/12)+X21</f>
-        <v>145.291971126385</v>
+        <f aca="false">IF(23&lt;Assumptions!$B$26,0,X17/Assumptions!$B$11*Assumptions!$B$23+IF(23&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
+        <v>7.2</v>
       </c>
       <c r="Y22" s="18" t="n">
-        <f aca="false">X22*(1-0.08/12)+Y21</f>
-        <v>151.523357985543</v>
-      </c>
-      <c r="Z22" s="2"/>
-      <c r="AA22" s="2"/>
-      <c r="AB22" s="2"/>
+        <f aca="false">IF(24&lt;Assumptions!$B$26,0,Y17/Assumptions!$B$11*Assumptions!$B$23+IF(24&lt;=Assumptions!$B$26+11,Assumptions!$B$24*Assumptions!$B$25/12,0))</f>
+        <v>7.2</v>
+      </c>
+      <c r="Z22" s="18" t="n">
+        <f aca="false">SUM(B22:M22)</f>
+        <v>71.95</v>
+      </c>
+      <c r="AA22" s="18" t="n">
+        <f aca="false">SUM(N22:Y22)</f>
+        <v>90.15</v>
+      </c>
+      <c r="AB22" s="18" t="n">
+        <f aca="false">SUM(B22:Y22)</f>
+        <v>162.1</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="B23" s="21" t="n">
-        <f aca="false">B22/12/Assumptions!$B$22*Assumptions!$B$21</f>
-        <v>0</v>
-      </c>
-      <c r="C23" s="21" t="n">
-        <f aca="false">C22/12/Assumptions!$B$22*Assumptions!$B$21</f>
-        <v>0</v>
-      </c>
-      <c r="D23" s="21" t="n">
-        <f aca="false">D22/12/Assumptions!$B$22*Assumptions!$B$21</f>
+        <v>151</v>
+      </c>
+      <c r="B23" s="18" t="n">
+        <f aca="false">0+B22</f>
+        <v>0</v>
+      </c>
+      <c r="C23" s="18" t="n">
+        <f aca="false">B23*(1-0.08/12)+C22</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="18" t="n">
+        <f aca="false">C23*(1-0.08/12)+D22</f>
+        <v>4.875</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <f aca="false">D23*(1-0.08/12)+E22</f>
+        <v>9.9175</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <f aca="false">E23*(1-0.08/12)+F22</f>
+        <v>15.1263833333333</v>
+      </c>
+      <c r="G23" s="18" t="n">
+        <f aca="false">F23*(1-0.08/12)+G22</f>
+        <v>20.5005407777778</v>
+      </c>
+      <c r="H23" s="18" t="n">
+        <f aca="false">G23*(1-0.08/12)+H22</f>
+        <v>27.8388705059259</v>
+      </c>
+      <c r="I23" s="18" t="n">
+        <f aca="false">H23*(1-0.08/12)+I22</f>
+        <v>35.6616113692198</v>
+      </c>
+      <c r="J23" s="18" t="n">
+        <f aca="false">I23*(1-0.08/12)+J22</f>
+        <v>43.9655339600916</v>
+      </c>
+      <c r="K23" s="18" t="n">
+        <f aca="false">J23*(1-0.08/12)+K22</f>
+        <v>52.7474304003577</v>
+      </c>
+      <c r="L23" s="18" t="n">
+        <f aca="false">K23*(1-0.08/12)+L22</f>
+        <v>61.4707808643553</v>
+      </c>
+      <c r="M23" s="18" t="n">
+        <f aca="false">L23*(1-0.08/12)+M22</f>
+        <v>70.1359756585929</v>
+      </c>
+      <c r="N23" s="18" t="n">
+        <f aca="false">M23*(1-0.08/12)+N22</f>
+        <v>78.7434024875356</v>
+      </c>
+      <c r="O23" s="18" t="n">
+        <f aca="false">N23*(1-0.08/12)+O22</f>
+        <v>87.2934464709521</v>
+      </c>
+      <c r="P23" s="18" t="n">
+        <f aca="false">O23*(1-0.08/12)+P22</f>
+        <v>93.9114901611457</v>
+      </c>
+      <c r="Q23" s="18" t="n">
+        <f aca="false">P23*(1-0.08/12)+Q22</f>
+        <v>100.485413560071</v>
+      </c>
+      <c r="R23" s="18" t="n">
+        <f aca="false">Q23*(1-0.08/12)+R22</f>
+        <v>107.015510803004</v>
+      </c>
+      <c r="S23" s="18" t="n">
+        <f aca="false">R23*(1-0.08/12)+S22</f>
+        <v>113.502074064318</v>
+      </c>
+      <c r="T23" s="18" t="n">
+        <f aca="false">S23*(1-0.08/12)+T22</f>
+        <v>119.945393570555</v>
+      </c>
+      <c r="U23" s="18" t="n">
+        <f aca="false">T23*(1-0.08/12)+U22</f>
+        <v>126.345757613418</v>
+      </c>
+      <c r="V23" s="18" t="n">
+        <f aca="false">U23*(1-0.08/12)+V22</f>
+        <v>132.703452562662</v>
+      </c>
+      <c r="W23" s="18" t="n">
+        <f aca="false">V23*(1-0.08/12)+W22</f>
+        <v>139.018762878911</v>
+      </c>
+      <c r="X23" s="18" t="n">
+        <f aca="false">W23*(1-0.08/12)+X22</f>
+        <v>145.291971126385</v>
+      </c>
+      <c r="Y23" s="18" t="n">
+        <f aca="false">X23*(1-0.08/12)+Y22</f>
+        <v>151.523357985543</v>
+      </c>
+      <c r="Z23" s="2"/>
+      <c r="AA23" s="2"/>
+      <c r="AB23" s="2"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="B24" s="21" t="n">
+        <f aca="false">B23/12/Assumptions!$B$22*Assumptions!$B$21</f>
+        <v>0</v>
+      </c>
+      <c r="C24" s="21" t="n">
+        <f aca="false">C23/12/Assumptions!$B$22*Assumptions!$B$21</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="21" t="n">
+        <f aca="false">D23/12/Assumptions!$B$22*Assumptions!$B$21</f>
         <v>101.15625</v>
       </c>
-      <c r="E23" s="21" t="n">
-        <f aca="false">E22/12/Assumptions!$B$22*Assumptions!$B$21</f>
+      <c r="E24" s="21" t="n">
+        <f aca="false">E23/12/Assumptions!$B$22*Assumptions!$B$21</f>
         <v>205.788125</v>
       </c>
-      <c r="F23" s="21" t="n">
-        <f aca="false">F22/12/Assumptions!$B$22*Assumptions!$B$21</f>
+      <c r="F24" s="21" t="n">
+        <f aca="false">F23/12/Assumptions!$B$22*Assumptions!$B$21</f>
         <v>313.872454166667</v>
       </c>
-      <c r="G23" s="21" t="n">
-        <f aca="false">G22/12/Assumptions!$B$22*Assumptions!$B$21</f>
+      <c r="G24" s="21" t="n">
+        <f aca="false">G23/12/Assumptions!$B$22*Assumptions!$B$21</f>
         <v>425.386221138889</v>
       </c>
-      <c r="H23" s="21" t="n">
-        <f aca="false">H22/12/Assumptions!$B$22*Assumptions!$B$21</f>
+      <c r="H24" s="21" t="n">
+        <f aca="false">H23/12/Assumptions!$B$22*Assumptions!$B$21</f>
         <v>577.656562997963</v>
       </c>
-      <c r="I23" s="21" t="n">
-        <f aca="false">I22/12/Assumptions!$B$22*Assumptions!$B$21</f>
+      <c r="I24" s="21" t="n">
+        <f aca="false">I23/12/Assumptions!$B$22*Assumptions!$B$21</f>
         <v>739.97843591131</v>
       </c>
-      <c r="J23" s="21" t="n">
-        <f aca="false">J22/12/Assumptions!$B$22*Assumptions!$B$21</f>
+      <c r="J24" s="21" t="n">
+        <f aca="false">J23/12/Assumptions!$B$22*Assumptions!$B$21</f>
         <v>912.284829671901</v>
       </c>
-      <c r="K23" s="21" t="n">
-        <f aca="false">K22/12/Assumptions!$B$22*Assumptions!$B$21</f>
+      <c r="K24" s="21" t="n">
+        <f aca="false">K23/12/Assumptions!$B$22*Assumptions!$B$21</f>
         <v>1094.50918080742</v>
       </c>
-      <c r="L23" s="21" t="n">
-        <f aca="false">L22/12/Assumptions!$B$22*Assumptions!$B$21</f>
+      <c r="L24" s="21" t="n">
+        <f aca="false">L23/12/Assumptions!$B$22*Assumptions!$B$21</f>
         <v>1275.51870293537</v>
       </c>
-      <c r="M23" s="21" t="n">
-        <f aca="false">M22/12/Assumptions!$B$22*Assumptions!$B$21</f>
+      <c r="M24" s="21" t="n">
+        <f aca="false">M23/12/Assumptions!$B$22*Assumptions!$B$21</f>
         <v>1455.3214949158</v>
       </c>
-      <c r="N23" s="21" t="n">
-        <f aca="false">N22/12/Assumptions!$B$22*Assumptions!$B$21</f>
+      <c r="N24" s="21" t="n">
+        <f aca="false">N23/12/Assumptions!$B$22*Assumptions!$B$21</f>
         <v>1633.92560161636</v>
       </c>
-      <c r="O23" s="21" t="n">
-        <f aca="false">O22/12/Assumptions!$B$22*Assumptions!$B$21</f>
+      <c r="O24" s="21" t="n">
+        <f aca="false">O23/12/Assumptions!$B$22*Assumptions!$B$21</f>
         <v>1811.33901427225</v>
       </c>
-      <c r="P23" s="21" t="n">
-        <f aca="false">P22/12/Assumptions!$B$22*Assumptions!$B$21</f>
+      <c r="P24" s="21" t="n">
+        <f aca="false">P23/12/Assumptions!$B$22*Assumptions!$B$21</f>
         <v>1948.66342084377</v>
       </c>
-      <c r="Q23" s="21" t="n">
-        <f aca="false">Q22/12/Assumptions!$B$22*Assumptions!$B$21</f>
+      <c r="Q24" s="21" t="n">
+        <f aca="false">Q23/12/Assumptions!$B$22*Assumptions!$B$21</f>
         <v>2085.07233137148</v>
       </c>
-      <c r="R23" s="21" t="n">
-        <f aca="false">R22/12/Assumptions!$B$22*Assumptions!$B$21</f>
+      <c r="R24" s="21" t="n">
+        <f aca="false">R23/12/Assumptions!$B$22*Assumptions!$B$21</f>
         <v>2220.57184916234</v>
       </c>
-      <c r="S23" s="21" t="n">
-        <f aca="false">S22/12/Assumptions!$B$22*Assumptions!$B$21</f>
+      <c r="S24" s="21" t="n">
+        <f aca="false">S23/12/Assumptions!$B$22*Assumptions!$B$21</f>
         <v>2355.16803683459</v>
       </c>
-      <c r="T23" s="21" t="n">
-        <f aca="false">T22/12/Assumptions!$B$22*Assumptions!$B$21</f>
+      <c r="T24" s="21" t="n">
+        <f aca="false">T23/12/Assumptions!$B$22*Assumptions!$B$21</f>
         <v>2488.86691658903</v>
       </c>
-      <c r="U23" s="21" t="n">
-        <f aca="false">U22/12/Assumptions!$B$22*Assumptions!$B$21</f>
+      <c r="U24" s="21" t="n">
+        <f aca="false">U23/12/Assumptions!$B$22*Assumptions!$B$21</f>
         <v>2621.67447047843</v>
       </c>
-      <c r="V23" s="21" t="n">
-        <f aca="false">V22/12/Assumptions!$B$22*Assumptions!$B$21</f>
+      <c r="V24" s="21" t="n">
+        <f aca="false">V23/12/Assumptions!$B$22*Assumptions!$B$21</f>
         <v>2753.59664067524</v>
       </c>
-      <c r="W23" s="21" t="n">
-        <f aca="false">W22/12/Assumptions!$B$22*Assumptions!$B$21</f>
+      <c r="W24" s="21" t="n">
+        <f aca="false">W23/12/Assumptions!$B$22*Assumptions!$B$21</f>
         <v>2884.63932973741</v>
       </c>
-      <c r="X23" s="21" t="n">
-        <f aca="false">X22/12/Assumptions!$B$22*Assumptions!$B$21</f>
+      <c r="X24" s="21" t="n">
+        <f aca="false">X23/12/Assumptions!$B$22*Assumptions!$B$21</f>
         <v>3014.80840087249</v>
       </c>
-      <c r="Y23" s="21" t="n">
-        <f aca="false">Y22/12/Assumptions!$B$22*Assumptions!$B$21</f>
+      <c r="Y24" s="21" t="n">
+        <f aca="false">Y23/12/Assumptions!$B$22*Assumptions!$B$21</f>
         <v>3144.10967820001</v>
       </c>
-      <c r="Z23" s="21" t="n">
-        <f aca="false">SUM(B23:M23)</f>
+      <c r="Z24" s="21" t="n">
+        <f aca="false">SUM(B24:M24)</f>
         <v>7101.47225754533</v>
       </c>
-      <c r="AA23" s="21" t="n">
-        <f aca="false">SUM(N23:Y23)</f>
+      <c r="AA24" s="21" t="n">
+        <f aca="false">SUM(N24:Y24)</f>
         <v>28962.4356906534</v>
       </c>
-      <c r="AB23" s="21" t="n">
-        <f aca="false">SUM(B23:Y23)</f>
+      <c r="AB24" s="21" t="n">
+        <f aca="false">SUM(B24:Y24)</f>
         <v>36063.9079481987</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="B24" s="22" t="n">
-        <f aca="false">B20+B23</f>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="B25" s="22" t="n">
+        <f aca="false">B21+B24</f>
         <v>27300</v>
       </c>
-      <c r="C24" s="22" t="n">
-        <f aca="false">C20+C23</f>
+      <c r="C25" s="22" t="n">
+        <f aca="false">C21+C24</f>
         <v>29400</v>
       </c>
-      <c r="D24" s="22" t="n">
-        <f aca="false">D20+D23</f>
+      <c r="D25" s="22" t="n">
+        <f aca="false">D21+D24</f>
         <v>31601.15625</v>
       </c>
-      <c r="E24" s="22" t="n">
-        <f aca="false">E20+E23</f>
+      <c r="E25" s="22" t="n">
+        <f aca="false">E21+E24</f>
         <v>33805.788125</v>
       </c>
-      <c r="F24" s="22" t="n">
-        <f aca="false">F20+F23</f>
+      <c r="F25" s="22" t="n">
+        <f aca="false">F21+F24</f>
         <v>36013.8724541667</v>
       </c>
-      <c r="G24" s="22" t="n">
-        <f aca="false">G20+G23</f>
+      <c r="G25" s="22" t="n">
+        <f aca="false">G21+G24</f>
         <v>38225.3862211389</v>
       </c>
-      <c r="H24" s="22" t="n">
-        <f aca="false">H20+H23</f>
+      <c r="H25" s="22" t="n">
+        <f aca="false">H21+H24</f>
         <v>59377.656562998</v>
       </c>
-      <c r="I24" s="22" t="n">
-        <f aca="false">I20+I23</f>
+      <c r="I25" s="22" t="n">
+        <f aca="false">I21+I24</f>
         <v>65139.9784359113</v>
       </c>
-      <c r="J24" s="22" t="n">
-        <f aca="false">J20+J23</f>
+      <c r="J25" s="22" t="n">
+        <f aca="false">J21+J24</f>
         <v>70912.2848296719</v>
       </c>
-      <c r="K24" s="22" t="n">
-        <f aca="false">K20+K23</f>
+      <c r="K25" s="22" t="n">
+        <f aca="false">K21+K24</f>
         <v>76694.5091808074</v>
       </c>
-      <c r="L24" s="22" t="n">
-        <f aca="false">L20+L23</f>
+      <c r="L25" s="22" t="n">
+        <f aca="false">L21+L24</f>
         <v>76875.5187029354</v>
       </c>
-      <c r="M24" s="22" t="n">
-        <f aca="false">M20+M23</f>
+      <c r="M25" s="22" t="n">
+        <f aca="false">M21+M24</f>
         <v>77055.3214949158</v>
       </c>
-      <c r="N24" s="22" t="n">
-        <f aca="false">N20+N23</f>
+      <c r="N25" s="22" t="n">
+        <f aca="false">N21+N24</f>
         <v>77233.9256016164</v>
       </c>
-      <c r="O24" s="22" t="n">
-        <f aca="false">O20+O23</f>
+      <c r="O25" s="22" t="n">
+        <f aca="false">O21+O24</f>
         <v>77411.3390142723</v>
       </c>
-      <c r="P24" s="22" t="n">
-        <f aca="false">P20+P23</f>
+      <c r="P25" s="22" t="n">
+        <f aca="false">P21+P24</f>
         <v>77548.6634208438</v>
       </c>
-      <c r="Q24" s="22" t="n">
-        <f aca="false">Q20+Q23</f>
+      <c r="Q25" s="22" t="n">
+        <f aca="false">Q21+Q24</f>
         <v>77685.0723313715</v>
       </c>
-      <c r="R24" s="22" t="n">
-        <f aca="false">R20+R23</f>
+      <c r="R25" s="22" t="n">
+        <f aca="false">R21+R24</f>
         <v>77820.5718491623</v>
       </c>
-      <c r="S24" s="22" t="n">
-        <f aca="false">S20+S23</f>
+      <c r="S25" s="22" t="n">
+        <f aca="false">S21+S24</f>
         <v>77955.1680368346</v>
       </c>
-      <c r="T24" s="22" t="n">
-        <f aca="false">T20+T23</f>
+      <c r="T25" s="22" t="n">
+        <f aca="false">T21+T24</f>
         <v>78088.866916589</v>
       </c>
-      <c r="U24" s="22" t="n">
-        <f aca="false">U20+U23</f>
+      <c r="U25" s="22" t="n">
+        <f aca="false">U21+U24</f>
         <v>78221.6744704784</v>
       </c>
-      <c r="V24" s="22" t="n">
-        <f aca="false">V20+V23</f>
+      <c r="V25" s="22" t="n">
+        <f aca="false">V21+V24</f>
         <v>78353.5966406752</v>
       </c>
-      <c r="W24" s="22" t="n">
-        <f aca="false">W20+W23</f>
+      <c r="W25" s="22" t="n">
+        <f aca="false">W21+W24</f>
         <v>78484.6393297374</v>
       </c>
-      <c r="X24" s="22" t="n">
-        <f aca="false">X20+X23</f>
+      <c r="X25" s="22" t="n">
+        <f aca="false">X21+X24</f>
         <v>78614.8084008725</v>
       </c>
-      <c r="Y24" s="22" t="n">
-        <f aca="false">Y20+Y23</f>
+      <c r="Y25" s="22" t="n">
+        <f aca="false">Y21+Y24</f>
         <v>78744.1096782</v>
       </c>
-      <c r="Z24" s="23" t="n">
-        <f aca="false">SUM(B24:M24)</f>
+      <c r="Z25" s="23" t="n">
+        <f aca="false">SUM(B25:M25)</f>
         <v>622401.472257545</v>
       </c>
-      <c r="AA24" s="23" t="n">
-        <f aca="false">SUM(N24:Y24)</f>
+      <c r="AA25" s="23" t="n">
+        <f aca="false">SUM(N25:Y25)</f>
         <v>936162.435690653</v>
       </c>
-      <c r="AB24" s="23" t="n">
-        <f aca="false">SUM(B24:Y24)</f>
+      <c r="AB25" s="23" t="n">
+        <f aca="false">SUM(B25:Y25)</f>
         <v>1558563.9079482</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="5"/>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="5"/>
-      <c r="R25" s="5"/>
-      <c r="S25" s="5"/>
-      <c r="T25" s="5"/>
-      <c r="U25" s="5"/>
-      <c r="V25" s="5"/>
-      <c r="W25" s="5"/>
-      <c r="X25" s="5"/>
-      <c r="Y25" s="5"/>
-      <c r="Z25" s="5"/>
-      <c r="AA25" s="5"/>
-      <c r="AB25" s="5"/>
-    </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="B26" s="21" t="n">
-        <f aca="false">B20*Assumptions!$B$14</f>
-        <v>8736</v>
-      </c>
-      <c r="C26" s="21" t="n">
-        <f aca="false">C20*Assumptions!$B$14</f>
-        <v>9408</v>
-      </c>
-      <c r="D26" s="21" t="n">
-        <f aca="false">D20*Assumptions!$B$14</f>
-        <v>10080</v>
-      </c>
-      <c r="E26" s="21" t="n">
-        <f aca="false">E20*Assumptions!$B$14</f>
-        <v>10752</v>
-      </c>
-      <c r="F26" s="21" t="n">
-        <f aca="false">F20*Assumptions!$B$14</f>
-        <v>11424</v>
-      </c>
-      <c r="G26" s="21" t="n">
-        <f aca="false">G20*Assumptions!$B$14</f>
-        <v>12096</v>
-      </c>
-      <c r="H26" s="21" t="n">
-        <f aca="false">H20*Assumptions!$B$14</f>
-        <v>18816</v>
-      </c>
-      <c r="I26" s="21" t="n">
-        <f aca="false">I20*Assumptions!$B$14</f>
-        <v>20608</v>
-      </c>
-      <c r="J26" s="21" t="n">
-        <f aca="false">J20*Assumptions!$B$14</f>
-        <v>22400</v>
-      </c>
-      <c r="K26" s="21" t="n">
-        <f aca="false">K20*Assumptions!$B$14</f>
-        <v>24192</v>
-      </c>
-      <c r="L26" s="21" t="n">
-        <f aca="false">L20*Assumptions!$B$14</f>
-        <v>24192</v>
-      </c>
-      <c r="M26" s="21" t="n">
-        <f aca="false">M20*Assumptions!$B$14</f>
-        <v>24192</v>
-      </c>
-      <c r="N26" s="21" t="n">
-        <f aca="false">N20*Assumptions!$B$14</f>
-        <v>24192</v>
-      </c>
-      <c r="O26" s="21" t="n">
-        <f aca="false">O20*Assumptions!$B$14</f>
-        <v>24192</v>
-      </c>
-      <c r="P26" s="21" t="n">
-        <f aca="false">P20*Assumptions!$B$14</f>
-        <v>24192</v>
-      </c>
-      <c r="Q26" s="21" t="n">
-        <f aca="false">Q20*Assumptions!$B$14</f>
-        <v>24192</v>
-      </c>
-      <c r="R26" s="21" t="n">
-        <f aca="false">R20*Assumptions!$B$14</f>
-        <v>24192</v>
-      </c>
-      <c r="S26" s="21" t="n">
-        <f aca="false">S20*Assumptions!$B$14</f>
-        <v>24192</v>
-      </c>
-      <c r="T26" s="21" t="n">
-        <f aca="false">T20*Assumptions!$B$14</f>
-        <v>24192</v>
-      </c>
-      <c r="U26" s="21" t="n">
-        <f aca="false">U20*Assumptions!$B$14</f>
-        <v>24192</v>
-      </c>
-      <c r="V26" s="21" t="n">
-        <f aca="false">V20*Assumptions!$B$14</f>
-        <v>24192</v>
-      </c>
-      <c r="W26" s="21" t="n">
-        <f aca="false">W20*Assumptions!$B$14</f>
-        <v>24192</v>
-      </c>
-      <c r="X26" s="21" t="n">
-        <f aca="false">X20*Assumptions!$B$14</f>
-        <v>24192</v>
-      </c>
-      <c r="Y26" s="21" t="n">
-        <f aca="false">Y20*Assumptions!$B$14</f>
-        <v>24192</v>
-      </c>
-      <c r="Z26" s="21" t="n">
-        <f aca="false">SUM(B26:M26)</f>
-        <v>196896</v>
-      </c>
-      <c r="AA26" s="21" t="n">
-        <f aca="false">SUM(N26:Y26)</f>
-        <v>290304</v>
-      </c>
-      <c r="AB26" s="21" t="n">
-        <f aca="false">SUM(B26:Y26)</f>
-        <v>487200</v>
-      </c>
+      <c r="A26" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="5"/>
+      <c r="R26" s="5"/>
+      <c r="S26" s="5"/>
+      <c r="T26" s="5"/>
+      <c r="U26" s="5"/>
+      <c r="V26" s="5"/>
+      <c r="W26" s="5"/>
+      <c r="X26" s="5"/>
+      <c r="Y26" s="5"/>
+      <c r="Z26" s="5"/>
+      <c r="AA26" s="5"/>
+      <c r="AB26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="17" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B27" s="21" t="n">
-        <f aca="false">B20*Assumptions!$B$15</f>
-        <v>5460</v>
+        <f aca="false">B21*Assumptions!$B$14</f>
+        <v>8736</v>
       </c>
       <c r="C27" s="21" t="n">
-        <f aca="false">C20*Assumptions!$B$15</f>
-        <v>5880</v>
+        <f aca="false">C21*Assumptions!$B$14</f>
+        <v>9408</v>
       </c>
       <c r="D27" s="21" t="n">
-        <f aca="false">D20*Assumptions!$B$15</f>
-        <v>6300</v>
+        <f aca="false">D21*Assumptions!$B$14</f>
+        <v>10080</v>
       </c>
       <c r="E27" s="21" t="n">
-        <f aca="false">E20*Assumptions!$B$15</f>
-        <v>6720</v>
+        <f aca="false">E21*Assumptions!$B$14</f>
+        <v>10752</v>
       </c>
       <c r="F27" s="21" t="n">
-        <f aca="false">F20*Assumptions!$B$15</f>
-        <v>7140</v>
+        <f aca="false">F21*Assumptions!$B$14</f>
+        <v>11424</v>
       </c>
       <c r="G27" s="21" t="n">
-        <f aca="false">G20*Assumptions!$B$15</f>
-        <v>7560</v>
+        <f aca="false">G21*Assumptions!$B$14</f>
+        <v>12096</v>
       </c>
       <c r="H27" s="21" t="n">
-        <f aca="false">H20*Assumptions!$B$15</f>
-        <v>11760</v>
+        <f aca="false">H21*Assumptions!$B$14</f>
+        <v>18816</v>
       </c>
       <c r="I27" s="21" t="n">
-        <f aca="false">I20*Assumptions!$B$15</f>
-        <v>12880</v>
+        <f aca="false">I21*Assumptions!$B$14</f>
+        <v>20608</v>
       </c>
       <c r="J27" s="21" t="n">
-        <f aca="false">J20*Assumptions!$B$15</f>
-        <v>14000</v>
+        <f aca="false">J21*Assumptions!$B$14</f>
+        <v>22400</v>
       </c>
       <c r="K27" s="21" t="n">
-        <f aca="false">K20*Assumptions!$B$15</f>
-        <v>15120</v>
+        <f aca="false">K21*Assumptions!$B$14</f>
+        <v>24192</v>
       </c>
       <c r="L27" s="21" t="n">
-        <f aca="false">L20*Assumptions!$B$15</f>
-        <v>15120</v>
+        <f aca="false">L21*Assumptions!$B$14</f>
+        <v>24192</v>
       </c>
       <c r="M27" s="21" t="n">
-        <f aca="false">M20*Assumptions!$B$15</f>
-        <v>15120</v>
+        <f aca="false">M21*Assumptions!$B$14</f>
+        <v>24192</v>
       </c>
       <c r="N27" s="21" t="n">
-        <f aca="false">N20*Assumptions!$B$15</f>
-        <v>15120</v>
+        <f aca="false">N21*Assumptions!$B$14</f>
+        <v>24192</v>
       </c>
       <c r="O27" s="21" t="n">
-        <f aca="false">O20*Assumptions!$B$15</f>
-        <v>15120</v>
+        <f aca="false">O21*Assumptions!$B$14</f>
+        <v>24192</v>
       </c>
       <c r="P27" s="21" t="n">
-        <f aca="false">P20*Assumptions!$B$15</f>
-        <v>15120</v>
+        <f aca="false">P21*Assumptions!$B$14</f>
+        <v>24192</v>
       </c>
       <c r="Q27" s="21" t="n">
-        <f aca="false">Q20*Assumptions!$B$15</f>
-        <v>15120</v>
+        <f aca="false">Q21*Assumptions!$B$14</f>
+        <v>24192</v>
       </c>
       <c r="R27" s="21" t="n">
-        <f aca="false">R20*Assumptions!$B$15</f>
-        <v>15120</v>
+        <f aca="false">R21*Assumptions!$B$14</f>
+        <v>24192</v>
       </c>
       <c r="S27" s="21" t="n">
-        <f aca="false">S20*Assumptions!$B$15</f>
-        <v>15120</v>
+        <f aca="false">S21*Assumptions!$B$14</f>
+        <v>24192</v>
       </c>
       <c r="T27" s="21" t="n">
-        <f aca="false">T20*Assumptions!$B$15</f>
-        <v>15120</v>
+        <f aca="false">T21*Assumptions!$B$14</f>
+        <v>24192</v>
       </c>
       <c r="U27" s="21" t="n">
-        <f aca="false">U20*Assumptions!$B$15</f>
-        <v>15120</v>
+        <f aca="false">U21*Assumptions!$B$14</f>
+        <v>24192</v>
       </c>
       <c r="V27" s="21" t="n">
-        <f aca="false">V20*Assumptions!$B$15</f>
-        <v>15120</v>
+        <f aca="false">V21*Assumptions!$B$14</f>
+        <v>24192</v>
       </c>
       <c r="W27" s="21" t="n">
-        <f aca="false">W20*Assumptions!$B$15</f>
-        <v>15120</v>
+        <f aca="false">W21*Assumptions!$B$14</f>
+        <v>24192</v>
       </c>
       <c r="X27" s="21" t="n">
-        <f aca="false">X20*Assumptions!$B$15</f>
-        <v>15120</v>
+        <f aca="false">X21*Assumptions!$B$14</f>
+        <v>24192</v>
       </c>
       <c r="Y27" s="21" t="n">
-        <f aca="false">Y20*Assumptions!$B$15</f>
-        <v>15120</v>
+        <f aca="false">Y21*Assumptions!$B$14</f>
+        <v>24192</v>
       </c>
       <c r="Z27" s="21" t="n">
         <f aca="false">SUM(B27:M27)</f>
-        <v>123060</v>
+        <v>196896</v>
       </c>
       <c r="AA27" s="21" t="n">
         <f aca="false">SUM(N27:Y27)</f>
-        <v>181440</v>
+        <v>290304</v>
       </c>
       <c r="AB27" s="21" t="n">
         <f aca="false">SUM(B27:Y27)</f>
-        <v>304500</v>
+        <v>487200</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="17" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B28" s="21" t="n">
-        <f aca="false">B22/12/Assumptions!$B$22*Assumptions!$B$27</f>
-        <v>0</v>
+        <f aca="false">B21*Assumptions!$B$15</f>
+        <v>5460</v>
       </c>
       <c r="C28" s="21" t="n">
-        <f aca="false">C22/12/Assumptions!$B$22*Assumptions!$B$27</f>
-        <v>0</v>
+        <f aca="false">C21*Assumptions!$B$15</f>
+        <v>5880</v>
       </c>
       <c r="D28" s="21" t="n">
-        <f aca="false">D22/12/Assumptions!$B$22*Assumptions!$B$27</f>
-        <v>28.4375</v>
+        <f aca="false">D21*Assumptions!$B$15</f>
+        <v>6300</v>
       </c>
       <c r="E28" s="21" t="n">
-        <f aca="false">E22/12/Assumptions!$B$22*Assumptions!$B$27</f>
-        <v>57.8520833333333</v>
+        <f aca="false">E21*Assumptions!$B$15</f>
+        <v>6720</v>
       </c>
       <c r="F28" s="21" t="n">
-        <f aca="false">F22/12/Assumptions!$B$22*Assumptions!$B$27</f>
-        <v>88.2372361111111</v>
+        <f aca="false">F21*Assumptions!$B$15</f>
+        <v>7140</v>
       </c>
       <c r="G28" s="21" t="n">
-        <f aca="false">G22/12/Assumptions!$B$22*Assumptions!$B$27</f>
-        <v>119.58648787037</v>
+        <f aca="false">G21*Assumptions!$B$15</f>
+        <v>7560</v>
       </c>
       <c r="H28" s="21" t="n">
-        <f aca="false">H22/12/Assumptions!$B$22*Assumptions!$B$27</f>
-        <v>162.393411284568</v>
+        <f aca="false">H21*Assumptions!$B$15</f>
+        <v>11760</v>
       </c>
       <c r="I28" s="21" t="n">
-        <f aca="false">I22/12/Assumptions!$B$22*Assumptions!$B$27</f>
-        <v>208.026066320449</v>
+        <f aca="false">I21*Assumptions!$B$15</f>
+        <v>12880</v>
       </c>
       <c r="J28" s="21" t="n">
-        <f aca="false">J22/12/Assumptions!$B$22*Assumptions!$B$27</f>
-        <v>256.465614767201</v>
+        <f aca="false">J21*Assumptions!$B$15</f>
+        <v>14000</v>
       </c>
       <c r="K28" s="21" t="n">
-        <f aca="false">K22/12/Assumptions!$B$22*Assumptions!$B$27</f>
-        <v>307.693344002086</v>
+        <f aca="false">K21*Assumptions!$B$15</f>
+        <v>15120</v>
       </c>
       <c r="L28" s="21" t="n">
-        <f aca="false">L22/12/Assumptions!$B$22*Assumptions!$B$27</f>
-        <v>358.579555042073</v>
+        <f aca="false">L21*Assumptions!$B$15</f>
+        <v>15120</v>
       </c>
       <c r="M28" s="21" t="n">
-        <f aca="false">M22/12/Assumptions!$B$22*Assumptions!$B$27</f>
-        <v>409.126524675125</v>
+        <f aca="false">M21*Assumptions!$B$15</f>
+        <v>15120</v>
       </c>
       <c r="N28" s="21" t="n">
-        <f aca="false">N22/12/Assumptions!$B$22*Assumptions!$B$27</f>
-        <v>459.336514510624</v>
+        <f aca="false">N21*Assumptions!$B$15</f>
+        <v>15120</v>
       </c>
       <c r="O28" s="21" t="n">
-        <f aca="false">O22/12/Assumptions!$B$22*Assumptions!$B$27</f>
-        <v>509.211771080554</v>
+        <f aca="false">O21*Assumptions!$B$15</f>
+        <v>15120</v>
       </c>
       <c r="P28" s="21" t="n">
-        <f aca="false">P22/12/Assumptions!$B$22*Assumptions!$B$27</f>
-        <v>547.817025940017</v>
+        <f aca="false">P21*Assumptions!$B$15</f>
+        <v>15120</v>
       </c>
       <c r="Q28" s="21" t="n">
-        <f aca="false">Q22/12/Assumptions!$B$22*Assumptions!$B$27</f>
-        <v>586.16491243375</v>
+        <f aca="false">Q21*Assumptions!$B$15</f>
+        <v>15120</v>
       </c>
       <c r="R28" s="21" t="n">
-        <f aca="false">R22/12/Assumptions!$B$22*Assumptions!$B$27</f>
-        <v>624.257146350858</v>
+        <f aca="false">R21*Assumptions!$B$15</f>
+        <v>15120</v>
       </c>
       <c r="S28" s="21" t="n">
-        <f aca="false">S22/12/Assumptions!$B$22*Assumptions!$B$27</f>
-        <v>662.095432041853</v>
+        <f aca="false">S21*Assumptions!$B$15</f>
+        <v>15120</v>
       </c>
       <c r="T28" s="21" t="n">
-        <f aca="false">T22/12/Assumptions!$B$22*Assumptions!$B$27</f>
-        <v>699.681462494907</v>
+        <f aca="false">T21*Assumptions!$B$15</f>
+        <v>15120</v>
       </c>
       <c r="U28" s="21" t="n">
-        <f aca="false">U22/12/Assumptions!$B$22*Assumptions!$B$27</f>
-        <v>737.016919411607</v>
+        <f aca="false">U21*Assumptions!$B$15</f>
+        <v>15120</v>
       </c>
       <c r="V28" s="21" t="n">
-        <f aca="false">V22/12/Assumptions!$B$22*Assumptions!$B$27</f>
-        <v>774.103473282197</v>
+        <f aca="false">V21*Assumptions!$B$15</f>
+        <v>15120</v>
       </c>
       <c r="W28" s="21" t="n">
-        <f aca="false">W22/12/Assumptions!$B$22*Assumptions!$B$27</f>
-        <v>810.942783460315</v>
+        <f aca="false">W21*Assumptions!$B$15</f>
+        <v>15120</v>
       </c>
       <c r="X28" s="21" t="n">
-        <f aca="false">X22/12/Assumptions!$B$22*Assumptions!$B$27</f>
-        <v>847.536498237246</v>
+        <f aca="false">X21*Assumptions!$B$15</f>
+        <v>15120</v>
       </c>
       <c r="Y28" s="21" t="n">
-        <f aca="false">Y22/12/Assumptions!$B$22*Assumptions!$B$27</f>
-        <v>883.886254915665</v>
+        <f aca="false">Y21*Assumptions!$B$15</f>
+        <v>15120</v>
       </c>
       <c r="Z28" s="21" t="n">
         <f aca="false">SUM(B28:M28)</f>
-        <v>1996.39782340632</v>
+        <v>123060</v>
       </c>
       <c r="AA28" s="21" t="n">
         <f aca="false">SUM(N28:Y28)</f>
-        <v>8142.05019415959</v>
+        <v>181440</v>
       </c>
       <c r="AB28" s="21" t="n">
         <f aca="false">SUM(B28:Y28)</f>
+        <v>304500</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="B29" s="21" t="n">
+        <f aca="false">B23/12/Assumptions!$B$22*Assumptions!$B$27</f>
+        <v>0</v>
+      </c>
+      <c r="C29" s="21" t="n">
+        <f aca="false">C23/12/Assumptions!$B$22*Assumptions!$B$27</f>
+        <v>0</v>
+      </c>
+      <c r="D29" s="21" t="n">
+        <f aca="false">D23/12/Assumptions!$B$22*Assumptions!$B$27</f>
+        <v>28.4375</v>
+      </c>
+      <c r="E29" s="21" t="n">
+        <f aca="false">E23/12/Assumptions!$B$22*Assumptions!$B$27</f>
+        <v>57.8520833333333</v>
+      </c>
+      <c r="F29" s="21" t="n">
+        <f aca="false">F23/12/Assumptions!$B$22*Assumptions!$B$27</f>
+        <v>88.2372361111111</v>
+      </c>
+      <c r="G29" s="21" t="n">
+        <f aca="false">G23/12/Assumptions!$B$22*Assumptions!$B$27</f>
+        <v>119.58648787037</v>
+      </c>
+      <c r="H29" s="21" t="n">
+        <f aca="false">H23/12/Assumptions!$B$22*Assumptions!$B$27</f>
+        <v>162.393411284568</v>
+      </c>
+      <c r="I29" s="21" t="n">
+        <f aca="false">I23/12/Assumptions!$B$22*Assumptions!$B$27</f>
+        <v>208.026066320449</v>
+      </c>
+      <c r="J29" s="21" t="n">
+        <f aca="false">J23/12/Assumptions!$B$22*Assumptions!$B$27</f>
+        <v>256.465614767201</v>
+      </c>
+      <c r="K29" s="21" t="n">
+        <f aca="false">K23/12/Assumptions!$B$22*Assumptions!$B$27</f>
+        <v>307.693344002086</v>
+      </c>
+      <c r="L29" s="21" t="n">
+        <f aca="false">L23/12/Assumptions!$B$22*Assumptions!$B$27</f>
+        <v>358.579555042073</v>
+      </c>
+      <c r="M29" s="21" t="n">
+        <f aca="false">M23/12/Assumptions!$B$22*Assumptions!$B$27</f>
+        <v>409.126524675125</v>
+      </c>
+      <c r="N29" s="21" t="n">
+        <f aca="false">N23/12/Assumptions!$B$22*Assumptions!$B$27</f>
+        <v>459.336514510624</v>
+      </c>
+      <c r="O29" s="21" t="n">
+        <f aca="false">O23/12/Assumptions!$B$22*Assumptions!$B$27</f>
+        <v>509.211771080554</v>
+      </c>
+      <c r="P29" s="21" t="n">
+        <f aca="false">P23/12/Assumptions!$B$22*Assumptions!$B$27</f>
+        <v>547.817025940017</v>
+      </c>
+      <c r="Q29" s="21" t="n">
+        <f aca="false">Q23/12/Assumptions!$B$22*Assumptions!$B$27</f>
+        <v>586.16491243375</v>
+      </c>
+      <c r="R29" s="21" t="n">
+        <f aca="false">R23/12/Assumptions!$B$22*Assumptions!$B$27</f>
+        <v>624.257146350858</v>
+      </c>
+      <c r="S29" s="21" t="n">
+        <f aca="false">S23/12/Assumptions!$B$22*Assumptions!$B$27</f>
+        <v>662.095432041853</v>
+      </c>
+      <c r="T29" s="21" t="n">
+        <f aca="false">T23/12/Assumptions!$B$22*Assumptions!$B$27</f>
+        <v>699.681462494907</v>
+      </c>
+      <c r="U29" s="21" t="n">
+        <f aca="false">U23/12/Assumptions!$B$22*Assumptions!$B$27</f>
+        <v>737.016919411607</v>
+      </c>
+      <c r="V29" s="21" t="n">
+        <f aca="false">V23/12/Assumptions!$B$22*Assumptions!$B$27</f>
+        <v>774.103473282197</v>
+      </c>
+      <c r="W29" s="21" t="n">
+        <f aca="false">W23/12/Assumptions!$B$22*Assumptions!$B$27</f>
+        <v>810.942783460315</v>
+      </c>
+      <c r="X29" s="21" t="n">
+        <f aca="false">X23/12/Assumptions!$B$22*Assumptions!$B$27</f>
+        <v>847.536498237246</v>
+      </c>
+      <c r="Y29" s="21" t="n">
+        <f aca="false">Y23/12/Assumptions!$B$22*Assumptions!$B$27</f>
+        <v>883.886254915665</v>
+      </c>
+      <c r="Z29" s="21" t="n">
+        <f aca="false">SUM(B29:M29)</f>
+        <v>1996.39782340632</v>
+      </c>
+      <c r="AA29" s="21" t="n">
+        <f aca="false">SUM(N29:Y29)</f>
+        <v>8142.05019415959</v>
+      </c>
+      <c r="AB29" s="21" t="n">
+        <f aca="false">SUM(B29:Y29)</f>
         <v>10138.4480175659</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="B29" s="22" t="n">
-        <f aca="false">B26+B27+B28</f>
-        <v>14196</v>
-      </c>
-      <c r="C29" s="22" t="n">
-        <f aca="false">C26+C27+C28</f>
-        <v>15288</v>
-      </c>
-      <c r="D29" s="22" t="n">
-        <f aca="false">D26+D27+D28</f>
-        <v>16408.4375</v>
-      </c>
-      <c r="E29" s="22" t="n">
-        <f aca="false">E26+E27+E28</f>
-        <v>17529.8520833333</v>
-      </c>
-      <c r="F29" s="22" t="n">
-        <f aca="false">F26+F27+F28</f>
-        <v>18652.2372361111</v>
-      </c>
-      <c r="G29" s="22" t="n">
-        <f aca="false">G26+G27+G28</f>
-        <v>19775.5864878704</v>
-      </c>
-      <c r="H29" s="22" t="n">
-        <f aca="false">H26+H27+H28</f>
-        <v>30738.3934112846</v>
-      </c>
-      <c r="I29" s="22" t="n">
-        <f aca="false">I26+I27+I28</f>
-        <v>33696.0260663205</v>
-      </c>
-      <c r="J29" s="22" t="n">
-        <f aca="false">J26+J27+J28</f>
-        <v>36656.4656147672</v>
-      </c>
-      <c r="K29" s="22" t="n">
-        <f aca="false">K26+K27+K28</f>
-        <v>39619.6933440021</v>
-      </c>
-      <c r="L29" s="22" t="n">
-        <f aca="false">L26+L27+L28</f>
-        <v>39670.5795550421</v>
-      </c>
-      <c r="M29" s="22" t="n">
-        <f aca="false">M26+M27+M28</f>
-        <v>39721.1265246751</v>
-      </c>
-      <c r="N29" s="22" t="n">
-        <f aca="false">N26+N27+N28</f>
-        <v>39771.3365145106</v>
-      </c>
-      <c r="O29" s="22" t="n">
-        <f aca="false">O26+O27+O28</f>
-        <v>39821.2117710806</v>
-      </c>
-      <c r="P29" s="22" t="n">
-        <f aca="false">P26+P27+P28</f>
-        <v>39859.81702594</v>
-      </c>
-      <c r="Q29" s="22" t="n">
-        <f aca="false">Q26+Q27+Q28</f>
-        <v>39898.1649124338</v>
-      </c>
-      <c r="R29" s="22" t="n">
-        <f aca="false">R26+R27+R28</f>
-        <v>39936.2571463509</v>
-      </c>
-      <c r="S29" s="22" t="n">
-        <f aca="false">S26+S27+S28</f>
-        <v>39974.0954320419</v>
-      </c>
-      <c r="T29" s="22" t="n">
-        <f aca="false">T26+T27+T28</f>
-        <v>40011.6814624949</v>
-      </c>
-      <c r="U29" s="22" t="n">
-        <f aca="false">U26+U27+U28</f>
-        <v>40049.0169194116</v>
-      </c>
-      <c r="V29" s="22" t="n">
-        <f aca="false">V26+V27+V28</f>
-        <v>40086.1034732822</v>
-      </c>
-      <c r="W29" s="22" t="n">
-        <f aca="false">W26+W27+W28</f>
-        <v>40122.9427834603</v>
-      </c>
-      <c r="X29" s="22" t="n">
-        <f aca="false">X26+X27+X28</f>
-        <v>40159.5364982373</v>
-      </c>
-      <c r="Y29" s="22" t="n">
-        <f aca="false">Y26+Y27+Y28</f>
-        <v>40195.8862549157</v>
-      </c>
-      <c r="Z29" s="23" t="n">
-        <f aca="false">SUM(B29:M29)</f>
-        <v>321952.397823406</v>
-      </c>
-      <c r="AA29" s="23" t="n">
-        <f aca="false">SUM(N29:Y29)</f>
-        <v>479886.05019416</v>
-      </c>
-      <c r="AB29" s="23" t="n">
-        <f aca="false">SUM(B29:Y29)</f>
-        <v>801838.448017566</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="B30" s="23" t="n">
-        <f aca="false">B24-B29</f>
-        <v>13104</v>
-      </c>
-      <c r="C30" s="23" t="n">
-        <f aca="false">C24-C29</f>
-        <v>14112</v>
-      </c>
-      <c r="D30" s="23" t="n">
-        <f aca="false">D24-D29</f>
-        <v>15192.71875</v>
-      </c>
-      <c r="E30" s="23" t="n">
-        <f aca="false">E24-E29</f>
-        <v>16275.9360416667</v>
-      </c>
-      <c r="F30" s="23" t="n">
-        <f aca="false">F24-F29</f>
-        <v>17361.6352180556</v>
-      </c>
-      <c r="G30" s="23" t="n">
-        <f aca="false">G24-G29</f>
-        <v>18449.7997332685</v>
-      </c>
-      <c r="H30" s="23" t="n">
-        <f aca="false">H24-H29</f>
-        <v>28639.2631517134</v>
-      </c>
-      <c r="I30" s="23" t="n">
-        <f aca="false">I24-I29</f>
-        <v>31443.9523695909</v>
-      </c>
-      <c r="J30" s="23" t="n">
-        <f aca="false">J24-J29</f>
-        <v>34255.8192149047</v>
-      </c>
-      <c r="K30" s="23" t="n">
-        <f aca="false">K24-K29</f>
-        <v>37074.8158368053</v>
-      </c>
-      <c r="L30" s="23" t="n">
-        <f aca="false">L24-L29</f>
-        <v>37204.9391478933</v>
-      </c>
-      <c r="M30" s="23" t="n">
-        <f aca="false">M24-M29</f>
-        <v>37334.1949702407</v>
-      </c>
-      <c r="N30" s="23" t="n">
-        <f aca="false">N24-N29</f>
-        <v>37462.5890871058</v>
-      </c>
-      <c r="O30" s="23" t="n">
-        <f aca="false">O24-O29</f>
-        <v>37590.1272431917</v>
-      </c>
-      <c r="P30" s="23" t="n">
-        <f aca="false">P24-P29</f>
-        <v>37688.8463949038</v>
-      </c>
-      <c r="Q30" s="23" t="n">
-        <f aca="false">Q24-Q29</f>
-        <v>37786.9074189377</v>
-      </c>
-      <c r="R30" s="23" t="n">
-        <f aca="false">R24-R29</f>
-        <v>37884.3147028115</v>
-      </c>
-      <c r="S30" s="23" t="n">
-        <f aca="false">S24-S29</f>
-        <v>37981.0726047927</v>
-      </c>
-      <c r="T30" s="23" t="n">
-        <f aca="false">T24-T29</f>
-        <v>38077.1854540941</v>
-      </c>
-      <c r="U30" s="23" t="n">
-        <f aca="false">U24-U29</f>
-        <v>38172.6575510668</v>
-      </c>
-      <c r="V30" s="23" t="n">
-        <f aca="false">V24-V29</f>
-        <v>38267.4931673931</v>
-      </c>
-      <c r="W30" s="23" t="n">
-        <f aca="false">W24-W29</f>
-        <v>38361.6965462771</v>
-      </c>
-      <c r="X30" s="23" t="n">
-        <f aca="false">X24-X29</f>
-        <v>38455.2719026352</v>
-      </c>
-      <c r="Y30" s="23" t="n">
-        <f aca="false">Y24-Y29</f>
-        <v>38548.2234232844</v>
+        <v>158</v>
+      </c>
+      <c r="B30" s="22" t="n">
+        <f aca="false">B27+B28+B29</f>
+        <v>14196</v>
+      </c>
+      <c r="C30" s="22" t="n">
+        <f aca="false">C27+C28+C29</f>
+        <v>15288</v>
+      </c>
+      <c r="D30" s="22" t="n">
+        <f aca="false">D27+D28+D29</f>
+        <v>16408.4375</v>
+      </c>
+      <c r="E30" s="22" t="n">
+        <f aca="false">E27+E28+E29</f>
+        <v>17529.8520833333</v>
+      </c>
+      <c r="F30" s="22" t="n">
+        <f aca="false">F27+F28+F29</f>
+        <v>18652.2372361111</v>
+      </c>
+      <c r="G30" s="22" t="n">
+        <f aca="false">G27+G28+G29</f>
+        <v>19775.5864878704</v>
+      </c>
+      <c r="H30" s="22" t="n">
+        <f aca="false">H27+H28+H29</f>
+        <v>30738.3934112846</v>
+      </c>
+      <c r="I30" s="22" t="n">
+        <f aca="false">I27+I28+I29</f>
+        <v>33696.0260663205</v>
+      </c>
+      <c r="J30" s="22" t="n">
+        <f aca="false">J27+J28+J29</f>
+        <v>36656.4656147672</v>
+      </c>
+      <c r="K30" s="22" t="n">
+        <f aca="false">K27+K28+K29</f>
+        <v>39619.6933440021</v>
+      </c>
+      <c r="L30" s="22" t="n">
+        <f aca="false">L27+L28+L29</f>
+        <v>39670.5795550421</v>
+      </c>
+      <c r="M30" s="22" t="n">
+        <f aca="false">M27+M28+M29</f>
+        <v>39721.1265246751</v>
+      </c>
+      <c r="N30" s="22" t="n">
+        <f aca="false">N27+N28+N29</f>
+        <v>39771.3365145106</v>
+      </c>
+      <c r="O30" s="22" t="n">
+        <f aca="false">O27+O28+O29</f>
+        <v>39821.2117710806</v>
+      </c>
+      <c r="P30" s="22" t="n">
+        <f aca="false">P27+P28+P29</f>
+        <v>39859.81702594</v>
+      </c>
+      <c r="Q30" s="22" t="n">
+        <f aca="false">Q27+Q28+Q29</f>
+        <v>39898.1649124338</v>
+      </c>
+      <c r="R30" s="22" t="n">
+        <f aca="false">R27+R28+R29</f>
+        <v>39936.2571463509</v>
+      </c>
+      <c r="S30" s="22" t="n">
+        <f aca="false">S27+S28+S29</f>
+        <v>39974.0954320419</v>
+      </c>
+      <c r="T30" s="22" t="n">
+        <f aca="false">T27+T28+T29</f>
+        <v>40011.6814624949</v>
+      </c>
+      <c r="U30" s="22" t="n">
+        <f aca="false">U27+U28+U29</f>
+        <v>40049.0169194116</v>
+      </c>
+      <c r="V30" s="22" t="n">
+        <f aca="false">V27+V28+V29</f>
+        <v>40086.1034732822</v>
+      </c>
+      <c r="W30" s="22" t="n">
+        <f aca="false">W27+W28+W29</f>
+        <v>40122.9427834603</v>
+      </c>
+      <c r="X30" s="22" t="n">
+        <f aca="false">X27+X28+X29</f>
+        <v>40159.5364982373</v>
+      </c>
+      <c r="Y30" s="22" t="n">
+        <f aca="false">Y27+Y28+Y29</f>
+        <v>40195.8862549157</v>
       </c>
       <c r="Z30" s="23" t="n">
         <f aca="false">SUM(B30:M30)</f>
-        <v>300449.074434139</v>
+        <v>321952.397823406</v>
       </c>
       <c r="AA30" s="23" t="n">
         <f aca="false">SUM(N30:Y30)</f>
-        <v>456276.385496494</v>
+        <v>479886.05019416</v>
       </c>
       <c r="AB30" s="23" t="n">
         <f aca="false">SUM(B30:Y30)</f>
+        <v>801838.448017566</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="B31" s="23" t="n">
+        <f aca="false">B25-B30</f>
+        <v>13104</v>
+      </c>
+      <c r="C31" s="23" t="n">
+        <f aca="false">C25-C30</f>
+        <v>14112</v>
+      </c>
+      <c r="D31" s="23" t="n">
+        <f aca="false">D25-D30</f>
+        <v>15192.71875</v>
+      </c>
+      <c r="E31" s="23" t="n">
+        <f aca="false">E25-E30</f>
+        <v>16275.9360416667</v>
+      </c>
+      <c r="F31" s="23" t="n">
+        <f aca="false">F25-F30</f>
+        <v>17361.6352180556</v>
+      </c>
+      <c r="G31" s="23" t="n">
+        <f aca="false">G25-G30</f>
+        <v>18449.7997332685</v>
+      </c>
+      <c r="H31" s="23" t="n">
+        <f aca="false">H25-H30</f>
+        <v>28639.2631517134</v>
+      </c>
+      <c r="I31" s="23" t="n">
+        <f aca="false">I25-I30</f>
+        <v>31443.9523695909</v>
+      </c>
+      <c r="J31" s="23" t="n">
+        <f aca="false">J25-J30</f>
+        <v>34255.8192149047</v>
+      </c>
+      <c r="K31" s="23" t="n">
+        <f aca="false">K25-K30</f>
+        <v>37074.8158368053</v>
+      </c>
+      <c r="L31" s="23" t="n">
+        <f aca="false">L25-L30</f>
+        <v>37204.9391478933</v>
+      </c>
+      <c r="M31" s="23" t="n">
+        <f aca="false">M25-M30</f>
+        <v>37334.1949702407</v>
+      </c>
+      <c r="N31" s="23" t="n">
+        <f aca="false">N25-N30</f>
+        <v>37462.5890871058</v>
+      </c>
+      <c r="O31" s="23" t="n">
+        <f aca="false">O25-O30</f>
+        <v>37590.1272431917</v>
+      </c>
+      <c r="P31" s="23" t="n">
+        <f aca="false">P25-P30</f>
+        <v>37688.8463949038</v>
+      </c>
+      <c r="Q31" s="23" t="n">
+        <f aca="false">Q25-Q30</f>
+        <v>37786.9074189377</v>
+      </c>
+      <c r="R31" s="23" t="n">
+        <f aca="false">R25-R30</f>
+        <v>37884.3147028115</v>
+      </c>
+      <c r="S31" s="23" t="n">
+        <f aca="false">S25-S30</f>
+        <v>37981.0726047927</v>
+      </c>
+      <c r="T31" s="23" t="n">
+        <f aca="false">T25-T30</f>
+        <v>38077.1854540941</v>
+      </c>
+      <c r="U31" s="23" t="n">
+        <f aca="false">U25-U30</f>
+        <v>38172.6575510668</v>
+      </c>
+      <c r="V31" s="23" t="n">
+        <f aca="false">V25-V30</f>
+        <v>38267.4931673931</v>
+      </c>
+      <c r="W31" s="23" t="n">
+        <f aca="false">W25-W30</f>
+        <v>38361.6965462771</v>
+      </c>
+      <c r="X31" s="23" t="n">
+        <f aca="false">X25-X30</f>
+        <v>38455.2719026352</v>
+      </c>
+      <c r="Y31" s="23" t="n">
+        <f aca="false">Y25-Y30</f>
+        <v>38548.2234232844</v>
+      </c>
+      <c r="Z31" s="23" t="n">
+        <f aca="false">SUM(B31:M31)</f>
+        <v>300449.074434139</v>
+      </c>
+      <c r="AA31" s="23" t="n">
+        <f aca="false">SUM(N31:Y31)</f>
+        <v>456276.385496494</v>
+      </c>
+      <c r="AB31" s="23" t="n">
+        <f aca="false">SUM(B31:Y31)</f>
         <v>756725.459930633</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="B31" s="20" t="n">
-        <f aca="false">IF(B24=0,0,B30/B24)</f>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="B32" s="20" t="n">
+        <f aca="false">IF(B25=0,0,B31/B25)</f>
         <v>0.48</v>
       </c>
-      <c r="C31" s="20" t="n">
-        <f aca="false">IF(C24=0,0,C30/C24)</f>
+      <c r="C32" s="20" t="n">
+        <f aca="false">IF(C25=0,0,C31/C25)</f>
         <v>0.48</v>
       </c>
-      <c r="D31" s="20" t="n">
-        <f aca="false">IF(D24=0,0,D30/D24)</f>
+      <c r="D32" s="20" t="n">
+        <f aca="false">IF(D25=0,0,D31/D25)</f>
         <v>0.480764647654309</v>
       </c>
-      <c r="E31" s="20" t="n">
-        <f aca="false">IF(E24=0,0,E30/E24)</f>
+      <c r="E32" s="20" t="n">
+        <f aca="false">IF(E25=0,0,E31/E25)</f>
         <v>0.481454122042205</v>
       </c>
-      <c r="F31" s="20" t="n">
-        <f aca="false">IF(F24=0,0,F30/F24)</f>
+      <c r="F32" s="20" t="n">
+        <f aca="false">IF(F25=0,0,F31/F25)</f>
         <v>0.482081876647699</v>
       </c>
-      <c r="G31" s="20" t="n">
-        <f aca="false">IF(G24=0,0,G30/G24)</f>
+      <c r="G32" s="20" t="n">
+        <f aca="false">IF(G25=0,0,G31/G25)</f>
         <v>0.482658294844531</v>
       </c>
-      <c r="H31" s="20" t="n">
-        <f aca="false">IF(H24=0,0,H30/H24)</f>
+      <c r="H32" s="20" t="n">
+        <f aca="false">IF(H25=0,0,H31/H25)</f>
         <v>0.482323904469486</v>
       </c>
-      <c r="I31" s="20" t="n">
-        <f aca="false">IF(I24=0,0,I30/I24)</f>
+      <c r="I32" s="20" t="n">
+        <f aca="false">IF(I25=0,0,I31/I25)</f>
         <v>0.4827135827275</v>
       </c>
-      <c r="J31" s="20" t="n">
-        <f aca="false">IF(J24=0,0,J30/J24)</f>
+      <c r="J32" s="20" t="n">
+        <f aca="false">IF(J25=0,0,J31/J25)</f>
         <v>0.483073127557314</v>
       </c>
-      <c r="K31" s="20" t="n">
-        <f aca="false">IF(K24=0,0,K30/K24)</f>
+      <c r="K32" s="20" t="n">
+        <f aca="false">IF(K25=0,0,K31/K25)</f>
         <v>0.483408998020985</v>
       </c>
-      <c r="L31" s="20" t="n">
-        <f aca="false">IF(L24=0,0,L30/L24)</f>
+      <c r="L32" s="20" t="n">
+        <f aca="false">IF(L25=0,0,L31/L25)</f>
         <v>0.483963422629533</v>
       </c>
-      <c r="M31" s="20" t="n">
-        <f aca="false">IF(M24=0,0,M30/M24)</f>
+      <c r="M32" s="20" t="n">
+        <f aca="false">IF(M25=0,0,M31/M25)</f>
         <v>0.484511572282571</v>
       </c>
-      <c r="N31" s="20" t="n">
-        <f aca="false">IF(N24=0,0,N30/N24)</f>
+      <c r="N32" s="20" t="n">
+        <f aca="false">IF(N25=0,0,N31/N25)</f>
         <v>0.485053540853836</v>
       </c>
-      <c r="O31" s="20" t="n">
-        <f aca="false">IF(O24=0,0,O30/O24)</f>
+      <c r="O32" s="20" t="n">
+        <f aca="false">IF(O25=0,0,O31/O25)</f>
         <v>0.485589420385316</v>
       </c>
-      <c r="P31" s="20" t="n">
-        <f aca="false">IF(P24=0,0,P30/P24)</f>
+      <c r="P32" s="20" t="n">
+        <f aca="false">IF(P25=0,0,P31/P25)</f>
         <v>0.486002527088992</v>
       </c>
-      <c r="Q31" s="20" t="n">
-        <f aca="false">IF(Q24=0,0,Q30/Q24)</f>
+      <c r="Q32" s="20" t="n">
+        <f aca="false">IF(Q25=0,0,Q31/Q25)</f>
         <v>0.486411433817746</v>
       </c>
-      <c r="R31" s="20" t="n">
-        <f aca="false">IF(R24=0,0,R30/R24)</f>
+      <c r="R32" s="20" t="n">
+        <f aca="false">IF(R25=0,0,R31/R25)</f>
         <v>0.486816195288846</v>
       </c>
-      <c r="S31" s="20" t="n">
-        <f aca="false">IF(S24=0,0,S30/S24)</f>
+      <c r="S32" s="20" t="n">
+        <f aca="false">IF(S25=0,0,S31/S25)</f>
         <v>0.487216865299377</v>
       </c>
-      <c r="T31" s="20" t="n">
-        <f aca="false">IF(T24=0,0,T30/T24)</f>
+      <c r="T32" s="20" t="n">
+        <f aca="false">IF(T25=0,0,T31/T25)</f>
         <v>0.487613496745528</v>
       </c>
-      <c r="U31" s="20" t="n">
-        <f aca="false">IF(U24=0,0,U30/U24)</f>
+      <c r="U32" s="20" t="n">
+        <f aca="false">IF(U25=0,0,U31/U25)</f>
         <v>0.488006141641388</v>
       </c>
-      <c r="V31" s="20" t="n">
-        <f aca="false">IF(V24=0,0,V30/V24)</f>
+      <c r="V32" s="20" t="n">
+        <f aca="false">IF(V25=0,0,V31/V25)</f>
         <v>0.48839485113728</v>
       </c>
-      <c r="W31" s="20" t="n">
-        <f aca="false">IF(W24=0,0,W30/W24)</f>
+      <c r="W32" s="20" t="n">
+        <f aca="false">IF(W25=0,0,W31/W25)</f>
         <v>0.488779675537632</v>
       </c>
-      <c r="X31" s="20" t="n">
-        <f aca="false">IF(X24=0,0,X30/X24)</f>
+      <c r="X32" s="20" t="n">
+        <f aca="false">IF(X25=0,0,X31/X25)</f>
         <v>0.489160664318409</v>
       </c>
-      <c r="Y31" s="20" t="n">
-        <f aca="false">IF(Y24=0,0,Y30/Y24)</f>
+      <c r="Y32" s="20" t="n">
+        <f aca="false">IF(Y25=0,0,Y31/Y25)</f>
         <v>0.489537866144117</v>
       </c>
-      <c r="Z31" s="2"/>
-      <c r="AA31" s="2"/>
-      <c r="AB31" s="2"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="5"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="5"/>
-      <c r="L32" s="5"/>
-      <c r="M32" s="5"/>
-      <c r="N32" s="5"/>
-      <c r="O32" s="5"/>
-      <c r="P32" s="5"/>
-      <c r="Q32" s="5"/>
-      <c r="R32" s="5"/>
-      <c r="S32" s="5"/>
-      <c r="T32" s="5"/>
-      <c r="U32" s="5"/>
-      <c r="V32" s="5"/>
-      <c r="W32" s="5"/>
-      <c r="X32" s="5"/>
-      <c r="Y32" s="5"/>
-      <c r="Z32" s="5"/>
-      <c r="AA32" s="5"/>
-      <c r="AB32" s="5"/>
+      <c r="Z32" s="2"/>
+      <c r="AA32" s="2"/>
+      <c r="AB32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="B33" s="21" t="n">
-        <f aca="false">Assumptions!$B$46</f>
-        <v>6000</v>
-      </c>
-      <c r="C33" s="21" t="n">
-        <f aca="false">Assumptions!$B$46</f>
-        <v>6000</v>
-      </c>
-      <c r="D33" s="21" t="n">
-        <f aca="false">Assumptions!$B$46</f>
-        <v>6000</v>
-      </c>
-      <c r="E33" s="21" t="n">
-        <f aca="false">Assumptions!$B$46</f>
-        <v>6000</v>
-      </c>
-      <c r="F33" s="21" t="n">
-        <f aca="false">Assumptions!$B$46</f>
-        <v>6000</v>
-      </c>
-      <c r="G33" s="21" t="n">
-        <f aca="false">Assumptions!$B$46</f>
-        <v>6000</v>
-      </c>
-      <c r="H33" s="21" t="n">
-        <f aca="false">Assumptions!$B$46</f>
-        <v>6000</v>
-      </c>
-      <c r="I33" s="21" t="n">
-        <f aca="false">Assumptions!$B$46</f>
-        <v>6000</v>
-      </c>
-      <c r="J33" s="21" t="n">
-        <f aca="false">Assumptions!$B$46</f>
-        <v>6000</v>
-      </c>
-      <c r="K33" s="21" t="n">
-        <f aca="false">Assumptions!$B$46</f>
-        <v>6000</v>
-      </c>
-      <c r="L33" s="21" t="n">
-        <f aca="false">Assumptions!$B$46</f>
-        <v>6000</v>
-      </c>
-      <c r="M33" s="21" t="n">
-        <f aca="false">Assumptions!$B$46</f>
-        <v>6000</v>
-      </c>
-      <c r="N33" s="21" t="n">
-        <f aca="false">Assumptions!$B$46</f>
-        <v>6000</v>
-      </c>
-      <c r="O33" s="21" t="n">
-        <f aca="false">Assumptions!$B$46</f>
-        <v>6000</v>
-      </c>
-      <c r="P33" s="21" t="n">
-        <f aca="false">Assumptions!$B$46</f>
-        <v>6000</v>
-      </c>
-      <c r="Q33" s="21" t="n">
-        <f aca="false">Assumptions!$B$46</f>
-        <v>6000</v>
-      </c>
-      <c r="R33" s="21" t="n">
-        <f aca="false">Assumptions!$B$46</f>
-        <v>6000</v>
-      </c>
-      <c r="S33" s="21" t="n">
-        <f aca="false">Assumptions!$B$46</f>
-        <v>6000</v>
-      </c>
-      <c r="T33" s="21" t="n">
-        <f aca="false">Assumptions!$B$46</f>
-        <v>6000</v>
-      </c>
-      <c r="U33" s="21" t="n">
-        <f aca="false">Assumptions!$B$46</f>
-        <v>6000</v>
-      </c>
-      <c r="V33" s="21" t="n">
-        <f aca="false">Assumptions!$B$46</f>
-        <v>6000</v>
-      </c>
-      <c r="W33" s="21" t="n">
-        <f aca="false">Assumptions!$B$46</f>
-        <v>6000</v>
-      </c>
-      <c r="X33" s="21" t="n">
-        <f aca="false">Assumptions!$B$46</f>
-        <v>6000</v>
-      </c>
-      <c r="Y33" s="21" t="n">
-        <f aca="false">Assumptions!$B$46</f>
-        <v>6000</v>
-      </c>
-      <c r="Z33" s="21" t="n">
-        <f aca="false">SUM(B33:M33)</f>
-        <v>72000</v>
-      </c>
-      <c r="AA33" s="21" t="n">
-        <f aca="false">SUM(N33:Y33)</f>
-        <v>72000</v>
-      </c>
-      <c r="AB33" s="21" t="n">
-        <f aca="false">SUM(B33:Y33)</f>
-        <v>144000</v>
-      </c>
+      <c r="A33" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="5"/>
+      <c r="R33" s="5"/>
+      <c r="S33" s="5"/>
+      <c r="T33" s="5"/>
+      <c r="U33" s="5"/>
+      <c r="V33" s="5"/>
+      <c r="W33" s="5"/>
+      <c r="X33" s="5"/>
+      <c r="Y33" s="5"/>
+      <c r="Z33" s="5"/>
+      <c r="AA33" s="5"/>
+      <c r="AB33" s="5"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="17" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B34" s="21" t="n">
-        <f aca="false">Assumptions!$B$47</f>
-        <v>900</v>
+        <f aca="false">Assumptions!$B$48</f>
+        <v>6000</v>
       </c>
       <c r="C34" s="21" t="n">
-        <f aca="false">Assumptions!$B$47</f>
-        <v>900</v>
+        <f aca="false">Assumptions!$B$48</f>
+        <v>6000</v>
       </c>
       <c r="D34" s="21" t="n">
-        <f aca="false">Assumptions!$B$47</f>
-        <v>900</v>
+        <f aca="false">Assumptions!$B$48</f>
+        <v>6000</v>
       </c>
       <c r="E34" s="21" t="n">
-        <f aca="false">Assumptions!$B$47</f>
-        <v>900</v>
+        <f aca="false">Assumptions!$B$48</f>
+        <v>6000</v>
       </c>
       <c r="F34" s="21" t="n">
-        <f aca="false">Assumptions!$B$47</f>
-        <v>900</v>
+        <f aca="false">Assumptions!$B$48</f>
+        <v>6000</v>
       </c>
       <c r="G34" s="21" t="n">
-        <f aca="false">Assumptions!$B$47</f>
-        <v>900</v>
+        <f aca="false">Assumptions!$B$48</f>
+        <v>6000</v>
       </c>
       <c r="H34" s="21" t="n">
-        <f aca="false">Assumptions!$B$47</f>
-        <v>900</v>
+        <f aca="false">Assumptions!$B$48</f>
+        <v>6000</v>
       </c>
       <c r="I34" s="21" t="n">
-        <f aca="false">Assumptions!$B$47</f>
-        <v>900</v>
+        <f aca="false">Assumptions!$B$48</f>
+        <v>6000</v>
       </c>
       <c r="J34" s="21" t="n">
-        <f aca="false">Assumptions!$B$47</f>
-        <v>900</v>
+        <f aca="false">Assumptions!$B$48</f>
+        <v>6000</v>
       </c>
       <c r="K34" s="21" t="n">
-        <f aca="false">Assumptions!$B$47</f>
-        <v>900</v>
+        <f aca="false">Assumptions!$B$48</f>
+        <v>6000</v>
       </c>
       <c r="L34" s="21" t="n">
-        <f aca="false">Assumptions!$B$47</f>
-        <v>900</v>
+        <f aca="false">Assumptions!$B$48</f>
+        <v>6000</v>
       </c>
       <c r="M34" s="21" t="n">
-        <f aca="false">Assumptions!$B$47</f>
-        <v>900</v>
+        <f aca="false">Assumptions!$B$48</f>
+        <v>6000</v>
       </c>
       <c r="N34" s="21" t="n">
-        <f aca="false">Assumptions!$B$47</f>
-        <v>900</v>
+        <f aca="false">Assumptions!$B$48</f>
+        <v>6000</v>
       </c>
       <c r="O34" s="21" t="n">
-        <f aca="false">Assumptions!$B$47</f>
-        <v>900</v>
+        <f aca="false">Assumptions!$B$48</f>
+        <v>6000</v>
       </c>
       <c r="P34" s="21" t="n">
-        <f aca="false">Assumptions!$B$47</f>
-        <v>900</v>
+        <f aca="false">Assumptions!$B$48</f>
+        <v>6000</v>
       </c>
       <c r="Q34" s="21" t="n">
-        <f aca="false">Assumptions!$B$47</f>
-        <v>900</v>
+        <f aca="false">Assumptions!$B$48</f>
+        <v>6000</v>
       </c>
       <c r="R34" s="21" t="n">
-        <f aca="false">Assumptions!$B$47</f>
-        <v>900</v>
+        <f aca="false">Assumptions!$B$48</f>
+        <v>6000</v>
       </c>
       <c r="S34" s="21" t="n">
-        <f aca="false">Assumptions!$B$47</f>
-        <v>900</v>
+        <f aca="false">Assumptions!$B$48</f>
+        <v>6000</v>
       </c>
       <c r="T34" s="21" t="n">
-        <f aca="false">Assumptions!$B$47</f>
-        <v>900</v>
+        <f aca="false">Assumptions!$B$48</f>
+        <v>6000</v>
       </c>
       <c r="U34" s="21" t="n">
-        <f aca="false">Assumptions!$B$47</f>
-        <v>900</v>
+        <f aca="false">Assumptions!$B$48</f>
+        <v>6000</v>
       </c>
       <c r="V34" s="21" t="n">
-        <f aca="false">Assumptions!$B$47</f>
-        <v>900</v>
+        <f aca="false">Assumptions!$B$48</f>
+        <v>6000</v>
       </c>
       <c r="W34" s="21" t="n">
-        <f aca="false">Assumptions!$B$47</f>
-        <v>900</v>
+        <f aca="false">Assumptions!$B$48</f>
+        <v>6000</v>
       </c>
       <c r="X34" s="21" t="n">
-        <f aca="false">Assumptions!$B$47</f>
-        <v>900</v>
+        <f aca="false">Assumptions!$B$48</f>
+        <v>6000</v>
       </c>
       <c r="Y34" s="21" t="n">
-        <f aca="false">Assumptions!$B$47</f>
-        <v>900</v>
+        <f aca="false">Assumptions!$B$48</f>
+        <v>6000</v>
       </c>
       <c r="Z34" s="21" t="n">
         <f aca="false">SUM(B34:M34)</f>
-        <v>10800</v>
+        <v>72000</v>
       </c>
       <c r="AA34" s="21" t="n">
         <f aca="false">SUM(N34:Y34)</f>
-        <v>10800</v>
+        <v>72000</v>
       </c>
       <c r="AB34" s="21" t="n">
         <f aca="false">SUM(B34:Y34)</f>
-        <v>21600</v>
+        <v>144000</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="17" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B35" s="21" t="n">
-        <f aca="false">Assumptions!$B$48</f>
-        <v>1800</v>
+        <f aca="false">Assumptions!$B$49</f>
+        <v>900</v>
       </c>
       <c r="C35" s="21" t="n">
-        <f aca="false">Assumptions!$B$48</f>
-        <v>1800</v>
+        <f aca="false">Assumptions!$B$49</f>
+        <v>900</v>
       </c>
       <c r="D35" s="21" t="n">
-        <f aca="false">Assumptions!$B$48</f>
-        <v>1800</v>
+        <f aca="false">Assumptions!$B$49</f>
+        <v>900</v>
       </c>
       <c r="E35" s="21" t="n">
-        <f aca="false">Assumptions!$B$48</f>
-        <v>1800</v>
+        <f aca="false">Assumptions!$B$49</f>
+        <v>900</v>
       </c>
       <c r="F35" s="21" t="n">
-        <f aca="false">Assumptions!$B$48</f>
-        <v>1800</v>
+        <f aca="false">Assumptions!$B$49</f>
+        <v>900</v>
       </c>
       <c r="G35" s="21" t="n">
-        <f aca="false">Assumptions!$B$48</f>
-        <v>1800</v>
+        <f aca="false">Assumptions!$B$49</f>
+        <v>900</v>
       </c>
       <c r="H35" s="21" t="n">
-        <f aca="false">Assumptions!$B$48</f>
-        <v>1800</v>
+        <f aca="false">Assumptions!$B$49</f>
+        <v>900</v>
       </c>
       <c r="I35" s="21" t="n">
-        <f aca="false">Assumptions!$B$48</f>
-        <v>1800</v>
+        <f aca="false">Assumptions!$B$49</f>
+        <v>900</v>
       </c>
       <c r="J35" s="21" t="n">
-        <f aca="false">Assumptions!$B$48</f>
-        <v>1800</v>
+        <f aca="false">Assumptions!$B$49</f>
+        <v>900</v>
       </c>
       <c r="K35" s="21" t="n">
-        <f aca="false">Assumptions!$B$48</f>
-        <v>1800</v>
+        <f aca="false">Assumptions!$B$49</f>
+        <v>900</v>
       </c>
       <c r="L35" s="21" t="n">
-        <f aca="false">Assumptions!$B$48</f>
-        <v>1800</v>
+        <f aca="false">Assumptions!$B$49</f>
+        <v>900</v>
       </c>
       <c r="M35" s="21" t="n">
-        <f aca="false">Assumptions!$B$48</f>
-        <v>1800</v>
+        <f aca="false">Assumptions!$B$49</f>
+        <v>900</v>
       </c>
       <c r="N35" s="21" t="n">
-        <f aca="false">Assumptions!$B$48</f>
-        <v>1800</v>
+        <f aca="false">Assumptions!$B$49</f>
+        <v>900</v>
       </c>
       <c r="O35" s="21" t="n">
-        <f aca="false">Assumptions!$B$48</f>
-        <v>1800</v>
+        <f aca="false">Assumptions!$B$49</f>
+        <v>900</v>
       </c>
       <c r="P35" s="21" t="n">
-        <f aca="false">Assumptions!$B$48</f>
-        <v>1800</v>
+        <f aca="false">Assumptions!$B$49</f>
+        <v>900</v>
       </c>
       <c r="Q35" s="21" t="n">
-        <f aca="false">Assumptions!$B$48</f>
-        <v>1800</v>
+        <f aca="false">Assumptions!$B$49</f>
+        <v>900</v>
       </c>
       <c r="R35" s="21" t="n">
-        <f aca="false">Assumptions!$B$48</f>
-        <v>1800</v>
+        <f aca="false">Assumptions!$B$49</f>
+        <v>900</v>
       </c>
       <c r="S35" s="21" t="n">
-        <f aca="false">Assumptions!$B$48</f>
-        <v>1800</v>
+        <f aca="false">Assumptions!$B$49</f>
+        <v>900</v>
       </c>
       <c r="T35" s="21" t="n">
-        <f aca="false">Assumptions!$B$48</f>
-        <v>1800</v>
+        <f aca="false">Assumptions!$B$49</f>
+        <v>900</v>
       </c>
       <c r="U35" s="21" t="n">
-        <f aca="false">Assumptions!$B$48</f>
-        <v>1800</v>
+        <f aca="false">Assumptions!$B$49</f>
+        <v>900</v>
       </c>
       <c r="V35" s="21" t="n">
-        <f aca="false">Assumptions!$B$48</f>
-        <v>1800</v>
+        <f aca="false">Assumptions!$B$49</f>
+        <v>900</v>
       </c>
       <c r="W35" s="21" t="n">
-        <f aca="false">Assumptions!$B$48</f>
-        <v>1800</v>
+        <f aca="false">Assumptions!$B$49</f>
+        <v>900</v>
       </c>
       <c r="X35" s="21" t="n">
-        <f aca="false">Assumptions!$B$48</f>
-        <v>1800</v>
+        <f aca="false">Assumptions!$B$49</f>
+        <v>900</v>
       </c>
       <c r="Y35" s="21" t="n">
-        <f aca="false">Assumptions!$B$48</f>
-        <v>1800</v>
+        <f aca="false">Assumptions!$B$49</f>
+        <v>900</v>
       </c>
       <c r="Z35" s="21" t="n">
         <f aca="false">SUM(B35:M35)</f>
-        <v>21600</v>
+        <v>10800</v>
       </c>
       <c r="AA35" s="21" t="n">
         <f aca="false">SUM(N35:Y35)</f>
-        <v>21600</v>
+        <v>10800</v>
       </c>
       <c r="AB35" s="21" t="n">
         <f aca="false">SUM(B35:Y35)</f>
-        <v>43200</v>
+        <v>21600</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="17" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B36" s="21" t="n">
-        <f aca="false">Assumptions!$B$49</f>
-        <v>350</v>
+        <f aca="false">Assumptions!$B$50</f>
+        <v>1800</v>
       </c>
       <c r="C36" s="21" t="n">
-        <f aca="false">Assumptions!$B$49</f>
-        <v>350</v>
+        <f aca="false">Assumptions!$B$50</f>
+        <v>1800</v>
       </c>
       <c r="D36" s="21" t="n">
-        <f aca="false">Assumptions!$B$49</f>
-        <v>350</v>
+        <f aca="false">Assumptions!$B$50</f>
+        <v>1800</v>
       </c>
       <c r="E36" s="21" t="n">
-        <f aca="false">Assumptions!$B$49</f>
-        <v>350</v>
+        <f aca="false">Assumptions!$B$50</f>
+        <v>1800</v>
       </c>
       <c r="F36" s="21" t="n">
-        <f aca="false">Assumptions!$B$49</f>
-        <v>350</v>
+        <f aca="false">Assumptions!$B$50</f>
+        <v>1800</v>
       </c>
       <c r="G36" s="21" t="n">
-        <f aca="false">Assumptions!$B$49</f>
-        <v>350</v>
+        <f aca="false">Assumptions!$B$50</f>
+        <v>1800</v>
       </c>
       <c r="H36" s="21" t="n">
-        <f aca="false">Assumptions!$B$49</f>
-        <v>350</v>
+        <f aca="false">Assumptions!$B$50</f>
+        <v>1800</v>
       </c>
       <c r="I36" s="21" t="n">
-        <f aca="false">Assumptions!$B$49</f>
-        <v>350</v>
+        <f aca="false">Assumptions!$B$50</f>
+        <v>1800</v>
       </c>
       <c r="J36" s="21" t="n">
-        <f aca="false">Assumptions!$B$49</f>
-        <v>350</v>
+        <f aca="false">Assumptions!$B$50</f>
+        <v>1800</v>
       </c>
       <c r="K36" s="21" t="n">
-        <f aca="false">Assumptions!$B$49</f>
-        <v>350</v>
+        <f aca="false">Assumptions!$B$50</f>
+        <v>1800</v>
       </c>
       <c r="L36" s="21" t="n">
-        <f aca="false">Assumptions!$B$49</f>
-        <v>350</v>
+        <f aca="false">Assumptions!$B$50</f>
+        <v>1800</v>
       </c>
       <c r="M36" s="21" t="n">
-        <f aca="false">Assumptions!$B$49</f>
-        <v>350</v>
+        <f aca="false">Assumptions!$B$50</f>
+        <v>1800</v>
       </c>
       <c r="N36" s="21" t="n">
-        <f aca="false">Assumptions!$B$49</f>
-        <v>350</v>
+        <f aca="false">Assumptions!$B$50</f>
+        <v>1800</v>
       </c>
       <c r="O36" s="21" t="n">
-        <f aca="false">Assumptions!$B$49</f>
-        <v>350</v>
+        <f aca="false">Assumptions!$B$50</f>
+        <v>1800</v>
       </c>
       <c r="P36" s="21" t="n">
-        <f aca="false">Assumptions!$B$49</f>
-        <v>350</v>
+        <f aca="false">Assumptions!$B$50</f>
+        <v>1800</v>
       </c>
       <c r="Q36" s="21" t="n">
-        <f aca="false">Assumptions!$B$49</f>
-        <v>350</v>
+        <f aca="false">Assumptions!$B$50</f>
+        <v>1800</v>
       </c>
       <c r="R36" s="21" t="n">
-        <f aca="false">Assumptions!$B$49</f>
-        <v>350</v>
+        <f aca="false">Assumptions!$B$50</f>
+        <v>1800</v>
       </c>
       <c r="S36" s="21" t="n">
-        <f aca="false">Assumptions!$B$49</f>
-        <v>350</v>
+        <f aca="false">Assumptions!$B$50</f>
+        <v>1800</v>
       </c>
       <c r="T36" s="21" t="n">
-        <f aca="false">Assumptions!$B$49</f>
-        <v>350</v>
+        <f aca="false">Assumptions!$B$50</f>
+        <v>1800</v>
       </c>
       <c r="U36" s="21" t="n">
-        <f aca="false">Assumptions!$B$49</f>
-        <v>350</v>
+        <f aca="false">Assumptions!$B$50</f>
+        <v>1800</v>
       </c>
       <c r="V36" s="21" t="n">
-        <f aca="false">Assumptions!$B$49</f>
-        <v>350</v>
+        <f aca="false">Assumptions!$B$50</f>
+        <v>1800</v>
       </c>
       <c r="W36" s="21" t="n">
-        <f aca="false">Assumptions!$B$49</f>
-        <v>350</v>
+        <f aca="false">Assumptions!$B$50</f>
+        <v>1800</v>
       </c>
       <c r="X36" s="21" t="n">
-        <f aca="false">Assumptions!$B$49</f>
-        <v>350</v>
+        <f aca="false">Assumptions!$B$50</f>
+        <v>1800</v>
       </c>
       <c r="Y36" s="21" t="n">
-        <f aca="false">Assumptions!$B$49</f>
-        <v>350</v>
+        <f aca="false">Assumptions!$B$50</f>
+        <v>1800</v>
       </c>
       <c r="Z36" s="21" t="n">
         <f aca="false">SUM(B36:M36)</f>
-        <v>4200</v>
+        <v>21600</v>
       </c>
       <c r="AA36" s="21" t="n">
         <f aca="false">SUM(N36:Y36)</f>
-        <v>4200</v>
+        <v>21600</v>
       </c>
       <c r="AB36" s="21" t="n">
         <f aca="false">SUM(B36:Y36)</f>
-        <v>8400</v>
+        <v>43200</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="17" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B37" s="21" t="n">
-        <f aca="false">Assumptions!$B$50</f>
-        <v>250</v>
+        <f aca="false">Assumptions!$B$51</f>
+        <v>350</v>
       </c>
       <c r="C37" s="21" t="n">
-        <f aca="false">Assumptions!$B$50</f>
-        <v>250</v>
+        <f aca="false">Assumptions!$B$51</f>
+        <v>350</v>
       </c>
       <c r="D37" s="21" t="n">
-        <f aca="false">Assumptions!$B$50</f>
-        <v>250</v>
+        <f aca="false">Assumptions!$B$51</f>
+        <v>350</v>
       </c>
       <c r="E37" s="21" t="n">
-        <f aca="false">Assumptions!$B$50</f>
-        <v>250</v>
+        <f aca="false">Assumptions!$B$51</f>
+        <v>350</v>
       </c>
       <c r="F37" s="21" t="n">
-        <f aca="false">Assumptions!$B$50</f>
-        <v>250</v>
+        <f aca="false">Assumptions!$B$51</f>
+        <v>350</v>
       </c>
       <c r="G37" s="21" t="n">
-        <f aca="false">Assumptions!$B$50</f>
-        <v>250</v>
+        <f aca="false">Assumptions!$B$51</f>
+        <v>350</v>
       </c>
       <c r="H37" s="21" t="n">
-        <f aca="false">Assumptions!$B$50</f>
-        <v>250</v>
+        <f aca="false">Assumptions!$B$51</f>
+        <v>350</v>
       </c>
       <c r="I37" s="21" t="n">
-        <f aca="false">Assumptions!$B$50</f>
-        <v>250</v>
+        <f aca="false">Assumptions!$B$51</f>
+        <v>350</v>
       </c>
       <c r="J37" s="21" t="n">
-        <f aca="false">Assumptions!$B$50</f>
-        <v>250</v>
+        <f aca="false">Assumptions!$B$51</f>
+        <v>350</v>
       </c>
       <c r="K37" s="21" t="n">
-        <f aca="false">Assumptions!$B$50</f>
-        <v>250</v>
+        <f aca="false">Assumptions!$B$51</f>
+        <v>350</v>
       </c>
       <c r="L37" s="21" t="n">
-        <f aca="false">Assumptions!$B$50</f>
-        <v>250</v>
+        <f aca="false">Assumptions!$B$51</f>
+        <v>350</v>
       </c>
       <c r="M37" s="21" t="n">
-        <f aca="false">Assumptions!$B$50</f>
-        <v>250</v>
+        <f aca="false">Assumptions!$B$51</f>
+        <v>350</v>
       </c>
       <c r="N37" s="21" t="n">
-        <f aca="false">Assumptions!$B$50</f>
-        <v>250</v>
+        <f aca="false">Assumptions!$B$51</f>
+        <v>350</v>
       </c>
       <c r="O37" s="21" t="n">
-        <f aca="false">Assumptions!$B$50</f>
-        <v>250</v>
+        <f aca="false">Assumptions!$B$51</f>
+        <v>350</v>
       </c>
       <c r="P37" s="21" t="n">
-        <f aca="false">Assumptions!$B$50</f>
-        <v>250</v>
+        <f aca="false">Assumptions!$B$51</f>
+        <v>350</v>
       </c>
       <c r="Q37" s="21" t="n">
-        <f aca="false">Assumptions!$B$50</f>
-        <v>250</v>
+        <f aca="false">Assumptions!$B$51</f>
+        <v>350</v>
       </c>
       <c r="R37" s="21" t="n">
-        <f aca="false">Assumptions!$B$50</f>
-        <v>250</v>
+        <f aca="false">Assumptions!$B$51</f>
+        <v>350</v>
       </c>
       <c r="S37" s="21" t="n">
-        <f aca="false">Assumptions!$B$50</f>
-        <v>250</v>
+        <f aca="false">Assumptions!$B$51</f>
+        <v>350</v>
       </c>
       <c r="T37" s="21" t="n">
-        <f aca="false">Assumptions!$B$50</f>
-        <v>250</v>
+        <f aca="false">Assumptions!$B$51</f>
+        <v>350</v>
       </c>
       <c r="U37" s="21" t="n">
-        <f aca="false">Assumptions!$B$50</f>
-        <v>250</v>
+        <f aca="false">Assumptions!$B$51</f>
+        <v>350</v>
       </c>
       <c r="V37" s="21" t="n">
-        <f aca="false">Assumptions!$B$50</f>
-        <v>250</v>
+        <f aca="false">Assumptions!$B$51</f>
+        <v>350</v>
       </c>
       <c r="W37" s="21" t="n">
-        <f aca="false">Assumptions!$B$50</f>
-        <v>250</v>
+        <f aca="false">Assumptions!$B$51</f>
+        <v>350</v>
       </c>
       <c r="X37" s="21" t="n">
-        <f aca="false">Assumptions!$B$50</f>
-        <v>250</v>
+        <f aca="false">Assumptions!$B$51</f>
+        <v>350</v>
       </c>
       <c r="Y37" s="21" t="n">
-        <f aca="false">Assumptions!$B$50</f>
-        <v>250</v>
+        <f aca="false">Assumptions!$B$51</f>
+        <v>350</v>
       </c>
       <c r="Z37" s="21" t="n">
         <f aca="false">SUM(B37:M37)</f>
-        <v>3000</v>
+        <v>4200</v>
       </c>
       <c r="AA37" s="21" t="n">
         <f aca="false">SUM(N37:Y37)</f>
-        <v>3000</v>
+        <v>4200</v>
       </c>
       <c r="AB37" s="21" t="n">
         <f aca="false">SUM(B37:Y37)</f>
-        <v>6000</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="17" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B38" s="21" t="n">
-        <f aca="false">Assumptions!$B$51</f>
-        <v>600</v>
+        <f aca="false">Assumptions!$B$52</f>
+        <v>250</v>
       </c>
       <c r="C38" s="21" t="n">
-        <f aca="false">Assumptions!$B$51</f>
-        <v>600</v>
+        <f aca="false">Assumptions!$B$52</f>
+        <v>250</v>
       </c>
       <c r="D38" s="21" t="n">
-        <f aca="false">Assumptions!$B$51</f>
-        <v>600</v>
+        <f aca="false">Assumptions!$B$52</f>
+        <v>250</v>
       </c>
       <c r="E38" s="21" t="n">
-        <f aca="false">Assumptions!$B$51</f>
-        <v>600</v>
+        <f aca="false">Assumptions!$B$52</f>
+        <v>250</v>
       </c>
       <c r="F38" s="21" t="n">
-        <f aca="false">Assumptions!$B$51</f>
-        <v>600</v>
+        <f aca="false">Assumptions!$B$52</f>
+        <v>250</v>
       </c>
       <c r="G38" s="21" t="n">
-        <f aca="false">Assumptions!$B$51</f>
-        <v>600</v>
+        <f aca="false">Assumptions!$B$52</f>
+        <v>250</v>
       </c>
       <c r="H38" s="21" t="n">
-        <f aca="false">Assumptions!$B$51</f>
-        <v>600</v>
+        <f aca="false">Assumptions!$B$52</f>
+        <v>250</v>
       </c>
       <c r="I38" s="21" t="n">
-        <f aca="false">Assumptions!$B$51</f>
-        <v>600</v>
+        <f aca="false">Assumptions!$B$52</f>
+        <v>250</v>
       </c>
       <c r="J38" s="21" t="n">
-        <f aca="false">Assumptions!$B$51</f>
-        <v>600</v>
+        <f aca="false">Assumptions!$B$52</f>
+        <v>250</v>
       </c>
       <c r="K38" s="21" t="n">
-        <f aca="false">Assumptions!$B$51</f>
-        <v>600</v>
+        <f aca="false">Assumptions!$B$52</f>
+        <v>250</v>
       </c>
       <c r="L38" s="21" t="n">
-        <f aca="false">Assumptions!$B$51</f>
-        <v>600</v>
+        <f aca="false">Assumptions!$B$52</f>
+        <v>250</v>
       </c>
       <c r="M38" s="21" t="n">
-        <f aca="false">Assumptions!$B$51</f>
-        <v>600</v>
+        <f aca="false">Assumptions!$B$52</f>
+        <v>250</v>
       </c>
       <c r="N38" s="21" t="n">
-        <f aca="false">Assumptions!$B$51</f>
-        <v>600</v>
+        <f aca="false">Assumptions!$B$52</f>
+        <v>250</v>
       </c>
       <c r="O38" s="21" t="n">
-        <f aca="false">Assumptions!$B$51</f>
-        <v>600</v>
+        <f aca="false">Assumptions!$B$52</f>
+        <v>250</v>
       </c>
       <c r="P38" s="21" t="n">
-        <f aca="false">Assumptions!$B$51</f>
-        <v>600</v>
+        <f aca="false">Assumptions!$B$52</f>
+        <v>250</v>
       </c>
       <c r="Q38" s="21" t="n">
-        <f aca="false">Assumptions!$B$51</f>
-        <v>600</v>
+        <f aca="false">Assumptions!$B$52</f>
+        <v>250</v>
       </c>
       <c r="R38" s="21" t="n">
-        <f aca="false">Assumptions!$B$51</f>
-        <v>600</v>
+        <f aca="false">Assumptions!$B$52</f>
+        <v>250</v>
       </c>
       <c r="S38" s="21" t="n">
-        <f aca="false">Assumptions!$B$51</f>
-        <v>600</v>
+        <f aca="false">Assumptions!$B$52</f>
+        <v>250</v>
       </c>
       <c r="T38" s="21" t="n">
-        <f aca="false">Assumptions!$B$51</f>
-        <v>600</v>
+        <f aca="false">Assumptions!$B$52</f>
+        <v>250</v>
       </c>
       <c r="U38" s="21" t="n">
-        <f aca="false">Assumptions!$B$51</f>
-        <v>600</v>
+        <f aca="false">Assumptions!$B$52</f>
+        <v>250</v>
       </c>
       <c r="V38" s="21" t="n">
-        <f aca="false">Assumptions!$B$51</f>
-        <v>600</v>
+        <f aca="false">Assumptions!$B$52</f>
+        <v>250</v>
       </c>
       <c r="W38" s="21" t="n">
-        <f aca="false">Assumptions!$B$51</f>
-        <v>600</v>
+        <f aca="false">Assumptions!$B$52</f>
+        <v>250</v>
       </c>
       <c r="X38" s="21" t="n">
-        <f aca="false">Assumptions!$B$51</f>
-        <v>600</v>
+        <f aca="false">Assumptions!$B$52</f>
+        <v>250</v>
       </c>
       <c r="Y38" s="21" t="n">
-        <f aca="false">Assumptions!$B$51</f>
-        <v>600</v>
+        <f aca="false">Assumptions!$B$52</f>
+        <v>250</v>
       </c>
       <c r="Z38" s="21" t="n">
         <f aca="false">SUM(B38:M38)</f>
-        <v>7200</v>
+        <v>3000</v>
       </c>
       <c r="AA38" s="21" t="n">
         <f aca="false">SUM(N38:Y38)</f>
-        <v>7200</v>
+        <v>3000</v>
       </c>
       <c r="AB38" s="21" t="n">
         <f aca="false">SUM(B38:Y38)</f>
-        <v>14400</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="17" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B39" s="21" t="n">
-        <f aca="false">Assumptions!$B$52</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$53</f>
+        <v>600</v>
       </c>
       <c r="C39" s="21" t="n">
-        <f aca="false">Assumptions!$B$52</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$53</f>
+        <v>600</v>
       </c>
       <c r="D39" s="21" t="n">
-        <f aca="false">Assumptions!$B$52</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$53</f>
+        <v>600</v>
       </c>
       <c r="E39" s="21" t="n">
-        <f aca="false">Assumptions!$B$52</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$53</f>
+        <v>600</v>
       </c>
       <c r="F39" s="21" t="n">
-        <f aca="false">Assumptions!$B$52</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$53</f>
+        <v>600</v>
       </c>
       <c r="G39" s="21" t="n">
-        <f aca="false">Assumptions!$B$52</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$53</f>
+        <v>600</v>
       </c>
       <c r="H39" s="21" t="n">
-        <f aca="false">Assumptions!$B$52</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$53</f>
+        <v>600</v>
       </c>
       <c r="I39" s="21" t="n">
-        <f aca="false">Assumptions!$B$52</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$53</f>
+        <v>600</v>
       </c>
       <c r="J39" s="21" t="n">
-        <f aca="false">Assumptions!$B$52</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$53</f>
+        <v>600</v>
       </c>
       <c r="K39" s="21" t="n">
-        <f aca="false">Assumptions!$B$52</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$53</f>
+        <v>600</v>
       </c>
       <c r="L39" s="21" t="n">
-        <f aca="false">Assumptions!$B$52</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$53</f>
+        <v>600</v>
       </c>
       <c r="M39" s="21" t="n">
-        <f aca="false">Assumptions!$B$52</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$53</f>
+        <v>600</v>
       </c>
       <c r="N39" s="21" t="n">
-        <f aca="false">Assumptions!$B$52</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$53</f>
+        <v>600</v>
       </c>
       <c r="O39" s="21" t="n">
-        <f aca="false">Assumptions!$B$52</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$53</f>
+        <v>600</v>
       </c>
       <c r="P39" s="21" t="n">
-        <f aca="false">Assumptions!$B$52</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$53</f>
+        <v>600</v>
       </c>
       <c r="Q39" s="21" t="n">
-        <f aca="false">Assumptions!$B$52</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$53</f>
+        <v>600</v>
       </c>
       <c r="R39" s="21" t="n">
-        <f aca="false">Assumptions!$B$52</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$53</f>
+        <v>600</v>
       </c>
       <c r="S39" s="21" t="n">
-        <f aca="false">Assumptions!$B$52</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$53</f>
+        <v>600</v>
       </c>
       <c r="T39" s="21" t="n">
-        <f aca="false">Assumptions!$B$52</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$53</f>
+        <v>600</v>
       </c>
       <c r="U39" s="21" t="n">
-        <f aca="false">Assumptions!$B$52</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$53</f>
+        <v>600</v>
       </c>
       <c r="V39" s="21" t="n">
-        <f aca="false">Assumptions!$B$52</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$53</f>
+        <v>600</v>
       </c>
       <c r="W39" s="21" t="n">
-        <f aca="false">Assumptions!$B$52</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$53</f>
+        <v>600</v>
       </c>
       <c r="X39" s="21" t="n">
-        <f aca="false">Assumptions!$B$52</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$53</f>
+        <v>600</v>
       </c>
       <c r="Y39" s="21" t="n">
-        <f aca="false">Assumptions!$B$52</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$53</f>
+        <v>600</v>
       </c>
       <c r="Z39" s="21" t="n">
         <f aca="false">SUM(B39:M39)</f>
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="AA39" s="21" t="n">
         <f aca="false">SUM(N39:Y39)</f>
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="AB39" s="21" t="n">
         <f aca="false">SUM(B39:Y39)</f>
-        <v>0</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="17" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B40" s="21" t="n">
-        <f aca="false">Assumptions!$B$34*IF(1&gt;=Assumptions!$B$8,Assumptions!$B$43,1)</f>
-        <v>900</v>
+        <f aca="false">Assumptions!$B$54</f>
+        <v>0</v>
       </c>
       <c r="C40" s="21" t="n">
-        <f aca="false">Assumptions!$B$34*IF(2&gt;=Assumptions!$B$8,Assumptions!$B$43,1)</f>
-        <v>900</v>
+        <f aca="false">Assumptions!$B$54</f>
+        <v>0</v>
       </c>
       <c r="D40" s="21" t="n">
-        <f aca="false">Assumptions!$B$34*IF(3&gt;=Assumptions!$B$8,Assumptions!$B$43,1)</f>
-        <v>900</v>
+        <f aca="false">Assumptions!$B$54</f>
+        <v>0</v>
       </c>
       <c r="E40" s="21" t="n">
-        <f aca="false">Assumptions!$B$34*IF(4&gt;=Assumptions!$B$8,Assumptions!$B$43,1)</f>
-        <v>900</v>
+        <f aca="false">Assumptions!$B$54</f>
+        <v>0</v>
       </c>
       <c r="F40" s="21" t="n">
-        <f aca="false">Assumptions!$B$34*IF(5&gt;=Assumptions!$B$8,Assumptions!$B$43,1)</f>
-        <v>900</v>
+        <f aca="false">Assumptions!$B$54</f>
+        <v>0</v>
       </c>
       <c r="G40" s="21" t="n">
-        <f aca="false">Assumptions!$B$34*IF(6&gt;=Assumptions!$B$8,Assumptions!$B$43,1)</f>
-        <v>900</v>
+        <f aca="false">Assumptions!$B$54</f>
+        <v>0</v>
       </c>
       <c r="H40" s="21" t="n">
-        <f aca="false">Assumptions!$B$34*IF(7&gt;=Assumptions!$B$8,Assumptions!$B$43,1)</f>
-        <v>1440</v>
+        <f aca="false">Assumptions!$B$54</f>
+        <v>0</v>
       </c>
       <c r="I40" s="21" t="n">
-        <f aca="false">Assumptions!$B$34*IF(8&gt;=Assumptions!$B$8,Assumptions!$B$43,1)</f>
-        <v>1440</v>
+        <f aca="false">Assumptions!$B$54</f>
+        <v>0</v>
       </c>
       <c r="J40" s="21" t="n">
-        <f aca="false">Assumptions!$B$34*IF(9&gt;=Assumptions!$B$8,Assumptions!$B$43,1)</f>
-        <v>1440</v>
+        <f aca="false">Assumptions!$B$54</f>
+        <v>0</v>
       </c>
       <c r="K40" s="21" t="n">
-        <f aca="false">Assumptions!$B$34*IF(10&gt;=Assumptions!$B$8,Assumptions!$B$43,1)</f>
-        <v>1440</v>
+        <f aca="false">Assumptions!$B$54</f>
+        <v>0</v>
       </c>
       <c r="L40" s="21" t="n">
-        <f aca="false">Assumptions!$B$34*IF(11&gt;=Assumptions!$B$8,Assumptions!$B$43,1)</f>
-        <v>1440</v>
+        <f aca="false">Assumptions!$B$54</f>
+        <v>0</v>
       </c>
       <c r="M40" s="21" t="n">
-        <f aca="false">Assumptions!$B$34*IF(12&gt;=Assumptions!$B$8,Assumptions!$B$43,1)</f>
-        <v>1440</v>
+        <f aca="false">Assumptions!$B$54</f>
+        <v>0</v>
       </c>
       <c r="N40" s="21" t="n">
-        <f aca="false">Assumptions!$B$34*IF(13&gt;=Assumptions!$B$8,Assumptions!$B$43,1)</f>
-        <v>1440</v>
+        <f aca="false">Assumptions!$B$54</f>
+        <v>0</v>
       </c>
       <c r="O40" s="21" t="n">
-        <f aca="false">Assumptions!$B$34*IF(14&gt;=Assumptions!$B$8,Assumptions!$B$43,1)</f>
-        <v>1440</v>
+        <f aca="false">Assumptions!$B$54</f>
+        <v>0</v>
       </c>
       <c r="P40" s="21" t="n">
-        <f aca="false">Assumptions!$B$34*IF(15&gt;=Assumptions!$B$8,Assumptions!$B$43,1)</f>
-        <v>1440</v>
+        <f aca="false">Assumptions!$B$54</f>
+        <v>0</v>
       </c>
       <c r="Q40" s="21" t="n">
-        <f aca="false">Assumptions!$B$34*IF(16&gt;=Assumptions!$B$8,Assumptions!$B$43,1)</f>
-        <v>1440</v>
+        <f aca="false">Assumptions!$B$54</f>
+        <v>0</v>
       </c>
       <c r="R40" s="21" t="n">
-        <f aca="false">Assumptions!$B$34*IF(17&gt;=Assumptions!$B$8,Assumptions!$B$43,1)</f>
-        <v>1440</v>
+        <f aca="false">Assumptions!$B$54</f>
+        <v>0</v>
       </c>
       <c r="S40" s="21" t="n">
-        <f aca="false">Assumptions!$B$34*IF(18&gt;=Assumptions!$B$8,Assumptions!$B$43,1)</f>
-        <v>1440</v>
+        <f aca="false">Assumptions!$B$54</f>
+        <v>0</v>
       </c>
       <c r="T40" s="21" t="n">
-        <f aca="false">Assumptions!$B$34*IF(19&gt;=Assumptions!$B$8,Assumptions!$B$43,1)</f>
-        <v>1440</v>
+        <f aca="false">Assumptions!$B$54</f>
+        <v>0</v>
       </c>
       <c r="U40" s="21" t="n">
-        <f aca="false">Assumptions!$B$34*IF(20&gt;=Assumptions!$B$8,Assumptions!$B$43,1)</f>
-        <v>1440</v>
+        <f aca="false">Assumptions!$B$54</f>
+        <v>0</v>
       </c>
       <c r="V40" s="21" t="n">
-        <f aca="false">Assumptions!$B$34*IF(21&gt;=Assumptions!$B$8,Assumptions!$B$43,1)</f>
-        <v>1440</v>
+        <f aca="false">Assumptions!$B$54</f>
+        <v>0</v>
       </c>
       <c r="W40" s="21" t="n">
-        <f aca="false">Assumptions!$B$34*IF(22&gt;=Assumptions!$B$8,Assumptions!$B$43,1)</f>
-        <v>1440</v>
+        <f aca="false">Assumptions!$B$54</f>
+        <v>0</v>
       </c>
       <c r="X40" s="21" t="n">
-        <f aca="false">Assumptions!$B$34*IF(23&gt;=Assumptions!$B$8,Assumptions!$B$43,1)</f>
-        <v>1440</v>
+        <f aca="false">Assumptions!$B$54</f>
+        <v>0</v>
       </c>
       <c r="Y40" s="21" t="n">
-        <f aca="false">Assumptions!$B$34*IF(24&gt;=Assumptions!$B$8,Assumptions!$B$43,1)</f>
-        <v>1440</v>
+        <f aca="false">Assumptions!$B$54</f>
+        <v>0</v>
       </c>
       <c r="Z40" s="21" t="n">
         <f aca="false">SUM(B40:M40)</f>
-        <v>14040</v>
+        <v>0</v>
       </c>
       <c r="AA40" s="21" t="n">
         <f aca="false">SUM(N40:Y40)</f>
-        <v>17280</v>
+        <v>0</v>
       </c>
       <c r="AB40" s="21" t="n">
         <f aca="false">SUM(B40:Y40)</f>
-        <v>31320</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="17" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B41" s="21" t="n">
-        <f aca="false">IF(1&gt;=2,Assumptions!$B$37*IF(1&gt;=Assumptions!$B$8,Assumptions!$B$43,1),0)</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$34*IF(1&gt;=Assumptions!$B$8,Assumptions!$B$45,1)</f>
+        <v>900</v>
       </c>
       <c r="C41" s="21" t="n">
-        <f aca="false">IF(2&gt;=2,Assumptions!$B$37*IF(2&gt;=Assumptions!$B$8,Assumptions!$B$43,1),0)</f>
-        <v>600</v>
+        <f aca="false">Assumptions!$B$34*IF(2&gt;=Assumptions!$B$8,Assumptions!$B$45,1)</f>
+        <v>900</v>
       </c>
       <c r="D41" s="21" t="n">
-        <f aca="false">IF(3&gt;=2,Assumptions!$B$37*IF(3&gt;=Assumptions!$B$8,Assumptions!$B$43,1),0)</f>
-        <v>600</v>
+        <f aca="false">Assumptions!$B$34*IF(3&gt;=Assumptions!$B$8,Assumptions!$B$45,1)</f>
+        <v>900</v>
       </c>
       <c r="E41" s="21" t="n">
-        <f aca="false">IF(4&gt;=2,Assumptions!$B$37*IF(4&gt;=Assumptions!$B$8,Assumptions!$B$43,1),0)</f>
-        <v>600</v>
+        <f aca="false">Assumptions!$B$34*IF(4&gt;=Assumptions!$B$8,Assumptions!$B$45,1)</f>
+        <v>900</v>
       </c>
       <c r="F41" s="21" t="n">
-        <f aca="false">IF(5&gt;=2,Assumptions!$B$37*IF(5&gt;=Assumptions!$B$8,Assumptions!$B$43,1),0)</f>
-        <v>600</v>
+        <f aca="false">Assumptions!$B$34*IF(5&gt;=Assumptions!$B$8,Assumptions!$B$45,1)</f>
+        <v>900</v>
       </c>
       <c r="G41" s="21" t="n">
-        <f aca="false">IF(6&gt;=2,Assumptions!$B$37*IF(6&gt;=Assumptions!$B$8,Assumptions!$B$43,1),0)</f>
-        <v>600</v>
+        <f aca="false">Assumptions!$B$34*IF(6&gt;=Assumptions!$B$8,Assumptions!$B$45,1)</f>
+        <v>900</v>
       </c>
       <c r="H41" s="21" t="n">
-        <f aca="false">IF(7&gt;=2,Assumptions!$B$37*IF(7&gt;=Assumptions!$B$8,Assumptions!$B$43,1),0)</f>
-        <v>960</v>
+        <f aca="false">Assumptions!$B$34*IF(7&gt;=Assumptions!$B$8,Assumptions!$B$45,1)</f>
+        <v>1440</v>
       </c>
       <c r="I41" s="21" t="n">
-        <f aca="false">IF(8&gt;=2,Assumptions!$B$37*IF(8&gt;=Assumptions!$B$8,Assumptions!$B$43,1),0)</f>
-        <v>960</v>
+        <f aca="false">Assumptions!$B$34*IF(8&gt;=Assumptions!$B$8,Assumptions!$B$45,1)</f>
+        <v>1440</v>
       </c>
       <c r="J41" s="21" t="n">
-        <f aca="false">IF(9&gt;=2,Assumptions!$B$37*IF(9&gt;=Assumptions!$B$8,Assumptions!$B$43,1),0)</f>
-        <v>960</v>
+        <f aca="false">Assumptions!$B$34*IF(9&gt;=Assumptions!$B$8,Assumptions!$B$45,1)</f>
+        <v>1440</v>
       </c>
       <c r="K41" s="21" t="n">
-        <f aca="false">IF(10&gt;=2,Assumptions!$B$37*IF(10&gt;=Assumptions!$B$8,Assumptions!$B$43,1),0)</f>
-        <v>960</v>
+        <f aca="false">Assumptions!$B$34*IF(10&gt;=Assumptions!$B$8,Assumptions!$B$45,1)</f>
+        <v>1440</v>
       </c>
       <c r="L41" s="21" t="n">
-        <f aca="false">IF(11&gt;=2,Assumptions!$B$37*IF(11&gt;=Assumptions!$B$8,Assumptions!$B$43,1),0)</f>
-        <v>960</v>
+        <f aca="false">Assumptions!$B$34*IF(11&gt;=Assumptions!$B$8,Assumptions!$B$45,1)</f>
+        <v>1440</v>
       </c>
       <c r="M41" s="21" t="n">
-        <f aca="false">IF(12&gt;=2,Assumptions!$B$37*IF(12&gt;=Assumptions!$B$8,Assumptions!$B$43,1),0)</f>
-        <v>960</v>
+        <f aca="false">Assumptions!$B$34*IF(12&gt;=Assumptions!$B$8,Assumptions!$B$45,1)</f>
+        <v>1440</v>
       </c>
       <c r="N41" s="21" t="n">
-        <f aca="false">IF(13&gt;=2,Assumptions!$B$37*IF(13&gt;=Assumptions!$B$8,Assumptions!$B$43,1),0)</f>
-        <v>960</v>
+        <f aca="false">Assumptions!$B$34*IF(13&gt;=Assumptions!$B$8,Assumptions!$B$45,1)</f>
+        <v>1440</v>
       </c>
       <c r="O41" s="21" t="n">
-        <f aca="false">IF(14&gt;=2,Assumptions!$B$37*IF(14&gt;=Assumptions!$B$8,Assumptions!$B$43,1),0)</f>
-        <v>960</v>
+        <f aca="false">Assumptions!$B$34*IF(14&gt;=Assumptions!$B$8,Assumptions!$B$45,1)</f>
+        <v>1440</v>
       </c>
       <c r="P41" s="21" t="n">
-        <f aca="false">IF(15&gt;=2,Assumptions!$B$37*IF(15&gt;=Assumptions!$B$8,Assumptions!$B$43,1),0)</f>
-        <v>960</v>
+        <f aca="false">Assumptions!$B$34*IF(15&gt;=Assumptions!$B$8,Assumptions!$B$45,1)</f>
+        <v>1440</v>
       </c>
       <c r="Q41" s="21" t="n">
-        <f aca="false">IF(16&gt;=2,Assumptions!$B$37*IF(16&gt;=Assumptions!$B$8,Assumptions!$B$43,1),0)</f>
-        <v>960</v>
+        <f aca="false">Assumptions!$B$34*IF(16&gt;=Assumptions!$B$8,Assumptions!$B$45,1)</f>
+        <v>1440</v>
       </c>
       <c r="R41" s="21" t="n">
-        <f aca="false">IF(17&gt;=2,Assumptions!$B$37*IF(17&gt;=Assumptions!$B$8,Assumptions!$B$43,1),0)</f>
-        <v>960</v>
+        <f aca="false">Assumptions!$B$34*IF(17&gt;=Assumptions!$B$8,Assumptions!$B$45,1)</f>
+        <v>1440</v>
       </c>
       <c r="S41" s="21" t="n">
-        <f aca="false">IF(18&gt;=2,Assumptions!$B$37*IF(18&gt;=Assumptions!$B$8,Assumptions!$B$43,1),0)</f>
-        <v>960</v>
+        <f aca="false">Assumptions!$B$34*IF(18&gt;=Assumptions!$B$8,Assumptions!$B$45,1)</f>
+        <v>1440</v>
       </c>
       <c r="T41" s="21" t="n">
-        <f aca="false">IF(19&gt;=2,Assumptions!$B$37*IF(19&gt;=Assumptions!$B$8,Assumptions!$B$43,1),0)</f>
-        <v>960</v>
+        <f aca="false">Assumptions!$B$34*IF(19&gt;=Assumptions!$B$8,Assumptions!$B$45,1)</f>
+        <v>1440</v>
       </c>
       <c r="U41" s="21" t="n">
-        <f aca="false">IF(20&gt;=2,Assumptions!$B$37*IF(20&gt;=Assumptions!$B$8,Assumptions!$B$43,1),0)</f>
-        <v>960</v>
+        <f aca="false">Assumptions!$B$34*IF(20&gt;=Assumptions!$B$8,Assumptions!$B$45,1)</f>
+        <v>1440</v>
       </c>
       <c r="V41" s="21" t="n">
-        <f aca="false">IF(21&gt;=2,Assumptions!$B$37*IF(21&gt;=Assumptions!$B$8,Assumptions!$B$43,1),0)</f>
-        <v>960</v>
+        <f aca="false">Assumptions!$B$34*IF(21&gt;=Assumptions!$B$8,Assumptions!$B$45,1)</f>
+        <v>1440</v>
       </c>
       <c r="W41" s="21" t="n">
-        <f aca="false">IF(22&gt;=2,Assumptions!$B$37*IF(22&gt;=Assumptions!$B$8,Assumptions!$B$43,1),0)</f>
-        <v>960</v>
+        <f aca="false">Assumptions!$B$34*IF(22&gt;=Assumptions!$B$8,Assumptions!$B$45,1)</f>
+        <v>1440</v>
       </c>
       <c r="X41" s="21" t="n">
-        <f aca="false">IF(23&gt;=2,Assumptions!$B$37*IF(23&gt;=Assumptions!$B$8,Assumptions!$B$43,1),0)</f>
-        <v>960</v>
+        <f aca="false">Assumptions!$B$34*IF(23&gt;=Assumptions!$B$8,Assumptions!$B$45,1)</f>
+        <v>1440</v>
       </c>
       <c r="Y41" s="21" t="n">
-        <f aca="false">IF(24&gt;=2,Assumptions!$B$37*IF(24&gt;=Assumptions!$B$8,Assumptions!$B$43,1),0)</f>
-        <v>960</v>
+        <f aca="false">Assumptions!$B$34*IF(24&gt;=Assumptions!$B$8,Assumptions!$B$45,1)</f>
+        <v>1440</v>
       </c>
       <c r="Z41" s="21" t="n">
         <f aca="false">SUM(B41:M41)</f>
-        <v>8760</v>
+        <v>14040</v>
       </c>
       <c r="AA41" s="21" t="n">
         <f aca="false">SUM(N41:Y41)</f>
-        <v>11520</v>
+        <v>17280</v>
       </c>
       <c r="AB41" s="21" t="n">
         <f aca="false">SUM(B41:Y41)</f>
-        <v>20280</v>
+        <v>31320</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="17" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B42" s="21" t="n">
-        <f aca="false">Assumptions!$B$44</f>
-        <v>300</v>
+        <f aca="false">IF(1&gt;=2,Assumptions!$B$37*IF(1&gt;=Assumptions!$B$8,Assumptions!$B$45,1),0)</f>
+        <v>0</v>
       </c>
       <c r="C42" s="21" t="n">
-        <f aca="false">Assumptions!$B$44</f>
-        <v>300</v>
+        <f aca="false">IF(2&gt;=2,Assumptions!$B$37*IF(2&gt;=Assumptions!$B$8,Assumptions!$B$45,1),0)</f>
+        <v>600</v>
       </c>
       <c r="D42" s="21" t="n">
-        <f aca="false">Assumptions!$B$44</f>
-        <v>300</v>
+        <f aca="false">IF(3&gt;=2,Assumptions!$B$37*IF(3&gt;=Assumptions!$B$8,Assumptions!$B$45,1),0)</f>
+        <v>600</v>
       </c>
       <c r="E42" s="21" t="n">
-        <f aca="false">Assumptions!$B$44</f>
-        <v>300</v>
+        <f aca="false">IF(4&gt;=2,Assumptions!$B$37*IF(4&gt;=Assumptions!$B$8,Assumptions!$B$45,1),0)</f>
+        <v>600</v>
       </c>
       <c r="F42" s="21" t="n">
-        <f aca="false">Assumptions!$B$44</f>
-        <v>300</v>
+        <f aca="false">IF(5&gt;=2,Assumptions!$B$37*IF(5&gt;=Assumptions!$B$8,Assumptions!$B$45,1),0)</f>
+        <v>600</v>
       </c>
       <c r="G42" s="21" t="n">
-        <f aca="false">Assumptions!$B$44</f>
-        <v>300</v>
+        <f aca="false">IF(6&gt;=2,Assumptions!$B$37*IF(6&gt;=Assumptions!$B$8,Assumptions!$B$45,1),0)</f>
+        <v>600</v>
       </c>
       <c r="H42" s="21" t="n">
-        <f aca="false">Assumptions!$B$44</f>
-        <v>300</v>
+        <f aca="false">IF(7&gt;=2,Assumptions!$B$37*IF(7&gt;=Assumptions!$B$8,Assumptions!$B$45,1),0)</f>
+        <v>960</v>
       </c>
       <c r="I42" s="21" t="n">
-        <f aca="false">Assumptions!$B$44</f>
-        <v>300</v>
+        <f aca="false">IF(8&gt;=2,Assumptions!$B$37*IF(8&gt;=Assumptions!$B$8,Assumptions!$B$45,1),0)</f>
+        <v>960</v>
       </c>
       <c r="J42" s="21" t="n">
-        <f aca="false">Assumptions!$B$44</f>
-        <v>300</v>
+        <f aca="false">IF(9&gt;=2,Assumptions!$B$37*IF(9&gt;=Assumptions!$B$8,Assumptions!$B$45,1),0)</f>
+        <v>960</v>
       </c>
       <c r="K42" s="21" t="n">
-        <f aca="false">Assumptions!$B$44</f>
-        <v>300</v>
+        <f aca="false">IF(10&gt;=2,Assumptions!$B$37*IF(10&gt;=Assumptions!$B$8,Assumptions!$B$45,1),0)</f>
+        <v>960</v>
       </c>
       <c r="L42" s="21" t="n">
-        <f aca="false">Assumptions!$B$44</f>
-        <v>300</v>
+        <f aca="false">IF(11&gt;=2,Assumptions!$B$37*IF(11&gt;=Assumptions!$B$8,Assumptions!$B$45,1),0)</f>
+        <v>960</v>
       </c>
       <c r="M42" s="21" t="n">
-        <f aca="false">Assumptions!$B$44</f>
-        <v>300</v>
+        <f aca="false">IF(12&gt;=2,Assumptions!$B$37*IF(12&gt;=Assumptions!$B$8,Assumptions!$B$45,1),0)</f>
+        <v>960</v>
       </c>
       <c r="N42" s="21" t="n">
-        <f aca="false">Assumptions!$B$44</f>
-        <v>300</v>
+        <f aca="false">IF(13&gt;=2,Assumptions!$B$37*IF(13&gt;=Assumptions!$B$8,Assumptions!$B$45,1),0)</f>
+        <v>960</v>
       </c>
       <c r="O42" s="21" t="n">
-        <f aca="false">Assumptions!$B$44</f>
-        <v>300</v>
+        <f aca="false">IF(14&gt;=2,Assumptions!$B$37*IF(14&gt;=Assumptions!$B$8,Assumptions!$B$45,1),0)</f>
+        <v>960</v>
       </c>
       <c r="P42" s="21" t="n">
-        <f aca="false">Assumptions!$B$44</f>
-        <v>300</v>
+        <f aca="false">IF(15&gt;=2,Assumptions!$B$37*IF(15&gt;=Assumptions!$B$8,Assumptions!$B$45,1),0)</f>
+        <v>960</v>
       </c>
       <c r="Q42" s="21" t="n">
-        <f aca="false">Assumptions!$B$44</f>
-        <v>300</v>
+        <f aca="false">IF(16&gt;=2,Assumptions!$B$37*IF(16&gt;=Assumptions!$B$8,Assumptions!$B$45,1),0)</f>
+        <v>960</v>
       </c>
       <c r="R42" s="21" t="n">
-        <f aca="false">Assumptions!$B$44</f>
-        <v>300</v>
+        <f aca="false">IF(17&gt;=2,Assumptions!$B$37*IF(17&gt;=Assumptions!$B$8,Assumptions!$B$45,1),0)</f>
+        <v>960</v>
       </c>
       <c r="S42" s="21" t="n">
-        <f aca="false">Assumptions!$B$44</f>
-        <v>300</v>
+        <f aca="false">IF(18&gt;=2,Assumptions!$B$37*IF(18&gt;=Assumptions!$B$8,Assumptions!$B$45,1),0)</f>
+        <v>960</v>
       </c>
       <c r="T42" s="21" t="n">
-        <f aca="false">Assumptions!$B$44</f>
-        <v>300</v>
+        <f aca="false">IF(19&gt;=2,Assumptions!$B$37*IF(19&gt;=Assumptions!$B$8,Assumptions!$B$45,1),0)</f>
+        <v>960</v>
       </c>
       <c r="U42" s="21" t="n">
-        <f aca="false">Assumptions!$B$44</f>
-        <v>300</v>
+        <f aca="false">IF(20&gt;=2,Assumptions!$B$37*IF(20&gt;=Assumptions!$B$8,Assumptions!$B$45,1),0)</f>
+        <v>960</v>
       </c>
       <c r="V42" s="21" t="n">
-        <f aca="false">Assumptions!$B$44</f>
-        <v>300</v>
+        <f aca="false">IF(21&gt;=2,Assumptions!$B$37*IF(21&gt;=Assumptions!$B$8,Assumptions!$B$45,1),0)</f>
+        <v>960</v>
       </c>
       <c r="W42" s="21" t="n">
-        <f aca="false">Assumptions!$B$44</f>
-        <v>300</v>
+        <f aca="false">IF(22&gt;=2,Assumptions!$B$37*IF(22&gt;=Assumptions!$B$8,Assumptions!$B$45,1),0)</f>
+        <v>960</v>
       </c>
       <c r="X42" s="21" t="n">
-        <f aca="false">Assumptions!$B$44</f>
-        <v>300</v>
+        <f aca="false">IF(23&gt;=2,Assumptions!$B$37*IF(23&gt;=Assumptions!$B$8,Assumptions!$B$45,1),0)</f>
+        <v>960</v>
       </c>
       <c r="Y42" s="21" t="n">
-        <f aca="false">Assumptions!$B$44</f>
-        <v>300</v>
+        <f aca="false">IF(24&gt;=2,Assumptions!$B$37*IF(24&gt;=Assumptions!$B$8,Assumptions!$B$45,1),0)</f>
+        <v>960</v>
       </c>
       <c r="Z42" s="21" t="n">
         <f aca="false">SUM(B42:M42)</f>
-        <v>3600</v>
+        <v>8760</v>
       </c>
       <c r="AA42" s="21" t="n">
         <f aca="false">SUM(N42:Y42)</f>
-        <v>3600</v>
+        <v>11520</v>
       </c>
       <c r="AB42" s="21" t="n">
         <f aca="false">SUM(B42:Y42)</f>
-        <v>7200</v>
+        <v>20280</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="17" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B43" s="21" t="n">
-        <f aca="false">IF(AND(1&gt;=Assumptions!$B$8,1&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(1&gt;=Assumptions!$B$8,1&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(1&gt;=Assumptions!$B$8,1&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(1&gt;=Assumptions!$B$8,1&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(1&gt;=Assumptions!$B$8,1&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(1=Assumptions!$B$8,Assumptions!$B$72,0)</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$46</f>
+        <v>300</v>
       </c>
       <c r="C43" s="21" t="n">
-        <f aca="false">IF(AND(2&gt;=Assumptions!$B$8,2&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(2&gt;=Assumptions!$B$8,2&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(2&gt;=Assumptions!$B$8,2&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(2&gt;=Assumptions!$B$8,2&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(2&gt;=Assumptions!$B$8,2&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(2=Assumptions!$B$8,Assumptions!$B$72,0)</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$46</f>
+        <v>300</v>
       </c>
       <c r="D43" s="21" t="n">
-        <f aca="false">IF(AND(3&gt;=Assumptions!$B$8,3&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(3&gt;=Assumptions!$B$8,3&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(3&gt;=Assumptions!$B$8,3&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(3&gt;=Assumptions!$B$8,3&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(3&gt;=Assumptions!$B$8,3&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(3=Assumptions!$B$8,Assumptions!$B$72,0)</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$46</f>
+        <v>300</v>
       </c>
       <c r="E43" s="21" t="n">
-        <f aca="false">IF(AND(4&gt;=Assumptions!$B$8,4&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(4&gt;=Assumptions!$B$8,4&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(4&gt;=Assumptions!$B$8,4&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(4&gt;=Assumptions!$B$8,4&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(4&gt;=Assumptions!$B$8,4&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(4=Assumptions!$B$8,Assumptions!$B$72,0)</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$46</f>
+        <v>300</v>
       </c>
       <c r="F43" s="21" t="n">
-        <f aca="false">IF(AND(5&gt;=Assumptions!$B$8,5&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(5&gt;=Assumptions!$B$8,5&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(5&gt;=Assumptions!$B$8,5&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(5&gt;=Assumptions!$B$8,5&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(5&gt;=Assumptions!$B$8,5&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(5=Assumptions!$B$8,Assumptions!$B$72,0)</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$46</f>
+        <v>300</v>
       </c>
       <c r="G43" s="21" t="n">
-        <f aca="false">IF(AND(6&gt;=Assumptions!$B$8,6&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(6&gt;=Assumptions!$B$8,6&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(6&gt;=Assumptions!$B$8,6&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(6&gt;=Assumptions!$B$8,6&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(6&gt;=Assumptions!$B$8,6&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(6=Assumptions!$B$8,Assumptions!$B$72,0)</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$46</f>
+        <v>300</v>
       </c>
       <c r="H43" s="21" t="n">
-        <f aca="false">IF(AND(7&gt;=Assumptions!$B$8,7&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(7&gt;=Assumptions!$B$8,7&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(7&gt;=Assumptions!$B$8,7&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(7&gt;=Assumptions!$B$8,7&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(7&gt;=Assumptions!$B$8,7&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(7=Assumptions!$B$8,Assumptions!$B$72,0)</f>
-        <v>8200</v>
+        <f aca="false">Assumptions!$B$46</f>
+        <v>300</v>
       </c>
       <c r="I43" s="21" t="n">
-        <f aca="false">IF(AND(8&gt;=Assumptions!$B$8,8&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(8&gt;=Assumptions!$B$8,8&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(8&gt;=Assumptions!$B$8,8&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(8&gt;=Assumptions!$B$8,8&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(8&gt;=Assumptions!$B$8,8&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(8=Assumptions!$B$8,Assumptions!$B$72,0)</f>
-        <v>3700</v>
+        <f aca="false">Assumptions!$B$46</f>
+        <v>300</v>
       </c>
       <c r="J43" s="21" t="n">
-        <f aca="false">IF(AND(9&gt;=Assumptions!$B$8,9&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(9&gt;=Assumptions!$B$8,9&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(9&gt;=Assumptions!$B$8,9&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(9&gt;=Assumptions!$B$8,9&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(9&gt;=Assumptions!$B$8,9&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(9=Assumptions!$B$8,Assumptions!$B$72,0)</f>
-        <v>3700</v>
+        <f aca="false">Assumptions!$B$46</f>
+        <v>300</v>
       </c>
       <c r="K43" s="21" t="n">
-        <f aca="false">IF(AND(10&gt;=Assumptions!$B$8,10&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(10&gt;=Assumptions!$B$8,10&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(10&gt;=Assumptions!$B$8,10&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(10&gt;=Assumptions!$B$8,10&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(10&gt;=Assumptions!$B$8,10&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(10=Assumptions!$B$8,Assumptions!$B$72,0)</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$46</f>
+        <v>300</v>
       </c>
       <c r="L43" s="21" t="n">
-        <f aca="false">IF(AND(11&gt;=Assumptions!$B$8,11&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(11&gt;=Assumptions!$B$8,11&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(11&gt;=Assumptions!$B$8,11&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(11&gt;=Assumptions!$B$8,11&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(11&gt;=Assumptions!$B$8,11&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(11=Assumptions!$B$8,Assumptions!$B$72,0)</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$46</f>
+        <v>300</v>
       </c>
       <c r="M43" s="21" t="n">
-        <f aca="false">IF(AND(12&gt;=Assumptions!$B$8,12&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(12&gt;=Assumptions!$B$8,12&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(12&gt;=Assumptions!$B$8,12&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(12&gt;=Assumptions!$B$8,12&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(12&gt;=Assumptions!$B$8,12&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(12=Assumptions!$B$8,Assumptions!$B$72,0)</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$46</f>
+        <v>300</v>
       </c>
       <c r="N43" s="21" t="n">
-        <f aca="false">IF(AND(13&gt;=Assumptions!$B$8,13&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(13&gt;=Assumptions!$B$8,13&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(13&gt;=Assumptions!$B$8,13&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(13&gt;=Assumptions!$B$8,13&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(13&gt;=Assumptions!$B$8,13&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(13=Assumptions!$B$8,Assumptions!$B$72,0)</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$46</f>
+        <v>300</v>
       </c>
       <c r="O43" s="21" t="n">
-        <f aca="false">IF(AND(14&gt;=Assumptions!$B$8,14&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(14&gt;=Assumptions!$B$8,14&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(14&gt;=Assumptions!$B$8,14&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(14&gt;=Assumptions!$B$8,14&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(14&gt;=Assumptions!$B$8,14&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(14=Assumptions!$B$8,Assumptions!$B$72,0)</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$46</f>
+        <v>300</v>
       </c>
       <c r="P43" s="21" t="n">
-        <f aca="false">IF(AND(15&gt;=Assumptions!$B$8,15&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(15&gt;=Assumptions!$B$8,15&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(15&gt;=Assumptions!$B$8,15&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(15&gt;=Assumptions!$B$8,15&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(15&gt;=Assumptions!$B$8,15&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(15=Assumptions!$B$8,Assumptions!$B$72,0)</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$46</f>
+        <v>300</v>
       </c>
       <c r="Q43" s="21" t="n">
-        <f aca="false">IF(AND(16&gt;=Assumptions!$B$8,16&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(16&gt;=Assumptions!$B$8,16&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(16&gt;=Assumptions!$B$8,16&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(16&gt;=Assumptions!$B$8,16&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(16&gt;=Assumptions!$B$8,16&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(16=Assumptions!$B$8,Assumptions!$B$72,0)</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$46</f>
+        <v>300</v>
       </c>
       <c r="R43" s="21" t="n">
-        <f aca="false">IF(AND(17&gt;=Assumptions!$B$8,17&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(17&gt;=Assumptions!$B$8,17&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(17&gt;=Assumptions!$B$8,17&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(17&gt;=Assumptions!$B$8,17&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(17&gt;=Assumptions!$B$8,17&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(17=Assumptions!$B$8,Assumptions!$B$72,0)</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$46</f>
+        <v>300</v>
       </c>
       <c r="S43" s="21" t="n">
-        <f aca="false">IF(AND(18&gt;=Assumptions!$B$8,18&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(18&gt;=Assumptions!$B$8,18&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(18&gt;=Assumptions!$B$8,18&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(18&gt;=Assumptions!$B$8,18&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(18&gt;=Assumptions!$B$8,18&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(18=Assumptions!$B$8,Assumptions!$B$72,0)</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$46</f>
+        <v>300</v>
       </c>
       <c r="T43" s="21" t="n">
-        <f aca="false">IF(AND(19&gt;=Assumptions!$B$8,19&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(19&gt;=Assumptions!$B$8,19&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(19&gt;=Assumptions!$B$8,19&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(19&gt;=Assumptions!$B$8,19&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(19&gt;=Assumptions!$B$8,19&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(19=Assumptions!$B$8,Assumptions!$B$72,0)</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$46</f>
+        <v>300</v>
       </c>
       <c r="U43" s="21" t="n">
-        <f aca="false">IF(AND(20&gt;=Assumptions!$B$8,20&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(20&gt;=Assumptions!$B$8,20&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(20&gt;=Assumptions!$B$8,20&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(20&gt;=Assumptions!$B$8,20&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(20&gt;=Assumptions!$B$8,20&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(20=Assumptions!$B$8,Assumptions!$B$72,0)</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$46</f>
+        <v>300</v>
       </c>
       <c r="V43" s="21" t="n">
-        <f aca="false">IF(AND(21&gt;=Assumptions!$B$8,21&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(21&gt;=Assumptions!$B$8,21&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(21&gt;=Assumptions!$B$8,21&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(21&gt;=Assumptions!$B$8,21&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(21&gt;=Assumptions!$B$8,21&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(21=Assumptions!$B$8,Assumptions!$B$72,0)</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$46</f>
+        <v>300</v>
       </c>
       <c r="W43" s="21" t="n">
-        <f aca="false">IF(AND(22&gt;=Assumptions!$B$8,22&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(22&gt;=Assumptions!$B$8,22&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(22&gt;=Assumptions!$B$8,22&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(22&gt;=Assumptions!$B$8,22&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(22&gt;=Assumptions!$B$8,22&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(22=Assumptions!$B$8,Assumptions!$B$72,0)</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$46</f>
+        <v>300</v>
       </c>
       <c r="X43" s="21" t="n">
-        <f aca="false">IF(AND(23&gt;=Assumptions!$B$8,23&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(23&gt;=Assumptions!$B$8,23&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(23&gt;=Assumptions!$B$8,23&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(23&gt;=Assumptions!$B$8,23&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(23&gt;=Assumptions!$B$8,23&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(23=Assumptions!$B$8,Assumptions!$B$72,0)</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$46</f>
+        <v>300</v>
       </c>
       <c r="Y43" s="21" t="n">
-        <f aca="false">IF(AND(24&gt;=Assumptions!$B$8,24&lt;Assumptions!$B$8+Assumptions!$B$56),Assumptions!$B$55,0)+IF(AND(24&gt;=Assumptions!$B$8,24&lt;Assumptions!$B$8+Assumptions!$B$59),Assumptions!$B$58,0)+IF(AND(24&gt;=Assumptions!$B$8,24&lt;Assumptions!$B$8+Assumptions!$B$62),Assumptions!$B$61,0)+IF(AND(24&gt;=Assumptions!$B$8,24&lt;Assumptions!$B$8+Assumptions!$B$65),Assumptions!$B$64,0)+IF(AND(24&gt;=Assumptions!$B$8,24&lt;Assumptions!$B$8+Assumptions!$B$68),Assumptions!$B$67,0)+IF(24=Assumptions!$B$8,Assumptions!$B$72,0)</f>
-        <v>0</v>
+        <f aca="false">Assumptions!$B$46</f>
+        <v>300</v>
       </c>
       <c r="Z43" s="21" t="n">
         <f aca="false">SUM(B43:M43)</f>
-        <v>15600</v>
+        <v>3600</v>
       </c>
       <c r="AA43" s="21" t="n">
         <f aca="false">SUM(N43:Y43)</f>
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="AB43" s="21" t="n">
         <f aca="false">SUM(B43:Y43)</f>
-        <v>15600</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="17" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B44" s="21" t="n">
-        <f aca="false">IF(1&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(1&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(1&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(1&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(1&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
+        <f aca="false">IF(AND(1&gt;=Assumptions!$B$8,1&lt;Assumptions!$B$8+Assumptions!$B$58),Assumptions!$B$57,0)+IF(AND(1&gt;=Assumptions!$B$8,1&lt;Assumptions!$B$8+Assumptions!$B$61),Assumptions!$B$60,0)+IF(AND(1&gt;=Assumptions!$B$8,1&lt;Assumptions!$B$8+Assumptions!$B$64),Assumptions!$B$63,0)+IF(AND(1&gt;=Assumptions!$B$8,1&lt;Assumptions!$B$8+Assumptions!$B$67),Assumptions!$B$66,0)+IF(AND(1&gt;=Assumptions!$B$8,1&lt;Assumptions!$B$8+Assumptions!$B$70),Assumptions!$B$69,0)+IF(1=Assumptions!$B$8,Assumptions!$B$74,0)</f>
         <v>0</v>
       </c>
       <c r="C44" s="21" t="n">
-        <f aca="false">IF(2&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(2&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(2&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(2&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(2&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
+        <f aca="false">IF(AND(2&gt;=Assumptions!$B$8,2&lt;Assumptions!$B$8+Assumptions!$B$58),Assumptions!$B$57,0)+IF(AND(2&gt;=Assumptions!$B$8,2&lt;Assumptions!$B$8+Assumptions!$B$61),Assumptions!$B$60,0)+IF(AND(2&gt;=Assumptions!$B$8,2&lt;Assumptions!$B$8+Assumptions!$B$64),Assumptions!$B$63,0)+IF(AND(2&gt;=Assumptions!$B$8,2&lt;Assumptions!$B$8+Assumptions!$B$67),Assumptions!$B$66,0)+IF(AND(2&gt;=Assumptions!$B$8,2&lt;Assumptions!$B$8+Assumptions!$B$70),Assumptions!$B$69,0)+IF(2=Assumptions!$B$8,Assumptions!$B$74,0)</f>
         <v>0</v>
       </c>
       <c r="D44" s="21" t="n">
-        <f aca="false">IF(3&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(3&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(3&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(3&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(3&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
+        <f aca="false">IF(AND(3&gt;=Assumptions!$B$8,3&lt;Assumptions!$B$8+Assumptions!$B$58),Assumptions!$B$57,0)+IF(AND(3&gt;=Assumptions!$B$8,3&lt;Assumptions!$B$8+Assumptions!$B$61),Assumptions!$B$60,0)+IF(AND(3&gt;=Assumptions!$B$8,3&lt;Assumptions!$B$8+Assumptions!$B$64),Assumptions!$B$63,0)+IF(AND(3&gt;=Assumptions!$B$8,3&lt;Assumptions!$B$8+Assumptions!$B$67),Assumptions!$B$66,0)+IF(AND(3&gt;=Assumptions!$B$8,3&lt;Assumptions!$B$8+Assumptions!$B$70),Assumptions!$B$69,0)+IF(3=Assumptions!$B$8,Assumptions!$B$74,0)</f>
         <v>0</v>
       </c>
       <c r="E44" s="21" t="n">
-        <f aca="false">IF(4&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(4&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(4&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(4&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(4&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
+        <f aca="false">IF(AND(4&gt;=Assumptions!$B$8,4&lt;Assumptions!$B$8+Assumptions!$B$58),Assumptions!$B$57,0)+IF(AND(4&gt;=Assumptions!$B$8,4&lt;Assumptions!$B$8+Assumptions!$B$61),Assumptions!$B$60,0)+IF(AND(4&gt;=Assumptions!$B$8,4&lt;Assumptions!$B$8+Assumptions!$B$64),Assumptions!$B$63,0)+IF(AND(4&gt;=Assumptions!$B$8,4&lt;Assumptions!$B$8+Assumptions!$B$67),Assumptions!$B$66,0)+IF(AND(4&gt;=Assumptions!$B$8,4&lt;Assumptions!$B$8+Assumptions!$B$70),Assumptions!$B$69,0)+IF(4=Assumptions!$B$8,Assumptions!$B$74,0)</f>
         <v>0</v>
       </c>
       <c r="F44" s="21" t="n">
-        <f aca="false">IF(5&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(5&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(5&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(5&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(5&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
+        <f aca="false">IF(AND(5&gt;=Assumptions!$B$8,5&lt;Assumptions!$B$8+Assumptions!$B$58),Assumptions!$B$57,0)+IF(AND(5&gt;=Assumptions!$B$8,5&lt;Assumptions!$B$8+Assumptions!$B$61),Assumptions!$B$60,0)+IF(AND(5&gt;=Assumptions!$B$8,5&lt;Assumptions!$B$8+Assumptions!$B$64),Assumptions!$B$63,0)+IF(AND(5&gt;=Assumptions!$B$8,5&lt;Assumptions!$B$8+Assumptions!$B$67),Assumptions!$B$66,0)+IF(AND(5&gt;=Assumptions!$B$8,5&lt;Assumptions!$B$8+Assumptions!$B$70),Assumptions!$B$69,0)+IF(5=Assumptions!$B$8,Assumptions!$B$74,0)</f>
         <v>0</v>
       </c>
       <c r="G44" s="21" t="n">
-        <f aca="false">IF(6&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(6&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(6&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(6&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(6&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
+        <f aca="false">IF(AND(6&gt;=Assumptions!$B$8,6&lt;Assumptions!$B$8+Assumptions!$B$58),Assumptions!$B$57,0)+IF(AND(6&gt;=Assumptions!$B$8,6&lt;Assumptions!$B$8+Assumptions!$B$61),Assumptions!$B$60,0)+IF(AND(6&gt;=Assumptions!$B$8,6&lt;Assumptions!$B$8+Assumptions!$B$64),Assumptions!$B$63,0)+IF(AND(6&gt;=Assumptions!$B$8,6&lt;Assumptions!$B$8+Assumptions!$B$67),Assumptions!$B$66,0)+IF(AND(6&gt;=Assumptions!$B$8,6&lt;Assumptions!$B$8+Assumptions!$B$70),Assumptions!$B$69,0)+IF(6=Assumptions!$B$8,Assumptions!$B$74,0)</f>
         <v>0</v>
       </c>
       <c r="H44" s="21" t="n">
-        <f aca="false">IF(7&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(7&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(7&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(7&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(7&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
-        <v>838.637551144702</v>
+        <f aca="false">IF(AND(7&gt;=Assumptions!$B$8,7&lt;Assumptions!$B$8+Assumptions!$B$58),Assumptions!$B$57,0)+IF(AND(7&gt;=Assumptions!$B$8,7&lt;Assumptions!$B$8+Assumptions!$B$61),Assumptions!$B$60,0)+IF(AND(7&gt;=Assumptions!$B$8,7&lt;Assumptions!$B$8+Assumptions!$B$64),Assumptions!$B$63,0)+IF(AND(7&gt;=Assumptions!$B$8,7&lt;Assumptions!$B$8+Assumptions!$B$67),Assumptions!$B$66,0)+IF(AND(7&gt;=Assumptions!$B$8,7&lt;Assumptions!$B$8+Assumptions!$B$70),Assumptions!$B$69,0)+IF(7=Assumptions!$B$8,Assumptions!$B$74,0)</f>
+        <v>8200</v>
       </c>
       <c r="I44" s="21" t="n">
-        <f aca="false">IF(8&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(8&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(8&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(8&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(8&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
-        <v>838.637551144702</v>
+        <f aca="false">IF(AND(8&gt;=Assumptions!$B$8,8&lt;Assumptions!$B$8+Assumptions!$B$58),Assumptions!$B$57,0)+IF(AND(8&gt;=Assumptions!$B$8,8&lt;Assumptions!$B$8+Assumptions!$B$61),Assumptions!$B$60,0)+IF(AND(8&gt;=Assumptions!$B$8,8&lt;Assumptions!$B$8+Assumptions!$B$64),Assumptions!$B$63,0)+IF(AND(8&gt;=Assumptions!$B$8,8&lt;Assumptions!$B$8+Assumptions!$B$67),Assumptions!$B$66,0)+IF(AND(8&gt;=Assumptions!$B$8,8&lt;Assumptions!$B$8+Assumptions!$B$70),Assumptions!$B$69,0)+IF(8=Assumptions!$B$8,Assumptions!$B$74,0)</f>
+        <v>3700</v>
       </c>
       <c r="J44" s="21" t="n">
-        <f aca="false">IF(9&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(9&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(9&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(9&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(9&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
-        <v>838.637551144702</v>
+        <f aca="false">IF(AND(9&gt;=Assumptions!$B$8,9&lt;Assumptions!$B$8+Assumptions!$B$58),Assumptions!$B$57,0)+IF(AND(9&gt;=Assumptions!$B$8,9&lt;Assumptions!$B$8+Assumptions!$B$61),Assumptions!$B$60,0)+IF(AND(9&gt;=Assumptions!$B$8,9&lt;Assumptions!$B$8+Assumptions!$B$64),Assumptions!$B$63,0)+IF(AND(9&gt;=Assumptions!$B$8,9&lt;Assumptions!$B$8+Assumptions!$B$67),Assumptions!$B$66,0)+IF(AND(9&gt;=Assumptions!$B$8,9&lt;Assumptions!$B$8+Assumptions!$B$70),Assumptions!$B$69,0)+IF(9=Assumptions!$B$8,Assumptions!$B$74,0)</f>
+        <v>3700</v>
       </c>
       <c r="K44" s="21" t="n">
-        <f aca="false">IF(10&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(10&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(10&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(10&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(10&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
-        <v>2300.02575908002</v>
+        <f aca="false">IF(AND(10&gt;=Assumptions!$B$8,10&lt;Assumptions!$B$8+Assumptions!$B$58),Assumptions!$B$57,0)+IF(AND(10&gt;=Assumptions!$B$8,10&lt;Assumptions!$B$8+Assumptions!$B$61),Assumptions!$B$60,0)+IF(AND(10&gt;=Assumptions!$B$8,10&lt;Assumptions!$B$8+Assumptions!$B$64),Assumptions!$B$63,0)+IF(AND(10&gt;=Assumptions!$B$8,10&lt;Assumptions!$B$8+Assumptions!$B$67),Assumptions!$B$66,0)+IF(AND(10&gt;=Assumptions!$B$8,10&lt;Assumptions!$B$8+Assumptions!$B$70),Assumptions!$B$69,0)+IF(10=Assumptions!$B$8,Assumptions!$B$74,0)</f>
+        <v>0</v>
       </c>
       <c r="L44" s="21" t="n">
-        <f aca="false">IF(11&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(11&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(11&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(11&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(11&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
-        <v>2300.02575908002</v>
+        <f aca="false">IF(AND(11&gt;=Assumptions!$B$8,11&lt;Assumptions!$B$8+Assumptions!$B$58),Assumptions!$B$57,0)+IF(AND(11&gt;=Assumptions!$B$8,11&lt;Assumptions!$B$8+Assumptions!$B$61),Assumptions!$B$60,0)+IF(AND(11&gt;=Assumptions!$B$8,11&lt;Assumptions!$B$8+Assumptions!$B$64),Assumptions!$B$63,0)+IF(AND(11&gt;=Assumptions!$B$8,11&lt;Assumptions!$B$8+Assumptions!$B$67),Assumptions!$B$66,0)+IF(AND(11&gt;=Assumptions!$B$8,11&lt;Assumptions!$B$8+Assumptions!$B$70),Assumptions!$B$69,0)+IF(11=Assumptions!$B$8,Assumptions!$B$74,0)</f>
+        <v>0</v>
       </c>
       <c r="M44" s="21" t="n">
-        <f aca="false">IF(12&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(12&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(12&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(12&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(12&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
-        <v>2300.02575908002</v>
+        <f aca="false">IF(AND(12&gt;=Assumptions!$B$8,12&lt;Assumptions!$B$8+Assumptions!$B$58),Assumptions!$B$57,0)+IF(AND(12&gt;=Assumptions!$B$8,12&lt;Assumptions!$B$8+Assumptions!$B$61),Assumptions!$B$60,0)+IF(AND(12&gt;=Assumptions!$B$8,12&lt;Assumptions!$B$8+Assumptions!$B$64),Assumptions!$B$63,0)+IF(AND(12&gt;=Assumptions!$B$8,12&lt;Assumptions!$B$8+Assumptions!$B$67),Assumptions!$B$66,0)+IF(AND(12&gt;=Assumptions!$B$8,12&lt;Assumptions!$B$8+Assumptions!$B$70),Assumptions!$B$69,0)+IF(12=Assumptions!$B$8,Assumptions!$B$74,0)</f>
+        <v>0</v>
       </c>
       <c r="N44" s="21" t="n">
-        <f aca="false">IF(13&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(13&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(13&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(13&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(13&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
-        <v>2300.02575908002</v>
+        <f aca="false">IF(AND(13&gt;=Assumptions!$B$8,13&lt;Assumptions!$B$8+Assumptions!$B$58),Assumptions!$B$57,0)+IF(AND(13&gt;=Assumptions!$B$8,13&lt;Assumptions!$B$8+Assumptions!$B$61),Assumptions!$B$60,0)+IF(AND(13&gt;=Assumptions!$B$8,13&lt;Assumptions!$B$8+Assumptions!$B$64),Assumptions!$B$63,0)+IF(AND(13&gt;=Assumptions!$B$8,13&lt;Assumptions!$B$8+Assumptions!$B$67),Assumptions!$B$66,0)+IF(AND(13&gt;=Assumptions!$B$8,13&lt;Assumptions!$B$8+Assumptions!$B$70),Assumptions!$B$69,0)+IF(13=Assumptions!$B$8,Assumptions!$B$74,0)</f>
+        <v>0</v>
       </c>
       <c r="O44" s="21" t="n">
-        <f aca="false">IF(14&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(14&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(14&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(14&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(14&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
-        <v>2300.02575908002</v>
+        <f aca="false">IF(AND(14&gt;=Assumptions!$B$8,14&lt;Assumptions!$B$8+Assumptions!$B$58),Assumptions!$B$57,0)+IF(AND(14&gt;=Assumptions!$B$8,14&lt;Assumptions!$B$8+Assumptions!$B$61),Assumptions!$B$60,0)+IF(AND(14&gt;=Assumptions!$B$8,14&lt;Assumptions!$B$8+Assumptions!$B$64),Assumptions!$B$63,0)+IF(AND(14&gt;=Assumptions!$B$8,14&lt;Assumptions!$B$8+Assumptions!$B$67),Assumptions!$B$66,0)+IF(AND(14&gt;=Assumptions!$B$8,14&lt;Assumptions!$B$8+Assumptions!$B$70),Assumptions!$B$69,0)+IF(14=Assumptions!$B$8,Assumptions!$B$74,0)</f>
+        <v>0</v>
       </c>
       <c r="P44" s="21" t="n">
-        <f aca="false">IF(15&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(15&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(15&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(15&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(15&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
-        <v>2300.02575908002</v>
+        <f aca="false">IF(AND(15&gt;=Assumptions!$B$8,15&lt;Assumptions!$B$8+Assumptions!$B$58),Assumptions!$B$57,0)+IF(AND(15&gt;=Assumptions!$B$8,15&lt;Assumptions!$B$8+Assumptions!$B$61),Assumptions!$B$60,0)+IF(AND(15&gt;=Assumptions!$B$8,15&lt;Assumptions!$B$8+Assumptions!$B$64),Assumptions!$B$63,0)+IF(AND(15&gt;=Assumptions!$B$8,15&lt;Assumptions!$B$8+Assumptions!$B$67),Assumptions!$B$66,0)+IF(AND(15&gt;=Assumptions!$B$8,15&lt;Assumptions!$B$8+Assumptions!$B$70),Assumptions!$B$69,0)+IF(15=Assumptions!$B$8,Assumptions!$B$74,0)</f>
+        <v>0</v>
       </c>
       <c r="Q44" s="21" t="n">
-        <f aca="false">IF(16&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(16&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(16&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(16&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(16&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
-        <v>2300.02575908002</v>
+        <f aca="false">IF(AND(16&gt;=Assumptions!$B$8,16&lt;Assumptions!$B$8+Assumptions!$B$58),Assumptions!$B$57,0)+IF(AND(16&gt;=Assumptions!$B$8,16&lt;Assumptions!$B$8+Assumptions!$B$61),Assumptions!$B$60,0)+IF(AND(16&gt;=Assumptions!$B$8,16&lt;Assumptions!$B$8+Assumptions!$B$64),Assumptions!$B$63,0)+IF(AND(16&gt;=Assumptions!$B$8,16&lt;Assumptions!$B$8+Assumptions!$B$67),Assumptions!$B$66,0)+IF(AND(16&gt;=Assumptions!$B$8,16&lt;Assumptions!$B$8+Assumptions!$B$70),Assumptions!$B$69,0)+IF(16=Assumptions!$B$8,Assumptions!$B$74,0)</f>
+        <v>0</v>
       </c>
       <c r="R44" s="21" t="n">
-        <f aca="false">IF(17&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(17&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(17&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(17&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(17&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
-        <v>2300.02575908002</v>
+        <f aca="false">IF(AND(17&gt;=Assumptions!$B$8,17&lt;Assumptions!$B$8+Assumptions!$B$58),Assumptions!$B$57,0)+IF(AND(17&gt;=Assumptions!$B$8,17&lt;Assumptions!$B$8+Assumptions!$B$61),Assumptions!$B$60,0)+IF(AND(17&gt;=Assumptions!$B$8,17&lt;Assumptions!$B$8+Assumptions!$B$64),Assumptions!$B$63,0)+IF(AND(17&gt;=Assumptions!$B$8,17&lt;Assumptions!$B$8+Assumptions!$B$67),Assumptions!$B$66,0)+IF(AND(17&gt;=Assumptions!$B$8,17&lt;Assumptions!$B$8+Assumptions!$B$70),Assumptions!$B$69,0)+IF(17=Assumptions!$B$8,Assumptions!$B$74,0)</f>
+        <v>0</v>
       </c>
       <c r="S44" s="21" t="n">
-        <f aca="false">IF(18&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(18&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(18&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(18&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(18&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
-        <v>2300.02575908002</v>
+        <f aca="false">IF(AND(18&gt;=Assumptions!$B$8,18&lt;Assumptions!$B$8+Assumptions!$B$58),Assumptions!$B$57,0)+IF(AND(18&gt;=Assumptions!$B$8,18&lt;Assumptions!$B$8+Assumptions!$B$61),Assumptions!$B$60,0)+IF(AND(18&gt;=Assumptions!$B$8,18&lt;Assumptions!$B$8+Assumptions!$B$64),Assumptions!$B$63,0)+IF(AND(18&gt;=Assumptions!$B$8,18&lt;Assumptions!$B$8+Assumptions!$B$67),Assumptions!$B$66,0)+IF(AND(18&gt;=Assumptions!$B$8,18&lt;Assumptions!$B$8+Assumptions!$B$70),Assumptions!$B$69,0)+IF(18=Assumptions!$B$8,Assumptions!$B$74,0)</f>
+        <v>0</v>
       </c>
       <c r="T44" s="21" t="n">
-        <f aca="false">IF(19&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(19&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(19&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(19&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(19&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
-        <v>2300.02575908002</v>
+        <f aca="false">IF(AND(19&gt;=Assumptions!$B$8,19&lt;Assumptions!$B$8+Assumptions!$B$58),Assumptions!$B$57,0)+IF(AND(19&gt;=Assumptions!$B$8,19&lt;Assumptions!$B$8+Assumptions!$B$61),Assumptions!$B$60,0)+IF(AND(19&gt;=Assumptions!$B$8,19&lt;Assumptions!$B$8+Assumptions!$B$64),Assumptions!$B$63,0)+IF(AND(19&gt;=Assumptions!$B$8,19&lt;Assumptions!$B$8+Assumptions!$B$67),Assumptions!$B$66,0)+IF(AND(19&gt;=Assumptions!$B$8,19&lt;Assumptions!$B$8+Assumptions!$B$70),Assumptions!$B$69,0)+IF(19=Assumptions!$B$8,Assumptions!$B$74,0)</f>
+        <v>0</v>
       </c>
       <c r="U44" s="21" t="n">
-        <f aca="false">IF(20&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(20&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(20&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(20&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(20&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
-        <v>2300.02575908002</v>
+        <f aca="false">IF(AND(20&gt;=Assumptions!$B$8,20&lt;Assumptions!$B$8+Assumptions!$B$58),Assumptions!$B$57,0)+IF(AND(20&gt;=Assumptions!$B$8,20&lt;Assumptions!$B$8+Assumptions!$B$61),Assumptions!$B$60,0)+IF(AND(20&gt;=Assumptions!$B$8,20&lt;Assumptions!$B$8+Assumptions!$B$64),Assumptions!$B$63,0)+IF(AND(20&gt;=Assumptions!$B$8,20&lt;Assumptions!$B$8+Assumptions!$B$67),Assumptions!$B$66,0)+IF(AND(20&gt;=Assumptions!$B$8,20&lt;Assumptions!$B$8+Assumptions!$B$70),Assumptions!$B$69,0)+IF(20=Assumptions!$B$8,Assumptions!$B$74,0)</f>
+        <v>0</v>
       </c>
       <c r="V44" s="21" t="n">
-        <f aca="false">IF(21&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(21&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(21&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(21&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(21&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
-        <v>2300.02575908002</v>
+        <f aca="false">IF(AND(21&gt;=Assumptions!$B$8,21&lt;Assumptions!$B$8+Assumptions!$B$58),Assumptions!$B$57,0)+IF(AND(21&gt;=Assumptions!$B$8,21&lt;Assumptions!$B$8+Assumptions!$B$61),Assumptions!$B$60,0)+IF(AND(21&gt;=Assumptions!$B$8,21&lt;Assumptions!$B$8+Assumptions!$B$64),Assumptions!$B$63,0)+IF(AND(21&gt;=Assumptions!$B$8,21&lt;Assumptions!$B$8+Assumptions!$B$67),Assumptions!$B$66,0)+IF(AND(21&gt;=Assumptions!$B$8,21&lt;Assumptions!$B$8+Assumptions!$B$70),Assumptions!$B$69,0)+IF(21=Assumptions!$B$8,Assumptions!$B$74,0)</f>
+        <v>0</v>
       </c>
       <c r="W44" s="21" t="n">
-        <f aca="false">IF(22&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(22&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(22&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(22&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(22&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
-        <v>2300.02575908002</v>
+        <f aca="false">IF(AND(22&gt;=Assumptions!$B$8,22&lt;Assumptions!$B$8+Assumptions!$B$58),Assumptions!$B$57,0)+IF(AND(22&gt;=Assumptions!$B$8,22&lt;Assumptions!$B$8+Assumptions!$B$61),Assumptions!$B$60,0)+IF(AND(22&gt;=Assumptions!$B$8,22&lt;Assumptions!$B$8+Assumptions!$B$64),Assumptions!$B$63,0)+IF(AND(22&gt;=Assumptions!$B$8,22&lt;Assumptions!$B$8+Assumptions!$B$67),Assumptions!$B$66,0)+IF(AND(22&gt;=Assumptions!$B$8,22&lt;Assumptions!$B$8+Assumptions!$B$70),Assumptions!$B$69,0)+IF(22=Assumptions!$B$8,Assumptions!$B$74,0)</f>
+        <v>0</v>
       </c>
       <c r="X44" s="21" t="n">
-        <f aca="false">IF(23&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(23&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(23&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(23&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(23&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
-        <v>2300.02575908002</v>
+        <f aca="false">IF(AND(23&gt;=Assumptions!$B$8,23&lt;Assumptions!$B$8+Assumptions!$B$58),Assumptions!$B$57,0)+IF(AND(23&gt;=Assumptions!$B$8,23&lt;Assumptions!$B$8+Assumptions!$B$61),Assumptions!$B$60,0)+IF(AND(23&gt;=Assumptions!$B$8,23&lt;Assumptions!$B$8+Assumptions!$B$64),Assumptions!$B$63,0)+IF(AND(23&gt;=Assumptions!$B$8,23&lt;Assumptions!$B$8+Assumptions!$B$67),Assumptions!$B$66,0)+IF(AND(23&gt;=Assumptions!$B$8,23&lt;Assumptions!$B$8+Assumptions!$B$70),Assumptions!$B$69,0)+IF(23=Assumptions!$B$8,Assumptions!$B$74,0)</f>
+        <v>0</v>
       </c>
       <c r="Y44" s="21" t="n">
-        <f aca="false">IF(24&gt;=Assumptions!$B$8+Assumptions!$B$56,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$54*Assumptions!$B$69),0)+IF(24&gt;=Assumptions!$B$8+Assumptions!$B$59,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$57*Assumptions!$B$69),0)+IF(24&gt;=Assumptions!$B$8+Assumptions!$B$62,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$60*Assumptions!$B$69),0)+IF(24&gt;=Assumptions!$B$8+Assumptions!$B$65,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$63*Assumptions!$B$69),0)+IF(24&gt;=Assumptions!$B$8+Assumptions!$B$68,-PMT(Assumptions!$B$70/12,Assumptions!$B$71,Assumptions!$B$66*Assumptions!$B$69),0)</f>
-        <v>2300.02575908002</v>
+        <f aca="false">IF(AND(24&gt;=Assumptions!$B$8,24&lt;Assumptions!$B$8+Assumptions!$B$58),Assumptions!$B$57,0)+IF(AND(24&gt;=Assumptions!$B$8,24&lt;Assumptions!$B$8+Assumptions!$B$61),Assumptions!$B$60,0)+IF(AND(24&gt;=Assumptions!$B$8,24&lt;Assumptions!$B$8+Assumptions!$B$64),Assumptions!$B$63,0)+IF(AND(24&gt;=Assumptions!$B$8,24&lt;Assumptions!$B$8+Assumptions!$B$67),Assumptions!$B$66,0)+IF(AND(24&gt;=Assumptions!$B$8,24&lt;Assumptions!$B$8+Assumptions!$B$70),Assumptions!$B$69,0)+IF(24=Assumptions!$B$8,Assumptions!$B$74,0)</f>
+        <v>0</v>
       </c>
       <c r="Z44" s="21" t="n">
         <f aca="false">SUM(B44:M44)</f>
-        <v>9415.98993067418</v>
+        <v>15600</v>
       </c>
       <c r="AA44" s="21" t="n">
         <f aca="false">SUM(N44:Y44)</f>
-        <v>27600.3091089603</v>
+        <v>0</v>
       </c>
       <c r="AB44" s="21" t="n">
         <f aca="false">SUM(B44:Y44)</f>
+        <v>15600</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="B45" s="21" t="n">
+        <f aca="false">IF(1&gt;=Assumptions!$B$8+Assumptions!$B$58,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$56*Assumptions!$B$71),0)+IF(1&gt;=Assumptions!$B$8+Assumptions!$B$61,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$59*Assumptions!$B$71),0)+IF(1&gt;=Assumptions!$B$8+Assumptions!$B$64,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$62*Assumptions!$B$71),0)+IF(1&gt;=Assumptions!$B$8+Assumptions!$B$67,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$65*Assumptions!$B$71),0)+IF(1&gt;=Assumptions!$B$8+Assumptions!$B$70,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$68*Assumptions!$B$71),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C45" s="21" t="n">
+        <f aca="false">IF(2&gt;=Assumptions!$B$8+Assumptions!$B$58,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$56*Assumptions!$B$71),0)+IF(2&gt;=Assumptions!$B$8+Assumptions!$B$61,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$59*Assumptions!$B$71),0)+IF(2&gt;=Assumptions!$B$8+Assumptions!$B$64,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$62*Assumptions!$B$71),0)+IF(2&gt;=Assumptions!$B$8+Assumptions!$B$67,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$65*Assumptions!$B$71),0)+IF(2&gt;=Assumptions!$B$8+Assumptions!$B$70,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$68*Assumptions!$B$71),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D45" s="21" t="n">
+        <f aca="false">IF(3&gt;=Assumptions!$B$8+Assumptions!$B$58,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$56*Assumptions!$B$71),0)+IF(3&gt;=Assumptions!$B$8+Assumptions!$B$61,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$59*Assumptions!$B$71),0)+IF(3&gt;=Assumptions!$B$8+Assumptions!$B$64,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$62*Assumptions!$B$71),0)+IF(3&gt;=Assumptions!$B$8+Assumptions!$B$67,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$65*Assumptions!$B$71),0)+IF(3&gt;=Assumptions!$B$8+Assumptions!$B$70,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$68*Assumptions!$B$71),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="21" t="n">
+        <f aca="false">IF(4&gt;=Assumptions!$B$8+Assumptions!$B$58,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$56*Assumptions!$B$71),0)+IF(4&gt;=Assumptions!$B$8+Assumptions!$B$61,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$59*Assumptions!$B$71),0)+IF(4&gt;=Assumptions!$B$8+Assumptions!$B$64,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$62*Assumptions!$B$71),0)+IF(4&gt;=Assumptions!$B$8+Assumptions!$B$67,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$65*Assumptions!$B$71),0)+IF(4&gt;=Assumptions!$B$8+Assumptions!$B$70,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$68*Assumptions!$B$71),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F45" s="21" t="n">
+        <f aca="false">IF(5&gt;=Assumptions!$B$8+Assumptions!$B$58,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$56*Assumptions!$B$71),0)+IF(5&gt;=Assumptions!$B$8+Assumptions!$B$61,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$59*Assumptions!$B$71),0)+IF(5&gt;=Assumptions!$B$8+Assumptions!$B$64,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$62*Assumptions!$B$71),0)+IF(5&gt;=Assumptions!$B$8+Assumptions!$B$67,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$65*Assumptions!$B$71),0)+IF(5&gt;=Assumptions!$B$8+Assumptions!$B$70,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$68*Assumptions!$B$71),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G45" s="21" t="n">
+        <f aca="false">IF(6&gt;=Assumptions!$B$8+Assumptions!$B$58,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$56*Assumptions!$B$71),0)+IF(6&gt;=Assumptions!$B$8+Assumptions!$B$61,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$59*Assumptions!$B$71),0)+IF(6&gt;=Assumptions!$B$8+Assumptions!$B$64,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$62*Assumptions!$B$71),0)+IF(6&gt;=Assumptions!$B$8+Assumptions!$B$67,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$65*Assumptions!$B$71),0)+IF(6&gt;=Assumptions!$B$8+Assumptions!$B$70,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$68*Assumptions!$B$71),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H45" s="21" t="n">
+        <f aca="false">IF(7&gt;=Assumptions!$B$8+Assumptions!$B$58,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$56*Assumptions!$B$71),0)+IF(7&gt;=Assumptions!$B$8+Assumptions!$B$61,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$59*Assumptions!$B$71),0)+IF(7&gt;=Assumptions!$B$8+Assumptions!$B$64,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$62*Assumptions!$B$71),0)+IF(7&gt;=Assumptions!$B$8+Assumptions!$B$67,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$65*Assumptions!$B$71),0)+IF(7&gt;=Assumptions!$B$8+Assumptions!$B$70,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$68*Assumptions!$B$71),0)</f>
+        <v>838.637551144702</v>
+      </c>
+      <c r="I45" s="21" t="n">
+        <f aca="false">IF(8&gt;=Assumptions!$B$8+Assumptions!$B$58,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$56*Assumptions!$B$71),0)+IF(8&gt;=Assumptions!$B$8+Assumptions!$B$61,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$59*Assumptions!$B$71),0)+IF(8&gt;=Assumptions!$B$8+Assumptions!$B$64,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$62*Assumptions!$B$71),0)+IF(8&gt;=Assumptions!$B$8+Assumptions!$B$67,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$65*Assumptions!$B$71),0)+IF(8&gt;=Assumptions!$B$8+Assumptions!$B$70,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$68*Assumptions!$B$71),0)</f>
+        <v>838.637551144702</v>
+      </c>
+      <c r="J45" s="21" t="n">
+        <f aca="false">IF(9&gt;=Assumptions!$B$8+Assumptions!$B$58,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$56*Assumptions!$B$71),0)+IF(9&gt;=Assumptions!$B$8+Assumptions!$B$61,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$59*Assumptions!$B$71),0)+IF(9&gt;=Assumptions!$B$8+Assumptions!$B$64,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$62*Assumptions!$B$71),0)+IF(9&gt;=Assumptions!$B$8+Assumptions!$B$67,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$65*Assumptions!$B$71),0)+IF(9&gt;=Assumptions!$B$8+Assumptions!$B$70,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$68*Assumptions!$B$71),0)</f>
+        <v>838.637551144702</v>
+      </c>
+      <c r="K45" s="21" t="n">
+        <f aca="false">IF(10&gt;=Assumptions!$B$8+Assumptions!$B$58,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$56*Assumptions!$B$71),0)+IF(10&gt;=Assumptions!$B$8+Assumptions!$B$61,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$59*Assumptions!$B$71),0)+IF(10&gt;=Assumptions!$B$8+Assumptions!$B$64,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$62*Assumptions!$B$71),0)+IF(10&gt;=Assumptions!$B$8+Assumptions!$B$67,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$65*Assumptions!$B$71),0)+IF(10&gt;=Assumptions!$B$8+Assumptions!$B$70,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$68*Assumptions!$B$71),0)</f>
+        <v>2300.02575908002</v>
+      </c>
+      <c r="L45" s="21" t="n">
+        <f aca="false">IF(11&gt;=Assumptions!$B$8+Assumptions!$B$58,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$56*Assumptions!$B$71),0)+IF(11&gt;=Assumptions!$B$8+Assumptions!$B$61,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$59*Assumptions!$B$71),0)+IF(11&gt;=Assumptions!$B$8+Assumptions!$B$64,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$62*Assumptions!$B$71),0)+IF(11&gt;=Assumptions!$B$8+Assumptions!$B$67,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$65*Assumptions!$B$71),0)+IF(11&gt;=Assumptions!$B$8+Assumptions!$B$70,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$68*Assumptions!$B$71),0)</f>
+        <v>2300.02575908002</v>
+      </c>
+      <c r="M45" s="21" t="n">
+        <f aca="false">IF(12&gt;=Assumptions!$B$8+Assumptions!$B$58,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$56*Assumptions!$B$71),0)+IF(12&gt;=Assumptions!$B$8+Assumptions!$B$61,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$59*Assumptions!$B$71),0)+IF(12&gt;=Assumptions!$B$8+Assumptions!$B$64,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$62*Assumptions!$B$71),0)+IF(12&gt;=Assumptions!$B$8+Assumptions!$B$67,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$65*Assumptions!$B$71),0)+IF(12&gt;=Assumptions!$B$8+Assumptions!$B$70,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$68*Assumptions!$B$71),0)</f>
+        <v>2300.02575908002</v>
+      </c>
+      <c r="N45" s="21" t="n">
+        <f aca="false">IF(13&gt;=Assumptions!$B$8+Assumptions!$B$58,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$56*Assumptions!$B$71),0)+IF(13&gt;=Assumptions!$B$8+Assumptions!$B$61,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$59*Assumptions!$B$71),0)+IF(13&gt;=Assumptions!$B$8+Assumptions!$B$64,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$62*Assumptions!$B$71),0)+IF(13&gt;=Assumptions!$B$8+Assumptions!$B$67,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$65*Assumptions!$B$71),0)+IF(13&gt;=Assumptions!$B$8+Assumptions!$B$70,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$68*Assumptions!$B$71),0)</f>
+        <v>2300.02575908002</v>
+      </c>
+      <c r="O45" s="21" t="n">
+        <f aca="false">IF(14&gt;=Assumptions!$B$8+Assumptions!$B$58,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$56*Assumptions!$B$71),0)+IF(14&gt;=Assumptions!$B$8+Assumptions!$B$61,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$59*Assumptions!$B$71),0)+IF(14&gt;=Assumptions!$B$8+Assumptions!$B$64,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$62*Assumptions!$B$71),0)+IF(14&gt;=Assumptions!$B$8+Assumptions!$B$67,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$65*Assumptions!$B$71),0)+IF(14&gt;=Assumptions!$B$8+Assumptions!$B$70,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$68*Assumptions!$B$71),0)</f>
+        <v>2300.02575908002</v>
+      </c>
+      <c r="P45" s="21" t="n">
+        <f aca="false">IF(15&gt;=Assumptions!$B$8+Assumptions!$B$58,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$56*Assumptions!$B$71),0)+IF(15&gt;=Assumptions!$B$8+Assumptions!$B$61,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$59*Assumptions!$B$71),0)+IF(15&gt;=Assumptions!$B$8+Assumptions!$B$64,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$62*Assumptions!$B$71),0)+IF(15&gt;=Assumptions!$B$8+Assumptions!$B$67,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$65*Assumptions!$B$71),0)+IF(15&gt;=Assumptions!$B$8+Assumptions!$B$70,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$68*Assumptions!$B$71),0)</f>
+        <v>2300.02575908002</v>
+      </c>
+      <c r="Q45" s="21" t="n">
+        <f aca="false">IF(16&gt;=Assumptions!$B$8+Assumptions!$B$58,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$56*Assumptions!$B$71),0)+IF(16&gt;=Assumptions!$B$8+Assumptions!$B$61,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$59*Assumptions!$B$71),0)+IF(16&gt;=Assumptions!$B$8+Assumptions!$B$64,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$62*Assumptions!$B$71),0)+IF(16&gt;=Assumptions!$B$8+Assumptions!$B$67,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$65*Assumptions!$B$71),0)+IF(16&gt;=Assumptions!$B$8+Assumptions!$B$70,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$68*Assumptions!$B$71),0)</f>
+        <v>2300.02575908002</v>
+      </c>
+      <c r="R45" s="21" t="n">
+        <f aca="false">IF(17&gt;=Assumptions!$B$8+Assumptions!$B$58,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$56*Assumptions!$B$71),0)+IF(17&gt;=Assumptions!$B$8+Assumptions!$B$61,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$59*Assumptions!$B$71),0)+IF(17&gt;=Assumptions!$B$8+Assumptions!$B$64,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$62*Assumptions!$B$71),0)+IF(17&gt;=Assumptions!$B$8+Assumptions!$B$67,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$65*Assumptions!$B$71),0)+IF(17&gt;=Assumptions!$B$8+Assumptions!$B$70,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$68*Assumptions!$B$71),0)</f>
+        <v>2300.02575908002</v>
+      </c>
+      <c r="S45" s="21" t="n">
+        <f aca="false">IF(18&gt;=Assumptions!$B$8+Assumptions!$B$58,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$56*Assumptions!$B$71),0)+IF(18&gt;=Assumptions!$B$8+Assumptions!$B$61,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$59*Assumptions!$B$71),0)+IF(18&gt;=Assumptions!$B$8+Assumptions!$B$64,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$62*Assumptions!$B$71),0)+IF(18&gt;=Assumptions!$B$8+Assumptions!$B$67,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$65*Assumptions!$B$71),0)+IF(18&gt;=Assumptions!$B$8+Assumptions!$B$70,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$68*Assumptions!$B$71),0)</f>
+        <v>2300.02575908002</v>
+      </c>
+      <c r="T45" s="21" t="n">
+        <f aca="false">IF(19&gt;=Assumptions!$B$8+Assumptions!$B$58,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$56*Assumptions!$B$71),0)+IF(19&gt;=Assumptions!$B$8+Assumptions!$B$61,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$59*Assumptions!$B$71),0)+IF(19&gt;=Assumptions!$B$8+Assumptions!$B$64,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$62*Assumptions!$B$71),0)+IF(19&gt;=Assumptions!$B$8+Assumptions!$B$67,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$65*Assumptions!$B$71),0)+IF(19&gt;=Assumptions!$B$8+Assumptions!$B$70,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$68*Assumptions!$B$71),0)</f>
+        <v>2300.02575908002</v>
+      </c>
+      <c r="U45" s="21" t="n">
+        <f aca="false">IF(20&gt;=Assumptions!$B$8+Assumptions!$B$58,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$56*Assumptions!$B$71),0)+IF(20&gt;=Assumptions!$B$8+Assumptions!$B$61,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$59*Assumptions!$B$71),0)+IF(20&gt;=Assumptions!$B$8+Assumptions!$B$64,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$62*Assumptions!$B$71),0)+IF(20&gt;=Assumptions!$B$8+Assumptions!$B$67,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$65*Assumptions!$B$71),0)+IF(20&gt;=Assumptions!$B$8+Assumptions!$B$70,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$68*Assumptions!$B$71),0)</f>
+        <v>2300.02575908002</v>
+      </c>
+      <c r="V45" s="21" t="n">
+        <f aca="false">IF(21&gt;=Assumptions!$B$8+Assumptions!$B$58,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$56*Assumptions!$B$71),0)+IF(21&gt;=Assumptions!$B$8+Assumptions!$B$61,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$59*Assumptions!$B$71),0)+IF(21&gt;=Assumptions!$B$8+Assumptions!$B$64,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$62*Assumptions!$B$71),0)+IF(21&gt;=Assumptions!$B$8+Assumptions!$B$67,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$65*Assumptions!$B$71),0)+IF(21&gt;=Assumptions!$B$8+Assumptions!$B$70,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$68*Assumptions!$B$71),0)</f>
+        <v>2300.02575908002</v>
+      </c>
+      <c r="W45" s="21" t="n">
+        <f aca="false">IF(22&gt;=Assumptions!$B$8+Assumptions!$B$58,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$56*Assumptions!$B$71),0)+IF(22&gt;=Assumptions!$B$8+Assumptions!$B$61,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$59*Assumptions!$B$71),0)+IF(22&gt;=Assumptions!$B$8+Assumptions!$B$64,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$62*Assumptions!$B$71),0)+IF(22&gt;=Assumptions!$B$8+Assumptions!$B$67,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$65*Assumptions!$B$71),0)+IF(22&gt;=Assumptions!$B$8+Assumptions!$B$70,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$68*Assumptions!$B$71),0)</f>
+        <v>2300.02575908002</v>
+      </c>
+      <c r="X45" s="21" t="n">
+        <f aca="false">IF(23&gt;=Assumptions!$B$8+Assumptions!$B$58,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$56*Assumptions!$B$71),0)+IF(23&gt;=Assumptions!$B$8+Assumptions!$B$61,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$59*Assumptions!$B$71),0)+IF(23&gt;=Assumptions!$B$8+Assumptions!$B$64,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$62*Assumptions!$B$71),0)+IF(23&gt;=Assumptions!$B$8+Assumptions!$B$67,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$65*Assumptions!$B$71),0)+IF(23&gt;=Assumptions!$B$8+Assumptions!$B$70,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$68*Assumptions!$B$71),0)</f>
+        <v>2300.02575908002</v>
+      </c>
+      <c r="Y45" s="21" t="n">
+        <f aca="false">IF(24&gt;=Assumptions!$B$8+Assumptions!$B$58,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$56*Assumptions!$B$71),0)+IF(24&gt;=Assumptions!$B$8+Assumptions!$B$61,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$59*Assumptions!$B$71),0)+IF(24&gt;=Assumptions!$B$8+Assumptions!$B$64,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$62*Assumptions!$B$71),0)+IF(24&gt;=Assumptions!$B$8+Assumptions!$B$67,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$65*Assumptions!$B$71),0)+IF(24&gt;=Assumptions!$B$8+Assumptions!$B$70,-PMT(Assumptions!$B$72/12,Assumptions!$B$73,Assumptions!$B$68*Assumptions!$B$71),0)</f>
+        <v>2300.02575908002</v>
+      </c>
+      <c r="Z45" s="21" t="n">
+        <f aca="false">SUM(B45:M45)</f>
+        <v>9415.98993067418</v>
+      </c>
+      <c r="AA45" s="21" t="n">
+        <f aca="false">SUM(N45:Y45)</f>
+        <v>27600.3091089603</v>
+      </c>
+      <c r="AB45" s="21" t="n">
+        <f aca="false">SUM(B45:Y45)</f>
         <v>37016.2990396345</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="B45" s="22" t="n">
-        <f aca="false">SUM(B33:B44)</f>
-        <v>11100</v>
-      </c>
-      <c r="C45" s="22" t="n">
-        <f aca="false">SUM(C33:C44)</f>
-        <v>11700</v>
-      </c>
-      <c r="D45" s="22" t="n">
-        <f aca="false">SUM(D33:D44)</f>
-        <v>11700</v>
-      </c>
-      <c r="E45" s="22" t="n">
-        <f aca="false">SUM(E33:E44)</f>
-        <v>11700</v>
-      </c>
-      <c r="F45" s="22" t="n">
-        <f aca="false">SUM(F33:F44)</f>
-        <v>11700</v>
-      </c>
-      <c r="G45" s="22" t="n">
-        <f aca="false">SUM(G33:G44)</f>
-        <v>11700</v>
-      </c>
-      <c r="H45" s="22" t="n">
-        <f aca="false">SUM(H33:H44)</f>
-        <v>21638.6375511447</v>
-      </c>
-      <c r="I45" s="22" t="n">
-        <f aca="false">SUM(I33:I44)</f>
-        <v>17138.6375511447</v>
-      </c>
-      <c r="J45" s="22" t="n">
-        <f aca="false">SUM(J33:J44)</f>
-        <v>17138.6375511447</v>
-      </c>
-      <c r="K45" s="22" t="n">
-        <f aca="false">SUM(K33:K44)</f>
-        <v>14900.02575908</v>
-      </c>
-      <c r="L45" s="22" t="n">
-        <f aca="false">SUM(L33:L44)</f>
-        <v>14900.02575908</v>
-      </c>
-      <c r="M45" s="22" t="n">
-        <f aca="false">SUM(M33:M44)</f>
-        <v>14900.02575908</v>
-      </c>
-      <c r="N45" s="22" t="n">
-        <f aca="false">SUM(N33:N44)</f>
-        <v>14900.02575908</v>
-      </c>
-      <c r="O45" s="22" t="n">
-        <f aca="false">SUM(O33:O44)</f>
-        <v>14900.02575908</v>
-      </c>
-      <c r="P45" s="22" t="n">
-        <f aca="false">SUM(P33:P44)</f>
-        <v>14900.02575908</v>
-      </c>
-      <c r="Q45" s="22" t="n">
-        <f aca="false">SUM(Q33:Q44)</f>
-        <v>14900.02575908</v>
-      </c>
-      <c r="R45" s="22" t="n">
-        <f aca="false">SUM(R33:R44)</f>
-        <v>14900.02575908</v>
-      </c>
-      <c r="S45" s="22" t="n">
-        <f aca="false">SUM(S33:S44)</f>
-        <v>14900.02575908</v>
-      </c>
-      <c r="T45" s="22" t="n">
-        <f aca="false">SUM(T33:T44)</f>
-        <v>14900.02575908</v>
-      </c>
-      <c r="U45" s="22" t="n">
-        <f aca="false">SUM(U33:U44)</f>
-        <v>14900.02575908</v>
-      </c>
-      <c r="V45" s="22" t="n">
-        <f aca="false">SUM(V33:V44)</f>
-        <v>14900.02575908</v>
-      </c>
-      <c r="W45" s="22" t="n">
-        <f aca="false">SUM(W33:W44)</f>
-        <v>14900.02575908</v>
-      </c>
-      <c r="X45" s="22" t="n">
-        <f aca="false">SUM(X33:X44)</f>
-        <v>14900.02575908</v>
-      </c>
-      <c r="Y45" s="22" t="n">
-        <f aca="false">SUM(Y33:Y44)</f>
-        <v>14900.02575908</v>
-      </c>
-      <c r="Z45" s="23" t="n">
-        <f aca="false">SUM(B45:M45)</f>
-        <v>170215.989930674</v>
-      </c>
-      <c r="AA45" s="23" t="n">
-        <f aca="false">SUM(N45:Y45)</f>
-        <v>178800.30910896</v>
-      </c>
-      <c r="AB45" s="23" t="n">
-        <f aca="false">SUM(B45:Y45)</f>
-        <v>349016.299039634</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="B46" s="23" t="n">
-        <f aca="false">B30-B45</f>
-        <v>2004</v>
-      </c>
-      <c r="C46" s="23" t="n">
-        <f aca="false">C30-C45</f>
-        <v>2412</v>
-      </c>
-      <c r="D46" s="23" t="n">
-        <f aca="false">D30-D45</f>
-        <v>3492.71875</v>
-      </c>
-      <c r="E46" s="23" t="n">
-        <f aca="false">E30-E45</f>
-        <v>4575.93604166666</v>
-      </c>
-      <c r="F46" s="23" t="n">
-        <f aca="false">F30-F45</f>
-        <v>5661.63521805556</v>
-      </c>
-      <c r="G46" s="23" t="n">
-        <f aca="false">G30-G45</f>
-        <v>6749.79973326852</v>
-      </c>
-      <c r="H46" s="23" t="n">
-        <f aca="false">H30-H45</f>
-        <v>7000.62560056869</v>
-      </c>
-      <c r="I46" s="23" t="n">
-        <f aca="false">I30-I45</f>
-        <v>14305.3148184462</v>
-      </c>
-      <c r="J46" s="23" t="n">
-        <f aca="false">J30-J45</f>
-        <v>17117.18166376</v>
-      </c>
-      <c r="K46" s="23" t="n">
-        <f aca="false">K30-K45</f>
-        <v>22174.7900777253</v>
-      </c>
-      <c r="L46" s="23" t="n">
-        <f aca="false">L30-L45</f>
-        <v>22304.9133888133</v>
-      </c>
-      <c r="M46" s="23" t="n">
-        <f aca="false">M30-M45</f>
-        <v>22434.1692111606</v>
-      </c>
-      <c r="N46" s="23" t="n">
-        <f aca="false">N30-N45</f>
-        <v>22562.5633280257</v>
-      </c>
-      <c r="O46" s="23" t="n">
-        <f aca="false">O30-O45</f>
-        <v>22690.1014841117</v>
-      </c>
-      <c r="P46" s="23" t="n">
-        <f aca="false">P30-P45</f>
-        <v>22788.8206358237</v>
-      </c>
-      <c r="Q46" s="23" t="n">
-        <f aca="false">Q30-Q45</f>
-        <v>22886.8816598577</v>
-      </c>
-      <c r="R46" s="23" t="n">
-        <f aca="false">R30-R45</f>
-        <v>22984.2889437315</v>
-      </c>
-      <c r="S46" s="23" t="n">
-        <f aca="false">S30-S45</f>
-        <v>23081.0468457127</v>
-      </c>
-      <c r="T46" s="23" t="n">
-        <f aca="false">T30-T45</f>
-        <v>23177.1596950141</v>
-      </c>
-      <c r="U46" s="23" t="n">
-        <f aca="false">U30-U45</f>
-        <v>23272.6317919868</v>
-      </c>
-      <c r="V46" s="23" t="n">
-        <f aca="false">V30-V45</f>
-        <v>23367.467408313</v>
-      </c>
-      <c r="W46" s="23" t="n">
-        <f aca="false">W30-W45</f>
-        <v>23461.6707871971</v>
-      </c>
-      <c r="X46" s="23" t="n">
-        <f aca="false">X30-X45</f>
-        <v>23555.2461435552</v>
-      </c>
-      <c r="Y46" s="23" t="n">
-        <f aca="false">Y30-Y45</f>
-        <v>23648.1976642043</v>
+        <v>174</v>
+      </c>
+      <c r="B46" s="22" t="n">
+        <f aca="false">SUM(B34:B45)</f>
+        <v>11100</v>
+      </c>
+      <c r="C46" s="22" t="n">
+        <f aca="false">SUM(C34:C45)</f>
+        <v>11700</v>
+      </c>
+      <c r="D46" s="22" t="n">
+        <f aca="false">SUM(D34:D45)</f>
+        <v>11700</v>
+      </c>
+      <c r="E46" s="22" t="n">
+        <f aca="false">SUM(E34:E45)</f>
+        <v>11700</v>
+      </c>
+      <c r="F46" s="22" t="n">
+        <f aca="false">SUM(F34:F45)</f>
+        <v>11700</v>
+      </c>
+      <c r="G46" s="22" t="n">
+        <f aca="false">SUM(G34:G45)</f>
+        <v>11700</v>
+      </c>
+      <c r="H46" s="22" t="n">
+        <f aca="false">SUM(H34:H45)</f>
+        <v>21638.6375511447</v>
+      </c>
+      <c r="I46" s="22" t="n">
+        <f aca="false">SUM(I34:I45)</f>
+        <v>17138.6375511447</v>
+      </c>
+      <c r="J46" s="22" t="n">
+        <f aca="false">SUM(J34:J45)</f>
+        <v>17138.6375511447</v>
+      </c>
+      <c r="K46" s="22" t="n">
+        <f aca="false">SUM(K34:K45)</f>
+        <v>14900.02575908</v>
+      </c>
+      <c r="L46" s="22" t="n">
+        <f aca="false">SUM(L34:L45)</f>
+        <v>14900.02575908</v>
+      </c>
+      <c r="M46" s="22" t="n">
+        <f aca="false">SUM(M34:M45)</f>
+        <v>14900.02575908</v>
+      </c>
+      <c r="N46" s="22" t="n">
+        <f aca="false">SUM(N34:N45)</f>
+        <v>14900.02575908</v>
+      </c>
+      <c r="O46" s="22" t="n">
+        <f aca="false">SUM(O34:O45)</f>
+        <v>14900.02575908</v>
+      </c>
+      <c r="P46" s="22" t="n">
+        <f aca="false">SUM(P34:P45)</f>
+        <v>14900.02575908</v>
+      </c>
+      <c r="Q46" s="22" t="n">
+        <f aca="false">SUM(Q34:Q45)</f>
+        <v>14900.02575908</v>
+      </c>
+      <c r="R46" s="22" t="n">
+        <f aca="false">SUM(R34:R45)</f>
+        <v>14900.02575908</v>
+      </c>
+      <c r="S46" s="22" t="n">
+        <f aca="false">SUM(S34:S45)</f>
+        <v>14900.02575908</v>
+      </c>
+      <c r="T46" s="22" t="n">
+        <f aca="false">SUM(T34:T45)</f>
+        <v>14900.02575908</v>
+      </c>
+      <c r="U46" s="22" t="n">
+        <f aca="false">SUM(U34:U45)</f>
+        <v>14900.02575908</v>
+      </c>
+      <c r="V46" s="22" t="n">
+        <f aca="false">SUM(V34:V45)</f>
+        <v>14900.02575908</v>
+      </c>
+      <c r="W46" s="22" t="n">
+        <f aca="false">SUM(W34:W45)</f>
+        <v>14900.02575908</v>
+      </c>
+      <c r="X46" s="22" t="n">
+        <f aca="false">SUM(X34:X45)</f>
+        <v>14900.02575908</v>
+      </c>
+      <c r="Y46" s="22" t="n">
+        <f aca="false">SUM(Y34:Y45)</f>
+        <v>14900.02575908</v>
       </c>
       <c r="Z46" s="23" t="n">
         <f aca="false">SUM(B46:M46)</f>
-        <v>130233.084503465</v>
+        <v>170215.989930674</v>
       </c>
       <c r="AA46" s="23" t="n">
         <f aca="false">SUM(N46:Y46)</f>
-        <v>277476.076387534</v>
+        <v>178800.30910896</v>
       </c>
       <c r="AB46" s="23" t="n">
         <f aca="false">SUM(B46:Y46)</f>
+        <v>349016.299039634</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="B47" s="23" t="n">
+        <f aca="false">B31-B46</f>
+        <v>2004</v>
+      </c>
+      <c r="C47" s="23" t="n">
+        <f aca="false">C31-C46</f>
+        <v>2412</v>
+      </c>
+      <c r="D47" s="23" t="n">
+        <f aca="false">D31-D46</f>
+        <v>3492.71875</v>
+      </c>
+      <c r="E47" s="23" t="n">
+        <f aca="false">E31-E46</f>
+        <v>4575.93604166666</v>
+      </c>
+      <c r="F47" s="23" t="n">
+        <f aca="false">F31-F46</f>
+        <v>5661.63521805556</v>
+      </c>
+      <c r="G47" s="23" t="n">
+        <f aca="false">G31-G46</f>
+        <v>6749.79973326852</v>
+      </c>
+      <c r="H47" s="23" t="n">
+        <f aca="false">H31-H46</f>
+        <v>7000.62560056869</v>
+      </c>
+      <c r="I47" s="23" t="n">
+        <f aca="false">I31-I46</f>
+        <v>14305.3148184462</v>
+      </c>
+      <c r="J47" s="23" t="n">
+        <f aca="false">J31-J46</f>
+        <v>17117.18166376</v>
+      </c>
+      <c r="K47" s="23" t="n">
+        <f aca="false">K31-K46</f>
+        <v>22174.7900777253</v>
+      </c>
+      <c r="L47" s="23" t="n">
+        <f aca="false">L31-L46</f>
+        <v>22304.9133888133</v>
+      </c>
+      <c r="M47" s="23" t="n">
+        <f aca="false">M31-M46</f>
+        <v>22434.1692111606</v>
+      </c>
+      <c r="N47" s="23" t="n">
+        <f aca="false">N31-N46</f>
+        <v>22562.5633280257</v>
+      </c>
+      <c r="O47" s="23" t="n">
+        <f aca="false">O31-O46</f>
+        <v>22690.1014841117</v>
+      </c>
+      <c r="P47" s="23" t="n">
+        <f aca="false">P31-P46</f>
+        <v>22788.8206358237</v>
+      </c>
+      <c r="Q47" s="23" t="n">
+        <f aca="false">Q31-Q46</f>
+        <v>22886.8816598577</v>
+      </c>
+      <c r="R47" s="23" t="n">
+        <f aca="false">R31-R46</f>
+        <v>22984.2889437315</v>
+      </c>
+      <c r="S47" s="23" t="n">
+        <f aca="false">S31-S46</f>
+        <v>23081.0468457127</v>
+      </c>
+      <c r="T47" s="23" t="n">
+        <f aca="false">T31-T46</f>
+        <v>23177.1596950141</v>
+      </c>
+      <c r="U47" s="23" t="n">
+        <f aca="false">U31-U46</f>
+        <v>23272.6317919868</v>
+      </c>
+      <c r="V47" s="23" t="n">
+        <f aca="false">V31-V46</f>
+        <v>23367.467408313</v>
+      </c>
+      <c r="W47" s="23" t="n">
+        <f aca="false">W31-W46</f>
+        <v>23461.6707871971</v>
+      </c>
+      <c r="X47" s="23" t="n">
+        <f aca="false">X31-X46</f>
+        <v>23555.2461435552</v>
+      </c>
+      <c r="Y47" s="23" t="n">
+        <f aca="false">Y31-Y46</f>
+        <v>23648.1976642043</v>
+      </c>
+      <c r="Z47" s="23" t="n">
+        <f aca="false">SUM(B47:M47)</f>
+        <v>130233.084503465</v>
+      </c>
+      <c r="AA47" s="23" t="n">
+        <f aca="false">SUM(N47:Y47)</f>
+        <v>277476.076387534</v>
+      </c>
+      <c r="AB47" s="23" t="n">
+        <f aca="false">SUM(B47:Y47)</f>
         <v>407709.160890998</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="B47" s="20" t="n">
-        <f aca="false">IF(B24=0,0,B46/B24)</f>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="B48" s="20" t="n">
+        <f aca="false">IF(B25=0,0,B47/B25)</f>
         <v>0.0734065934065934</v>
       </c>
-      <c r="C47" s="20" t="n">
-        <f aca="false">IF(C24=0,0,C46/C24)</f>
+      <c r="C48" s="20" t="n">
+        <f aca="false">IF(C25=0,0,C47/C25)</f>
         <v>0.0820408163265306</v>
       </c>
-      <c r="D47" s="20" t="n">
-        <f aca="false">IF(D24=0,0,D46/D24)</f>
+      <c r="D48" s="20" t="n">
+        <f aca="false">IF(D25=0,0,D47/D25)</f>
         <v>0.110525030235247</v>
       </c>
-      <c r="E47" s="20" t="n">
-        <f aca="false">IF(E24=0,0,E46/E24)</f>
+      <c r="E48" s="20" t="n">
+        <f aca="false">IF(E25=0,0,E47/E25)</f>
         <v>0.135359543305032</v>
       </c>
-      <c r="F47" s="20" t="n">
-        <f aca="false">IF(F24=0,0,F46/F24)</f>
+      <c r="F48" s="20" t="n">
+        <f aca="false">IF(F25=0,0,F47/F25)</f>
         <v>0.15720706584</v>
       </c>
-      <c r="G47" s="20" t="n">
-        <f aca="false">IF(G24=0,0,G46/G24)</f>
+      <c r="G48" s="20" t="n">
+        <f aca="false">IF(G25=0,0,G47/G25)</f>
         <v>0.17657898063397</v>
       </c>
-      <c r="H47" s="20" t="n">
-        <f aca="false">IF(H24=0,0,H46/H24)</f>
+      <c r="H48" s="20" t="n">
+        <f aca="false">IF(H25=0,0,H47/H25)</f>
         <v>0.117899998177618</v>
       </c>
-      <c r="I47" s="20" t="n">
-        <f aca="false">IF(I24=0,0,I46/I24)</f>
+      <c r="I48" s="20" t="n">
+        <f aca="false">IF(I25=0,0,I47/I25)</f>
         <v>0.219608835647998</v>
       </c>
-      <c r="J47" s="20" t="n">
-        <f aca="false">IF(J24=0,0,J46/J24)</f>
+      <c r="J48" s="20" t="n">
+        <f aca="false">IF(J25=0,0,J47/J25)</f>
         <v>0.241385279079284</v>
       </c>
-      <c r="K47" s="20" t="n">
-        <f aca="false">IF(K24=0,0,K46/K24)</f>
+      <c r="K48" s="20" t="n">
+        <f aca="false">IF(K25=0,0,K47/K25)</f>
         <v>0.289131390429114</v>
       </c>
-      <c r="L47" s="20" t="n">
-        <f aca="false">IF(L24=0,0,L46/L24)</f>
+      <c r="L48" s="20" t="n">
+        <f aca="false">IF(L25=0,0,L47/L25)</f>
         <v>0.2901432571142</v>
       </c>
-      <c r="M47" s="20" t="n">
-        <f aca="false">IF(M24=0,0,M46/M24)</f>
+      <c r="M48" s="20" t="n">
+        <f aca="false">IF(M25=0,0,M47/M25)</f>
         <v>0.291143671532678</v>
       </c>
-      <c r="N47" s="20" t="n">
-        <f aca="false">IF(N24=0,0,N46/N24)</f>
+      <c r="N48" s="20" t="n">
+        <f aca="false">IF(N25=0,0,N47/N25)</f>
         <v>0.29213280501119</v>
       </c>
-      <c r="O47" s="20" t="n">
-        <f aca="false">IF(O24=0,0,O46/O24)</f>
+      <c r="O48" s="20" t="n">
+        <f aca="false">IF(O25=0,0,O47/O25)</f>
         <v>0.293110825533302</v>
       </c>
-      <c r="P47" s="20" t="n">
-        <f aca="false">IF(P24=0,0,P46/P24)</f>
+      <c r="P48" s="20" t="n">
+        <f aca="false">IF(P25=0,0,P47/P25)</f>
         <v>0.29386477639405</v>
       </c>
-      <c r="Q47" s="20" t="n">
-        <f aca="false">IF(Q24=0,0,Q46/Q24)</f>
+      <c r="Q48" s="20" t="n">
+        <f aca="false">IF(Q25=0,0,Q47/Q25)</f>
         <v>0.294611061984109</v>
       </c>
-      <c r="R47" s="20" t="n">
-        <f aca="false">IF(R24=0,0,R46/R24)</f>
+      <c r="R48" s="20" t="n">
+        <f aca="false">IF(R25=0,0,R47/R25)</f>
         <v>0.295349782166614</v>
       </c>
-      <c r="S47" s="20" t="n">
-        <f aca="false">IF(S24=0,0,S46/S24)</f>
+      <c r="S48" s="20" t="n">
+        <f aca="false">IF(S25=0,0,S47/S25)</f>
         <v>0.2960810351253</v>
       </c>
-      <c r="T47" s="20" t="n">
-        <f aca="false">IF(T24=0,0,T46/T24)</f>
+      <c r="T48" s="20" t="n">
+        <f aca="false">IF(T25=0,0,T47/T25)</f>
         <v>0.296804917399697</v>
       </c>
-      <c r="U47" s="20" t="n">
-        <f aca="false">IF(U24=0,0,U46/U24)</f>
+      <c r="U48" s="20" t="n">
+        <f aca="false">IF(U25=0,0,U47/U25)</f>
         <v>0.297521523919436</v>
       </c>
-      <c r="V47" s="20" t="n">
-        <f aca="false">IF(V24=0,0,V46/V24)</f>
+      <c r="V48" s="20" t="n">
+        <f aca="false">IF(V25=0,0,V47/V25)</f>
         <v>0.298230948037712</v>
       </c>
-      <c r="W47" s="20" t="n">
-        <f aca="false">IF(W24=0,0,W46/W24)</f>
+      <c r="W48" s="20" t="n">
+        <f aca="false">IF(W25=0,0,W47/W25)</f>
         <v>0.298933281563894</v>
       </c>
-      <c r="X47" s="20" t="n">
-        <f aca="false">IF(X24=0,0,X46/X24)</f>
+      <c r="X48" s="20" t="n">
+        <f aca="false">IF(X25=0,0,X47/X25)</f>
         <v>0.299628614795349</v>
       </c>
-      <c r="Y47" s="20" t="n">
-        <f aca="false">IF(Y24=0,0,Y46/Y24)</f>
+      <c r="Y48" s="20" t="n">
+        <f aca="false">IF(Y25=0,0,Y47/Y25)</f>
         <v>0.300317036548465</v>
       </c>
-      <c r="Z47" s="2"/>
-      <c r="AA47" s="2"/>
-      <c r="AB47" s="2"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
-      <c r="I48" s="5"/>
-      <c r="J48" s="5"/>
-      <c r="K48" s="5"/>
-      <c r="L48" s="5"/>
-      <c r="M48" s="5"/>
-      <c r="N48" s="5"/>
-      <c r="O48" s="5"/>
-      <c r="P48" s="5"/>
-      <c r="Q48" s="5"/>
-      <c r="R48" s="5"/>
-      <c r="S48" s="5"/>
-      <c r="T48" s="5"/>
-      <c r="U48" s="5"/>
-      <c r="V48" s="5"/>
-      <c r="W48" s="5"/>
-      <c r="X48" s="5"/>
-      <c r="Y48" s="5"/>
-      <c r="Z48" s="5"/>
-      <c r="AA48" s="5"/>
-      <c r="AB48" s="5"/>
+      <c r="Z48" s="2"/>
+      <c r="AA48" s="2"/>
+      <c r="AB48" s="2"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="B49" s="21" t="n">
-        <f aca="false">B20*Assumptions!$B$29+B20*(1-Assumptions!$B$29)*Assumptions!$B$30+0+B23</f>
-        <v>25389</v>
-      </c>
-      <c r="C49" s="21" t="n">
-        <f aca="false">C20*Assumptions!$B$29+C20*(1-Assumptions!$B$29)*Assumptions!$B$30+B20*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+C23</f>
-        <v>29253</v>
-      </c>
-      <c r="D49" s="21" t="n">
-        <f aca="false">D20*Assumptions!$B$29+D20*(1-Assumptions!$B$29)*Assumptions!$B$30+C20*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+D23</f>
-        <v>31454.15625</v>
-      </c>
-      <c r="E49" s="21" t="n">
-        <f aca="false">E20*Assumptions!$B$29+E20*(1-Assumptions!$B$29)*Assumptions!$B$30+D20*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+E23</f>
-        <v>33658.788125</v>
-      </c>
-      <c r="F49" s="21" t="n">
-        <f aca="false">F20*Assumptions!$B$29+F20*(1-Assumptions!$B$29)*Assumptions!$B$30+E20*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+F23</f>
-        <v>35866.8724541667</v>
-      </c>
-      <c r="G49" s="21" t="n">
-        <f aca="false">G20*Assumptions!$B$29+G20*(1-Assumptions!$B$29)*Assumptions!$B$30+F20*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+G23</f>
-        <v>38078.3862211389</v>
-      </c>
-      <c r="H49" s="21" t="n">
-        <f aca="false">H20*Assumptions!$B$29+H20*(1-Assumptions!$B$29)*Assumptions!$B$30+G20*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+H23</f>
-        <v>57907.656562998</v>
-      </c>
-      <c r="I49" s="21" t="n">
-        <f aca="false">I20*Assumptions!$B$29+I20*(1-Assumptions!$B$29)*Assumptions!$B$30+H20*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+I23</f>
-        <v>64747.9784359113</v>
-      </c>
-      <c r="J49" s="21" t="n">
-        <f aca="false">J20*Assumptions!$B$29+J20*(1-Assumptions!$B$29)*Assumptions!$B$30+I20*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+J23</f>
-        <v>70520.2848296719</v>
-      </c>
-      <c r="K49" s="21" t="n">
-        <f aca="false">K20*Assumptions!$B$29+K20*(1-Assumptions!$B$29)*Assumptions!$B$30+J20*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+K23</f>
-        <v>76302.5091808074</v>
-      </c>
-      <c r="L49" s="21" t="n">
-        <f aca="false">L20*Assumptions!$B$29+L20*(1-Assumptions!$B$29)*Assumptions!$B$30+K20*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+L23</f>
-        <v>76875.5187029354</v>
-      </c>
-      <c r="M49" s="21" t="n">
-        <f aca="false">M20*Assumptions!$B$29+M20*(1-Assumptions!$B$29)*Assumptions!$B$30+L20*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+M23</f>
-        <v>77055.3214949158</v>
-      </c>
-      <c r="N49" s="21" t="n">
-        <f aca="false">N20*Assumptions!$B$29+N20*(1-Assumptions!$B$29)*Assumptions!$B$30+M20*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+N23</f>
-        <v>77233.9256016164</v>
-      </c>
-      <c r="O49" s="21" t="n">
-        <f aca="false">O20*Assumptions!$B$29+O20*(1-Assumptions!$B$29)*Assumptions!$B$30+N20*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+O23</f>
-        <v>77411.3390142723</v>
-      </c>
-      <c r="P49" s="21" t="n">
-        <f aca="false">P20*Assumptions!$B$29+P20*(1-Assumptions!$B$29)*Assumptions!$B$30+O20*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+P23</f>
-        <v>77548.6634208438</v>
-      </c>
-      <c r="Q49" s="21" t="n">
-        <f aca="false">Q20*Assumptions!$B$29+Q20*(1-Assumptions!$B$29)*Assumptions!$B$30+P20*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+Q23</f>
-        <v>77685.0723313715</v>
-      </c>
-      <c r="R49" s="21" t="n">
-        <f aca="false">R20*Assumptions!$B$29+R20*(1-Assumptions!$B$29)*Assumptions!$B$30+Q20*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+R23</f>
-        <v>77820.5718491623</v>
-      </c>
-      <c r="S49" s="21" t="n">
-        <f aca="false">S20*Assumptions!$B$29+S20*(1-Assumptions!$B$29)*Assumptions!$B$30+R20*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+S23</f>
-        <v>77955.1680368346</v>
-      </c>
-      <c r="T49" s="21" t="n">
-        <f aca="false">T20*Assumptions!$B$29+T20*(1-Assumptions!$B$29)*Assumptions!$B$30+S20*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+T23</f>
-        <v>78088.866916589</v>
-      </c>
-      <c r="U49" s="21" t="n">
-        <f aca="false">U20*Assumptions!$B$29+U20*(1-Assumptions!$B$29)*Assumptions!$B$30+T20*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+U23</f>
-        <v>78221.6744704784</v>
-      </c>
-      <c r="V49" s="21" t="n">
-        <f aca="false">V20*Assumptions!$B$29+V20*(1-Assumptions!$B$29)*Assumptions!$B$30+U20*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+V23</f>
-        <v>78353.5966406752</v>
-      </c>
-      <c r="W49" s="21" t="n">
-        <f aca="false">W20*Assumptions!$B$29+W20*(1-Assumptions!$B$29)*Assumptions!$B$30+V20*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+W23</f>
-        <v>78484.6393297374</v>
-      </c>
-      <c r="X49" s="21" t="n">
-        <f aca="false">X20*Assumptions!$B$29+X20*(1-Assumptions!$B$29)*Assumptions!$B$30+W20*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+X23</f>
-        <v>78614.8084008725</v>
-      </c>
-      <c r="Y49" s="21" t="n">
-        <f aca="false">Y20*Assumptions!$B$29+Y20*(1-Assumptions!$B$29)*Assumptions!$B$30+X20*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+Y23</f>
-        <v>78744.1096782</v>
-      </c>
-      <c r="Z49" s="21" t="n">
-        <f aca="false">SUM(B49:M49)</f>
-        <v>617109.472257545</v>
-      </c>
-      <c r="AA49" s="21" t="n">
-        <f aca="false">SUM(N49:Y49)</f>
-        <v>936162.435690653</v>
-      </c>
-      <c r="AB49" s="21" t="n">
-        <f aca="false">SUM(B49:Y49)</f>
-        <v>1553271.9079482</v>
-      </c>
+      <c r="A49" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B49" s="5"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="5"/>
+      <c r="J49" s="5"/>
+      <c r="K49" s="5"/>
+      <c r="L49" s="5"/>
+      <c r="M49" s="5"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="5"/>
+      <c r="P49" s="5"/>
+      <c r="Q49" s="5"/>
+      <c r="R49" s="5"/>
+      <c r="S49" s="5"/>
+      <c r="T49" s="5"/>
+      <c r="U49" s="5"/>
+      <c r="V49" s="5"/>
+      <c r="W49" s="5"/>
+      <c r="X49" s="5"/>
+      <c r="Y49" s="5"/>
+      <c r="Z49" s="5"/>
+      <c r="AA49" s="5"/>
+      <c r="AB49" s="5"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="17" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B50" s="21" t="n">
-        <f aca="false">B29+B45</f>
-        <v>25296</v>
+        <f aca="false">B21*Assumptions!$B$29+B21*(1-Assumptions!$B$29)*Assumptions!$B$30+0+B24</f>
+        <v>25389</v>
       </c>
       <c r="C50" s="21" t="n">
-        <f aca="false">C29+C45</f>
-        <v>26988</v>
+        <f aca="false">C21*Assumptions!$B$29+C21*(1-Assumptions!$B$29)*Assumptions!$B$30+B21*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+C24</f>
+        <v>29253</v>
       </c>
       <c r="D50" s="21" t="n">
-        <f aca="false">D29+D45</f>
-        <v>28108.4375</v>
+        <f aca="false">D21*Assumptions!$B$29+D21*(1-Assumptions!$B$29)*Assumptions!$B$30+C21*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+D24</f>
+        <v>31454.15625</v>
       </c>
       <c r="E50" s="21" t="n">
-        <f aca="false">E29+E45</f>
-        <v>29229.8520833333</v>
+        <f aca="false">E21*Assumptions!$B$29+E21*(1-Assumptions!$B$29)*Assumptions!$B$30+D21*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+E24</f>
+        <v>33658.788125</v>
       </c>
       <c r="F50" s="21" t="n">
-        <f aca="false">F29+F45</f>
-        <v>30352.2372361111</v>
+        <f aca="false">F21*Assumptions!$B$29+F21*(1-Assumptions!$B$29)*Assumptions!$B$30+E21*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+F24</f>
+        <v>35866.8724541667</v>
       </c>
       <c r="G50" s="21" t="n">
-        <f aca="false">G29+G45</f>
-        <v>31475.5864878704</v>
+        <f aca="false">G21*Assumptions!$B$29+G21*(1-Assumptions!$B$29)*Assumptions!$B$30+F21*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+G24</f>
+        <v>38078.3862211389</v>
       </c>
       <c r="H50" s="21" t="n">
-        <f aca="false">H29+H45</f>
-        <v>52377.0309624293</v>
+        <f aca="false">H21*Assumptions!$B$29+H21*(1-Assumptions!$B$29)*Assumptions!$B$30+G21*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+H24</f>
+        <v>57907.656562998</v>
       </c>
       <c r="I50" s="21" t="n">
-        <f aca="false">I29+I45</f>
-        <v>50834.6636174652</v>
+        <f aca="false">I21*Assumptions!$B$29+I21*(1-Assumptions!$B$29)*Assumptions!$B$30+H21*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+I24</f>
+        <v>64747.9784359113</v>
       </c>
       <c r="J50" s="21" t="n">
-        <f aca="false">J29+J45</f>
-        <v>53795.1031659119</v>
+        <f aca="false">J21*Assumptions!$B$29+J21*(1-Assumptions!$B$29)*Assumptions!$B$30+I21*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+J24</f>
+        <v>70520.2848296719</v>
       </c>
       <c r="K50" s="21" t="n">
-        <f aca="false">K29+K45</f>
-        <v>54519.7191030821</v>
+        <f aca="false">K21*Assumptions!$B$29+K21*(1-Assumptions!$B$29)*Assumptions!$B$30+J21*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+K24</f>
+        <v>76302.5091808074</v>
       </c>
       <c r="L50" s="21" t="n">
-        <f aca="false">L29+L45</f>
-        <v>54570.6053141221</v>
+        <f aca="false">L21*Assumptions!$B$29+L21*(1-Assumptions!$B$29)*Assumptions!$B$30+K21*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+L24</f>
+        <v>76875.5187029354</v>
       </c>
       <c r="M50" s="21" t="n">
-        <f aca="false">M29+M45</f>
-        <v>54621.1522837552</v>
+        <f aca="false">M21*Assumptions!$B$29+M21*(1-Assumptions!$B$29)*Assumptions!$B$30+L21*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+M24</f>
+        <v>77055.3214949158</v>
       </c>
       <c r="N50" s="21" t="n">
-        <f aca="false">N29+N45</f>
-        <v>54671.3622735907</v>
+        <f aca="false">N21*Assumptions!$B$29+N21*(1-Assumptions!$B$29)*Assumptions!$B$30+M21*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+N24</f>
+        <v>77233.9256016164</v>
       </c>
       <c r="O50" s="21" t="n">
-        <f aca="false">O29+O45</f>
-        <v>54721.2375301606</v>
+        <f aca="false">O21*Assumptions!$B$29+O21*(1-Assumptions!$B$29)*Assumptions!$B$30+N21*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+O24</f>
+        <v>77411.3390142723</v>
       </c>
       <c r="P50" s="21" t="n">
-        <f aca="false">P29+P45</f>
-        <v>54759.84278502</v>
+        <f aca="false">P21*Assumptions!$B$29+P21*(1-Assumptions!$B$29)*Assumptions!$B$30+O21*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+P24</f>
+        <v>77548.6634208438</v>
       </c>
       <c r="Q50" s="21" t="n">
-        <f aca="false">Q29+Q45</f>
-        <v>54798.1906715138</v>
+        <f aca="false">Q21*Assumptions!$B$29+Q21*(1-Assumptions!$B$29)*Assumptions!$B$30+P21*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+Q24</f>
+        <v>77685.0723313715</v>
       </c>
       <c r="R50" s="21" t="n">
-        <f aca="false">R29+R45</f>
-        <v>54836.2829054309</v>
+        <f aca="false">R21*Assumptions!$B$29+R21*(1-Assumptions!$B$29)*Assumptions!$B$30+Q21*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+R24</f>
+        <v>77820.5718491623</v>
       </c>
       <c r="S50" s="21" t="n">
-        <f aca="false">S29+S45</f>
-        <v>54874.1211911219</v>
+        <f aca="false">S21*Assumptions!$B$29+S21*(1-Assumptions!$B$29)*Assumptions!$B$30+R21*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+S24</f>
+        <v>77955.1680368346</v>
       </c>
       <c r="T50" s="21" t="n">
-        <f aca="false">T29+T45</f>
-        <v>54911.7072215749</v>
+        <f aca="false">T21*Assumptions!$B$29+T21*(1-Assumptions!$B$29)*Assumptions!$B$30+S21*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+T24</f>
+        <v>78088.866916589</v>
       </c>
       <c r="U50" s="21" t="n">
-        <f aca="false">U29+U45</f>
-        <v>54949.0426784916</v>
+        <f aca="false">U21*Assumptions!$B$29+U21*(1-Assumptions!$B$29)*Assumptions!$B$30+T21*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+U24</f>
+        <v>78221.6744704784</v>
       </c>
       <c r="V50" s="21" t="n">
-        <f aca="false">V29+V45</f>
-        <v>54986.1292323622</v>
+        <f aca="false">V21*Assumptions!$B$29+V21*(1-Assumptions!$B$29)*Assumptions!$B$30+U21*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+V24</f>
+        <v>78353.5966406752</v>
       </c>
       <c r="W50" s="21" t="n">
-        <f aca="false">W29+W45</f>
-        <v>55022.9685425403</v>
+        <f aca="false">W21*Assumptions!$B$29+W21*(1-Assumptions!$B$29)*Assumptions!$B$30+V21*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+W24</f>
+        <v>78484.6393297374</v>
       </c>
       <c r="X50" s="21" t="n">
-        <f aca="false">X29+X45</f>
-        <v>55059.5622573173</v>
+        <f aca="false">X21*Assumptions!$B$29+X21*(1-Assumptions!$B$29)*Assumptions!$B$30+W21*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+X24</f>
+        <v>78614.8084008725</v>
       </c>
       <c r="Y50" s="21" t="n">
-        <f aca="false">Y29+Y45</f>
-        <v>55095.9120139957</v>
+        <f aca="false">Y21*Assumptions!$B$29+Y21*(1-Assumptions!$B$29)*Assumptions!$B$30+X21*(1-Assumptions!$B$29)*(1-Assumptions!$B$30)+Y24</f>
+        <v>78744.1096782</v>
       </c>
       <c r="Z50" s="21" t="n">
         <f aca="false">SUM(B50:M50)</f>
-        <v>492168.38775408</v>
+        <v>617109.472257545</v>
       </c>
       <c r="AA50" s="21" t="n">
         <f aca="false">SUM(N50:Y50)</f>
-        <v>658686.35930312</v>
+        <v>936162.435690653</v>
       </c>
       <c r="AB50" s="21" t="n">
         <f aca="false">SUM(B50:Y50)</f>
-        <v>1150854.7470572</v>
+        <v>1553271.9079482</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="17" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B51" s="21" t="n">
-        <f aca="false">IF(1=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(1=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(1=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(1=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(1=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
-        <v>0</v>
+        <f aca="false">B30+B46</f>
+        <v>25296</v>
       </c>
       <c r="C51" s="21" t="n">
-        <f aca="false">IF(2=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(2=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(2=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(2=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(2=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
-        <v>0</v>
+        <f aca="false">C30+C46</f>
+        <v>26988</v>
       </c>
       <c r="D51" s="21" t="n">
-        <f aca="false">IF(3=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(3=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(3=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(3=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(3=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
-        <v>0</v>
+        <f aca="false">D30+D46</f>
+        <v>28108.4375</v>
       </c>
       <c r="E51" s="21" t="n">
-        <f aca="false">IF(4=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(4=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(4=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(4=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(4=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
-        <v>0</v>
+        <f aca="false">E30+E46</f>
+        <v>29229.8520833333</v>
       </c>
       <c r="F51" s="21" t="n">
-        <f aca="false">IF(5=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(5=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(5=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(5=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(5=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
-        <v>0</v>
+        <f aca="false">F30+F46</f>
+        <v>30352.2372361111</v>
       </c>
       <c r="G51" s="21" t="n">
-        <f aca="false">IF(6=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(6=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(6=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(6=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(6=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
-        <v>0</v>
+        <f aca="false">G30+G46</f>
+        <v>31475.5864878704</v>
       </c>
       <c r="H51" s="21" t="n">
-        <f aca="false">IF(7=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(7=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(7=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(7=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(7=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
-        <v>10100</v>
+        <f aca="false">H30+H46</f>
+        <v>52377.0309624293</v>
       </c>
       <c r="I51" s="21" t="n">
-        <f aca="false">IF(8=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(8=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(8=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(8=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(8=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
-        <v>0</v>
+        <f aca="false">I30+I46</f>
+        <v>50834.6636174652</v>
       </c>
       <c r="J51" s="21" t="n">
-        <f aca="false">IF(9=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(9=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(9=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(9=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(9=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
-        <v>0</v>
+        <f aca="false">J30+J46</f>
+        <v>53795.1031659119</v>
       </c>
       <c r="K51" s="21" t="n">
-        <f aca="false">IF(10=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(10=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(10=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(10=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(10=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
-        <v>17600</v>
+        <f aca="false">K30+K46</f>
+        <v>54519.7191030821</v>
       </c>
       <c r="L51" s="21" t="n">
-        <f aca="false">IF(11=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(11=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(11=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(11=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(11=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
-        <v>0</v>
+        <f aca="false">L30+L46</f>
+        <v>54570.6053141221</v>
       </c>
       <c r="M51" s="21" t="n">
-        <f aca="false">IF(12=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(12=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(12=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(12=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(12=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
-        <v>0</v>
+        <f aca="false">M30+M46</f>
+        <v>54621.1522837552</v>
       </c>
       <c r="N51" s="21" t="n">
-        <f aca="false">IF(13=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(13=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(13=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(13=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(13=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
-        <v>0</v>
+        <f aca="false">N30+N46</f>
+        <v>54671.3622735907</v>
       </c>
       <c r="O51" s="21" t="n">
-        <f aca="false">IF(14=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(14=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(14=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(14=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(14=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
-        <v>0</v>
+        <f aca="false">O30+O46</f>
+        <v>54721.2375301606</v>
       </c>
       <c r="P51" s="21" t="n">
-        <f aca="false">IF(15=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(15=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(15=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(15=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(15=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
-        <v>0</v>
+        <f aca="false">P30+P46</f>
+        <v>54759.84278502</v>
       </c>
       <c r="Q51" s="21" t="n">
-        <f aca="false">IF(16=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(16=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(16=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(16=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(16=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
-        <v>0</v>
+        <f aca="false">Q30+Q46</f>
+        <v>54798.1906715138</v>
       </c>
       <c r="R51" s="21" t="n">
-        <f aca="false">IF(17=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(17=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(17=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(17=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(17=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
-        <v>0</v>
+        <f aca="false">R30+R46</f>
+        <v>54836.2829054309</v>
       </c>
       <c r="S51" s="21" t="n">
-        <f aca="false">IF(18=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(18=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(18=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(18=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(18=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
-        <v>0</v>
+        <f aca="false">S30+S46</f>
+        <v>54874.1211911219</v>
       </c>
       <c r="T51" s="21" t="n">
-        <f aca="false">IF(19=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(19=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(19=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(19=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(19=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
-        <v>0</v>
+        <f aca="false">T30+T46</f>
+        <v>54911.7072215749</v>
       </c>
       <c r="U51" s="21" t="n">
-        <f aca="false">IF(20=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(20=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(20=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(20=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(20=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
-        <v>0</v>
+        <f aca="false">U30+U46</f>
+        <v>54949.0426784916</v>
       </c>
       <c r="V51" s="21" t="n">
-        <f aca="false">IF(21=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(21=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(21=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(21=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(21=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
-        <v>0</v>
+        <f aca="false">V30+V46</f>
+        <v>54986.1292323622</v>
       </c>
       <c r="W51" s="21" t="n">
-        <f aca="false">IF(22=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(22=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(22=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(22=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(22=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
-        <v>0</v>
+        <f aca="false">W30+W46</f>
+        <v>55022.9685425403</v>
       </c>
       <c r="X51" s="21" t="n">
-        <f aca="false">IF(23=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(23=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(23=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(23=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(23=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
-        <v>0</v>
+        <f aca="false">X30+X46</f>
+        <v>55059.5622573173</v>
       </c>
       <c r="Y51" s="21" t="n">
-        <f aca="false">IF(24=Assumptions!$B$8+Assumptions!$B$56,Assumptions!$B$54*(1-Assumptions!$B$69),0)+IF(24=Assumptions!$B$8+Assumptions!$B$59,Assumptions!$B$57*(1-Assumptions!$B$69),0)+IF(24=Assumptions!$B$8+Assumptions!$B$62,Assumptions!$B$60*(1-Assumptions!$B$69),0)+IF(24=Assumptions!$B$8+Assumptions!$B$65,Assumptions!$B$63*(1-Assumptions!$B$69),0)+IF(24=Assumptions!$B$8+Assumptions!$B$68,Assumptions!$B$66*(1-Assumptions!$B$69),0)</f>
-        <v>0</v>
+        <f aca="false">Y30+Y46</f>
+        <v>55095.9120139957</v>
       </c>
       <c r="Z51" s="21" t="n">
         <f aca="false">SUM(B51:M51)</f>
-        <v>27700</v>
+        <v>492168.38775408</v>
       </c>
       <c r="AA51" s="21" t="n">
         <f aca="false">SUM(N51:Y51)</f>
-        <v>0</v>
+        <v>658686.35930312</v>
       </c>
       <c r="AB51" s="21" t="n">
         <f aca="false">SUM(B51:Y51)</f>
+        <v>1150854.7470572</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="B52" s="21" t="n">
+        <f aca="false">IF(1=Assumptions!$B$8+Assumptions!$B$58,Assumptions!$B$56*(1-Assumptions!$B$71),0)+IF(1=Assumptions!$B$8+Assumptions!$B$61,Assumptions!$B$59*(1-Assumptions!$B$71),0)+IF(1=Assumptions!$B$8+Assumptions!$B$64,Assumptions!$B$62*(1-Assumptions!$B$71),0)+IF(1=Assumptions!$B$8+Assumptions!$B$67,Assumptions!$B$65*(1-Assumptions!$B$71),0)+IF(1=Assumptions!$B$8+Assumptions!$B$70,Assumptions!$B$68*(1-Assumptions!$B$71),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C52" s="21" t="n">
+        <f aca="false">IF(2=Assumptions!$B$8+Assumptions!$B$58,Assumptions!$B$56*(1-Assumptions!$B$71),0)+IF(2=Assumptions!$B$8+Assumptions!$B$61,Assumptions!$B$59*(1-Assumptions!$B$71),0)+IF(2=Assumptions!$B$8+Assumptions!$B$64,Assumptions!$B$62*(1-Assumptions!$B$71),0)+IF(2=Assumptions!$B$8+Assumptions!$B$67,Assumptions!$B$65*(1-Assumptions!$B$71),0)+IF(2=Assumptions!$B$8+Assumptions!$B$70,Assumptions!$B$68*(1-Assumptions!$B$71),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D52" s="21" t="n">
+        <f aca="false">IF(3=Assumptions!$B$8+Assumptions!$B$58,Assumptions!$B$56*(1-Assumptions!$B$71),0)+IF(3=Assumptions!$B$8+Assumptions!$B$61,Assumptions!$B$59*(1-Assumptions!$B$71),0)+IF(3=Assumptions!$B$8+Assumptions!$B$64,Assumptions!$B$62*(1-Assumptions!$B$71),0)+IF(3=Assumptions!$B$8+Assumptions!$B$67,Assumptions!$B$65*(1-Assumptions!$B$71),0)+IF(3=Assumptions!$B$8+Assumptions!$B$70,Assumptions!$B$68*(1-Assumptions!$B$71),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E52" s="21" t="n">
+        <f aca="false">IF(4=Assumptions!$B$8+Assumptions!$B$58,Assumptions!$B$56*(1-Assumptions!$B$71),0)+IF(4=Assumptions!$B$8+Assumptions!$B$61,Assumptions!$B$59*(1-Assumptions!$B$71),0)+IF(4=Assumptions!$B$8+Assumptions!$B$64,Assumptions!$B$62*(1-Assumptions!$B$71),0)+IF(4=Assumptions!$B$8+Assumptions!$B$67,Assumptions!$B$65*(1-Assumptions!$B$71),0)+IF(4=Assumptions!$B$8+Assumptions!$B$70,Assumptions!$B$68*(1-Assumptions!$B$71),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F52" s="21" t="n">
+        <f aca="false">IF(5=Assumptions!$B$8+Assumptions!$B$58,Assumptions!$B$56*(1-Assumptions!$B$71),0)+IF(5=Assumptions!$B$8+Assumptions!$B$61,Assumptions!$B$59*(1-Assumptions!$B$71),0)+IF(5=Assumptions!$B$8+Assumptions!$B$64,Assumptions!$B$62*(1-Assumptions!$B$71),0)+IF(5=Assumptions!$B$8+Assumptions!$B$67,Assumptions!$B$65*(1-Assumptions!$B$71),0)+IF(5=Assumptions!$B$8+Assumptions!$B$70,Assumptions!$B$68*(1-Assumptions!$B$71),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G52" s="21" t="n">
+        <f aca="false">IF(6=Assumptions!$B$8+Assumptions!$B$58,Assumptions!$B$56*(1-Assumptions!$B$71),0)+IF(6=Assumptions!$B$8+Assumptions!$B$61,Assumptions!$B$59*(1-Assumptions!$B$71),0)+IF(6=Assumptions!$B$8+Assumptions!$B$64,Assumptions!$B$62*(1-Assumptions!$B$71),0)+IF(6=Assumptions!$B$8+Assumptions!$B$67,Assumptions!$B$65*(1-Assumptions!$B$71),0)+IF(6=Assumptions!$B$8+Assumptions!$B$70,Assumptions!$B$68*(1-Assumptions!$B$71),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H52" s="21" t="n">
+        <f aca="false">IF(7=Assumptions!$B$8+Assumptions!$B$58,Assumptions!$B$56*(1-Assumptions!$B$71),0)+IF(7=Assumptions!$B$8+Assumptions!$B$61,Assumptions!$B$59*(1-Assumptions!$B$71),0)+IF(7=Assumptions!$B$8+Assumptions!$B$64,Assumptions!$B$62*(1-Assumptions!$B$71),0)+IF(7=Assumptions!$B$8+Assumptions!$B$67,Assumptions!$B$65*(1-Assumptions!$B$71),0)+IF(7=Assumptions!$B$8+Assumptions!$B$70,Assumptions!$B$68*(1-Assumptions!$B$71),0)</f>
+        <v>10100</v>
+      </c>
+      <c r="I52" s="21" t="n">
+        <f aca="false">IF(8=Assumptions!$B$8+Assumptions!$B$58,Assumptions!$B$56*(1-Assumptions!$B$71),0)+IF(8=Assumptions!$B$8+Assumptions!$B$61,Assumptions!$B$59*(1-Assumptions!$B$71),0)+IF(8=Assumptions!$B$8+Assumptions!$B$64,Assumptions!$B$62*(1-Assumptions!$B$71),0)+IF(8=Assumptions!$B$8+Assumptions!$B$67,Assumptions!$B$65*(1-Assumptions!$B$71),0)+IF(8=Assumptions!$B$8+Assumptions!$B$70,Assumptions!$B$68*(1-Assumptions!$B$71),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J52" s="21" t="n">
+        <f aca="false">IF(9=Assumptions!$B$8+Assumptions!$B$58,Assumptions!$B$56*(1-Assumptions!$B$71),0)+IF(9=Assumptions!$B$8+Assumptions!$B$61,Assumptions!$B$59*(1-Assumptions!$B$71),0)+IF(9=Assumptions!$B$8+Assumptions!$B$64,Assumptions!$B$62*(1-Assumptions!$B$71),0)+IF(9=Assumptions!$B$8+Assumptions!$B$67,Assumptions!$B$65*(1-Assumptions!$B$71),0)+IF(9=Assumptions!$B$8+Assumptions!$B$70,Assumptions!$B$68*(1-Assumptions!$B$71),0)</f>
+        <v>0</v>
+      </c>
+      <c r="K52" s="21" t="n">
+        <f aca="false">IF(10=Assumptions!$B$8+Assumptions!$B$58,Assumptions!$B$56*(1-Assumptions!$B$71),0)+IF(10=Assumptions!$B$8+Assumptions!$B$61,Assumptions!$B$59*(1-Assumptions!$B$71),0)+IF(10=Assumptions!$B$8+Assumptions!$B$64,Assumptions!$B$62*(1-Assumptions!$B$71),0)+IF(10=Assumptions!$B$8+Assumptions!$B$67,Assumptions!$B$65*(1-Assumptions!$B$71),0)+IF(10=Assumptions!$B$8+Assumptions!$B$70,Assumptions!$B$68*(1-Assumptions!$B$71),0)</f>
+        <v>17600</v>
+      </c>
+      <c r="L52" s="21" t="n">
+        <f aca="false">IF(11=Assumptions!$B$8+Assumptions!$B$58,Assumptions!$B$56*(1-Assumptions!$B$71),0)+IF(11=Assumptions!$B$8+Assumptions!$B$61,Assumptions!$B$59*(1-Assumptions!$B$71),0)+IF(11=Assumptions!$B$8+Assumptions!$B$64,Assumptions!$B$62*(1-Assumptions!$B$71),0)+IF(11=Assumptions!$B$8+Assumptions!$B$67,Assumptions!$B$65*(1-Assumptions!$B$71),0)+IF(11=Assumptions!$B$8+Assumptions!$B$70,Assumptions!$B$68*(1-Assumptions!$B$71),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M52" s="21" t="n">
+        <f aca="false">IF(12=Assumptions!$B$8+Assumptions!$B$58,Assumptions!$B$56*(1-Assumptions!$B$71),0)+IF(12=Assumptions!$B$8+Assumptions!$B$61,Assumptions!$B$59*(1-Assumptions!$B$71),0)+IF(12=Assumptions!$B$8+Assumptions!$B$64,Assumptions!$B$62*(1-Assumptions!$B$71),0)+IF(12=Assumptions!$B$8+Assumptions!$B$67,Assumptions!$B$65*(1-Assumptions!$B$71),0)+IF(12=Assumptions!$B$8+Assumptions!$B$70,Assumptions!$B$68*(1-Assumptions!$B$71),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N52" s="21" t="n">
+        <f aca="false">IF(13=Assumptions!$B$8+Assumptions!$B$58,Assumptions!$B$56*(1-Assumptions!$B$71),0)+IF(13=Assumptions!$B$8+Assumptions!$B$61,Assumptions!$B$59*(1-Assumptions!$B$71),0)+IF(13=Assumptions!$B$8+Assumptions!$B$64,Assumptions!$B$62*(1-Assumptions!$B$71),0)+IF(13=Assumptions!$B$8+Assumptions!$B$67,Assumptions!$B$65*(1-Assumptions!$B$71),0)+IF(13=Assumptions!$B$8+Assumptions!$B$70,Assumptions!$B$68*(1-Assumptions!$B$71),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O52" s="21" t="n">
+        <f aca="false">IF(14=Assumptions!$B$8+Assumptions!$B$58,Assumptions!$B$56*(1-Assumptions!$B$71),0)+IF(14=Assumptions!$B$8+Assumptions!$B$61,Assumptions!$B$59*(1-Assumptions!$B$71),0)+IF(14=Assumptions!$B$8+Assumptions!$B$64,Assumptions!$B$62*(1-Assumptions!$B$71),0)+IF(14=Assumptions!$B$8+Assumptions!$B$67,Assumptions!$B$65*(1-Assumptions!$B$71),0)+IF(14=Assumptions!$B$8+Assumptions!$B$70,Assumptions!$B$68*(1-Assumptions!$B$71),0)</f>
+        <v>0</v>
+      </c>
+      <c r="P52" s="21" t="n">
+        <f aca="false">IF(15=Assumptions!$B$8+Assumptions!$B$58,Assumptions!$B$56*(1-Assumptions!$B$71),0)+IF(15=Assumptions!$B$8+Assumptions!$B$61,Assumptions!$B$59*(1-Assumptions!$B$71),0)+IF(15=Assumptions!$B$8+Assumptions!$B$64,Assumptions!$B$62*(1-Assumptions!$B$71),0)+IF(15=Assumptions!$B$8+Assumptions!$B$67,Assumptions!$B$65*(1-Assumptions!$B$71),0)+IF(15=Assumptions!$B$8+Assumptions!$B$70,Assumptions!$B$68*(1-Assumptions!$B$71),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q52" s="21" t="n">
+        <f aca="false">IF(16=Assumptions!$B$8+Assumptions!$B$58,Assumptions!$B$56*(1-Assumptions!$B$71),0)+IF(16=Assumptions!$B$8+Assumptions!$B$61,Assumptions!$B$59*(1-Assumptions!$B$71),0)+IF(16=Assumptions!$B$8+Assumptions!$B$64,Assumptions!$B$62*(1-Assumptions!$B$71),0)+IF(16=Assumptions!$B$8+Assumptions!$B$67,Assumptions!$B$65*(1-Assumptions!$B$71),0)+IF(16=Assumptions!$B$8+Assumptions!$B$70,Assumptions!$B$68*(1-Assumptions!$B$71),0)</f>
+        <v>0</v>
+      </c>
+      <c r="R52" s="21" t="n">
+        <f aca="false">IF(17=Assumptions!$B$8+Assumptions!$B$58,Assumptions!$B$56*(1-Assumptions!$B$71),0)+IF(17=Assumptions!$B$8+Assumptions!$B$61,Assumptions!$B$59*(1-Assumptions!$B$71),0)+IF(17=Assumptions!$B$8+Assumptions!$B$64,Assumptions!$B$62*(1-Assumptions!$B$71),0)+IF(17=Assumptions!$B$8+Assumptions!$B$67,Assumptions!$B$65*(1-Assumptions!$B$71),0)+IF(17=Assumptions!$B$8+Assumptions!$B$70,Assumptions!$B$68*(1-Assumptions!$B$71),0)</f>
+        <v>0</v>
+      </c>
+      <c r="S52" s="21" t="n">
+        <f aca="false">IF(18=Assumptions!$B$8+Assumptions!$B$58,Assumptions!$B$56*(1-Assumptions!$B$71),0)+IF(18=Assumptions!$B$8+Assumptions!$B$61,Assumptions!$B$59*(1-Assumptions!$B$71),0)+IF(18=Assumptions!$B$8+Assumptions!$B$64,Assumptions!$B$62*(1-Assumptions!$B$71),0)+IF(18=Assumptions!$B$8+Assumptions!$B$67,Assumptions!$B$65*(1-Assumptions!$B$71),0)+IF(18=Assumptions!$B$8+Assumptions!$B$70,Assumptions!$B$68*(1-Assumptions!$B$71),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T52" s="21" t="n">
+        <f aca="false">IF(19=Assumptions!$B$8+Assumptions!$B$58,Assumptions!$B$56*(1-Assumptions!$B$71),0)+IF(19=Assumptions!$B$8+Assumptions!$B$61,Assumptions!$B$59*(1-Assumptions!$B$71),0)+IF(19=Assumptions!$B$8+Assumptions!$B$64,Assumptions!$B$62*(1-Assumptions!$B$71),0)+IF(19=Assumptions!$B$8+Assumptions!$B$67,Assumptions!$B$65*(1-Assumptions!$B$71),0)+IF(19=Assumptions!$B$8+Assumptions!$B$70,Assumptions!$B$68*(1-Assumptions!$B$71),0)</f>
+        <v>0</v>
+      </c>
+      <c r="U52" s="21" t="n">
+        <f aca="false">IF(20=Assumptions!$B$8+Assumptions!$B$58,Assumptions!$B$56*(1-Assumptions!$B$71),0)+IF(20=Assumptions!$B$8+Assumptions!$B$61,Assumptions!$B$59*(1-Assumptions!$B$71),0)+IF(20=Assumptions!$B$8+Assumptions!$B$64,Assumptions!$B$62*(1-Assumptions!$B$71),0)+IF(20=Assumptions!$B$8+Assumptions!$B$67,Assumptions!$B$65*(1-Assumptions!$B$71),0)+IF(20=Assumptions!$B$8+Assumptions!$B$70,Assumptions!$B$68*(1-Assumptions!$B$71),0)</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="21" t="n">
+        <f aca="false">IF(21=Assumptions!$B$8+Assumptions!$B$58,Assumptions!$B$56*(1-Assumptions!$B$71),0)+IF(21=Assumptions!$B$8+Assumptions!$B$61,Assumptions!$B$59*(1-Assumptions!$B$71),0)+IF(21=Assumptions!$B$8+Assumptions!$B$64,Assumptions!$B$62*(1-Assumptions!$B$71),0)+IF(21=Assumptions!$B$8+Assumptions!$B$67,Assumptions!$B$65*(1-Assumptions!$B$71),0)+IF(21=Assumptions!$B$8+Assumptions!$B$70,Assumptions!$B$68*(1-Assumptions!$B$71),0)</f>
+        <v>0</v>
+      </c>
+      <c r="W52" s="21" t="n">
+        <f aca="false">IF(22=Assumptions!$B$8+Assumptions!$B$58,Assumptions!$B$56*(1-Assumptions!$B$71),0)+IF(22=Assumptions!$B$8+Assumptions!$B$61,Assumptions!$B$59*(1-Assumptions!$B$71),0)+IF(22=Assumptions!$B$8+Assumptions!$B$64,Assumptions!$B$62*(1-Assumptions!$B$71),0)+IF(22=Assumptions!$B$8+Assumptions!$B$67,Assumptions!$B$65*(1-Assumptions!$B$71),0)+IF(22=Assumptions!$B$8+Assumptions!$B$70,Assumptions!$B$68*(1-Assumptions!$B$71),0)</f>
+        <v>0</v>
+      </c>
+      <c r="X52" s="21" t="n">
+        <f aca="false">IF(23=Assumptions!$B$8+Assumptions!$B$58,Assumptions!$B$56*(1-Assumptions!$B$71),0)+IF(23=Assumptions!$B$8+Assumptions!$B$61,Assumptions!$B$59*(1-Assumptions!$B$71),0)+IF(23=Assumptions!$B$8+Assumptions!$B$64,Assumptions!$B$62*(1-Assumptions!$B$71),0)+IF(23=Assumptions!$B$8+Assumptions!$B$67,Assumptions!$B$65*(1-Assumptions!$B$71),0)+IF(23=Assumptions!$B$8+Assumptions!$B$70,Assumptions!$B$68*(1-Assumptions!$B$71),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="21" t="n">
+        <f aca="false">IF(24=Assumptions!$B$8+Assumptions!$B$58,Assumptions!$B$56*(1-Assumptions!$B$71),0)+IF(24=Assumptions!$B$8+Assumptions!$B$61,Assumptions!$B$59*(1-Assumptions!$B$71),0)+IF(24=Assumptions!$B$8+Assumptions!$B$64,Assumptions!$B$62*(1-Assumptions!$B$71),0)+IF(24=Assumptions!$B$8+Assumptions!$B$67,Assumptions!$B$65*(1-Assumptions!$B$71),0)+IF(24=Assumptions!$B$8+Assumptions!$B$70,Assumptions!$B$68*(1-Assumptions!$B$71),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z52" s="21" t="n">
+        <f aca="false">SUM(B52:M52)</f>
         <v>27700</v>
       </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="B52" s="22" t="n">
-        <f aca="false">B49-B50-B51</f>
-        <v>93</v>
-      </c>
-      <c r="C52" s="22" t="n">
-        <f aca="false">C49-C50-C51</f>
-        <v>2265</v>
-      </c>
-      <c r="D52" s="22" t="n">
-        <f aca="false">D49-D50-D51</f>
-        <v>3345.71875</v>
-      </c>
-      <c r="E52" s="22" t="n">
-        <f aca="false">E49-E50-E51</f>
-        <v>4428.93604166666</v>
-      </c>
-      <c r="F52" s="22" t="n">
-        <f aca="false">F49-F50-F51</f>
-        <v>5514.63521805556</v>
-      </c>
-      <c r="G52" s="22" t="n">
-        <f aca="false">G49-G50-G51</f>
-        <v>6602.79973326852</v>
-      </c>
-      <c r="H52" s="22" t="n">
-        <f aca="false">H49-H50-H51</f>
-        <v>-4569.37439943131</v>
-      </c>
-      <c r="I52" s="22" t="n">
-        <f aca="false">I49-I50-I51</f>
-        <v>13913.3148184462</v>
-      </c>
-      <c r="J52" s="22" t="n">
-        <f aca="false">J49-J50-J51</f>
-        <v>16725.18166376</v>
-      </c>
-      <c r="K52" s="22" t="n">
-        <f aca="false">K49-K50-K51</f>
-        <v>4182.79007772531</v>
-      </c>
-      <c r="L52" s="22" t="n">
-        <f aca="false">L49-L50-L51</f>
-        <v>22304.9133888133</v>
-      </c>
-      <c r="M52" s="22" t="n">
-        <f aca="false">M49-M50-M51</f>
-        <v>22434.1692111606</v>
-      </c>
-      <c r="N52" s="22" t="n">
-        <f aca="false">N49-N50-N51</f>
-        <v>22562.5633280257</v>
-      </c>
-      <c r="O52" s="22" t="n">
-        <f aca="false">O49-O50-O51</f>
-        <v>22690.1014841117</v>
-      </c>
-      <c r="P52" s="22" t="n">
-        <f aca="false">P49-P50-P51</f>
-        <v>22788.8206358237</v>
-      </c>
-      <c r="Q52" s="22" t="n">
-        <f aca="false">Q49-Q50-Q51</f>
-        <v>22886.8816598577</v>
-      </c>
-      <c r="R52" s="22" t="n">
-        <f aca="false">R49-R50-R51</f>
-        <v>22984.2889437315</v>
-      </c>
-      <c r="S52" s="22" t="n">
-        <f aca="false">S49-S50-S51</f>
-        <v>23081.0468457127</v>
-      </c>
-      <c r="T52" s="22" t="n">
-        <f aca="false">T49-T50-T51</f>
-        <v>23177.1596950141</v>
-      </c>
-      <c r="U52" s="22" t="n">
-        <f aca="false">U49-U50-U51</f>
-        <v>23272.6317919868</v>
-      </c>
-      <c r="V52" s="22" t="n">
-        <f aca="false">V49-V50-V51</f>
-        <v>23367.467408313</v>
-      </c>
-      <c r="W52" s="22" t="n">
-        <f aca="false">W49-W50-W51</f>
-        <v>23461.6707871971</v>
-      </c>
-      <c r="X52" s="22" t="n">
-        <f aca="false">X49-X50-X51</f>
-        <v>23555.2461435552</v>
-      </c>
-      <c r="Y52" s="22" t="n">
-        <f aca="false">Y49-Y50-Y51</f>
-        <v>23648.1976642043</v>
-      </c>
-      <c r="Z52" s="23" t="n">
-        <f aca="false">SUM(B52:M52)</f>
-        <v>97241.0845034648</v>
-      </c>
-      <c r="AA52" s="23" t="n">
+      <c r="AA52" s="21" t="n">
         <f aca="false">SUM(N52:Y52)</f>
-        <v>277476.076387534</v>
-      </c>
-      <c r="AB52" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="21" t="n">
         <f aca="false">SUM(B52:Y52)</f>
-        <v>374717.160890998</v>
+        <v>27700</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="B53" s="23" t="n">
-        <f aca="false">Assumptions!$B$32+B52</f>
+        <v>181</v>
+      </c>
+      <c r="B53" s="22" t="n">
+        <f aca="false">B50-B51-B52</f>
+        <v>93</v>
+      </c>
+      <c r="C53" s="22" t="n">
+        <f aca="false">C50-C51-C52</f>
+        <v>2265</v>
+      </c>
+      <c r="D53" s="22" t="n">
+        <f aca="false">D50-D51-D52</f>
+        <v>3345.71875</v>
+      </c>
+      <c r="E53" s="22" t="n">
+        <f aca="false">E50-E51-E52</f>
+        <v>4428.93604166666</v>
+      </c>
+      <c r="F53" s="22" t="n">
+        <f aca="false">F50-F51-F52</f>
+        <v>5514.63521805556</v>
+      </c>
+      <c r="G53" s="22" t="n">
+        <f aca="false">G50-G51-G52</f>
+        <v>6602.79973326852</v>
+      </c>
+      <c r="H53" s="22" t="n">
+        <f aca="false">H50-H51-H52</f>
+        <v>-4569.37439943131</v>
+      </c>
+      <c r="I53" s="22" t="n">
+        <f aca="false">I50-I51-I52</f>
+        <v>13913.3148184462</v>
+      </c>
+      <c r="J53" s="22" t="n">
+        <f aca="false">J50-J51-J52</f>
+        <v>16725.18166376</v>
+      </c>
+      <c r="K53" s="22" t="n">
+        <f aca="false">K50-K51-K52</f>
+        <v>4182.79007772531</v>
+      </c>
+      <c r="L53" s="22" t="n">
+        <f aca="false">L50-L51-L52</f>
+        <v>22304.9133888133</v>
+      </c>
+      <c r="M53" s="22" t="n">
+        <f aca="false">M50-M51-M52</f>
+        <v>22434.1692111606</v>
+      </c>
+      <c r="N53" s="22" t="n">
+        <f aca="false">N50-N51-N52</f>
+        <v>22562.5633280257</v>
+      </c>
+      <c r="O53" s="22" t="n">
+        <f aca="false">O50-O51-O52</f>
+        <v>22690.1014841117</v>
+      </c>
+      <c r="P53" s="22" t="n">
+        <f aca="false">P50-P51-P52</f>
+        <v>22788.8206358237</v>
+      </c>
+      <c r="Q53" s="22" t="n">
+        <f aca="false">Q50-Q51-Q52</f>
+        <v>22886.8816598577</v>
+      </c>
+      <c r="R53" s="22" t="n">
+        <f aca="false">R50-R51-R52</f>
+        <v>22984.2889437315</v>
+      </c>
+      <c r="S53" s="22" t="n">
+        <f aca="false">S50-S51-S52</f>
+        <v>23081.0468457127</v>
+      </c>
+      <c r="T53" s="22" t="n">
+        <f aca="false">T50-T51-T52</f>
+        <v>23177.1596950141</v>
+      </c>
+      <c r="U53" s="22" t="n">
+        <f aca="false">U50-U51-U52</f>
+        <v>23272.6317919868</v>
+      </c>
+      <c r="V53" s="22" t="n">
+        <f aca="false">V50-V51-V52</f>
+        <v>23367.467408313</v>
+      </c>
+      <c r="W53" s="22" t="n">
+        <f aca="false">W50-W51-W52</f>
+        <v>23461.6707871971</v>
+      </c>
+      <c r="X53" s="22" t="n">
+        <f aca="false">X50-X51-X52</f>
+        <v>23555.2461435552</v>
+      </c>
+      <c r="Y53" s="22" t="n">
+        <f aca="false">Y50-Y51-Y52</f>
+        <v>23648.1976642043</v>
+      </c>
+      <c r="Z53" s="23" t="n">
+        <f aca="false">SUM(B53:M53)</f>
+        <v>97241.0845034648</v>
+      </c>
+      <c r="AA53" s="23" t="n">
+        <f aca="false">SUM(N53:Y53)</f>
+        <v>277476.076387534</v>
+      </c>
+      <c r="AB53" s="23" t="n">
+        <f aca="false">SUM(B53:Y53)</f>
+        <v>374717.160890998</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="B54" s="23" t="n">
+        <f aca="false">Assumptions!$B$32+B53</f>
         <v>25093</v>
       </c>
-      <c r="C53" s="23" t="n">
-        <f aca="false">B53+C52</f>
+      <c r="C54" s="23" t="n">
+        <f aca="false">B54+C53</f>
         <v>27358</v>
       </c>
-      <c r="D53" s="23" t="n">
-        <f aca="false">C53+D52</f>
+      <c r="D54" s="23" t="n">
+        <f aca="false">C54+D53</f>
         <v>30703.71875</v>
       </c>
-      <c r="E53" s="23" t="n">
-        <f aca="false">D53+E52</f>
+      <c r="E54" s="23" t="n">
+        <f aca="false">D54+E53</f>
         <v>35132.6547916667</v>
       </c>
-      <c r="F53" s="23" t="n">
-        <f aca="false">E53+F52</f>
+      <c r="F54" s="23" t="n">
+        <f aca="false">E54+F53</f>
         <v>40647.2900097222</v>
       </c>
-      <c r="G53" s="23" t="n">
-        <f aca="false">F53+G52</f>
+      <c r="G54" s="23" t="n">
+        <f aca="false">F54+G53</f>
         <v>47250.0897429907</v>
       </c>
-      <c r="H53" s="23" t="n">
-        <f aca="false">G53+H52</f>
+      <c r="H54" s="23" t="n">
+        <f aca="false">G54+H53</f>
         <v>42680.7153435594</v>
       </c>
-      <c r="I53" s="23" t="n">
-        <f aca="false">H53+I52</f>
+      <c r="I54" s="23" t="n">
+        <f aca="false">H54+I53</f>
         <v>56594.0301620056</v>
       </c>
-      <c r="J53" s="23" t="n">
-        <f aca="false">I53+J52</f>
+      <c r="J54" s="23" t="n">
+        <f aca="false">I54+J53</f>
         <v>73319.2118257656</v>
       </c>
-      <c r="K53" s="23" t="n">
-        <f aca="false">J53+K52</f>
+      <c r="K54" s="23" t="n">
+        <f aca="false">J54+K53</f>
         <v>77502.0019034909</v>
       </c>
-      <c r="L53" s="23" t="n">
-        <f aca="false">K53+L52</f>
+      <c r="L54" s="23" t="n">
+        <f aca="false">K54+L53</f>
         <v>99806.9152923042</v>
       </c>
-      <c r="M53" s="23" t="n">
-        <f aca="false">L53+M52</f>
+      <c r="M54" s="23" t="n">
+        <f aca="false">L54+M53</f>
         <v>122241.084503465</v>
       </c>
-      <c r="N53" s="23" t="n">
-        <f aca="false">M53+N52</f>
+      <c r="N54" s="23" t="n">
+        <f aca="false">M54+N53</f>
         <v>144803.647831491</v>
       </c>
-      <c r="O53" s="23" t="n">
-        <f aca="false">N53+O52</f>
+      <c r="O54" s="23" t="n">
+        <f aca="false">N54+O53</f>
         <v>167493.749315602</v>
       </c>
-      <c r="P53" s="23" t="n">
-        <f aca="false">O53+P52</f>
+      <c r="P54" s="23" t="n">
+        <f aca="false">O54+P53</f>
         <v>190282.569951426</v>
       </c>
-      <c r="Q53" s="23" t="n">
-        <f aca="false">P53+Q52</f>
+      <c r="Q54" s="23" t="n">
+        <f aca="false">P54+Q53</f>
         <v>213169.451611284</v>
       </c>
-      <c r="R53" s="23" t="n">
-        <f aca="false">Q53+R52</f>
+      <c r="R54" s="23" t="n">
+        <f aca="false">Q54+R53</f>
         <v>236153.740555015</v>
       </c>
-      <c r="S53" s="23" t="n">
-        <f aca="false">R53+S52</f>
+      <c r="S54" s="23" t="n">
+        <f aca="false">R54+S53</f>
         <v>259234.787400728</v>
       </c>
-      <c r="T53" s="23" t="n">
-        <f aca="false">S53+T52</f>
+      <c r="T54" s="23" t="n">
+        <f aca="false">S54+T53</f>
         <v>282411.947095742</v>
       </c>
-      <c r="U53" s="23" t="n">
-        <f aca="false">T53+U52</f>
+      <c r="U54" s="23" t="n">
+        <f aca="false">T54+U53</f>
         <v>305684.578887729</v>
       </c>
-      <c r="V53" s="23" t="n">
-        <f aca="false">U53+V52</f>
+      <c r="V54" s="23" t="n">
+        <f aca="false">U54+V53</f>
         <v>329052.046296042</v>
       </c>
-      <c r="W53" s="23" t="n">
-        <f aca="false">V53+W52</f>
+      <c r="W54" s="23" t="n">
+        <f aca="false">V54+W53</f>
         <v>352513.717083239</v>
       </c>
-      <c r="X53" s="23" t="n">
-        <f aca="false">W53+X52</f>
+      <c r="X54" s="23" t="n">
+        <f aca="false">W54+X53</f>
         <v>376068.963226794</v>
       </c>
-      <c r="Y53" s="23" t="n">
-        <f aca="false">X53+Y52</f>
+      <c r="Y54" s="23" t="n">
+        <f aca="false">X54+Y53</f>
         <v>399717.160890998</v>
       </c>
-      <c r="Z53" s="2"/>
-      <c r="AA53" s="2"/>
-      <c r="AB53" s="2"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="B54" s="5"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
-      <c r="H54" s="5"/>
-      <c r="I54" s="5"/>
-      <c r="J54" s="5"/>
-      <c r="K54" s="5"/>
-      <c r="L54" s="5"/>
-      <c r="M54" s="5"/>
-      <c r="N54" s="5"/>
-      <c r="O54" s="5"/>
-      <c r="P54" s="5"/>
-      <c r="Q54" s="5"/>
-      <c r="R54" s="5"/>
-      <c r="S54" s="5"/>
-      <c r="T54" s="5"/>
-      <c r="U54" s="5"/>
-      <c r="V54" s="5"/>
-      <c r="W54" s="5"/>
-      <c r="X54" s="5"/>
-      <c r="Y54" s="5"/>
-      <c r="Z54" s="5"/>
-      <c r="AA54" s="5"/>
-      <c r="AB54" s="5"/>
+      <c r="Z54" s="2"/>
+      <c r="AA54" s="2"/>
+      <c r="AB54" s="2"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="B55" s="21" t="n">
-        <f aca="false">IF(B8=0,0,B20/IF(B7&gt;0,2,1))</f>
-        <v>27300</v>
-      </c>
-      <c r="C55" s="21" t="n">
-        <f aca="false">IF(C8=0,0,C20/IF(C7&gt;0,2,1))</f>
-        <v>29400</v>
-      </c>
-      <c r="D55" s="21" t="n">
-        <f aca="false">IF(D8=0,0,D20/IF(D7&gt;0,2,1))</f>
-        <v>31500</v>
-      </c>
-      <c r="E55" s="21" t="n">
-        <f aca="false">IF(E8=0,0,E20/IF(E7&gt;0,2,1))</f>
-        <v>33600</v>
-      </c>
-      <c r="F55" s="21" t="n">
-        <f aca="false">IF(F8=0,0,F20/IF(F7&gt;0,2,1))</f>
-        <v>35700</v>
-      </c>
-      <c r="G55" s="21" t="n">
-        <f aca="false">IF(G8=0,0,G20/IF(G7&gt;0,2,1))</f>
-        <v>37800</v>
-      </c>
-      <c r="H55" s="21" t="n">
-        <f aca="false">IF(H8=0,0,H20/IF(H7&gt;0,2,1))</f>
-        <v>29400</v>
-      </c>
-      <c r="I55" s="21" t="n">
-        <f aca="false">IF(I8=0,0,I20/IF(I7&gt;0,2,1))</f>
-        <v>32200</v>
-      </c>
-      <c r="J55" s="21" t="n">
-        <f aca="false">IF(J8=0,0,J20/IF(J7&gt;0,2,1))</f>
-        <v>35000</v>
-      </c>
-      <c r="K55" s="21" t="n">
-        <f aca="false">IF(K8=0,0,K20/IF(K7&gt;0,2,1))</f>
-        <v>37800</v>
-      </c>
-      <c r="L55" s="21" t="n">
-        <f aca="false">IF(L8=0,0,L20/IF(L7&gt;0,2,1))</f>
-        <v>37800</v>
-      </c>
-      <c r="M55" s="21" t="n">
-        <f aca="false">IF(M8=0,0,M20/IF(M7&gt;0,2,1))</f>
-        <v>37800</v>
-      </c>
-      <c r="N55" s="21" t="n">
-        <f aca="false">IF(N8=0,0,N20/IF(N7&gt;0,2,1))</f>
-        <v>37800</v>
-      </c>
-      <c r="O55" s="21" t="n">
-        <f aca="false">IF(O8=0,0,O20/IF(O7&gt;0,2,1))</f>
-        <v>37800</v>
-      </c>
-      <c r="P55" s="21" t="n">
-        <f aca="false">IF(P8=0,0,P20/IF(P7&gt;0,2,1))</f>
-        <v>37800</v>
-      </c>
-      <c r="Q55" s="21" t="n">
-        <f aca="false">IF(Q8=0,0,Q20/IF(Q7&gt;0,2,1))</f>
-        <v>37800</v>
-      </c>
-      <c r="R55" s="21" t="n">
-        <f aca="false">IF(R8=0,0,R20/IF(R7&gt;0,2,1))</f>
-        <v>37800</v>
-      </c>
-      <c r="S55" s="21" t="n">
-        <f aca="false">IF(S8=0,0,S20/IF(S7&gt;0,2,1))</f>
-        <v>37800</v>
-      </c>
-      <c r="T55" s="21" t="n">
-        <f aca="false">IF(T8=0,0,T20/IF(T7&gt;0,2,1))</f>
-        <v>37800</v>
-      </c>
-      <c r="U55" s="21" t="n">
-        <f aca="false">IF(U8=0,0,U20/IF(U7&gt;0,2,1))</f>
-        <v>37800</v>
-      </c>
-      <c r="V55" s="21" t="n">
-        <f aca="false">IF(V8=0,0,V20/IF(V7&gt;0,2,1))</f>
-        <v>37800</v>
-      </c>
-      <c r="W55" s="21" t="n">
-        <f aca="false">IF(W8=0,0,W20/IF(W7&gt;0,2,1))</f>
-        <v>37800</v>
-      </c>
-      <c r="X55" s="21" t="n">
-        <f aca="false">IF(X8=0,0,X20/IF(X7&gt;0,2,1))</f>
-        <v>37800</v>
-      </c>
-      <c r="Y55" s="21" t="n">
-        <f aca="false">IF(Y8=0,0,Y20/IF(Y7&gt;0,2,1))</f>
-        <v>37800</v>
-      </c>
-      <c r="Z55" s="2"/>
-      <c r="AA55" s="2"/>
-      <c r="AB55" s="2"/>
+      <c r="A55" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B55" s="5"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="5"/>
+      <c r="K55" s="5"/>
+      <c r="L55" s="5"/>
+      <c r="M55" s="5"/>
+      <c r="N55" s="5"/>
+      <c r="O55" s="5"/>
+      <c r="P55" s="5"/>
+      <c r="Q55" s="5"/>
+      <c r="R55" s="5"/>
+      <c r="S55" s="5"/>
+      <c r="T55" s="5"/>
+      <c r="U55" s="5"/>
+      <c r="V55" s="5"/>
+      <c r="W55" s="5"/>
+      <c r="X55" s="5"/>
+      <c r="Y55" s="5"/>
+      <c r="Z55" s="5"/>
+      <c r="AA55" s="5"/>
+      <c r="AB55" s="5"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="17" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B56" s="21" t="n">
-        <f aca="false">IF(B13=0,0,(B40+B41+B42)/B13)</f>
-        <v>56.4593301435407</v>
+        <f aca="false">IF(B8=0,0,B21/IF(B7&gt;0,2,1))</f>
+        <v>27300</v>
       </c>
       <c r="C56" s="21" t="n">
-        <f aca="false">IF(C13=0,0,(C40+C41+C42)/C13)</f>
-        <v>55.344889338647</v>
+        <f aca="false">IF(C8=0,0,C21/IF(C7&gt;0,2,1))</f>
+        <v>29400</v>
       </c>
       <c r="D56" s="21" t="n">
-        <f aca="false">IF(D13=0,0,(D40+D41+D42)/D13)</f>
-        <v>54.7030520538172</v>
+        <f aca="false">IF(D8=0,0,D21/IF(D7&gt;0,2,1))</f>
+        <v>31500</v>
       </c>
       <c r="E56" s="21" t="n">
-        <f aca="false">IF(E13=0,0,(E40+E41+E42)/E13)</f>
-        <v>54.0387606024687</v>
+        <f aca="false">IF(E8=0,0,E21/IF(E7&gt;0,2,1))</f>
+        <v>33600</v>
       </c>
       <c r="F56" s="21" t="n">
-        <f aca="false">IF(F13=0,0,(F40+F41+F42)/F13)</f>
-        <v>53.3520026498769</v>
+        <f aca="false">IF(F8=0,0,F21/IF(F7&gt;0,2,1))</f>
+        <v>35700</v>
       </c>
       <c r="G56" s="21" t="n">
-        <f aca="false">IF(G13=0,0,(G40+G41+G42)/G13)</f>
-        <v>52.64284380353</v>
+        <f aca="false">IF(G8=0,0,G21/IF(G7&gt;0,2,1))</f>
+        <v>37800</v>
       </c>
       <c r="H56" s="21" t="n">
-        <f aca="false">IF(H13=0,0,(H40+H41+H42)/H13)</f>
-        <v>53.6007390411201</v>
+        <f aca="false">IF(H8=0,0,H21/IF(H7&gt;0,2,1))</f>
+        <v>29400</v>
       </c>
       <c r="I56" s="21" t="n">
-        <f aca="false">IF(I13=0,0,(I40+I41+I42)/I13)</f>
-        <v>53.0627977874208</v>
+        <f aca="false">IF(I8=0,0,I21/IF(I7&gt;0,2,1))</f>
+        <v>32200</v>
       </c>
       <c r="J56" s="21" t="n">
-        <f aca="false">IF(J13=0,0,(J40+J41+J42)/J13)</f>
-        <v>52.5042448312122</v>
+        <f aca="false">IF(J8=0,0,J21/IF(J7&gt;0,2,1))</f>
+        <v>35000</v>
       </c>
       <c r="K56" s="21" t="n">
-        <f aca="false">IF(K13=0,0,(K40+K41+K42)/K13)</f>
-        <v>51.9248754514001</v>
+        <f aca="false">IF(K8=0,0,K21/IF(K7&gt;0,2,1))</f>
+        <v>37800</v>
       </c>
       <c r="L56" s="21" t="n">
-        <f aca="false">IF(L13=0,0,(L40+L41+L42)/L13)</f>
-        <v>51.3245426468748</v>
+        <f aca="false">IF(L8=0,0,L21/IF(L7&gt;0,2,1))</f>
+        <v>37800</v>
       </c>
       <c r="M56" s="21" t="n">
-        <f aca="false">IF(M13=0,0,(M40+M41+M42)/M13)</f>
-        <v>50.7031622847844</v>
+        <f aca="false">IF(M8=0,0,M21/IF(M7&gt;0,2,1))</f>
+        <v>37800</v>
       </c>
       <c r="N56" s="21" t="n">
-        <f aca="false">IF(N13=0,0,(N40+N41+N42)/N13)</f>
-        <v>50.0607181383268</v>
+        <f aca="false">IF(N8=0,0,N21/IF(N7&gt;0,2,1))</f>
+        <v>37800</v>
       </c>
       <c r="O56" s="21" t="n">
-        <f aca="false">IF(O13=0,0,(O40+O41+O42)/O13)</f>
-        <v>49.3972667391676</v>
+        <f aca="false">IF(O8=0,0,O21/IF(O7&gt;0,2,1))</f>
+        <v>37800</v>
       </c>
       <c r="P56" s="21" t="n">
-        <f aca="false">IF(P13=0,0,(P40+P41+P42)/P13)</f>
-        <v>48.712941964224</v>
+        <f aca="false">IF(P8=0,0,P21/IF(P7&gt;0,2,1))</f>
+        <v>37800</v>
       </c>
       <c r="Q56" s="21" t="n">
-        <f aca="false">IF(Q13=0,0,(Q40+Q41+Q42)/Q13)</f>
-        <v>48.0079592722895</v>
+        <f aca="false">IF(Q8=0,0,Q21/IF(Q7&gt;0,2,1))</f>
+        <v>37800</v>
       </c>
       <c r="R56" s="21" t="n">
-        <f aca="false">IF(R13=0,0,(R40+R41+R42)/R13)</f>
-        <v>47.2826195030823</v>
+        <f aca="false">IF(R8=0,0,R21/IF(R7&gt;0,2,1))</f>
+        <v>37800</v>
       </c>
       <c r="S56" s="21" t="n">
-        <f aca="false">IF(S13=0,0,(S40+S41+S42)/S13)</f>
-        <v>46.5373121500501</v>
+        <f aca="false">IF(S8=0,0,S21/IF(S7&gt;0,2,1))</f>
+        <v>37800</v>
       </c>
       <c r="T56" s="21" t="n">
-        <f aca="false">IF(T13=0,0,(T40+T41+T42)/T13)</f>
-        <v>45.7725180189062</v>
+        <f aca="false">IF(T8=0,0,T21/IF(T7&gt;0,2,1))</f>
+        <v>37800</v>
       </c>
       <c r="U56" s="21" t="n">
-        <f aca="false">IF(U13=0,0,(U40+U41+U42)/U13)</f>
-        <v>44.9888111866158</v>
+        <f aca="false">IF(U8=0,0,U21/IF(U7&gt;0,2,1))</f>
+        <v>37800</v>
       </c>
       <c r="V56" s="21" t="n">
-        <f aca="false">IF(V13=0,0,(V40+V41+V42)/V13)</f>
-        <v>44.186860180576</v>
+        <f aca="false">IF(V8=0,0,V21/IF(V7&gt;0,2,1))</f>
+        <v>37800</v>
       </c>
       <c r="W56" s="21" t="n">
-        <f aca="false">IF(W13=0,0,(W40+W41+W42)/W13)</f>
-        <v>43.3674283051422</v>
+        <f aca="false">IF(W8=0,0,W21/IF(W7&gt;0,2,1))</f>
+        <v>37800</v>
       </c>
       <c r="X56" s="21" t="n">
-        <f aca="false">IF(X13=0,0,(X40+X41+X42)/X13)</f>
-        <v>42.5313730524876</v>
+        <f aca="false">IF(X8=0,0,X21/IF(X7&gt;0,2,1))</f>
+        <v>37800</v>
       </c>
       <c r="Y56" s="21" t="n">
-        <f aca="false">IF(Y13=0,0,(Y40+Y41+Y42)/Y13)</f>
-        <v>41.6796445469942</v>
+        <f aca="false">IF(Y8=0,0,Y21/IF(Y7&gt;0,2,1))</f>
+        <v>37800</v>
       </c>
       <c r="Z56" s="2"/>
       <c r="AA56" s="2"/>
@@ -7625,103 +7670,103 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="17" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B57" s="21" t="n">
-        <f aca="false">IF(B14=0,0,(B40+B41+B42)/B14)</f>
-        <v>149.272612270715</v>
+        <f aca="false">IF(B13=0,0,(B41+B42+B43)/B13)</f>
+        <v>56.4593301435407</v>
       </c>
       <c r="C57" s="21" t="n">
-        <f aca="false">IF(C14=0,0,(C40+C41+C42)/C14)</f>
-        <v>177.084839736856</v>
+        <f aca="false">IF(C13=0,0,(C41+C42+C43)/C13)</f>
+        <v>55.344889338647</v>
       </c>
       <c r="D57" s="21" t="n">
-        <f aca="false">IF(D14=0,0,(D40+D41+D42)/D14)</f>
-        <v>174.14288829155</v>
+        <f aca="false">IF(D13=0,0,(D41+D42+D43)/D13)</f>
+        <v>54.7030520538172</v>
       </c>
       <c r="E57" s="21" t="n">
-        <f aca="false">IF(E14=0,0,(E40+E41+E42)/E14)</f>
-        <v>171.129297018282</v>
+        <f aca="false">IF(E13=0,0,(E41+E42+E43)/E13)</f>
+        <v>54.0387606024687</v>
       </c>
       <c r="F57" s="21" t="n">
-        <f aca="false">IF(F14=0,0,(F40+F41+F42)/F14)</f>
-        <v>168.046715989101</v>
+        <f aca="false">IF(F13=0,0,(F41+F42+F43)/F13)</f>
+        <v>53.3520026498769</v>
       </c>
       <c r="G57" s="21" t="n">
-        <f aca="false">IF(G14=0,0,(G40+G41+G42)/G14)</f>
-        <v>164.898157229817</v>
+        <f aca="false">IF(G13=0,0,(G41+G42+G43)/G13)</f>
+        <v>52.64284380353</v>
       </c>
       <c r="H57" s="21" t="n">
-        <f aca="false">IF(H14=0,0,(H40+H41+H42)/H14)</f>
-        <v>174.034192953591</v>
+        <f aca="false">IF(H13=0,0,(H41+H42+H43)/H13)</f>
+        <v>53.6007390411201</v>
       </c>
       <c r="I57" s="21" t="n">
-        <f aca="false">IF(I14=0,0,(I40+I41+I42)/I14)</f>
-        <v>171.493981275161</v>
+        <f aca="false">IF(I13=0,0,(I41+I42+I43)/I13)</f>
+        <v>53.0627977874208</v>
       </c>
       <c r="J57" s="21" t="n">
-        <f aca="false">IF(J14=0,0,(J40+J41+J42)/J14)</f>
-        <v>168.881084818212</v>
+        <f aca="false">IF(J13=0,0,(J41+J42+J43)/J13)</f>
+        <v>52.5042448312122</v>
       </c>
       <c r="K57" s="21" t="n">
-        <f aca="false">IF(K14=0,0,(K40+K41+K42)/K14)</f>
-        <v>166.196962734354</v>
+        <f aca="false">IF(K13=0,0,(K41+K42+K43)/K13)</f>
+        <v>51.9248754514001</v>
       </c>
       <c r="L57" s="21" t="n">
-        <f aca="false">IF(L14=0,0,(L40+L41+L42)/L14)</f>
-        <v>163.44340291119</v>
+        <f aca="false">IF(L13=0,0,(L41+L42+L43)/L13)</f>
+        <v>51.3245426468748</v>
       </c>
       <c r="M57" s="21" t="n">
-        <f aca="false">IF(M14=0,0,(M40+M41+M42)/M14)</f>
-        <v>160.622528463055</v>
+        <f aca="false">IF(M13=0,0,(M41+M42+M43)/M13)</f>
+        <v>50.7031622847844</v>
       </c>
       <c r="N57" s="21" t="n">
-        <f aca="false">IF(N14=0,0,(N40+N41+N42)/N14)</f>
-        <v>157.736801374181</v>
+        <f aca="false">IF(N13=0,0,(N41+N42+N43)/N13)</f>
+        <v>50.0607181383268</v>
       </c>
       <c r="O57" s="21" t="n">
-        <f aca="false">IF(O14=0,0,(O40+O41+O42)/O14)</f>
-        <v>154.789023039554</v>
+        <f aca="false">IF(O13=0,0,(O41+O42+O43)/O13)</f>
+        <v>49.3972667391676</v>
       </c>
       <c r="P57" s="21" t="n">
-        <f aca="false">IF(P14=0,0,(P40+P41+P42)/P14)</f>
-        <v>151.782331485644</v>
+        <f aca="false">IF(P13=0,0,(P41+P42+P43)/P13)</f>
+        <v>48.712941964224</v>
       </c>
       <c r="Q57" s="21" t="n">
-        <f aca="false">IF(Q14=0,0,(Q40+Q41+Q42)/Q14)</f>
-        <v>148.720195098573</v>
+        <f aca="false">IF(Q13=0,0,(Q41+Q42+Q43)/Q13)</f>
+        <v>48.0079592722895</v>
       </c>
       <c r="R57" s="21" t="n">
-        <f aca="false">IF(R14=0,0,(R40+R41+R42)/R14)</f>
-        <v>145.606402740545</v>
+        <f aca="false">IF(R13=0,0,(R41+R42+R43)/R13)</f>
+        <v>47.2826195030823</v>
       </c>
       <c r="S57" s="21" t="n">
-        <f aca="false">IF(S14=0,0,(S40+S41+S42)/S14)</f>
-        <v>142.445050195582</v>
+        <f aca="false">IF(S13=0,0,(S41+S42+S43)/S13)</f>
+        <v>46.5373121500501</v>
       </c>
       <c r="T57" s="21" t="n">
-        <f aca="false">IF(T14=0,0,(T40+T41+T42)/T14)</f>
-        <v>139.24052295153</v>
+        <f aca="false">IF(T13=0,0,(T41+T42+T43)/T13)</f>
+        <v>45.7725180189062</v>
       </c>
       <c r="U57" s="21" t="n">
-        <f aca="false">IF(U14=0,0,(U40+U41+U42)/U14)</f>
-        <v>135.997475395339</v>
+        <f aca="false">IF(U13=0,0,(U41+U42+U43)/U13)</f>
+        <v>44.9888111866158</v>
       </c>
       <c r="V57" s="21" t="n">
-        <f aca="false">IF(V14=0,0,(V40+V41+V42)/V14)</f>
-        <v>132.720806570929</v>
+        <f aca="false">IF(V13=0,0,(V41+V42+V43)/V13)</f>
+        <v>44.186860180576</v>
       </c>
       <c r="W57" s="21" t="n">
-        <f aca="false">IF(W14=0,0,(W40+W41+W42)/W14)</f>
-        <v>129.41563272141</v>
+        <f aca="false">IF(W13=0,0,(W41+W42+W43)/W13)</f>
+        <v>43.3674283051422</v>
       </c>
       <c r="X57" s="21" t="n">
-        <f aca="false">IF(X14=0,0,(X40+X41+X42)/X14)</f>
-        <v>126.087256907851</v>
+        <f aca="false">IF(X13=0,0,(X41+X42+X43)/X13)</f>
+        <v>42.5313730524876</v>
       </c>
       <c r="Y57" s="21" t="n">
-        <f aca="false">IF(Y14=0,0,(Y40+Y41+Y42)/Y14)</f>
-        <v>122.741136062862</v>
+        <f aca="false">IF(Y13=0,0,(Y41+Y42+Y43)/Y13)</f>
+        <v>41.6796445469942</v>
       </c>
       <c r="Z57" s="2"/>
       <c r="AA57" s="2"/>
@@ -7729,103 +7774,103 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="B58" s="20" t="n">
-        <f aca="false">IF(B24=0,0,B23/B24)</f>
-        <v>0</v>
-      </c>
-      <c r="C58" s="20" t="n">
-        <f aca="false">IF(C24=0,0,C23/C24)</f>
-        <v>0</v>
-      </c>
-      <c r="D58" s="20" t="n">
-        <f aca="false">IF(D24=0,0,D23/D24)</f>
-        <v>0.00320103002560231</v>
-      </c>
-      <c r="E58" s="20" t="n">
-        <f aca="false">IF(E24=0,0,E23/E24)</f>
-        <v>0.00608736362658015</v>
-      </c>
-      <c r="F58" s="20" t="n">
-        <f aca="false">IF(F24=0,0,F23/F24)</f>
-        <v>0.00871532086881573</v>
-      </c>
-      <c r="G58" s="20" t="n">
-        <f aca="false">IF(G24=0,0,G23/G24)</f>
-        <v>0.0111283694735738</v>
-      </c>
-      <c r="H58" s="20" t="n">
-        <f aca="false">IF(H24=0,0,H23/H24)</f>
-        <v>0.00972851736553608</v>
-      </c>
-      <c r="I58" s="20" t="n">
-        <f aca="false">IF(I24=0,0,I23/I24)</f>
-        <v>0.011359820093268</v>
-      </c>
-      <c r="J58" s="20" t="n">
-        <f aca="false">IF(J24=0,0,J23/J24)</f>
-        <v>0.0128649758199608</v>
-      </c>
-      <c r="K58" s="20" t="n">
-        <f aca="false">IF(K24=0,0,K23/K24)</f>
-        <v>0.014271023995044</v>
-      </c>
-      <c r="L58" s="20" t="n">
-        <f aca="false">IF(L24=0,0,L23/L24)</f>
-        <v>0.0165920012567885</v>
-      </c>
-      <c r="M58" s="20" t="n">
-        <f aca="false">IF(M24=0,0,M23/M24)</f>
-        <v>0.0188867097908589</v>
-      </c>
-      <c r="N58" s="20" t="n">
-        <f aca="false">IF(N24=0,0,N23/N24)</f>
-        <v>0.0211555425791042</v>
-      </c>
-      <c r="O58" s="20" t="n">
-        <f aca="false">IF(O24=0,0,O23/O24)</f>
-        <v>0.0233988849351682</v>
-      </c>
-      <c r="P58" s="20" t="n">
-        <f aca="false">IF(P24=0,0,P23/P24)</f>
-        <v>0.0251282657222433</v>
-      </c>
-      <c r="Q58" s="20" t="n">
-        <f aca="false">IF(Q24=0,0,Q23/Q24)</f>
-        <v>0.0268400642336722</v>
-      </c>
-      <c r="R58" s="20" t="n">
-        <f aca="false">IF(R24=0,0,R23/R24)</f>
-        <v>0.0285345095313154</v>
-      </c>
-      <c r="S58" s="20" t="n">
-        <f aca="false">IF(S24=0,0,S23/S24)</f>
-        <v>0.030211826824897</v>
-      </c>
-      <c r="T58" s="20" t="n">
-        <f aca="false">IF(T24=0,0,T23/T24)</f>
-        <v>0.0318722375527298</v>
-      </c>
-      <c r="U58" s="20" t="n">
-        <f aca="false">IF(U24=0,0,U23/U24)</f>
-        <v>0.0335159594604163</v>
-      </c>
-      <c r="V58" s="20" t="n">
-        <f aca="false">IF(V24=0,0,V23/V24)</f>
-        <v>0.0351432066775832</v>
-      </c>
-      <c r="W58" s="20" t="n">
-        <f aca="false">IF(W24=0,0,W23/W24)</f>
-        <v>0.0367541897927081</v>
-      </c>
-      <c r="X58" s="20" t="n">
-        <f aca="false">IF(X24=0,0,X23/X24)</f>
-        <v>0.038349115926091</v>
-      </c>
-      <c r="Y58" s="20" t="n">
-        <f aca="false">IF(Y24=0,0,Y23/Y24)</f>
-        <v>0.0399281888010278</v>
+        <v>186</v>
+      </c>
+      <c r="B58" s="21" t="n">
+        <f aca="false">IF(B15=0,0,(B41+B42+B43)/B15)</f>
+        <v>148.717625559266</v>
+      </c>
+      <c r="C58" s="21" t="n">
+        <f aca="false">IF(C15=0,0,(C41+C42+C43)/C15)</f>
+        <v>171.042631782989</v>
+      </c>
+      <c r="D58" s="21" t="n">
+        <f aca="false">IF(D15=0,0,(D41+D42+D43)/D15)</f>
+        <v>168.266442075878</v>
+      </c>
+      <c r="E58" s="21" t="n">
+        <f aca="false">IF(E15=0,0,(E41+E42+E43)/E15)</f>
+        <v>165.420410404825</v>
+      </c>
+      <c r="F58" s="21" t="n">
+        <f aca="false">IF(F15=0,0,(F41+F42+F43)/F15)</f>
+        <v>162.506878156393</v>
+      </c>
+      <c r="G58" s="21" t="n">
+        <f aca="false">IF(G15=0,0,(G41+G42+G43)/G15)</f>
+        <v>159.528533362776</v>
+      </c>
+      <c r="H58" s="21" t="n">
+        <f aca="false">IF(H15=0,0,(H41+H42+H43)/H15)</f>
+        <v>167.906431756057</v>
+      </c>
+      <c r="I58" s="21" t="n">
+        <f aca="false">IF(I15=0,0,(I41+I42+I43)/I15)</f>
+        <v>165.514826168126</v>
+      </c>
+      <c r="J58" s="21" t="n">
+        <f aca="false">IF(J15=0,0,(J41+J42+J43)/J15)</f>
+        <v>163.053002778718</v>
+      </c>
+      <c r="K58" s="21" t="n">
+        <f aca="false">IF(K15=0,0,(K41+K42+K43)/K15)</f>
+        <v>160.522184756031</v>
+      </c>
+      <c r="L58" s="21" t="n">
+        <f aca="false">IF(L15=0,0,(L41+L42+L43)/L15)</f>
+        <v>157.923905310094</v>
+      </c>
+      <c r="M58" s="21" t="n">
+        <f aca="false">IF(M15=0,0,(M41+M42+M43)/M15)</f>
+        <v>155.260015321119</v>
+      </c>
+      <c r="N58" s="21" t="n">
+        <f aca="false">IF(N15=0,0,(N41+N42+N43)/N15)</f>
+        <v>152.532688392057</v>
+      </c>
+      <c r="O58" s="21" t="n">
+        <f aca="false">IF(O15=0,0,(O41+O42+O43)/O15)</f>
+        <v>149.744423065292</v>
+      </c>
+      <c r="P58" s="21" t="n">
+        <f aca="false">IF(P15=0,0,(P41+P42+P43)/P15)</f>
+        <v>146.898041974108</v>
+      </c>
+      <c r="Q58" s="21" t="n">
+        <f aca="false">IF(Q15=0,0,(Q41+Q42+Q43)/Q15)</f>
+        <v>143.99668773848</v>
+      </c>
+      <c r="R58" s="21" t="n">
+        <f aca="false">IF(R15=0,0,(R41+R42+R43)/R15)</f>
+        <v>141.043815461538</v>
+      </c>
+      <c r="S58" s="21" t="n">
+        <f aca="false">IF(S15=0,0,(S41+S42+S43)/S15)</f>
+        <v>138.043181737105</v>
+      </c>
+      <c r="T58" s="21" t="n">
+        <f aca="false">IF(T15=0,0,(T41+T42+T43)/T15)</f>
+        <v>134.998830138866</v>
+      </c>
+      <c r="U58" s="21" t="n">
+        <f aca="false">IF(U15=0,0,(U41+U42+U43)/U15)</f>
+        <v>131.915073226764</v>
+      </c>
+      <c r="V58" s="21" t="n">
+        <f aca="false">IF(V15=0,0,(V41+V42+V43)/V15)</f>
+        <v>128.796471174437</v>
+      </c>
+      <c r="W58" s="21" t="n">
+        <f aca="false">IF(W15=0,0,(W41+W42+W43)/W15)</f>
+        <v>125.647807191021</v>
+      </c>
+      <c r="X58" s="21" t="n">
+        <f aca="false">IF(X15=0,0,(X41+X42+X43)/X15)</f>
+        <v>122.474059979422</v>
+      </c>
+      <c r="Y58" s="21" t="n">
+        <f aca="false">IF(Y15=0,0,(Y41+Y42+Y43)/Y15)</f>
+        <v>119.280373539014</v>
       </c>
       <c r="Z58" s="2"/>
       <c r="AA58" s="2"/>
@@ -7833,107 +7878,315 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="17" t="s">
-        <v>184</v>
-      </c>
-      <c r="B59" s="18" t="n">
-        <f aca="false">B45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>550.595238095238</v>
-      </c>
-      <c r="C59" s="18" t="n">
-        <f aca="false">C45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>580.357142857143</v>
-      </c>
-      <c r="D59" s="18" t="n">
-        <f aca="false">D45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>580.357142857143</v>
-      </c>
-      <c r="E59" s="18" t="n">
-        <f aca="false">E45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>580.357142857143</v>
-      </c>
-      <c r="F59" s="18" t="n">
-        <f aca="false">F45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>580.357142857143</v>
-      </c>
-      <c r="G59" s="18" t="n">
-        <f aca="false">G45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>580.357142857143</v>
-      </c>
-      <c r="H59" s="18" t="n">
-        <f aca="false">H45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>1073.34511662424</v>
-      </c>
-      <c r="I59" s="18" t="n">
-        <f aca="false">I45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>850.130830909956</v>
-      </c>
-      <c r="J59" s="18" t="n">
-        <f aca="false">J45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>850.130830909956</v>
-      </c>
-      <c r="K59" s="18" t="n">
-        <f aca="false">K45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>739.088579319446</v>
-      </c>
-      <c r="L59" s="18" t="n">
-        <f aca="false">L45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>739.088579319446</v>
-      </c>
-      <c r="M59" s="18" t="n">
-        <f aca="false">M45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>739.088579319446</v>
-      </c>
-      <c r="N59" s="18" t="n">
-        <f aca="false">N45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>739.088579319446</v>
-      </c>
-      <c r="O59" s="18" t="n">
-        <f aca="false">O45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>739.088579319446</v>
-      </c>
-      <c r="P59" s="18" t="n">
-        <f aca="false">P45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>739.088579319446</v>
-      </c>
-      <c r="Q59" s="18" t="n">
-        <f aca="false">Q45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>739.088579319446</v>
-      </c>
-      <c r="R59" s="18" t="n">
-        <f aca="false">R45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>739.088579319446</v>
-      </c>
-      <c r="S59" s="18" t="n">
-        <f aca="false">S45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>739.088579319446</v>
-      </c>
-      <c r="T59" s="18" t="n">
-        <f aca="false">T45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>739.088579319446</v>
-      </c>
-      <c r="U59" s="18" t="n">
-        <f aca="false">U45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>739.088579319446</v>
-      </c>
-      <c r="V59" s="18" t="n">
-        <f aca="false">V45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>739.088579319446</v>
-      </c>
-      <c r="W59" s="18" t="n">
-        <f aca="false">W45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>739.088579319446</v>
-      </c>
-      <c r="X59" s="18" t="n">
-        <f aca="false">X45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>739.088579319446</v>
-      </c>
-      <c r="Y59" s="18" t="n">
-        <f aca="false">Y45/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
-        <v>739.088579319446</v>
+        <v>187</v>
+      </c>
+      <c r="B59" s="20" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>0.7</v>
+      </c>
+      <c r="C59" s="20" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>0.7</v>
+      </c>
+      <c r="D59" s="20" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>0.7</v>
+      </c>
+      <c r="E59" s="20" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>0.7</v>
+      </c>
+      <c r="F59" s="20" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>0.7</v>
+      </c>
+      <c r="G59" s="20" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>0.7</v>
+      </c>
+      <c r="H59" s="20" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>0.7</v>
+      </c>
+      <c r="I59" s="20" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>0.7</v>
+      </c>
+      <c r="J59" s="20" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>0.7</v>
+      </c>
+      <c r="K59" s="20" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>0.7</v>
+      </c>
+      <c r="L59" s="20" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>0.7</v>
+      </c>
+      <c r="M59" s="20" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>0.7</v>
+      </c>
+      <c r="N59" s="20" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>0.7</v>
+      </c>
+      <c r="O59" s="20" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>0.7</v>
+      </c>
+      <c r="P59" s="20" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>0.7</v>
+      </c>
+      <c r="Q59" s="20" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>0.7</v>
+      </c>
+      <c r="R59" s="20" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>0.7</v>
+      </c>
+      <c r="S59" s="20" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>0.7</v>
+      </c>
+      <c r="T59" s="20" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>0.7</v>
+      </c>
+      <c r="U59" s="20" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>0.7</v>
+      </c>
+      <c r="V59" s="20" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>0.7</v>
+      </c>
+      <c r="W59" s="20" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>0.7</v>
+      </c>
+      <c r="X59" s="20" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>0.7</v>
+      </c>
+      <c r="Y59" s="20" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>0.7</v>
       </c>
       <c r="Z59" s="2"/>
       <c r="AA59" s="2"/>
       <c r="AB59" s="2"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="B60" s="20" t="n">
+        <f aca="false">IF(B25=0,0,B24/B25)</f>
+        <v>0</v>
+      </c>
+      <c r="C60" s="20" t="n">
+        <f aca="false">IF(C25=0,0,C24/C25)</f>
+        <v>0</v>
+      </c>
+      <c r="D60" s="20" t="n">
+        <f aca="false">IF(D25=0,0,D24/D25)</f>
+        <v>0.00320103002560231</v>
+      </c>
+      <c r="E60" s="20" t="n">
+        <f aca="false">IF(E25=0,0,E24/E25)</f>
+        <v>0.00608736362658015</v>
+      </c>
+      <c r="F60" s="20" t="n">
+        <f aca="false">IF(F25=0,0,F24/F25)</f>
+        <v>0.00871532086881573</v>
+      </c>
+      <c r="G60" s="20" t="n">
+        <f aca="false">IF(G25=0,0,G24/G25)</f>
+        <v>0.0111283694735738</v>
+      </c>
+      <c r="H60" s="20" t="n">
+        <f aca="false">IF(H25=0,0,H24/H25)</f>
+        <v>0.00972851736553608</v>
+      </c>
+      <c r="I60" s="20" t="n">
+        <f aca="false">IF(I25=0,0,I24/I25)</f>
+        <v>0.011359820093268</v>
+      </c>
+      <c r="J60" s="20" t="n">
+        <f aca="false">IF(J25=0,0,J24/J25)</f>
+        <v>0.0128649758199608</v>
+      </c>
+      <c r="K60" s="20" t="n">
+        <f aca="false">IF(K25=0,0,K24/K25)</f>
+        <v>0.014271023995044</v>
+      </c>
+      <c r="L60" s="20" t="n">
+        <f aca="false">IF(L25=0,0,L24/L25)</f>
+        <v>0.0165920012567885</v>
+      </c>
+      <c r="M60" s="20" t="n">
+        <f aca="false">IF(M25=0,0,M24/M25)</f>
+        <v>0.0188867097908589</v>
+      </c>
+      <c r="N60" s="20" t="n">
+        <f aca="false">IF(N25=0,0,N24/N25)</f>
+        <v>0.0211555425791042</v>
+      </c>
+      <c r="O60" s="20" t="n">
+        <f aca="false">IF(O25=0,0,O24/O25)</f>
+        <v>0.0233988849351682</v>
+      </c>
+      <c r="P60" s="20" t="n">
+        <f aca="false">IF(P25=0,0,P24/P25)</f>
+        <v>0.0251282657222433</v>
+      </c>
+      <c r="Q60" s="20" t="n">
+        <f aca="false">IF(Q25=0,0,Q24/Q25)</f>
+        <v>0.0268400642336722</v>
+      </c>
+      <c r="R60" s="20" t="n">
+        <f aca="false">IF(R25=0,0,R24/R25)</f>
+        <v>0.0285345095313154</v>
+      </c>
+      <c r="S60" s="20" t="n">
+        <f aca="false">IF(S25=0,0,S24/S25)</f>
+        <v>0.030211826824897</v>
+      </c>
+      <c r="T60" s="20" t="n">
+        <f aca="false">IF(T25=0,0,T24/T25)</f>
+        <v>0.0318722375527298</v>
+      </c>
+      <c r="U60" s="20" t="n">
+        <f aca="false">IF(U25=0,0,U24/U25)</f>
+        <v>0.0335159594604163</v>
+      </c>
+      <c r="V60" s="20" t="n">
+        <f aca="false">IF(V25=0,0,V24/V25)</f>
+        <v>0.0351432066775832</v>
+      </c>
+      <c r="W60" s="20" t="n">
+        <f aca="false">IF(W25=0,0,W24/W25)</f>
+        <v>0.0367541897927081</v>
+      </c>
+      <c r="X60" s="20" t="n">
+        <f aca="false">IF(X25=0,0,X24/X25)</f>
+        <v>0.038349115926091</v>
+      </c>
+      <c r="Y60" s="20" t="n">
+        <f aca="false">IF(Y25=0,0,Y24/Y25)</f>
+        <v>0.0399281888010278</v>
+      </c>
+      <c r="Z60" s="2"/>
+      <c r="AA60" s="2"/>
+      <c r="AB60" s="2"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="B61" s="18" t="n">
+        <f aca="false">B46/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
+        <v>550.595238095238</v>
+      </c>
+      <c r="C61" s="18" t="n">
+        <f aca="false">C46/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
+        <v>580.357142857143</v>
+      </c>
+      <c r="D61" s="18" t="n">
+        <f aca="false">D46/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
+        <v>580.357142857143</v>
+      </c>
+      <c r="E61" s="18" t="n">
+        <f aca="false">E46/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
+        <v>580.357142857143</v>
+      </c>
+      <c r="F61" s="18" t="n">
+        <f aca="false">F46/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
+        <v>580.357142857143</v>
+      </c>
+      <c r="G61" s="18" t="n">
+        <f aca="false">G46/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
+        <v>580.357142857143</v>
+      </c>
+      <c r="H61" s="18" t="n">
+        <f aca="false">H46/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
+        <v>1073.34511662424</v>
+      </c>
+      <c r="I61" s="18" t="n">
+        <f aca="false">I46/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
+        <v>850.130830909956</v>
+      </c>
+      <c r="J61" s="18" t="n">
+        <f aca="false">J46/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
+        <v>850.130830909956</v>
+      </c>
+      <c r="K61" s="18" t="n">
+        <f aca="false">K46/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
+        <v>739.088579319446</v>
+      </c>
+      <c r="L61" s="18" t="n">
+        <f aca="false">L46/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
+        <v>739.088579319446</v>
+      </c>
+      <c r="M61" s="18" t="n">
+        <f aca="false">M46/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
+        <v>739.088579319446</v>
+      </c>
+      <c r="N61" s="18" t="n">
+        <f aca="false">N46/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
+        <v>739.088579319446</v>
+      </c>
+      <c r="O61" s="18" t="n">
+        <f aca="false">O46/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
+        <v>739.088579319446</v>
+      </c>
+      <c r="P61" s="18" t="n">
+        <f aca="false">P46/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
+        <v>739.088579319446</v>
+      </c>
+      <c r="Q61" s="18" t="n">
+        <f aca="false">Q46/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
+        <v>739.088579319446</v>
+      </c>
+      <c r="R61" s="18" t="n">
+        <f aca="false">R46/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
+        <v>739.088579319446</v>
+      </c>
+      <c r="S61" s="18" t="n">
+        <f aca="false">S46/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
+        <v>739.088579319446</v>
+      </c>
+      <c r="T61" s="18" t="n">
+        <f aca="false">T46/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
+        <v>739.088579319446</v>
+      </c>
+      <c r="U61" s="18" t="n">
+        <f aca="false">U46/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
+        <v>739.088579319446</v>
+      </c>
+      <c r="V61" s="18" t="n">
+        <f aca="false">V46/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
+        <v>739.088579319446</v>
+      </c>
+      <c r="W61" s="18" t="n">
+        <f aca="false">W46/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
+        <v>739.088579319446</v>
+      </c>
+      <c r="X61" s="18" t="n">
+        <f aca="false">X46/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
+        <v>739.088579319446</v>
+      </c>
+      <c r="Y61" s="18" t="n">
+        <f aca="false">Y46/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
+        <v>739.088579319446</v>
+      </c>
+      <c r="Z61" s="2"/>
+      <c r="AA61" s="2"/>
+      <c r="AB61" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -7961,21 +8214,21 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B3" s="24" t="n">
         <f aca="false">Assumptions!$B$11</f>
@@ -7985,7 +8238,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B4" s="25" t="n">
         <f aca="false">B3*Assumptions!$B$5</f>
@@ -7995,7 +8248,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B5" s="25" t="n">
         <f aca="false">B4*Assumptions!$B$14</f>
@@ -8005,7 +8258,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B6" s="25" t="n">
         <f aca="false">B4*Assumptions!$B$15</f>
@@ -8015,7 +8268,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B7" s="21" t="n">
         <f aca="false">B4-B5-B6</f>
@@ -8025,7 +8278,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B8" s="20" t="n">
         <f aca="false">B7/B4</f>
@@ -8035,7 +8288,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B9" s="26" t="n">
         <f aca="false">B3/(Assumptions!$B$7/21)</f>
@@ -8045,14 +8298,14 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B11" s="24" t="n">
         <f aca="false">Assumptions!$B$7</f>
@@ -8062,7 +8315,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B12" s="25" t="n">
         <f aca="false">B11*Assumptions!$B$5</f>
@@ -8072,7 +8325,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B13" s="25" t="n">
         <f aca="false">Assumptions!$B$18*Assumptions!$B$19*Assumptions!$B$16</f>
@@ -8082,7 +8335,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B14" s="25" t="n">
         <f aca="false">B13*(1+Assumptions!$B$17)</f>
@@ -8092,19 +8345,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B15" s="20" t="n">
         <f aca="false">B14/B12</f>
         <v>0.352178571428572</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B16" s="25" t="n">
         <f aca="false">B12*(1-Assumptions!$B$14-Assumptions!$B$15)</f>
@@ -8114,14 +8367,14 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B18" s="25" t="n">
         <f aca="false">Assumptions!$B$21</f>
@@ -8131,7 +8384,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B19" s="25" t="n">
         <f aca="false">Assumptions!$B$27</f>
@@ -8141,7 +8394,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B20" s="21" t="n">
         <f aca="false">B18-B19</f>
@@ -8151,7 +8404,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B21" s="20" t="n">
         <f aca="false">B20/B18</f>
@@ -8161,7 +8414,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B22" s="24" t="n">
         <f aca="false">5/Assumptions!$B$22</f>
@@ -8171,7 +8424,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B23" s="21" t="n">
         <f aca="false">B20*B22</f>
@@ -8181,36 +8434,36 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B24" s="21" t="n">
         <f aca="false">0.25*B4*(1-0.52)</f>
         <v>504</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B26" s="25" t="n">
-        <f aca="false">'Proforma 24 mo'!D45</f>
+        <f aca="false">'Proforma 24 mo'!D46</f>
         <v>11700</v>
       </c>
       <c r="C26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B27" s="24" t="n">
         <f aca="false">B26/(Assumptions!$B$5*(1-Assumptions!$B$14-Assumptions!$B$15))</f>
@@ -8220,7 +8473,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B28" s="27" t="n">
         <f aca="false">B27/Assumptions!$B$7</f>
@@ -8253,7 +8506,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8261,7 +8514,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8276,18 +8529,18 @@
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="28"/>
       <c r="B4" s="28" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B5" s="8" t="n">
         <v>700</v>
@@ -8301,7 +8554,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B6" s="8" t="n">
         <v>1</v>
@@ -8315,7 +8568,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B7" s="14" t="n">
         <v>38</v>
@@ -8329,7 +8582,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B8" s="8" t="n">
         <v>40</v>
@@ -8343,7 +8596,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B9" s="21" t="n">
         <f aca="false">B5*B6*B7</f>
@@ -8360,7 +8613,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B10" s="21" t="n">
         <f aca="false">B8/12/Assumptions!$B$22*Assumptions!$B$21</f>
@@ -8377,7 +8630,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B11" s="21" t="n">
         <f aca="false">B9+B10</f>
@@ -8394,7 +8647,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B12" s="23" t="n">
         <f aca="false">B9*(1-Assumptions!$B$14-Assumptions!$B$15)+B10*(1-Assumptions!$B$27/Assumptions!$B$21)</f>
@@ -8411,24 +8664,24 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B13" s="21" t="n">
-        <f aca="false">IF(B6=1,'Proforma 24 mo'!D45,'Proforma 24 mo'!Y45)</f>
+        <f aca="false">IF(B6=1,'Proforma 24 mo'!D46,'Proforma 24 mo'!Y46)</f>
         <v>11700</v>
       </c>
       <c r="C13" s="21" t="n">
-        <f aca="false">IF(C6=1,'Proforma 24 mo'!D45,'Proforma 24 mo'!Y45)</f>
+        <f aca="false">IF(C6=1,'Proforma 24 mo'!D46,'Proforma 24 mo'!Y46)</f>
         <v>14900.02575908</v>
       </c>
       <c r="D13" s="21" t="n">
-        <f aca="false">IF(D6=1,'Proforma 24 mo'!D45,'Proforma 24 mo'!Y45)</f>
+        <f aca="false">IF(D6=1,'Proforma 24 mo'!D46,'Proforma 24 mo'!Y46)</f>
         <v>14900.02575908</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B14" s="23" t="n">
         <f aca="false">B12-B13</f>
@@ -8445,7 +8698,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B15" s="23" t="n">
         <f aca="false">B14*12</f>
@@ -8462,7 +8715,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B16" s="20" t="n">
         <f aca="false">IF(B11=0,0,B14/B11)</f>
@@ -8479,30 +8732,41 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B17" s="18" t="n">
-        <f aca="false">B5*B6/Assumptions!$B$11/0.3</f>
-        <v>23.3333333333333</v>
+        <f aca="false">B5*B6/Assumptions!$B$11/Assumptions!$B$44</f>
+        <v>10</v>
       </c>
       <c r="C17" s="18" t="n">
-        <f aca="false">C5*C6/Assumptions!$B$11/0.3</f>
-        <v>60</v>
+        <f aca="false">C5*C6/Assumptions!$B$11/Assumptions!$B$44</f>
+        <v>25.7142857142857</v>
       </c>
       <c r="D17" s="18" t="n">
-        <f aca="false">D5*D6/Assumptions!$B$11/0.3</f>
-        <v>66.6666666666667</v>
+        <f aca="false">D5*D6/Assumptions!$B$11/Assumptions!$B$44</f>
+        <v>28.5714285714286</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
+      <c r="A18" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B18" s="18" t="n">
+        <f aca="false">B17/0.45</f>
+        <v>22.2222222222222</v>
+      </c>
+      <c r="C18" s="18" t="n">
+        <f aca="false">C17/0.45</f>
+        <v>57.1428571428571</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <f aca="false">D17/0.45</f>
+        <v>63.4920634920635</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="29" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -8510,7 +8774,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -8518,7 +8782,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -8526,7 +8790,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -8557,7 +8821,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8571,7 +8835,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8597,50 +8861,50 @@
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="30" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F4" s="30" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="G4" s="30" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="H4" s="30" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="I4" s="30" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="J4" s="30" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B5" s="25" t="n">
-        <f aca="false">Assumptions!$B$54</f>
+        <f aca="false">Assumptions!$B$56</f>
         <v>50000</v>
       </c>
       <c r="C5" s="25" t="n">
-        <f aca="false">Assumptions!$B$55</f>
+        <f aca="false">Assumptions!$B$57</f>
         <v>2000</v>
       </c>
       <c r="D5" s="24" t="n">
-        <f aca="false">Assumptions!$B$56</f>
+        <f aca="false">Assumptions!$B$58</f>
         <v>3</v>
       </c>
       <c r="E5" s="21" t="n">
@@ -8652,15 +8916,15 @@
         <v>10</v>
       </c>
       <c r="G5" s="21" t="n">
-        <f aca="false">B5*(1-Assumptions!$B$69)</f>
+        <f aca="false">B5*(1-Assumptions!$B$71)</f>
         <v>10000</v>
       </c>
       <c r="H5" s="21" t="n">
-        <f aca="false">-PMT(Assumptions!$B$70/12,Assumptions!$B$71,B5*Assumptions!$B$69)</f>
+        <f aca="false">-PMT(Assumptions!$B$72/12,Assumptions!$B$73,B5*Assumptions!$B$71)</f>
         <v>830.33420905416</v>
       </c>
       <c r="I5" s="18" t="n">
-        <f aca="false">F5+Assumptions!$B$71</f>
+        <f aca="false">F5+Assumptions!$B$73</f>
         <v>70</v>
       </c>
       <c r="J5" s="18" t="n">
@@ -8670,18 +8934,18 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B6" s="25" t="n">
-        <f aca="false">Assumptions!$B$57</f>
+        <f aca="false">Assumptions!$B$59</f>
         <v>38000</v>
       </c>
       <c r="C6" s="25" t="n">
-        <f aca="false">Assumptions!$B$58</f>
+        <f aca="false">Assumptions!$B$60</f>
         <v>1700</v>
       </c>
       <c r="D6" s="24" t="n">
-        <f aca="false">Assumptions!$B$59</f>
+        <f aca="false">Assumptions!$B$61</f>
         <v>3</v>
       </c>
       <c r="E6" s="21" t="n">
@@ -8693,15 +8957,15 @@
         <v>10</v>
       </c>
       <c r="G6" s="21" t="n">
-        <f aca="false">B6*(1-Assumptions!$B$69)</f>
+        <f aca="false">B6*(1-Assumptions!$B$71)</f>
         <v>7600</v>
       </c>
       <c r="H6" s="21" t="n">
-        <f aca="false">-PMT(Assumptions!$B$70/12,Assumptions!$B$71,B6*Assumptions!$B$69)</f>
+        <f aca="false">-PMT(Assumptions!$B$72/12,Assumptions!$B$73,B6*Assumptions!$B$71)</f>
         <v>631.053998881162</v>
       </c>
       <c r="I6" s="18" t="n">
-        <f aca="false">F6+Assumptions!$B$71</f>
+        <f aca="false">F6+Assumptions!$B$73</f>
         <v>70</v>
       </c>
       <c r="J6" s="18" t="n">
@@ -8711,18 +8975,18 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B7" s="25" t="n">
-        <f aca="false">Assumptions!$B$60</f>
+        <f aca="false">Assumptions!$B$62</f>
         <v>9500</v>
       </c>
       <c r="C7" s="25" t="n">
-        <f aca="false">Assumptions!$B$61</f>
+        <f aca="false">Assumptions!$B$63</f>
         <v>600</v>
       </c>
       <c r="D7" s="24" t="n">
-        <f aca="false">Assumptions!$B$62</f>
+        <f aca="false">Assumptions!$B$64</f>
         <v>0</v>
       </c>
       <c r="E7" s="21" t="n">
@@ -8734,15 +8998,15 @@
         <v>7</v>
       </c>
       <c r="G7" s="21" t="n">
-        <f aca="false">B7*(1-Assumptions!$B$69)</f>
+        <f aca="false">B7*(1-Assumptions!$B$71)</f>
         <v>1900</v>
       </c>
       <c r="H7" s="21" t="n">
-        <f aca="false">-PMT(Assumptions!$B$70/12,Assumptions!$B$71,B7*Assumptions!$B$69)</f>
+        <f aca="false">-PMT(Assumptions!$B$72/12,Assumptions!$B$73,B7*Assumptions!$B$71)</f>
         <v>157.76349972029</v>
       </c>
       <c r="I7" s="18" t="n">
-        <f aca="false">F7+Assumptions!$B$71</f>
+        <f aca="false">F7+Assumptions!$B$73</f>
         <v>67</v>
       </c>
       <c r="J7" s="18" t="n">
@@ -8752,18 +9016,18 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B8" s="25" t="n">
-        <f aca="false">Assumptions!$B$63</f>
+        <f aca="false">Assumptions!$B$65</f>
         <v>35000</v>
       </c>
       <c r="C8" s="25" t="n">
-        <f aca="false">Assumptions!$B$64</f>
+        <f aca="false">Assumptions!$B$66</f>
         <v>0</v>
       </c>
       <c r="D8" s="24" t="n">
-        <f aca="false">Assumptions!$B$65</f>
+        <f aca="false">Assumptions!$B$67</f>
         <v>0</v>
       </c>
       <c r="E8" s="21" t="n">
@@ -8775,15 +9039,15 @@
         <v>7</v>
       </c>
       <c r="G8" s="21" t="n">
-        <f aca="false">B8*(1-Assumptions!$B$69)</f>
+        <f aca="false">B8*(1-Assumptions!$B$71)</f>
         <v>7000</v>
       </c>
       <c r="H8" s="21" t="n">
-        <f aca="false">-PMT(Assumptions!$B$70/12,Assumptions!$B$71,B8*Assumptions!$B$69)</f>
+        <f aca="false">-PMT(Assumptions!$B$72/12,Assumptions!$B$73,B8*Assumptions!$B$71)</f>
         <v>581.233946337912</v>
       </c>
       <c r="I8" s="18" t="n">
-        <f aca="false">F8+Assumptions!$B$71</f>
+        <f aca="false">F8+Assumptions!$B$73</f>
         <v>67</v>
       </c>
       <c r="J8" s="18" t="str">
@@ -8793,18 +9057,18 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B9" s="25" t="n">
-        <f aca="false">Assumptions!$B$66</f>
+        <f aca="false">Assumptions!$B$68</f>
         <v>6000</v>
       </c>
       <c r="C9" s="25" t="n">
-        <f aca="false">Assumptions!$B$67</f>
+        <f aca="false">Assumptions!$B$69</f>
         <v>0</v>
       </c>
       <c r="D9" s="24" t="n">
-        <f aca="false">Assumptions!$B$68</f>
+        <f aca="false">Assumptions!$B$70</f>
         <v>0</v>
       </c>
       <c r="E9" s="21" t="n">
@@ -8816,15 +9080,15 @@
         <v>7</v>
       </c>
       <c r="G9" s="21" t="n">
-        <f aca="false">B9*(1-Assumptions!$B$69)</f>
+        <f aca="false">B9*(1-Assumptions!$B$71)</f>
         <v>1200</v>
       </c>
       <c r="H9" s="21" t="n">
-        <f aca="false">-PMT(Assumptions!$B$70/12,Assumptions!$B$71,B9*Assumptions!$B$69)</f>
+        <f aca="false">-PMT(Assumptions!$B$72/12,Assumptions!$B$73,B9*Assumptions!$B$71)</f>
         <v>99.6401050864993</v>
       </c>
       <c r="I9" s="18" t="n">
-        <f aca="false">F9+Assumptions!$B$71</f>
+        <f aca="false">F9+Assumptions!$B$73</f>
         <v>67</v>
       </c>
       <c r="J9" s="18" t="str">
@@ -8834,7 +9098,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B10" s="23" t="n">
         <f aca="false">SUM(B5:B9)</f>
@@ -8872,7 +9136,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="29" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -8886,7 +9150,7 @@
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="31" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B13" s="31"/>
       <c r="C13" s="31"/>
@@ -8900,7 +9164,7 @@
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="B14" s="31"/>
       <c r="C14" s="31"/>
@@ -8914,7 +9178,7 @@
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B15" s="31"/>
       <c r="C15" s="31"/>
@@ -8928,7 +9192,7 @@
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B16" s="31"/>
       <c r="C16" s="31"/>
@@ -8942,7 +9206,7 @@
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B17" s="31"/>
       <c r="C17" s="31"/>
@@ -8986,7 +9250,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B1" s="2"/>
     </row>
@@ -8996,98 +9260,98 @@
     </row>
     <row r="3" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="32" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="32" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="32" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="32" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="32" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="32" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="32" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="32" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="32" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="32" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Scag-Scapes-Proforma.xlsx
+++ b/docs/Scag-Scapes-Proforma.xlsx
@@ -13,7 +13,8 @@
     <sheet name="Unit economics" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Scenarios" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Equipment plan" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Sources &amp; notes" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="5-year plan" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Sources &amp; notes" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="395">
   <si>
     <t xml:space="preserve">Scag Scapes LLC - Growth Proforma - Assumptions</t>
   </si>
@@ -915,6 +916,222 @@
     <t xml:space="preserve">Time to full ownership of Crew 2's set: trailer, truck and tools on day one; mini-ex and skid steer bought in month start+3; all loans paid off 60 months after that (month 70 in the base case). Equity builds from the first payment; the machines outlast the loans.</t>
   </si>
   <si>
+    <t xml:space="preserve">Five-year plan - annual, safe-scaling (Year 1-2 pull from the 24-month proforma; Years 3-5 from the blue inputs below)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blue = input. Every year is gated: the next crew is added only when the previous one has run at target for 3 months, backlog &gt; 4 weeks, and cash &gt; 2 months of overhead.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today (run rate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPACITY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crews at year end</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crew 3 in year 3, Crew 4 in year 4, then consolidate. Change to test a slower or faster path.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average crews running during the year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crew 3 starts mid-year 3; Crew 4 mid-year 4.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LF per crew per year at target x utilization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today = 400 LF x 12. Years 3-5: 900 LF x 12 x 95% utilization.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total LF installed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average $/LF (3% a year after year 2 - reviews and the map justify it)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drainage + other install revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Years 1-2 include other-work days; years 3-5 crews are full on drainage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drain Check active plans at year end</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40% attach on installs plus past customers; ~8%/yr churn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drain Check revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crew labor (crews x fixed crew cost; wages +3%/yr from year 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change the wage on Assumptions and every year moves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drain Check visit costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OVERHEAD - the layers that let the company handle the volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charlie's pay rises with the company.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office admin / bookkeeper (part-time year 2, full-time year 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Answers the phone the software cannot, books, AP/AR, reviews, scheduling. Hire when two crews are running.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations manager (runs crews, purchasing, quality)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hired in month 4 of year 3 (about $65K/yr), before Crew 3 starts, so Charlie is not the bottleneck at three crews. Usually the best crew lead, promoted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimator / sales (runs Moasure surveys and quotes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At four crews Charlie cannot run 40+ estimates a month alone. Base + commission.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crew-lead bonus pool (LF/day and callbacks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$500/quarter per lead when the crew beats 43 LF/day with no callbacks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insurance - GL, auto, equipment, WC excess (per crew)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today's premium plus about $9K per additional crew (auto, equipment, WC); get quotes before each hire.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Truck + equipment loan payments (existing + one set per crew)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each new crew carries its own set (Equipment plan tab); rent-first 3 months before each purchase.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yard / shop (Cottondale: 2,500 sq ft yr 2, 3,000 sq ft yr 3, 4,000 sq ft yr 4+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Introductory $0.85 then $1.05/sq ft; more footage as crews and bins are added.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software, phones, hosting, payment fees (+ per crew)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bookkeeping / CPA / payroll service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuickBooks Online + payroll service + monthly close; CPA quarterly. Grows with headcount.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing (Google LSA, Meta, content) - ~5% of revenue from year 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Falls as a % of revenue as reviews, referrals and the plan book compound.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shop, tools, uniforms, training, misc (+ per crew)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crew hiring, training and rent-first equipment months (per new crew)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GROWTH &amp; OPERATIONS LEAD (Ned) - proposed, for discussion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base ($/yr) - fractional, about 25 hours a week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For scale: Baton Rouge general/operations managers average $129,840 full-time (BLS OEWS). Set to 0 to see the plan without it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Growth share - % of operating profit above the baseline year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paid only on profit above what the business makes today; nothing on the baseline.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline operating profit (today's run rate after owner draw, floored at 0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today's column, computed below. The share is earned only on profit the growth creates.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Growth lead cost (base + share)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share is computed on operating profit before the share itself.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL OVERHEAD (excl. growth lead)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating profit before growth lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPERATING PROFIT after growth lead (owner draw already deducted)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CASH AND SAFETY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equipment down payments (20% per new crew set)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash at year end (opening + profit - down payments)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Before distributions beyond the owner draw and before income tax.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserve rule: 2 months of overhead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash must stay above this before any hire or purchase.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserve met?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WHAT THE COMPANY IS WORTH (indicative)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seller's discretionary earnings (operating profit + owner draw)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDE multiple (BizBuySell landscaping median 2021-25: 2.46x)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recurring Drain Check revenue, documented systems and a manager who is not the owner all push toward the top of the range.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicative enterprise value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross-check: revenue x 0.70 (BizBuySell). Not a promise; a benchmark.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sources and notes</t>
   </si>
   <si>
@@ -964,6 +1181,12 @@
   </si>
   <si>
     <t xml:space="preserve">Population ~35,700; median home value ~$411-423K; 56% owner-occupied; large 1970-1989 housing stock (original drainage aging out). https://www.city-data.com/zips/70808.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BizBuySell - Landscaping &amp; Yard Service valuation benchmarks (945 sold businesses, 2021-2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median sale price $425,000; median revenue $708,412; median SDE $187,761; revenue multiple 0.70x; SDE multiple 2.46x. https://www.bizbuysell.com/learning-center/valuation-benchmarks/landscaping-yard-service/</t>
   </si>
   <si>
     <t xml:space="preserve">BLS OEWS May 2023 - Baton Rouge MSA</t>
@@ -994,12 +1217,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="0.00"/>
+    <numFmt numFmtId="169" formatCode="@"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -1157,7 +1381,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1288,6 +1512,14 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -10334,7 +10566,1407 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:H53"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="60"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="29"/>
+      <c r="B4" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>299</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>300</v>
+      </c>
+      <c r="G4" s="29" t="s">
+        <v>301</v>
+      </c>
+      <c r="H4" s="29" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="17" t="s">
+        <v>304</v>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="17" t="s">
+        <v>306</v>
+      </c>
+      <c r="B7" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="21" t="n">
+        <f aca="false">(6*1+6*2)/12</f>
+        <v>1.5</v>
+      </c>
+      <c r="D7" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F7" s="33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G7" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>4800</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <f aca="false">'Proforma 24 mo'!Z17/C7</f>
+        <v>9266.66666666667</v>
+      </c>
+      <c r="D8" s="25" t="n">
+        <f aca="false">'Proforma 24 mo'!AA17/D7</f>
+        <v>10800</v>
+      </c>
+      <c r="E8" s="25" t="n">
+        <f aca="false">Assumptions!$B$11*12*0.95</f>
+        <v>10260</v>
+      </c>
+      <c r="F8" s="25" t="n">
+        <f aca="false">Assumptions!$B$11*12*0.95</f>
+        <v>10260</v>
+      </c>
+      <c r="G8" s="25" t="n">
+        <f aca="false">Assumptions!$B$11*12*0.95</f>
+        <v>10260</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="15" t="s">
+        <v>310</v>
+      </c>
+      <c r="B9" s="19" t="n">
+        <f aca="false">B7*B8</f>
+        <v>4800</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <f aca="false">'Proforma 24 mo'!Z17</f>
+        <v>13900</v>
+      </c>
+      <c r="D9" s="25" t="n">
+        <f aca="false">'Proforma 24 mo'!AA17</f>
+        <v>21600</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <f aca="false">E7*E8</f>
+        <v>25650</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <f aca="false">F7*F8</f>
+        <v>35910</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <f aca="false">G7*G8</f>
+        <v>41040</v>
+      </c>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="B11" s="26" t="n">
+        <f aca="false">Assumptions!$B$5</f>
+        <v>50</v>
+      </c>
+      <c r="C11" s="26" t="n">
+        <f aca="false">Assumptions!$B$5</f>
+        <v>50</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <f aca="false">Assumptions!$B$5</f>
+        <v>50</v>
+      </c>
+      <c r="E11" s="22" t="n">
+        <f aca="false">D11*1.03</f>
+        <v>51.5</v>
+      </c>
+      <c r="F11" s="22" t="n">
+        <f aca="false">E11*1.03</f>
+        <v>53.045</v>
+      </c>
+      <c r="G11" s="22" t="n">
+        <f aca="false">F11*1.03</f>
+        <v>54.63635</v>
+      </c>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="17" t="s">
+        <v>312</v>
+      </c>
+      <c r="B12" s="26" t="n">
+        <f aca="false">'Proforma 24 mo'!B25*12</f>
+        <v>380372.093023256</v>
+      </c>
+      <c r="C12" s="26" t="n">
+        <f aca="false">'Proforma 24 mo'!Z25</f>
+        <v>749744.186046512</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <f aca="false">'Proforma 24 mo'!AA25</f>
+        <v>1081674.41860465</v>
+      </c>
+      <c r="E12" s="22" t="n">
+        <f aca="false">E9*E11</f>
+        <v>1320975</v>
+      </c>
+      <c r="F12" s="22" t="n">
+        <f aca="false">F9*F11</f>
+        <v>1904845.95</v>
+      </c>
+      <c r="G12" s="22" t="n">
+        <f aca="false">G9*G11</f>
+        <v>2242275.804</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <f aca="false">'Proforma 24 mo'!M27</f>
+        <v>69.0010213081308</v>
+      </c>
+      <c r="D13" s="25" t="n">
+        <f aca="false">'Proforma 24 mo'!Y27</f>
+        <v>150.475943667911</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>260</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>380</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>480</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="17" t="s">
+        <v>316</v>
+      </c>
+      <c r="B14" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="26" t="n">
+        <f aca="false">'Proforma 24 mo'!Z28</f>
+        <v>6875.46737058665</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <f aca="false">'Proforma 24 mo'!AA28</f>
+        <v>28691.7837941484</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <f aca="false">(D13+E13)/2*Assumptions!$B$28</f>
+        <v>51104.254986655</v>
+      </c>
+      <c r="F14" s="26" t="n">
+        <f aca="false">(E13+F13)/2*Assumptions!$B$28*1.03</f>
+        <v>82070.4</v>
+      </c>
+      <c r="G14" s="26" t="n">
+        <f aca="false">(F13+G13)/2*Assumptions!$B$28*1.06</f>
+        <v>113494.2</v>
+      </c>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="B15" s="23" t="n">
+        <f aca="false">B12+B14</f>
+        <v>380372.093023256</v>
+      </c>
+      <c r="C15" s="23" t="n">
+        <f aca="false">C12+C14</f>
+        <v>756619.653417098</v>
+      </c>
+      <c r="D15" s="23" t="n">
+        <f aca="false">D12+D14</f>
+        <v>1110366.2023988</v>
+      </c>
+      <c r="E15" s="23" t="n">
+        <f aca="false">E12+E14</f>
+        <v>1372079.25498666</v>
+      </c>
+      <c r="F15" s="23" t="n">
+        <f aca="false">F12+F14</f>
+        <v>1986916.35</v>
+      </c>
+      <c r="G15" s="23" t="n">
+        <f aca="false">G12+G14</f>
+        <v>2355770.004</v>
+      </c>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="B17" s="26" t="n">
+        <f aca="false">B7*(Assumptions!$B$24*Assumptions!$B$25*Assumptions!$B$21+Assumptions!$B$25*Assumptions!$B$22)*(1+Assumptions!$B$23)*12</f>
+        <v>166848.12</v>
+      </c>
+      <c r="C17" s="26" t="n">
+        <f aca="false">'Proforma 24 mo'!Z32</f>
+        <v>250272.18</v>
+      </c>
+      <c r="D17" s="26" t="n">
+        <f aca="false">'Proforma 24 mo'!AA32</f>
+        <v>333696.24</v>
+      </c>
+      <c r="E17" s="26" t="n">
+        <f aca="false">E7*(Assumptions!$B$24*Assumptions!$B$25*Assumptions!$B$21+Assumptions!$B$25*Assumptions!$B$22)*(1+Assumptions!$B$23)*12*1.03</f>
+        <v>429633.909</v>
+      </c>
+      <c r="F17" s="26" t="n">
+        <f aca="false">F7*(Assumptions!$B$24*Assumptions!$B$25*Assumptions!$B$21+Assumptions!$B$25*Assumptions!$B$22)*(1+Assumptions!$B$23)*12*1.03^2</f>
+        <v>619532.096778</v>
+      </c>
+      <c r="G17" s="26" t="n">
+        <f aca="false">G7*(Assumptions!$B$24*Assumptions!$B$25*Assumptions!$B$21+Assumptions!$B$25*Assumptions!$B$22)*(1+Assumptions!$B$23)*12*1.03^3</f>
+        <v>729277.78249296</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="B18" s="26" t="n">
+        <f aca="false">B12*Assumptions!$B$20</f>
+        <v>76074.4186046512</v>
+      </c>
+      <c r="C18" s="26" t="n">
+        <f aca="false">'Proforma 24 mo'!Z33</f>
+        <v>149948.837209302</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <f aca="false">'Proforma 24 mo'!AA33</f>
+        <v>216334.88372093</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <f aca="false">E12*Assumptions!$B$20</f>
+        <v>264195</v>
+      </c>
+      <c r="F18" s="26" t="n">
+        <f aca="false">F12*Assumptions!$B$20</f>
+        <v>380969.19</v>
+      </c>
+      <c r="G18" s="26" t="n">
+        <f aca="false">G12*Assumptions!$B$20</f>
+        <v>448455.1608</v>
+      </c>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="B19" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="26" t="n">
+        <f aca="false">'Proforma 24 mo'!Z34</f>
+        <v>1932.86231301633</v>
+      </c>
+      <c r="D19" s="26" t="n">
+        <f aca="false">'Proforma 24 mo'!AA34</f>
+        <v>8065.96331562404</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <f aca="false">E14/Assumptions!$B$28*Assumptions!$B$34</f>
+        <v>14366.6580283769</v>
+      </c>
+      <c r="F19" s="26" t="n">
+        <f aca="false">F14/Assumptions!$B$28/1.03*Assumptions!$B$34</f>
+        <v>22400</v>
+      </c>
+      <c r="G19" s="26" t="n">
+        <f aca="false">G14/Assumptions!$B$28/1.06*Assumptions!$B$34</f>
+        <v>30100</v>
+      </c>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="B20" s="23" t="n">
+        <f aca="false">B15-B17-B18-B19</f>
+        <v>137449.554418605</v>
+      </c>
+      <c r="C20" s="23" t="n">
+        <f aca="false">C15-C17-C18-C19</f>
+        <v>354465.77389478</v>
+      </c>
+      <c r="D20" s="23" t="n">
+        <f aca="false">D15-D17-D18-D19</f>
+        <v>552269.115362245</v>
+      </c>
+      <c r="E20" s="23" t="n">
+        <f aca="false">E15-E17-E18-E19</f>
+        <v>663883.687958278</v>
+      </c>
+      <c r="F20" s="23" t="n">
+        <f aca="false">F15-F17-F18-F19</f>
+        <v>964015.063222</v>
+      </c>
+      <c r="G20" s="23" t="n">
+        <f aca="false">G15-G17-G18-G19</f>
+        <v>1147937.06070704</v>
+      </c>
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="B21" s="20" t="n">
+        <f aca="false">IF(B15=0,0,B20/B15)</f>
+        <v>0.361355517241379</v>
+      </c>
+      <c r="C21" s="20" t="n">
+        <f aca="false">IF(C15=0,0,C20/C15)</f>
+        <v>0.468486077904422</v>
+      </c>
+      <c r="D21" s="20" t="n">
+        <f aca="false">IF(D15=0,0,D20/D15)</f>
+        <v>0.497375653337737</v>
+      </c>
+      <c r="E21" s="20" t="n">
+        <f aca="false">IF(E15=0,0,E20/E15)</f>
+        <v>0.483852288813109</v>
+      </c>
+      <c r="F21" s="20" t="n">
+        <f aca="false">IF(F15=0,0,F20/F15)</f>
+        <v>0.485181504104086</v>
+      </c>
+      <c r="G21" s="20" t="n">
+        <f aca="false">IF(G15=0,0,G20/G15)</f>
+        <v>0.487287408685012</v>
+      </c>
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="B23" s="26" t="n">
+        <f aca="false">Assumptions!$B$55*12</f>
+        <v>72000</v>
+      </c>
+      <c r="C23" s="26" t="n">
+        <f aca="false">Assumptions!$B$55*12</f>
+        <v>72000</v>
+      </c>
+      <c r="D23" s="26" t="n">
+        <f aca="false">Assumptions!$B$55*12</f>
+        <v>72000</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>84000</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>96000</v>
+      </c>
+      <c r="G23" s="9" t="n">
+        <v>108000</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="17" t="s">
+        <v>322</v>
+      </c>
+      <c r="B24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>48000</v>
+      </c>
+      <c r="G24" s="9" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="B25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>48750</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>70000</v>
+      </c>
+      <c r="G25" s="9" t="n">
+        <v>72000</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="B26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>55000</v>
+      </c>
+      <c r="G26" s="9" t="n">
+        <v>58000</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="B27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>18000</v>
+      </c>
+      <c r="G27" s="9" t="n">
+        <v>20000</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="17" t="s">
+        <v>330</v>
+      </c>
+      <c r="B28" s="26" t="n">
+        <f aca="false">Assumptions!$B$56*12</f>
+        <v>10800</v>
+      </c>
+      <c r="C28" s="26" t="n">
+        <f aca="false">'Proforma 24 mo'!Z40</f>
+        <v>10800</v>
+      </c>
+      <c r="D28" s="26" t="n">
+        <f aca="false">'Proforma 24 mo'!AA40</f>
+        <v>10800</v>
+      </c>
+      <c r="E28" s="26" t="n">
+        <f aca="false">Assumptions!$B$56*12+9000*(E6-1)</f>
+        <v>28800</v>
+      </c>
+      <c r="F28" s="26" t="n">
+        <f aca="false">Assumptions!$B$56*12+9000*(F6-1)</f>
+        <v>37800</v>
+      </c>
+      <c r="G28" s="26" t="n">
+        <f aca="false">Assumptions!$B$56*12+9000*(G6-1)</f>
+        <v>37800</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="B29" s="26" t="n">
+        <f aca="false">Assumptions!$B$57*12</f>
+        <v>21600</v>
+      </c>
+      <c r="C29" s="26" t="n">
+        <f aca="false">'Proforma 24 mo'!Z41+'Proforma 24 mo'!Z51</f>
+        <v>31015.9899306742</v>
+      </c>
+      <c r="D29" s="26" t="n">
+        <f aca="false">'Proforma 24 mo'!AA41+'Proforma 24 mo'!AA51</f>
+        <v>49200.3091089603</v>
+      </c>
+      <c r="E29" s="26" t="n">
+        <f aca="false">Assumptions!$B$57*12+'Equipment plan'!H10*12*(E6-1)</f>
+        <v>76800.6182179206</v>
+      </c>
+      <c r="F29" s="26" t="n">
+        <f aca="false">Assumptions!$B$57*12+'Equipment plan'!H10*12*(F6-1)</f>
+        <v>104400.927326881</v>
+      </c>
+      <c r="G29" s="26" t="n">
+        <f aca="false">Assumptions!$B$57*12+'Equipment plan'!H10*12*(G6-1)</f>
+        <v>104400.927326881</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="17" t="s">
+        <v>334</v>
+      </c>
+      <c r="B30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="26" t="n">
+        <f aca="false">Assumptions!$B$61*12</f>
+        <v>0</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>25500</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>37800</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>50400</v>
+      </c>
+      <c r="G30" s="9" t="n">
+        <v>52000</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="17" t="s">
+        <v>336</v>
+      </c>
+      <c r="B31" s="26" t="n">
+        <f aca="false">Assumptions!$B$58*12</f>
+        <v>4200</v>
+      </c>
+      <c r="C31" s="26" t="n">
+        <f aca="false">'Proforma 24 mo'!Z42</f>
+        <v>4200</v>
+      </c>
+      <c r="D31" s="26" t="n">
+        <f aca="false">'Proforma 24 mo'!AA42</f>
+        <v>4200</v>
+      </c>
+      <c r="E31" s="22" t="n">
+        <f aca="false">4200+1200*E6</f>
+        <v>7800</v>
+      </c>
+      <c r="F31" s="22" t="n">
+        <f aca="false">4200+1200*F6</f>
+        <v>9000</v>
+      </c>
+      <c r="G31" s="22" t="n">
+        <f aca="false">4200+1200*G6</f>
+        <v>9000</v>
+      </c>
+      <c r="H31" s="2"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="B32" s="26" t="n">
+        <f aca="false">Assumptions!$B$59*12</f>
+        <v>3000</v>
+      </c>
+      <c r="C32" s="26" t="n">
+        <f aca="false">'Proforma 24 mo'!Z43</f>
+        <v>3000</v>
+      </c>
+      <c r="D32" s="26" t="n">
+        <f aca="false">'Proforma 24 mo'!AA43</f>
+        <v>3000</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>7200</v>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G32" s="9" t="n">
+        <v>9600</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="17" t="s">
+        <v>339</v>
+      </c>
+      <c r="B33" s="26" t="n">
+        <f aca="false">(Assumptions!$B$41+Assumptions!$B$44+Assumptions!$B$53)*12</f>
+        <v>21600</v>
+      </c>
+      <c r="C33" s="26" t="n">
+        <f aca="false">'Proforma 24 mo'!Z47+'Proforma 24 mo'!Z48+'Proforma 24 mo'!Z49</f>
+        <v>26400</v>
+      </c>
+      <c r="D33" s="26" t="n">
+        <f aca="false">'Proforma 24 mo'!AA47+'Proforma 24 mo'!AA48+'Proforma 24 mo'!AA49</f>
+        <v>32400</v>
+      </c>
+      <c r="E33" s="22" t="n">
+        <f aca="false">E15*0.05</f>
+        <v>68603.9627493328</v>
+      </c>
+      <c r="F33" s="22" t="n">
+        <f aca="false">F15*0.05</f>
+        <v>99345.8175</v>
+      </c>
+      <c r="G33" s="22" t="n">
+        <f aca="false">G15*0.045</f>
+        <v>106009.65018</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B34" s="26" t="n">
+        <f aca="false">Assumptions!$B$60*12</f>
+        <v>7200</v>
+      </c>
+      <c r="C34" s="26" t="n">
+        <f aca="false">'Proforma 24 mo'!Z44</f>
+        <v>7200</v>
+      </c>
+      <c r="D34" s="26" t="n">
+        <f aca="false">'Proforma 24 mo'!AA44</f>
+        <v>7200</v>
+      </c>
+      <c r="E34" s="22" t="n">
+        <f aca="false">7200+3000*E6</f>
+        <v>16200</v>
+      </c>
+      <c r="F34" s="22" t="n">
+        <f aca="false">7200+3000*F6</f>
+        <v>19200</v>
+      </c>
+      <c r="G34" s="22" t="n">
+        <f aca="false">7200+3000*G6</f>
+        <v>19200</v>
+      </c>
+      <c r="H34" s="2"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="17" t="s">
+        <v>342</v>
+      </c>
+      <c r="B35" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="26" t="n">
+        <f aca="false">'Proforma 24 mo'!Z50</f>
+        <v>15600</v>
+      </c>
+      <c r="D35" s="26" t="n">
+        <f aca="false">'Proforma 24 mo'!AA50</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="26" t="n">
+        <f aca="false">(E6-D6)*('Equipment plan'!E10+Assumptions!$B$82)</f>
+        <v>15600</v>
+      </c>
+      <c r="F35" s="26" t="n">
+        <f aca="false">(F6-E6)*('Equipment plan'!E10+Assumptions!$B$82)</f>
+        <v>15600</v>
+      </c>
+      <c r="G35" s="26" t="n">
+        <f aca="false">(G6-F6)*('Equipment plan'!E10+Assumptions!$B$82)</f>
+        <v>0</v>
+      </c>
+      <c r="H35" s="2"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="B37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="9" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>66000</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>72000</v>
+      </c>
+      <c r="G37" s="9" t="n">
+        <v>72000</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="17" t="s">
+        <v>346</v>
+      </c>
+      <c r="B38" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D38" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E38" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G38" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="17" t="s">
+        <v>348</v>
+      </c>
+      <c r="B39" s="22" t="n">
+        <f aca="false">MAX(0,B43)</f>
+        <v>0</v>
+      </c>
+      <c r="C39" s="22" t="n">
+        <f aca="false">MAX(0,B43)</f>
+        <v>0</v>
+      </c>
+      <c r="D39" s="22" t="n">
+        <f aca="false">MAX(0,B43)</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="22" t="n">
+        <f aca="false">MAX(0,B43)</f>
+        <v>0</v>
+      </c>
+      <c r="F39" s="22" t="n">
+        <f aca="false">MAX(0,B43)</f>
+        <v>0</v>
+      </c>
+      <c r="G39" s="22" t="n">
+        <f aca="false">MAX(0,B43)</f>
+        <v>0</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="17" t="s">
+        <v>350</v>
+      </c>
+      <c r="B40" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="22" t="n">
+        <f aca="false">C37+C38*MAX(0,C42-C39)</f>
+        <v>78424.9783964105</v>
+      </c>
+      <c r="D40" s="22" t="n">
+        <f aca="false">D37+D38*MAX(0,D42-D39)</f>
+        <v>91796.8806253285</v>
+      </c>
+      <c r="E40" s="22" t="n">
+        <f aca="false">E37+E38*MAX(0,E42-E39)</f>
+        <v>87832.9106991025</v>
+      </c>
+      <c r="F40" s="22" t="n">
+        <f aca="false">F37+F38*MAX(0,F42-F39)</f>
+        <v>105226.831839512</v>
+      </c>
+      <c r="G40" s="22" t="n">
+        <f aca="false">G37+G38*MAX(0,G42-G39)</f>
+        <v>122192.648320016</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="B41" s="23" t="n">
+        <f aca="false">SUM(B23:B35)</f>
+        <v>140400</v>
+      </c>
+      <c r="C41" s="23" t="n">
+        <f aca="false">SUM(C23:C35)</f>
+        <v>170215.989930674</v>
+      </c>
+      <c r="D41" s="23" t="n">
+        <f aca="false">SUM(D23:D35)</f>
+        <v>234300.30910896</v>
+      </c>
+      <c r="E41" s="23" t="n">
+        <f aca="false">SUM(E23:E35)</f>
+        <v>445554.580967253</v>
+      </c>
+      <c r="F41" s="23" t="n">
+        <f aca="false">SUM(F23:F35)</f>
+        <v>631746.744826881</v>
+      </c>
+      <c r="G41" s="23" t="n">
+        <f aca="false">SUM(G23:G35)</f>
+        <v>646010.577506881</v>
+      </c>
+      <c r="H41" s="2"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="B42" s="23" t="n">
+        <f aca="false">B20-B41</f>
+        <v>-2950.44558139535</v>
+      </c>
+      <c r="C42" s="23" t="n">
+        <f aca="false">C20-C41</f>
+        <v>184249.783964105</v>
+      </c>
+      <c r="D42" s="23" t="n">
+        <f aca="false">D20-D41</f>
+        <v>317968.806253285</v>
+      </c>
+      <c r="E42" s="23" t="n">
+        <f aca="false">E20-E41</f>
+        <v>218329.106991025</v>
+      </c>
+      <c r="F42" s="23" t="n">
+        <f aca="false">F20-F41</f>
+        <v>332268.318395119</v>
+      </c>
+      <c r="G42" s="23" t="n">
+        <f aca="false">G20-G41</f>
+        <v>501926.483200159</v>
+      </c>
+      <c r="H42" s="2"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="B43" s="23" t="n">
+        <f aca="false">B42-B40</f>
+        <v>-2950.44558139535</v>
+      </c>
+      <c r="C43" s="23" t="n">
+        <f aca="false">C42-C40</f>
+        <v>105824.805567695</v>
+      </c>
+      <c r="D43" s="23" t="n">
+        <f aca="false">D42-D40</f>
+        <v>226171.925627957</v>
+      </c>
+      <c r="E43" s="23" t="n">
+        <f aca="false">E42-E40</f>
+        <v>130496.196291922</v>
+      </c>
+      <c r="F43" s="23" t="n">
+        <f aca="false">F42-F40</f>
+        <v>227041.486555607</v>
+      </c>
+      <c r="G43" s="23" t="n">
+        <f aca="false">G42-G40</f>
+        <v>379733.834880143</v>
+      </c>
+      <c r="H43" s="2"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="B44" s="20" t="n">
+        <f aca="false">IF(B15=0,0,B43/B15)</f>
+        <v>-0.00775673514306678</v>
+      </c>
+      <c r="C44" s="20" t="n">
+        <f aca="false">IF(C15=0,0,C43/C15)</f>
+        <v>0.139865261349955</v>
+      </c>
+      <c r="D44" s="20" t="n">
+        <f aca="false">IF(D15=0,0,D43/D15)</f>
+        <v>0.203691291340949</v>
+      </c>
+      <c r="E44" s="20" t="n">
+        <f aca="false">IF(E15=0,0,E43/E15)</f>
+        <v>0.0951083516623765</v>
+      </c>
+      <c r="F44" s="20" t="n">
+        <f aca="false">IF(F15=0,0,F43/F15)</f>
+        <v>0.114268266278853</v>
+      </c>
+      <c r="G44" s="20" t="n">
+        <f aca="false">IF(G15=0,0,G43/G15)</f>
+        <v>0.161193085163395</v>
+      </c>
+      <c r="H44" s="2"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="B46" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="26" t="n">
+        <f aca="false">'Proforma 24 mo'!Z58</f>
+        <v>27700</v>
+      </c>
+      <c r="D46" s="26" t="n">
+        <f aca="false">'Proforma 24 mo'!AA58</f>
+        <v>0</v>
+      </c>
+      <c r="E46" s="22" t="n">
+        <f aca="false">(E6-D6)*'Equipment plan'!G10</f>
+        <v>27700</v>
+      </c>
+      <c r="F46" s="22" t="n">
+        <f aca="false">(F6-E6)*'Equipment plan'!G10</f>
+        <v>27700</v>
+      </c>
+      <c r="G46" s="22" t="n">
+        <f aca="false">(G6-F6)*'Equipment plan'!G10</f>
+        <v>0</v>
+      </c>
+      <c r="H46" s="2"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="B47" s="26" t="n">
+        <f aca="false">Assumptions!$B$39</f>
+        <v>25000</v>
+      </c>
+      <c r="C47" s="23" t="n">
+        <f aca="false">B47+C43-C46</f>
+        <v>103124.805567695</v>
+      </c>
+      <c r="D47" s="23" t="n">
+        <f aca="false">C47+D43-D46</f>
+        <v>329296.731195651</v>
+      </c>
+      <c r="E47" s="23" t="n">
+        <f aca="false">D47+E43-E46</f>
+        <v>432092.927487574</v>
+      </c>
+      <c r="F47" s="23" t="n">
+        <f aca="false">E47+F43-F46</f>
+        <v>631434.414043181</v>
+      </c>
+      <c r="G47" s="23" t="n">
+        <f aca="false">F47+G43-G46</f>
+        <v>1011168.24892332</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="B48" s="22" t="n">
+        <f aca="false">B41/6</f>
+        <v>23400</v>
+      </c>
+      <c r="C48" s="22" t="n">
+        <f aca="false">C41/6</f>
+        <v>28369.3316551124</v>
+      </c>
+      <c r="D48" s="22" t="n">
+        <f aca="false">D41/6</f>
+        <v>39050.0515181601</v>
+      </c>
+      <c r="E48" s="22" t="n">
+        <f aca="false">E41/6</f>
+        <v>74259.0968278756</v>
+      </c>
+      <c r="F48" s="22" t="n">
+        <f aca="false">F41/6</f>
+        <v>105291.124137813</v>
+      </c>
+      <c r="G48" s="22" t="n">
+        <f aca="false">G41/6</f>
+        <v>107668.42958448</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="17" t="s">
+        <v>361</v>
+      </c>
+      <c r="B49" s="34" t="str">
+        <f aca="false">IF(B47&gt;=B48,"yes","NO")</f>
+        <v>yes</v>
+      </c>
+      <c r="C49" s="34" t="str">
+        <f aca="false">IF(C47&gt;=C48,"yes","NO")</f>
+        <v>yes</v>
+      </c>
+      <c r="D49" s="34" t="str">
+        <f aca="false">IF(D47&gt;=D48,"yes","NO")</f>
+        <v>yes</v>
+      </c>
+      <c r="E49" s="34" t="str">
+        <f aca="false">IF(E47&gt;=E48,"yes","NO")</f>
+        <v>yes</v>
+      </c>
+      <c r="F49" s="34" t="str">
+        <f aca="false">IF(F47&gt;=F48,"yes","NO")</f>
+        <v>yes</v>
+      </c>
+      <c r="G49" s="34" t="str">
+        <f aca="false">IF(G47&gt;=G48,"yes","NO")</f>
+        <v>yes</v>
+      </c>
+      <c r="H49" s="2"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="17" t="s">
+        <v>363</v>
+      </c>
+      <c r="B51" s="22" t="n">
+        <f aca="false">B43+B23</f>
+        <v>69049.5544186047</v>
+      </c>
+      <c r="C51" s="22" t="n">
+        <f aca="false">C43+C23</f>
+        <v>177824.805567695</v>
+      </c>
+      <c r="D51" s="22" t="n">
+        <f aca="false">D43+D23</f>
+        <v>298171.925627957</v>
+      </c>
+      <c r="E51" s="22" t="n">
+        <f aca="false">E43+E23</f>
+        <v>214496.196291922</v>
+      </c>
+      <c r="F51" s="22" t="n">
+        <f aca="false">F43+F23</f>
+        <v>323041.486555607</v>
+      </c>
+      <c r="G51" s="22" t="n">
+        <f aca="false">G43+G23</f>
+        <v>487733.834880143</v>
+      </c>
+      <c r="H51" s="2"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="17" t="s">
+        <v>364</v>
+      </c>
+      <c r="B52" s="33" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="C52" s="33" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="D52" s="33" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="E52" s="33" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="F52" s="33" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G52" s="33" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="15" t="s">
+        <v>366</v>
+      </c>
+      <c r="B53" s="23" t="n">
+        <f aca="false">B51*B52</f>
+        <v>169861.903869767</v>
+      </c>
+      <c r="C53" s="23" t="n">
+        <f aca="false">C51*C52</f>
+        <v>437449.021696529</v>
+      </c>
+      <c r="D53" s="23" t="n">
+        <f aca="false">D51*D52</f>
+        <v>733502.937044773</v>
+      </c>
+      <c r="E53" s="23" t="n">
+        <f aca="false">E51*E52</f>
+        <v>527660.642878129</v>
+      </c>
+      <c r="F53" s="23" t="n">
+        <f aca="false">F51*F52</f>
+        <v>794682.056926794</v>
+      </c>
+      <c r="G53" s="23" t="n">
+        <f aca="false">G51*G52</f>
+        <v>1199825.23380515</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>367</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="60"/>
@@ -10343,7 +11975,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>296</v>
+        <v>368</v>
       </c>
       <c r="B1" s="2"/>
     </row>
@@ -10352,99 +11984,107 @@
       <c r="B2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="33" t="s">
-        <v>297</v>
-      </c>
-      <c r="B3" s="34" t="s">
-        <v>298</v>
+      <c r="A3" s="35" t="s">
+        <v>369</v>
+      </c>
+      <c r="B3" s="36" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="33" t="s">
-        <v>299</v>
-      </c>
-      <c r="B4" s="34" t="s">
-        <v>300</v>
+      <c r="A4" s="35" t="s">
+        <v>371</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="B5" s="34" t="s">
-        <v>302</v>
+      <c r="A5" s="35" t="s">
+        <v>373</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="B6" s="34" t="s">
-        <v>304</v>
+      <c r="A6" s="35" t="s">
+        <v>375</v>
+      </c>
+      <c r="B6" s="36" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="33" t="s">
-        <v>305</v>
-      </c>
-      <c r="B7" s="34" t="s">
-        <v>306</v>
+      <c r="A7" s="35" t="s">
+        <v>377</v>
+      </c>
+      <c r="B7" s="36" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="33" t="s">
-        <v>307</v>
-      </c>
-      <c r="B8" s="34" t="s">
-        <v>308</v>
+      <c r="A8" s="35" t="s">
+        <v>379</v>
+      </c>
+      <c r="B8" s="36" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="33" t="s">
-        <v>309</v>
-      </c>
-      <c r="B9" s="34" t="s">
-        <v>310</v>
+      <c r="A9" s="35" t="s">
+        <v>381</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="B10" s="34" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="33" t="s">
-        <v>313</v>
-      </c>
-      <c r="B11" s="34" t="s">
-        <v>314</v>
+      <c r="A10" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="B10" s="36" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="35" t="s">
+        <v>385</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="33" t="s">
-        <v>315</v>
-      </c>
-      <c r="B12" s="34" t="s">
-        <v>316</v>
+      <c r="A12" s="35" t="s">
+        <v>387</v>
+      </c>
+      <c r="B12" s="36" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="33" t="s">
-        <v>317</v>
-      </c>
-      <c r="B13" s="34" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="33" t="s">
-        <v>319</v>
-      </c>
-      <c r="B14" s="34" t="s">
-        <v>320</v>
+      <c r="A13" s="35" t="s">
+        <v>389</v>
+      </c>
+      <c r="B13" s="36" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="35" t="s">
+        <v>391</v>
+      </c>
+      <c r="B14" s="36" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="35" t="s">
+        <v>393</v>
+      </c>
+      <c r="B15" s="36" t="s">
+        <v>394</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Scag-Scapes-Proforma.xlsx
+++ b/docs/Scag-Scapes-Proforma.xlsx
@@ -14,7 +14,8 @@
     <sheet name="Scenarios" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Equipment plan" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="5-year plan" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Sources &amp; notes" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Three cases 5-yr" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Sources &amp; notes" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="463">
   <si>
     <t xml:space="preserve">Scag Scapes LLC - Growth Proforma - Assumptions</t>
   </si>
@@ -1157,6 +1158,183 @@
   </si>
   <si>
     <t xml:space="preserve">Cross-check: revenue x 0.70 (BizBuySell). Not a promise; a benchmark.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worst case, conservative, strong - the same business run three ways</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blue = change it. The middle block is the plan in the blueprint. Today's run rate is on the '5-year plan' tab and is the same in all three cases; what differs is only how fast crews fill their days, what a foot sells for, how many plans attach, and when a crew is added.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Side by side</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worst case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue - year 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue - year 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linear feet installed - year 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross margin - year 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating profit before the growth lead - year 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating profit after the growth lead - year 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating profit after the growth lead - year 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What the growth lead costs - year 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What the growth lead costs - year 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner's cash from the business - year 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash at the end of year 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicative value at the end of year 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read it this way: plan around the worst case. There the 90-day gate ends the growth-lead arrangement for $15,000 and the company ends up roughly where it is today - that is the floor. The middle block is what the blueprint commits to. The right-hand block is the same plan with the levers landing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WORST CASE - most of it does not work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leads cost more and close worse, crews never beat 36 LF a day, Crew 2 slips to the middle of year 2, few plans attach. The 90-day gate is missed, so the growth lead is ended after three months (that is the $15,000 in year 1 - the whole exposure) and no share is ever earned. The company then looks much like it does today: it covers itself and pays the owner, and it does not run away from anyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drivers - change any blue cell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Half a crew = started mid-year. A crew is added only after three months at target, backlog over four weeks and cash above two months of overhead.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of crew days on drainage (the rest is pads, fences, sod, patios)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today one crew spends about 42% of its days on drain feet. Filling the calendar is the whole growth engine.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LF a crew installs per working day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charlie's target is 43 (900 LF / 21 days).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual price change from year 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drain Check plans active at year end</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing as a share of revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overhead per crew per year (insurance, tools, uniforms, phones)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office admin, operations manager, estimator, bonus pool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hired in that order, each before the crew that needs it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crew days worked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linear feet installed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drainage revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other work on the remaining days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crew labor (wages from the Assumptions tab, +3% a year from year 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materials, fuel and plan visit costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overhead (owner draw, fixed costs, per crew, staff, marketing, yard, equipment loans)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner draw, existing payments, software, CPA, shop and the yard (sq ft x rate) all come from the Assumptions tab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating profit before the growth lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Growth lead - base for the year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set any year to 0 to see the plan without it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Growth lead - share of profit above today's baseline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earned only on profit above what the business makes today.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Growth lead - total cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPERATING PROFIT after the growth lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating margin (the owner draw is already paid)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equipment down payments for new crews</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash at year end</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Before income tax and before any distribution beyond the owner draw. A falling line means the owner draw is larger than the business earns - the draw is a blue cell.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner's cash from the business (operating profit + owner draw)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicative value at 2.46x SDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BizBuySell landscaping median, 945 sales 2021-2025. A benchmark, not a promise.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONSERVATIVE - the plan in the blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charlie's own targets on the blueprint's schedule: 900 LF a crew a month, 70% close, 40% plan attach, Crew 3 in year 3 and Crew 4 in year 4 - each only after its gate. This is an annual approximation of the 24-month proforma and lands within about 4% of it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STRONG - the levers work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reviews, referrals and the Moasure map support a 3% price step each year, crews settle at 48 LF a day, the plan book compounds and HOA / property-manager work fills the winter. Note the gross margin runs above Charlie's 50% rule - that is what productivity does to a fixed crew cost.</t>
   </si>
   <si>
     <t xml:space="preserve">Sources and notes</t>
@@ -1253,7 +1431,7 @@
     <numFmt numFmtId="169" formatCode="\$0.00"/>
     <numFmt numFmtId="170" formatCode="@"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1339,6 +1517,14 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF46524E"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1409,7 +1595,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="45">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1565,6 +1751,22 @@
     <xf numFmtId="170" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="true"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
@@ -12114,6 +12316,2883 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:H122"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="56"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="5"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="16"/>
+      <c r="B5" s="29" t="s">
+        <v>380</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>257</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>381</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="18" t="s">
+        <v>382</v>
+      </c>
+      <c r="B6" s="15" t="n">
+        <f aca="false">B39</f>
+        <v>359125.8</v>
+      </c>
+      <c r="C6" s="15" t="n">
+        <f aca="false">B73</f>
+        <v>721206</v>
+      </c>
+      <c r="D6" s="15" t="n">
+        <f aca="false">B107</f>
+        <v>881074.8</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="18" t="s">
+        <v>383</v>
+      </c>
+      <c r="B7" s="15" t="n">
+        <f aca="false">F39</f>
+        <v>644276.4</v>
+      </c>
+      <c r="C7" s="15" t="n">
+        <f aca="false">F73</f>
+        <v>2487162.5583804</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <f aca="false">F107</f>
+        <v>3237506.55996845</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="18" t="s">
+        <v>384</v>
+      </c>
+      <c r="B8" s="19" t="n">
+        <f aca="false">F35</f>
+        <v>11566.8</v>
+      </c>
+      <c r="C8" s="19" t="n">
+        <f aca="false">F69</f>
+        <v>41176.8</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <f aca="false">F103</f>
+        <v>51710.4</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="18" t="s">
+        <v>385</v>
+      </c>
+      <c r="B9" s="21" t="n">
+        <f aca="false">F43</f>
+        <v>0.358714949844654</v>
+      </c>
+      <c r="C9" s="21" t="n">
+        <f aca="false">F77</f>
+        <v>0.494088304198659</v>
+      </c>
+      <c r="D9" s="21" t="n">
+        <f aca="false">F111</f>
+        <v>0.535112619981201</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="18" t="s">
+        <v>386</v>
+      </c>
+      <c r="B10" s="15" t="n">
+        <f aca="false">B45</f>
+        <v>-64486.915</v>
+      </c>
+      <c r="C10" s="15" t="n">
+        <f aca="false">B79</f>
+        <v>108938.36544552</v>
+      </c>
+      <c r="D10" s="15" t="n">
+        <f aca="false">B113</f>
+        <v>220821.13944552</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="16" t="s">
+        <v>387</v>
+      </c>
+      <c r="B11" s="23" t="n">
+        <f aca="false">B49</f>
+        <v>-79486.915</v>
+      </c>
+      <c r="C11" s="23" t="n">
+        <f aca="false">B83</f>
+        <v>38044.5289009678</v>
+      </c>
+      <c r="D11" s="23" t="n">
+        <f aca="false">B117</f>
+        <v>138739.025500968</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="16" t="s">
+        <v>388</v>
+      </c>
+      <c r="B12" s="23" t="n">
+        <f aca="false">F49</f>
+        <v>-44509.308042386</v>
+      </c>
+      <c r="C12" s="23" t="n">
+        <f aca="false">F83</f>
+        <v>468196.987941603</v>
+      </c>
+      <c r="D12" s="23" t="n">
+        <f aca="false">F117</f>
+        <v>798877.56638799</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="18" t="s">
+        <v>389</v>
+      </c>
+      <c r="B13" s="15" t="n">
+        <f aca="false">B48</f>
+        <v>15000</v>
+      </c>
+      <c r="C13" s="15" t="n">
+        <f aca="false">B82</f>
+        <v>70893.836544552</v>
+      </c>
+      <c r="D13" s="15" t="n">
+        <f aca="false">B116</f>
+        <v>82082.113944552</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="18" t="s">
+        <v>390</v>
+      </c>
+      <c r="B14" s="15" t="n">
+        <f aca="false">F48</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="15" t="n">
+        <f aca="false">F82</f>
+        <v>132021.887549067</v>
+      </c>
+      <c r="D14" s="15" t="n">
+        <f aca="false">F116</f>
+        <v>168764.17404311</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="B15" s="23" t="n">
+        <f aca="false">F53</f>
+        <v>27490.691957614</v>
+      </c>
+      <c r="C15" s="23" t="n">
+        <f aca="false">F87</f>
+        <v>540196.987941603</v>
+      </c>
+      <c r="D15" s="23" t="n">
+        <f aca="false">F121</f>
+        <v>870877.56638799</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="18" t="s">
+        <v>392</v>
+      </c>
+      <c r="B16" s="15" t="n">
+        <f aca="false">F52</f>
+        <v>-220618.989948206</v>
+      </c>
+      <c r="C16" s="15" t="n">
+        <f aca="false">F86</f>
+        <v>1165532.33955517</v>
+      </c>
+      <c r="D16" s="15" t="n">
+        <f aca="false">F120</f>
+        <v>2443286.01286937</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="B17" s="23" t="n">
+        <f aca="false">F54</f>
+        <v>67627.1022157304</v>
+      </c>
+      <c r="C17" s="23" t="n">
+        <f aca="false">F88</f>
+        <v>1328884.59033634</v>
+      </c>
+      <c r="D17" s="23" t="n">
+        <f aca="false">F122</f>
+        <v>2142358.81331445</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="39" t="s">
+        <v>394</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="40" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="29" t="s">
+        <v>397</v>
+      </c>
+      <c r="B23" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="C23" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="D23" s="29" t="s">
+        <v>305</v>
+      </c>
+      <c r="E23" s="29" t="s">
+        <v>306</v>
+      </c>
+      <c r="F23" s="29" t="s">
+        <v>307</v>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="18" t="s">
+        <v>312</v>
+      </c>
+      <c r="B24" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E24" s="33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F24" s="33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="7" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="18" t="s">
+        <v>399</v>
+      </c>
+      <c r="B25" s="13" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="7" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="B26" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="7" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="B27" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="C27" s="15" t="n">
+        <f aca="false">B27*(1+$B$28)</f>
+        <v>48</v>
+      </c>
+      <c r="D27" s="15" t="n">
+        <f aca="false">C27*(1+$B$28)</f>
+        <v>48</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <f aca="false">D27*(1+$B$28)</f>
+        <v>48</v>
+      </c>
+      <c r="F27" s="15" t="n">
+        <f aca="false">E27*(1+$B$28)</f>
+        <v>48</v>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="B28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="B29" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="C29" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>130</v>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="B30" s="13" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="C30" s="13" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D30" s="13" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="E30" s="13" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="B31" s="9" t="n">
+        <v>24000</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>24000</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>24000</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>24000</v>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="18" t="s">
+        <v>407</v>
+      </c>
+      <c r="B32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>44000</v>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="7" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="41" t="s">
+        <v>409</v>
+      </c>
+      <c r="B33" s="42"/>
+      <c r="C33" s="42"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="42"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="42"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="18" t="s">
+        <v>410</v>
+      </c>
+      <c r="B34" s="19" t="n">
+        <f aca="false">B24*Assumptions!$B$8*12</f>
+        <v>252</v>
+      </c>
+      <c r="C34" s="19" t="n">
+        <f aca="false">C24*Assumptions!$B$8*12</f>
+        <v>252</v>
+      </c>
+      <c r="D34" s="19" t="n">
+        <f aca="false">D24*Assumptions!$B$8*12</f>
+        <v>378</v>
+      </c>
+      <c r="E34" s="19" t="n">
+        <f aca="false">E24*Assumptions!$B$8*12</f>
+        <v>378</v>
+      </c>
+      <c r="F34" s="19" t="n">
+        <f aca="false">F24*Assumptions!$B$8*12</f>
+        <v>378</v>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="16" t="s">
+        <v>411</v>
+      </c>
+      <c r="B35" s="20" t="n">
+        <f aca="false">B34*B25*B26</f>
+        <v>4989.6</v>
+      </c>
+      <c r="C35" s="20" t="n">
+        <f aca="false">C34*C25*C26</f>
+        <v>6350.4</v>
+      </c>
+      <c r="D35" s="20" t="n">
+        <f aca="false">D34*D25*D26</f>
+        <v>10886.4</v>
+      </c>
+      <c r="E35" s="20" t="n">
+        <f aca="false">E34*E25*E26</f>
+        <v>11566.8</v>
+      </c>
+      <c r="F35" s="20" t="n">
+        <f aca="false">F34*F25*F26</f>
+        <v>11566.8</v>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="B36" s="15" t="n">
+        <f aca="false">B35*B27</f>
+        <v>239500.8</v>
+      </c>
+      <c r="C36" s="15" t="n">
+        <f aca="false">C35*C27</f>
+        <v>304819.2</v>
+      </c>
+      <c r="D36" s="15" t="n">
+        <f aca="false">D35*D27</f>
+        <v>522547.2</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <f aca="false">E35*E27</f>
+        <v>555206.4</v>
+      </c>
+      <c r="F36" s="15" t="n">
+        <f aca="false">F35*F27</f>
+        <v>555206.4</v>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="18" t="s">
+        <v>413</v>
+      </c>
+      <c r="B37" s="15" t="n">
+        <f aca="false">B34*(1-B25)*Assumptions!$B$10</f>
+        <v>113400</v>
+      </c>
+      <c r="C37" s="15" t="n">
+        <f aca="false">C34*(1-C25)*Assumptions!$B$10</f>
+        <v>75600</v>
+      </c>
+      <c r="D37" s="15" t="n">
+        <f aca="false">D34*(1-D25)*Assumptions!$B$10</f>
+        <v>75600</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <f aca="false">E34*(1-E25)*Assumptions!$B$10</f>
+        <v>56700</v>
+      </c>
+      <c r="F37" s="15" t="n">
+        <f aca="false">F34*(1-F25)*Assumptions!$B$10</f>
+        <v>56700</v>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="18" t="s">
+        <v>322</v>
+      </c>
+      <c r="B38" s="15" t="n">
+        <f aca="false">B29*Assumptions!$B$28/Assumptions!$B$29</f>
+        <v>6225</v>
+      </c>
+      <c r="C38" s="15" t="n">
+        <f aca="false">C29*Assumptions!$B$28/Assumptions!$B$29</f>
+        <v>13695</v>
+      </c>
+      <c r="D38" s="15" t="n">
+        <f aca="false">D29*Assumptions!$B$28/Assumptions!$B$29</f>
+        <v>21165</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <f aca="false">E29*Assumptions!$B$28/Assumptions!$B$29</f>
+        <v>27390</v>
+      </c>
+      <c r="F38" s="15" t="n">
+        <f aca="false">F29*Assumptions!$B$28/Assumptions!$B$29</f>
+        <v>32370</v>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="B39" s="23" t="n">
+        <f aca="false">B36+B37+B38</f>
+        <v>359125.8</v>
+      </c>
+      <c r="C39" s="23" t="n">
+        <f aca="false">C36+C37+C38</f>
+        <v>394114.2</v>
+      </c>
+      <c r="D39" s="23" t="n">
+        <f aca="false">D36+D37+D38</f>
+        <v>619312.2</v>
+      </c>
+      <c r="E39" s="23" t="n">
+        <f aca="false">E36+E37+E38</f>
+        <v>639296.4</v>
+      </c>
+      <c r="F39" s="23" t="n">
+        <f aca="false">F36+F37+F38</f>
+        <v>644276.4</v>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="18" t="s">
+        <v>414</v>
+      </c>
+      <c r="B40" s="15" t="n">
+        <f aca="false">B24*(Assumptions!$B$24*Assumptions!$B$25*Assumptions!$B$21+Assumptions!$B$25*Assumptions!$B$22)*(1+Assumptions!$B$23)*12*1.03^MAX(0,COLUMN(B1)-2)</f>
+        <v>166848.12</v>
+      </c>
+      <c r="C40" s="15" t="n">
+        <f aca="false">C24*(Assumptions!$B$24*Assumptions!$B$25*Assumptions!$B$21+Assumptions!$B$25*Assumptions!$B$22)*(1+Assumptions!$B$23)*12*1.03^MAX(0,COLUMN(C1)-2)</f>
+        <v>171853.5636</v>
+      </c>
+      <c r="D40" s="15" t="n">
+        <f aca="false">D24*(Assumptions!$B$24*Assumptions!$B$25*Assumptions!$B$21+Assumptions!$B$25*Assumptions!$B$22)*(1+Assumptions!$B$23)*12*1.03^MAX(0,COLUMN(D1)-2)</f>
+        <v>265513.755762</v>
+      </c>
+      <c r="E40" s="15" t="n">
+        <f aca="false">E24*(Assumptions!$B$24*Assumptions!$B$25*Assumptions!$B$21+Assumptions!$B$25*Assumptions!$B$22)*(1+Assumptions!$B$23)*12*1.03^MAX(0,COLUMN(E1)-2)</f>
+        <v>273479.16843486</v>
+      </c>
+      <c r="F40" s="15" t="n">
+        <f aca="false">F24*(Assumptions!$B$24*Assumptions!$B$25*Assumptions!$B$21+Assumptions!$B$25*Assumptions!$B$22)*(1+Assumptions!$B$23)*12*1.03^MAX(0,COLUMN(F1)-2)</f>
+        <v>281683.543487906</v>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="18" t="s">
+        <v>415</v>
+      </c>
+      <c r="B41" s="15" t="n">
+        <f aca="false">(B36+B37)*Assumptions!$B$20+B29/Assumptions!$B$29*Assumptions!$B$34</f>
+        <v>72330.16</v>
+      </c>
+      <c r="C41" s="15" t="n">
+        <f aca="false">(C36+C37)*Assumptions!$B$20+C29/Assumptions!$B$29*Assumptions!$B$34</f>
+        <v>79933.84</v>
+      </c>
+      <c r="D41" s="15" t="n">
+        <f aca="false">(D36+D37)*Assumptions!$B$20+D29/Assumptions!$B$29*Assumptions!$B$34</f>
+        <v>125579.44</v>
+      </c>
+      <c r="E41" s="15" t="n">
+        <f aca="false">(E36+E37)*Assumptions!$B$20+E29/Assumptions!$B$29*Assumptions!$B$34</f>
+        <v>130081.28</v>
+      </c>
+      <c r="F41" s="15" t="n">
+        <f aca="false">(F36+F37)*Assumptions!$B$20+F29/Assumptions!$B$29*Assumptions!$B$34</f>
+        <v>131481.28</v>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B42" s="23" t="n">
+        <f aca="false">B39-B40-B41</f>
+        <v>119947.52</v>
+      </c>
+      <c r="C42" s="23" t="n">
+        <f aca="false">C39-C40-C41</f>
+        <v>142326.7964</v>
+      </c>
+      <c r="D42" s="23" t="n">
+        <f aca="false">D39-D40-D41</f>
+        <v>228219.004238</v>
+      </c>
+      <c r="E42" s="23" t="n">
+        <f aca="false">E39-E40-E41</f>
+        <v>235735.95156514</v>
+      </c>
+      <c r="F42" s="23" t="n">
+        <f aca="false">F39-F40-F41</f>
+        <v>231111.576512094</v>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="B43" s="21" t="n">
+        <f aca="false">IF(B39=0,0,B42/B39)</f>
+        <v>0.333998615526927</v>
+      </c>
+      <c r="C43" s="21" t="n">
+        <f aca="false">IF(C39=0,0,C42/C39)</f>
+        <v>0.361130850905651</v>
+      </c>
+      <c r="D43" s="21" t="n">
+        <f aca="false">IF(D39=0,0,D42/D39)</f>
+        <v>0.368503969787774</v>
+      </c>
+      <c r="E43" s="21" t="n">
+        <f aca="false">IF(E39=0,0,E42/E39)</f>
+        <v>0.368742810948317</v>
+      </c>
+      <c r="F43" s="21" t="n">
+        <f aca="false">IF(F39=0,0,F42/F39)</f>
+        <v>0.358714949844654</v>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="18" t="s">
+        <v>416</v>
+      </c>
+      <c r="B44" s="15" t="n">
+        <f aca="false">(Assumptions!$B$55+Assumptions!$B$57+Assumptions!$B$58+Assumptions!$B$59+Assumptions!$B$60)*12+B24*B31+B32+B39*B30+Assumptions!$B$61*Assumptions!$B$62*12+'Equipment plan'!$H$10*12*MAX(0,B24-1)</f>
+        <v>184434.435</v>
+      </c>
+      <c r="C44" s="15" t="n">
+        <f aca="false">(Assumptions!$B$55+Assumptions!$B$57+Assumptions!$B$58+Assumptions!$B$59+Assumptions!$B$60)*12+C24*C31+C32+C39*C30+Assumptions!$B$61*Assumptions!$B$62*12+'Equipment plan'!$H$10*12*MAX(0,C24-1)</f>
+        <v>187058.565</v>
+      </c>
+      <c r="D44" s="15" t="n">
+        <f aca="false">(Assumptions!$B$55+Assumptions!$B$57+Assumptions!$B$58+Assumptions!$B$59+Assumptions!$B$60)*12+D24*D31+D32+D39*D30+Assumptions!$B$61*Assumptions!$B$62*12+'Equipment plan'!$H$10*12*MAX(0,D24-1)</f>
+        <v>253748.56955448</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <f aca="false">(Assumptions!$B$55+Assumptions!$B$57+Assumptions!$B$58+Assumptions!$B$59+Assumptions!$B$60)*12+E24*E31+E32+E39*E30+Assumptions!$B$61*Assumptions!$B$62*12+'Equipment plan'!$H$10*12*MAX(0,E24-1)</f>
+        <v>273247.38455448</v>
+      </c>
+      <c r="F44" s="15" t="n">
+        <f aca="false">(Assumptions!$B$55+Assumptions!$B$57+Assumptions!$B$58+Assumptions!$B$59+Assumptions!$B$60)*12+F24*F31+F32+F39*F30+Assumptions!$B$61*Assumptions!$B$62*12+'Equipment plan'!$H$10*12*MAX(0,F24-1)</f>
+        <v>275620.88455448</v>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="7" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="16" t="s">
+        <v>418</v>
+      </c>
+      <c r="B45" s="23" t="n">
+        <f aca="false">B42-B44</f>
+        <v>-64486.915</v>
+      </c>
+      <c r="C45" s="23" t="n">
+        <f aca="false">C42-C44</f>
+        <v>-44731.7686000001</v>
+      </c>
+      <c r="D45" s="23" t="n">
+        <f aca="false">D42-D44</f>
+        <v>-25529.5653164801</v>
+      </c>
+      <c r="E45" s="23" t="n">
+        <f aca="false">E42-E44</f>
+        <v>-37511.4329893402</v>
+      </c>
+      <c r="F45" s="23" t="n">
+        <f aca="false">F42-F44</f>
+        <v>-44509.308042386</v>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="B46" s="9" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="7" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="18" t="s">
+        <v>421</v>
+      </c>
+      <c r="B47" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C47" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D47" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E47" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="7" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="18" t="s">
+        <v>423</v>
+      </c>
+      <c r="B48" s="15" t="n">
+        <f aca="false">B46+IF(B46=0,0,B47*MAX(0,B45-MAX(0,'5-year plan'!$B$44)))</f>
+        <v>15000</v>
+      </c>
+      <c r="C48" s="15" t="n">
+        <f aca="false">C46+IF(C46=0,0,C47*MAX(0,C45-MAX(0,'5-year plan'!$B$44)))</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="15" t="n">
+        <f aca="false">D46+IF(D46=0,0,D47*MAX(0,D45-MAX(0,'5-year plan'!$B$44)))</f>
+        <v>0</v>
+      </c>
+      <c r="E48" s="15" t="n">
+        <f aca="false">E46+IF(E46=0,0,E47*MAX(0,E45-MAX(0,'5-year plan'!$B$44)))</f>
+        <v>0</v>
+      </c>
+      <c r="F48" s="15" t="n">
+        <f aca="false">F46+IF(F46=0,0,F47*MAX(0,F45-MAX(0,'5-year plan'!$B$44)))</f>
+        <v>0</v>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="16" t="s">
+        <v>424</v>
+      </c>
+      <c r="B49" s="23" t="n">
+        <f aca="false">B45-B48</f>
+        <v>-79486.915</v>
+      </c>
+      <c r="C49" s="23" t="n">
+        <f aca="false">C45-C48</f>
+        <v>-44731.7686000001</v>
+      </c>
+      <c r="D49" s="23" t="n">
+        <f aca="false">D45-D48</f>
+        <v>-25529.5653164801</v>
+      </c>
+      <c r="E49" s="23" t="n">
+        <f aca="false">E45-E48</f>
+        <v>-37511.4329893402</v>
+      </c>
+      <c r="F49" s="23" t="n">
+        <f aca="false">F45-F48</f>
+        <v>-44509.308042386</v>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="18" t="s">
+        <v>425</v>
+      </c>
+      <c r="B50" s="21" t="n">
+        <f aca="false">IF(B39=0,0,B49/B39)</f>
+        <v>-0.221334459958043</v>
+      </c>
+      <c r="C50" s="21" t="n">
+        <f aca="false">IF(C39=0,0,C49/C39)</f>
+        <v>-0.113499510040491</v>
+      </c>
+      <c r="D50" s="21" t="n">
+        <f aca="false">IF(D39=0,0,D49/D39)</f>
+        <v>-0.0412224485751776</v>
+      </c>
+      <c r="E50" s="21" t="n">
+        <f aca="false">IF(E39=0,0,E49/E39)</f>
+        <v>-0.0586761211064855</v>
+      </c>
+      <c r="F50" s="21" t="n">
+        <f aca="false">IF(F39=0,0,F49/F39)</f>
+        <v>-0.0690841819479745</v>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="18" t="s">
+        <v>426</v>
+      </c>
+      <c r="B51" s="15" t="n">
+        <f aca="false">MAX(0,B24-1)*'Equipment plan'!$G$10</f>
+        <v>0</v>
+      </c>
+      <c r="C51" s="15" t="n">
+        <f aca="false">MAX(0,C24-B24)*'Equipment plan'!$G$10</f>
+        <v>0</v>
+      </c>
+      <c r="D51" s="15" t="n">
+        <f aca="false">MAX(0,D24-C24)*'Equipment plan'!$G$10</f>
+        <v>13850</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <f aca="false">MAX(0,E24-D24)*'Equipment plan'!$G$10</f>
+        <v>0</v>
+      </c>
+      <c r="F51" s="15" t="n">
+        <f aca="false">MAX(0,F24-E24)*'Equipment plan'!$G$10</f>
+        <v>0</v>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="B52" s="23" t="n">
+        <f aca="false">Assumptions!$B$39+B49-B51</f>
+        <v>-54486.915</v>
+      </c>
+      <c r="C52" s="23" t="n">
+        <f aca="false">B52+C49-C51</f>
+        <v>-99218.6836000001</v>
+      </c>
+      <c r="D52" s="23" t="n">
+        <f aca="false">C52+D49-D51</f>
+        <v>-138598.24891648</v>
+      </c>
+      <c r="E52" s="23" t="n">
+        <f aca="false">D52+E49-E51</f>
+        <v>-176109.68190582</v>
+      </c>
+      <c r="F52" s="23" t="n">
+        <f aca="false">E52+F49-F51</f>
+        <v>-220618.989948206</v>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="7" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="18" t="s">
+        <v>429</v>
+      </c>
+      <c r="B53" s="15" t="n">
+        <f aca="false">B49+Assumptions!$B$55*12</f>
+        <v>-7486.91500000004</v>
+      </c>
+      <c r="C53" s="15" t="n">
+        <f aca="false">C49+Assumptions!$B$55*12</f>
+        <v>27268.2313999999</v>
+      </c>
+      <c r="D53" s="15" t="n">
+        <f aca="false">D49+Assumptions!$B$55*12</f>
+        <v>46470.4346835199</v>
+      </c>
+      <c r="E53" s="15" t="n">
+        <f aca="false">E49+Assumptions!$B$55*12</f>
+        <v>34488.5670106598</v>
+      </c>
+      <c r="F53" s="15" t="n">
+        <f aca="false">F49+Assumptions!$B$55*12</f>
+        <v>27490.691957614</v>
+      </c>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="18" t="s">
+        <v>430</v>
+      </c>
+      <c r="B54" s="15" t="n">
+        <f aca="false">MAX(0,B53)*2.46</f>
+        <v>0</v>
+      </c>
+      <c r="C54" s="15" t="n">
+        <f aca="false">MAX(0,C53)*2.46</f>
+        <v>67079.8492439998</v>
+      </c>
+      <c r="D54" s="15" t="n">
+        <f aca="false">MAX(0,D53)*2.46</f>
+        <v>114317.269321459</v>
+      </c>
+      <c r="E54" s="15" t="n">
+        <f aca="false">MAX(0,E53)*2.46</f>
+        <v>84841.8748462231</v>
+      </c>
+      <c r="F54" s="15" t="n">
+        <f aca="false">MAX(0,F53)*2.46</f>
+        <v>67627.1022157304</v>
+      </c>
+      <c r="G54" s="2"/>
+      <c r="H54" s="7" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+    </row>
+    <row r="56" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="40" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="29" t="s">
+        <v>397</v>
+      </c>
+      <c r="B57" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="C57" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="D57" s="29" t="s">
+        <v>305</v>
+      </c>
+      <c r="E57" s="29" t="s">
+        <v>306</v>
+      </c>
+      <c r="F57" s="29" t="s">
+        <v>307</v>
+      </c>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="18" t="s">
+        <v>312</v>
+      </c>
+      <c r="B58" s="33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C58" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" s="33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E58" s="33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F58" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="G58" s="2"/>
+      <c r="H58" s="7" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="18" t="s">
+        <v>399</v>
+      </c>
+      <c r="B59" s="13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C59" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D59" s="13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E59" s="13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F59" s="13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G59" s="2"/>
+      <c r="H59" s="7" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="B60" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="C60" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="D60" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="E60" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="F60" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="G60" s="2"/>
+      <c r="H60" s="7" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="B61" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="C61" s="15" t="n">
+        <f aca="false">B61*(1+$B$62)</f>
+        <v>51.5</v>
+      </c>
+      <c r="D61" s="15" t="n">
+        <f aca="false">C61*(1+$B$62)</f>
+        <v>53.045</v>
+      </c>
+      <c r="E61" s="15" t="n">
+        <f aca="false">D61*(1+$B$62)</f>
+        <v>54.63635</v>
+      </c>
+      <c r="F61" s="15" t="n">
+        <f aca="false">E61*(1+$B$62)</f>
+        <v>56.2754405</v>
+      </c>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="B62" s="13" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C62" s="13" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D62" s="13" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E62" s="13" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F62" s="13" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="B63" s="12" t="n">
+        <v>69</v>
+      </c>
+      <c r="C63" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="D63" s="12" t="n">
+        <v>260</v>
+      </c>
+      <c r="E63" s="12" t="n">
+        <v>380</v>
+      </c>
+      <c r="F63" s="12" t="n">
+        <v>480</v>
+      </c>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="B64" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C64" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D64" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E64" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F64" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="B65" s="9" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C65" s="9" t="n">
+        <v>22000</v>
+      </c>
+      <c r="D65" s="9" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E65" s="9" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F65" s="9" t="n">
+        <v>22000</v>
+      </c>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="18" t="s">
+        <v>407</v>
+      </c>
+      <c r="B66" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="9" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D66" s="9" t="n">
+        <v>102750</v>
+      </c>
+      <c r="E66" s="9" t="n">
+        <v>191000</v>
+      </c>
+      <c r="F66" s="9" t="n">
+        <v>200000</v>
+      </c>
+      <c r="G66" s="2"/>
+      <c r="H66" s="7" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="41" t="s">
+        <v>409</v>
+      </c>
+      <c r="B67" s="42"/>
+      <c r="C67" s="42"/>
+      <c r="D67" s="42"/>
+      <c r="E67" s="42"/>
+      <c r="F67" s="42"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="42"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="18" t="s">
+        <v>410</v>
+      </c>
+      <c r="B68" s="19" t="n">
+        <f aca="false">B58*Assumptions!$B$8*12</f>
+        <v>378</v>
+      </c>
+      <c r="C68" s="19" t="n">
+        <f aca="false">C58*Assumptions!$B$8*12</f>
+        <v>504</v>
+      </c>
+      <c r="D68" s="19" t="n">
+        <f aca="false">D58*Assumptions!$B$8*12</f>
+        <v>630</v>
+      </c>
+      <c r="E68" s="19" t="n">
+        <f aca="false">E58*Assumptions!$B$8*12</f>
+        <v>882</v>
+      </c>
+      <c r="F68" s="19" t="n">
+        <f aca="false">F58*Assumptions!$B$8*12</f>
+        <v>1008</v>
+      </c>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="16" t="s">
+        <v>411</v>
+      </c>
+      <c r="B69" s="20" t="n">
+        <f aca="false">B68*B59*B60</f>
+        <v>12190.5</v>
+      </c>
+      <c r="C69" s="20" t="n">
+        <f aca="false">C68*C59*C60</f>
+        <v>19504.8</v>
+      </c>
+      <c r="D69" s="20" t="n">
+        <f aca="false">D68*D59*D60</f>
+        <v>25735.5</v>
+      </c>
+      <c r="E69" s="20" t="n">
+        <f aca="false">E68*E59*E60</f>
+        <v>36029.7</v>
+      </c>
+      <c r="F69" s="20" t="n">
+        <f aca="false">F68*F59*F60</f>
+        <v>41176.8</v>
+      </c>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="B70" s="15" t="n">
+        <f aca="false">B69*B61</f>
+        <v>609525</v>
+      </c>
+      <c r="C70" s="15" t="n">
+        <f aca="false">C69*C61</f>
+        <v>1004497.2</v>
+      </c>
+      <c r="D70" s="15" t="n">
+        <f aca="false">D69*D61</f>
+        <v>1365139.5975</v>
+      </c>
+      <c r="E70" s="15" t="n">
+        <f aca="false">E69*E61</f>
+        <v>1968531.299595</v>
+      </c>
+      <c r="F70" s="15" t="n">
+        <f aca="false">F69*F61</f>
+        <v>2317242.5583804</v>
+      </c>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="18" t="s">
+        <v>413</v>
+      </c>
+      <c r="B71" s="15" t="n">
+        <f aca="false">B68*(1-B59)*Assumptions!$B$10</f>
+        <v>94500</v>
+      </c>
+      <c r="C71" s="15" t="n">
+        <f aca="false">C68*(1-C59)*Assumptions!$B$10</f>
+        <v>50400</v>
+      </c>
+      <c r="D71" s="15" t="n">
+        <f aca="false">D68*(1-D59)*Assumptions!$B$10</f>
+        <v>31500</v>
+      </c>
+      <c r="E71" s="15" t="n">
+        <f aca="false">E68*(1-E59)*Assumptions!$B$10</f>
+        <v>44100</v>
+      </c>
+      <c r="F71" s="15" t="n">
+        <f aca="false">F68*(1-F59)*Assumptions!$B$10</f>
+        <v>50400.0000000001</v>
+      </c>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="18" t="s">
+        <v>322</v>
+      </c>
+      <c r="B72" s="15" t="n">
+        <f aca="false">B63*Assumptions!$B$28/Assumptions!$B$29</f>
+        <v>17181</v>
+      </c>
+      <c r="C72" s="15" t="n">
+        <f aca="false">C63*Assumptions!$B$28/Assumptions!$B$29</f>
+        <v>37350</v>
+      </c>
+      <c r="D72" s="15" t="n">
+        <f aca="false">D63*Assumptions!$B$28/Assumptions!$B$29</f>
+        <v>64740</v>
+      </c>
+      <c r="E72" s="15" t="n">
+        <f aca="false">E63*Assumptions!$B$28/Assumptions!$B$29</f>
+        <v>94620</v>
+      </c>
+      <c r="F72" s="15" t="n">
+        <f aca="false">F63*Assumptions!$B$28/Assumptions!$B$29</f>
+        <v>119520</v>
+      </c>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="B73" s="23" t="n">
+        <f aca="false">B70+B71+B72</f>
+        <v>721206</v>
+      </c>
+      <c r="C73" s="23" t="n">
+        <f aca="false">C70+C71+C72</f>
+        <v>1092247.2</v>
+      </c>
+      <c r="D73" s="23" t="n">
+        <f aca="false">D70+D71+D72</f>
+        <v>1461379.5975</v>
+      </c>
+      <c r="E73" s="23" t="n">
+        <f aca="false">E70+E71+E72</f>
+        <v>2107251.299595</v>
+      </c>
+      <c r="F73" s="23" t="n">
+        <f aca="false">F70+F71+F72</f>
+        <v>2487162.5583804</v>
+      </c>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="18" t="s">
+        <v>414</v>
+      </c>
+      <c r="B74" s="15" t="n">
+        <f aca="false">B58*(Assumptions!$B$24*Assumptions!$B$25*Assumptions!$B$21+Assumptions!$B$25*Assumptions!$B$22)*(1+Assumptions!$B$23)*12*1.03^MAX(0,COLUMN(B1)-2)</f>
+        <v>250272.18</v>
+      </c>
+      <c r="C74" s="15" t="n">
+        <f aca="false">C58*(Assumptions!$B$24*Assumptions!$B$25*Assumptions!$B$21+Assumptions!$B$25*Assumptions!$B$22)*(1+Assumptions!$B$23)*12*1.03^MAX(0,COLUMN(C1)-2)</f>
+        <v>343707.1272</v>
+      </c>
+      <c r="D74" s="15" t="n">
+        <f aca="false">D58*(Assumptions!$B$24*Assumptions!$B$25*Assumptions!$B$21+Assumptions!$B$25*Assumptions!$B$22)*(1+Assumptions!$B$23)*12*1.03^MAX(0,COLUMN(D1)-2)</f>
+        <v>442522.92627</v>
+      </c>
+      <c r="E74" s="15" t="n">
+        <f aca="false">E58*(Assumptions!$B$24*Assumptions!$B$25*Assumptions!$B$21+Assumptions!$B$25*Assumptions!$B$22)*(1+Assumptions!$B$23)*12*1.03^MAX(0,COLUMN(E1)-2)</f>
+        <v>638118.05968134</v>
+      </c>
+      <c r="F74" s="15" t="n">
+        <f aca="false">F58*(Assumptions!$B$24*Assumptions!$B$25*Assumptions!$B$21+Assumptions!$B$25*Assumptions!$B$22)*(1+Assumptions!$B$23)*12*1.03^MAX(0,COLUMN(F1)-2)</f>
+        <v>751156.115967749</v>
+      </c>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="18" t="s">
+        <v>415</v>
+      </c>
+      <c r="B75" s="15" t="n">
+        <f aca="false">(B70+B71)*Assumptions!$B$20+B63/Assumptions!$B$29*Assumptions!$B$34</f>
+        <v>145635</v>
+      </c>
+      <c r="C75" s="15" t="n">
+        <f aca="false">(C70+C71)*Assumptions!$B$20+C63/Assumptions!$B$29*Assumptions!$B$34</f>
+        <v>221479.44</v>
+      </c>
+      <c r="D75" s="15" t="n">
+        <f aca="false">(D70+D71)*Assumptions!$B$20+D63/Assumptions!$B$29*Assumptions!$B$34</f>
+        <v>297527.9195</v>
+      </c>
+      <c r="E75" s="15" t="n">
+        <f aca="false">(E70+E71)*Assumptions!$B$20+E63/Assumptions!$B$29*Assumptions!$B$34</f>
+        <v>429126.259919</v>
+      </c>
+      <c r="F75" s="15" t="n">
+        <f aca="false">(F70+F71)*Assumptions!$B$20+F63/Assumptions!$B$29*Assumptions!$B$34</f>
+        <v>507128.51167608</v>
+      </c>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B76" s="23" t="n">
+        <f aca="false">B73-B74-B75</f>
+        <v>325298.82</v>
+      </c>
+      <c r="C76" s="23" t="n">
+        <f aca="false">C73-C74-C75</f>
+        <v>527060.6328</v>
+      </c>
+      <c r="D76" s="23" t="n">
+        <f aca="false">D73-D74-D75</f>
+        <v>721328.75173</v>
+      </c>
+      <c r="E76" s="23" t="n">
+        <f aca="false">E73-E74-E75</f>
+        <v>1040006.97999466</v>
+      </c>
+      <c r="F76" s="23" t="n">
+        <f aca="false">F73-F74-F75</f>
+        <v>1228877.93073657</v>
+      </c>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="B77" s="21" t="n">
+        <f aca="false">IF(B73=0,0,B76/B73)</f>
+        <v>0.451048410578947</v>
+      </c>
+      <c r="C77" s="21" t="n">
+        <f aca="false">IF(C73=0,0,C76/C73)</f>
+        <v>0.482547021223767</v>
+      </c>
+      <c r="D77" s="21" t="n">
+        <f aca="false">IF(D73=0,0,D76/D73)</f>
+        <v>0.493594376823097</v>
+      </c>
+      <c r="E77" s="21" t="n">
+        <f aca="false">IF(E73=0,0,E76/E73)</f>
+        <v>0.49353723506757</v>
+      </c>
+      <c r="F77" s="21" t="n">
+        <f aca="false">IF(F73=0,0,F76/F73)</f>
+        <v>0.494088304198659</v>
+      </c>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="18" t="s">
+        <v>416</v>
+      </c>
+      <c r="B78" s="15" t="n">
+        <f aca="false">(Assumptions!$B$55+Assumptions!$B$57+Assumptions!$B$58+Assumptions!$B$59+Assumptions!$B$60)*12+B58*B65+B66+B73*B64+Assumptions!$B$61*Assumptions!$B$62*12+'Equipment plan'!$H$10*12*MAX(0,B58-1)</f>
+        <v>216360.45455448</v>
+      </c>
+      <c r="C78" s="15" t="n">
+        <f aca="false">(Assumptions!$B$55+Assumptions!$B$57+Assumptions!$B$58+Assumptions!$B$59+Assumptions!$B$60)*12+C58*C65+C66+C73*C64+Assumptions!$B$61*Assumptions!$B$62*12+'Equipment plan'!$H$10*12*MAX(0,C58-1)</f>
+        <v>289712.66910896</v>
+      </c>
+      <c r="D78" s="15" t="n">
+        <f aca="false">(Assumptions!$B$55+Assumptions!$B$57+Assumptions!$B$58+Assumptions!$B$59+Assumptions!$B$60)*12+D58*D65+D66+D73*D64+Assumptions!$B$61*Assumptions!$B$62*12+'Equipment plan'!$H$10*12*MAX(0,D58-1)</f>
+        <v>405719.44353844</v>
+      </c>
+      <c r="E78" s="15" t="n">
+        <f aca="false">(Assumptions!$B$55+Assumptions!$B$57+Assumptions!$B$58+Assumptions!$B$59+Assumptions!$B$60)*12+E58*E65+E66+E73*E64+Assumptions!$B$61*Assumptions!$B$62*12+'Equipment plan'!$H$10*12*MAX(0,E58-1)</f>
+        <v>575863.337752151</v>
+      </c>
+      <c r="F78" s="15" t="n">
+        <f aca="false">(Assumptions!$B$55+Assumptions!$B$57+Assumptions!$B$58+Assumptions!$B$59+Assumptions!$B$60)*12+F58*F65+F66+F73*F64+Assumptions!$B$61*Assumptions!$B$62*12+'Equipment plan'!$H$10*12*MAX(0,F58-1)</f>
+        <v>628659.055245901</v>
+      </c>
+      <c r="G78" s="2"/>
+      <c r="H78" s="7" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="16" t="s">
+        <v>418</v>
+      </c>
+      <c r="B79" s="23" t="n">
+        <f aca="false">B76-B78</f>
+        <v>108938.36544552</v>
+      </c>
+      <c r="C79" s="23" t="n">
+        <f aca="false">C76-C78</f>
+        <v>237347.96369104</v>
+      </c>
+      <c r="D79" s="23" t="n">
+        <f aca="false">D76-D78</f>
+        <v>315609.30819156</v>
+      </c>
+      <c r="E79" s="23" t="n">
+        <f aca="false">E76-E78</f>
+        <v>464143.642242509</v>
+      </c>
+      <c r="F79" s="23" t="n">
+        <f aca="false">F76-F78</f>
+        <v>600218.87549067</v>
+      </c>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="B80" s="9" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C80" s="9" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D80" s="9" t="n">
+        <v>66000</v>
+      </c>
+      <c r="E80" s="9" t="n">
+        <v>72000</v>
+      </c>
+      <c r="F80" s="9" t="n">
+        <v>72000</v>
+      </c>
+      <c r="G80" s="2"/>
+      <c r="H80" s="7" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="18" t="s">
+        <v>421</v>
+      </c>
+      <c r="B81" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C81" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D81" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E81" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F81" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G81" s="2"/>
+      <c r="H81" s="7" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="18" t="s">
+        <v>423</v>
+      </c>
+      <c r="B82" s="15" t="n">
+        <f aca="false">B80+IF(B80=0,0,B81*MAX(0,B79-MAX(0,'5-year plan'!$B$44)))</f>
+        <v>70893.836544552</v>
+      </c>
+      <c r="C82" s="15" t="n">
+        <f aca="false">C80+IF(C80=0,0,C81*MAX(0,C79-MAX(0,'5-year plan'!$B$44)))</f>
+        <v>83734.796369104</v>
+      </c>
+      <c r="D82" s="15" t="n">
+        <f aca="false">D80+IF(D80=0,0,D81*MAX(0,D79-MAX(0,'5-year plan'!$B$44)))</f>
+        <v>97560.930819156</v>
+      </c>
+      <c r="E82" s="15" t="n">
+        <f aca="false">E80+IF(E80=0,0,E81*MAX(0,E79-MAX(0,'5-year plan'!$B$44)))</f>
+        <v>118414.364224251</v>
+      </c>
+      <c r="F82" s="15" t="n">
+        <f aca="false">F80+IF(F80=0,0,F81*MAX(0,F79-MAX(0,'5-year plan'!$B$44)))</f>
+        <v>132021.887549067</v>
+      </c>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="16" t="s">
+        <v>424</v>
+      </c>
+      <c r="B83" s="23" t="n">
+        <f aca="false">B79-B82</f>
+        <v>38044.5289009678</v>
+      </c>
+      <c r="C83" s="23" t="n">
+        <f aca="false">C79-C82</f>
+        <v>153613.167321936</v>
+      </c>
+      <c r="D83" s="23" t="n">
+        <f aca="false">D79-D82</f>
+        <v>218048.377372404</v>
+      </c>
+      <c r="E83" s="23" t="n">
+        <f aca="false">E79-E82</f>
+        <v>345729.278018258</v>
+      </c>
+      <c r="F83" s="23" t="n">
+        <f aca="false">F79-F82</f>
+        <v>468196.987941603</v>
+      </c>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="18" t="s">
+        <v>425</v>
+      </c>
+      <c r="B84" s="21" t="n">
+        <f aca="false">IF(B73=0,0,B83/B73)</f>
+        <v>0.0527512651045164</v>
+      </c>
+      <c r="C84" s="21" t="n">
+        <f aca="false">IF(C73=0,0,C83/C73)</f>
+        <v>0.1406395615589</v>
+      </c>
+      <c r="D84" s="21" t="n">
+        <f aca="false">IF(D73=0,0,D83/D73)</f>
+        <v>0.149207213338288</v>
+      </c>
+      <c r="E84" s="21" t="n">
+        <f aca="false">IF(E73=0,0,E83/E73)</f>
+        <v>0.164066468049969</v>
+      </c>
+      <c r="F84" s="21" t="n">
+        <f aca="false">IF(F73=0,0,F83/F73)</f>
+        <v>0.188245431069244</v>
+      </c>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="18" t="s">
+        <v>426</v>
+      </c>
+      <c r="B85" s="15" t="n">
+        <f aca="false">MAX(0,B58-1)*'Equipment plan'!$G$10</f>
+        <v>13850</v>
+      </c>
+      <c r="C85" s="15" t="n">
+        <f aca="false">MAX(0,C58-B58)*'Equipment plan'!$G$10</f>
+        <v>13850</v>
+      </c>
+      <c r="D85" s="15" t="n">
+        <f aca="false">MAX(0,D58-C58)*'Equipment plan'!$G$10</f>
+        <v>13850</v>
+      </c>
+      <c r="E85" s="15" t="n">
+        <f aca="false">MAX(0,E58-D58)*'Equipment plan'!$G$10</f>
+        <v>27700</v>
+      </c>
+      <c r="F85" s="15" t="n">
+        <f aca="false">MAX(0,F58-E58)*'Equipment plan'!$G$10</f>
+        <v>13850</v>
+      </c>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="B86" s="23" t="n">
+        <f aca="false">Assumptions!$B$39+B83-B85</f>
+        <v>49194.5289009678</v>
+      </c>
+      <c r="C86" s="23" t="n">
+        <f aca="false">B86+C83-C85</f>
+        <v>188957.696222904</v>
+      </c>
+      <c r="D86" s="23" t="n">
+        <f aca="false">C86+D83-D85</f>
+        <v>393156.073595307</v>
+      </c>
+      <c r="E86" s="23" t="n">
+        <f aca="false">D86+E83-E85</f>
+        <v>711185.351613565</v>
+      </c>
+      <c r="F86" s="23" t="n">
+        <f aca="false">E86+F83-F85</f>
+        <v>1165532.33955517</v>
+      </c>
+      <c r="G86" s="2"/>
+      <c r="H86" s="7" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="18" t="s">
+        <v>429</v>
+      </c>
+      <c r="B87" s="15" t="n">
+        <f aca="false">B83+Assumptions!$B$55*12</f>
+        <v>110044.528900968</v>
+      </c>
+      <c r="C87" s="15" t="n">
+        <f aca="false">C83+Assumptions!$B$55*12</f>
+        <v>225613.167321936</v>
+      </c>
+      <c r="D87" s="15" t="n">
+        <f aca="false">D83+Assumptions!$B$55*12</f>
+        <v>290048.377372404</v>
+      </c>
+      <c r="E87" s="15" t="n">
+        <f aca="false">E83+Assumptions!$B$55*12</f>
+        <v>417729.278018258</v>
+      </c>
+      <c r="F87" s="15" t="n">
+        <f aca="false">F83+Assumptions!$B$55*12</f>
+        <v>540196.987941603</v>
+      </c>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="18" t="s">
+        <v>430</v>
+      </c>
+      <c r="B88" s="15" t="n">
+        <f aca="false">MAX(0,B87)*2.46</f>
+        <v>270709.541096381</v>
+      </c>
+      <c r="C88" s="15" t="n">
+        <f aca="false">MAX(0,C87)*2.46</f>
+        <v>555008.391611962</v>
+      </c>
+      <c r="D88" s="15" t="n">
+        <f aca="false">MAX(0,D87)*2.46</f>
+        <v>713519.008336113</v>
+      </c>
+      <c r="E88" s="15" t="n">
+        <f aca="false">MAX(0,E87)*2.46</f>
+        <v>1027614.02392491</v>
+      </c>
+      <c r="F88" s="15" t="n">
+        <f aca="false">MAX(0,F87)*2.46</f>
+        <v>1328884.59033634</v>
+      </c>
+      <c r="G88" s="2"/>
+      <c r="H88" s="7" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2"/>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
+    </row>
+    <row r="90" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B90" s="5"/>
+      <c r="C90" s="5"/>
+      <c r="D90" s="5"/>
+      <c r="E90" s="5"/>
+      <c r="F90" s="5"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="40" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="29" t="s">
+        <v>397</v>
+      </c>
+      <c r="B91" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="C91" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="D91" s="29" t="s">
+        <v>305</v>
+      </c>
+      <c r="E91" s="29" t="s">
+        <v>306</v>
+      </c>
+      <c r="F91" s="29" t="s">
+        <v>307</v>
+      </c>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="18" t="s">
+        <v>312</v>
+      </c>
+      <c r="B92" s="33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C92" s="33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D92" s="33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E92" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="F92" s="33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G92" s="2"/>
+      <c r="H92" s="7" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="18" t="s">
+        <v>399</v>
+      </c>
+      <c r="B93" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C93" s="13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D93" s="13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E93" s="13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F93" s="13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G93" s="2"/>
+      <c r="H93" s="7" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="B94" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="C94" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="D94" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="E94" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="F94" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="G94" s="2"/>
+      <c r="H94" s="7" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="B95" s="9" t="n">
+        <v>52</v>
+      </c>
+      <c r="C95" s="15" t="n">
+        <f aca="false">B95*(1+$B$96)</f>
+        <v>53.56</v>
+      </c>
+      <c r="D95" s="15" t="n">
+        <f aca="false">C95*(1+$B$96)</f>
+        <v>55.1668</v>
+      </c>
+      <c r="E95" s="15" t="n">
+        <f aca="false">D95*(1+$B$96)</f>
+        <v>56.821804</v>
+      </c>
+      <c r="F95" s="15" t="n">
+        <f aca="false">E95*(1+$B$96)</f>
+        <v>58.52645812</v>
+      </c>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="B96" s="13" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C96" s="13" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D96" s="13" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E96" s="13" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F96" s="13" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="B97" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="C97" s="12" t="n">
+        <v>200</v>
+      </c>
+      <c r="D97" s="12" t="n">
+        <v>340</v>
+      </c>
+      <c r="E97" s="12" t="n">
+        <v>480</v>
+      </c>
+      <c r="F97" s="12" t="n">
+        <v>620</v>
+      </c>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2"/>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="B98" s="13" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="C98" s="13" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="D98" s="13" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="E98" s="13" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F98" s="13" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="B99" s="9" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C99" s="9" t="n">
+        <v>22000</v>
+      </c>
+      <c r="D99" s="9" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E99" s="9" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F99" s="9" t="n">
+        <v>22000</v>
+      </c>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2"/>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="18" t="s">
+        <v>407</v>
+      </c>
+      <c r="B100" s="9" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C100" s="9" t="n">
+        <v>54000</v>
+      </c>
+      <c r="D100" s="9" t="n">
+        <v>191000</v>
+      </c>
+      <c r="E100" s="9" t="n">
+        <v>265000</v>
+      </c>
+      <c r="F100" s="9" t="n">
+        <v>290000</v>
+      </c>
+      <c r="G100" s="2"/>
+      <c r="H100" s="7" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="41" t="s">
+        <v>409</v>
+      </c>
+      <c r="B101" s="42"/>
+      <c r="C101" s="42"/>
+      <c r="D101" s="42"/>
+      <c r="E101" s="42"/>
+      <c r="F101" s="42"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="42"/>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="18" t="s">
+        <v>410</v>
+      </c>
+      <c r="B102" s="19" t="n">
+        <f aca="false">B92*Assumptions!$B$8*12</f>
+        <v>378</v>
+      </c>
+      <c r="C102" s="19" t="n">
+        <f aca="false">C92*Assumptions!$B$8*12</f>
+        <v>630</v>
+      </c>
+      <c r="D102" s="19" t="n">
+        <f aca="false">D92*Assumptions!$B$8*12</f>
+        <v>882</v>
+      </c>
+      <c r="E102" s="19" t="n">
+        <f aca="false">E92*Assumptions!$B$8*12</f>
+        <v>1008</v>
+      </c>
+      <c r="F102" s="19" t="n">
+        <f aca="false">F92*Assumptions!$B$8*12</f>
+        <v>1134</v>
+      </c>
+      <c r="G102" s="2"/>
+      <c r="H102" s="2"/>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="16" t="s">
+        <v>411</v>
+      </c>
+      <c r="B103" s="20" t="n">
+        <f aca="false">B102*B93*B94</f>
+        <v>15422.4</v>
+      </c>
+      <c r="C103" s="20" t="n">
+        <f aca="false">C102*C93*C94</f>
+        <v>28728</v>
+      </c>
+      <c r="D103" s="20" t="n">
+        <f aca="false">D102*D93*D94</f>
+        <v>40219.2</v>
+      </c>
+      <c r="E103" s="20" t="n">
+        <f aca="false">E102*E93*E94</f>
+        <v>45964.8</v>
+      </c>
+      <c r="F103" s="20" t="n">
+        <f aca="false">F102*F93*F94</f>
+        <v>51710.4</v>
+      </c>
+      <c r="G103" s="2"/>
+      <c r="H103" s="2"/>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="B104" s="15" t="n">
+        <f aca="false">B103*B95</f>
+        <v>801964.8</v>
+      </c>
+      <c r="C104" s="15" t="n">
+        <f aca="false">C103*C95</f>
+        <v>1538671.68</v>
+      </c>
+      <c r="D104" s="15" t="n">
+        <f aca="false">D103*D95</f>
+        <v>2218764.56256</v>
+      </c>
+      <c r="E104" s="15" t="n">
+        <f aca="false">E103*E95</f>
+        <v>2611802.8564992</v>
+      </c>
+      <c r="F104" s="15" t="n">
+        <f aca="false">F103*F95</f>
+        <v>3026426.55996845</v>
+      </c>
+      <c r="G104" s="2"/>
+      <c r="H104" s="2"/>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="18" t="s">
+        <v>413</v>
+      </c>
+      <c r="B105" s="15" t="n">
+        <f aca="false">B102*(1-B93)*Assumptions!$B$10</f>
+        <v>56700</v>
+      </c>
+      <c r="C105" s="15" t="n">
+        <f aca="false">C102*(1-C93)*Assumptions!$B$10</f>
+        <v>31500</v>
+      </c>
+      <c r="D105" s="15" t="n">
+        <f aca="false">D102*(1-D93)*Assumptions!$B$10</f>
+        <v>44100</v>
+      </c>
+      <c r="E105" s="15" t="n">
+        <f aca="false">E102*(1-E93)*Assumptions!$B$10</f>
+        <v>50400.0000000001</v>
+      </c>
+      <c r="F105" s="15" t="n">
+        <f aca="false">F102*(1-F93)*Assumptions!$B$10</f>
+        <v>56700.0000000001</v>
+      </c>
+      <c r="G105" s="2"/>
+      <c r="H105" s="2"/>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="18" t="s">
+        <v>322</v>
+      </c>
+      <c r="B106" s="15" t="n">
+        <f aca="false">B97*Assumptions!$B$28/Assumptions!$B$29</f>
+        <v>22410</v>
+      </c>
+      <c r="C106" s="15" t="n">
+        <f aca="false">C97*Assumptions!$B$28/Assumptions!$B$29</f>
+        <v>49800</v>
+      </c>
+      <c r="D106" s="15" t="n">
+        <f aca="false">D97*Assumptions!$B$28/Assumptions!$B$29</f>
+        <v>84660</v>
+      </c>
+      <c r="E106" s="15" t="n">
+        <f aca="false">E97*Assumptions!$B$28/Assumptions!$B$29</f>
+        <v>119520</v>
+      </c>
+      <c r="F106" s="15" t="n">
+        <f aca="false">F97*Assumptions!$B$28/Assumptions!$B$29</f>
+        <v>154380</v>
+      </c>
+      <c r="G106" s="2"/>
+      <c r="H106" s="2"/>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="B107" s="23" t="n">
+        <f aca="false">B104+B105+B106</f>
+        <v>881074.8</v>
+      </c>
+      <c r="C107" s="23" t="n">
+        <f aca="false">C104+C105+C106</f>
+        <v>1619971.68</v>
+      </c>
+      <c r="D107" s="23" t="n">
+        <f aca="false">D104+D105+D106</f>
+        <v>2347524.56256</v>
+      </c>
+      <c r="E107" s="23" t="n">
+        <f aca="false">E104+E105+E106</f>
+        <v>2781722.8564992</v>
+      </c>
+      <c r="F107" s="23" t="n">
+        <f aca="false">F104+F105+F106</f>
+        <v>3237506.55996845</v>
+      </c>
+      <c r="G107" s="2"/>
+      <c r="H107" s="2"/>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="18" t="s">
+        <v>414</v>
+      </c>
+      <c r="B108" s="15" t="n">
+        <f aca="false">B92*(Assumptions!$B$24*Assumptions!$B$25*Assumptions!$B$21+Assumptions!$B$25*Assumptions!$B$22)*(1+Assumptions!$B$23)*12*1.03^MAX(0,COLUMN(B1)-2)</f>
+        <v>250272.18</v>
+      </c>
+      <c r="C108" s="15" t="n">
+        <f aca="false">C92*(Assumptions!$B$24*Assumptions!$B$25*Assumptions!$B$21+Assumptions!$B$25*Assumptions!$B$22)*(1+Assumptions!$B$23)*12*1.03^MAX(0,COLUMN(C1)-2)</f>
+        <v>429633.909</v>
+      </c>
+      <c r="D108" s="15" t="n">
+        <f aca="false">D92*(Assumptions!$B$24*Assumptions!$B$25*Assumptions!$B$21+Assumptions!$B$25*Assumptions!$B$22)*(1+Assumptions!$B$23)*12*1.03^MAX(0,COLUMN(D1)-2)</f>
+        <v>619532.096778</v>
+      </c>
+      <c r="E108" s="15" t="n">
+        <f aca="false">E92*(Assumptions!$B$24*Assumptions!$B$25*Assumptions!$B$21+Assumptions!$B$25*Assumptions!$B$22)*(1+Assumptions!$B$23)*12*1.03^MAX(0,COLUMN(E1)-2)</f>
+        <v>729277.78249296</v>
+      </c>
+      <c r="F108" s="15" t="n">
+        <f aca="false">F92*(Assumptions!$B$24*Assumptions!$B$25*Assumptions!$B$21+Assumptions!$B$25*Assumptions!$B$22)*(1+Assumptions!$B$23)*12*1.03^MAX(0,COLUMN(F1)-2)</f>
+        <v>845050.630463718</v>
+      </c>
+      <c r="G108" s="2"/>
+      <c r="H108" s="2"/>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="18" t="s">
+        <v>415</v>
+      </c>
+      <c r="B109" s="15" t="n">
+        <f aca="false">(B104+B105)*Assumptions!$B$20+B97/Assumptions!$B$29*Assumptions!$B$34</f>
+        <v>178032.96</v>
+      </c>
+      <c r="C109" s="15" t="n">
+        <f aca="false">(C104+C105)*Assumptions!$B$20+C97/Assumptions!$B$29*Assumptions!$B$34</f>
+        <v>328034.336</v>
+      </c>
+      <c r="D109" s="15" t="n">
+        <f aca="false">(D104+D105)*Assumptions!$B$20+D97/Assumptions!$B$29*Assumptions!$B$34</f>
+        <v>476372.912512</v>
+      </c>
+      <c r="E109" s="15" t="n">
+        <f aca="false">(E104+E105)*Assumptions!$B$20+E97/Assumptions!$B$29*Assumptions!$B$34</f>
+        <v>566040.57129984</v>
+      </c>
+      <c r="F109" s="15" t="n">
+        <f aca="false">(F104+F105)*Assumptions!$B$20+F97/Assumptions!$B$29*Assumptions!$B$34</f>
+        <v>660025.31199369</v>
+      </c>
+      <c r="G109" s="2"/>
+      <c r="H109" s="2"/>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B110" s="23" t="n">
+        <f aca="false">B107-B108-B109</f>
+        <v>452769.66</v>
+      </c>
+      <c r="C110" s="23" t="n">
+        <f aca="false">C107-C108-C109</f>
+        <v>862303.435</v>
+      </c>
+      <c r="D110" s="23" t="n">
+        <f aca="false">D107-D108-D109</f>
+        <v>1251619.55327</v>
+      </c>
+      <c r="E110" s="23" t="n">
+        <f aca="false">E107-E108-E109</f>
+        <v>1486404.5027064</v>
+      </c>
+      <c r="F110" s="23" t="n">
+        <f aca="false">F107-F108-F109</f>
+        <v>1732430.61751104</v>
+      </c>
+      <c r="G110" s="2"/>
+      <c r="H110" s="2"/>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="B111" s="21" t="n">
+        <f aca="false">IF(B107=0,0,B110/B107)</f>
+        <v>0.513883338849324</v>
+      </c>
+      <c r="C111" s="21" t="n">
+        <f aca="false">IF(C107=0,0,C110/C107)</f>
+        <v>0.532295376299418</v>
+      </c>
+      <c r="D111" s="21" t="n">
+        <f aca="false">IF(D107=0,0,D110/D107)</f>
+        <v>0.533165690034398</v>
+      </c>
+      <c r="E111" s="21" t="n">
+        <f aca="false">IF(E107=0,0,E110/E107)</f>
+        <v>0.53434672660994</v>
+      </c>
+      <c r="F111" s="21" t="n">
+        <f aca="false">IF(F107=0,0,F110/F107)</f>
+        <v>0.535112619981201</v>
+      </c>
+      <c r="G111" s="2"/>
+      <c r="H111" s="2"/>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="18" t="s">
+        <v>416</v>
+      </c>
+      <c r="B112" s="15" t="n">
+        <f aca="false">(Assumptions!$B$55+Assumptions!$B$57+Assumptions!$B$58+Assumptions!$B$59+Assumptions!$B$60)*12+B92*B99+B100+B107*B98+Assumptions!$B$61*Assumptions!$B$62*12+'Equipment plan'!$H$10*12*MAX(0,B92-1)</f>
+        <v>231948.52055448</v>
+      </c>
+      <c r="C112" s="15" t="n">
+        <f aca="false">(Assumptions!$B$55+Assumptions!$B$57+Assumptions!$B$58+Assumptions!$B$59+Assumptions!$B$60)*12+C92*C99+C100+C107*C98+Assumptions!$B$61*Assumptions!$B$62*12+'Equipment plan'!$H$10*12*MAX(0,C92-1)</f>
+        <v>356799.18926344</v>
+      </c>
+      <c r="D112" s="15" t="n">
+        <f aca="false">(Assumptions!$B$55+Assumptions!$B$57+Assumptions!$B$58+Assumptions!$B$59+Assumptions!$B$60)*12+D92*D99+D100+D107*D98+Assumptions!$B$61*Assumptions!$B$62*12+'Equipment plan'!$H$10*12*MAX(0,D92-1)</f>
+        <v>576139.378087601</v>
+      </c>
+      <c r="E112" s="15" t="n">
+        <f aca="false">(Assumptions!$B$55+Assumptions!$B$57+Assumptions!$B$58+Assumptions!$B$59+Assumptions!$B$60)*12+E92*E99+E100+E107*E98+Assumptions!$B$61*Assumptions!$B$62*12+'Equipment plan'!$H$10*12*MAX(0,E92-1)</f>
+        <v>694478.455869345</v>
+      </c>
+      <c r="F112" s="15" t="n">
+        <f aca="false">(Assumptions!$B$55+Assumptions!$B$57+Assumptions!$B$58+Assumptions!$B$59+Assumptions!$B$60)*12+F92*F99+F100+F107*F98+Assumptions!$B$61*Assumptions!$B$62*12+'Equipment plan'!$H$10*12*MAX(0,F92-1)</f>
+        <v>764788.877079941</v>
+      </c>
+      <c r="G112" s="2"/>
+      <c r="H112" s="7" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="16" t="s">
+        <v>418</v>
+      </c>
+      <c r="B113" s="23" t="n">
+        <f aca="false">B110-B112</f>
+        <v>220821.13944552</v>
+      </c>
+      <c r="C113" s="23" t="n">
+        <f aca="false">C110-C112</f>
+        <v>505504.24573656</v>
+      </c>
+      <c r="D113" s="23" t="n">
+        <f aca="false">D110-D112</f>
+        <v>675480.175182399</v>
+      </c>
+      <c r="E113" s="23" t="n">
+        <f aca="false">E110-E112</f>
+        <v>791926.046837055</v>
+      </c>
+      <c r="F113" s="23" t="n">
+        <f aca="false">F110-F112</f>
+        <v>967641.740431099</v>
+      </c>
+      <c r="G113" s="2"/>
+      <c r="H113" s="2"/>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="B114" s="9" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C114" s="9" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D114" s="9" t="n">
+        <v>66000</v>
+      </c>
+      <c r="E114" s="9" t="n">
+        <v>72000</v>
+      </c>
+      <c r="F114" s="9" t="n">
+        <v>72000</v>
+      </c>
+      <c r="G114" s="2"/>
+      <c r="H114" s="7" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="18" t="s">
+        <v>421</v>
+      </c>
+      <c r="B115" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C115" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D115" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E115" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F115" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G115" s="2"/>
+      <c r="H115" s="7" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="18" t="s">
+        <v>423</v>
+      </c>
+      <c r="B116" s="15" t="n">
+        <f aca="false">B114+IF(B114=0,0,B115*MAX(0,B113-MAX(0,'5-year plan'!$B$44)))</f>
+        <v>82082.113944552</v>
+      </c>
+      <c r="C116" s="15" t="n">
+        <f aca="false">C114+IF(C114=0,0,C115*MAX(0,C113-MAX(0,'5-year plan'!$B$44)))</f>
+        <v>110550.424573656</v>
+      </c>
+      <c r="D116" s="15" t="n">
+        <f aca="false">D114+IF(D114=0,0,D115*MAX(0,D113-MAX(0,'5-year plan'!$B$44)))</f>
+        <v>133548.01751824</v>
+      </c>
+      <c r="E116" s="15" t="n">
+        <f aca="false">E114+IF(E114=0,0,E115*MAX(0,E113-MAX(0,'5-year plan'!$B$44)))</f>
+        <v>151192.604683706</v>
+      </c>
+      <c r="F116" s="15" t="n">
+        <f aca="false">F114+IF(F114=0,0,F115*MAX(0,F113-MAX(0,'5-year plan'!$B$44)))</f>
+        <v>168764.17404311</v>
+      </c>
+      <c r="G116" s="2"/>
+      <c r="H116" s="2"/>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="16" t="s">
+        <v>424</v>
+      </c>
+      <c r="B117" s="23" t="n">
+        <f aca="false">B113-B116</f>
+        <v>138739.025500968</v>
+      </c>
+      <c r="C117" s="23" t="n">
+        <f aca="false">C113-C116</f>
+        <v>394953.821162904</v>
+      </c>
+      <c r="D117" s="23" t="n">
+        <f aca="false">D113-D116</f>
+        <v>541932.157664159</v>
+      </c>
+      <c r="E117" s="23" t="n">
+        <f aca="false">E113-E116</f>
+        <v>640733.442153349</v>
+      </c>
+      <c r="F117" s="23" t="n">
+        <f aca="false">F113-F116</f>
+        <v>798877.56638799</v>
+      </c>
+      <c r="G117" s="2"/>
+      <c r="H117" s="2"/>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="18" t="s">
+        <v>425</v>
+      </c>
+      <c r="B118" s="21" t="n">
+        <f aca="false">IF(B107=0,0,B117/B107)</f>
+        <v>0.157465660691882</v>
+      </c>
+      <c r="C118" s="21" t="n">
+        <f aca="false">IF(C107=0,0,C117/C107)</f>
+        <v>0.243802917075009</v>
+      </c>
+      <c r="D118" s="21" t="n">
+        <f aca="false">IF(D107=0,0,D117/D107)</f>
+        <v>0.230852603762824</v>
+      </c>
+      <c r="E118" s="21" t="n">
+        <f aca="false">IF(E107=0,0,E117/E107)</f>
+        <v>0.23033690817054</v>
+      </c>
+      <c r="F118" s="21" t="n">
+        <f aca="false">IF(F107=0,0,F117/F107)</f>
+        <v>0.246757049473214</v>
+      </c>
+      <c r="G118" s="2"/>
+      <c r="H118" s="2"/>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="18" t="s">
+        <v>426</v>
+      </c>
+      <c r="B119" s="15" t="n">
+        <f aca="false">MAX(0,B92-1)*'Equipment plan'!$G$10</f>
+        <v>13850</v>
+      </c>
+      <c r="C119" s="15" t="n">
+        <f aca="false">MAX(0,C92-B92)*'Equipment plan'!$G$10</f>
+        <v>27700</v>
+      </c>
+      <c r="D119" s="15" t="n">
+        <f aca="false">MAX(0,D92-C92)*'Equipment plan'!$G$10</f>
+        <v>27700</v>
+      </c>
+      <c r="E119" s="15" t="n">
+        <f aca="false">MAX(0,E92-D92)*'Equipment plan'!$G$10</f>
+        <v>13850</v>
+      </c>
+      <c r="F119" s="15" t="n">
+        <f aca="false">MAX(0,F92-E92)*'Equipment plan'!$G$10</f>
+        <v>13850</v>
+      </c>
+      <c r="G119" s="2"/>
+      <c r="H119" s="2"/>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="B120" s="23" t="n">
+        <f aca="false">Assumptions!$B$39+B117-B119</f>
+        <v>149889.025500968</v>
+      </c>
+      <c r="C120" s="23" t="n">
+        <f aca="false">B120+C117-C119</f>
+        <v>517142.846663872</v>
+      </c>
+      <c r="D120" s="23" t="n">
+        <f aca="false">C120+D117-D119</f>
+        <v>1031375.00432803</v>
+      </c>
+      <c r="E120" s="23" t="n">
+        <f aca="false">D120+E117-E119</f>
+        <v>1658258.44648138</v>
+      </c>
+      <c r="F120" s="23" t="n">
+        <f aca="false">E120+F117-F119</f>
+        <v>2443286.01286937</v>
+      </c>
+      <c r="G120" s="2"/>
+      <c r="H120" s="7" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="18" t="s">
+        <v>429</v>
+      </c>
+      <c r="B121" s="15" t="n">
+        <f aca="false">B117+Assumptions!$B$55*12</f>
+        <v>210739.025500968</v>
+      </c>
+      <c r="C121" s="15" t="n">
+        <f aca="false">C117+Assumptions!$B$55*12</f>
+        <v>466953.821162904</v>
+      </c>
+      <c r="D121" s="15" t="n">
+        <f aca="false">D117+Assumptions!$B$55*12</f>
+        <v>613932.157664159</v>
+      </c>
+      <c r="E121" s="15" t="n">
+        <f aca="false">E117+Assumptions!$B$55*12</f>
+        <v>712733.442153349</v>
+      </c>
+      <c r="F121" s="15" t="n">
+        <f aca="false">F117+Assumptions!$B$55*12</f>
+        <v>870877.56638799</v>
+      </c>
+      <c r="G121" s="2"/>
+      <c r="H121" s="2"/>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="18" t="s">
+        <v>430</v>
+      </c>
+      <c r="B122" s="15" t="n">
+        <f aca="false">MAX(0,B121)*2.46</f>
+        <v>518418.002732381</v>
+      </c>
+      <c r="C122" s="15" t="n">
+        <f aca="false">MAX(0,C121)*2.46</f>
+        <v>1148706.40006074</v>
+      </c>
+      <c r="D122" s="15" t="n">
+        <f aca="false">MAX(0,D121)*2.46</f>
+        <v>1510273.10785383</v>
+      </c>
+      <c r="E122" s="15" t="n">
+        <f aca="false">MAX(0,E121)*2.46</f>
+        <v>1753324.26769724</v>
+      </c>
+      <c r="F122" s="15" t="n">
+        <f aca="false">MAX(0,F121)*2.46</f>
+        <v>2142358.81331445</v>
+      </c>
+      <c r="G122" s="2"/>
+      <c r="H122" s="7" t="s">
+        <v>431</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="true" password="ef11" formatCells="false" formatColumns="false" formatRows="false"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:B15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -12123,7 +15202,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>436</v>
       </c>
       <c r="B1" s="2"/>
     </row>
@@ -12132,107 +15211,107 @@
       <c r="B2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="39" t="s">
-        <v>378</v>
-      </c>
-      <c r="B3" s="40" t="s">
-        <v>379</v>
+      <c r="A3" s="43" t="s">
+        <v>437</v>
+      </c>
+      <c r="B3" s="44" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="39" t="s">
-        <v>380</v>
-      </c>
-      <c r="B4" s="40" t="s">
-        <v>381</v>
+      <c r="A4" s="43" t="s">
+        <v>439</v>
+      </c>
+      <c r="B4" s="44" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="39" t="s">
-        <v>382</v>
-      </c>
-      <c r="B5" s="40" t="s">
-        <v>383</v>
+      <c r="A5" s="43" t="s">
+        <v>441</v>
+      </c>
+      <c r="B5" s="44" t="s">
+        <v>442</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="39" t="s">
-        <v>384</v>
-      </c>
-      <c r="B6" s="40" t="s">
-        <v>385</v>
+      <c r="A6" s="43" t="s">
+        <v>443</v>
+      </c>
+      <c r="B6" s="44" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="39" t="s">
-        <v>386</v>
-      </c>
-      <c r="B7" s="40" t="s">
-        <v>387</v>
+      <c r="A7" s="43" t="s">
+        <v>445</v>
+      </c>
+      <c r="B7" s="44" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="39" t="s">
-        <v>388</v>
-      </c>
-      <c r="B8" s="40" t="s">
-        <v>389</v>
+      <c r="A8" s="43" t="s">
+        <v>447</v>
+      </c>
+      <c r="B8" s="44" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="39" t="s">
-        <v>390</v>
-      </c>
-      <c r="B9" s="40" t="s">
-        <v>391</v>
+      <c r="A9" s="43" t="s">
+        <v>449</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="39" t="s">
-        <v>392</v>
-      </c>
-      <c r="B10" s="40" t="s">
-        <v>393</v>
+      <c r="A10" s="43" t="s">
+        <v>451</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="39" t="s">
-        <v>394</v>
-      </c>
-      <c r="B11" s="40" t="s">
-        <v>395</v>
+      <c r="A11" s="43" t="s">
+        <v>453</v>
+      </c>
+      <c r="B11" s="44" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="39" t="s">
-        <v>396</v>
-      </c>
-      <c r="B12" s="40" t="s">
-        <v>397</v>
+      <c r="A12" s="43" t="s">
+        <v>455</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="39" t="s">
-        <v>398</v>
-      </c>
-      <c r="B13" s="40" t="s">
-        <v>399</v>
+      <c r="A13" s="43" t="s">
+        <v>457</v>
+      </c>
+      <c r="B13" s="44" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="39" t="s">
-        <v>400</v>
-      </c>
-      <c r="B14" s="40" t="s">
-        <v>401</v>
+      <c r="A14" s="43" t="s">
+        <v>459</v>
+      </c>
+      <c r="B14" s="44" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="39" t="s">
-        <v>402</v>
-      </c>
-      <c r="B15" s="40" t="s">
-        <v>403</v>
+      <c r="A15" s="43" t="s">
+        <v>461</v>
+      </c>
+      <c r="B15" s="44" t="s">
+        <v>462</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Scag-Scapes-Proforma.xlsx
+++ b/docs/Scag-Scapes-Proforma.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="560">
   <si>
     <t xml:space="preserve">Scag Scapes LLC - Growth Proforma - Assumptions</t>
   </si>
@@ -1335,25 +1335,19 @@
     <t xml:space="preserve">WORST CASE - most of it does not work</t>
   </si>
   <si>
-    <t xml:space="preserve">Leads cost more and close worse, crews never beat 36 LF a day, Crew 2 slips to the middle of year 2, few plans attach. The 90-day gate is missed, so the growth lead is ended after three months (that is the $15,000 in year 1 - the whole exposure) and no share is ever earned. The company then looks much like it does today: it covers itself and pays the owner, and it does not run away from anyone.</t>
+    <t xml:space="preserve">Both crews still launch together in month 1 on the initial investment, but leads cost more, close worse, and crews never beat 36 LF a day - few plans attach. The 90-day gate is missed, so the growth lead is ended after three months (that is the $15,000 in year 1 - the whole exposure) and no share is ever earned. The company still runs two full crews on drains; it just runs them at a lower gear than Charlie's target.</t>
   </si>
   <si>
     <t xml:space="preserve">Drivers - change any blue cell</t>
   </si>
   <si>
-    <t xml:space="preserve">Half a crew = started mid-year. A crew is added only after three months at target, backlog over four weeks and cash above two months of overhead.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of crew days on drainage (the rest is pads, fences, sod, patios)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Today one crew spends about 42% of its days on drain feet. Filling the calendar is the whole growth engine.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LF a crew installs per working day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charlie's target is 43 (900 LF / 21 days).</t>
+    <t xml:space="preserve">Both crews launch together in year 1, funded by the initial investment. A third or fourth crew is added only after the last one runs at target for three months, backlog over four weeks and cash above two months of overhead - half a crew = started mid-year.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LF a crew installs per working day - 100% on french drains</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charlie's target is 43 (900 LF / 21 days). No other work is modeled - every working day is a drain day.</t>
   </si>
   <si>
     <t xml:space="preserve">Annual price change from year 2</t>
@@ -1443,13 +1437,13 @@
     <t xml:space="preserve">CONSERVATIVE - the plan in the blueprint</t>
   </si>
   <si>
-    <t xml:space="preserve">Charlie's own targets on the blueprint's schedule: 900 LF a crew a month, 70% close on estimates, 60% plan close, Crew 3 in year 3 and Crew 4 in year 4 - each only after its gate. This is an annual approximation of the 24-month proforma and lands within about 4% of it.</t>
+    <t xml:space="preserve">Two crews at Charlie's own target from month 1: 900 LF a crew a month, 70% close on estimates, 60% plan close, Crew 3 in year 3 and Crew 4 in year 4 - each only after its gate. This is an annual approximation of the 24-month proforma and lands within about 4% of it.</t>
   </si>
   <si>
     <t xml:space="preserve">STRONG - the levers work</t>
   </si>
   <si>
-    <t xml:space="preserve">Reviews, referrals and the Moasure map support a 3% price step each year, crews settle at 48 LF a day, the plan book compounds and HOA / property-manager work fills the winter. Note the gross margin runs above Charlie's 50% rule - that is what productivity does to a fixed crew cost.</t>
+    <t xml:space="preserve">Reviews, referrals and the Moasure map support a 3% price step each year, crews settle at 48 LF a day, the plan book compounds and HOA / property-manager work fills the winter faster than the base case. Note the gross margin runs above Charlie's 50% rule - that is what productivity does to a fixed crew cost.</t>
   </si>
   <si>
     <t xml:space="preserve">The long view - the same roadmap run out fifteen years</t>
@@ -1507,9 +1501,6 @@
   </si>
   <si>
     <t xml:space="preserve">Years 1-5 from the five-year plan; after that the rate and the ceiling are both blue cells on Assumptions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LF a crew installs per working day - 100% on french drains</t>
   </si>
   <si>
     <t xml:space="preserve">Held flat at Charlie's target. Every working day is a drain day - no other work is modeled.</t>
@@ -12663,7 +12654,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H119"/>
+  <dimension ref="A1:H116"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="52"/>
@@ -12739,16 +12730,16 @@
         <v>421</v>
       </c>
       <c r="B6" s="17" t="n">
-        <f aca="false">B38</f>
-        <v>443859.75</v>
+        <f aca="false">B37</f>
+        <v>879315.75</v>
       </c>
       <c r="C6" s="17" t="n">
-        <f aca="false">B71</f>
-        <v>830254.5</v>
+        <f aca="false">B69</f>
+        <v>1101154.5</v>
       </c>
       <c r="D6" s="17" t="n">
-        <f aca="false">B104</f>
-        <v>967765.5</v>
+        <f aca="false">B101</f>
+        <v>1282261.5</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -12760,16 +12751,16 @@
         <v>422</v>
       </c>
       <c r="B7" s="17" t="n">
-        <f aca="false">F38</f>
-        <v>699871.5</v>
+        <f aca="false">F37</f>
+        <v>1135327.5</v>
       </c>
       <c r="C7" s="17" t="n">
-        <f aca="false">F71</f>
+        <f aca="false">F69</f>
         <v>2578331.443032</v>
       </c>
       <c r="D7" s="17" t="n">
-        <f aca="false">F104</f>
-        <v>3363124.66838784</v>
+        <f aca="false">F101</f>
+        <v>3717092.6870976</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -12781,16 +12772,16 @@
         <v>423</v>
       </c>
       <c r="B8" s="21" t="n">
-        <f aca="false">F35</f>
-        <v>13608</v>
+        <f aca="false">F34</f>
+        <v>22680</v>
       </c>
       <c r="C8" s="21" t="n">
-        <f aca="false">F68</f>
+        <f aca="false">F66</f>
         <v>43344</v>
       </c>
       <c r="D8" s="21" t="n">
-        <f aca="false">F101</f>
-        <v>54432</v>
+        <f aca="false">F98</f>
+        <v>60480</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -12802,16 +12793,16 @@
         <v>424</v>
       </c>
       <c r="B9" s="23" t="n">
-        <f aca="false">F42</f>
-        <v>0.392109346518745</v>
+        <f aca="false">F41</f>
+        <v>0.383151053348181</v>
       </c>
       <c r="C9" s="23" t="n">
-        <f aca="false">F75</f>
+        <f aca="false">F73</f>
         <v>0.504288264401278</v>
       </c>
       <c r="D9" s="23" t="n">
-        <f aca="false">F108</f>
-        <v>0.544451004584465</v>
+        <f aca="false">F105</f>
+        <v>0.543525995929879</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -12823,16 +12814,16 @@
         <v>425</v>
       </c>
       <c r="B10" s="17" t="n">
-        <f aca="false">B44</f>
-        <v>-3231.55125000002</v>
+        <f aca="false">B43</f>
+        <v>94025.6196410397</v>
       </c>
       <c r="C10" s="17" t="n">
-        <f aca="false">B77</f>
-        <v>190694.44044552</v>
+        <f aca="false">B75</f>
+        <v>285645.22589104</v>
       </c>
       <c r="D10" s="17" t="n">
-        <f aca="false">B110</f>
-        <v>286121.11794552</v>
+        <f aca="false">B107</f>
+        <v>415341.38339104</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -12844,16 +12835,16 @@
         <v>426</v>
       </c>
       <c r="B11" s="24" t="n">
-        <f aca="false">B48</f>
-        <v>-18231.55125</v>
+        <f aca="false">B47</f>
+        <v>69623.0576769357</v>
       </c>
       <c r="C11" s="24" t="n">
-        <f aca="false">B81</f>
-        <v>111624.996400968</v>
+        <f aca="false">B79</f>
+        <v>197080.703301936</v>
       </c>
       <c r="D11" s="24" t="n">
-        <f aca="false">B114</f>
-        <v>197509.006150968</v>
+        <f aca="false">B111</f>
+        <v>313807.245051936</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -12865,16 +12856,16 @@
         <v>427</v>
       </c>
       <c r="B12" s="24" t="n">
-        <f aca="false">F48</f>
-        <v>-5364.36054238601</v>
+        <f aca="false">F47</f>
+        <v>70951.9013567164</v>
       </c>
       <c r="C12" s="24" t="n">
-        <f aca="false">F81</f>
+        <f aca="false">F79</f>
         <v>528304.310081433</v>
       </c>
       <c r="D12" s="24" t="n">
-        <f aca="false">F114</f>
-        <v>882553.421058966</v>
+        <f aca="false">F111</f>
+        <v>1016249.48762684</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -12886,16 +12877,16 @@
         <v>428</v>
       </c>
       <c r="B13" s="17" t="n">
-        <f aca="false">B47</f>
-        <v>15000</v>
+        <f aca="false">B46</f>
+        <v>24402.561964104</v>
       </c>
       <c r="C13" s="17" t="n">
-        <f aca="false">B80</f>
-        <v>79069.444044552</v>
+        <f aca="false">B78</f>
+        <v>88564.522589104</v>
       </c>
       <c r="D13" s="17" t="n">
-        <f aca="false">B113</f>
-        <v>88612.111794552</v>
+        <f aca="false">B110</f>
+        <v>101534.138339104</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -12907,16 +12898,16 @@
         <v>429</v>
       </c>
       <c r="B14" s="17" t="n">
-        <f aca="false">F47</f>
+        <f aca="false">F46</f>
         <v>0</v>
       </c>
       <c r="C14" s="17" t="n">
-        <f aca="false">F80</f>
+        <f aca="false">F78</f>
         <v>138700.478897937</v>
       </c>
       <c r="D14" s="17" t="n">
-        <f aca="false">F113</f>
-        <v>178061.491228774</v>
+        <f aca="false">F110</f>
+        <v>192916.609736316</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -12928,16 +12919,16 @@
         <v>430</v>
       </c>
       <c r="B15" s="24" t="n">
-        <f aca="false">F52</f>
-        <v>66635.639457614</v>
+        <f aca="false">F51</f>
+        <v>142951.901356716</v>
       </c>
       <c r="C15" s="24" t="n">
-        <f aca="false">F85</f>
+        <f aca="false">F83</f>
         <v>600304.310081433</v>
       </c>
       <c r="D15" s="24" t="n">
-        <f aca="false">F118</f>
-        <v>954553.421058966</v>
+        <f aca="false">F115</f>
+        <v>1088249.48762684</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
@@ -12949,16 +12940,16 @@
         <v>431</v>
       </c>
       <c r="B16" s="17" t="n">
-        <f aca="false">F51</f>
-        <v>2938.16005179359</v>
+        <f aca="false">F50</f>
+        <v>356994.663628191</v>
       </c>
       <c r="C16" s="17" t="n">
-        <f aca="false">F84</f>
-        <v>1414423.42297337</v>
+        <f aca="false">F82</f>
+        <v>1499879.12987434</v>
       </c>
       <c r="D16" s="17" t="n">
-        <f aca="false">F117</f>
-        <v>2746020.81175933</v>
+        <f aca="false">F114</f>
+        <v>3356513.91082809</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -12970,16 +12961,16 @@
         <v>432</v>
       </c>
       <c r="B17" s="24" t="n">
-        <f aca="false">F53</f>
-        <v>163923.67306573</v>
+        <f aca="false">F52</f>
+        <v>351661.677337522</v>
       </c>
       <c r="C17" s="24" t="n">
-        <f aca="false">F86</f>
+        <f aca="false">F84</f>
         <v>1476748.60280033</v>
       </c>
       <c r="D17" s="24" t="n">
-        <f aca="false">F119</f>
-        <v>2348201.41580506</v>
+        <f aca="false">F116</f>
+        <v>2677093.73956204</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -13069,19 +13060,19 @@
         <v>351</v>
       </c>
       <c r="B24" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" s="34" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E24" s="34" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F24" s="34" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="8" t="s">
@@ -13092,20 +13083,20 @@
       <c r="A25" s="20" t="s">
         <v>438</v>
       </c>
-      <c r="B25" s="14" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="C25" s="14" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D25" s="14" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E25" s="14" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="F25" s="14" t="n">
-        <v>0.85</v>
+      <c r="B25" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>36</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="8" t="s">
@@ -13114,495 +13105,495 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>440</v>
-      </c>
-      <c r="B26" s="13" t="n">
-        <v>36</v>
-      </c>
-      <c r="C26" s="13" t="n">
-        <v>36</v>
-      </c>
-      <c r="D26" s="13" t="n">
-        <v>36</v>
-      </c>
-      <c r="E26" s="13" t="n">
-        <v>36</v>
-      </c>
-      <c r="F26" s="13" t="n">
-        <v>36</v>
+        <v>301</v>
+      </c>
+      <c r="B26" s="11" t="n">
+        <v>48</v>
+      </c>
+      <c r="C26" s="17" t="n">
+        <f aca="false">B26*(1+$B$27)</f>
+        <v>48</v>
+      </c>
+      <c r="D26" s="17" t="n">
+        <f aca="false">C26*(1+$B$27)</f>
+        <v>48</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <f aca="false">D26*(1+$B$27)</f>
+        <v>48</v>
+      </c>
+      <c r="F26" s="17" t="n">
+        <f aca="false">E26*(1+$B$27)</f>
+        <v>48</v>
       </c>
       <c r="G26" s="3"/>
-      <c r="H26" s="8" t="s">
-        <v>441</v>
-      </c>
+      <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="B27" s="11" t="n">
-        <v>48</v>
-      </c>
-      <c r="C27" s="17" t="n">
-        <f aca="false">B27*(1+$B$28)</f>
-        <v>48</v>
-      </c>
-      <c r="D27" s="17" t="n">
-        <f aca="false">C27*(1+$B$28)</f>
-        <v>48</v>
-      </c>
-      <c r="E27" s="17" t="n">
-        <f aca="false">D27*(1+$B$28)</f>
-        <v>48</v>
-      </c>
-      <c r="F27" s="17" t="n">
-        <f aca="false">E27*(1+$B$28)</f>
-        <v>48</v>
+        <v>440</v>
+      </c>
+      <c r="B27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="20" t="s">
-        <v>442</v>
-      </c>
-      <c r="B28" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="14" t="n">
-        <v>0</v>
+        <v>441</v>
+      </c>
+      <c r="B28" s="13" t="n">
+        <v>45</v>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>95</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>250</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="20" t="s">
-        <v>443</v>
-      </c>
-      <c r="B29" s="13" t="n">
-        <v>45</v>
-      </c>
-      <c r="C29" s="13" t="n">
-        <v>95</v>
-      </c>
-      <c r="D29" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="E29" s="13" t="n">
-        <v>200</v>
-      </c>
-      <c r="F29" s="13" t="n">
-        <v>250</v>
+        <v>442</v>
+      </c>
+      <c r="B29" s="14" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>0.075</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="20" t="s">
-        <v>444</v>
-      </c>
-      <c r="B30" s="14" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="C30" s="14" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="D30" s="14" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E30" s="14" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="F30" s="14" t="n">
-        <v>0.075</v>
+        <v>443</v>
+      </c>
+      <c r="B30" s="11" t="n">
+        <v>24000</v>
+      </c>
+      <c r="C30" s="11" t="n">
+        <v>24000</v>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>24000</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>24000</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="20" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B31" s="11" t="n">
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="D31" s="11" t="n">
         <v>24000</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>24000</v>
+        <v>42000</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>24000</v>
+        <v>44000</v>
       </c>
       <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
+      <c r="H31" s="8" t="s">
+        <v>445</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="20" t="s">
+      <c r="A32" s="42" t="s">
         <v>446</v>
       </c>
-      <c r="B32" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="11" t="n">
-        <v>24000</v>
-      </c>
-      <c r="E32" s="11" t="n">
-        <v>42000</v>
-      </c>
-      <c r="F32" s="11" t="n">
-        <v>44000</v>
-      </c>
+      <c r="B32" s="43"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="43"/>
       <c r="G32" s="3"/>
-      <c r="H32" s="8" t="s">
+      <c r="H32" s="43"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="42" t="s">
+      <c r="B33" s="21" t="n">
+        <f aca="false">B24*Assumptions!$B$10*12</f>
+        <v>504</v>
+      </c>
+      <c r="C33" s="21" t="n">
+        <f aca="false">C24*Assumptions!$B$10*12</f>
+        <v>504</v>
+      </c>
+      <c r="D33" s="21" t="n">
+        <f aca="false">D24*Assumptions!$B$10*12</f>
+        <v>504</v>
+      </c>
+      <c r="E33" s="21" t="n">
+        <f aca="false">E24*Assumptions!$B$10*12</f>
+        <v>630</v>
+      </c>
+      <c r="F33" s="21" t="n">
+        <f aca="false">F24*Assumptions!$B$10*12</f>
+        <v>630</v>
+      </c>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="18" t="s">
         <v>448</v>
       </c>
-      <c r="B33" s="43"/>
-      <c r="C33" s="43"/>
-      <c r="D33" s="43"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="43"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="43"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="20" t="s">
-        <v>449</v>
-      </c>
-      <c r="B34" s="21" t="n">
-        <f aca="false">B24*Assumptions!$B$10*12</f>
-        <v>252</v>
-      </c>
-      <c r="C34" s="21" t="n">
-        <f aca="false">C24*Assumptions!$B$10*12</f>
-        <v>252</v>
-      </c>
-      <c r="D34" s="21" t="n">
-        <f aca="false">D24*Assumptions!$B$10*12</f>
-        <v>378</v>
-      </c>
-      <c r="E34" s="21" t="n">
-        <f aca="false">E24*Assumptions!$B$10*12</f>
-        <v>378</v>
-      </c>
-      <c r="F34" s="21" t="n">
-        <f aca="false">F24*Assumptions!$B$10*12</f>
-        <v>378</v>
+      <c r="B34" s="22" t="n">
+        <f aca="false">B33*B25</f>
+        <v>18144</v>
+      </c>
+      <c r="C34" s="22" t="n">
+        <f aca="false">C33*C25</f>
+        <v>18144</v>
+      </c>
+      <c r="D34" s="22" t="n">
+        <f aca="false">D33*D25</f>
+        <v>18144</v>
+      </c>
+      <c r="E34" s="22" t="n">
+        <f aca="false">E33*E25</f>
+        <v>22680</v>
+      </c>
+      <c r="F34" s="22" t="n">
+        <f aca="false">F33*F25</f>
+        <v>22680</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="18" t="s">
-        <v>450</v>
-      </c>
-      <c r="B35" s="22" t="n">
+      <c r="A35" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="B35" s="17" t="n">
         <f aca="false">B34*B26</f>
-        <v>9072</v>
-      </c>
-      <c r="C35" s="22" t="n">
+        <v>870912</v>
+      </c>
+      <c r="C35" s="17" t="n">
         <f aca="false">C34*C26</f>
-        <v>9072</v>
-      </c>
-      <c r="D35" s="22" t="n">
+        <v>870912</v>
+      </c>
+      <c r="D35" s="17" t="n">
         <f aca="false">D34*D26</f>
-        <v>13608</v>
-      </c>
-      <c r="E35" s="22" t="n">
+        <v>870912</v>
+      </c>
+      <c r="E35" s="17" t="n">
         <f aca="false">E34*E26</f>
-        <v>13608</v>
-      </c>
-      <c r="F35" s="22" t="n">
+        <v>1088640</v>
+      </c>
+      <c r="F35" s="17" t="n">
         <f aca="false">F34*F26</f>
-        <v>13608</v>
+        <v>1088640</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="20" t="s">
-        <v>451</v>
+        <v>361</v>
       </c>
       <c r="B36" s="17" t="n">
-        <f aca="false">B35*B27</f>
-        <v>435456</v>
+        <f aca="false">B28*Assumptions!$B$30*Assumptions!$B$33</f>
+        <v>8403.75</v>
       </c>
       <c r="C36" s="17" t="n">
-        <f aca="false">C35*C27</f>
-        <v>435456</v>
+        <f aca="false">C28*Assumptions!$B$30*Assumptions!$B$33</f>
+        <v>17741.25</v>
       </c>
       <c r="D36" s="17" t="n">
-        <f aca="false">D35*D27</f>
-        <v>653184</v>
+        <f aca="false">D28*Assumptions!$B$30*Assumptions!$B$33</f>
+        <v>28012.5</v>
       </c>
       <c r="E36" s="17" t="n">
-        <f aca="false">E35*E27</f>
-        <v>653184</v>
+        <f aca="false">E28*Assumptions!$B$30*Assumptions!$B$33</f>
+        <v>37350</v>
       </c>
       <c r="F36" s="17" t="n">
-        <f aca="false">F35*F27</f>
-        <v>653184</v>
+        <f aca="false">F28*Assumptions!$B$30*Assumptions!$B$33</f>
+        <v>46687.5</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="20" t="s">
-        <v>361</v>
-      </c>
-      <c r="B37" s="17" t="n">
-        <f aca="false">B29*Assumptions!$B$30*Assumptions!$B$33</f>
-        <v>8403.75</v>
-      </c>
-      <c r="C37" s="17" t="n">
-        <f aca="false">C29*Assumptions!$B$30*Assumptions!$B$33</f>
-        <v>17741.25</v>
-      </c>
-      <c r="D37" s="17" t="n">
-        <f aca="false">D29*Assumptions!$B$30*Assumptions!$B$33</f>
-        <v>28012.5</v>
-      </c>
-      <c r="E37" s="17" t="n">
-        <f aca="false">E29*Assumptions!$B$30*Assumptions!$B$33</f>
-        <v>37350</v>
-      </c>
-      <c r="F37" s="17" t="n">
-        <f aca="false">F29*Assumptions!$B$30*Assumptions!$B$33</f>
-        <v>46687.5</v>
+      <c r="A37" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="B37" s="24" t="n">
+        <f aca="false">B35+B36</f>
+        <v>879315.75</v>
+      </c>
+      <c r="C37" s="24" t="n">
+        <f aca="false">C35+C36</f>
+        <v>888653.25</v>
+      </c>
+      <c r="D37" s="24" t="n">
+        <f aca="false">D35+D36</f>
+        <v>898924.5</v>
+      </c>
+      <c r="E37" s="24" t="n">
+        <f aca="false">E35+E36</f>
+        <v>1125990</v>
+      </c>
+      <c r="F37" s="24" t="n">
+        <f aca="false">F35+F36</f>
+        <v>1135327.5</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="B38" s="24" t="n">
-        <f aca="false">B36+B37</f>
-        <v>443859.75</v>
-      </c>
-      <c r="C38" s="24" t="n">
-        <f aca="false">C36+C37</f>
-        <v>453197.25</v>
-      </c>
-      <c r="D38" s="24" t="n">
-        <f aca="false">D36+D37</f>
-        <v>681196.5</v>
-      </c>
-      <c r="E38" s="24" t="n">
-        <f aca="false">E36+E37</f>
-        <v>690534</v>
-      </c>
-      <c r="F38" s="24" t="n">
-        <f aca="false">F36+F37</f>
-        <v>699871.5</v>
+      <c r="A38" s="20" t="s">
+        <v>450</v>
+      </c>
+      <c r="B38" s="17" t="n">
+        <f aca="false">B24*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(B1)-2)</f>
+        <v>333696.24</v>
+      </c>
+      <c r="C38" s="17" t="n">
+        <f aca="false">C24*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(C1)-2)</f>
+        <v>343707.1272</v>
+      </c>
+      <c r="D38" s="17" t="n">
+        <f aca="false">D24*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(D1)-2)</f>
+        <v>354018.341016</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <f aca="false">E24*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(E1)-2)</f>
+        <v>455798.6140581</v>
+      </c>
+      <c r="F38" s="17" t="n">
+        <f aca="false">F24*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(F1)-2)</f>
+        <v>469472.572479843</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="20" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B39" s="17" t="n">
-        <f aca="false">B24*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(B1)-2)</f>
-        <v>166848.12</v>
+        <f aca="false">B35*Assumptions!$B$22+B28*Assumptions!$B$33*Assumptions!$B$37</f>
+        <v>176544.9</v>
       </c>
       <c r="C39" s="17" t="n">
-        <f aca="false">C24*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(C1)-2)</f>
-        <v>171853.5636</v>
+        <f aca="false">C35*Assumptions!$B$22+C28*Assumptions!$B$33*Assumptions!$B$37</f>
+        <v>179169.9</v>
       </c>
       <c r="D39" s="17" t="n">
-        <f aca="false">D24*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(D1)-2)</f>
-        <v>265513.755762</v>
+        <f aca="false">D35*Assumptions!$B$22+D28*Assumptions!$B$33*Assumptions!$B$37</f>
+        <v>182057.4</v>
       </c>
       <c r="E39" s="17" t="n">
-        <f aca="false">E24*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(E1)-2)</f>
-        <v>273479.16843486</v>
+        <f aca="false">E35*Assumptions!$B$22+E28*Assumptions!$B$33*Assumptions!$B$37</f>
+        <v>228228</v>
       </c>
       <c r="F39" s="17" t="n">
-        <f aca="false">F24*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(F1)-2)</f>
-        <v>281683.543487906</v>
+        <f aca="false">F35*Assumptions!$B$22+F28*Assumptions!$B$33*Assumptions!$B$37</f>
+        <v>230853</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="20" t="s">
-        <v>453</v>
-      </c>
-      <c r="B40" s="17" t="n">
-        <f aca="false">B36*Assumptions!$B$22+B29*Assumptions!$B$33*Assumptions!$B$37</f>
-        <v>89453.7</v>
-      </c>
-      <c r="C40" s="17" t="n">
-        <f aca="false">C36*Assumptions!$B$22+C29*Assumptions!$B$33*Assumptions!$B$37</f>
-        <v>92078.7</v>
-      </c>
-      <c r="D40" s="17" t="n">
-        <f aca="false">D36*Assumptions!$B$22+D29*Assumptions!$B$33*Assumptions!$B$37</f>
-        <v>138511.8</v>
-      </c>
-      <c r="E40" s="17" t="n">
-        <f aca="false">E36*Assumptions!$B$22+E29*Assumptions!$B$33*Assumptions!$B$37</f>
-        <v>141136.8</v>
-      </c>
-      <c r="F40" s="17" t="n">
-        <f aca="false">F36*Assumptions!$B$22+F29*Assumptions!$B$33*Assumptions!$B$37</f>
-        <v>143761.8</v>
+      <c r="A40" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="B40" s="24" t="n">
+        <f aca="false">B37-B38-B39</f>
+        <v>369074.61</v>
+      </c>
+      <c r="C40" s="24" t="n">
+        <f aca="false">C37-C38-C39</f>
+        <v>365776.2228</v>
+      </c>
+      <c r="D40" s="24" t="n">
+        <f aca="false">D37-D38-D39</f>
+        <v>362848.758984</v>
+      </c>
+      <c r="E40" s="24" t="n">
+        <f aca="false">E37-E38-E39</f>
+        <v>441963.3859419</v>
+      </c>
+      <c r="F40" s="24" t="n">
+        <f aca="false">F37-F38-F39</f>
+        <v>435001.927520157</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="18" t="s">
-        <v>224</v>
-      </c>
-      <c r="B41" s="24" t="n">
-        <f aca="false">B38-B39-B40</f>
-        <v>187557.93</v>
-      </c>
-      <c r="C41" s="24" t="n">
-        <f aca="false">C38-C39-C40</f>
-        <v>189264.9864</v>
-      </c>
-      <c r="D41" s="24" t="n">
-        <f aca="false">D38-D39-D40</f>
-        <v>277170.944238</v>
-      </c>
-      <c r="E41" s="24" t="n">
-        <f aca="false">E38-E39-E40</f>
-        <v>275918.03156514</v>
-      </c>
-      <c r="F41" s="24" t="n">
-        <f aca="false">F38-F39-F40</f>
-        <v>274426.156512094</v>
+      <c r="A41" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="B41" s="23" t="n">
+        <f aca="false">IF(B37=0,0,B40/B37)</f>
+        <v>0.419729329310887</v>
+      </c>
+      <c r="C41" s="23" t="n">
+        <f aca="false">IF(C37=0,0,C40/C37)</f>
+        <v>0.411607365189966</v>
+      </c>
+      <c r="D41" s="23" t="n">
+        <f aca="false">IF(D37=0,0,D40/D37)</f>
+        <v>0.403647646697804</v>
+      </c>
+      <c r="E41" s="23" t="n">
+        <f aca="false">IF(E37=0,0,E40/E37)</f>
+        <v>0.392510933438041</v>
+      </c>
+      <c r="F41" s="23" t="n">
+        <f aca="false">IF(F37=0,0,F40/F37)</f>
+        <v>0.383151053348181</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="20" t="s">
-        <v>265</v>
-      </c>
-      <c r="B42" s="23" t="n">
-        <f aca="false">IF(B38=0,0,B41/B38)</f>
-        <v>0.422561248232127</v>
-      </c>
-      <c r="C42" s="23" t="n">
-        <f aca="false">IF(C38=0,0,C41/C38)</f>
-        <v>0.417621656795137</v>
-      </c>
-      <c r="D42" s="23" t="n">
-        <f aca="false">IF(D38=0,0,D41/D38)</f>
-        <v>0.406888385712493</v>
-      </c>
-      <c r="E42" s="23" t="n">
-        <f aca="false">IF(E38=0,0,E41/E38)</f>
-        <v>0.399571971206544</v>
-      </c>
-      <c r="F42" s="23" t="n">
-        <f aca="false">IF(F38=0,0,F41/F38)</f>
-        <v>0.392109346518745</v>
+        <v>452</v>
+      </c>
+      <c r="B42" s="17" t="n">
+        <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+B24*B30+B31+B37*B29+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,B24-1)</f>
+        <v>275048.99035896</v>
+      </c>
+      <c r="C42" s="17" t="n">
+        <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+C24*C30+C31+C37*C29+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,C24-1)</f>
+        <v>275749.30285896</v>
+      </c>
+      <c r="D42" s="17" t="n">
+        <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+D24*D30+D31+D37*D29+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,D24-1)</f>
+        <v>300519.64660896</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+E24*E30+E31+E37*E29+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,E24-1)</f>
+        <v>361349.71366344</v>
+      </c>
+      <c r="F42" s="17" t="n">
+        <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+F24*F30+F31+F37*F29+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,F24-1)</f>
+        <v>364050.02616344</v>
       </c>
       <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
+      <c r="H42" s="8" t="s">
+        <v>453</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="20" t="s">
+      <c r="A43" s="18" t="s">
         <v>454</v>
       </c>
-      <c r="B43" s="17" t="n">
-        <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+B24*B31+B32+B38*B30+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,B24-1)</f>
-        <v>190789.48125</v>
-      </c>
-      <c r="C43" s="17" t="n">
-        <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+C24*C31+C32+C38*C30+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,C24-1)</f>
-        <v>191489.79375</v>
-      </c>
-      <c r="D43" s="17" t="n">
-        <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+D24*D31+D32+D38*D30+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,D24-1)</f>
-        <v>258389.89205448</v>
-      </c>
-      <c r="E43" s="17" t="n">
-        <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+E24*E31+E32+E38*E30+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,E24-1)</f>
-        <v>277090.20455448</v>
-      </c>
-      <c r="F43" s="17" t="n">
-        <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+F24*F31+F32+F38*F30+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,F24-1)</f>
-        <v>279790.51705448</v>
+      <c r="B43" s="24" t="n">
+        <f aca="false">B40-B42</f>
+        <v>94025.6196410397</v>
+      </c>
+      <c r="C43" s="24" t="n">
+        <f aca="false">C40-C42</f>
+        <v>90026.9199410397</v>
+      </c>
+      <c r="D43" s="24" t="n">
+        <f aca="false">D40-D42</f>
+        <v>62329.1123750397</v>
+      </c>
+      <c r="E43" s="24" t="n">
+        <f aca="false">E40-E42</f>
+        <v>80613.6722784595</v>
+      </c>
+      <c r="F43" s="24" t="n">
+        <f aca="false">F40-F42</f>
+        <v>70951.9013567164</v>
       </c>
       <c r="G43" s="3"/>
-      <c r="H43" s="8" t="s">
+      <c r="H43" s="3"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="20" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="18" t="s">
+      <c r="B44" s="11" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3"/>
+      <c r="H44" s="8" t="s">
         <v>456</v>
       </c>
-      <c r="B44" s="24" t="n">
-        <f aca="false">B41-B43</f>
-        <v>-3231.55125000002</v>
-      </c>
-      <c r="C44" s="24" t="n">
-        <f aca="false">C41-C43</f>
-        <v>-2224.80735000002</v>
-      </c>
-      <c r="D44" s="24" t="n">
-        <f aca="false">D41-D43</f>
-        <v>18781.0521835198</v>
-      </c>
-      <c r="E44" s="24" t="n">
-        <f aca="false">E41-E43</f>
-        <v>-1172.17298934021</v>
-      </c>
-      <c r="F44" s="24" t="n">
-        <f aca="false">F41-F43</f>
-        <v>-5364.36054238601</v>
-      </c>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="B45" s="11" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="11" t="n">
-        <v>0</v>
+      <c r="B45" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C45" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D45" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E45" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F45" s="14" t="n">
+        <v>0.1</v>
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="8" t="s">
@@ -13613,359 +13604,355 @@
       <c r="A46" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="B46" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C46" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D46" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E46" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F46" s="14" t="n">
-        <v>0.1</v>
+      <c r="B46" s="17" t="n">
+        <f aca="false">B44+IF(B44=0,0,B45*MAX(0,B43-MAX(0,'5-year plan'!$B$44)))</f>
+        <v>24402.561964104</v>
+      </c>
+      <c r="C46" s="17" t="n">
+        <f aca="false">C44+IF(C44=0,0,C45*MAX(0,C43-MAX(0,'5-year plan'!$B$44)))</f>
+        <v>0</v>
+      </c>
+      <c r="D46" s="17" t="n">
+        <f aca="false">D44+IF(D44=0,0,D45*MAX(0,D43-MAX(0,'5-year plan'!$B$44)))</f>
+        <v>0</v>
+      </c>
+      <c r="E46" s="17" t="n">
+        <f aca="false">E44+IF(E44=0,0,E45*MAX(0,E43-MAX(0,'5-year plan'!$B$44)))</f>
+        <v>0</v>
+      </c>
+      <c r="F46" s="17" t="n">
+        <f aca="false">F44+IF(F44=0,0,F45*MAX(0,F43-MAX(0,'5-year plan'!$B$44)))</f>
+        <v>0</v>
       </c>
       <c r="G46" s="3"/>
-      <c r="H46" s="8" t="s">
+      <c r="H46" s="3"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="18" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="20" t="s">
-        <v>461</v>
-      </c>
-      <c r="B47" s="17" t="n">
-        <f aca="false">B45+IF(B45=0,0,B46*MAX(0,B44-MAX(0,'5-year plan'!$B$44)))</f>
-        <v>15000</v>
-      </c>
-      <c r="C47" s="17" t="n">
-        <f aca="false">C45+IF(C45=0,0,C46*MAX(0,C44-MAX(0,'5-year plan'!$B$44)))</f>
-        <v>0</v>
-      </c>
-      <c r="D47" s="17" t="n">
-        <f aca="false">D45+IF(D45=0,0,D46*MAX(0,D44-MAX(0,'5-year plan'!$B$44)))</f>
-        <v>0</v>
-      </c>
-      <c r="E47" s="17" t="n">
-        <f aca="false">E45+IF(E45=0,0,E46*MAX(0,E44-MAX(0,'5-year plan'!$B$44)))</f>
-        <v>0</v>
-      </c>
-      <c r="F47" s="17" t="n">
-        <f aca="false">F45+IF(F45=0,0,F46*MAX(0,F44-MAX(0,'5-year plan'!$B$44)))</f>
-        <v>0</v>
+      <c r="B47" s="24" t="n">
+        <f aca="false">B43-B46</f>
+        <v>69623.0576769357</v>
+      </c>
+      <c r="C47" s="24" t="n">
+        <f aca="false">C43-C46</f>
+        <v>90026.9199410397</v>
+      </c>
+      <c r="D47" s="24" t="n">
+        <f aca="false">D43-D46</f>
+        <v>62329.1123750397</v>
+      </c>
+      <c r="E47" s="24" t="n">
+        <f aca="false">E43-E46</f>
+        <v>80613.6722784595</v>
+      </c>
+      <c r="F47" s="24" t="n">
+        <f aca="false">F43-F46</f>
+        <v>70951.9013567164</v>
       </c>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="18" t="s">
-        <v>462</v>
-      </c>
-      <c r="B48" s="24" t="n">
-        <f aca="false">B44-B47</f>
-        <v>-18231.55125</v>
-      </c>
-      <c r="C48" s="24" t="n">
-        <f aca="false">C44-C47</f>
-        <v>-2224.80735000002</v>
-      </c>
-      <c r="D48" s="24" t="n">
-        <f aca="false">D44-D47</f>
-        <v>18781.0521835198</v>
-      </c>
-      <c r="E48" s="24" t="n">
-        <f aca="false">E44-E47</f>
-        <v>-1172.17298934021</v>
-      </c>
-      <c r="F48" s="24" t="n">
-        <f aca="false">F44-F47</f>
-        <v>-5364.36054238601</v>
+      <c r="A48" s="20" t="s">
+        <v>461</v>
+      </c>
+      <c r="B48" s="23" t="n">
+        <f aca="false">IF(B37=0,0,B47/B37)</f>
+        <v>0.079178676916609</v>
+      </c>
+      <c r="C48" s="23" t="n">
+        <f aca="false">IF(C37=0,0,C47/C37)</f>
+        <v>0.101307140823532</v>
+      </c>
+      <c r="D48" s="23" t="n">
+        <f aca="false">IF(D37=0,0,D47/D37)</f>
+        <v>0.0693374275314998</v>
+      </c>
+      <c r="E48" s="23" t="n">
+        <f aca="false">IF(E37=0,0,E47/E37)</f>
+        <v>0.0715935952170619</v>
+      </c>
+      <c r="F48" s="23" t="n">
+        <f aca="false">IF(F37=0,0,F47/F37)</f>
+        <v>0.0624946558210881</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="20" t="s">
-        <v>463</v>
-      </c>
-      <c r="B49" s="23" t="n">
-        <f aca="false">IF(B38=0,0,B48/B38)</f>
-        <v>-0.0410750270778101</v>
-      </c>
-      <c r="C49" s="23" t="n">
-        <f aca="false">IF(C38=0,0,C48/C38)</f>
-        <v>-0.0049091369155484</v>
-      </c>
-      <c r="D49" s="23" t="n">
-        <f aca="false">IF(D38=0,0,D48/D38)</f>
-        <v>0.0275706821504806</v>
-      </c>
-      <c r="E49" s="23" t="n">
-        <f aca="false">IF(E38=0,0,E48/E38)</f>
-        <v>-0.00169748772593414</v>
-      </c>
-      <c r="F49" s="23" t="n">
-        <f aca="false">IF(F38=0,0,F48/F38)</f>
-        <v>-0.00766477923788297</v>
+        <v>462</v>
+      </c>
+      <c r="B49" s="17" t="n">
+        <f aca="false">MAX(0,B24-1)*'Equipment plan'!$G$10</f>
+        <v>27700</v>
+      </c>
+      <c r="C49" s="17" t="n">
+        <f aca="false">MAX(0,C24-B24)*'Equipment plan'!$G$10</f>
+        <v>0</v>
+      </c>
+      <c r="D49" s="17" t="n">
+        <f aca="false">MAX(0,D24-C24)*'Equipment plan'!$G$10</f>
+        <v>0</v>
+      </c>
+      <c r="E49" s="17" t="n">
+        <f aca="false">MAX(0,E24-D24)*'Equipment plan'!$G$10</f>
+        <v>13850</v>
+      </c>
+      <c r="F49" s="17" t="n">
+        <f aca="false">MAX(0,F24-E24)*'Equipment plan'!$G$10</f>
+        <v>0</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="20" t="s">
+      <c r="A50" s="18" t="s">
+        <v>463</v>
+      </c>
+      <c r="B50" s="24" t="n">
+        <f aca="false">Assumptions!$B$62+B47-B49</f>
+        <v>66923.0576769357</v>
+      </c>
+      <c r="C50" s="24" t="n">
+        <f aca="false">B50+C47-C49</f>
+        <v>156949.977617975</v>
+      </c>
+      <c r="D50" s="24" t="n">
+        <f aca="false">C50+D47-D49</f>
+        <v>219279.089993015</v>
+      </c>
+      <c r="E50" s="24" t="n">
+        <f aca="false">D50+E47-E49</f>
+        <v>286042.762271475</v>
+      </c>
+      <c r="F50" s="24" t="n">
+        <f aca="false">E50+F47-F49</f>
+        <v>356994.663628191</v>
+      </c>
+      <c r="G50" s="3"/>
+      <c r="H50" s="8" t="s">
         <v>464</v>
       </c>
-      <c r="B50" s="17" t="n">
-        <f aca="false">MAX(0,B24-1)*'Equipment plan'!$G$10</f>
-        <v>0</v>
-      </c>
-      <c r="C50" s="17" t="n">
-        <f aca="false">MAX(0,C24-B24)*'Equipment plan'!$G$10</f>
-        <v>0</v>
-      </c>
-      <c r="D50" s="17" t="n">
-        <f aca="false">MAX(0,D24-C24)*'Equipment plan'!$G$10</f>
-        <v>13850</v>
-      </c>
-      <c r="E50" s="17" t="n">
-        <f aca="false">MAX(0,E24-D24)*'Equipment plan'!$G$10</f>
-        <v>0</v>
-      </c>
-      <c r="F50" s="17" t="n">
-        <f aca="false">MAX(0,F24-E24)*'Equipment plan'!$G$10</f>
-        <v>0</v>
-      </c>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="18" t="s">
+      <c r="A51" s="20" t="s">
         <v>465</v>
       </c>
-      <c r="B51" s="24" t="n">
-        <f aca="false">Assumptions!$B$62+B48-B50</f>
-        <v>6768.44874999998</v>
-      </c>
-      <c r="C51" s="24" t="n">
-        <f aca="false">B51+C48-C50</f>
-        <v>4543.64139999996</v>
-      </c>
-      <c r="D51" s="24" t="n">
-        <f aca="false">C51+D48-D50</f>
-        <v>9474.69358351981</v>
-      </c>
-      <c r="E51" s="24" t="n">
-        <f aca="false">D51+E48-E50</f>
-        <v>8302.52059417961</v>
-      </c>
-      <c r="F51" s="24" t="n">
-        <f aca="false">E51+F48-F50</f>
-        <v>2938.16005179359</v>
+      <c r="B51" s="17" t="n">
+        <f aca="false">B47+Assumptions!$B$78*12</f>
+        <v>141623.057676936</v>
+      </c>
+      <c r="C51" s="17" t="n">
+        <f aca="false">C47+Assumptions!$B$78*12</f>
+        <v>162026.91994104</v>
+      </c>
+      <c r="D51" s="17" t="n">
+        <f aca="false">D47+Assumptions!$B$78*12</f>
+        <v>134329.11237504</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <f aca="false">E47+Assumptions!$B$78*12</f>
+        <v>152613.67227846</v>
+      </c>
+      <c r="F51" s="17" t="n">
+        <f aca="false">F47+Assumptions!$B$78*12</f>
+        <v>142951.901356716</v>
       </c>
       <c r="G51" s="3"/>
-      <c r="H51" s="8" t="s">
-        <v>466</v>
-      </c>
+      <c r="H51" s="3"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="20" t="s">
+        <v>466</v>
+      </c>
+      <c r="B52" s="17" t="n">
+        <f aca="false">MAX(0,B51)*2.46</f>
+        <v>348392.721885262</v>
+      </c>
+      <c r="C52" s="17" t="n">
+        <f aca="false">MAX(0,C51)*2.46</f>
+        <v>398586.223054958</v>
+      </c>
+      <c r="D52" s="17" t="n">
+        <f aca="false">MAX(0,D51)*2.46</f>
+        <v>330449.616442598</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <f aca="false">MAX(0,E51)*2.46</f>
+        <v>375429.63380501</v>
+      </c>
+      <c r="F52" s="17" t="n">
+        <f aca="false">MAX(0,F51)*2.46</f>
+        <v>351661.677337522</v>
+      </c>
+      <c r="G52" s="3"/>
+      <c r="H52" s="8" t="s">
         <v>467</v>
       </c>
-      <c r="B52" s="17" t="n">
-        <f aca="false">B48+Assumptions!$B$78*12</f>
-        <v>53768.44875</v>
-      </c>
-      <c r="C52" s="17" t="n">
-        <f aca="false">C48+Assumptions!$B$78*12</f>
-        <v>69775.19265</v>
-      </c>
-      <c r="D52" s="17" t="n">
-        <f aca="false">D48+Assumptions!$B$78*12</f>
-        <v>90781.0521835199</v>
-      </c>
-      <c r="E52" s="17" t="n">
-        <f aca="false">E48+Assumptions!$B$78*12</f>
-        <v>70827.8270106598</v>
-      </c>
-      <c r="F52" s="17" t="n">
-        <f aca="false">F48+Assumptions!$B$78*12</f>
-        <v>66635.639457614</v>
-      </c>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="20" t="s">
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+    </row>
+    <row r="54" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="B53" s="17" t="n">
-        <f aca="false">MAX(0,B52)*2.46</f>
-        <v>132270.383925</v>
-      </c>
-      <c r="C53" s="17" t="n">
-        <f aca="false">MAX(0,C52)*2.46</f>
-        <v>171646.973919</v>
-      </c>
-      <c r="D53" s="17" t="n">
-        <f aca="false">MAX(0,D52)*2.46</f>
-        <v>223321.388371459</v>
-      </c>
-      <c r="E53" s="17" t="n">
-        <f aca="false">MAX(0,E52)*2.46</f>
-        <v>174236.454446223</v>
-      </c>
-      <c r="F53" s="17" t="n">
-        <f aca="false">MAX(0,F52)*2.46</f>
-        <v>163923.67306573</v>
-      </c>
-      <c r="G53" s="3"/>
-      <c r="H53" s="8" t="s">
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="41" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="3"/>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
-      <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
-    </row>
-    <row r="55" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="B55" s="6"/>
-      <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="6"/>
-      <c r="F55" s="6"/>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="30" t="s">
+        <v>436</v>
+      </c>
+      <c r="B55" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="C55" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="D55" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="E55" s="30" t="s">
+        <v>345</v>
+      </c>
+      <c r="F55" s="30" t="s">
+        <v>346</v>
+      </c>
       <c r="G55" s="3"/>
-      <c r="H55" s="41" t="s">
-        <v>471</v>
-      </c>
+      <c r="H55" s="3"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="30" t="s">
-        <v>436</v>
-      </c>
-      <c r="B56" s="30" t="s">
-        <v>192</v>
-      </c>
-      <c r="C56" s="30" t="s">
-        <v>193</v>
-      </c>
-      <c r="D56" s="30" t="s">
-        <v>344</v>
-      </c>
-      <c r="E56" s="30" t="s">
-        <v>345</v>
-      </c>
-      <c r="F56" s="30" t="s">
-        <v>346</v>
+      <c r="A56" s="20" t="s">
+        <v>351</v>
+      </c>
+      <c r="B56" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="C56" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" s="34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E56" s="34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F56" s="34" t="n">
+        <v>4</v>
       </c>
       <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
+      <c r="H56" s="8" t="s">
+        <v>437</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="20" t="s">
-        <v>351</v>
-      </c>
-      <c r="B57" s="34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C57" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="D57" s="34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E57" s="34" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F57" s="34" t="n">
-        <v>4</v>
+        <v>438</v>
+      </c>
+      <c r="B57" s="13" t="n">
+        <v>43</v>
+      </c>
+      <c r="C57" s="13" t="n">
+        <v>43</v>
+      </c>
+      <c r="D57" s="13" t="n">
+        <v>43</v>
+      </c>
+      <c r="E57" s="13" t="n">
+        <v>43</v>
+      </c>
+      <c r="F57" s="13" t="n">
+        <v>43</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="8" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="20" t="s">
-        <v>438</v>
-      </c>
-      <c r="B58" s="14" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="C58" s="14" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D58" s="14" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E58" s="14" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F58" s="14" t="n">
-        <v>0.95</v>
+        <v>301</v>
+      </c>
+      <c r="B58" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="C58" s="17" t="n">
+        <f aca="false">B58*(1+$B$59)</f>
+        <v>51.5</v>
+      </c>
+      <c r="D58" s="17" t="n">
+        <f aca="false">C58*(1+$B$59)</f>
+        <v>53.045</v>
+      </c>
+      <c r="E58" s="17" t="n">
+        <f aca="false">D58*(1+$B$59)</f>
+        <v>54.63635</v>
+      </c>
+      <c r="F58" s="17" t="n">
+        <f aca="false">E58*(1+$B$59)</f>
+        <v>56.2754405</v>
       </c>
       <c r="G58" s="3"/>
-      <c r="H58" s="8" t="s">
-        <v>439</v>
-      </c>
+      <c r="H58" s="3"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="20" t="s">
         <v>440</v>
       </c>
-      <c r="B59" s="13" t="n">
-        <v>43</v>
-      </c>
-      <c r="C59" s="13" t="n">
-        <v>43</v>
-      </c>
-      <c r="D59" s="13" t="n">
-        <v>43</v>
-      </c>
-      <c r="E59" s="13" t="n">
-        <v>43</v>
-      </c>
-      <c r="F59" s="13" t="n">
-        <v>43</v>
+      <c r="B59" s="14" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C59" s="14" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D59" s="14" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E59" s="14" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F59" s="14" t="n">
+        <v>0.03</v>
       </c>
       <c r="G59" s="3"/>
-      <c r="H59" s="8" t="s">
-        <v>441</v>
-      </c>
+      <c r="H59" s="3"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="B60" s="11" t="n">
-        <v>50</v>
-      </c>
-      <c r="C60" s="17" t="n">
-        <f aca="false">B60*(1+$B$61)</f>
-        <v>51.5</v>
-      </c>
-      <c r="D60" s="17" t="n">
-        <f aca="false">C60*(1+$B$61)</f>
-        <v>53.045</v>
-      </c>
-      <c r="E60" s="17" t="n">
-        <f aca="false">D60*(1+$B$61)</f>
-        <v>54.63635</v>
-      </c>
-      <c r="F60" s="17" t="n">
-        <f aca="false">E60*(1+$B$61)</f>
-        <v>56.2754405</v>
+        <v>441</v>
+      </c>
+      <c r="B60" s="13" t="n">
+        <v>94</v>
+      </c>
+      <c r="C60" s="13" t="n">
+        <v>216</v>
+      </c>
+      <c r="D60" s="13" t="n">
+        <v>355</v>
+      </c>
+      <c r="E60" s="13" t="n">
+        <v>540</v>
+      </c>
+      <c r="F60" s="13" t="n">
+        <v>745</v>
       </c>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
@@ -13975,19 +13962,19 @@
         <v>442</v>
       </c>
       <c r="B61" s="14" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="C61" s="14" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="D61" s="14" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="E61" s="14" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="F61" s="14" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
@@ -13996,20 +13983,20 @@
       <c r="A62" s="20" t="s">
         <v>443</v>
       </c>
-      <c r="B62" s="13" t="n">
-        <v>94</v>
-      </c>
-      <c r="C62" s="13" t="n">
-        <v>216</v>
-      </c>
-      <c r="D62" s="13" t="n">
-        <v>355</v>
-      </c>
-      <c r="E62" s="13" t="n">
-        <v>540</v>
-      </c>
-      <c r="F62" s="13" t="n">
-        <v>745</v>
+      <c r="B62" s="11" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C62" s="11" t="n">
+        <v>22000</v>
+      </c>
+      <c r="D62" s="11" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E62" s="11" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F62" s="11" t="n">
+        <v>22000</v>
       </c>
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
@@ -14018,1428 +14005,1360 @@
       <c r="A63" s="20" t="s">
         <v>444</v>
       </c>
-      <c r="B63" s="14" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C63" s="14" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D63" s="14" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E63" s="14" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F63" s="14" t="n">
-        <v>0.05</v>
+      <c r="B63" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" s="11" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D63" s="11" t="n">
+        <v>102750</v>
+      </c>
+      <c r="E63" s="11" t="n">
+        <v>191000</v>
+      </c>
+      <c r="F63" s="11" t="n">
+        <v>200000</v>
       </c>
       <c r="G63" s="3"/>
-      <c r="H63" s="3"/>
+      <c r="H63" s="8" t="s">
+        <v>445</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="20" t="s">
-        <v>445</v>
-      </c>
-      <c r="B64" s="11" t="n">
-        <v>22000</v>
-      </c>
-      <c r="C64" s="11" t="n">
-        <v>22000</v>
-      </c>
-      <c r="D64" s="11" t="n">
-        <v>22000</v>
-      </c>
-      <c r="E64" s="11" t="n">
-        <v>22000</v>
-      </c>
-      <c r="F64" s="11" t="n">
-        <v>22000</v>
-      </c>
+      <c r="A64" s="42" t="s">
+        <v>446</v>
+      </c>
+      <c r="B64" s="43"/>
+      <c r="C64" s="43"/>
+      <c r="D64" s="43"/>
+      <c r="E64" s="43"/>
+      <c r="F64" s="43"/>
       <c r="G64" s="3"/>
-      <c r="H64" s="3"/>
+      <c r="H64" s="43"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="20" t="s">
-        <v>446</v>
-      </c>
-      <c r="B65" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C65" s="11" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D65" s="11" t="n">
-        <v>102750</v>
-      </c>
-      <c r="E65" s="11" t="n">
-        <v>191000</v>
-      </c>
-      <c r="F65" s="11" t="n">
-        <v>200000</v>
+        <v>447</v>
+      </c>
+      <c r="B65" s="21" t="n">
+        <f aca="false">B56*Assumptions!$B$10*12</f>
+        <v>504</v>
+      </c>
+      <c r="C65" s="21" t="n">
+        <f aca="false">C56*Assumptions!$B$10*12</f>
+        <v>504</v>
+      </c>
+      <c r="D65" s="21" t="n">
+        <f aca="false">D56*Assumptions!$B$10*12</f>
+        <v>630</v>
+      </c>
+      <c r="E65" s="21" t="n">
+        <f aca="false">E56*Assumptions!$B$10*12</f>
+        <v>882</v>
+      </c>
+      <c r="F65" s="21" t="n">
+        <f aca="false">F56*Assumptions!$B$10*12</f>
+        <v>1008</v>
       </c>
       <c r="G65" s="3"/>
-      <c r="H65" s="8" t="s">
-        <v>447</v>
-      </c>
+      <c r="H65" s="3"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="42" t="s">
+      <c r="A66" s="18" t="s">
         <v>448</v>
       </c>
-      <c r="B66" s="43"/>
-      <c r="C66" s="43"/>
-      <c r="D66" s="43"/>
-      <c r="E66" s="43"/>
-      <c r="F66" s="43"/>
+      <c r="B66" s="22" t="n">
+        <f aca="false">B65*B57</f>
+        <v>21672</v>
+      </c>
+      <c r="C66" s="22" t="n">
+        <f aca="false">C65*C57</f>
+        <v>21672</v>
+      </c>
+      <c r="D66" s="22" t="n">
+        <f aca="false">D65*D57</f>
+        <v>27090</v>
+      </c>
+      <c r="E66" s="22" t="n">
+        <f aca="false">E65*E57</f>
+        <v>37926</v>
+      </c>
+      <c r="F66" s="22" t="n">
+        <f aca="false">F65*F57</f>
+        <v>43344</v>
+      </c>
       <c r="G66" s="3"/>
-      <c r="H66" s="43"/>
+      <c r="H66" s="3"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="20" t="s">
         <v>449</v>
       </c>
-      <c r="B67" s="21" t="n">
-        <f aca="false">B57*Assumptions!$B$10*12</f>
-        <v>378</v>
-      </c>
-      <c r="C67" s="21" t="n">
-        <f aca="false">C57*Assumptions!$B$10*12</f>
-        <v>504</v>
-      </c>
-      <c r="D67" s="21" t="n">
-        <f aca="false">D57*Assumptions!$B$10*12</f>
-        <v>630</v>
-      </c>
-      <c r="E67" s="21" t="n">
-        <f aca="false">E57*Assumptions!$B$10*12</f>
-        <v>882</v>
-      </c>
-      <c r="F67" s="21" t="n">
-        <f aca="false">F57*Assumptions!$B$10*12</f>
-        <v>1008</v>
+      <c r="B67" s="17" t="n">
+        <f aca="false">B66*B58</f>
+        <v>1083600</v>
+      </c>
+      <c r="C67" s="17" t="n">
+        <f aca="false">C66*C58</f>
+        <v>1116108</v>
+      </c>
+      <c r="D67" s="17" t="n">
+        <f aca="false">D66*D58</f>
+        <v>1436989.05</v>
+      </c>
+      <c r="E67" s="17" t="n">
+        <f aca="false">E66*E58</f>
+        <v>2072138.2101</v>
+      </c>
+      <c r="F67" s="17" t="n">
+        <f aca="false">F66*F58</f>
+        <v>2439202.693032</v>
       </c>
       <c r="G67" s="3"/>
       <c r="H67" s="3"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="18" t="s">
-        <v>450</v>
-      </c>
-      <c r="B68" s="22" t="n">
-        <f aca="false">B67*B59</f>
-        <v>16254</v>
-      </c>
-      <c r="C68" s="22" t="n">
-        <f aca="false">C67*C59</f>
-        <v>21672</v>
-      </c>
-      <c r="D68" s="22" t="n">
-        <f aca="false">D67*D59</f>
-        <v>27090</v>
-      </c>
-      <c r="E68" s="22" t="n">
-        <f aca="false">E67*E59</f>
-        <v>37926</v>
-      </c>
-      <c r="F68" s="22" t="n">
-        <f aca="false">F67*F59</f>
-        <v>43344</v>
+      <c r="A68" s="20" t="s">
+        <v>361</v>
+      </c>
+      <c r="B68" s="17" t="n">
+        <f aca="false">B60*Assumptions!$B$30*Assumptions!$B$33</f>
+        <v>17554.5</v>
+      </c>
+      <c r="C68" s="17" t="n">
+        <f aca="false">C60*Assumptions!$B$30*Assumptions!$B$33</f>
+        <v>40338</v>
+      </c>
+      <c r="D68" s="17" t="n">
+        <f aca="false">D60*Assumptions!$B$30*Assumptions!$B$33</f>
+        <v>66296.25</v>
+      </c>
+      <c r="E68" s="17" t="n">
+        <f aca="false">E60*Assumptions!$B$30*Assumptions!$B$33</f>
+        <v>100845</v>
+      </c>
+      <c r="F68" s="17" t="n">
+        <f aca="false">F60*Assumptions!$B$30*Assumptions!$B$33</f>
+        <v>139128.75</v>
       </c>
       <c r="G68" s="3"/>
       <c r="H68" s="3"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="20" t="s">
-        <v>451</v>
-      </c>
-      <c r="B69" s="17" t="n">
-        <f aca="false">B68*B60</f>
-        <v>812700</v>
-      </c>
-      <c r="C69" s="17" t="n">
-        <f aca="false">C68*C60</f>
-        <v>1116108</v>
-      </c>
-      <c r="D69" s="17" t="n">
-        <f aca="false">D68*D60</f>
-        <v>1436989.05</v>
-      </c>
-      <c r="E69" s="17" t="n">
-        <f aca="false">E68*E60</f>
-        <v>2072138.2101</v>
-      </c>
-      <c r="F69" s="17" t="n">
-        <f aca="false">F68*F60</f>
-        <v>2439202.693032</v>
+      <c r="A69" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="B69" s="24" t="n">
+        <f aca="false">B67+B68</f>
+        <v>1101154.5</v>
+      </c>
+      <c r="C69" s="24" t="n">
+        <f aca="false">C67+C68</f>
+        <v>1156446</v>
+      </c>
+      <c r="D69" s="24" t="n">
+        <f aca="false">D67+D68</f>
+        <v>1503285.3</v>
+      </c>
+      <c r="E69" s="24" t="n">
+        <f aca="false">E67+E68</f>
+        <v>2172983.2101</v>
+      </c>
+      <c r="F69" s="24" t="n">
+        <f aca="false">F67+F68</f>
+        <v>2578331.443032</v>
       </c>
       <c r="G69" s="3"/>
       <c r="H69" s="3"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="20" t="s">
-        <v>361</v>
+        <v>450</v>
       </c>
       <c r="B70" s="17" t="n">
-        <f aca="false">B62*Assumptions!$B$30*Assumptions!$B$33</f>
-        <v>17554.5</v>
+        <f aca="false">B56*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(B1)-2)</f>
+        <v>333696.24</v>
       </c>
       <c r="C70" s="17" t="n">
-        <f aca="false">C62*Assumptions!$B$30*Assumptions!$B$33</f>
-        <v>40338</v>
+        <f aca="false">C56*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(C1)-2)</f>
+        <v>343707.1272</v>
       </c>
       <c r="D70" s="17" t="n">
-        <f aca="false">D62*Assumptions!$B$30*Assumptions!$B$33</f>
-        <v>66296.25</v>
+        <f aca="false">D56*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(D1)-2)</f>
+        <v>442522.92627</v>
       </c>
       <c r="E70" s="17" t="n">
-        <f aca="false">E62*Assumptions!$B$30*Assumptions!$B$33</f>
-        <v>100845</v>
+        <f aca="false">E56*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(E1)-2)</f>
+        <v>638118.05968134</v>
       </c>
       <c r="F70" s="17" t="n">
-        <f aca="false">F62*Assumptions!$B$30*Assumptions!$B$33</f>
-        <v>139128.75</v>
+        <f aca="false">F56*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(F1)-2)</f>
+        <v>751156.115967749</v>
       </c>
       <c r="G70" s="3"/>
       <c r="H70" s="3"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="B71" s="24" t="n">
-        <f aca="false">B69+B70</f>
-        <v>830254.5</v>
-      </c>
-      <c r="C71" s="24" t="n">
-        <f aca="false">C69+C70</f>
-        <v>1156446</v>
-      </c>
-      <c r="D71" s="24" t="n">
-        <f aca="false">D69+D70</f>
-        <v>1503285.3</v>
-      </c>
-      <c r="E71" s="24" t="n">
-        <f aca="false">E69+E70</f>
-        <v>2172983.2101</v>
-      </c>
-      <c r="F71" s="24" t="n">
-        <f aca="false">F69+F70</f>
-        <v>2578331.443032</v>
+      <c r="A71" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B71" s="17" t="n">
+        <f aca="false">B67*Assumptions!$B$22+B60*Assumptions!$B$33*Assumptions!$B$37</f>
+        <v>221655</v>
+      </c>
+      <c r="C71" s="17" t="n">
+        <f aca="false">C67*Assumptions!$B$22+C60*Assumptions!$B$33*Assumptions!$B$37</f>
+        <v>234561.6</v>
+      </c>
+      <c r="D71" s="17" t="n">
+        <f aca="false">D67*Assumptions!$B$22+D60*Assumptions!$B$33*Assumptions!$B$37</f>
+        <v>306035.31</v>
+      </c>
+      <c r="E71" s="17" t="n">
+        <f aca="false">E67*Assumptions!$B$22+E60*Assumptions!$B$33*Assumptions!$B$37</f>
+        <v>442777.64202</v>
+      </c>
+      <c r="F71" s="17" t="n">
+        <f aca="false">F67*Assumptions!$B$22+F60*Assumptions!$B$33*Assumptions!$B$37</f>
+        <v>526953.0386064</v>
       </c>
       <c r="G71" s="3"/>
       <c r="H71" s="3"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="20" t="s">
-        <v>452</v>
-      </c>
-      <c r="B72" s="17" t="n">
-        <f aca="false">B57*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(B1)-2)</f>
-        <v>250272.18</v>
-      </c>
-      <c r="C72" s="17" t="n">
-        <f aca="false">C57*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(C1)-2)</f>
-        <v>343707.1272</v>
-      </c>
-      <c r="D72" s="17" t="n">
-        <f aca="false">D57*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(D1)-2)</f>
-        <v>442522.92627</v>
-      </c>
-      <c r="E72" s="17" t="n">
-        <f aca="false">E57*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(E1)-2)</f>
-        <v>638118.05968134</v>
-      </c>
-      <c r="F72" s="17" t="n">
-        <f aca="false">F57*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(F1)-2)</f>
-        <v>751156.115967749</v>
+      <c r="A72" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="B72" s="24" t="n">
+        <f aca="false">B69-B70-B71</f>
+        <v>545803.26</v>
+      </c>
+      <c r="C72" s="24" t="n">
+        <f aca="false">C69-C70-C71</f>
+        <v>578177.2728</v>
+      </c>
+      <c r="D72" s="24" t="n">
+        <f aca="false">D69-D70-D71</f>
+        <v>754727.06373</v>
+      </c>
+      <c r="E72" s="24" t="n">
+        <f aca="false">E69-E70-E71</f>
+        <v>1092087.50839866</v>
+      </c>
+      <c r="F72" s="24" t="n">
+        <f aca="false">F69-F70-F71</f>
+        <v>1300222.28845785</v>
       </c>
       <c r="G72" s="3"/>
       <c r="H72" s="3"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="20" t="s">
-        <v>453</v>
-      </c>
-      <c r="B73" s="17" t="n">
-        <f aca="false">B69*Assumptions!$B$22+B62*Assumptions!$B$33*Assumptions!$B$37</f>
-        <v>167475</v>
-      </c>
-      <c r="C73" s="17" t="n">
-        <f aca="false">C69*Assumptions!$B$22+C62*Assumptions!$B$33*Assumptions!$B$37</f>
-        <v>234561.6</v>
-      </c>
-      <c r="D73" s="17" t="n">
-        <f aca="false">D69*Assumptions!$B$22+D62*Assumptions!$B$33*Assumptions!$B$37</f>
-        <v>306035.31</v>
-      </c>
-      <c r="E73" s="17" t="n">
-        <f aca="false">E69*Assumptions!$B$22+E62*Assumptions!$B$33*Assumptions!$B$37</f>
-        <v>442777.64202</v>
-      </c>
-      <c r="F73" s="17" t="n">
-        <f aca="false">F69*Assumptions!$B$22+F62*Assumptions!$B$33*Assumptions!$B$37</f>
-        <v>526953.0386064</v>
+        <v>265</v>
+      </c>
+      <c r="B73" s="23" t="n">
+        <f aca="false">IF(B69=0,0,B72/B69)</f>
+        <v>0.495664559332955</v>
+      </c>
+      <c r="C73" s="23" t="n">
+        <f aca="false">IF(C69=0,0,C72/C69)</f>
+        <v>0.49996045885411</v>
+      </c>
+      <c r="D73" s="23" t="n">
+        <f aca="false">IF(D69=0,0,D72/D69)</f>
+        <v>0.502051782007048</v>
+      </c>
+      <c r="E73" s="23" t="n">
+        <f aca="false">IF(E69=0,0,E72/E69)</f>
+        <v>0.502575217020845</v>
+      </c>
+      <c r="F73" s="23" t="n">
+        <f aca="false">IF(F69=0,0,F72/F69)</f>
+        <v>0.504288264401278</v>
       </c>
       <c r="G73" s="3"/>
       <c r="H73" s="3"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="18" t="s">
-        <v>224</v>
-      </c>
-      <c r="B74" s="24" t="n">
-        <f aca="false">B71-B72-B73</f>
-        <v>412507.32</v>
-      </c>
-      <c r="C74" s="24" t="n">
-        <f aca="false">C71-C72-C73</f>
-        <v>578177.2728</v>
-      </c>
-      <c r="D74" s="24" t="n">
-        <f aca="false">D71-D72-D73</f>
-        <v>754727.06373</v>
-      </c>
-      <c r="E74" s="24" t="n">
-        <f aca="false">E71-E72-E73</f>
-        <v>1092087.50839866</v>
-      </c>
-      <c r="F74" s="24" t="n">
-        <f aca="false">F71-F72-F73</f>
-        <v>1300222.28845785</v>
+      <c r="A74" s="20" t="s">
+        <v>452</v>
+      </c>
+      <c r="B74" s="17" t="n">
+        <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+B56*B62+B63+B69*B61+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,B56-1)</f>
+        <v>260158.03410896</v>
+      </c>
+      <c r="C74" s="17" t="n">
+        <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+C56*C62+C63+C69*C61+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,C56-1)</f>
+        <v>292922.60910896</v>
+      </c>
+      <c r="D74" s="17" t="n">
+        <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+D56*D62+D63+D69*D61+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,D56-1)</f>
+        <v>407814.72866344</v>
+      </c>
+      <c r="E74" s="17" t="n">
+        <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+E56*E62+E63+E69*E61+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,E56-1)</f>
+        <v>579149.933277401</v>
+      </c>
+      <c r="F74" s="17" t="n">
+        <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+F56*F62+F63+F69*F61+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,F56-1)</f>
+        <v>633217.499478481</v>
       </c>
       <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
+      <c r="H74" s="8" t="s">
+        <v>453</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="20" t="s">
-        <v>265</v>
-      </c>
-      <c r="B75" s="23" t="n">
-        <f aca="false">IF(B71=0,0,B74/B71)</f>
-        <v>0.496844425414135</v>
-      </c>
-      <c r="C75" s="23" t="n">
-        <f aca="false">IF(C71=0,0,C74/C71)</f>
-        <v>0.49996045885411</v>
-      </c>
-      <c r="D75" s="23" t="n">
-        <f aca="false">IF(D71=0,0,D74/D71)</f>
-        <v>0.502051782007048</v>
-      </c>
-      <c r="E75" s="23" t="n">
-        <f aca="false">IF(E71=0,0,E74/E71)</f>
-        <v>0.502575217020845</v>
-      </c>
-      <c r="F75" s="23" t="n">
-        <f aca="false">IF(F71=0,0,F74/F71)</f>
-        <v>0.504288264401278</v>
+      <c r="A75" s="18" t="s">
+        <v>454</v>
+      </c>
+      <c r="B75" s="24" t="n">
+        <f aca="false">B72-B74</f>
+        <v>285645.22589104</v>
+      </c>
+      <c r="C75" s="24" t="n">
+        <f aca="false">C72-C74</f>
+        <v>285254.66369104</v>
+      </c>
+      <c r="D75" s="24" t="n">
+        <f aca="false">D72-D74</f>
+        <v>346912.33506656</v>
+      </c>
+      <c r="E75" s="24" t="n">
+        <f aca="false">E72-E74</f>
+        <v>512937.575121259</v>
+      </c>
+      <c r="F75" s="24" t="n">
+        <f aca="false">F72-F74</f>
+        <v>667004.78897937</v>
       </c>
       <c r="G75" s="3"/>
       <c r="H75" s="3"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="20" t="s">
-        <v>454</v>
-      </c>
-      <c r="B76" s="17" t="n">
-        <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+B57*B64+B65+B71*B63+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,B57-1)</f>
-        <v>221812.87955448</v>
-      </c>
-      <c r="C76" s="17" t="n">
-        <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+C57*C64+C65+C71*C63+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,C57-1)</f>
-        <v>292922.60910896</v>
-      </c>
-      <c r="D76" s="17" t="n">
-        <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+D57*D64+D65+D71*D63+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,D57-1)</f>
-        <v>407814.72866344</v>
-      </c>
-      <c r="E76" s="17" t="n">
-        <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+E57*E64+E65+E71*E63+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,E57-1)</f>
-        <v>579149.933277401</v>
-      </c>
-      <c r="F76" s="17" t="n">
-        <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+F57*F64+F65+F71*F63+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,F57-1)</f>
-        <v>633217.499478481</v>
+        <v>455</v>
+      </c>
+      <c r="B76" s="11" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C76" s="11" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D76" s="11" t="n">
+        <v>66000</v>
+      </c>
+      <c r="E76" s="11" t="n">
+        <v>72000</v>
+      </c>
+      <c r="F76" s="11" t="n">
+        <v>72000</v>
       </c>
       <c r="G76" s="3"/>
       <c r="H76" s="8" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="18" t="s">
-        <v>456</v>
-      </c>
-      <c r="B77" s="24" t="n">
-        <f aca="false">B74-B76</f>
-        <v>190694.44044552</v>
-      </c>
-      <c r="C77" s="24" t="n">
-        <f aca="false">C74-C76</f>
-        <v>285254.66369104</v>
-      </c>
-      <c r="D77" s="24" t="n">
-        <f aca="false">D74-D76</f>
-        <v>346912.33506656</v>
-      </c>
-      <c r="E77" s="24" t="n">
-        <f aca="false">E74-E76</f>
-        <v>512937.575121259</v>
-      </c>
-      <c r="F77" s="24" t="n">
-        <f aca="false">F74-F76</f>
-        <v>667004.78897937</v>
+      <c r="A77" s="20" t="s">
+        <v>457</v>
+      </c>
+      <c r="B77" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C77" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D77" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E77" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F77" s="14" t="n">
+        <v>0.1</v>
       </c>
       <c r="G77" s="3"/>
-      <c r="H77" s="3"/>
+      <c r="H77" s="8" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="20" t="s">
-        <v>457</v>
-      </c>
-      <c r="B78" s="11" t="n">
-        <v>60000</v>
-      </c>
-      <c r="C78" s="11" t="n">
-        <v>60000</v>
-      </c>
-      <c r="D78" s="11" t="n">
-        <v>66000</v>
-      </c>
-      <c r="E78" s="11" t="n">
-        <v>72000</v>
-      </c>
-      <c r="F78" s="11" t="n">
-        <v>72000</v>
+        <v>459</v>
+      </c>
+      <c r="B78" s="17" t="n">
+        <f aca="false">B76+IF(B76=0,0,B77*MAX(0,B75-MAX(0,'5-year plan'!$B$44)))</f>
+        <v>88564.522589104</v>
+      </c>
+      <c r="C78" s="17" t="n">
+        <f aca="false">C76+IF(C76=0,0,C77*MAX(0,C75-MAX(0,'5-year plan'!$B$44)))</f>
+        <v>88525.466369104</v>
+      </c>
+      <c r="D78" s="17" t="n">
+        <f aca="false">D76+IF(D76=0,0,D77*MAX(0,D75-MAX(0,'5-year plan'!$B$44)))</f>
+        <v>100691.233506656</v>
+      </c>
+      <c r="E78" s="17" t="n">
+        <f aca="false">E76+IF(E76=0,0,E77*MAX(0,E75-MAX(0,'5-year plan'!$B$44)))</f>
+        <v>123293.757512126</v>
+      </c>
+      <c r="F78" s="17" t="n">
+        <f aca="false">F76+IF(F76=0,0,F77*MAX(0,F75-MAX(0,'5-year plan'!$B$44)))</f>
+        <v>138700.478897937</v>
       </c>
       <c r="G78" s="3"/>
-      <c r="H78" s="8" t="s">
-        <v>458</v>
-      </c>
+      <c r="H78" s="3"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="20" t="s">
-        <v>459</v>
-      </c>
-      <c r="B79" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C79" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D79" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E79" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F79" s="14" t="n">
-        <v>0.1</v>
+      <c r="A79" s="18" t="s">
+        <v>460</v>
+      </c>
+      <c r="B79" s="24" t="n">
+        <f aca="false">B75-B78</f>
+        <v>197080.703301936</v>
+      </c>
+      <c r="C79" s="24" t="n">
+        <f aca="false">C75-C78</f>
+        <v>196729.197321936</v>
+      </c>
+      <c r="D79" s="24" t="n">
+        <f aca="false">D75-D78</f>
+        <v>246221.101559904</v>
+      </c>
+      <c r="E79" s="24" t="n">
+        <f aca="false">E75-E78</f>
+        <v>389643.817609133</v>
+      </c>
+      <c r="F79" s="24" t="n">
+        <f aca="false">F75-F78</f>
+        <v>528304.310081433</v>
       </c>
       <c r="G79" s="3"/>
-      <c r="H79" s="8" t="s">
-        <v>460</v>
-      </c>
+      <c r="H79" s="3"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="20" t="s">
         <v>461</v>
       </c>
-      <c r="B80" s="17" t="n">
-        <f aca="false">B78+IF(B78=0,0,B79*MAX(0,B77-MAX(0,'5-year plan'!$B$44)))</f>
-        <v>79069.444044552</v>
-      </c>
-      <c r="C80" s="17" t="n">
-        <f aca="false">C78+IF(C78=0,0,C79*MAX(0,C77-MAX(0,'5-year plan'!$B$44)))</f>
-        <v>88525.466369104</v>
-      </c>
-      <c r="D80" s="17" t="n">
-        <f aca="false">D78+IF(D78=0,0,D79*MAX(0,D77-MAX(0,'5-year plan'!$B$44)))</f>
-        <v>100691.233506656</v>
-      </c>
-      <c r="E80" s="17" t="n">
-        <f aca="false">E78+IF(E78=0,0,E79*MAX(0,E77-MAX(0,'5-year plan'!$B$44)))</f>
-        <v>123293.757512126</v>
-      </c>
-      <c r="F80" s="17" t="n">
-        <f aca="false">F78+IF(F78=0,0,F79*MAX(0,F77-MAX(0,'5-year plan'!$B$44)))</f>
-        <v>138700.478897937</v>
+      <c r="B80" s="23" t="n">
+        <f aca="false">IF(B69=0,0,B79/B69)</f>
+        <v>0.178976431828536</v>
+      </c>
+      <c r="C80" s="23" t="n">
+        <f aca="false">IF(C69=0,0,C79/C69)</f>
+        <v>0.170115333808873</v>
+      </c>
+      <c r="D80" s="23" t="n">
+        <f aca="false">IF(D69=0,0,D79/D69)</f>
+        <v>0.163788671092509</v>
+      </c>
+      <c r="E80" s="23" t="n">
+        <f aca="false">IF(E69=0,0,E79/E69)</f>
+        <v>0.179312852394843</v>
+      </c>
+      <c r="F80" s="23" t="n">
+        <f aca="false">IF(F69=0,0,F79/F69)</f>
+        <v>0.204901627953686</v>
       </c>
       <c r="G80" s="3"/>
       <c r="H80" s="3"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="18" t="s">
+      <c r="A81" s="20" t="s">
         <v>462</v>
       </c>
-      <c r="B81" s="24" t="n">
-        <f aca="false">B77-B80</f>
-        <v>111624.996400968</v>
-      </c>
-      <c r="C81" s="24" t="n">
-        <f aca="false">C77-C80</f>
-        <v>196729.197321936</v>
-      </c>
-      <c r="D81" s="24" t="n">
-        <f aca="false">D77-D80</f>
-        <v>246221.101559904</v>
-      </c>
-      <c r="E81" s="24" t="n">
-        <f aca="false">E77-E80</f>
-        <v>389643.817609133</v>
-      </c>
-      <c r="F81" s="24" t="n">
-        <f aca="false">F77-F80</f>
-        <v>528304.310081433</v>
+      <c r="B81" s="17" t="n">
+        <f aca="false">MAX(0,B56-1)*'Equipment plan'!$G$10</f>
+        <v>27700</v>
+      </c>
+      <c r="C81" s="17" t="n">
+        <f aca="false">MAX(0,C56-B56)*'Equipment plan'!$G$10</f>
+        <v>0</v>
+      </c>
+      <c r="D81" s="17" t="n">
+        <f aca="false">MAX(0,D56-C56)*'Equipment plan'!$G$10</f>
+        <v>13850</v>
+      </c>
+      <c r="E81" s="17" t="n">
+        <f aca="false">MAX(0,E56-D56)*'Equipment plan'!$G$10</f>
+        <v>27700</v>
+      </c>
+      <c r="F81" s="17" t="n">
+        <f aca="false">MAX(0,F56-E56)*'Equipment plan'!$G$10</f>
+        <v>13850</v>
       </c>
       <c r="G81" s="3"/>
       <c r="H81" s="3"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="20" t="s">
+      <c r="A82" s="18" t="s">
         <v>463</v>
       </c>
-      <c r="B82" s="23" t="n">
-        <f aca="false">IF(B71=0,0,B81/B71)</f>
-        <v>0.134446722542266</v>
-      </c>
-      <c r="C82" s="23" t="n">
-        <f aca="false">IF(C71=0,0,C81/C71)</f>
-        <v>0.170115333808873</v>
-      </c>
-      <c r="D82" s="23" t="n">
-        <f aca="false">IF(D71=0,0,D81/D71)</f>
-        <v>0.163788671092509</v>
-      </c>
-      <c r="E82" s="23" t="n">
-        <f aca="false">IF(E71=0,0,E81/E71)</f>
-        <v>0.179312852394843</v>
-      </c>
-      <c r="F82" s="23" t="n">
-        <f aca="false">IF(F71=0,0,F81/F71)</f>
-        <v>0.204901627953686</v>
+      <c r="B82" s="24" t="n">
+        <f aca="false">Assumptions!$B$62+B79-B81</f>
+        <v>194380.703301936</v>
+      </c>
+      <c r="C82" s="24" t="n">
+        <f aca="false">B82+C79-C81</f>
+        <v>391109.900623872</v>
+      </c>
+      <c r="D82" s="24" t="n">
+        <f aca="false">C82+D79-D81</f>
+        <v>623481.002183775</v>
+      </c>
+      <c r="E82" s="24" t="n">
+        <f aca="false">D82+E79-E81</f>
+        <v>985424.819792908</v>
+      </c>
+      <c r="F82" s="24" t="n">
+        <f aca="false">E82+F79-F81</f>
+        <v>1499879.12987434</v>
       </c>
       <c r="G82" s="3"/>
-      <c r="H82" s="3"/>
+      <c r="H82" s="8" t="s">
+        <v>464</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="20" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B83" s="17" t="n">
-        <f aca="false">MAX(0,B57-1)*'Equipment plan'!$G$10</f>
-        <v>13850</v>
+        <f aca="false">B79+Assumptions!$B$78*12</f>
+        <v>269080.703301936</v>
       </c>
       <c r="C83" s="17" t="n">
-        <f aca="false">MAX(0,C57-B57)*'Equipment plan'!$G$10</f>
-        <v>13850</v>
+        <f aca="false">C79+Assumptions!$B$78*12</f>
+        <v>268729.197321936</v>
       </c>
       <c r="D83" s="17" t="n">
-        <f aca="false">MAX(0,D57-C57)*'Equipment plan'!$G$10</f>
-        <v>13850</v>
+        <f aca="false">D79+Assumptions!$B$78*12</f>
+        <v>318221.101559904</v>
       </c>
       <c r="E83" s="17" t="n">
-        <f aca="false">MAX(0,E57-D57)*'Equipment plan'!$G$10</f>
-        <v>27700</v>
+        <f aca="false">E79+Assumptions!$B$78*12</f>
+        <v>461643.817609133</v>
       </c>
       <c r="F83" s="17" t="n">
-        <f aca="false">MAX(0,F57-E57)*'Equipment plan'!$G$10</f>
-        <v>13850</v>
+        <f aca="false">F79+Assumptions!$B$78*12</f>
+        <v>600304.310081433</v>
       </c>
       <c r="G83" s="3"/>
       <c r="H83" s="3"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="18" t="s">
-        <v>465</v>
-      </c>
-      <c r="B84" s="24" t="n">
-        <f aca="false">Assumptions!$B$62+B81-B83</f>
-        <v>122774.996400968</v>
-      </c>
-      <c r="C84" s="24" t="n">
-        <f aca="false">B84+C81-C83</f>
-        <v>305654.193722904</v>
-      </c>
-      <c r="D84" s="24" t="n">
-        <f aca="false">C84+D81-D83</f>
-        <v>538025.295282807</v>
-      </c>
-      <c r="E84" s="24" t="n">
-        <f aca="false">D84+E81-E83</f>
-        <v>899969.11289194</v>
-      </c>
-      <c r="F84" s="24" t="n">
-        <f aca="false">E84+F81-F83</f>
-        <v>1414423.42297337</v>
+      <c r="A84" s="20" t="s">
+        <v>466</v>
+      </c>
+      <c r="B84" s="17" t="n">
+        <f aca="false">MAX(0,B83)*2.46</f>
+        <v>661938.530122762</v>
+      </c>
+      <c r="C84" s="17" t="n">
+        <f aca="false">MAX(0,C83)*2.46</f>
+        <v>661073.825411962</v>
+      </c>
+      <c r="D84" s="17" t="n">
+        <f aca="false">MAX(0,D83)*2.46</f>
+        <v>782823.909837363</v>
+      </c>
+      <c r="E84" s="17" t="n">
+        <f aca="false">MAX(0,E83)*2.46</f>
+        <v>1135643.79131847</v>
+      </c>
+      <c r="F84" s="17" t="n">
+        <f aca="false">MAX(0,F83)*2.46</f>
+        <v>1476748.60280033</v>
       </c>
       <c r="G84" s="3"/>
       <c r="H84" s="8" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="20" t="s">
-        <v>467</v>
-      </c>
-      <c r="B85" s="17" t="n">
-        <f aca="false">B81+Assumptions!$B$78*12</f>
-        <v>183624.996400968</v>
-      </c>
-      <c r="C85" s="17" t="n">
-        <f aca="false">C81+Assumptions!$B$78*12</f>
-        <v>268729.197321936</v>
-      </c>
-      <c r="D85" s="17" t="n">
-        <f aca="false">D81+Assumptions!$B$78*12</f>
-        <v>318221.101559904</v>
-      </c>
-      <c r="E85" s="17" t="n">
-        <f aca="false">E81+Assumptions!$B$78*12</f>
-        <v>461643.817609133</v>
-      </c>
-      <c r="F85" s="17" t="n">
-        <f aca="false">F81+Assumptions!$B$78*12</f>
-        <v>600304.310081433</v>
-      </c>
+      <c r="A85" s="3"/>
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
       <c r="G85" s="3"/>
       <c r="H85" s="3"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="20" t="s">
-        <v>468</v>
-      </c>
-      <c r="B86" s="17" t="n">
-        <f aca="false">MAX(0,B85)*2.46</f>
-        <v>451717.491146381</v>
-      </c>
-      <c r="C86" s="17" t="n">
-        <f aca="false">MAX(0,C85)*2.46</f>
-        <v>661073.825411962</v>
-      </c>
-      <c r="D86" s="17" t="n">
-        <f aca="false">MAX(0,D85)*2.46</f>
-        <v>782823.909837363</v>
-      </c>
-      <c r="E86" s="17" t="n">
-        <f aca="false">MAX(0,E85)*2.46</f>
-        <v>1135643.79131847</v>
-      </c>
-      <c r="F86" s="17" t="n">
-        <f aca="false">MAX(0,F85)*2.46</f>
-        <v>1476748.60280033</v>
-      </c>
+    <row r="86" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="B86" s="6"/>
+      <c r="C86" s="6"/>
+      <c r="D86" s="6"/>
+      <c r="E86" s="6"/>
+      <c r="F86" s="6"/>
       <c r="G86" s="3"/>
-      <c r="H86" s="8" t="s">
-        <v>469</v>
+      <c r="H86" s="41" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="3"/>
-      <c r="B87" s="3"/>
-      <c r="C87" s="3"/>
-      <c r="D87" s="3"/>
-      <c r="E87" s="3"/>
-      <c r="F87" s="3"/>
+      <c r="A87" s="30" t="s">
+        <v>436</v>
+      </c>
+      <c r="B87" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="C87" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="D87" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="E87" s="30" t="s">
+        <v>345</v>
+      </c>
+      <c r="F87" s="30" t="s">
+        <v>346</v>
+      </c>
       <c r="G87" s="3"/>
       <c r="H87" s="3"/>
     </row>
-    <row r="88" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="5" t="s">
-        <v>472</v>
-      </c>
-      <c r="B88" s="6"/>
-      <c r="C88" s="6"/>
-      <c r="D88" s="6"/>
-      <c r="E88" s="6"/>
-      <c r="F88" s="6"/>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="20" t="s">
+        <v>351</v>
+      </c>
+      <c r="B88" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="C88" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D88" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="E88" s="34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F88" s="34" t="n">
+        <v>5</v>
+      </c>
       <c r="G88" s="3"/>
-      <c r="H88" s="41" t="s">
-        <v>473</v>
+      <c r="H88" s="8" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="30" t="s">
-        <v>436</v>
-      </c>
-      <c r="B89" s="30" t="s">
-        <v>192</v>
-      </c>
-      <c r="C89" s="30" t="s">
-        <v>193</v>
-      </c>
-      <c r="D89" s="30" t="s">
-        <v>344</v>
-      </c>
-      <c r="E89" s="30" t="s">
-        <v>345</v>
-      </c>
-      <c r="F89" s="30" t="s">
-        <v>346</v>
+      <c r="A89" s="20" t="s">
+        <v>438</v>
+      </c>
+      <c r="B89" s="13" t="n">
+        <v>48</v>
+      </c>
+      <c r="C89" s="13" t="n">
+        <v>48</v>
+      </c>
+      <c r="D89" s="13" t="n">
+        <v>48</v>
+      </c>
+      <c r="E89" s="13" t="n">
+        <v>48</v>
+      </c>
+      <c r="F89" s="13" t="n">
+        <v>48</v>
       </c>
       <c r="G89" s="3"/>
-      <c r="H89" s="3"/>
+      <c r="H89" s="8" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="20" t="s">
-        <v>351</v>
-      </c>
-      <c r="B90" s="34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C90" s="34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D90" s="34" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E90" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="F90" s="34" t="n">
-        <v>4.5</v>
+        <v>301</v>
+      </c>
+      <c r="B90" s="11" t="n">
+        <v>52</v>
+      </c>
+      <c r="C90" s="17" t="n">
+        <f aca="false">B90*(1+$B$91)</f>
+        <v>53.56</v>
+      </c>
+      <c r="D90" s="17" t="n">
+        <f aca="false">C90*(1+$B$91)</f>
+        <v>55.1668</v>
+      </c>
+      <c r="E90" s="17" t="n">
+        <f aca="false">D90*(1+$B$91)</f>
+        <v>56.821804</v>
+      </c>
+      <c r="F90" s="17" t="n">
+        <f aca="false">E90*(1+$B$91)</f>
+        <v>58.52645812</v>
       </c>
       <c r="G90" s="3"/>
-      <c r="H90" s="8" t="s">
-        <v>437</v>
-      </c>
+      <c r="H90" s="3"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="20" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B91" s="14" t="n">
-        <v>0.85</v>
+        <v>0.03</v>
       </c>
       <c r="C91" s="14" t="n">
-        <v>0.95</v>
+        <v>0.03</v>
       </c>
       <c r="D91" s="14" t="n">
-        <v>0.95</v>
+        <v>0.03</v>
       </c>
       <c r="E91" s="14" t="n">
-        <v>0.95</v>
+        <v>0.03</v>
       </c>
       <c r="F91" s="14" t="n">
-        <v>0.95</v>
+        <v>0.03</v>
       </c>
       <c r="G91" s="3"/>
-      <c r="H91" s="8" t="s">
-        <v>439</v>
-      </c>
+      <c r="H91" s="3"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B92" s="13" t="n">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="C92" s="13" t="n">
-        <v>48</v>
+        <v>300</v>
       </c>
       <c r="D92" s="13" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="E92" s="13" t="n">
-        <v>48</v>
+        <v>720</v>
       </c>
       <c r="F92" s="13" t="n">
-        <v>48</v>
+        <v>950</v>
       </c>
       <c r="G92" s="3"/>
-      <c r="H92" s="8" t="s">
-        <v>441</v>
-      </c>
+      <c r="H92" s="3"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="B93" s="11" t="n">
-        <v>52</v>
-      </c>
-      <c r="C93" s="17" t="n">
-        <f aca="false">B93*(1+$B$94)</f>
-        <v>53.56</v>
-      </c>
-      <c r="D93" s="17" t="n">
-        <f aca="false">C93*(1+$B$94)</f>
-        <v>55.1668</v>
-      </c>
-      <c r="E93" s="17" t="n">
-        <f aca="false">D93*(1+$B$94)</f>
-        <v>56.821804</v>
-      </c>
-      <c r="F93" s="17" t="n">
-        <f aca="false">E93*(1+$B$94)</f>
-        <v>58.52645812</v>
+        <v>442</v>
+      </c>
+      <c r="B93" s="14" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="C93" s="14" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="D93" s="14" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="E93" s="14" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F93" s="14" t="n">
+        <v>0.045</v>
       </c>
       <c r="G93" s="3"/>
       <c r="H93" s="3"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="20" t="s">
-        <v>442</v>
-      </c>
-      <c r="B94" s="14" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="C94" s="14" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D94" s="14" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E94" s="14" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F94" s="14" t="n">
-        <v>0.03</v>
+        <v>443</v>
+      </c>
+      <c r="B94" s="11" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C94" s="11" t="n">
+        <v>22000</v>
+      </c>
+      <c r="D94" s="11" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E94" s="11" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F94" s="11" t="n">
+        <v>22000</v>
       </c>
       <c r="G94" s="3"/>
       <c r="H94" s="3"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="20" t="s">
-        <v>443</v>
-      </c>
-      <c r="B95" s="13" t="n">
-        <v>130</v>
-      </c>
-      <c r="C95" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="D95" s="13" t="n">
-        <v>500</v>
-      </c>
-      <c r="E95" s="13" t="n">
-        <v>720</v>
-      </c>
-      <c r="F95" s="13" t="n">
-        <v>950</v>
+        <v>444</v>
+      </c>
+      <c r="B95" s="11" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C95" s="11" t="n">
+        <v>54000</v>
+      </c>
+      <c r="D95" s="11" t="n">
+        <v>191000</v>
+      </c>
+      <c r="E95" s="11" t="n">
+        <v>265000</v>
+      </c>
+      <c r="F95" s="11" t="n">
+        <v>290000</v>
       </c>
       <c r="G95" s="3"/>
-      <c r="H95" s="3"/>
+      <c r="H95" s="8" t="s">
+        <v>445</v>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="20" t="s">
-        <v>444</v>
-      </c>
-      <c r="B96" s="14" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="C96" s="14" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="D96" s="14" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="E96" s="14" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="F96" s="14" t="n">
-        <v>0.045</v>
-      </c>
+      <c r="A96" s="42" t="s">
+        <v>446</v>
+      </c>
+      <c r="B96" s="43"/>
+      <c r="C96" s="43"/>
+      <c r="D96" s="43"/>
+      <c r="E96" s="43"/>
+      <c r="F96" s="43"/>
       <c r="G96" s="3"/>
-      <c r="H96" s="3"/>
+      <c r="H96" s="43"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="20" t="s">
-        <v>445</v>
-      </c>
-      <c r="B97" s="11" t="n">
-        <v>22000</v>
-      </c>
-      <c r="C97" s="11" t="n">
-        <v>22000</v>
-      </c>
-      <c r="D97" s="11" t="n">
-        <v>22000</v>
-      </c>
-      <c r="E97" s="11" t="n">
-        <v>22000</v>
-      </c>
-      <c r="F97" s="11" t="n">
-        <v>22000</v>
+        <v>447</v>
+      </c>
+      <c r="B97" s="21" t="n">
+        <f aca="false">B88*Assumptions!$B$10*12</f>
+        <v>504</v>
+      </c>
+      <c r="C97" s="21" t="n">
+        <f aca="false">C88*Assumptions!$B$10*12</f>
+        <v>756</v>
+      </c>
+      <c r="D97" s="21" t="n">
+        <f aca="false">D88*Assumptions!$B$10*12</f>
+        <v>1008</v>
+      </c>
+      <c r="E97" s="21" t="n">
+        <f aca="false">E88*Assumptions!$B$10*12</f>
+        <v>1134</v>
+      </c>
+      <c r="F97" s="21" t="n">
+        <f aca="false">F88*Assumptions!$B$10*12</f>
+        <v>1260</v>
       </c>
       <c r="G97" s="3"/>
       <c r="H97" s="3"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="20" t="s">
-        <v>446</v>
-      </c>
-      <c r="B98" s="11" t="n">
-        <v>12000</v>
-      </c>
-      <c r="C98" s="11" t="n">
-        <v>54000</v>
-      </c>
-      <c r="D98" s="11" t="n">
-        <v>191000</v>
-      </c>
-      <c r="E98" s="11" t="n">
-        <v>265000</v>
-      </c>
-      <c r="F98" s="11" t="n">
-        <v>290000</v>
+      <c r="A98" s="18" t="s">
+        <v>448</v>
+      </c>
+      <c r="B98" s="22" t="n">
+        <f aca="false">B97*B89</f>
+        <v>24192</v>
+      </c>
+      <c r="C98" s="22" t="n">
+        <f aca="false">C97*C89</f>
+        <v>36288</v>
+      </c>
+      <c r="D98" s="22" t="n">
+        <f aca="false">D97*D89</f>
+        <v>48384</v>
+      </c>
+      <c r="E98" s="22" t="n">
+        <f aca="false">E97*E89</f>
+        <v>54432</v>
+      </c>
+      <c r="F98" s="22" t="n">
+        <f aca="false">F97*F89</f>
+        <v>60480</v>
       </c>
       <c r="G98" s="3"/>
-      <c r="H98" s="8" t="s">
-        <v>447</v>
-      </c>
+      <c r="H98" s="3"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="42" t="s">
-        <v>448</v>
-      </c>
-      <c r="B99" s="43"/>
-      <c r="C99" s="43"/>
-      <c r="D99" s="43"/>
-      <c r="E99" s="43"/>
-      <c r="F99" s="43"/>
+      <c r="A99" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="B99" s="17" t="n">
+        <f aca="false">B98*B90</f>
+        <v>1257984</v>
+      </c>
+      <c r="C99" s="17" t="n">
+        <f aca="false">C98*C90</f>
+        <v>1943585.28</v>
+      </c>
+      <c r="D99" s="17" t="n">
+        <f aca="false">D98*D90</f>
+        <v>2669190.4512</v>
+      </c>
+      <c r="E99" s="17" t="n">
+        <f aca="false">E98*E90</f>
+        <v>3092924.435328</v>
+      </c>
+      <c r="F99" s="17" t="n">
+        <f aca="false">F98*F90</f>
+        <v>3539680.1870976</v>
+      </c>
       <c r="G99" s="3"/>
-      <c r="H99" s="43"/>
+      <c r="H99" s="3"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="20" t="s">
-        <v>449</v>
-      </c>
-      <c r="B100" s="21" t="n">
-        <f aca="false">B90*Assumptions!$B$10*12</f>
-        <v>378</v>
-      </c>
-      <c r="C100" s="21" t="n">
-        <f aca="false">C90*Assumptions!$B$10*12</f>
-        <v>630</v>
-      </c>
-      <c r="D100" s="21" t="n">
-        <f aca="false">D90*Assumptions!$B$10*12</f>
-        <v>882</v>
-      </c>
-      <c r="E100" s="21" t="n">
-        <f aca="false">E90*Assumptions!$B$10*12</f>
-        <v>1008</v>
-      </c>
-      <c r="F100" s="21" t="n">
-        <f aca="false">F90*Assumptions!$B$10*12</f>
-        <v>1134</v>
+        <v>361</v>
+      </c>
+      <c r="B100" s="17" t="n">
+        <f aca="false">B92*Assumptions!$B$30*Assumptions!$B$33</f>
+        <v>24277.5</v>
+      </c>
+      <c r="C100" s="17" t="n">
+        <f aca="false">C92*Assumptions!$B$30*Assumptions!$B$33</f>
+        <v>56025</v>
+      </c>
+      <c r="D100" s="17" t="n">
+        <f aca="false">D92*Assumptions!$B$30*Assumptions!$B$33</f>
+        <v>93375</v>
+      </c>
+      <c r="E100" s="17" t="n">
+        <f aca="false">E92*Assumptions!$B$30*Assumptions!$B$33</f>
+        <v>134460</v>
+      </c>
+      <c r="F100" s="17" t="n">
+        <f aca="false">F92*Assumptions!$B$30*Assumptions!$B$33</f>
+        <v>177412.5</v>
       </c>
       <c r="G100" s="3"/>
       <c r="H100" s="3"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="18" t="s">
-        <v>450</v>
-      </c>
-      <c r="B101" s="22" t="n">
-        <f aca="false">B100*B92</f>
-        <v>18144</v>
-      </c>
-      <c r="C101" s="22" t="n">
-        <f aca="false">C100*C92</f>
-        <v>30240</v>
-      </c>
-      <c r="D101" s="22" t="n">
-        <f aca="false">D100*D92</f>
-        <v>42336</v>
-      </c>
-      <c r="E101" s="22" t="n">
-        <f aca="false">E100*E92</f>
-        <v>48384</v>
-      </c>
-      <c r="F101" s="22" t="n">
-        <f aca="false">F100*F92</f>
-        <v>54432</v>
+        <v>217</v>
+      </c>
+      <c r="B101" s="24" t="n">
+        <f aca="false">B99+B100</f>
+        <v>1282261.5</v>
+      </c>
+      <c r="C101" s="24" t="n">
+        <f aca="false">C99+C100</f>
+        <v>1999610.28</v>
+      </c>
+      <c r="D101" s="24" t="n">
+        <f aca="false">D99+D100</f>
+        <v>2762565.4512</v>
+      </c>
+      <c r="E101" s="24" t="n">
+        <f aca="false">E99+E100</f>
+        <v>3227384.435328</v>
+      </c>
+      <c r="F101" s="24" t="n">
+        <f aca="false">F99+F100</f>
+        <v>3717092.6870976</v>
       </c>
       <c r="G101" s="3"/>
       <c r="H101" s="3"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="20" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B102" s="17" t="n">
-        <f aca="false">B101*B93</f>
-        <v>943488</v>
+        <f aca="false">B88*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(B1)-2)</f>
+        <v>333696.24</v>
       </c>
       <c r="C102" s="17" t="n">
-        <f aca="false">C101*C93</f>
-        <v>1619654.4</v>
+        <f aca="false">C88*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(C1)-2)</f>
+        <v>515560.6908</v>
       </c>
       <c r="D102" s="17" t="n">
-        <f aca="false">D101*D93</f>
-        <v>2335541.6448</v>
+        <f aca="false">D88*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(D1)-2)</f>
+        <v>708036.682032</v>
       </c>
       <c r="E102" s="17" t="n">
-        <f aca="false">E101*E93</f>
-        <v>2749266.164736</v>
+        <f aca="false">E88*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(E1)-2)</f>
+        <v>820437.50530458</v>
       </c>
       <c r="F102" s="17" t="n">
-        <f aca="false">F101*F93</f>
-        <v>3185712.16838784</v>
+        <f aca="false">F88*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(F1)-2)</f>
+        <v>938945.144959686</v>
       </c>
       <c r="G102" s="3"/>
       <c r="H102" s="3"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="20" t="s">
-        <v>361</v>
+        <v>451</v>
       </c>
       <c r="B103" s="17" t="n">
-        <f aca="false">B95*Assumptions!$B$30*Assumptions!$B$33</f>
-        <v>24277.5</v>
+        <f aca="false">B99*Assumptions!$B$22+B92*Assumptions!$B$33*Assumptions!$B$37</f>
+        <v>258421.8</v>
       </c>
       <c r="C103" s="17" t="n">
-        <f aca="false">C95*Assumptions!$B$30*Assumptions!$B$33</f>
-        <v>56025</v>
+        <f aca="false">C99*Assumptions!$B$22+C92*Assumptions!$B$33*Assumptions!$B$37</f>
+        <v>404467.056</v>
       </c>
       <c r="D103" s="17" t="n">
-        <f aca="false">D95*Assumptions!$B$30*Assumptions!$B$33</f>
-        <v>93375</v>
+        <f aca="false">D99*Assumptions!$B$22+D92*Assumptions!$B$33*Assumptions!$B$37</f>
+        <v>560088.09024</v>
       </c>
       <c r="E103" s="17" t="n">
-        <f aca="false">E95*Assumptions!$B$30*Assumptions!$B$33</f>
-        <v>134460</v>
+        <f aca="false">E99*Assumptions!$B$22+E92*Assumptions!$B$33*Assumptions!$B$37</f>
+        <v>656384.8870656</v>
       </c>
       <c r="F103" s="17" t="n">
-        <f aca="false">F95*Assumptions!$B$30*Assumptions!$B$33</f>
-        <v>177412.5</v>
+        <f aca="false">F99*Assumptions!$B$22+F92*Assumptions!$B$33*Assumptions!$B$37</f>
+        <v>757811.03741952</v>
       </c>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="18" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B104" s="24" t="n">
-        <f aca="false">B102+B103</f>
-        <v>967765.5</v>
+        <f aca="false">B101-B102-B103</f>
+        <v>690143.46</v>
       </c>
       <c r="C104" s="24" t="n">
-        <f aca="false">C102+C103</f>
-        <v>1675679.4</v>
+        <f aca="false">C101-C102-C103</f>
+        <v>1079582.5332</v>
       </c>
       <c r="D104" s="24" t="n">
-        <f aca="false">D102+D103</f>
-        <v>2428916.6448</v>
+        <f aca="false">D101-D102-D103</f>
+        <v>1494440.678928</v>
       </c>
       <c r="E104" s="24" t="n">
-        <f aca="false">E102+E103</f>
-        <v>2883726.164736</v>
+        <f aca="false">E101-E102-E103</f>
+        <v>1750562.04295782</v>
       </c>
       <c r="F104" s="24" t="n">
-        <f aca="false">F102+F103</f>
-        <v>3363124.66838784</v>
+        <f aca="false">F101-F102-F103</f>
+        <v>2020336.50471839</v>
       </c>
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="20" t="s">
-        <v>452</v>
-      </c>
-      <c r="B105" s="17" t="n">
-        <f aca="false">B90*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(B1)-2)</f>
-        <v>250272.18</v>
-      </c>
-      <c r="C105" s="17" t="n">
-        <f aca="false">C90*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(C1)-2)</f>
-        <v>429633.909</v>
-      </c>
-      <c r="D105" s="17" t="n">
-        <f aca="false">D90*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(D1)-2)</f>
-        <v>619532.096778</v>
-      </c>
-      <c r="E105" s="17" t="n">
-        <f aca="false">E90*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(E1)-2)</f>
-        <v>729277.78249296</v>
-      </c>
-      <c r="F105" s="17" t="n">
-        <f aca="false">F90*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(F1)-2)</f>
-        <v>845050.630463718</v>
+        <v>265</v>
+      </c>
+      <c r="B105" s="23" t="n">
+        <f aca="false">IF(B101=0,0,B104/B101)</f>
+        <v>0.538223646268721</v>
+      </c>
+      <c r="C105" s="23" t="n">
+        <f aca="false">IF(C101=0,0,C104/C101)</f>
+        <v>0.539896470826305</v>
+      </c>
+      <c r="D105" s="23" t="n">
+        <f aca="false">IF(D101=0,0,D104/D101)</f>
+        <v>0.540961184568078</v>
+      </c>
+      <c r="E105" s="23" t="n">
+        <f aca="false">IF(E101=0,0,E104/E101)</f>
+        <v>0.542408900469246</v>
+      </c>
+      <c r="F105" s="23" t="n">
+        <f aca="false">IF(F101=0,0,F104/F101)</f>
+        <v>0.543525995929879</v>
       </c>
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="20" t="s">
+        <v>452</v>
+      </c>
+      <c r="B106" s="17" t="n">
+        <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+B88*B94+B95+B101*B93+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,B88-1)</f>
+        <v>274802.07660896</v>
+      </c>
+      <c r="C106" s="17" t="n">
+        <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+C88*C94+C95+C101*C93+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,C88-1)</f>
+        <v>398683.080817921</v>
+      </c>
+      <c r="D106" s="17" t="n">
+        <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+D88*D94+D95+D101*D93+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,D88-1)</f>
+        <v>619616.372630881</v>
+      </c>
+      <c r="E106" s="17" t="n">
+        <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+E88*E94+E95+E101*E93+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,E88-1)</f>
+        <v>739333.381471121</v>
+      </c>
+      <c r="F106" s="17" t="n">
+        <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+F88*F94+F95+F101*F93+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,F88-1)</f>
+        <v>811170.407355233</v>
+      </c>
+      <c r="G106" s="3"/>
+      <c r="H106" s="8" t="s">
         <v>453</v>
       </c>
-      <c r="B106" s="17" t="n">
-        <f aca="false">B102*Assumptions!$B$22+B95*Assumptions!$B$33*Assumptions!$B$37</f>
-        <v>195522.6</v>
-      </c>
-      <c r="C106" s="17" t="n">
-        <f aca="false">C102*Assumptions!$B$22+C95*Assumptions!$B$33*Assumptions!$B$37</f>
-        <v>339680.88</v>
-      </c>
-      <c r="D106" s="17" t="n">
-        <f aca="false">D102*Assumptions!$B$22+D95*Assumptions!$B$33*Assumptions!$B$37</f>
-        <v>493358.32896</v>
-      </c>
-      <c r="E106" s="17" t="n">
-        <f aca="false">E102*Assumptions!$B$22+E95*Assumptions!$B$33*Assumptions!$B$37</f>
-        <v>587653.2329472</v>
-      </c>
-      <c r="F106" s="17" t="n">
-        <f aca="false">F102*Assumptions!$B$22+F95*Assumptions!$B$33*Assumptions!$B$37</f>
-        <v>687017.433677568</v>
-      </c>
-      <c r="G106" s="3"/>
-      <c r="H106" s="3"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="18" t="s">
-        <v>224</v>
+        <v>454</v>
       </c>
       <c r="B107" s="24" t="n">
-        <f aca="false">B104-B105-B106</f>
-        <v>521970.72</v>
+        <f aca="false">B104-B106</f>
+        <v>415341.38339104</v>
       </c>
       <c r="C107" s="24" t="n">
-        <f aca="false">C104-C105-C106</f>
-        <v>906364.611</v>
+        <f aca="false">C104-C106</f>
+        <v>680899.452382079</v>
       </c>
       <c r="D107" s="24" t="n">
-        <f aca="false">D104-D105-D106</f>
-        <v>1316026.219062</v>
+        <f aca="false">D104-D106</f>
+        <v>874824.306297119</v>
       </c>
       <c r="E107" s="24" t="n">
-        <f aca="false">E104-E105-E106</f>
-        <v>1566795.14929584</v>
+        <f aca="false">E104-E106</f>
+        <v>1011228.6614867</v>
       </c>
       <c r="F107" s="24" t="n">
-        <f aca="false">F104-F105-F106</f>
-        <v>1831056.60424655</v>
+        <f aca="false">F104-F106</f>
+        <v>1209166.09736316</v>
       </c>
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="20" t="s">
-        <v>265</v>
-      </c>
-      <c r="B108" s="23" t="n">
-        <f aca="false">IF(B104=0,0,B107/B104)</f>
-        <v>0.53935661066653</v>
-      </c>
-      <c r="C108" s="23" t="n">
-        <f aca="false">IF(C104=0,0,C107/C104)</f>
-        <v>0.540893807610215</v>
-      </c>
-      <c r="D108" s="23" t="n">
-        <f aca="false">IF(D104=0,0,D107/D104)</f>
-        <v>0.541816131022629</v>
-      </c>
-      <c r="E108" s="23" t="n">
-        <f aca="false">IF(E104=0,0,E107/E104)</f>
-        <v>0.543323138117477</v>
-      </c>
-      <c r="F108" s="23" t="n">
-        <f aca="false">IF(F104=0,0,F107/F104)</f>
-        <v>0.544451004584465</v>
+        <v>455</v>
+      </c>
+      <c r="B108" s="11" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C108" s="11" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D108" s="11" t="n">
+        <v>66000</v>
+      </c>
+      <c r="E108" s="11" t="n">
+        <v>72000</v>
+      </c>
+      <c r="F108" s="11" t="n">
+        <v>72000</v>
       </c>
       <c r="G108" s="3"/>
-      <c r="H108" s="3"/>
+      <c r="H108" s="8" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="20" t="s">
-        <v>454</v>
-      </c>
-      <c r="B109" s="17" t="n">
-        <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+B90*B97+B98+B104*B96+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,B90-1)</f>
-        <v>235849.60205448</v>
-      </c>
-      <c r="C109" s="17" t="n">
-        <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+C90*C97+C98+C104*C96+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,C90-1)</f>
-        <v>359306.03666344</v>
-      </c>
-      <c r="D109" s="17" t="n">
-        <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+D90*D97+D98+D104*D96+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,D90-1)</f>
-        <v>579802.021788401</v>
-      </c>
-      <c r="E109" s="17" t="n">
-        <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+E90*E97+E98+E104*E96+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,E90-1)</f>
-        <v>699068.604740001</v>
-      </c>
-      <c r="F109" s="17" t="n">
-        <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+F90*F97+F98+F104*F96+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,F90-1)</f>
-        <v>770441.691958814</v>
+        <v>457</v>
+      </c>
+      <c r="B109" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C109" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D109" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E109" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F109" s="14" t="n">
+        <v>0.1</v>
       </c>
       <c r="G109" s="3"/>
       <c r="H109" s="8" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="18" t="s">
-        <v>456</v>
-      </c>
-      <c r="B110" s="24" t="n">
-        <f aca="false">B107-B109</f>
-        <v>286121.11794552</v>
-      </c>
-      <c r="C110" s="24" t="n">
-        <f aca="false">C107-C109</f>
-        <v>547058.57433656</v>
-      </c>
-      <c r="D110" s="24" t="n">
-        <f aca="false">D107-D109</f>
-        <v>736224.197273599</v>
-      </c>
-      <c r="E110" s="24" t="n">
-        <f aca="false">E107-E109</f>
-        <v>867726.544555839</v>
-      </c>
-      <c r="F110" s="24" t="n">
-        <f aca="false">F107-F109</f>
-        <v>1060614.91228774</v>
+      <c r="A110" s="20" t="s">
+        <v>459</v>
+      </c>
+      <c r="B110" s="17" t="n">
+        <f aca="false">B108+IF(B108=0,0,B109*MAX(0,B107-MAX(0,'5-year plan'!$B$44)))</f>
+        <v>101534.138339104</v>
+      </c>
+      <c r="C110" s="17" t="n">
+        <f aca="false">C108+IF(C108=0,0,C109*MAX(0,C107-MAX(0,'5-year plan'!$B$44)))</f>
+        <v>128089.945238208</v>
+      </c>
+      <c r="D110" s="17" t="n">
+        <f aca="false">D108+IF(D108=0,0,D109*MAX(0,D107-MAX(0,'5-year plan'!$B$44)))</f>
+        <v>153482.430629712</v>
+      </c>
+      <c r="E110" s="17" t="n">
+        <f aca="false">E108+IF(E108=0,0,E109*MAX(0,E107-MAX(0,'5-year plan'!$B$44)))</f>
+        <v>173122.86614867</v>
+      </c>
+      <c r="F110" s="17" t="n">
+        <f aca="false">F108+IF(F108=0,0,F109*MAX(0,F107-MAX(0,'5-year plan'!$B$44)))</f>
+        <v>192916.609736316</v>
       </c>
       <c r="G110" s="3"/>
       <c r="H110" s="3"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="20" t="s">
-        <v>457</v>
-      </c>
-      <c r="B111" s="11" t="n">
-        <v>60000</v>
-      </c>
-      <c r="C111" s="11" t="n">
-        <v>60000</v>
-      </c>
-      <c r="D111" s="11" t="n">
-        <v>66000</v>
-      </c>
-      <c r="E111" s="11" t="n">
-        <v>72000</v>
-      </c>
-      <c r="F111" s="11" t="n">
-        <v>72000</v>
+      <c r="A111" s="18" t="s">
+        <v>460</v>
+      </c>
+      <c r="B111" s="24" t="n">
+        <f aca="false">B107-B110</f>
+        <v>313807.245051936</v>
+      </c>
+      <c r="C111" s="24" t="n">
+        <f aca="false">C107-C110</f>
+        <v>552809.507143871</v>
+      </c>
+      <c r="D111" s="24" t="n">
+        <f aca="false">D107-D110</f>
+        <v>721341.875667407</v>
+      </c>
+      <c r="E111" s="24" t="n">
+        <f aca="false">E107-E110</f>
+        <v>838105.795338029</v>
+      </c>
+      <c r="F111" s="24" t="n">
+        <f aca="false">F107-F110</f>
+        <v>1016249.48762684</v>
       </c>
       <c r="G111" s="3"/>
-      <c r="H111" s="8" t="s">
-        <v>458</v>
-      </c>
+      <c r="H111" s="3"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="20" t="s">
-        <v>459</v>
-      </c>
-      <c r="B112" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C112" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D112" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E112" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F112" s="14" t="n">
-        <v>0.1</v>
+        <v>461</v>
+      </c>
+      <c r="B112" s="23" t="n">
+        <f aca="false">IF(B101=0,0,B111/B101)</f>
+        <v>0.24472952284065</v>
+      </c>
+      <c r="C112" s="23" t="n">
+        <f aca="false">IF(C101=0,0,C111/C101)</f>
+        <v>0.276458624299467</v>
+      </c>
+      <c r="D112" s="23" t="n">
+        <f aca="false">IF(D101=0,0,D111/D101)</f>
+        <v>0.261113044526808</v>
+      </c>
+      <c r="E112" s="23" t="n">
+        <f aca="false">IF(E101=0,0,E111/E101)</f>
+        <v>0.259685764783349</v>
+      </c>
+      <c r="F112" s="23" t="n">
+        <f aca="false">IF(F101=0,0,F111/F101)</f>
+        <v>0.273399017235795</v>
       </c>
       <c r="G112" s="3"/>
-      <c r="H112" s="8" t="s">
-        <v>460</v>
-      </c>
+      <c r="H112" s="3"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="20" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B113" s="17" t="n">
-        <f aca="false">B111+IF(B111=0,0,B112*MAX(0,B110-MAX(0,'5-year plan'!$B$44)))</f>
-        <v>88612.111794552</v>
+        <f aca="false">MAX(0,B88-1)*'Equipment plan'!$G$10</f>
+        <v>27700</v>
       </c>
       <c r="C113" s="17" t="n">
-        <f aca="false">C111+IF(C111=0,0,C112*MAX(0,C110-MAX(0,'5-year plan'!$B$44)))</f>
-        <v>114705.857433656</v>
+        <f aca="false">MAX(0,C88-B88)*'Equipment plan'!$G$10</f>
+        <v>27700</v>
       </c>
       <c r="D113" s="17" t="n">
-        <f aca="false">D111+IF(D111=0,0,D112*MAX(0,D110-MAX(0,'5-year plan'!$B$44)))</f>
-        <v>139622.41972736</v>
+        <f aca="false">MAX(0,D88-C88)*'Equipment plan'!$G$10</f>
+        <v>27700</v>
       </c>
       <c r="E113" s="17" t="n">
-        <f aca="false">E111+IF(E111=0,0,E112*MAX(0,E110-MAX(0,'5-year plan'!$B$44)))</f>
-        <v>158772.654455584</v>
+        <f aca="false">MAX(0,E88-D88)*'Equipment plan'!$G$10</f>
+        <v>13850</v>
       </c>
       <c r="F113" s="17" t="n">
-        <f aca="false">F111+IF(F111=0,0,F112*MAX(0,F110-MAX(0,'5-year plan'!$B$44)))</f>
-        <v>178061.491228774</v>
+        <f aca="false">MAX(0,F88-E88)*'Equipment plan'!$G$10</f>
+        <v>13850</v>
       </c>
       <c r="G113" s="3"/>
       <c r="H113" s="3"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="18" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B114" s="24" t="n">
-        <f aca="false">B110-B113</f>
-        <v>197509.006150968</v>
+        <f aca="false">Assumptions!$B$62+B111-B113</f>
+        <v>311107.245051936</v>
       </c>
       <c r="C114" s="24" t="n">
-        <f aca="false">C110-C113</f>
-        <v>432352.716902904</v>
+        <f aca="false">B114+C111-C113</f>
+        <v>836216.752195807</v>
       </c>
       <c r="D114" s="24" t="n">
-        <f aca="false">D110-D113</f>
-        <v>596601.777546239</v>
+        <f aca="false">C114+D111-D113</f>
+        <v>1529858.62786321</v>
       </c>
       <c r="E114" s="24" t="n">
-        <f aca="false">E110-E113</f>
-        <v>708953.890100255</v>
+        <f aca="false">D114+E111-E113</f>
+        <v>2354114.42320124</v>
       </c>
       <c r="F114" s="24" t="n">
-        <f aca="false">F110-F113</f>
-        <v>882553.421058966</v>
+        <f aca="false">E114+F111-F113</f>
+        <v>3356513.91082809</v>
       </c>
       <c r="G114" s="3"/>
-      <c r="H114" s="3"/>
+      <c r="H114" s="8" t="s">
+        <v>464</v>
+      </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="20" t="s">
-        <v>463</v>
-      </c>
-      <c r="B115" s="23" t="n">
-        <f aca="false">IF(B104=0,0,B114/B104)</f>
-        <v>0.204087670154565</v>
-      </c>
-      <c r="C115" s="23" t="n">
-        <f aca="false">IF(C104=0,0,C114/C104)</f>
-        <v>0.258016370495993</v>
-      </c>
-      <c r="D115" s="23" t="n">
-        <f aca="false">IF(D104=0,0,D114/D104)</f>
-        <v>0.245624640443503</v>
-      </c>
-      <c r="E115" s="23" t="n">
-        <f aca="false">IF(E104=0,0,E114/E104)</f>
-        <v>0.245846467244285</v>
-      </c>
-      <c r="F115" s="23" t="n">
-        <f aca="false">IF(F104=0,0,F114/F104)</f>
-        <v>0.262420667706627</v>
+        <v>465</v>
+      </c>
+      <c r="B115" s="17" t="n">
+        <f aca="false">B111+Assumptions!$B$78*12</f>
+        <v>385807.245051936</v>
+      </c>
+      <c r="C115" s="17" t="n">
+        <f aca="false">C111+Assumptions!$B$78*12</f>
+        <v>624809.507143871</v>
+      </c>
+      <c r="D115" s="17" t="n">
+        <f aca="false">D111+Assumptions!$B$78*12</f>
+        <v>793341.875667407</v>
+      </c>
+      <c r="E115" s="17" t="n">
+        <f aca="false">E111+Assumptions!$B$78*12</f>
+        <v>910105.795338029</v>
+      </c>
+      <c r="F115" s="17" t="n">
+        <f aca="false">F111+Assumptions!$B$78*12</f>
+        <v>1088249.48762684</v>
       </c>
       <c r="G115" s="3"/>
       <c r="H115" s="3"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="20" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B116" s="17" t="n">
-        <f aca="false">MAX(0,B90-1)*'Equipment plan'!$G$10</f>
-        <v>13850</v>
+        <f aca="false">MAX(0,B115)*2.46</f>
+        <v>949085.822827762</v>
       </c>
       <c r="C116" s="17" t="n">
-        <f aca="false">MAX(0,C90-B90)*'Equipment plan'!$G$10</f>
-        <v>27700</v>
+        <f aca="false">MAX(0,C115)*2.46</f>
+        <v>1537031.38757392</v>
       </c>
       <c r="D116" s="17" t="n">
-        <f aca="false">MAX(0,D90-C90)*'Equipment plan'!$G$10</f>
-        <v>27700</v>
+        <f aca="false">MAX(0,D115)*2.46</f>
+        <v>1951621.01414182</v>
       </c>
       <c r="E116" s="17" t="n">
-        <f aca="false">MAX(0,E90-D90)*'Equipment plan'!$G$10</f>
-        <v>13850</v>
+        <f aca="false">MAX(0,E115)*2.46</f>
+        <v>2238860.25653155</v>
       </c>
       <c r="F116" s="17" t="n">
-        <f aca="false">MAX(0,F90-E90)*'Equipment plan'!$G$10</f>
-        <v>13850</v>
+        <f aca="false">MAX(0,F115)*2.46</f>
+        <v>2677093.73956204</v>
       </c>
       <c r="G116" s="3"/>
-      <c r="H116" s="3"/>
-    </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="18" t="s">
-        <v>465</v>
-      </c>
-      <c r="B117" s="24" t="n">
-        <f aca="false">Assumptions!$B$62+B114-B116</f>
-        <v>208659.006150968</v>
-      </c>
-      <c r="C117" s="24" t="n">
-        <f aca="false">B117+C114-C116</f>
-        <v>613311.723053872</v>
-      </c>
-      <c r="D117" s="24" t="n">
-        <f aca="false">C117+D114-D116</f>
-        <v>1182213.50060011</v>
-      </c>
-      <c r="E117" s="24" t="n">
-        <f aca="false">D117+E114-E116</f>
-        <v>1877317.39070037</v>
-      </c>
-      <c r="F117" s="24" t="n">
-        <f aca="false">E117+F114-F116</f>
-        <v>2746020.81175933</v>
-      </c>
-      <c r="G117" s="3"/>
-      <c r="H117" s="8" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="20" t="s">
+      <c r="H116" s="8" t="s">
         <v>467</v>
-      </c>
-      <c r="B118" s="17" t="n">
-        <f aca="false">B114+Assumptions!$B$78*12</f>
-        <v>269509.006150968</v>
-      </c>
-      <c r="C118" s="17" t="n">
-        <f aca="false">C114+Assumptions!$B$78*12</f>
-        <v>504352.716902904</v>
-      </c>
-      <c r="D118" s="17" t="n">
-        <f aca="false">D114+Assumptions!$B$78*12</f>
-        <v>668601.777546239</v>
-      </c>
-      <c r="E118" s="17" t="n">
-        <f aca="false">E114+Assumptions!$B$78*12</f>
-        <v>780953.890100255</v>
-      </c>
-      <c r="F118" s="17" t="n">
-        <f aca="false">F114+Assumptions!$B$78*12</f>
-        <v>954553.421058966</v>
-      </c>
-      <c r="G118" s="3"/>
-      <c r="H118" s="3"/>
-    </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="20" t="s">
-        <v>468</v>
-      </c>
-      <c r="B119" s="17" t="n">
-        <f aca="false">MAX(0,B118)*2.46</f>
-        <v>662992.155131381</v>
-      </c>
-      <c r="C119" s="17" t="n">
-        <f aca="false">MAX(0,C118)*2.46</f>
-        <v>1240707.68358114</v>
-      </c>
-      <c r="D119" s="17" t="n">
-        <f aca="false">MAX(0,D118)*2.46</f>
-        <v>1644760.37276375</v>
-      </c>
-      <c r="E119" s="17" t="n">
-        <f aca="false">MAX(0,E118)*2.46</f>
-        <v>1921146.56964663</v>
-      </c>
-      <c r="F119" s="17" t="n">
-        <f aca="false">MAX(0,F118)*2.46</f>
-        <v>2348201.41580506</v>
-      </c>
-      <c r="G119" s="3"/>
-      <c r="H119" s="8" t="s">
-        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -15469,7 +15388,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -15491,7 +15410,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -15533,7 +15452,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -15555,25 +15474,25 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="8" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="8" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="8" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
@@ -15615,25 +15534,25 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="8" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="8" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="8" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
@@ -15675,25 +15594,25 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="8" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="8" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="8" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
@@ -15755,7 +15674,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="40" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -15817,7 +15736,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B15" s="19" t="n">
         <v>1</v>
@@ -15871,7 +15790,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -15893,7 +15812,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B17" s="16" t="n">
         <f aca="false">'5-year plan'!C7</f>
@@ -15957,12 +15876,12 @@
       </c>
       <c r="Q17" s="3"/>
       <c r="R17" s="8" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>493</v>
+        <v>438</v>
       </c>
       <c r="B18" s="21" t="n">
         <f aca="false">Assumptions!$B$11</f>
@@ -16026,12 +15945,12 @@
       </c>
       <c r="Q18" s="3"/>
       <c r="R18" s="8" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B19" s="21" t="n">
         <f aca="false">B17*Assumptions!$B$10*12</f>
@@ -16098,7 +16017,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="18" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B20" s="22" t="n">
         <f aca="false">B19*B18</f>
@@ -16165,7 +16084,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="42" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B21" s="43"/>
       <c r="C21" s="43"/>
@@ -16187,7 +16106,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="20" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B22" s="21" t="n">
         <f aca="false">ROUND(B17*Assumptions!$B$26,0)</f>
@@ -16254,7 +16173,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="20" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="B23" s="21" t="n">
         <f aca="false">IF(B17&gt;=2,ROUNDUP(B17/Assumptions!$B$51,0),0)</f>
@@ -16321,7 +16240,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="20" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B24" s="21" t="n">
         <f aca="false">IF(B17&gt;=3,ROUNDUP(B17/Assumptions!$B$52,0),0)</f>
@@ -16388,7 +16307,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B25" s="21" t="n">
         <f aca="false">IF(B17&gt;=4,ROUNDUP(B17/Assumptions!$B$53,0),0)</f>
@@ -16544,7 +16463,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="20" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B28" s="17" t="n">
         <f aca="false">B20*B27</f>
@@ -16611,7 +16530,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="20" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B29" s="21" t="n">
         <f aca="false">B20/Assumptions!$B$17</f>
@@ -16678,7 +16597,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="20" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B30" s="21" t="n">
         <f aca="false">B29*Assumptions!$B$31</f>
@@ -16745,7 +16664,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="18" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B31" s="22" t="n">
         <f aca="false">B30</f>
@@ -16809,7 +16728,7 @@
       </c>
       <c r="Q31" s="3"/>
       <c r="R31" s="8" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16881,7 +16800,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B33" s="21" t="n">
         <f aca="false">ROUNDUP(B31*Assumptions!$B$33/Assumptions!$B$54,0)</f>
@@ -16945,12 +16864,12 @@
       </c>
       <c r="Q33" s="3"/>
       <c r="R33" s="8" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="18" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B34" s="22" t="n">
         <f aca="false">1+B22+B23+B24+B25+B33</f>
@@ -17017,7 +16936,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="20" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B35" s="17" t="n">
         <f aca="false">B31*Assumptions!$B$33*B32</f>
@@ -17151,7 +17070,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="42" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B37" s="43"/>
       <c r="C37" s="43"/>
@@ -17173,7 +17092,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="20" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="B38" s="17" t="n">
         <f aca="false">B17*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12</f>
@@ -17240,7 +17159,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="20" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B39" s="17" t="n">
         <f aca="false">B28*Assumptions!$B$22+B31*Assumptions!$B$33*Assumptions!$B$37</f>
@@ -17374,7 +17293,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="20" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B41" s="17" t="n">
         <f aca="false">(B23*Assumptions!$B$55+B24*Assumptions!$B$56+B25*Assumptions!$B$57)</f>
@@ -17441,7 +17360,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="20" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B42" s="17" t="n">
         <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+B17*22000+B36*0.05+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,B17-1)</f>
@@ -17505,12 +17424,12 @@
       </c>
       <c r="Q42" s="3"/>
       <c r="R42" s="8" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="18" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="B43" s="24" t="n">
         <f aca="false">B40-B41-B42</f>
@@ -17577,7 +17496,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -17599,7 +17518,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="20" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B45" s="17" t="n">
         <f aca="false">MAX(0,B17-1)*'Equipment plan'!$B$10</f>
@@ -17666,7 +17585,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="20" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B46" s="17" t="n">
         <f aca="false">Assumptions!$B$45+B45</f>
@@ -17733,7 +17652,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="20" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="B47" s="17" t="n">
         <f aca="false">B46*(1-1/Assumptions!$B$46)</f>
@@ -17797,12 +17716,12 @@
       </c>
       <c r="Q47" s="3"/>
       <c r="R47" s="8" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="20" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B48" s="17" t="n">
         <f aca="false">MAX(0,B45*0.8*0.85)</f>
@@ -17866,12 +17785,12 @@
       </c>
       <c r="Q48" s="3"/>
       <c r="R48" s="8" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="20" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B49" s="17" t="n">
         <f aca="false">MAX(0,B43)*Assumptions!$B$44</f>
@@ -17935,12 +17854,12 @@
       </c>
       <c r="Q49" s="3"/>
       <c r="R49" s="8" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="18" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B50" s="24" t="n">
         <f aca="false">B49</f>
@@ -18004,12 +17923,12 @@
       </c>
       <c r="Q50" s="3"/>
       <c r="R50" s="8" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="18" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="B51" s="24" t="n">
         <f aca="false">Assumptions!$B$62+B43-B49-B45*0.2</f>
@@ -18073,12 +17992,12 @@
       </c>
       <c r="Q51" s="3"/>
       <c r="R51" s="8" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="20" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B52" s="17" t="n">
         <f aca="false">B43+Assumptions!$B$78*12</f>
@@ -18145,7 +18064,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="20" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B53" s="17" t="n">
         <f aca="false">B52-B35+B31*Assumptions!$B$33*Assumptions!$B$37</f>
@@ -18209,12 +18128,12 @@
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="8" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="18" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B54" s="24" t="n">
         <f aca="false">MAX(0,B52)*Assumptions!$B$47+B51-B48</f>
@@ -18278,12 +18197,12 @@
       </c>
       <c r="Q54" s="3"/>
       <c r="R54" s="8" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="18" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B55" s="24" t="n">
         <f aca="false">MAX(0,B53)*Assumptions!$B$48+B51-B48</f>
@@ -18350,7 +18269,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="18" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B56" s="24" t="n">
         <f aca="false">B54-B55</f>
@@ -18414,12 +18333,12 @@
       </c>
       <c r="Q56" s="3"/>
       <c r="R56" s="8" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="20" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B57" s="17" t="n">
         <f aca="false">B35*Assumptions!$B$49</f>
@@ -18510,7 +18429,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B1" s="3"/>
     </row>
@@ -18520,106 +18439,106 @@
     </row>
     <row r="3" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="47" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="47" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B4" s="48" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="47" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="B5" s="48" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="47" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B6" s="48" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="47" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B7" s="48" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="47" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="B8" s="48" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="47" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B9" s="48" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="47" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="B10" s="48" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="47" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B11" s="48" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="47" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="B12" s="48" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="47" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="B13" s="48" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="47" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B14" s="48" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="47" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B15" s="48" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Scag-Scapes-Proforma.xlsx
+++ b/docs/Scag-Scapes-Proforma.xlsx
@@ -16,7 +16,10 @@
     <sheet name="5-year plan" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="Three cases 5-yr" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="Long range 15-yr" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Sources &amp; notes" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Funding options" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Investor scenarios" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Buyout &amp; exit" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Sources &amp; notes" sheetId="12" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -28,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="737">
   <si>
     <t xml:space="preserve">Scag Scapes LLC - Growth Proforma - Assumptions</t>
   </si>
@@ -282,13 +285,13 @@
     <t xml:space="preserve">Value multiple WITH a recurring service book (x owner cash)</t>
   </si>
   <si>
-    <t xml:space="preserve">Judgment, not a published figure: contracted, repeating revenue and a manager in the seat sit at the top of the range. BizBuySell median for the category is 2.46x (945 sales).</t>
+    <t xml:space="preserve">JUDGMENT OVERLAY, not comp-derived - and narrower than it used to be. The transaction data does not support a large recurring-revenue premium at this size: pest control, the most contract-recurring home service there is, sells at 2.04x SDE - BELOW landscaping's 2.30x (BizBuySell, 945 sales). Recurring shows up in the REVENUE multiple (0.96x vs 0.63x), not the earnings multiple. 2.5x is defensible as an upper-quartile outcome for a documented, non-owner-dependent business (landscaping upper quartile is 3.01x), not as proof that plans add half a turn. The real multiple expansion is on the Buyout &amp; exit tab: it comes from getting bigger, not from the plan book.</t>
   </si>
   <si>
     <t xml:space="preserve">Value multiple WITHOUT a service book (x owner cash)</t>
   </si>
   <si>
-    <t xml:space="preserve">Judgment: a pure job shop with no repeating revenue sits at the bottom of the range.</t>
+    <t xml:space="preserve">Judgment: a pure job shop with no repeating revenue sits at the bottom of the range. Landscaping lower quartile is 1.70x, median 2.30x.</t>
   </si>
   <si>
     <t xml:space="preserve">Service contracts also valued at (x annual plan revenue)</t>
@@ -597,6 +600,120 @@
     <t xml:space="preserve">2 weeks of paid shadowing on Crew 1 + PPE + phones.</t>
   </si>
   <si>
+    <t xml:space="preserve">FUNDING - HOW THE GROWTH GETS PAID FOR (see the Funding options tab)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outside capital raised ($) - debt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What gets borrowed. $150,000 is the sweet spot on an SBA 7(a): the guaranty is 85% at or below $150,000 and drops to 75% above it, and the upfront fee steps from 2% to 3% at $150,001. That one dollar costs about $1,500. The next efficient size is above $350,000, where the rate cap falls from prime+6% to prime+3%. There is no good reason to land between the two.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interest rate on the raise (APR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SBA 7(a) variable cap for a $50,001-$250,000 loan is prime + 6.0%. Prime was 6.75% on Sept 15, 2026, so the cap is 12.75%. The cap is a ceiling, not a price - two competing term sheets is the lever that moves it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Term on the raise (years)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SBA working capital is 'ten years or less'. Take all ten: a longer term lowers the payment, which raises the coverage ratio, which is what gets the loan approved. There is no SBA prepayment penalty under a 15-year maturity, so paying it down early stays free.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upfront fee on the raise (% of the amount)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SBA FY2026 guaranty fee: 2.00% at or below $150,000, 3.00% from $150,001 to $700,000. Plus a 0.55% annual service fee on the guaranteed balance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash Charlie puts in himself ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The initial investment above. An expansion loan to an existing business carries NO mandatory SBA equity injection - the 10% rule applies to startups and changes of ownership, not to this. Lenders still like to see skin in the game.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INVESTOR - ONLY IF EQUITY IS SOLD (see the Investor scenarios tab)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outside equity taken ($) - set 0 to keep the company whole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set here as a worked example so the Investor scenarios tab shows real numbers - it is NOT a recommendation. Set it to 0 to model keeping the company whole, which is what the tab will tell you to do. At this size equity is the most expensive money on the table, and that tab prices it against the identical dollars borrowed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of the company given for it (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What the investor owns afterwards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year the investor comes in (1-15)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selling equity before year 1 is proven prices the company at today's near-zero earnings. Waiting until the two-crew run rate is real is worth more than any term you could negotiate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investor preferred return (% a year, accrues until exit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A preferred return plus a 1x non-participating preference lets the owner keep more percentage for the same dollars than straight common does.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NED'S STAKE - PROFITS INTEREST (see the Buyout &amp; exit tab)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ned's growth share of operating profit (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paid on profit above what the business already earns. Unchanged from the blueprint.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ned's profits interest (% of value created ABOVE the hurdle)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An LLC profits interest: a share of future profit and future appreciation only, with zero claim on what the company is worth the day it is granted. Rev. Proc. 93-27 means it is not taxable to either side at grant. This is the structure that costs Charlie none of today's value.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The hurdle - what the company is worth the day Ned starts ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The profits interest pays on nothing below this. Set at the indicative value of the business as it stands today. A CPA should price it contemporaneously and file an 83(b) within 30 days.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXIT MULTIPLES - FROM TRANSACTION DATA, NOT JUDGMENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDE multiple - under $1M revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BizBuySell closed sales, landscaping and yard service, 945 businesses 2021-2025: median 2.30x SDE, lower quartile 1.70x, upper quartile 3.01x. This is what a business this size actually sells for.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBITDA multiple - $2M to $5M revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBBA / M&amp;A Source Market Pulse Q1 2026, 203 closed transactions: median 4.0x EBITDA in the $2M-$5M band. Crossing into this band is where the multiple actually changes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBITDA multiple - above $5M revenue (private-equity add-on)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reported 2026 home-services add-on pricing: 5-8x EBITDA for $1-2M of EBITDA, more with a high recurring share. Platforms want roughly $3M revenue and $500K EBITDA before they will look at you.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manager's salary that replaces the owner when pricing on EBITDA ($/yr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A buyer pricing on EBITDA deducts the cost of replacing the owner. SDE does not. This is the single biggest reason the same company gets two very different valuations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash at closing in a sale (%) - the rest is seller note and earnout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBBA Q1 2026, $2M-$5M band: 76% cash at close, about 15% seller financing. Note that since June 2025 an SBA-financed buyer's seller note must sit on FULL STANDBY for the life of the loan - no principal, no interest, often for ten years.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Scag Scapes LLC - 24-month operating proforma ($, monthly)</t>
   </si>
   <si>
@@ -1629,6 +1746,345 @@
     <t xml:space="preserve">Cross-check: the plan book priced on its own (x annual plan revenue)</t>
   </si>
   <si>
+    <t xml:space="preserve">What the money costs - every source priced on the same loan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blue = change it. Each row borrows the same amount (the 'Outside capital raised' cell on Assumptions) and shows what it actually costs to pay back. Rates are the live September 2026 market, sourced on the Sources tab. The order is cheapest first, and the order is the recommendation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amount being raised</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change this on the Assumptions tab and every row below re-prices.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compare on THIS column, not total cost - a short loan looks cheap only because it is short.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where the money comes from</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rate (APR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Term (yrs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upfront fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly payment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total paid back</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost of the money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost per year borrowed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What it is, and what they want from you</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supplier net terms (SiteOne, Ferguson, aggregate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free money, and the first call. SiteOne bills Net 15th prox - every invoice in a month is due on the 15th of the next one, so roughly 30 days of float. At two crews, materials run $16,000-19,000 a month; thirty days of terms on that is $16,000-19,000 of permanent working capital at zero cost, and it takes a credit application, not a loan committee. Do this before drawing anything.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manufacturer 0% on the equipment (Bobcat, Kubota, Deere)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bobcat is running 0% for 60 months on compact loaders and 0% for 48 on compact excavators, OR $8,000-10,000 cash in lieu - PROMO EXPIRES SEPT 30, 2026. It is not really 0%: giving up an $8,000 rebate on an $85,000 excavator to get the 0% is an implied 4.93% APR, and 5.78% on the loader. Still the cheapest equipment money available, but ask every dealer for BOTH numbers - the 0% term and the cash-in-lieu - and compare.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equipment loan, independent lender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6-14% for a well-qualified borrower in 2026; 7.5-9.5% is the realistic band here given two-plus years operating, $60,000 of unencumbered iron and an engineer owner. The machine secures it, but a sole owner signs personally anyway. Application-only up to $150,000-$250,000 - no financial statements, just the app, 3-6 months of bank statements and the vendor quote. Approval in 24-48 hours. Do NOT let a dealer steer you into a fair-market-value lease to hit a payment target: it costs you the depreciation deduction and you own nothing at the end.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Louisiana SSBCI loan guaranty, through a bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE LEAD. Louisiana's state guaranty covers up to 80% of a bank loan (or $1.5M), fee 0-2%, minimum 15% equity for an existing business, no application fee. The job test is one job under $100K and two jobs above - a second crew is three or four hires, so it is met on day one and it is the strongest paragraph in the package. Eligible for equipment AND working capital. You do not apply to the state; a Louisiana bank originates and files it. Because it takes most of the risk off the bank, it is the thing that makes a $150,000 ask worth a bank's time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SBA 7(a) Small Loan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prime + 6.0% is the cap for $50,001-$250,000, so 12.75% at a 6.75% prime. 85% SBA-guaranteed at or below $150,000. No mandatory equity injection for an expansion. Coverage test is 1.1x on historical AND/OR projected cash flow - projections are allowed, which matters enormously here. Expect a blanket lien on every business asset, a personal guarantee, and a lien on the house if there is equity in it. 30-75 days. Note the perverse pricing: a $360,000 loan is priced 300bp cheaper than a $150,000 one.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDFI / mission lender (TruFund, HOPE, LiftFund)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8-13%. Slower and dearer than a bank but far more forgiving on collateral, credit history and messy books - several will help fix the books rather than decline over them. TruFund runs contractor mobilization loans specifically, which is working capital against signed contracts. Lead with jobs created in Baton Rouge and at what wage: with a CDFI that is not decoration, it is the underwriting criterion. Good for a $50,000-$100,000 first tranche while a bank deal is still being packaged.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank line of credit (working capital only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8-14% secured, 10-16% unsecured. At this revenue expect $25,000-$50,000 offered - banks size unsecured lines near 10% of revenue. Interest only on what is drawn. The trap for a weather-driven business is the annual clean-up: most banks require it paid to zero for 30 days a year. Right tool for payroll float between a job finishing and the homeowner paying. Wrong tool for equipment - never fund a five-year asset on a one-year facility.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merchant cash advance / daily-debit 'revenue' product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO NOT. A 1.35 factor over nine months is 84% APR; a 1.49 over six months is 171%. The factor rate tells you nothing - the term does, and brokers quote the factor and bury the term. The mechanism that kills a drainage contractor is specific: money arrives in lumps 20-40 days after a job closes, and the advance debits EVERY BUSINESS DAY regardless. $714 a weekday on a $100,000 advance is 47% of gross revenue before materials, fuel or payroll, and after three rainless weeks the receivables stop and the debits do not. New York's attorney general cancelled $534M of merchant debt from one funder in January 2025. Louisiana now forces written disclosure of the total dollar cost - demand it, then do the division yourself.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE STACK - what to actually do, in order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open or expand supplier accounts this week. $16,000-19,000 of interest-free float, one credit application, no lender involved.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Get the equipment credit app in before Sept 30 while the 0% promos are live. Ask each dealer for the cash-in-lieu number too, and take whichever is genuinely cheaper.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Walk the SSBCI guaranty into a Baton Rouge bank - b1BANK or Hancock Whitney - with the package built by the LSU Small Business Development Center. Free, and the referral gets you a named lender instead of a web form.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Add a $25,000-$50,000 bank line of credit for payroll float only. Apply now; it takes 15-45 days.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Place the equipment in service before Dec 31 to use 100% bonus depreciation. Roughly $33,000-44,000 of tax deferred on a $138,500 package - but a fair-market-value lease forfeits it, so use a $1-buyout lease or a straight loan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Only if 1-5 come up short: SBA 7(a) at $150,000 flat. Not a dollar more - the fee and the guaranty both step at $150,001.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. Never the last row of the table above. A profitable business can be killed by 84% money faster than an unprofitable one can be killed by competition.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIMING - the one that has a date on it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SBA's new rulebook (SOP 50 10 8.1) applies to any loan given an SBA number on or after October 1, 2026. If Ned is admitted as an owner as part of the same transaction, the loan is reclassified as a change of ownership: the coverage test becomes 1.25x on HISTORICAL cash flow and projections may not be used to meet it. On today's filed revenue that fails. Kept as a plain expansion loan to the existing company with Charlie as sole owner, the test stays 1.1x on historical AND/OR projected cash flow. Separate the capital raise from any equity admission by at least twelve months. This is worth more than any rate either of us could negotiate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What selling a piece of the company actually costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blue = change it on the Assumptions tab. This tab answers one question: for the same dollars, is it cheaper to borrow or to sell equity? It prices the investor's claim year by year against the identical amount borrowed, and shows what Charlie keeps under each.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year shown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company is worth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investor would take</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charlie keeps - sold equity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loan still owed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interest paid in total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charlie keeps - borrowed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BORROWING WINS BY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set 'Outside equity taken' to a real number on the Assumptions tab to price a specific offer. At zero, the equity rows sit at zero and only the borrowing path is live.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE COMPANY, FOR REFERENCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What the whole company is worth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATH A - SELL A PIECE OF IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investor money in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lands once, in the year set on the Assumptions tab. Set the amount to 0 to take this path off the table entirely.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What the investor is owed if they take their preference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Their money back plus an accruing preferred return. A 1x non-participating preference means at exit they take the GREATER of this or their percentage - not both. That structure lets the owner give away less of the company for the same cheque.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What their percentage would be worth instead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The investor walks away with</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHARLIE KEEPS - having sold equity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATH B - BORROW THE SAME MONEY INSTEAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loan still outstanding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The SAME amount the investor would have put in, borrowed instead, paid down straight-line over the term. Like for like - that is the only way the comparison means anything.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interest paid on it, running total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every dollar of interest the loan will ever cost, added up. This is the true and complete price of Path B - and unlike a percentage of the company, it stops.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHARLIE KEEPS - having borrowed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The whole company, less what is still owed and less all the interest paid to get there.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE ANSWER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Borrowing leaves Charlie ahead by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive means debt was cheaper. The gap widens every year, because interest is a fixed cost that stops when the loan is paid and equity is a share of a number that keeps growing. That is the whole argument in one row.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity only wins if the company is worth less than</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Below this value the investor's percentage is worth less than the debt would have cost, and selling equity was the better call. Compare it against the value line at the top: if the plan works at all, this number is never reached.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WHAT THE MARKET WILL ACTUALLY DO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two things worth knowing before anyone goes looking for an investor. First, institutional minority growth equity does not exist at a $200,000-$500,000 cheque size for a non-technology service business - no fund has that mandate. The realistic sources are family, a local operator with money, or an independent sponsor writing a personal cheque, and each of those comes with a relationship attached to it. Second, and more important: selling equity today prices the company on today's near-zero earnings, so an investor would demand a percentage that only looks reasonable if you ignore the plan. Every month the two-crew run rate is real is a month the same cheque costs less of the company. If equity is ever taken, take it after year 1 is proven, take it as preferred with an accruing return rather than common, and use it for something debt genuinely cannot fund.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What it is worth, and what it costs to buy somebody out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blue = change it on the Assumptions tab. The multiple is not one number - it depends on how big the company is, because size decides who is allowed to buy it. Under $1M of revenue a business is priced on owner's cash. Over $2M it is priced on profit after paying somebody to do the owner's job, which is a different and much larger number.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priced on</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiple it earns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash at closing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ned's profits interest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charlie's share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every figure is a formula off the Assumptions tab and the long-range plan. Change a multiple, the hurdle, the manager's salary or Ned's percentage and all fifteen years move.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE TWO WAYS A BUYER COUNTS THE EARNINGS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner's cash (SDE) - what the owner takes out in total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profit plus the owner's draw. This is what a small buyer who will run it himself cares about, because he is buying a job plus a return.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBITDA - the same earnings after paying a manager to do the owner's job</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A financial buyer will not work in the business, so he deducts what it costs to replace the owner. Lower number, much higher multiple. This one line is why the same company gets two valuations that differ by a factor of two.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WHICH MULTIPLE APPLIES, AND WHY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiple the size band earns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Under $2M the buyer is an individual using an SBA loan, and the multiple is set by what his debt service can carry - it sits in a narrow 2.0-2.3x band no matter how good the business is. Over $2M the buyer pool changes to searchers and regional platforms at 4x EBITDA. Over $5M it changes again to private equity at 5-8x. Growing is what moves the multiple; the service book is not.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earnings the multiple is applied to</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WHAT THE WHOLE COMPANY IS WORTH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earnings x multiple, plus the cash in the bank, less what is still owed on equipment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash actually handed over at closing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The rest is a seller note and an earnout. If the buyer uses an SBA loan, that note now sits on full standby for the life of his loan - ten years of no principal and no interest. Price that in before celebrating a headline number.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NED'S PROFITS INTEREST - WHAT IT PAYS, AND WHAT IT COSTS CHARLIE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value created above the hurdle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everything above what the company was worth the day Ned started. Below the hurdle the profits interest pays nothing at all.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ned's share of it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charlie's share of the sale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charlie keeps 100% of what the company is worth today and the large majority of everything built on top of it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What Charlie would have without the plan (today's value, held flat)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The honest comparison: not Charlie's share versus 100%, but Charlie's share versus what a business that stays as it is would be worth.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charlie ahead by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUYING NED OUT INSTEAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost to buy Ned's interest out in cash that year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A call right at a formula price - the same multiple arithmetic above, usually with an agreed discount for an internal buyout - keeps this from ever becoming an argument. Paper it at the start, when nobody knows who will want out.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The same, paid over five years at the raise rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A buyout almost never gets paid in one cheque. Five years of monthly payments out of the profit the interest was earning anyway is the usual shape.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WHY THE PLAN IS WORTH MORE THAN THE PLAN BOOK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The recurring service book is a good business and it throws off real profit. What it does not do, at this size, is raise the multiple: pest control, the most contract-recurring home service there is, sells at 2.04x owner's cash - below landscaping's 2.30x across 945 recorded sales. Recurring revenue shows up in the revenue multiple (0.96x against 0.63x), not the earnings multiple. What actually moves the multiple is crossing the size thresholds that change who is allowed to buy you: an individual with an SBA loan under $2M, a searcher or regional platform at $2-5M, private equity above that. Roughly 2.0x to 4.0x to 6.0x on a bigger number each time. That is the argument for growing, and it is drawn from recorded transactions rather than from anybody's opinion.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sources and notes</t>
   </si>
   <si>
@@ -1702,6 +2158,84 @@
   </si>
   <si>
     <t xml:space="preserve">PDF (with elevations, scale, logo), DXF/DWG, CSV point cloud (x,y,z), PNG/JPG/SVG. No public API; Command imports the CSV/PDF. https://www.moasure.com/pages/features-export</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSJ Prime rate (Sept 15, 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75%, unchanged since the December 2025 cut (7.50% a year earlier). Every SBA rate cap in this workbook is prime plus a spread. https://www.bankrate.com/rates/interest-rates/wall-street-prime-rate/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SBA 7(a) rate caps and terms (SBA, current)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variable caps over prime: &lt;=$50K +6.5%; $50,001-$250,000 +6.0%; $250,001-$350,000 +4.5%; &gt;$350,000 +3.0%. Guaranty 85% at or below $150,000, 75% above. Max loan $5M. Working capital 10 years or less; equipment to useful life. No prepayment penalty under a 15-year maturity. https://www.sba.gov/partners/lenders/7a-loan-program/terms-conditions-eligibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SBA FY2026 guaranty fee schedule (Information Notice 5000-872051, eff. Aug 28, 2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;=$150,000: 2.00%. $150,001-$700,000: 3.00%. $700,001-$1M: 3.50%. &gt;$1M: 3.75%. Annual service fee 0.55% of the guaranteed balance. The step at $150,001 is why the raise is sized at $150,000 flat. https://www.naggl.org/fy-2026-loan-fees-and-clarification-of-fee-calculation-for-multiple-wcp-or-ewcp-loans/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SBA coverage ratio and the October 1, 2026 rule change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7(a) Small Loans require DSCR &gt;= 1.1:1 on a historical AND/OR projected basis (SBA Procedural Notice 5000-875701, eff. March 1, 2026 - the same notice retired the FICO SBSS minimum). SOP 50 10 8.1 applies to any loan given an SBA number on or after Oct 1, 2026; under its Appendix 15 a change of ownership is tested at 1.25x on HISTORICAL cash flow with projections not usable. Keeping the raise a plain expansion loan to the existing entity preserves the projection-based test. https://www.sba.gov/document/procedural-notice-5000-875701-sunset-sbss-score-7a-small-loans and https://www.doeren.com/viewpoint/sop-50-10-8-1-what-sba-lenders-should-be-thinking-about-before-oct-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Louisiana SSBCI - Small Business Loan Guaranty (LED)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">State guarantees up to 80% of a bank loan or $1.5M, fee 0-2%, 15% minimum equity for an existing business, no application fee. Job test: 1 job at or below $100K, 2 jobs above. Equipment, working capital, inventory all eligible; refinancing is not. A Louisiana bank originates and files it. LEDSSBCI2@la.gov, 225.342.3000. Collateral Support pledges up to $250,000 cash behind a loan where collateral falls short. https://www.louisianassbci.com/programs/small-business-loan-guaranty/ (note: the legacy LEDC page still states 75% / 1-4% - confirm current terms in writing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equipment finance market, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banks and credit unions 6-12% for strong credit; alternative lenders 10-25%; well-qualified borrowers 6-14%. Terms 12-60 months, most fixed, many programs with no down payment. Application-only up to $150,000-$250,000 with no financial statements. https://dimensionfunding.com/equipment-financing-rates-in-2026/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bobcat financing promotion (verified Sept 17, 2026; expires Sept 30, 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compact loaders 0% for 60 months OR up to $10,000 cash in lieu; compact excavators 0% for 48 months OR up to $8,000 in lieu. Forgoing an $8,000 rebate on an $85,000 excavator to take the 0%/48 is an implied 4.93% APR; the loader case is 5.78%. The 0% is cheap, not free. https://bobcatofhouston.com/current-promotions/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Section 179 and bonus depreciation, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Section 179 limit $2,560,000, phase-out from $4,090,000. Bonus depreciation 100%, permanent for qualified property acquired and placed in service after January 19, 2025. Section 179 is capped at business taxable income; bonus is not. A $1-buyout lease or a straight loan qualifies - a fair-market-value lease does not. https://www.section179.org/section_179_deduction/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merchant cash advance pricing and enforcement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Factor rates 1.09-1.5+, stated APR equivalents 30-350%+, terms 3-36 months, holdback 10-20% of daily receipts; default rates estimated 10-25%. Worked APRs: 1.22 over 12 months = 41%; 1.35 over 9 months = 84%; 1.49 over 6 months = 171%. New York AG judgment against Yellowstone Capital, Jan 16, 2025: over $1 billion, $534 million of merchant debt cancelled, permanent industry ban. Louisiana HB 470 (eff. Aug 1, 2025) requires written disclosure of total dollar cost on revenue-based financing of any size - but not APR. https://www.nav.com/business-financing-options/merchant-cash-advance/ and https://ag.ny.gov/resources/individuals/credit-debt-lending/yellowstone-settlement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BizBuySell valuation benchmarks by category (closed sales, 2021-2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Landscaping &amp; yard service, 945 sales: median revenue $708,412, median SDE $187,761, SDE multiple 2.30x (lower quartile 1.70x, upper quartile 3.01x), revenue multiple 0.63x. Plumbing, 226 sales: 2.24x SDE. Pest control - the most contract-recurring home service - 2.04x SDE but 0.96x revenue. The recurring premium shows up in the revenue multiple, not the earnings multiple. https://www.bizbuysell.com/learning-center/valuation-benchmarks/landscaping-yard-service/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBBA / M&amp;A Source Market Pulse Q1 2026 (300 advisors, 203 closed transactions)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median multiples by size: under $500K 2.0x SDE; $500K-$1M 2.8x SDE; $1M-$2M 3.0x SDE; $2M-$5M 4.0x EBITDA; $5M-$50M 4.5x EBITDA (5.8x in Q2 2026). Cash at close in the $2M-$5M band 76%, seller financing ~15%. Deals under $500K draw 1-2 offers; deals over $5M draw 3+ offers 87% of the time. https://wabusinessbrokers.com/wp-content/uploads/2026/05/Q1-2026-IBBA-Market-Pulse-Report-Exec-Summary-compressed-with-logo.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profits interest - the structure for Ned's stake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An LLC profits interest gives a share of future profit and future appreciation above a hurdle set at the company's value on the grant date, with no claim on value below it. Rev. Proc. 93-27: not a taxable event to either party at grant. Rev. Proc. 2001-43 covers unvested grants. File an 83(b) election immediately even though not technically required. The holder becomes a partner, receives a K-1 and pays self-employment tax; proceeds above the hurdle are capital gain; the company gets no deduction. A CPA should price the hurdle contemporaneously. https://www.thetaxadviser.com/issues/2025/jan/profits-interests-the-most-tax-efficient-equity-grant-to-employees/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seller notes on standby (SBA SOP 50 10 8, eff. June 1, 2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A seller note must be on FULL STANDBY for the entire term of the SBA loan to count toward a buyer's equity injection - typically no principal and no interest for ten years. Any year-5 or year-10 exit financed by an SBA buyer must be modelled with this haircut. https://www.pioneercapitaladvisory.com/post/investor-equity-sba-7a-sop-50-10-8-1-new-rules-vs-old-rules</t>
   </si>
   <si>
     <t xml:space="preserve">Model conventions</t>
@@ -1714,7 +2248,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
@@ -1722,8 +2256,9 @@
     <numFmt numFmtId="168" formatCode="0.00"/>
     <numFmt numFmtId="169" formatCode="\$0.00"/>
     <numFmt numFmtId="170" formatCode="@"/>
+    <numFmt numFmtId="171" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1825,8 +2360,16 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FFB0771B"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1848,7 +2391,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEEF1EF"/>
-        <bgColor rgb="FFD8E7EC"/>
+        <bgColor rgb="FFF6E9CF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6E9CF"/>
+        <bgColor rgb="FFEEF1EF"/>
       </patternFill>
     </fill>
   </fills>
@@ -1895,7 +2444,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="62">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2084,6 +2633,58 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="true"/>
     </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="true"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="true"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="true"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="true"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2114,14 +2715,14 @@
       <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FFB0771B"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF1F5A6E"/>
       <rgbColor rgb="FFC0C0C0"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFF6E9CF"/>
       <rgbColor rgb="FFD8E7EC"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -2344,7 +2945,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C108"/>
+  <dimension ref="A1:C129"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46"/>
@@ -2832,7 +3433,7 @@
         <v>83</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>84</v>
@@ -3464,6 +4065,3323 @@
       </c>
       <c r="C108" s="8" t="s">
         <v>188</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B109" s="6"/>
+      <c r="C109" s="6"/>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B110" s="10" t="n">
+        <v>150000</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B111" s="15" t="n">
+        <v>0.1275</v>
+      </c>
+      <c r="C111" s="8" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B112" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C112" s="8" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B113" s="14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B114" s="10" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C114" s="8" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B115" s="6"/>
+      <c r="C115" s="6"/>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B116" s="10" t="n">
+        <v>300000</v>
+      </c>
+      <c r="C116" s="8" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B117" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C117" s="8" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B118" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C118" s="8" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B119" s="14" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C119" s="8" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B120" s="6"/>
+      <c r="C120" s="6"/>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B121" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C121" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B122" s="15" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C122" s="8" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B123" s="10" t="n">
+        <v>170000</v>
+      </c>
+      <c r="C123" s="8" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B124" s="6"/>
+      <c r="C124" s="6"/>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B125" s="7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C125" s="8" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B126" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C126" s="8" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B127" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C127" s="8" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B128" s="10" t="n">
+        <v>85000</v>
+      </c>
+      <c r="C128" s="8" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B129" s="14" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="C129" s="8" t="s">
+        <v>226</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="true" password="ef11" formatCells="false" formatColumns="false" formatRows="false"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:R32"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="60"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>512</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="8" t="s">
+        <v>614</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="8" t="s">
+        <v>615</v>
+      </c>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="44" t="n">
+        <f aca="false">Assumptions!$B$39</f>
+        <v>10</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="46" t="n">
+        <f aca="false">INDEX(B16:P16,Assumptions!$B$39)</f>
+        <v>7462399.63412436</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="46" t="n">
+        <f aca="false">INDEX(B21:P21,Assumptions!$B$39)</f>
+        <v>1492479.92682487</v>
+      </c>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="46" t="n">
+        <f aca="false">INDEX(B22:P22,Assumptions!$B$39)</f>
+        <v>5969919.70729948</v>
+      </c>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="8" t="s">
+        <v>618</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="8" t="s">
+        <v>620</v>
+      </c>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="46" t="n">
+        <f aca="false">INDEX(B24:P24,Assumptions!$B$39)</f>
+        <v>30000</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="46" t="n">
+        <f aca="false">INDEX(B25:P25,Assumptions!$B$39)</f>
+        <v>240975</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="46" t="n">
+        <f aca="false">INDEX(B26:P26,Assumptions!$B$39)</f>
+        <v>7191424.63412436</v>
+      </c>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="46" t="n">
+        <f aca="false">INDEX(B28:P28,Assumptions!$B$39)</f>
+        <v>1221504.92682487</v>
+      </c>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="40" t="s">
+        <v>621</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="18" t="s">
+        <v>526</v>
+      </c>
+      <c r="B13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="I13" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="K13" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L13" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="M13" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="N13" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="O13" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="P13" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="18" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="6"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="20" t="s">
+        <v>623</v>
+      </c>
+      <c r="B15" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!B36</f>
+        <v>1107883.476</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!C36</f>
+        <v>1130224.27392</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!D36</f>
+        <v>1470581.13731659</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!E36</f>
+        <v>2128361.5241759</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!F36</f>
+        <v>2531696.60117519</v>
+      </c>
+      <c r="G15" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!G36</f>
+        <v>2960567.60023987</v>
+      </c>
+      <c r="H15" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!H36</f>
+        <v>3415973.30476096</v>
+      </c>
+      <c r="I15" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!I36</f>
+        <v>3898958.3702101</v>
+      </c>
+      <c r="J15" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!J36</f>
+        <v>4410614.70976327</v>
+      </c>
+      <c r="K15" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!K36</f>
+        <v>4952082.94628947</v>
+      </c>
+      <c r="L15" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!L36</f>
+        <v>5524553.93215493</v>
+      </c>
+      <c r="M15" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!M36</f>
+        <v>6129270.33838766</v>
+      </c>
+      <c r="N15" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!N36</f>
+        <v>6767528.314843</v>
+      </c>
+      <c r="O15" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!O36</f>
+        <v>7045784.99129078</v>
+      </c>
+      <c r="P15" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!P36</f>
+        <v>7328447.27269707</v>
+      </c>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="18" t="s">
+        <v>624</v>
+      </c>
+      <c r="B16" s="24" t="n">
+        <f aca="false">'Buyout &amp; exit'!B23</f>
+        <v>722514.397345807</v>
+      </c>
+      <c r="C16" s="24" t="n">
+        <f aca="false">'Buyout &amp; exit'!C23</f>
+        <v>856235.104687023</v>
+      </c>
+      <c r="D16" s="24" t="n">
+        <f aca="false">'Buyout &amp; exit'!D23</f>
+        <v>1115787.2095688</v>
+      </c>
+      <c r="E16" s="24" t="n">
+        <f aca="false">'Buyout &amp; exit'!E23</f>
+        <v>2188649.93481688</v>
+      </c>
+      <c r="F16" s="24" t="n">
+        <f aca="false">'Buyout &amp; exit'!F23</f>
+        <v>2541790.86545043</v>
+      </c>
+      <c r="G16" s="24" t="n">
+        <f aca="false">'Buyout &amp; exit'!G23</f>
+        <v>2953355.41513757</v>
+      </c>
+      <c r="H16" s="24" t="n">
+        <f aca="false">'Buyout &amp; exit'!H23</f>
+        <v>3974892.90433904</v>
+      </c>
+      <c r="I16" s="24" t="n">
+        <f aca="false">'Buyout &amp; exit'!I23</f>
+        <v>5134348.7386574</v>
+      </c>
+      <c r="J16" s="24" t="n">
+        <f aca="false">'Buyout &amp; exit'!J23</f>
+        <v>6440058.91028011</v>
+      </c>
+      <c r="K16" s="24" t="n">
+        <f aca="false">'Buyout &amp; exit'!K23</f>
+        <v>7462399.63412436</v>
+      </c>
+      <c r="L16" s="24" t="n">
+        <f aca="false">'Buyout &amp; exit'!L23</f>
+        <v>12150988.8443229</v>
+      </c>
+      <c r="M16" s="24" t="n">
+        <f aca="false">'Buyout &amp; exit'!M23</f>
+        <v>14478029.3494997</v>
+      </c>
+      <c r="N16" s="24" t="n">
+        <f aca="false">'Buyout &amp; exit'!N23</f>
+        <v>17026792.7358957</v>
+      </c>
+      <c r="O16" s="24" t="n">
+        <f aca="false">'Buyout &amp; exit'!O23</f>
+        <v>18917198.5068543</v>
+      </c>
+      <c r="P16" s="24" t="n">
+        <f aca="false">'Buyout &amp; exit'!P23</f>
+        <v>20874996.3881506</v>
+      </c>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="42" t="s">
+        <v>625</v>
+      </c>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="43"/>
+      <c r="L17" s="43"/>
+      <c r="M17" s="43"/>
+      <c r="N17" s="43"/>
+      <c r="O17" s="43"/>
+      <c r="P17" s="43"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="43"/>
+    </row>
+    <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="s">
+        <v>626</v>
+      </c>
+      <c r="B18" s="17" t="n">
+        <f aca="false">IF(1=Assumptions!$B$118,Assumptions!$B$116,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="17" t="n">
+        <f aca="false">IF(2=Assumptions!$B$118,Assumptions!$B$116,0)</f>
+        <v>300000</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <f aca="false">IF(3=Assumptions!$B$118,Assumptions!$B$116,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <f aca="false">IF(4=Assumptions!$B$118,Assumptions!$B$116,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <f aca="false">IF(5=Assumptions!$B$118,Assumptions!$B$116,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="17" t="n">
+        <f aca="false">IF(6=Assumptions!$B$118,Assumptions!$B$116,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="17" t="n">
+        <f aca="false">IF(7=Assumptions!$B$118,Assumptions!$B$116,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="17" t="n">
+        <f aca="false">IF(8=Assumptions!$B$118,Assumptions!$B$116,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="17" t="n">
+        <f aca="false">IF(9=Assumptions!$B$118,Assumptions!$B$116,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="17" t="n">
+        <f aca="false">IF(10=Assumptions!$B$118,Assumptions!$B$116,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="17" t="n">
+        <f aca="false">IF(11=Assumptions!$B$118,Assumptions!$B$116,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M18" s="17" t="n">
+        <f aca="false">IF(12=Assumptions!$B$118,Assumptions!$B$116,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N18" s="17" t="n">
+        <f aca="false">IF(13=Assumptions!$B$118,Assumptions!$B$116,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O18" s="17" t="n">
+        <f aca="false">IF(14=Assumptions!$B$118,Assumptions!$B$116,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P18" s="17" t="n">
+        <f aca="false">IF(15=Assumptions!$B$118,Assumptions!$B$116,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="51" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="s">
+        <v>628</v>
+      </c>
+      <c r="B19" s="17" t="n">
+        <f aca="false">IF(1&lt;Assumptions!$B$118,0,Assumptions!$B$116*(1+Assumptions!$B$119)^(1-Assumptions!$B$118+1))</f>
+        <v>0</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <f aca="false">IF(2&lt;Assumptions!$B$118,0,Assumptions!$B$116*(1+Assumptions!$B$119)^(2-Assumptions!$B$118+1))</f>
+        <v>324000</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <f aca="false">IF(3&lt;Assumptions!$B$118,0,Assumptions!$B$116*(1+Assumptions!$B$119)^(3-Assumptions!$B$118+1))</f>
+        <v>349920</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <f aca="false">IF(4&lt;Assumptions!$B$118,0,Assumptions!$B$116*(1+Assumptions!$B$119)^(4-Assumptions!$B$118+1))</f>
+        <v>377913.6</v>
+      </c>
+      <c r="F19" s="17" t="n">
+        <f aca="false">IF(5&lt;Assumptions!$B$118,0,Assumptions!$B$116*(1+Assumptions!$B$119)^(5-Assumptions!$B$118+1))</f>
+        <v>408146.688</v>
+      </c>
+      <c r="G19" s="17" t="n">
+        <f aca="false">IF(6&lt;Assumptions!$B$118,0,Assumptions!$B$116*(1+Assumptions!$B$119)^(6-Assumptions!$B$118+1))</f>
+        <v>440798.42304</v>
+      </c>
+      <c r="H19" s="17" t="n">
+        <f aca="false">IF(7&lt;Assumptions!$B$118,0,Assumptions!$B$116*(1+Assumptions!$B$119)^(7-Assumptions!$B$118+1))</f>
+        <v>476062.2968832</v>
+      </c>
+      <c r="I19" s="17" t="n">
+        <f aca="false">IF(8&lt;Assumptions!$B$118,0,Assumptions!$B$116*(1+Assumptions!$B$119)^(8-Assumptions!$B$118+1))</f>
+        <v>514147.280633856</v>
+      </c>
+      <c r="J19" s="17" t="n">
+        <f aca="false">IF(9&lt;Assumptions!$B$118,0,Assumptions!$B$116*(1+Assumptions!$B$119)^(9-Assumptions!$B$118+1))</f>
+        <v>555279.063084565</v>
+      </c>
+      <c r="K19" s="17" t="n">
+        <f aca="false">IF(10&lt;Assumptions!$B$118,0,Assumptions!$B$116*(1+Assumptions!$B$119)^(10-Assumptions!$B$118+1))</f>
+        <v>599701.38813133</v>
+      </c>
+      <c r="L19" s="17" t="n">
+        <f aca="false">IF(11&lt;Assumptions!$B$118,0,Assumptions!$B$116*(1+Assumptions!$B$119)^(11-Assumptions!$B$118+1))</f>
+        <v>647677.499181837</v>
+      </c>
+      <c r="M19" s="17" t="n">
+        <f aca="false">IF(12&lt;Assumptions!$B$118,0,Assumptions!$B$116*(1+Assumptions!$B$119)^(12-Assumptions!$B$118+1))</f>
+        <v>699491.699116383</v>
+      </c>
+      <c r="N19" s="17" t="n">
+        <f aca="false">IF(13&lt;Assumptions!$B$118,0,Assumptions!$B$116*(1+Assumptions!$B$119)^(13-Assumptions!$B$118+1))</f>
+        <v>755451.035045694</v>
+      </c>
+      <c r="O19" s="17" t="n">
+        <f aca="false">IF(14&lt;Assumptions!$B$118,0,Assumptions!$B$116*(1+Assumptions!$B$119)^(14-Assumptions!$B$118+1))</f>
+        <v>815887.11784935</v>
+      </c>
+      <c r="P19" s="17" t="n">
+        <f aca="false">IF(15&lt;Assumptions!$B$118,0,Assumptions!$B$116*(1+Assumptions!$B$119)^(15-Assumptions!$B$118+1))</f>
+        <v>881158.087277298</v>
+      </c>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="51" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="s">
+        <v>630</v>
+      </c>
+      <c r="B20" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,1&lt;Assumptions!$B$118),0,B16*Assumptions!$B$117)</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,2&lt;Assumptions!$B$118),0,C16*Assumptions!$B$117)</f>
+        <v>171247.020937405</v>
+      </c>
+      <c r="D20" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,3&lt;Assumptions!$B$118),0,D16*Assumptions!$B$117)</f>
+        <v>223157.44191376</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,4&lt;Assumptions!$B$118),0,E16*Assumptions!$B$117)</f>
+        <v>437729.986963376</v>
+      </c>
+      <c r="F20" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,5&lt;Assumptions!$B$118),0,F16*Assumptions!$B$117)</f>
+        <v>508358.173090087</v>
+      </c>
+      <c r="G20" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,6&lt;Assumptions!$B$118),0,G16*Assumptions!$B$117)</f>
+        <v>590671.083027514</v>
+      </c>
+      <c r="H20" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,7&lt;Assumptions!$B$118),0,H16*Assumptions!$B$117)</f>
+        <v>794978.580867809</v>
+      </c>
+      <c r="I20" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,8&lt;Assumptions!$B$118),0,I16*Assumptions!$B$117)</f>
+        <v>1026869.74773148</v>
+      </c>
+      <c r="J20" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,9&lt;Assumptions!$B$118),0,J16*Assumptions!$B$117)</f>
+        <v>1288011.78205602</v>
+      </c>
+      <c r="K20" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,10&lt;Assumptions!$B$118),0,K16*Assumptions!$B$117)</f>
+        <v>1492479.92682487</v>
+      </c>
+      <c r="L20" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,11&lt;Assumptions!$B$118),0,L16*Assumptions!$B$117)</f>
+        <v>2430197.76886459</v>
+      </c>
+      <c r="M20" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,12&lt;Assumptions!$B$118),0,M16*Assumptions!$B$117)</f>
+        <v>2895605.86989995</v>
+      </c>
+      <c r="N20" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,13&lt;Assumptions!$B$118),0,N16*Assumptions!$B$117)</f>
+        <v>3405358.54717914</v>
+      </c>
+      <c r="O20" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,14&lt;Assumptions!$B$118),0,O16*Assumptions!$B$117)</f>
+        <v>3783439.70137085</v>
+      </c>
+      <c r="P20" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,15&lt;Assumptions!$B$118),0,P16*Assumptions!$B$117)</f>
+        <v>4174999.27763012</v>
+      </c>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18" t="s">
+        <v>631</v>
+      </c>
+      <c r="B21" s="24" t="n">
+        <f aca="false">MAX(B19,B20)</f>
+        <v>0</v>
+      </c>
+      <c r="C21" s="24" t="n">
+        <f aca="false">MAX(C19,C20)</f>
+        <v>324000</v>
+      </c>
+      <c r="D21" s="24" t="n">
+        <f aca="false">MAX(D19,D20)</f>
+        <v>349920</v>
+      </c>
+      <c r="E21" s="24" t="n">
+        <f aca="false">MAX(E19,E20)</f>
+        <v>437729.986963376</v>
+      </c>
+      <c r="F21" s="24" t="n">
+        <f aca="false">MAX(F19,F20)</f>
+        <v>508358.173090087</v>
+      </c>
+      <c r="G21" s="24" t="n">
+        <f aca="false">MAX(G19,G20)</f>
+        <v>590671.083027514</v>
+      </c>
+      <c r="H21" s="24" t="n">
+        <f aca="false">MAX(H19,H20)</f>
+        <v>794978.580867809</v>
+      </c>
+      <c r="I21" s="24" t="n">
+        <f aca="false">MAX(I19,I20)</f>
+        <v>1026869.74773148</v>
+      </c>
+      <c r="J21" s="24" t="n">
+        <f aca="false">MAX(J19,J20)</f>
+        <v>1288011.78205602</v>
+      </c>
+      <c r="K21" s="24" t="n">
+        <f aca="false">MAX(K19,K20)</f>
+        <v>1492479.92682487</v>
+      </c>
+      <c r="L21" s="24" t="n">
+        <f aca="false">MAX(L19,L20)</f>
+        <v>2430197.76886459</v>
+      </c>
+      <c r="M21" s="24" t="n">
+        <f aca="false">MAX(M19,M20)</f>
+        <v>2895605.86989995</v>
+      </c>
+      <c r="N21" s="24" t="n">
+        <f aca="false">MAX(N19,N20)</f>
+        <v>3405358.54717914</v>
+      </c>
+      <c r="O21" s="24" t="n">
+        <f aca="false">MAX(O19,O20)</f>
+        <v>3783439.70137085</v>
+      </c>
+      <c r="P21" s="24" t="n">
+        <f aca="false">MAX(P19,P20)</f>
+        <v>4174999.27763012</v>
+      </c>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="18" t="s">
+        <v>632</v>
+      </c>
+      <c r="B22" s="24" t="n">
+        <f aca="false">B16-B21</f>
+        <v>722514.397345807</v>
+      </c>
+      <c r="C22" s="24" t="n">
+        <f aca="false">C16-C21</f>
+        <v>532235.104687023</v>
+      </c>
+      <c r="D22" s="24" t="n">
+        <f aca="false">D16-D21</f>
+        <v>765867.209568801</v>
+      </c>
+      <c r="E22" s="24" t="n">
+        <f aca="false">E16-E21</f>
+        <v>1750919.9478535</v>
+      </c>
+      <c r="F22" s="24" t="n">
+        <f aca="false">F16-F21</f>
+        <v>2033432.69236035</v>
+      </c>
+      <c r="G22" s="24" t="n">
+        <f aca="false">G16-G21</f>
+        <v>2362684.33211006</v>
+      </c>
+      <c r="H22" s="24" t="n">
+        <f aca="false">H16-H21</f>
+        <v>3179914.32347124</v>
+      </c>
+      <c r="I22" s="24" t="n">
+        <f aca="false">I16-I21</f>
+        <v>4107478.99092592</v>
+      </c>
+      <c r="J22" s="24" t="n">
+        <f aca="false">J16-J21</f>
+        <v>5152047.12822409</v>
+      </c>
+      <c r="K22" s="24" t="n">
+        <f aca="false">K16-K21</f>
+        <v>5969919.70729948</v>
+      </c>
+      <c r="L22" s="24" t="n">
+        <f aca="false">L16-L21</f>
+        <v>9720791.07545834</v>
+      </c>
+      <c r="M22" s="24" t="n">
+        <f aca="false">M16-M21</f>
+        <v>11582423.4795998</v>
+      </c>
+      <c r="N22" s="24" t="n">
+        <f aca="false">N16-N21</f>
+        <v>13621434.1887165</v>
+      </c>
+      <c r="O22" s="24" t="n">
+        <f aca="false">O16-O21</f>
+        <v>15133758.8054834</v>
+      </c>
+      <c r="P22" s="24" t="n">
+        <f aca="false">P16-P21</f>
+        <v>16699997.1105205</v>
+      </c>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="6"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="6"/>
+    </row>
+    <row r="24" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="20" t="s">
+        <v>634</v>
+      </c>
+      <c r="B24" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,1&lt;Assumptions!$B$118),0,MAX(0,Assumptions!$B$116*(1-1/Assumptions!$B$112)))</f>
+        <v>0</v>
+      </c>
+      <c r="C24" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,2&lt;Assumptions!$B$118),0,MAX(0,Assumptions!$B$116*(1-(2-Assumptions!$B$118+1)/Assumptions!$B$112)))</f>
+        <v>270000</v>
+      </c>
+      <c r="D24" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,3&lt;Assumptions!$B$118),0,MAX(0,Assumptions!$B$116*(1-(3-Assumptions!$B$118+1)/Assumptions!$B$112)))</f>
+        <v>240000</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,4&lt;Assumptions!$B$118),0,MAX(0,Assumptions!$B$116*(1-(4-Assumptions!$B$118+1)/Assumptions!$B$112)))</f>
+        <v>210000</v>
+      </c>
+      <c r="F24" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,5&lt;Assumptions!$B$118),0,MAX(0,Assumptions!$B$116*(1-(5-Assumptions!$B$118+1)/Assumptions!$B$112)))</f>
+        <v>180000</v>
+      </c>
+      <c r="G24" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,6&lt;Assumptions!$B$118),0,MAX(0,Assumptions!$B$116*(1-(6-Assumptions!$B$118+1)/Assumptions!$B$112)))</f>
+        <v>150000</v>
+      </c>
+      <c r="H24" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,7&lt;Assumptions!$B$118),0,MAX(0,Assumptions!$B$116*(1-(7-Assumptions!$B$118+1)/Assumptions!$B$112)))</f>
+        <v>120000</v>
+      </c>
+      <c r="I24" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,8&lt;Assumptions!$B$118),0,MAX(0,Assumptions!$B$116*(1-(8-Assumptions!$B$118+1)/Assumptions!$B$112)))</f>
+        <v>90000</v>
+      </c>
+      <c r="J24" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,9&lt;Assumptions!$B$118),0,MAX(0,Assumptions!$B$116*(1-(9-Assumptions!$B$118+1)/Assumptions!$B$112)))</f>
+        <v>60000</v>
+      </c>
+      <c r="K24" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,10&lt;Assumptions!$B$118),0,MAX(0,Assumptions!$B$116*(1-(10-Assumptions!$B$118+1)/Assumptions!$B$112)))</f>
+        <v>30000</v>
+      </c>
+      <c r="L24" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,11&lt;Assumptions!$B$118),0,MAX(0,Assumptions!$B$116*(1-(11-Assumptions!$B$118+1)/Assumptions!$B$112)))</f>
+        <v>0</v>
+      </c>
+      <c r="M24" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,12&lt;Assumptions!$B$118),0,MAX(0,Assumptions!$B$116*(1-(12-Assumptions!$B$118+1)/Assumptions!$B$112)))</f>
+        <v>0</v>
+      </c>
+      <c r="N24" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,13&lt;Assumptions!$B$118),0,MAX(0,Assumptions!$B$116*(1-(13-Assumptions!$B$118+1)/Assumptions!$B$112)))</f>
+        <v>0</v>
+      </c>
+      <c r="O24" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,14&lt;Assumptions!$B$118),0,MAX(0,Assumptions!$B$116*(1-(14-Assumptions!$B$118+1)/Assumptions!$B$112)))</f>
+        <v>0</v>
+      </c>
+      <c r="P24" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,15&lt;Assumptions!$B$118),0,MAX(0,Assumptions!$B$116*(1-(15-Assumptions!$B$118+1)/Assumptions!$B$112)))</f>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="51" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="20" t="s">
+        <v>636</v>
+      </c>
+      <c r="B25" s="17" t="n">
+        <f aca="false">IF(OR(Assumptions!$B$116=0,1&lt;Assumptions!$B$118),0,Assumptions!$B$116*Assumptions!$B$111)</f>
+        <v>0</v>
+      </c>
+      <c r="C25" s="17" t="n">
+        <f aca="false">B25+IF(OR(Assumptions!$B$116=0,2&lt;Assumptions!$B$118),0,MAX(0,Assumptions!$B$116*(1-(1-Assumptions!$B$118)/Assumptions!$B$112))*Assumptions!$B$111)</f>
+        <v>42075</v>
+      </c>
+      <c r="D25" s="17" t="n">
+        <f aca="false">C25+IF(OR(Assumptions!$B$116=0,3&lt;Assumptions!$B$118),0,MAX(0,Assumptions!$B$116*(1-(2-Assumptions!$B$118)/Assumptions!$B$112))*Assumptions!$B$111)</f>
+        <v>80325</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <f aca="false">D25+IF(OR(Assumptions!$B$116=0,4&lt;Assumptions!$B$118),0,MAX(0,Assumptions!$B$116*(1-(3-Assumptions!$B$118)/Assumptions!$B$112))*Assumptions!$B$111)</f>
+        <v>114750</v>
+      </c>
+      <c r="F25" s="17" t="n">
+        <f aca="false">E25+IF(OR(Assumptions!$B$116=0,5&lt;Assumptions!$B$118),0,MAX(0,Assumptions!$B$116*(1-(4-Assumptions!$B$118)/Assumptions!$B$112))*Assumptions!$B$111)</f>
+        <v>145350</v>
+      </c>
+      <c r="G25" s="17" t="n">
+        <f aca="false">F25+IF(OR(Assumptions!$B$116=0,6&lt;Assumptions!$B$118),0,MAX(0,Assumptions!$B$116*(1-(5-Assumptions!$B$118)/Assumptions!$B$112))*Assumptions!$B$111)</f>
+        <v>172125</v>
+      </c>
+      <c r="H25" s="17" t="n">
+        <f aca="false">G25+IF(OR(Assumptions!$B$116=0,7&lt;Assumptions!$B$118),0,MAX(0,Assumptions!$B$116*(1-(6-Assumptions!$B$118)/Assumptions!$B$112))*Assumptions!$B$111)</f>
+        <v>195075</v>
+      </c>
+      <c r="I25" s="17" t="n">
+        <f aca="false">H25+IF(OR(Assumptions!$B$116=0,8&lt;Assumptions!$B$118),0,MAX(0,Assumptions!$B$116*(1-(7-Assumptions!$B$118)/Assumptions!$B$112))*Assumptions!$B$111)</f>
+        <v>214200</v>
+      </c>
+      <c r="J25" s="17" t="n">
+        <f aca="false">I25+IF(OR(Assumptions!$B$116=0,9&lt;Assumptions!$B$118),0,MAX(0,Assumptions!$B$116*(1-(8-Assumptions!$B$118)/Assumptions!$B$112))*Assumptions!$B$111)</f>
+        <v>229500</v>
+      </c>
+      <c r="K25" s="17" t="n">
+        <f aca="false">J25+IF(OR(Assumptions!$B$116=0,10&lt;Assumptions!$B$118),0,MAX(0,Assumptions!$B$116*(1-(9-Assumptions!$B$118)/Assumptions!$B$112))*Assumptions!$B$111)</f>
+        <v>240975</v>
+      </c>
+      <c r="L25" s="17" t="n">
+        <f aca="false">K25+IF(OR(Assumptions!$B$116=0,11&lt;Assumptions!$B$118),0,MAX(0,Assumptions!$B$116*(1-(10-Assumptions!$B$118)/Assumptions!$B$112))*Assumptions!$B$111)</f>
+        <v>248625</v>
+      </c>
+      <c r="M25" s="17" t="n">
+        <f aca="false">L25+IF(OR(Assumptions!$B$116=0,12&lt;Assumptions!$B$118),0,MAX(0,Assumptions!$B$116*(1-(11-Assumptions!$B$118)/Assumptions!$B$112))*Assumptions!$B$111)</f>
+        <v>252450</v>
+      </c>
+      <c r="N25" s="17" t="n">
+        <f aca="false">M25+IF(OR(Assumptions!$B$116=0,13&lt;Assumptions!$B$118),0,MAX(0,Assumptions!$B$116*(1-(12-Assumptions!$B$118)/Assumptions!$B$112))*Assumptions!$B$111)</f>
+        <v>252450</v>
+      </c>
+      <c r="O25" s="17" t="n">
+        <f aca="false">N25+IF(OR(Assumptions!$B$116=0,14&lt;Assumptions!$B$118),0,MAX(0,Assumptions!$B$116*(1-(13-Assumptions!$B$118)/Assumptions!$B$112))*Assumptions!$B$111)</f>
+        <v>252450</v>
+      </c>
+      <c r="P25" s="17" t="n">
+        <f aca="false">O25+IF(OR(Assumptions!$B$116=0,15&lt;Assumptions!$B$118),0,MAX(0,Assumptions!$B$116*(1-(14-Assumptions!$B$118)/Assumptions!$B$112))*Assumptions!$B$111)</f>
+        <v>252450</v>
+      </c>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="51" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="18" t="s">
+        <v>638</v>
+      </c>
+      <c r="B26" s="24" t="n">
+        <f aca="false">B16-B24-B25</f>
+        <v>722514.397345807</v>
+      </c>
+      <c r="C26" s="24" t="n">
+        <f aca="false">C16-C24-C25</f>
+        <v>544160.104687023</v>
+      </c>
+      <c r="D26" s="24" t="n">
+        <f aca="false">D16-D24-D25</f>
+        <v>795462.209568801</v>
+      </c>
+      <c r="E26" s="24" t="n">
+        <f aca="false">E16-E24-E25</f>
+        <v>1863899.93481688</v>
+      </c>
+      <c r="F26" s="24" t="n">
+        <f aca="false">F16-F24-F25</f>
+        <v>2216440.86545043</v>
+      </c>
+      <c r="G26" s="24" t="n">
+        <f aca="false">G16-G24-G25</f>
+        <v>2631230.41513757</v>
+      </c>
+      <c r="H26" s="24" t="n">
+        <f aca="false">H16-H24-H25</f>
+        <v>3659817.90433904</v>
+      </c>
+      <c r="I26" s="24" t="n">
+        <f aca="false">I16-I24-I25</f>
+        <v>4830148.7386574</v>
+      </c>
+      <c r="J26" s="24" t="n">
+        <f aca="false">J16-J24-J25</f>
+        <v>6150558.91028011</v>
+      </c>
+      <c r="K26" s="24" t="n">
+        <f aca="false">K16-K24-K25</f>
+        <v>7191424.63412436</v>
+      </c>
+      <c r="L26" s="24" t="n">
+        <f aca="false">L16-L24-L25</f>
+        <v>11902363.8443229</v>
+      </c>
+      <c r="M26" s="24" t="n">
+        <f aca="false">M16-M24-M25</f>
+        <v>14225579.3494997</v>
+      </c>
+      <c r="N26" s="24" t="n">
+        <f aca="false">N16-N24-N25</f>
+        <v>16774342.7358957</v>
+      </c>
+      <c r="O26" s="24" t="n">
+        <f aca="false">O16-O24-O25</f>
+        <v>18664748.5068543</v>
+      </c>
+      <c r="P26" s="24" t="n">
+        <f aca="false">P16-P24-P25</f>
+        <v>20622546.3881506</v>
+      </c>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="51" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="42" t="s">
+        <v>640</v>
+      </c>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="43"/>
+      <c r="L27" s="43"/>
+      <c r="M27" s="43"/>
+      <c r="N27" s="43"/>
+      <c r="O27" s="43"/>
+      <c r="P27" s="43"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="43"/>
+    </row>
+    <row r="28" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="18" t="s">
+        <v>641</v>
+      </c>
+      <c r="B28" s="24" t="n">
+        <f aca="false">B26-B22</f>
+        <v>0</v>
+      </c>
+      <c r="C28" s="24" t="n">
+        <f aca="false">C26-C22</f>
+        <v>11925</v>
+      </c>
+      <c r="D28" s="24" t="n">
+        <f aca="false">D26-D22</f>
+        <v>29595</v>
+      </c>
+      <c r="E28" s="24" t="n">
+        <f aca="false">E26-E22</f>
+        <v>112979.986963376</v>
+      </c>
+      <c r="F28" s="24" t="n">
+        <f aca="false">F26-F22</f>
+        <v>183008.173090087</v>
+      </c>
+      <c r="G28" s="24" t="n">
+        <f aca="false">G26-G22</f>
+        <v>268546.083027514</v>
+      </c>
+      <c r="H28" s="24" t="n">
+        <f aca="false">H26-H22</f>
+        <v>479903.580867809</v>
+      </c>
+      <c r="I28" s="24" t="n">
+        <f aca="false">I26-I22</f>
+        <v>722669.74773148</v>
+      </c>
+      <c r="J28" s="24" t="n">
+        <f aca="false">J26-J22</f>
+        <v>998511.782056022</v>
+      </c>
+      <c r="K28" s="24" t="n">
+        <f aca="false">K26-K22</f>
+        <v>1221504.92682487</v>
+      </c>
+      <c r="L28" s="24" t="n">
+        <f aca="false">L26-L22</f>
+        <v>2181572.76886459</v>
+      </c>
+      <c r="M28" s="24" t="n">
+        <f aca="false">M26-M22</f>
+        <v>2643155.86989995</v>
+      </c>
+      <c r="N28" s="24" t="n">
+        <f aca="false">N26-N22</f>
+        <v>3152908.54717914</v>
+      </c>
+      <c r="O28" s="24" t="n">
+        <f aca="false">O26-O22</f>
+        <v>3530989.70137085</v>
+      </c>
+      <c r="P28" s="24" t="n">
+        <f aca="false">P26-P22</f>
+        <v>3922549.27763012</v>
+      </c>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="51" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="20" t="s">
+        <v>643</v>
+      </c>
+      <c r="B29" s="17" t="n">
+        <f aca="false">IF(Assumptions!$B$117=0,0,(B24+B25)/Assumptions!$B$117)</f>
+        <v>0</v>
+      </c>
+      <c r="C29" s="17" t="n">
+        <f aca="false">IF(Assumptions!$B$117=0,0,(C24+C25)/Assumptions!$B$117)</f>
+        <v>1560375</v>
+      </c>
+      <c r="D29" s="17" t="n">
+        <f aca="false">IF(Assumptions!$B$117=0,0,(D24+D25)/Assumptions!$B$117)</f>
+        <v>1601625</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <f aca="false">IF(Assumptions!$B$117=0,0,(E24+E25)/Assumptions!$B$117)</f>
+        <v>1623750</v>
+      </c>
+      <c r="F29" s="17" t="n">
+        <f aca="false">IF(Assumptions!$B$117=0,0,(F24+F25)/Assumptions!$B$117)</f>
+        <v>1626750</v>
+      </c>
+      <c r="G29" s="17" t="n">
+        <f aca="false">IF(Assumptions!$B$117=0,0,(G24+G25)/Assumptions!$B$117)</f>
+        <v>1610625</v>
+      </c>
+      <c r="H29" s="17" t="n">
+        <f aca="false">IF(Assumptions!$B$117=0,0,(H24+H25)/Assumptions!$B$117)</f>
+        <v>1575375</v>
+      </c>
+      <c r="I29" s="17" t="n">
+        <f aca="false">IF(Assumptions!$B$117=0,0,(I24+I25)/Assumptions!$B$117)</f>
+        <v>1521000</v>
+      </c>
+      <c r="J29" s="17" t="n">
+        <f aca="false">IF(Assumptions!$B$117=0,0,(J24+J25)/Assumptions!$B$117)</f>
+        <v>1447500</v>
+      </c>
+      <c r="K29" s="17" t="n">
+        <f aca="false">IF(Assumptions!$B$117=0,0,(K24+K25)/Assumptions!$B$117)</f>
+        <v>1354875</v>
+      </c>
+      <c r="L29" s="17" t="n">
+        <f aca="false">IF(Assumptions!$B$117=0,0,(L24+L25)/Assumptions!$B$117)</f>
+        <v>1243125</v>
+      </c>
+      <c r="M29" s="17" t="n">
+        <f aca="false">IF(Assumptions!$B$117=0,0,(M24+M25)/Assumptions!$B$117)</f>
+        <v>1262250</v>
+      </c>
+      <c r="N29" s="17" t="n">
+        <f aca="false">IF(Assumptions!$B$117=0,0,(N24+N25)/Assumptions!$B$117)</f>
+        <v>1262250</v>
+      </c>
+      <c r="O29" s="17" t="n">
+        <f aca="false">IF(Assumptions!$B$117=0,0,(O24+O25)/Assumptions!$B$117)</f>
+        <v>1262250</v>
+      </c>
+      <c r="P29" s="17" t="n">
+        <f aca="false">IF(Assumptions!$B$117=0,0,(P24+P25)/Assumptions!$B$117)</f>
+        <v>1262250</v>
+      </c>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="51" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>645</v>
+      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
+      <c r="P31" s="6"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="6"/>
+    </row>
+    <row r="32" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="33" t="s">
+        <v>646</v>
+      </c>
+      <c r="B32" s="33"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="33"/>
+      <c r="K32" s="33"/>
+      <c r="L32" s="33"/>
+      <c r="M32" s="33"/>
+      <c r="N32" s="33"/>
+      <c r="O32" s="33"/>
+      <c r="P32" s="33"/>
+      <c r="Q32" s="33"/>
+      <c r="R32" s="33"/>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="true" password="ef11" formatCells="false" formatColumns="false" formatRows="false"/>
+  <mergeCells count="1">
+    <mergeCell ref="A32:R32"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:R36"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="62"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>512</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="8" t="s">
+        <v>649</v>
+      </c>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="44" t="n">
+        <f aca="false">Assumptions!$B$39</f>
+        <v>10</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="46" t="n">
+        <f aca="false">INDEX(B17:P17,Assumptions!$B$39)</f>
+        <v>4952082.94628947</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="46" t="n">
+        <f aca="false">INDEX(B22:P22,Assumptions!$B$39)</f>
+        <v>1285955.69948841</v>
+      </c>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="45" t="n">
+        <f aca="false">INDEX(B21:P21,Assumptions!$B$39)</f>
+        <v>4</v>
+      </c>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="46" t="n">
+        <f aca="false">INDEX(B23:P23,Assumptions!$B$39)</f>
+        <v>7462399.63412436</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="46" t="n">
+        <f aca="false">INDEX(B24:P24,Assumptions!$B$39)</f>
+        <v>5671423.72193451</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="46" t="n">
+        <f aca="false">INDEX(B27:P27,Assumptions!$B$39)</f>
+        <v>1093859.94511865</v>
+      </c>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="46" t="n">
+        <f aca="false">INDEX(B28:P28,Assumptions!$B$39)</f>
+        <v>6368539.6890057</v>
+      </c>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="40" t="s">
+        <v>654</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="18" t="s">
+        <v>526</v>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J15" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="K15" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L15" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="M15" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="N15" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="O15" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="P15" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="18" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>655</v>
+      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="6"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="6"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18" t="s">
+        <v>623</v>
+      </c>
+      <c r="B17" s="24" t="n">
+        <f aca="false">'Long range 15-yr'!B36</f>
+        <v>1107883.476</v>
+      </c>
+      <c r="C17" s="24" t="n">
+        <f aca="false">'Long range 15-yr'!C36</f>
+        <v>1130224.27392</v>
+      </c>
+      <c r="D17" s="24" t="n">
+        <f aca="false">'Long range 15-yr'!D36</f>
+        <v>1470581.13731659</v>
+      </c>
+      <c r="E17" s="24" t="n">
+        <f aca="false">'Long range 15-yr'!E36</f>
+        <v>2128361.5241759</v>
+      </c>
+      <c r="F17" s="24" t="n">
+        <f aca="false">'Long range 15-yr'!F36</f>
+        <v>2531696.60117519</v>
+      </c>
+      <c r="G17" s="24" t="n">
+        <f aca="false">'Long range 15-yr'!G36</f>
+        <v>2960567.60023987</v>
+      </c>
+      <c r="H17" s="24" t="n">
+        <f aca="false">'Long range 15-yr'!H36</f>
+        <v>3415973.30476096</v>
+      </c>
+      <c r="I17" s="24" t="n">
+        <f aca="false">'Long range 15-yr'!I36</f>
+        <v>3898958.3702101</v>
+      </c>
+      <c r="J17" s="24" t="n">
+        <f aca="false">'Long range 15-yr'!J36</f>
+        <v>4410614.70976327</v>
+      </c>
+      <c r="K17" s="24" t="n">
+        <f aca="false">'Long range 15-yr'!K36</f>
+        <v>4952082.94628947</v>
+      </c>
+      <c r="L17" s="24" t="n">
+        <f aca="false">'Long range 15-yr'!L36</f>
+        <v>5524553.93215493</v>
+      </c>
+      <c r="M17" s="24" t="n">
+        <f aca="false">'Long range 15-yr'!M36</f>
+        <v>6129270.33838766</v>
+      </c>
+      <c r="N17" s="24" t="n">
+        <f aca="false">'Long range 15-yr'!N36</f>
+        <v>6767528.314843</v>
+      </c>
+      <c r="O17" s="24" t="n">
+        <f aca="false">'Long range 15-yr'!O36</f>
+        <v>7045784.99129078</v>
+      </c>
+      <c r="P17" s="24" t="n">
+        <f aca="false">'Long range 15-yr'!P36</f>
+        <v>7328447.27269707</v>
+      </c>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="s">
+        <v>656</v>
+      </c>
+      <c r="B18" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!B52</f>
+        <v>314146.07309104</v>
+      </c>
+      <c r="C18" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!C52</f>
+        <v>319078.39831504</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!D52</f>
+        <v>394634.692965322</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!E52</f>
+        <v>555951.353765527</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!F52</f>
+        <v>596449.755413787</v>
+      </c>
+      <c r="G18" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!G52</f>
+        <v>646272.842030917</v>
+      </c>
+      <c r="H18" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!H52</f>
+        <v>829992.967618285</v>
+      </c>
+      <c r="I18" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!I52</f>
+        <v>1028203.48975863</v>
+      </c>
+      <c r="J18" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!J52</f>
+        <v>1241519.85642434</v>
+      </c>
+      <c r="K18" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!K52</f>
+        <v>1370955.69948841</v>
+      </c>
+      <c r="L18" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!L52</f>
+        <v>1622798.93817309</v>
+      </c>
+      <c r="M18" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!M52</f>
+        <v>1891737.89552063</v>
+      </c>
+      <c r="N18" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!N52</f>
+        <v>2178487.43083706</v>
+      </c>
+      <c r="O18" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!O52</f>
+        <v>2334906.1647436</v>
+      </c>
+      <c r="P18" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!P52</f>
+        <v>2493904.17086587</v>
+      </c>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="51" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="s">
+        <v>658</v>
+      </c>
+      <c r="B19" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!B52-Assumptions!$B$128</f>
+        <v>229146.07309104</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!C52-Assumptions!$B$128</f>
+        <v>234078.39831504</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!D52-Assumptions!$B$128</f>
+        <v>309634.692965322</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!E52-Assumptions!$B$128</f>
+        <v>470951.353765527</v>
+      </c>
+      <c r="F19" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!F52-Assumptions!$B$128</f>
+        <v>511449.755413787</v>
+      </c>
+      <c r="G19" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!G52-Assumptions!$B$128</f>
+        <v>561272.842030917</v>
+      </c>
+      <c r="H19" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!H52-Assumptions!$B$128</f>
+        <v>744992.967618285</v>
+      </c>
+      <c r="I19" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!I52-Assumptions!$B$128</f>
+        <v>943203.489758632</v>
+      </c>
+      <c r="J19" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!J52-Assumptions!$B$128</f>
+        <v>1156519.85642434</v>
+      </c>
+      <c r="K19" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!K52-Assumptions!$B$128</f>
+        <v>1285955.69948841</v>
+      </c>
+      <c r="L19" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!L52-Assumptions!$B$128</f>
+        <v>1537798.93817309</v>
+      </c>
+      <c r="M19" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!M52-Assumptions!$B$128</f>
+        <v>1806737.89552063</v>
+      </c>
+      <c r="N19" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!N52-Assumptions!$B$128</f>
+        <v>2093487.43083706</v>
+      </c>
+      <c r="O19" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!O52-Assumptions!$B$128</f>
+        <v>2249906.1647436</v>
+      </c>
+      <c r="P19" s="17" t="n">
+        <f aca="false">'Long range 15-yr'!P52-Assumptions!$B$128</f>
+        <v>2408904.17086587</v>
+      </c>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="51" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="42" t="s">
+        <v>660</v>
+      </c>
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+      <c r="L20" s="43"/>
+      <c r="M20" s="43"/>
+      <c r="N20" s="43"/>
+      <c r="O20" s="43"/>
+      <c r="P20" s="43"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="43"/>
+    </row>
+    <row r="21" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18" t="s">
+        <v>661</v>
+      </c>
+      <c r="B21" s="59" t="n">
+        <f aca="false">IF(B17&gt;=5000000,Assumptions!$B$127,IF(B17&gt;=2000000,Assumptions!$B$126,Assumptions!$B$125))</f>
+        <v>2.3</v>
+      </c>
+      <c r="C21" s="59" t="n">
+        <f aca="false">IF(C17&gt;=5000000,Assumptions!$B$127,IF(C17&gt;=2000000,Assumptions!$B$126,Assumptions!$B$125))</f>
+        <v>2.3</v>
+      </c>
+      <c r="D21" s="59" t="n">
+        <f aca="false">IF(D17&gt;=5000000,Assumptions!$B$127,IF(D17&gt;=2000000,Assumptions!$B$126,Assumptions!$B$125))</f>
+        <v>2.3</v>
+      </c>
+      <c r="E21" s="59" t="n">
+        <f aca="false">IF(E17&gt;=5000000,Assumptions!$B$127,IF(E17&gt;=2000000,Assumptions!$B$126,Assumptions!$B$125))</f>
+        <v>4</v>
+      </c>
+      <c r="F21" s="59" t="n">
+        <f aca="false">IF(F17&gt;=5000000,Assumptions!$B$127,IF(F17&gt;=2000000,Assumptions!$B$126,Assumptions!$B$125))</f>
+        <v>4</v>
+      </c>
+      <c r="G21" s="59" t="n">
+        <f aca="false">IF(G17&gt;=5000000,Assumptions!$B$127,IF(G17&gt;=2000000,Assumptions!$B$126,Assumptions!$B$125))</f>
+        <v>4</v>
+      </c>
+      <c r="H21" s="59" t="n">
+        <f aca="false">IF(H17&gt;=5000000,Assumptions!$B$127,IF(H17&gt;=2000000,Assumptions!$B$126,Assumptions!$B$125))</f>
+        <v>4</v>
+      </c>
+      <c r="I21" s="59" t="n">
+        <f aca="false">IF(I17&gt;=5000000,Assumptions!$B$127,IF(I17&gt;=2000000,Assumptions!$B$126,Assumptions!$B$125))</f>
+        <v>4</v>
+      </c>
+      <c r="J21" s="59" t="n">
+        <f aca="false">IF(J17&gt;=5000000,Assumptions!$B$127,IF(J17&gt;=2000000,Assumptions!$B$126,Assumptions!$B$125))</f>
+        <v>4</v>
+      </c>
+      <c r="K21" s="59" t="n">
+        <f aca="false">IF(K17&gt;=5000000,Assumptions!$B$127,IF(K17&gt;=2000000,Assumptions!$B$126,Assumptions!$B$125))</f>
+        <v>4</v>
+      </c>
+      <c r="L21" s="59" t="n">
+        <f aca="false">IF(L17&gt;=5000000,Assumptions!$B$127,IF(L17&gt;=2000000,Assumptions!$B$126,Assumptions!$B$125))</f>
+        <v>6</v>
+      </c>
+      <c r="M21" s="59" t="n">
+        <f aca="false">IF(M17&gt;=5000000,Assumptions!$B$127,IF(M17&gt;=2000000,Assumptions!$B$126,Assumptions!$B$125))</f>
+        <v>6</v>
+      </c>
+      <c r="N21" s="59" t="n">
+        <f aca="false">IF(N17&gt;=5000000,Assumptions!$B$127,IF(N17&gt;=2000000,Assumptions!$B$126,Assumptions!$B$125))</f>
+        <v>6</v>
+      </c>
+      <c r="O21" s="59" t="n">
+        <f aca="false">IF(O17&gt;=5000000,Assumptions!$B$127,IF(O17&gt;=2000000,Assumptions!$B$126,Assumptions!$B$125))</f>
+        <v>6</v>
+      </c>
+      <c r="P21" s="59" t="n">
+        <f aca="false">IF(P17&gt;=5000000,Assumptions!$B$127,IF(P17&gt;=2000000,Assumptions!$B$126,Assumptions!$B$125))</f>
+        <v>6</v>
+      </c>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="51" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="20" t="s">
+        <v>663</v>
+      </c>
+      <c r="B22" s="17" t="n">
+        <f aca="false">IF(B17&gt;=2000000,B19,B18)</f>
+        <v>314146.07309104</v>
+      </c>
+      <c r="C22" s="17" t="n">
+        <f aca="false">IF(C17&gt;=2000000,C19,C18)</f>
+        <v>319078.39831504</v>
+      </c>
+      <c r="D22" s="17" t="n">
+        <f aca="false">IF(D17&gt;=2000000,D19,D18)</f>
+        <v>394634.692965322</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <f aca="false">IF(E17&gt;=2000000,E19,E18)</f>
+        <v>470951.353765527</v>
+      </c>
+      <c r="F22" s="17" t="n">
+        <f aca="false">IF(F17&gt;=2000000,F19,F18)</f>
+        <v>511449.755413787</v>
+      </c>
+      <c r="G22" s="17" t="n">
+        <f aca="false">IF(G17&gt;=2000000,G19,G18)</f>
+        <v>561272.842030917</v>
+      </c>
+      <c r="H22" s="17" t="n">
+        <f aca="false">IF(H17&gt;=2000000,H19,H18)</f>
+        <v>744992.967618285</v>
+      </c>
+      <c r="I22" s="17" t="n">
+        <f aca="false">IF(I17&gt;=2000000,I19,I18)</f>
+        <v>943203.489758632</v>
+      </c>
+      <c r="J22" s="17" t="n">
+        <f aca="false">IF(J17&gt;=2000000,J19,J18)</f>
+        <v>1156519.85642434</v>
+      </c>
+      <c r="K22" s="17" t="n">
+        <f aca="false">IF(K17&gt;=2000000,K19,K18)</f>
+        <v>1285955.69948841</v>
+      </c>
+      <c r="L22" s="17" t="n">
+        <f aca="false">IF(L17&gt;=2000000,L19,L18)</f>
+        <v>1537798.93817309</v>
+      </c>
+      <c r="M22" s="17" t="n">
+        <f aca="false">IF(M17&gt;=2000000,M19,M18)</f>
+        <v>1806737.89552063</v>
+      </c>
+      <c r="N22" s="17" t="n">
+        <f aca="false">IF(N17&gt;=2000000,N19,N18)</f>
+        <v>2093487.43083706</v>
+      </c>
+      <c r="O22" s="17" t="n">
+        <f aca="false">IF(O17&gt;=2000000,O19,O18)</f>
+        <v>2249906.1647436</v>
+      </c>
+      <c r="P22" s="17" t="n">
+        <f aca="false">IF(P17&gt;=2000000,P19,P18)</f>
+        <v>2408904.17086587</v>
+      </c>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="18" t="s">
+        <v>664</v>
+      </c>
+      <c r="B23" s="24" t="n">
+        <f aca="false">MAX(0,B22)*B21+'Long range 15-yr'!B51-'Long range 15-yr'!B48</f>
+        <v>722514.397345807</v>
+      </c>
+      <c r="C23" s="24" t="n">
+        <f aca="false">MAX(0,C22)*C21+'Long range 15-yr'!C51-'Long range 15-yr'!C48</f>
+        <v>856235.104687023</v>
+      </c>
+      <c r="D23" s="24" t="n">
+        <f aca="false">MAX(0,D22)*D21+'Long range 15-yr'!D51-'Long range 15-yr'!D48</f>
+        <v>1115787.2095688</v>
+      </c>
+      <c r="E23" s="24" t="n">
+        <f aca="false">MAX(0,E22)*E21+'Long range 15-yr'!E51-'Long range 15-yr'!E48</f>
+        <v>2188649.93481688</v>
+      </c>
+      <c r="F23" s="24" t="n">
+        <f aca="false">MAX(0,F22)*F21+'Long range 15-yr'!F51-'Long range 15-yr'!F48</f>
+        <v>2541790.86545043</v>
+      </c>
+      <c r="G23" s="24" t="n">
+        <f aca="false">MAX(0,G22)*G21+'Long range 15-yr'!G51-'Long range 15-yr'!G48</f>
+        <v>2953355.41513757</v>
+      </c>
+      <c r="H23" s="24" t="n">
+        <f aca="false">MAX(0,H22)*H21+'Long range 15-yr'!H51-'Long range 15-yr'!H48</f>
+        <v>3974892.90433904</v>
+      </c>
+      <c r="I23" s="24" t="n">
+        <f aca="false">MAX(0,I22)*I21+'Long range 15-yr'!I51-'Long range 15-yr'!I48</f>
+        <v>5134348.7386574</v>
+      </c>
+      <c r="J23" s="24" t="n">
+        <f aca="false">MAX(0,J22)*J21+'Long range 15-yr'!J51-'Long range 15-yr'!J48</f>
+        <v>6440058.91028011</v>
+      </c>
+      <c r="K23" s="24" t="n">
+        <f aca="false">MAX(0,K22)*K21+'Long range 15-yr'!K51-'Long range 15-yr'!K48</f>
+        <v>7462399.63412436</v>
+      </c>
+      <c r="L23" s="24" t="n">
+        <f aca="false">MAX(0,L22)*L21+'Long range 15-yr'!L51-'Long range 15-yr'!L48</f>
+        <v>12150988.8443229</v>
+      </c>
+      <c r="M23" s="24" t="n">
+        <f aca="false">MAX(0,M22)*M21+'Long range 15-yr'!M51-'Long range 15-yr'!M48</f>
+        <v>14478029.3494997</v>
+      </c>
+      <c r="N23" s="24" t="n">
+        <f aca="false">MAX(0,N22)*N21+'Long range 15-yr'!N51-'Long range 15-yr'!N48</f>
+        <v>17026792.7358957</v>
+      </c>
+      <c r="O23" s="24" t="n">
+        <f aca="false">MAX(0,O22)*O21+'Long range 15-yr'!O51-'Long range 15-yr'!O48</f>
+        <v>18917198.5068543</v>
+      </c>
+      <c r="P23" s="24" t="n">
+        <f aca="false">MAX(0,P22)*P21+'Long range 15-yr'!P51-'Long range 15-yr'!P48</f>
+        <v>20874996.3881506</v>
+      </c>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="51" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="18" t="s">
+        <v>666</v>
+      </c>
+      <c r="B24" s="24" t="n">
+        <f aca="false">B23*Assumptions!$B$129</f>
+        <v>549110.941982814</v>
+      </c>
+      <c r="C24" s="24" t="n">
+        <f aca="false">C23*Assumptions!$B$129</f>
+        <v>650738.679562138</v>
+      </c>
+      <c r="D24" s="24" t="n">
+        <f aca="false">D23*Assumptions!$B$129</f>
+        <v>847998.279272289</v>
+      </c>
+      <c r="E24" s="24" t="n">
+        <f aca="false">E23*Assumptions!$B$129</f>
+        <v>1663373.95046083</v>
+      </c>
+      <c r="F24" s="24" t="n">
+        <f aca="false">F23*Assumptions!$B$129</f>
+        <v>1931761.05774233</v>
+      </c>
+      <c r="G24" s="24" t="n">
+        <f aca="false">G23*Assumptions!$B$129</f>
+        <v>2244550.11550455</v>
+      </c>
+      <c r="H24" s="24" t="n">
+        <f aca="false">H23*Assumptions!$B$129</f>
+        <v>3020918.60729767</v>
+      </c>
+      <c r="I24" s="24" t="n">
+        <f aca="false">I23*Assumptions!$B$129</f>
+        <v>3902105.04137962</v>
+      </c>
+      <c r="J24" s="24" t="n">
+        <f aca="false">J23*Assumptions!$B$129</f>
+        <v>4894444.77181288</v>
+      </c>
+      <c r="K24" s="24" t="n">
+        <f aca="false">K23*Assumptions!$B$129</f>
+        <v>5671423.72193451</v>
+      </c>
+      <c r="L24" s="24" t="n">
+        <f aca="false">L23*Assumptions!$B$129</f>
+        <v>9234751.52168543</v>
+      </c>
+      <c r="M24" s="24" t="n">
+        <f aca="false">M23*Assumptions!$B$129</f>
+        <v>11003302.3056198</v>
+      </c>
+      <c r="N24" s="24" t="n">
+        <f aca="false">N23*Assumptions!$B$129</f>
+        <v>12940362.4792807</v>
+      </c>
+      <c r="O24" s="24" t="n">
+        <f aca="false">O23*Assumptions!$B$129</f>
+        <v>14377070.8652092</v>
+      </c>
+      <c r="P24" s="24" t="n">
+        <f aca="false">P23*Assumptions!$B$129</f>
+        <v>15864997.2549944</v>
+      </c>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="51" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>668</v>
+      </c>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="6"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="6"/>
+    </row>
+    <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="20" t="s">
+        <v>669</v>
+      </c>
+      <c r="B26" s="17" t="n">
+        <f aca="false">MAX(0,B23-Assumptions!$B$123)</f>
+        <v>552514.397345807</v>
+      </c>
+      <c r="C26" s="17" t="n">
+        <f aca="false">MAX(0,C23-Assumptions!$B$123)</f>
+        <v>686235.104687023</v>
+      </c>
+      <c r="D26" s="17" t="n">
+        <f aca="false">MAX(0,D23-Assumptions!$B$123)</f>
+        <v>945787.209568801</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <f aca="false">MAX(0,E23-Assumptions!$B$123)</f>
+        <v>2018649.93481688</v>
+      </c>
+      <c r="F26" s="17" t="n">
+        <f aca="false">MAX(0,F23-Assumptions!$B$123)</f>
+        <v>2371790.86545043</v>
+      </c>
+      <c r="G26" s="17" t="n">
+        <f aca="false">MAX(0,G23-Assumptions!$B$123)</f>
+        <v>2783355.41513757</v>
+      </c>
+      <c r="H26" s="17" t="n">
+        <f aca="false">MAX(0,H23-Assumptions!$B$123)</f>
+        <v>3804892.90433904</v>
+      </c>
+      <c r="I26" s="17" t="n">
+        <f aca="false">MAX(0,I23-Assumptions!$B$123)</f>
+        <v>4964348.7386574</v>
+      </c>
+      <c r="J26" s="17" t="n">
+        <f aca="false">MAX(0,J23-Assumptions!$B$123)</f>
+        <v>6270058.91028011</v>
+      </c>
+      <c r="K26" s="17" t="n">
+        <f aca="false">MAX(0,K23-Assumptions!$B$123)</f>
+        <v>7292399.63412436</v>
+      </c>
+      <c r="L26" s="17" t="n">
+        <f aca="false">MAX(0,L23-Assumptions!$B$123)</f>
+        <v>11980988.8443229</v>
+      </c>
+      <c r="M26" s="17" t="n">
+        <f aca="false">MAX(0,M23-Assumptions!$B$123)</f>
+        <v>14308029.3494997</v>
+      </c>
+      <c r="N26" s="17" t="n">
+        <f aca="false">MAX(0,N23-Assumptions!$B$123)</f>
+        <v>16856792.7358957</v>
+      </c>
+      <c r="O26" s="17" t="n">
+        <f aca="false">MAX(0,O23-Assumptions!$B$123)</f>
+        <v>18747198.5068543</v>
+      </c>
+      <c r="P26" s="17" t="n">
+        <f aca="false">MAX(0,P23-Assumptions!$B$123)</f>
+        <v>20704996.3881506</v>
+      </c>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="51" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="18" t="s">
+        <v>671</v>
+      </c>
+      <c r="B27" s="24" t="n">
+        <f aca="false">B26*Assumptions!$B$122</f>
+        <v>82877.1596018711</v>
+      </c>
+      <c r="C27" s="24" t="n">
+        <f aca="false">C26*Assumptions!$B$122</f>
+        <v>102935.265703053</v>
+      </c>
+      <c r="D27" s="24" t="n">
+        <f aca="false">D26*Assumptions!$B$122</f>
+        <v>141868.08143532</v>
+      </c>
+      <c r="E27" s="24" t="n">
+        <f aca="false">E26*Assumptions!$B$122</f>
+        <v>302797.490222532</v>
+      </c>
+      <c r="F27" s="24" t="n">
+        <f aca="false">F26*Assumptions!$B$122</f>
+        <v>355768.629817565</v>
+      </c>
+      <c r="G27" s="24" t="n">
+        <f aca="false">G26*Assumptions!$B$122</f>
+        <v>417503.312270635</v>
+      </c>
+      <c r="H27" s="24" t="n">
+        <f aca="false">H26*Assumptions!$B$122</f>
+        <v>570733.935650857</v>
+      </c>
+      <c r="I27" s="24" t="n">
+        <f aca="false">I26*Assumptions!$B$122</f>
+        <v>744652.31079861</v>
+      </c>
+      <c r="J27" s="24" t="n">
+        <f aca="false">J26*Assumptions!$B$122</f>
+        <v>940508.836542016</v>
+      </c>
+      <c r="K27" s="24" t="n">
+        <f aca="false">K26*Assumptions!$B$122</f>
+        <v>1093859.94511865</v>
+      </c>
+      <c r="L27" s="24" t="n">
+        <f aca="false">L26*Assumptions!$B$122</f>
+        <v>1797148.32664844</v>
+      </c>
+      <c r="M27" s="24" t="n">
+        <f aca="false">M26*Assumptions!$B$122</f>
+        <v>2146204.40242496</v>
+      </c>
+      <c r="N27" s="24" t="n">
+        <f aca="false">N26*Assumptions!$B$122</f>
+        <v>2528518.91038435</v>
+      </c>
+      <c r="O27" s="24" t="n">
+        <f aca="false">O26*Assumptions!$B$122</f>
+        <v>2812079.77602814</v>
+      </c>
+      <c r="P27" s="24" t="n">
+        <f aca="false">P26*Assumptions!$B$122</f>
+        <v>3105749.45822259</v>
+      </c>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="18" t="s">
+        <v>672</v>
+      </c>
+      <c r="B28" s="24" t="n">
+        <f aca="false">B23-B27</f>
+        <v>639637.237743936</v>
+      </c>
+      <c r="C28" s="24" t="n">
+        <f aca="false">C23-C27</f>
+        <v>753299.83898397</v>
+      </c>
+      <c r="D28" s="24" t="n">
+        <f aca="false">D23-D27</f>
+        <v>973919.128133481</v>
+      </c>
+      <c r="E28" s="24" t="n">
+        <f aca="false">E23-E27</f>
+        <v>1885852.44459435</v>
+      </c>
+      <c r="F28" s="24" t="n">
+        <f aca="false">F23-F27</f>
+        <v>2186022.23563287</v>
+      </c>
+      <c r="G28" s="24" t="n">
+        <f aca="false">G23-G27</f>
+        <v>2535852.10286693</v>
+      </c>
+      <c r="H28" s="24" t="n">
+        <f aca="false">H23-H27</f>
+        <v>3404158.96868819</v>
+      </c>
+      <c r="I28" s="24" t="n">
+        <f aca="false">I23-I27</f>
+        <v>4389696.42785879</v>
+      </c>
+      <c r="J28" s="24" t="n">
+        <f aca="false">J23-J27</f>
+        <v>5499550.07373809</v>
+      </c>
+      <c r="K28" s="24" t="n">
+        <f aca="false">K23-K27</f>
+        <v>6368539.6890057</v>
+      </c>
+      <c r="L28" s="24" t="n">
+        <f aca="false">L23-L27</f>
+        <v>10353840.5176745</v>
+      </c>
+      <c r="M28" s="24" t="n">
+        <f aca="false">M23-M27</f>
+        <v>12331824.9470748</v>
+      </c>
+      <c r="N28" s="24" t="n">
+        <f aca="false">N23-N27</f>
+        <v>14498273.8255113</v>
+      </c>
+      <c r="O28" s="24" t="n">
+        <f aca="false">O23-O27</f>
+        <v>16105118.7308261</v>
+      </c>
+      <c r="P28" s="24" t="n">
+        <f aca="false">P23-P27</f>
+        <v>17769246.929928</v>
+      </c>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="51" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="20" t="s">
+        <v>674</v>
+      </c>
+      <c r="B29" s="17" t="n">
+        <f aca="false">Assumptions!$B$123</f>
+        <v>170000</v>
+      </c>
+      <c r="C29" s="17" t="n">
+        <f aca="false">Assumptions!$B$123</f>
+        <v>170000</v>
+      </c>
+      <c r="D29" s="17" t="n">
+        <f aca="false">Assumptions!$B$123</f>
+        <v>170000</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <f aca="false">Assumptions!$B$123</f>
+        <v>170000</v>
+      </c>
+      <c r="F29" s="17" t="n">
+        <f aca="false">Assumptions!$B$123</f>
+        <v>170000</v>
+      </c>
+      <c r="G29" s="17" t="n">
+        <f aca="false">Assumptions!$B$123</f>
+        <v>170000</v>
+      </c>
+      <c r="H29" s="17" t="n">
+        <f aca="false">Assumptions!$B$123</f>
+        <v>170000</v>
+      </c>
+      <c r="I29" s="17" t="n">
+        <f aca="false">Assumptions!$B$123</f>
+        <v>170000</v>
+      </c>
+      <c r="J29" s="17" t="n">
+        <f aca="false">Assumptions!$B$123</f>
+        <v>170000</v>
+      </c>
+      <c r="K29" s="17" t="n">
+        <f aca="false">Assumptions!$B$123</f>
+        <v>170000</v>
+      </c>
+      <c r="L29" s="17" t="n">
+        <f aca="false">Assumptions!$B$123</f>
+        <v>170000</v>
+      </c>
+      <c r="M29" s="17" t="n">
+        <f aca="false">Assumptions!$B$123</f>
+        <v>170000</v>
+      </c>
+      <c r="N29" s="17" t="n">
+        <f aca="false">Assumptions!$B$123</f>
+        <v>170000</v>
+      </c>
+      <c r="O29" s="17" t="n">
+        <f aca="false">Assumptions!$B$123</f>
+        <v>170000</v>
+      </c>
+      <c r="P29" s="17" t="n">
+        <f aca="false">Assumptions!$B$123</f>
+        <v>170000</v>
+      </c>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="51" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="18" t="s">
+        <v>676</v>
+      </c>
+      <c r="B30" s="24" t="n">
+        <f aca="false">B28-B29</f>
+        <v>469637.237743936</v>
+      </c>
+      <c r="C30" s="24" t="n">
+        <f aca="false">C28-C29</f>
+        <v>583299.83898397</v>
+      </c>
+      <c r="D30" s="24" t="n">
+        <f aca="false">D28-D29</f>
+        <v>803919.128133481</v>
+      </c>
+      <c r="E30" s="24" t="n">
+        <f aca="false">E28-E29</f>
+        <v>1715852.44459435</v>
+      </c>
+      <c r="F30" s="24" t="n">
+        <f aca="false">F28-F29</f>
+        <v>2016022.23563287</v>
+      </c>
+      <c r="G30" s="24" t="n">
+        <f aca="false">G28-G29</f>
+        <v>2365852.10286693</v>
+      </c>
+      <c r="H30" s="24" t="n">
+        <f aca="false">H28-H29</f>
+        <v>3234158.96868819</v>
+      </c>
+      <c r="I30" s="24" t="n">
+        <f aca="false">I28-I29</f>
+        <v>4219696.42785879</v>
+      </c>
+      <c r="J30" s="24" t="n">
+        <f aca="false">J28-J29</f>
+        <v>5329550.07373809</v>
+      </c>
+      <c r="K30" s="24" t="n">
+        <f aca="false">K28-K29</f>
+        <v>6198539.6890057</v>
+      </c>
+      <c r="L30" s="24" t="n">
+        <f aca="false">L28-L29</f>
+        <v>10183840.5176745</v>
+      </c>
+      <c r="M30" s="24" t="n">
+        <f aca="false">M28-M29</f>
+        <v>12161824.9470748</v>
+      </c>
+      <c r="N30" s="24" t="n">
+        <f aca="false">N28-N29</f>
+        <v>14328273.8255113</v>
+      </c>
+      <c r="O30" s="24" t="n">
+        <f aca="false">O28-O29</f>
+        <v>15935118.7308261</v>
+      </c>
+      <c r="P30" s="24" t="n">
+        <f aca="false">P28-P29</f>
+        <v>17599246.929928</v>
+      </c>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="42" t="s">
+        <v>677</v>
+      </c>
+      <c r="B31" s="43"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="43"/>
+      <c r="L31" s="43"/>
+      <c r="M31" s="43"/>
+      <c r="N31" s="43"/>
+      <c r="O31" s="43"/>
+      <c r="P31" s="43"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="43"/>
+    </row>
+    <row r="32" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="18" t="s">
+        <v>678</v>
+      </c>
+      <c r="B32" s="24" t="n">
+        <f aca="false">B27</f>
+        <v>82877.1596018711</v>
+      </c>
+      <c r="C32" s="24" t="n">
+        <f aca="false">C27</f>
+        <v>102935.265703053</v>
+      </c>
+      <c r="D32" s="24" t="n">
+        <f aca="false">D27</f>
+        <v>141868.08143532</v>
+      </c>
+      <c r="E32" s="24" t="n">
+        <f aca="false">E27</f>
+        <v>302797.490222532</v>
+      </c>
+      <c r="F32" s="24" t="n">
+        <f aca="false">F27</f>
+        <v>355768.629817565</v>
+      </c>
+      <c r="G32" s="24" t="n">
+        <f aca="false">G27</f>
+        <v>417503.312270635</v>
+      </c>
+      <c r="H32" s="24" t="n">
+        <f aca="false">H27</f>
+        <v>570733.935650857</v>
+      </c>
+      <c r="I32" s="24" t="n">
+        <f aca="false">I27</f>
+        <v>744652.31079861</v>
+      </c>
+      <c r="J32" s="24" t="n">
+        <f aca="false">J27</f>
+        <v>940508.836542016</v>
+      </c>
+      <c r="K32" s="24" t="n">
+        <f aca="false">K27</f>
+        <v>1093859.94511865</v>
+      </c>
+      <c r="L32" s="24" t="n">
+        <f aca="false">L27</f>
+        <v>1797148.32664844</v>
+      </c>
+      <c r="M32" s="24" t="n">
+        <f aca="false">M27</f>
+        <v>2146204.40242496</v>
+      </c>
+      <c r="N32" s="24" t="n">
+        <f aca="false">N27</f>
+        <v>2528518.91038435</v>
+      </c>
+      <c r="O32" s="24" t="n">
+        <f aca="false">O27</f>
+        <v>2812079.77602814</v>
+      </c>
+      <c r="P32" s="24" t="n">
+        <f aca="false">P27</f>
+        <v>3105749.45822259</v>
+      </c>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="51" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="s">
+        <v>680</v>
+      </c>
+      <c r="B33" s="17" t="n">
+        <f aca="false">IF(B32=0,0,PMT(Assumptions!$B$111/12,60,-B32))</f>
+        <v>1875.12063882218</v>
+      </c>
+      <c r="C33" s="17" t="n">
+        <f aca="false">IF(C32=0,0,PMT(Assumptions!$B$111/12,60,-C32))</f>
+        <v>2328.94131639717</v>
+      </c>
+      <c r="D33" s="17" t="n">
+        <f aca="false">IF(D32=0,0,PMT(Assumptions!$B$111/12,60,-D32))</f>
+        <v>3209.80797082563</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <f aca="false">IF(E32=0,0,PMT(Assumptions!$B$111/12,60,-E32))</f>
+        <v>6850.88420051266</v>
+      </c>
+      <c r="F33" s="17" t="n">
+        <f aca="false">IF(F32=0,0,PMT(Assumptions!$B$111/12,60,-F32))</f>
+        <v>8049.372150555</v>
+      </c>
+      <c r="G33" s="17" t="n">
+        <f aca="false">IF(G32=0,0,PMT(Assumptions!$B$111/12,60,-G32))</f>
+        <v>9446.13789101929</v>
+      </c>
+      <c r="H33" s="17" t="n">
+        <f aca="false">IF(H32=0,0,PMT(Assumptions!$B$111/12,60,-H32))</f>
+        <v>12913.0267875513</v>
+      </c>
+      <c r="I33" s="17" t="n">
+        <f aca="false">IF(I32=0,0,PMT(Assumptions!$B$111/12,60,-I32))</f>
+        <v>16847.9822840547</v>
+      </c>
+      <c r="J33" s="17" t="n">
+        <f aca="false">IF(J32=0,0,PMT(Assumptions!$B$111/12,60,-J32))</f>
+        <v>21279.295029734</v>
+      </c>
+      <c r="K33" s="17" t="n">
+        <f aca="false">IF(K32=0,0,PMT(Assumptions!$B$111/12,60,-K32))</f>
+        <v>24748.9099400382</v>
+      </c>
+      <c r="L33" s="17" t="n">
+        <f aca="false">IF(L32=0,0,PMT(Assumptions!$B$111/12,60,-L32))</f>
+        <v>40661.0208954017</v>
+      </c>
+      <c r="M33" s="17" t="n">
+        <f aca="false">IF(M32=0,0,PMT(Assumptions!$B$111/12,60,-M32))</f>
+        <v>48558.5194937979</v>
+      </c>
+      <c r="N33" s="17" t="n">
+        <f aca="false">IF(N32=0,0,PMT(Assumptions!$B$111/12,60,-N32))</f>
+        <v>57208.5001137854</v>
+      </c>
+      <c r="O33" s="17" t="n">
+        <f aca="false">IF(O32=0,0,PMT(Assumptions!$B$111/12,60,-O32))</f>
+        <v>63624.149903006</v>
+      </c>
+      <c r="P33" s="17" t="n">
+        <f aca="false">IF(P32=0,0,PMT(Assumptions!$B$111/12,60,-P32))</f>
+        <v>70268.5147041705</v>
+      </c>
+      <c r="Q33" s="3"/>
+      <c r="R33" s="51" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="3"/>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="s">
+        <v>682</v>
+      </c>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6"/>
+      <c r="P35" s="6"/>
+      <c r="Q35" s="3"/>
+      <c r="R35" s="6"/>
+    </row>
+    <row r="36" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="33" t="s">
+        <v>683</v>
+      </c>
+      <c r="B36" s="33"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="33"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="33"/>
+      <c r="K36" s="33"/>
+      <c r="L36" s="33"/>
+      <c r="M36" s="33"/>
+      <c r="N36" s="33"/>
+      <c r="O36" s="33"/>
+      <c r="P36" s="33"/>
+      <c r="Q36" s="33"/>
+      <c r="R36" s="33"/>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="true" password="ef11" formatCells="false" formatColumns="false" formatRows="false"/>
+  <mergeCells count="1">
+    <mergeCell ref="A36:R36"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B28"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="90"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="B1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="60" t="s">
+        <v>685</v>
+      </c>
+      <c r="B3" s="61" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="60" t="s">
+        <v>687</v>
+      </c>
+      <c r="B4" s="61" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="60" t="s">
+        <v>689</v>
+      </c>
+      <c r="B5" s="61" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="60" t="s">
+        <v>691</v>
+      </c>
+      <c r="B6" s="61" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="60" t="s">
+        <v>693</v>
+      </c>
+      <c r="B7" s="61" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="60" t="s">
+        <v>695</v>
+      </c>
+      <c r="B8" s="61" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="60" t="s">
+        <v>697</v>
+      </c>
+      <c r="B9" s="61" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="60" t="s">
+        <v>699</v>
+      </c>
+      <c r="B10" s="61" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="60" t="s">
+        <v>701</v>
+      </c>
+      <c r="B11" s="61" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="60" t="s">
+        <v>703</v>
+      </c>
+      <c r="B12" s="61" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="60" t="s">
+        <v>705</v>
+      </c>
+      <c r="B13" s="61" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="60" t="s">
+        <v>707</v>
+      </c>
+      <c r="B14" s="61" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="60" t="s">
+        <v>709</v>
+      </c>
+      <c r="B15" s="61" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="60" t="s">
+        <v>711</v>
+      </c>
+      <c r="B16" s="61" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="60" t="s">
+        <v>713</v>
+      </c>
+      <c r="B17" s="61" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="60" t="s">
+        <v>715</v>
+      </c>
+      <c r="B18" s="61" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="60" t="s">
+        <v>717</v>
+      </c>
+      <c r="B19" s="61" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="60" t="s">
+        <v>719</v>
+      </c>
+      <c r="B20" s="61" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="60" t="s">
+        <v>721</v>
+      </c>
+      <c r="B21" s="61" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="60" t="s">
+        <v>723</v>
+      </c>
+      <c r="B22" s="61" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="60" t="s">
+        <v>725</v>
+      </c>
+      <c r="B23" s="61" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="60" t="s">
+        <v>727</v>
+      </c>
+      <c r="B24" s="61" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="60" t="s">
+        <v>729</v>
+      </c>
+      <c r="B25" s="61" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="60" t="s">
+        <v>731</v>
+      </c>
+      <c r="B26" s="61" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="60" t="s">
+        <v>733</v>
+      </c>
+      <c r="B27" s="61" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="60" t="s">
+        <v>735</v>
+      </c>
+      <c r="B28" s="61" t="s">
+        <v>736</v>
       </c>
     </row>
   </sheetData>
@@ -3493,7 +7411,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>189</v>
+        <v>227</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -3525,7 +7443,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>190</v>
+        <v>228</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -3587,7 +7505,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>191</v>
+        <v>229</v>
       </c>
       <c r="B4" s="19" t="n">
         <v>1</v>
@@ -3662,18 +7580,18 @@
         <v>24</v>
       </c>
       <c r="Z4" s="18" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="AA4" s="18" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
       <c r="AB4" s="18" t="s">
-        <v>194</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>195</v>
+        <v>233</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -3705,7 +7623,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="20" t="s">
-        <v>196</v>
+        <v>234</v>
       </c>
       <c r="B6" s="21" t="n">
         <f aca="false">MIN(Assumptions!$B$13,Assumptions!$B$8+(Assumptions!$B$13-Assumptions!$B$8)*(1-1)/5)</f>
@@ -3818,7 +7736,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="B7" s="21" t="n">
         <f aca="false">IF(1&lt;Assumptions!$B$14,0,MIN(Assumptions!$B$16,Assumptions!$B$15+(Assumptions!$B$16-Assumptions!$B$15)*(1-Assumptions!$B$14)/3))</f>
@@ -3931,7 +7849,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="B8" s="22" t="n">
         <f aca="false">B6+B7</f>
@@ -4044,7 +7962,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -4076,7 +7994,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="20" t="s">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="B10" s="21" t="n">
         <f aca="false">Assumptions!$B$64*IF(1&gt;=Assumptions!$B$14,Assumptions!$B$75,1)/Assumptions!$B$65</f>
@@ -4189,7 +8107,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="20" t="s">
-        <v>201</v>
+        <v>239</v>
       </c>
       <c r="B11" s="21" t="n">
         <f aca="false">IF(1&gt;=2,Assumptions!$B$67*IF(1&gt;=Assumptions!$B$14,Assumptions!$B$75,1)/Assumptions!$B$68,0)</f>
@@ -4302,7 +8220,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="20" t="s">
-        <v>202</v>
+        <v>240</v>
       </c>
       <c r="B12" s="21" t="n">
         <f aca="false">Assumptions!$B$70*(1+Assumptions!$B$71)^(1-1)</f>
@@ -4415,7 +8333,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="B13" s="22" t="n">
         <f aca="false">B10+B11+B12</f>
@@ -4528,7 +8446,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="20" t="s">
-        <v>204</v>
+        <v>242</v>
       </c>
       <c r="B14" s="21" t="n">
         <f aca="false">B10*Assumptions!$B$66+B11*Assumptions!$B$69+B12*Assumptions!$B$72</f>
@@ -4641,7 +8559,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>205</v>
+        <v>243</v>
       </c>
       <c r="B15" s="22" t="n">
         <f aca="false">B14*Assumptions!$B$74</f>
@@ -4754,7 +8672,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="20" t="s">
-        <v>206</v>
+        <v>244</v>
       </c>
       <c r="B16" s="21" t="n">
         <f aca="false">B15*Assumptions!$B$17</f>
@@ -4867,7 +8785,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="s">
-        <v>207</v>
+        <v>245</v>
       </c>
       <c r="B17" s="22" t="n">
         <f aca="false">MIN(B16+0,B8)</f>
@@ -4980,7 +8898,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="B18" s="21" t="n">
         <f aca="false">MIN(B8*Assumptions!$B$18,MAX(0,B16+0-B17))</f>
@@ -5084,7 +9002,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>209</v>
+        <v>247</v>
       </c>
       <c r="B19" s="23" t="n">
         <f aca="false">IF(B8=0,0,B17/B8)</f>
@@ -5188,7 +9106,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>210</v>
+        <v>248</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -5220,7 +9138,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>211</v>
+        <v>249</v>
       </c>
       <c r="B21" s="16" t="n">
         <f aca="false">B17/Assumptions!$B$11</f>
@@ -5324,7 +9242,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="20" t="s">
-        <v>212</v>
+        <v>250</v>
       </c>
       <c r="B22" s="17" t="n">
         <f aca="false">B17*Assumptions!$B$5</f>
@@ -5437,7 +9355,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="18" t="s">
-        <v>213</v>
+        <v>251</v>
       </c>
       <c r="B23" s="24" t="n">
         <f aca="false">B22</f>
@@ -5550,7 +9468,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="20" t="s">
-        <v>214</v>
+        <v>252</v>
       </c>
       <c r="B24" s="21" t="n">
         <f aca="false">IF(1&lt;Assumptions!$B$36,0,B17/Assumptions!$B$17*Assumptions!$B$31+IF(1&lt;=Assumptions!$B$36+11,Assumptions!$B$34*Assumptions!$B$35/12,0))</f>
@@ -5663,7 +9581,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="B25" s="21" t="n">
         <f aca="false">0+B24</f>
@@ -5767,7 +9685,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>216</v>
+        <v>254</v>
       </c>
       <c r="B26" s="17" t="n">
         <f aca="false">B25/12*Assumptions!$B$33*Assumptions!$B$30</f>
@@ -5880,7 +9798,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="18" t="s">
-        <v>217</v>
+        <v>255</v>
       </c>
       <c r="B27" s="25" t="n">
         <f aca="false">B23+B26</f>
@@ -5993,7 +9911,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>218</v>
+        <v>256</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -6025,7 +9943,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="20" t="s">
-        <v>219</v>
+        <v>257</v>
       </c>
       <c r="B29" s="21" t="n">
         <f aca="false">1+IF(B7&gt;0,1,0)</f>
@@ -6129,7 +10047,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="20" t="s">
-        <v>220</v>
+        <v>258</v>
       </c>
       <c r="B30" s="17" t="n">
         <f aca="false">IF(Assumptions!$B$20=1,B23*Assumptions!$B$21,B29*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24+Assumptions!$B$26*Assumptions!$B$28*Assumptions!$B$23*1.5)*(1+Assumptions!$B$25))</f>
@@ -6242,7 +10160,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="20" t="s">
-        <v>221</v>
+        <v>259</v>
       </c>
       <c r="B31" s="17" t="n">
         <f aca="false">B23*Assumptions!$B$22</f>
@@ -6355,7 +10273,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>222</v>
+        <v>260</v>
       </c>
       <c r="B32" s="17" t="n">
         <f aca="false">B25/12*Assumptions!$B$33*Assumptions!$B$37</f>
@@ -6468,7 +10386,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="18" t="s">
-        <v>223</v>
+        <v>261</v>
       </c>
       <c r="B33" s="25" t="n">
         <f aca="false">B30+B31+B32</f>
@@ -6581,7 +10499,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="18" t="s">
-        <v>224</v>
+        <v>262</v>
       </c>
       <c r="B34" s="24" t="n">
         <f aca="false">B27-B33</f>
@@ -6694,7 +10612,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="20" t="s">
-        <v>225</v>
+        <v>263</v>
       </c>
       <c r="B35" s="23" t="n">
         <f aca="false">IF(B27=0,0,B34/B27)</f>
@@ -6798,7 +10716,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>226</v>
+        <v>264</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -6830,7 +10748,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="20" t="s">
-        <v>227</v>
+        <v>265</v>
       </c>
       <c r="B37" s="17" t="n">
         <f aca="false">Assumptions!$B$78</f>
@@ -6943,7 +10861,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="20" t="s">
-        <v>228</v>
+        <v>266</v>
       </c>
       <c r="B38" s="17" t="n">
         <f aca="false">Assumptions!$B$79</f>
@@ -7056,7 +10974,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="20" t="s">
-        <v>229</v>
+        <v>267</v>
       </c>
       <c r="B39" s="17" t="n">
         <f aca="false">Assumptions!$B$80</f>
@@ -7169,7 +11087,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="20" t="s">
-        <v>230</v>
+        <v>268</v>
       </c>
       <c r="B40" s="17" t="n">
         <f aca="false">Assumptions!$B$81</f>
@@ -7282,7 +11200,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="20" t="s">
-        <v>231</v>
+        <v>269</v>
       </c>
       <c r="B41" s="17" t="n">
         <f aca="false">Assumptions!$B$82</f>
@@ -7395,7 +11313,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="20" t="s">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="B42" s="17" t="n">
         <f aca="false">Assumptions!$B$83</f>
@@ -7508,7 +11426,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="20" t="s">
-        <v>233</v>
+        <v>271</v>
       </c>
       <c r="B43" s="17" t="n">
         <f aca="false">IF(1&gt;=Assumptions!$B$86,Assumptions!$B$87,0)</f>
@@ -7621,7 +11539,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="20" t="s">
-        <v>234</v>
+        <v>272</v>
       </c>
       <c r="B44" s="17" t="n">
         <f aca="false">Assumptions!$B$88</f>
@@ -7734,7 +11652,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="20" t="s">
-        <v>235</v>
+        <v>273</v>
       </c>
       <c r="B45" s="17" t="n">
         <f aca="false">Assumptions!$B$64*IF(1&gt;=Assumptions!$B$14,Assumptions!$B$75,1)</f>
@@ -7847,7 +11765,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="20" t="s">
-        <v>236</v>
+        <v>274</v>
       </c>
       <c r="B46" s="17" t="n">
         <f aca="false">IF(1&gt;=2,Assumptions!$B$67*IF(1&gt;=Assumptions!$B$14,Assumptions!$B$75,1),0)</f>
@@ -7960,7 +11878,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="20" t="s">
-        <v>237</v>
+        <v>275</v>
       </c>
       <c r="B47" s="17" t="n">
         <f aca="false">Assumptions!$B$76</f>
@@ -8073,7 +11991,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="20" t="s">
-        <v>238</v>
+        <v>276</v>
       </c>
       <c r="B48" s="17" t="n">
         <f aca="false">IF(AND(1&gt;=Assumptions!$B$14,1&lt;Assumptions!$B$14+Assumptions!$B$92),Assumptions!$B$91,0)+IF(AND(1&gt;=Assumptions!$B$14,1&lt;Assumptions!$B$14+Assumptions!$B$95),Assumptions!$B$94,0)+IF(AND(1&gt;=Assumptions!$B$14,1&lt;Assumptions!$B$14+Assumptions!$B$98),Assumptions!$B$97,0)+IF(AND(1&gt;=Assumptions!$B$14,1&lt;Assumptions!$B$14+Assumptions!$B$101),Assumptions!$B$100,0)+IF(AND(1&gt;=Assumptions!$B$14,1&lt;Assumptions!$B$14+Assumptions!$B$104),Assumptions!$B$103,0)+IF(1=Assumptions!$B$14,Assumptions!$B$108,0)</f>
@@ -8186,7 +12104,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="20" t="s">
-        <v>239</v>
+        <v>277</v>
       </c>
       <c r="B49" s="17" t="n">
         <f aca="false">IF(1&gt;=Assumptions!$B$14+Assumptions!$B$92,-PMT(Assumptions!$B$106/12,Assumptions!$B$107,Assumptions!$B$90*Assumptions!$B$105),0)+IF(1&gt;=Assumptions!$B$14+Assumptions!$B$95,-PMT(Assumptions!$B$106/12,Assumptions!$B$107,Assumptions!$B$93*Assumptions!$B$105),0)+IF(1&gt;=Assumptions!$B$14+Assumptions!$B$98,-PMT(Assumptions!$B$106/12,Assumptions!$B$107,Assumptions!$B$96*Assumptions!$B$105),0)+IF(1&gt;=Assumptions!$B$14+Assumptions!$B$101,-PMT(Assumptions!$B$106/12,Assumptions!$B$107,Assumptions!$B$99*Assumptions!$B$105),0)+IF(1&gt;=Assumptions!$B$14+Assumptions!$B$104,-PMT(Assumptions!$B$106/12,Assumptions!$B$107,Assumptions!$B$102*Assumptions!$B$105),0)</f>
@@ -8299,7 +12217,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="18" t="s">
-        <v>240</v>
+        <v>278</v>
       </c>
       <c r="B50" s="25" t="n">
         <f aca="false">SUM(B37:B49)</f>
@@ -8412,7 +12330,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="18" t="s">
-        <v>241</v>
+        <v>279</v>
       </c>
       <c r="B51" s="24" t="n">
         <f aca="false">B34-B50</f>
@@ -8525,7 +12443,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="20" t="s">
-        <v>242</v>
+        <v>280</v>
       </c>
       <c r="B52" s="23" t="n">
         <f aca="false">IF(B27=0,0,B51/B27)</f>
@@ -8629,7 +12547,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>243</v>
+        <v>281</v>
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -8661,7 +12579,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="20" t="s">
-        <v>244</v>
+        <v>282</v>
       </c>
       <c r="B54" s="17" t="n">
         <f aca="false">B23*Assumptions!$B$59+B23*(1-Assumptions!$B$59)*Assumptions!$B$60+0+B26</f>
@@ -8774,7 +12692,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="20" t="s">
-        <v>245</v>
+        <v>283</v>
       </c>
       <c r="B55" s="17" t="n">
         <f aca="false">B33+B50</f>
@@ -8887,7 +12805,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="20" t="s">
-        <v>246</v>
+        <v>284</v>
       </c>
       <c r="B56" s="17" t="n">
         <f aca="false">IF(1=Assumptions!$B$14+Assumptions!$B$92,Assumptions!$B$90*(1-Assumptions!$B$105),0)+IF(1=Assumptions!$B$14+Assumptions!$B$95,Assumptions!$B$93*(1-Assumptions!$B$105),0)+IF(1=Assumptions!$B$14+Assumptions!$B$98,Assumptions!$B$96*(1-Assumptions!$B$105),0)+IF(1=Assumptions!$B$14+Assumptions!$B$101,Assumptions!$B$99*(1-Assumptions!$B$105),0)+IF(1=Assumptions!$B$14+Assumptions!$B$104,Assumptions!$B$102*(1-Assumptions!$B$105),0)</f>
@@ -9000,7 +12918,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="18" t="s">
-        <v>247</v>
+        <v>285</v>
       </c>
       <c r="B57" s="25" t="n">
         <f aca="false">B54-B55-B56</f>
@@ -9113,7 +13031,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="18" t="s">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="B58" s="24" t="n">
         <f aca="false">Assumptions!$B$62+Assumptions!$B$7+B57</f>
@@ -9217,7 +13135,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
-        <v>249</v>
+        <v>287</v>
       </c>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -9249,7 +13167,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="20" t="s">
-        <v>250</v>
+        <v>288</v>
       </c>
       <c r="B60" s="17" t="n">
         <f aca="false">IF(B8=0,0,B23/IF(B7&gt;0,2,1))</f>
@@ -9353,7 +13271,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="20" t="s">
-        <v>251</v>
+        <v>289</v>
       </c>
       <c r="B61" s="17" t="n">
         <f aca="false">IF(B13=0,0,(B45+B46+B47)/B13)</f>
@@ -9457,7 +13375,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="20" t="s">
-        <v>252</v>
+        <v>290</v>
       </c>
       <c r="B62" s="17" t="n">
         <f aca="false">IF(B15=0,0,(B45+B46+B47)/B15)</f>
@@ -9561,7 +13479,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="20" t="s">
-        <v>253</v>
+        <v>291</v>
       </c>
       <c r="B63" s="23" t="n">
         <f aca="false">Assumptions!$B$74</f>
@@ -9665,7 +13583,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="20" t="s">
-        <v>254</v>
+        <v>292</v>
       </c>
       <c r="B64" s="23" t="n">
         <f aca="false">IF(B27=0,0,B26/B27)</f>
@@ -9769,7 +13687,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="20" t="s">
-        <v>255</v>
+        <v>293</v>
       </c>
       <c r="B65" s="23" t="n">
         <f aca="false">IF(B27=0,0,B30/B27)</f>
@@ -9873,7 +13791,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="20" t="s">
-        <v>256</v>
+        <v>294</v>
       </c>
       <c r="B66" s="17" t="n">
         <f aca="false">IF(B29=0,0,B23/B29/Assumptions!$B$10)</f>
@@ -9977,7 +13895,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="20" t="s">
-        <v>257</v>
+        <v>295</v>
       </c>
       <c r="B67" s="21" t="n">
         <f aca="false">IF(Assumptions!$B$20=1,B50/(Assumptions!$B$5*(1-Assumptions!$B$21-Assumptions!$B$22)),(B50+(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24+Assumptions!$B$26*Assumptions!$B$28*Assumptions!$B$23*1.5)*(1+Assumptions!$B$25))/(Assumptions!$B$5*(1-Assumptions!$B$22)))</f>
@@ -10106,21 +14024,21 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>258</v>
+        <v>296</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>259</v>
+        <v>297</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>260</v>
+        <v>298</v>
       </c>
       <c r="B3" s="26" t="n">
         <f aca="false">Assumptions!$B$17</f>
@@ -10130,7 +14048,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>261</v>
+        <v>299</v>
       </c>
       <c r="B4" s="27" t="n">
         <f aca="false">B3*Assumptions!$B$5</f>
@@ -10140,7 +14058,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>262</v>
+        <v>300</v>
       </c>
       <c r="B5" s="27" t="n">
         <f aca="false">B3/Assumptions!$B$13*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24+Assumptions!$B$26*Assumptions!$B$28*Assumptions!$B$23*1.5)*(1+Assumptions!$B$25)</f>
@@ -10150,7 +14068,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>263</v>
+        <v>301</v>
       </c>
       <c r="B6" s="27" t="n">
         <f aca="false">B4*Assumptions!$B$22</f>
@@ -10160,7 +14078,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>264</v>
+        <v>302</v>
       </c>
       <c r="B7" s="17" t="n">
         <f aca="false">B4-B5-B6</f>
@@ -10170,7 +14088,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>265</v>
+        <v>303</v>
       </c>
       <c r="B8" s="23" t="n">
         <f aca="false">B7/B4</f>
@@ -10180,7 +14098,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>266</v>
+        <v>304</v>
       </c>
       <c r="B9" s="28" t="n">
         <f aca="false">B3/(Assumptions!$B$13/Assumptions!$B$10)</f>
@@ -10190,14 +14108,14 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>267</v>
+        <v>305</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>268</v>
+        <v>306</v>
       </c>
       <c r="B11" s="26" t="n">
         <f aca="false">Assumptions!$B$13</f>
@@ -10207,7 +14125,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>250</v>
+        <v>288</v>
       </c>
       <c r="B12" s="27" t="n">
         <f aca="false">B11*Assumptions!$B$5</f>
@@ -10217,7 +14135,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>269</v>
+        <v>307</v>
       </c>
       <c r="B13" s="27" t="n">
         <f aca="false">Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24+Assumptions!$B$26*Assumptions!$B$28*Assumptions!$B$23*1.5</f>
@@ -10227,7 +14145,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>270</v>
+        <v>308</v>
       </c>
       <c r="B14" s="27" t="n">
         <f aca="false">B13*(1+Assumptions!$B$25)</f>
@@ -10237,19 +14155,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>271</v>
+        <v>309</v>
       </c>
       <c r="B15" s="23" t="n">
         <f aca="false">B14/B12</f>
         <v>0.308978</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>272</v>
+        <v>310</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>273</v>
+        <v>311</v>
       </c>
       <c r="B16" s="27" t="n">
         <f aca="false">B12*(1-Assumptions!$B$22)-B14</f>
@@ -10259,14 +14177,14 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>274</v>
+        <v>312</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>275</v>
+        <v>313</v>
       </c>
       <c r="B18" s="27" t="n">
         <f aca="false">Assumptions!$B$30</f>
@@ -10276,7 +14194,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>276</v>
+        <v>314</v>
       </c>
       <c r="B19" s="27" t="n">
         <f aca="false">Assumptions!$B$37</f>
@@ -10286,7 +14204,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>277</v>
+        <v>315</v>
       </c>
       <c r="B20" s="17" t="n">
         <f aca="false">B18-B19</f>
@@ -10296,7 +14214,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>278</v>
+        <v>316</v>
       </c>
       <c r="B21" s="23" t="n">
         <f aca="false">B20/B18</f>
@@ -10306,7 +14224,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>279</v>
+        <v>317</v>
       </c>
       <c r="B22" s="26" t="n">
         <f aca="false">5*Assumptions!$B$33</f>
@@ -10316,7 +14234,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>280</v>
+        <v>318</v>
       </c>
       <c r="B23" s="17" t="n">
         <f aca="false">B20*B22</f>
@@ -10326,26 +14244,26 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>281</v>
+        <v>319</v>
       </c>
       <c r="B24" s="17" t="n">
         <f aca="false">0.25*B7</f>
         <v>613.7775</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>282</v>
+        <v>320</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>283</v>
+        <v>321</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>284</v>
+        <v>322</v>
       </c>
       <c r="B26" s="26" t="n">
         <f aca="false">Assumptions!$B$6</f>
@@ -10355,7 +14273,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>285</v>
+        <v>323</v>
       </c>
       <c r="B27" s="27" t="n">
         <f aca="false">B26*Assumptions!$B$5+MAX(0,Assumptions!$B$10-B26/Assumptions!$B$11)*Assumptions!$B$12</f>
@@ -10365,31 +14283,31 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>286</v>
+        <v>324</v>
       </c>
       <c r="B28" s="27" t="n">
         <f aca="false">B27/Assumptions!$B$10</f>
         <v>1509.4130675526</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>287</v>
+        <v>325</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="B29" s="23" t="n">
         <f aca="false">B14/B27</f>
         <v>0.438644482758621</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>289</v>
+        <v>327</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>290</v>
+        <v>328</v>
       </c>
       <c r="B30" s="23" t="n">
         <f aca="false">B15</f>
@@ -10399,7 +14317,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>291</v>
+        <v>329</v>
       </c>
       <c r="B31" s="27" t="n">
         <f aca="false">Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83</f>
@@ -10409,7 +14327,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>292</v>
+        <v>330</v>
       </c>
       <c r="B32" s="26" t="n">
         <f aca="false">(B31+B14+Assumptions!$B$79)/(Assumptions!$B$5*(1-Assumptions!$B$22))</f>
@@ -10419,7 +14337,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>293</v>
+        <v>331</v>
       </c>
       <c r="B33" s="29" t="n">
         <f aca="false">B32/Assumptions!$B$13</f>
@@ -10453,7 +14371,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>294</v>
+        <v>332</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -10461,7 +14379,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>295</v>
+        <v>333</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -10476,18 +14394,18 @@
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="30"/>
       <c r="B4" s="30" t="s">
-        <v>296</v>
+        <v>334</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>297</v>
+        <v>335</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>298</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>299</v>
+        <v>337</v>
       </c>
       <c r="B5" s="13" t="n">
         <v>700</v>
@@ -10501,7 +14419,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>300</v>
+        <v>338</v>
       </c>
       <c r="B6" s="13" t="n">
         <v>1</v>
@@ -10515,7 +14433,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>301</v>
+        <v>339</v>
       </c>
       <c r="B7" s="11" t="n">
         <v>45</v>
@@ -10529,7 +14447,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>302</v>
+        <v>340</v>
       </c>
       <c r="B8" s="13" t="n">
         <v>40</v>
@@ -10543,7 +14461,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>303</v>
+        <v>341</v>
       </c>
       <c r="B9" s="17" t="n">
         <f aca="false">B5*B6*B7</f>
@@ -10560,7 +14478,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>304</v>
+        <v>342</v>
       </c>
       <c r="B10" s="17" t="n">
         <f aca="false">B8/12*Assumptions!$B$33*Assumptions!$B$30</f>
@@ -10577,7 +14495,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>305</v>
+        <v>343</v>
       </c>
       <c r="B11" s="17" t="n">
         <f aca="false">B9+B10</f>
@@ -10594,7 +14512,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>306</v>
+        <v>344</v>
       </c>
       <c r="B12" s="24" t="n">
         <f aca="false">B9*(1-Assumptions!$B$22)-B6*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24+Assumptions!$B$26*Assumptions!$B$28*Assumptions!$B$23*1.5)*(1+Assumptions!$B$25)+B10*(1-Assumptions!$B$37/Assumptions!$B$30)</f>
@@ -10611,7 +14529,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>307</v>
+        <v>345</v>
       </c>
       <c r="B13" s="17" t="n">
         <f aca="false">IF(B6=1,'Proforma 24 mo'!D50,'Proforma 24 mo'!Y50)</f>
@@ -10628,7 +14546,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>308</v>
+        <v>346</v>
       </c>
       <c r="B14" s="24" t="n">
         <f aca="false">B12-B13</f>
@@ -10645,7 +14563,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>309</v>
+        <v>347</v>
       </c>
       <c r="B15" s="24" t="n">
         <f aca="false">B14*12</f>
@@ -10662,7 +14580,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="B16" s="23" t="n">
         <f aca="false">IF(B11=0,0,B14/B11)</f>
@@ -10679,7 +14597,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>311</v>
+        <v>349</v>
       </c>
       <c r="B17" s="21" t="n">
         <f aca="false">B5*B6/Assumptions!$B$17/Assumptions!$B$74</f>
@@ -10696,7 +14614,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>312</v>
+        <v>350</v>
       </c>
       <c r="B18" s="21" t="n">
         <f aca="false">B17/0.45</f>
@@ -10713,7 +14631,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>313</v>
+        <v>351</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -10721,7 +14639,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>314</v>
+        <v>352</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -10729,7 +14647,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>315</v>
+        <v>353</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -10737,7 +14655,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>316</v>
+        <v>354</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -10769,7 +14687,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>317</v>
+        <v>355</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -10783,7 +14701,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>318</v>
+        <v>356</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -10809,39 +14727,39 @@
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="s">
-        <v>319</v>
+        <v>357</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>322</v>
+        <v>360</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>323</v>
+        <v>361</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>324</v>
+        <v>362</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>325</v>
+        <v>363</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>326</v>
+        <v>364</v>
       </c>
       <c r="I4" s="32" t="s">
-        <v>327</v>
+        <v>365</v>
       </c>
       <c r="J4" s="32" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>329</v>
+        <v>367</v>
       </c>
       <c r="B5" s="27" t="n">
         <f aca="false">Assumptions!$B$90</f>
@@ -10882,7 +14800,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>330</v>
+        <v>368</v>
       </c>
       <c r="B6" s="27" t="n">
         <f aca="false">Assumptions!$B$93</f>
@@ -10923,7 +14841,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>331</v>
+        <v>369</v>
       </c>
       <c r="B7" s="27" t="n">
         <f aca="false">Assumptions!$B$96</f>
@@ -10964,7 +14882,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>332</v>
+        <v>370</v>
       </c>
       <c r="B8" s="27" t="n">
         <f aca="false">Assumptions!$B$99</f>
@@ -11005,7 +14923,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
       <c r="B9" s="27" t="n">
         <f aca="false">Assumptions!$B$102</f>
@@ -11046,7 +14964,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>334</v>
+        <v>372</v>
       </c>
       <c r="B10" s="24" t="n">
         <f aca="false">SUM(B5:B9)</f>
@@ -11084,7 +15002,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>335</v>
+        <v>373</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -11098,7 +15016,7 @@
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="s">
-        <v>336</v>
+        <v>374</v>
       </c>
       <c r="B13" s="33"/>
       <c r="C13" s="33"/>
@@ -11112,7 +15030,7 @@
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
-        <v>337</v>
+        <v>375</v>
       </c>
       <c r="B14" s="33"/>
       <c r="C14" s="33"/>
@@ -11126,7 +15044,7 @@
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="33" t="s">
-        <v>338</v>
+        <v>376</v>
       </c>
       <c r="B15" s="33"/>
       <c r="C15" s="33"/>
@@ -11140,7 +15058,7 @@
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="33" t="s">
-        <v>339</v>
+        <v>377</v>
       </c>
       <c r="B16" s="33"/>
       <c r="C16" s="33"/>
@@ -11154,7 +15072,7 @@
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="33" t="s">
-        <v>340</v>
+        <v>378</v>
       </c>
       <c r="B17" s="33"/>
       <c r="C17" s="33"/>
@@ -11200,7 +15118,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>341</v>
+        <v>379</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -11212,7 +15130,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>342</v>
+        <v>380</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -11235,30 +15153,30 @@
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="30"/>
       <c r="B4" s="30" t="s">
-        <v>343</v>
+        <v>381</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>344</v>
+        <v>382</v>
       </c>
       <c r="F4" s="30" t="s">
-        <v>345</v>
+        <v>383</v>
       </c>
       <c r="G4" s="30" t="s">
-        <v>346</v>
+        <v>384</v>
       </c>
       <c r="H4" s="30" t="s">
-        <v>347</v>
+        <v>385</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>348</v>
+        <v>386</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -11270,7 +15188,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="20" t="s">
-        <v>349</v>
+        <v>387</v>
       </c>
       <c r="B6" s="13" t="n">
         <v>1</v>
@@ -11291,12 +15209,12 @@
         <v>4</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>350</v>
+        <v>388</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>351</v>
+        <v>389</v>
       </c>
       <c r="B7" s="34" t="n">
         <v>1</v>
@@ -11317,12 +15235,12 @@
         <v>4</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>352</v>
+        <v>390</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
-        <v>353</v>
+        <v>391</v>
       </c>
       <c r="B8" s="13" t="n">
         <v>4800</v>
@@ -11348,12 +15266,12 @@
         <v>10260</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>354</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>355</v>
+        <v>393</v>
       </c>
       <c r="B9" s="22" t="n">
         <f aca="false">B7*B8</f>
@@ -11383,7 +15301,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>210</v>
+        <v>248</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -11395,7 +15313,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="20" t="s">
-        <v>356</v>
+        <v>394</v>
       </c>
       <c r="B11" s="27" t="n">
         <f aca="false">Assumptions!$B$5</f>
@@ -11425,7 +15343,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="20" t="s">
-        <v>357</v>
+        <v>395</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">'Unit economics'!B27*12</f>
@@ -11452,12 +15370,12 @@
         <v>2242275.804</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>358</v>
+        <v>396</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="20" t="s">
-        <v>359</v>
+        <v>397</v>
       </c>
       <c r="B13" s="13" t="n">
         <v>0</v>
@@ -11480,12 +15398,12 @@
         <v>745</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>360</v>
+        <v>398</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="20" t="s">
-        <v>361</v>
+        <v>399</v>
       </c>
       <c r="B14" s="35" t="n">
         <v>0</v>
@@ -11514,7 +15432,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>217</v>
+        <v>255</v>
       </c>
       <c r="B15" s="24" t="n">
         <f aca="false">B12+B14</f>
@@ -11544,7 +15462,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>218</v>
+        <v>256</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -11556,7 +15474,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>362</v>
+        <v>400</v>
       </c>
       <c r="B17" s="27" t="n">
         <f aca="false">B7*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12</f>
@@ -11583,12 +15501,12 @@
         <v>729277.78249296</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>363</v>
+        <v>401</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>221</v>
+        <v>259</v>
       </c>
       <c r="B18" s="27" t="n">
         <f aca="false">B12*Assumptions!$B$22</f>
@@ -11618,7 +15536,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>364</v>
+        <v>402</v>
       </c>
       <c r="B19" s="35" t="n">
         <v>0</v>
@@ -11647,7 +15565,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="18" t="s">
-        <v>224</v>
+        <v>262</v>
       </c>
       <c r="B20" s="24" t="n">
         <f aca="false">B15-B17-B18-B19</f>
@@ -11677,7 +15595,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>265</v>
+        <v>303</v>
       </c>
       <c r="B21" s="23" t="n">
         <f aca="false">IF(B15=0,0,B20/B15)</f>
@@ -11707,7 +15625,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>365</v>
+        <v>403</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -11719,7 +15637,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="20" t="s">
-        <v>227</v>
+        <v>265</v>
       </c>
       <c r="B23" s="27" t="n">
         <f aca="false">Assumptions!$B$78*12</f>
@@ -11743,12 +15661,12 @@
         <v>108000</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>366</v>
+        <v>404</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="20" t="s">
-        <v>367</v>
+        <v>405</v>
       </c>
       <c r="B24" s="11" t="n">
         <v>0</v>
@@ -11769,12 +15687,12 @@
         <v>50000</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>368</v>
+        <v>406</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>369</v>
+        <v>407</v>
       </c>
       <c r="B25" s="11" t="n">
         <v>0</v>
@@ -11795,12 +15713,12 @@
         <v>72000</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>370</v>
+        <v>408</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>371</v>
+        <v>409</v>
       </c>
       <c r="B26" s="11" t="n">
         <v>0</v>
@@ -11821,12 +15739,12 @@
         <v>58000</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>372</v>
+        <v>410</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>373</v>
+        <v>411</v>
       </c>
       <c r="B27" s="11" t="n">
         <v>0</v>
@@ -11847,12 +15765,12 @@
         <v>20000</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>374</v>
+        <v>412</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="20" t="s">
-        <v>375</v>
+        <v>413</v>
       </c>
       <c r="B28" s="27" t="n">
         <f aca="false">Assumptions!$B$79*12</f>
@@ -11879,12 +15797,12 @@
         <v>37800</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>376</v>
+        <v>414</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="20" t="s">
-        <v>377</v>
+        <v>415</v>
       </c>
       <c r="B29" s="27" t="n">
         <f aca="false">Assumptions!$B$80*12</f>
@@ -11911,12 +15829,12 @@
         <v>104400.927326881</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>378</v>
+        <v>416</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="20" t="s">
-        <v>379</v>
+        <v>417</v>
       </c>
       <c r="B30" s="13" t="n">
         <v>0</v>
@@ -11939,7 +15857,7 @@
         <v>4000</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>380</v>
+        <v>418</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11970,12 +15888,12 @@
         <v>0.98398125</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>381</v>
+        <v>419</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>382</v>
+        <v>420</v>
       </c>
       <c r="B32" s="17" t="n">
         <f aca="false">B30*B31*12</f>
@@ -12002,12 +15920,12 @@
         <v>47231.1</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>383</v>
+        <v>421</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>384</v>
+        <v>422</v>
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Assumptions!$B$81*12</f>
@@ -12037,7 +15955,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>385</v>
+        <v>423</v>
       </c>
       <c r="B34" s="27" t="n">
         <f aca="false">Assumptions!$B$82*12</f>
@@ -12061,12 +15979,12 @@
         <v>9600</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>386</v>
+        <v>424</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="20" t="s">
-        <v>387</v>
+        <v>425</v>
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">(Assumptions!$B$64+Assumptions!$B$67+Assumptions!$B$76)*12</f>
@@ -12093,12 +16011,12 @@
         <v>108533.57643</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>388</v>
+        <v>426</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="20" t="s">
-        <v>389</v>
+        <v>427</v>
       </c>
       <c r="B36" s="27" t="n">
         <f aca="false">Assumptions!$B$83*12</f>
@@ -12128,7 +16046,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="20" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="B37" s="35" t="n">
         <v>0</v>
@@ -12157,7 +16075,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>391</v>
+        <v>429</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -12169,7 +16087,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="20" t="s">
-        <v>392</v>
+        <v>430</v>
       </c>
       <c r="B39" s="11" t="n">
         <v>0</v>
@@ -12190,12 +16108,12 @@
         <v>72000</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>393</v>
+        <v>431</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="20" t="s">
-        <v>394</v>
+        <v>432</v>
       </c>
       <c r="B40" s="14" t="n">
         <v>0</v>
@@ -12216,12 +16134,12 @@
         <v>0.1</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>395</v>
+        <v>433</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="20" t="s">
-        <v>396</v>
+        <v>434</v>
       </c>
       <c r="B41" s="17" t="n">
         <f aca="false">MAX(0,B45)</f>
@@ -12248,12 +16166,12 @@
         <v>0</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>397</v>
+        <v>435</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="20" t="s">
-        <v>398</v>
+        <v>436</v>
       </c>
       <c r="B42" s="35" t="n">
         <v>0</v>
@@ -12279,12 +16197,12 @@
         <v>126538.370695016</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>399</v>
+        <v>437</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="18" t="s">
-        <v>400</v>
+        <v>438</v>
       </c>
       <c r="B43" s="24" t="n">
         <f aca="false">SUM(B23:B37)-B30-B31</f>
@@ -12314,7 +16232,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="18" t="s">
-        <v>401</v>
+        <v>439</v>
       </c>
       <c r="B44" s="24" t="n">
         <f aca="false">B20-B43</f>
@@ -12344,7 +16262,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="18" t="s">
-        <v>402</v>
+        <v>440</v>
       </c>
       <c r="B45" s="24" t="n">
         <f aca="false">B44-B42</f>
@@ -12374,7 +16292,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="20" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="B46" s="23" t="n">
         <f aca="false">IF(B15=0,0,B45/B15)</f>
@@ -12404,7 +16322,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>403</v>
+        <v>441</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -12416,7 +16334,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="20" t="s">
-        <v>404</v>
+        <v>442</v>
       </c>
       <c r="B48" s="35" t="n">
         <v>0</v>
@@ -12445,7 +16363,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="18" t="s">
-        <v>405</v>
+        <v>443</v>
       </c>
       <c r="B49" s="27" t="n">
         <f aca="false">Assumptions!$B$62</f>
@@ -12472,12 +16390,12 @@
         <v>1121273.39910311</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>406</v>
+        <v>444</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="20" t="s">
-        <v>407</v>
+        <v>445</v>
       </c>
       <c r="B50" s="17" t="n">
         <f aca="false">B43/6</f>
@@ -12504,12 +16422,12 @@
         <v>107294.267292813</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="20" t="s">
-        <v>409</v>
+        <v>447</v>
       </c>
       <c r="B51" s="39" t="str">
         <f aca="false">IF(B49&gt;=B50,"yes","NO")</f>
@@ -12539,7 +16457,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
-        <v>410</v>
+        <v>448</v>
       </c>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -12551,7 +16469,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="20" t="s">
-        <v>411</v>
+        <v>449</v>
       </c>
       <c r="B53" s="17" t="n">
         <f aca="false">B45+B23</f>
@@ -12581,7 +16499,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="20" t="s">
-        <v>412</v>
+        <v>450</v>
       </c>
       <c r="B54" s="34" t="n">
         <v>2.46</v>
@@ -12602,12 +16520,12 @@
         <v>2.46</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>413</v>
+        <v>451</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="18" t="s">
-        <v>414</v>
+        <v>452</v>
       </c>
       <c r="B55" s="24" t="n">
         <f aca="false">B53*B54</f>
@@ -12634,7 +16552,7 @@
         <v>1296039.52718765</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>415</v>
+        <v>453</v>
       </c>
     </row>
   </sheetData>
@@ -12665,7 +16583,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>416</v>
+        <v>454</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -12677,7 +16595,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>417</v>
+        <v>455</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -12699,7 +16617,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>418</v>
+        <v>456</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -12712,13 +16630,13 @@
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="18"/>
       <c r="B5" s="30" t="s">
-        <v>419</v>
+        <v>457</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>296</v>
+        <v>334</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>420</v>
+        <v>458</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
@@ -12727,7 +16645,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="20" t="s">
-        <v>421</v>
+        <v>459</v>
       </c>
       <c r="B6" s="17" t="n">
         <f aca="false">B37</f>
@@ -12748,7 +16666,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>422</v>
+        <v>460</v>
       </c>
       <c r="B7" s="17" t="n">
         <f aca="false">F37</f>
@@ -12769,7 +16687,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
-        <v>423</v>
+        <v>461</v>
       </c>
       <c r="B8" s="21" t="n">
         <f aca="false">F34</f>
@@ -12790,7 +16708,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="20" t="s">
-        <v>424</v>
+        <v>462</v>
       </c>
       <c r="B9" s="23" t="n">
         <f aca="false">F41</f>
@@ -12811,7 +16729,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="20" t="s">
-        <v>425</v>
+        <v>463</v>
       </c>
       <c r="B10" s="17" t="n">
         <f aca="false">B43</f>
@@ -12832,7 +16750,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
-        <v>426</v>
+        <v>464</v>
       </c>
       <c r="B11" s="24" t="n">
         <f aca="false">B47</f>
@@ -12853,7 +16771,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>427</v>
+        <v>465</v>
       </c>
       <c r="B12" s="24" t="n">
         <f aca="false">F47</f>
@@ -12874,7 +16792,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="20" t="s">
-        <v>428</v>
+        <v>466</v>
       </c>
       <c r="B13" s="17" t="n">
         <f aca="false">B46</f>
@@ -12895,7 +16813,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="20" t="s">
-        <v>429</v>
+        <v>467</v>
       </c>
       <c r="B14" s="17" t="n">
         <f aca="false">F46</f>
@@ -12916,7 +16834,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>430</v>
+        <v>468</v>
       </c>
       <c r="B15" s="24" t="n">
         <f aca="false">F51</f>
@@ -12937,7 +16855,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="20" t="s">
-        <v>431</v>
+        <v>469</v>
       </c>
       <c r="B16" s="17" t="n">
         <f aca="false">F50</f>
@@ -12958,7 +16876,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="s">
-        <v>432</v>
+        <v>470</v>
       </c>
       <c r="B17" s="24" t="n">
         <f aca="false">F52</f>
@@ -12989,7 +16907,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="40" t="s">
-        <v>433</v>
+        <v>471</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -13021,7 +16939,7 @@
     </row>
     <row r="22" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>434</v>
+        <v>472</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -13030,34 +16948,34 @@
       <c r="F22" s="6"/>
       <c r="G22" s="3"/>
       <c r="H22" s="41" t="s">
-        <v>435</v>
+        <v>473</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="30" t="s">
-        <v>436</v>
+        <v>474</v>
       </c>
       <c r="B23" s="30" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="C23" s="30" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
       <c r="D23" s="30" t="s">
-        <v>344</v>
+        <v>382</v>
       </c>
       <c r="E23" s="30" t="s">
-        <v>345</v>
+        <v>383</v>
       </c>
       <c r="F23" s="30" t="s">
-        <v>346</v>
+        <v>384</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="20" t="s">
-        <v>351</v>
+        <v>389</v>
       </c>
       <c r="B24" s="34" t="n">
         <v>2</v>
@@ -13076,12 +16994,12 @@
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="8" t="s">
-        <v>437</v>
+        <v>475</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>438</v>
+        <v>476</v>
       </c>
       <c r="B25" s="13" t="n">
         <v>36</v>
@@ -13100,12 +17018,12 @@
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="8" t="s">
-        <v>439</v>
+        <v>477</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>301</v>
+        <v>339</v>
       </c>
       <c r="B26" s="11" t="n">
         <v>48</v>
@@ -13131,7 +17049,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>440</v>
+        <v>478</v>
       </c>
       <c r="B27" s="14" t="n">
         <v>0</v>
@@ -13153,7 +17071,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="20" t="s">
-        <v>441</v>
+        <v>479</v>
       </c>
       <c r="B28" s="13" t="n">
         <v>45</v>
@@ -13175,7 +17093,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="20" t="s">
-        <v>442</v>
+        <v>480</v>
       </c>
       <c r="B29" s="14" t="n">
         <v>0.075</v>
@@ -13197,7 +17115,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="20" t="s">
-        <v>443</v>
+        <v>481</v>
       </c>
       <c r="B30" s="11" t="n">
         <v>24000</v>
@@ -13219,7 +17137,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="20" t="s">
-        <v>444</v>
+        <v>482</v>
       </c>
       <c r="B31" s="11" t="n">
         <v>0</v>
@@ -13238,12 +17156,12 @@
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="8" t="s">
-        <v>445</v>
+        <v>483</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="42" t="s">
-        <v>446</v>
+        <v>484</v>
       </c>
       <c r="B32" s="43"/>
       <c r="C32" s="43"/>
@@ -13255,7 +17173,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>447</v>
+        <v>485</v>
       </c>
       <c r="B33" s="21" t="n">
         <f aca="false">B24*Assumptions!$B$10*12</f>
@@ -13282,7 +17200,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="18" t="s">
-        <v>448</v>
+        <v>486</v>
       </c>
       <c r="B34" s="22" t="n">
         <f aca="false">B33*B25</f>
@@ -13309,7 +17227,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="20" t="s">
-        <v>449</v>
+        <v>487</v>
       </c>
       <c r="B35" s="17" t="n">
         <f aca="false">B34*B26</f>
@@ -13336,7 +17254,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="20" t="s">
-        <v>361</v>
+        <v>399</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">B28*Assumptions!$B$30*Assumptions!$B$33</f>
@@ -13363,7 +17281,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="18" t="s">
-        <v>217</v>
+        <v>255</v>
       </c>
       <c r="B37" s="24" t="n">
         <f aca="false">B35+B36</f>
@@ -13390,7 +17308,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="20" t="s">
-        <v>450</v>
+        <v>488</v>
       </c>
       <c r="B38" s="17" t="n">
         <f aca="false">B24*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(B1)-2)</f>
@@ -13417,7 +17335,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="20" t="s">
-        <v>451</v>
+        <v>489</v>
       </c>
       <c r="B39" s="17" t="n">
         <f aca="false">B35*Assumptions!$B$22+B28*Assumptions!$B$33*Assumptions!$B$37</f>
@@ -13444,7 +17362,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="18" t="s">
-        <v>224</v>
+        <v>262</v>
       </c>
       <c r="B40" s="24" t="n">
         <f aca="false">B37-B38-B39</f>
@@ -13471,7 +17389,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="20" t="s">
-        <v>265</v>
+        <v>303</v>
       </c>
       <c r="B41" s="23" t="n">
         <f aca="false">IF(B37=0,0,B40/B37)</f>
@@ -13498,7 +17416,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="20" t="s">
-        <v>452</v>
+        <v>490</v>
       </c>
       <c r="B42" s="17" t="n">
         <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+B24*B30+B31+B37*B29+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,B24-1)</f>
@@ -13522,12 +17440,12 @@
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="8" t="s">
-        <v>453</v>
+        <v>491</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="18" t="s">
-        <v>454</v>
+        <v>492</v>
       </c>
       <c r="B43" s="24" t="n">
         <f aca="false">B40-B42</f>
@@ -13554,7 +17472,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="20" t="s">
-        <v>455</v>
+        <v>493</v>
       </c>
       <c r="B44" s="11" t="n">
         <v>15000</v>
@@ -13573,12 +17491,12 @@
       </c>
       <c r="G44" s="3"/>
       <c r="H44" s="8" t="s">
-        <v>456</v>
+        <v>494</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="20" t="s">
-        <v>457</v>
+        <v>495</v>
       </c>
       <c r="B45" s="14" t="n">
         <v>0.1</v>
@@ -13597,12 +17515,12 @@
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="8" t="s">
-        <v>458</v>
+        <v>496</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="20" t="s">
-        <v>459</v>
+        <v>497</v>
       </c>
       <c r="B46" s="17" t="n">
         <f aca="false">B44+IF(B44=0,0,B45*MAX(0,B43-MAX(0,'5-year plan'!$B$44)))</f>
@@ -13629,7 +17547,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="18" t="s">
-        <v>460</v>
+        <v>498</v>
       </c>
       <c r="B47" s="24" t="n">
         <f aca="false">B43-B46</f>
@@ -13656,7 +17574,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="20" t="s">
-        <v>461</v>
+        <v>499</v>
       </c>
       <c r="B48" s="23" t="n">
         <f aca="false">IF(B37=0,0,B47/B37)</f>
@@ -13683,7 +17601,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="20" t="s">
-        <v>462</v>
+        <v>500</v>
       </c>
       <c r="B49" s="17" t="n">
         <f aca="false">MAX(0,B24-1)*'Equipment plan'!$G$10</f>
@@ -13710,7 +17628,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="18" t="s">
-        <v>463</v>
+        <v>501</v>
       </c>
       <c r="B50" s="24" t="n">
         <f aca="false">Assumptions!$B$62+B47-B49</f>
@@ -13734,12 +17652,12 @@
       </c>
       <c r="G50" s="3"/>
       <c r="H50" s="8" t="s">
-        <v>464</v>
+        <v>502</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="20" t="s">
-        <v>465</v>
+        <v>503</v>
       </c>
       <c r="B51" s="17" t="n">
         <f aca="false">B47+Assumptions!$B$78*12</f>
@@ -13766,7 +17684,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="20" t="s">
-        <v>466</v>
+        <v>504</v>
       </c>
       <c r="B52" s="17" t="n">
         <f aca="false">MAX(0,B51)*2.46</f>
@@ -13790,7 +17708,7 @@
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="8" t="s">
-        <v>467</v>
+        <v>505</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13805,7 +17723,7 @@
     </row>
     <row r="54" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>468</v>
+        <v>506</v>
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -13814,34 +17732,34 @@
       <c r="F54" s="6"/>
       <c r="G54" s="3"/>
       <c r="H54" s="41" t="s">
-        <v>469</v>
+        <v>507</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="30" t="s">
-        <v>436</v>
+        <v>474</v>
       </c>
       <c r="B55" s="30" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="C55" s="30" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
       <c r="D55" s="30" t="s">
-        <v>344</v>
+        <v>382</v>
       </c>
       <c r="E55" s="30" t="s">
-        <v>345</v>
+        <v>383</v>
       </c>
       <c r="F55" s="30" t="s">
-        <v>346</v>
+        <v>384</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="20" t="s">
-        <v>351</v>
+        <v>389</v>
       </c>
       <c r="B56" s="34" t="n">
         <v>2</v>
@@ -13860,12 +17778,12 @@
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="8" t="s">
-        <v>437</v>
+        <v>475</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="20" t="s">
-        <v>438</v>
+        <v>476</v>
       </c>
       <c r="B57" s="13" t="n">
         <v>43</v>
@@ -13884,12 +17802,12 @@
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="8" t="s">
-        <v>439</v>
+        <v>477</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="20" t="s">
-        <v>301</v>
+        <v>339</v>
       </c>
       <c r="B58" s="11" t="n">
         <v>50</v>
@@ -13915,7 +17833,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="20" t="s">
-        <v>440</v>
+        <v>478</v>
       </c>
       <c r="B59" s="14" t="n">
         <v>0.03</v>
@@ -13937,7 +17855,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="20" t="s">
-        <v>441</v>
+        <v>479</v>
       </c>
       <c r="B60" s="13" t="n">
         <v>94</v>
@@ -13959,7 +17877,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="20" t="s">
-        <v>442</v>
+        <v>480</v>
       </c>
       <c r="B61" s="14" t="n">
         <v>0.05</v>
@@ -13981,7 +17899,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="20" t="s">
-        <v>443</v>
+        <v>481</v>
       </c>
       <c r="B62" s="11" t="n">
         <v>22000</v>
@@ -14003,7 +17921,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="20" t="s">
-        <v>444</v>
+        <v>482</v>
       </c>
       <c r="B63" s="11" t="n">
         <v>0</v>
@@ -14022,12 +17940,12 @@
       </c>
       <c r="G63" s="3"/>
       <c r="H63" s="8" t="s">
-        <v>445</v>
+        <v>483</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="42" t="s">
-        <v>446</v>
+        <v>484</v>
       </c>
       <c r="B64" s="43"/>
       <c r="C64" s="43"/>
@@ -14039,7 +17957,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="20" t="s">
-        <v>447</v>
+        <v>485</v>
       </c>
       <c r="B65" s="21" t="n">
         <f aca="false">B56*Assumptions!$B$10*12</f>
@@ -14066,7 +17984,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="18" t="s">
-        <v>448</v>
+        <v>486</v>
       </c>
       <c r="B66" s="22" t="n">
         <f aca="false">B65*B57</f>
@@ -14093,7 +18011,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="20" t="s">
-        <v>449</v>
+        <v>487</v>
       </c>
       <c r="B67" s="17" t="n">
         <f aca="false">B66*B58</f>
@@ -14120,7 +18038,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="20" t="s">
-        <v>361</v>
+        <v>399</v>
       </c>
       <c r="B68" s="17" t="n">
         <f aca="false">B60*Assumptions!$B$30*Assumptions!$B$33</f>
@@ -14147,7 +18065,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="18" t="s">
-        <v>217</v>
+        <v>255</v>
       </c>
       <c r="B69" s="24" t="n">
         <f aca="false">B67+B68</f>
@@ -14174,7 +18092,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="20" t="s">
-        <v>450</v>
+        <v>488</v>
       </c>
       <c r="B70" s="17" t="n">
         <f aca="false">B56*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(B1)-2)</f>
@@ -14201,7 +18119,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="20" t="s">
-        <v>451</v>
+        <v>489</v>
       </c>
       <c r="B71" s="17" t="n">
         <f aca="false">B67*Assumptions!$B$22+B60*Assumptions!$B$33*Assumptions!$B$37</f>
@@ -14228,7 +18146,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="18" t="s">
-        <v>224</v>
+        <v>262</v>
       </c>
       <c r="B72" s="24" t="n">
         <f aca="false">B69-B70-B71</f>
@@ -14255,7 +18173,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="20" t="s">
-        <v>265</v>
+        <v>303</v>
       </c>
       <c r="B73" s="23" t="n">
         <f aca="false">IF(B69=0,0,B72/B69)</f>
@@ -14282,7 +18200,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="20" t="s">
-        <v>452</v>
+        <v>490</v>
       </c>
       <c r="B74" s="17" t="n">
         <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+B56*B62+B63+B69*B61+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,B56-1)</f>
@@ -14306,12 +18224,12 @@
       </c>
       <c r="G74" s="3"/>
       <c r="H74" s="8" t="s">
-        <v>453</v>
+        <v>491</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="18" t="s">
-        <v>454</v>
+        <v>492</v>
       </c>
       <c r="B75" s="24" t="n">
         <f aca="false">B72-B74</f>
@@ -14338,7 +18256,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="20" t="s">
-        <v>455</v>
+        <v>493</v>
       </c>
       <c r="B76" s="11" t="n">
         <v>60000</v>
@@ -14357,12 +18275,12 @@
       </c>
       <c r="G76" s="3"/>
       <c r="H76" s="8" t="s">
-        <v>456</v>
+        <v>494</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="20" t="s">
-        <v>457</v>
+        <v>495</v>
       </c>
       <c r="B77" s="14" t="n">
         <v>0.1</v>
@@ -14381,12 +18299,12 @@
       </c>
       <c r="G77" s="3"/>
       <c r="H77" s="8" t="s">
-        <v>458</v>
+        <v>496</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="20" t="s">
-        <v>459</v>
+        <v>497</v>
       </c>
       <c r="B78" s="17" t="n">
         <f aca="false">B76+IF(B76=0,0,B77*MAX(0,B75-MAX(0,'5-year plan'!$B$44)))</f>
@@ -14413,7 +18331,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="18" t="s">
-        <v>460</v>
+        <v>498</v>
       </c>
       <c r="B79" s="24" t="n">
         <f aca="false">B75-B78</f>
@@ -14440,7 +18358,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="20" t="s">
-        <v>461</v>
+        <v>499</v>
       </c>
       <c r="B80" s="23" t="n">
         <f aca="false">IF(B69=0,0,B79/B69)</f>
@@ -14467,7 +18385,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="20" t="s">
-        <v>462</v>
+        <v>500</v>
       </c>
       <c r="B81" s="17" t="n">
         <f aca="false">MAX(0,B56-1)*'Equipment plan'!$G$10</f>
@@ -14494,7 +18412,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="18" t="s">
-        <v>463</v>
+        <v>501</v>
       </c>
       <c r="B82" s="24" t="n">
         <f aca="false">Assumptions!$B$62+B79-B81</f>
@@ -14518,12 +18436,12 @@
       </c>
       <c r="G82" s="3"/>
       <c r="H82" s="8" t="s">
-        <v>464</v>
+        <v>502</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="20" t="s">
-        <v>465</v>
+        <v>503</v>
       </c>
       <c r="B83" s="17" t="n">
         <f aca="false">B79+Assumptions!$B$78*12</f>
@@ -14550,7 +18468,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="20" t="s">
-        <v>466</v>
+        <v>504</v>
       </c>
       <c r="B84" s="17" t="n">
         <f aca="false">MAX(0,B83)*2.46</f>
@@ -14574,7 +18492,7 @@
       </c>
       <c r="G84" s="3"/>
       <c r="H84" s="8" t="s">
-        <v>467</v>
+        <v>505</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14589,7 +18507,7 @@
     </row>
     <row r="86" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="5" t="s">
-        <v>470</v>
+        <v>508</v>
       </c>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -14598,34 +18516,34 @@
       <c r="F86" s="6"/>
       <c r="G86" s="3"/>
       <c r="H86" s="41" t="s">
-        <v>471</v>
+        <v>509</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="30" t="s">
-        <v>436</v>
+        <v>474</v>
       </c>
       <c r="B87" s="30" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="C87" s="30" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
       <c r="D87" s="30" t="s">
-        <v>344</v>
+        <v>382</v>
       </c>
       <c r="E87" s="30" t="s">
-        <v>345</v>
+        <v>383</v>
       </c>
       <c r="F87" s="30" t="s">
-        <v>346</v>
+        <v>384</v>
       </c>
       <c r="G87" s="3"/>
       <c r="H87" s="3"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="20" t="s">
-        <v>351</v>
+        <v>389</v>
       </c>
       <c r="B88" s="34" t="n">
         <v>2</v>
@@ -14644,12 +18562,12 @@
       </c>
       <c r="G88" s="3"/>
       <c r="H88" s="8" t="s">
-        <v>437</v>
+        <v>475</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="20" t="s">
-        <v>438</v>
+        <v>476</v>
       </c>
       <c r="B89" s="13" t="n">
         <v>48</v>
@@ -14668,12 +18586,12 @@
       </c>
       <c r="G89" s="3"/>
       <c r="H89" s="8" t="s">
-        <v>439</v>
+        <v>477</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="20" t="s">
-        <v>301</v>
+        <v>339</v>
       </c>
       <c r="B90" s="11" t="n">
         <v>52</v>
@@ -14699,7 +18617,7 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="20" t="s">
-        <v>440</v>
+        <v>478</v>
       </c>
       <c r="B91" s="14" t="n">
         <v>0.03</v>
@@ -14721,7 +18639,7 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="20" t="s">
-        <v>441</v>
+        <v>479</v>
       </c>
       <c r="B92" s="13" t="n">
         <v>130</v>
@@ -14743,7 +18661,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="20" t="s">
-        <v>442</v>
+        <v>480</v>
       </c>
       <c r="B93" s="14" t="n">
         <v>0.045</v>
@@ -14765,7 +18683,7 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="20" t="s">
-        <v>443</v>
+        <v>481</v>
       </c>
       <c r="B94" s="11" t="n">
         <v>22000</v>
@@ -14787,7 +18705,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="20" t="s">
-        <v>444</v>
+        <v>482</v>
       </c>
       <c r="B95" s="11" t="n">
         <v>12000</v>
@@ -14806,12 +18724,12 @@
       </c>
       <c r="G95" s="3"/>
       <c r="H95" s="8" t="s">
-        <v>445</v>
+        <v>483</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="42" t="s">
-        <v>446</v>
+        <v>484</v>
       </c>
       <c r="B96" s="43"/>
       <c r="C96" s="43"/>
@@ -14823,7 +18741,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="20" t="s">
-        <v>447</v>
+        <v>485</v>
       </c>
       <c r="B97" s="21" t="n">
         <f aca="false">B88*Assumptions!$B$10*12</f>
@@ -14850,7 +18768,7 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="18" t="s">
-        <v>448</v>
+        <v>486</v>
       </c>
       <c r="B98" s="22" t="n">
         <f aca="false">B97*B89</f>
@@ -14877,7 +18795,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="20" t="s">
-        <v>449</v>
+        <v>487</v>
       </c>
       <c r="B99" s="17" t="n">
         <f aca="false">B98*B90</f>
@@ -14904,7 +18822,7 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="20" t="s">
-        <v>361</v>
+        <v>399</v>
       </c>
       <c r="B100" s="17" t="n">
         <f aca="false">B92*Assumptions!$B$30*Assumptions!$B$33</f>
@@ -14931,7 +18849,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="18" t="s">
-        <v>217</v>
+        <v>255</v>
       </c>
       <c r="B101" s="24" t="n">
         <f aca="false">B99+B100</f>
@@ -14958,7 +18876,7 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="20" t="s">
-        <v>450</v>
+        <v>488</v>
       </c>
       <c r="B102" s="17" t="n">
         <f aca="false">B88*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(B1)-2)</f>
@@ -14985,7 +18903,7 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="20" t="s">
-        <v>451</v>
+        <v>489</v>
       </c>
       <c r="B103" s="17" t="n">
         <f aca="false">B99*Assumptions!$B$22+B92*Assumptions!$B$33*Assumptions!$B$37</f>
@@ -15012,7 +18930,7 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="18" t="s">
-        <v>224</v>
+        <v>262</v>
       </c>
       <c r="B104" s="24" t="n">
         <f aca="false">B101-B102-B103</f>
@@ -15039,7 +18957,7 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="20" t="s">
-        <v>265</v>
+        <v>303</v>
       </c>
       <c r="B105" s="23" t="n">
         <f aca="false">IF(B101=0,0,B104/B101)</f>
@@ -15066,7 +18984,7 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="20" t="s">
-        <v>452</v>
+        <v>490</v>
       </c>
       <c r="B106" s="17" t="n">
         <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+B88*B94+B95+B101*B93+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,B88-1)</f>
@@ -15090,12 +19008,12 @@
       </c>
       <c r="G106" s="3"/>
       <c r="H106" s="8" t="s">
-        <v>453</v>
+        <v>491</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="18" t="s">
-        <v>454</v>
+        <v>492</v>
       </c>
       <c r="B107" s="24" t="n">
         <f aca="false">B104-B106</f>
@@ -15122,7 +19040,7 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="20" t="s">
-        <v>455</v>
+        <v>493</v>
       </c>
       <c r="B108" s="11" t="n">
         <v>60000</v>
@@ -15141,12 +19059,12 @@
       </c>
       <c r="G108" s="3"/>
       <c r="H108" s="8" t="s">
-        <v>456</v>
+        <v>494</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="20" t="s">
-        <v>457</v>
+        <v>495</v>
       </c>
       <c r="B109" s="14" t="n">
         <v>0.1</v>
@@ -15165,12 +19083,12 @@
       </c>
       <c r="G109" s="3"/>
       <c r="H109" s="8" t="s">
-        <v>458</v>
+        <v>496</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="20" t="s">
-        <v>459</v>
+        <v>497</v>
       </c>
       <c r="B110" s="17" t="n">
         <f aca="false">B108+IF(B108=0,0,B109*MAX(0,B107-MAX(0,'5-year plan'!$B$44)))</f>
@@ -15197,7 +19115,7 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="18" t="s">
-        <v>460</v>
+        <v>498</v>
       </c>
       <c r="B111" s="24" t="n">
         <f aca="false">B107-B110</f>
@@ -15224,7 +19142,7 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="20" t="s">
-        <v>461</v>
+        <v>499</v>
       </c>
       <c r="B112" s="23" t="n">
         <f aca="false">IF(B101=0,0,B111/B101)</f>
@@ -15251,7 +19169,7 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="20" t="s">
-        <v>462</v>
+        <v>500</v>
       </c>
       <c r="B113" s="17" t="n">
         <f aca="false">MAX(0,B88-1)*'Equipment plan'!$G$10</f>
@@ -15278,7 +19196,7 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="18" t="s">
-        <v>463</v>
+        <v>501</v>
       </c>
       <c r="B114" s="24" t="n">
         <f aca="false">Assumptions!$B$62+B111-B113</f>
@@ -15302,12 +19220,12 @@
       </c>
       <c r="G114" s="3"/>
       <c r="H114" s="8" t="s">
-        <v>464</v>
+        <v>502</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="20" t="s">
-        <v>465</v>
+        <v>503</v>
       </c>
       <c r="B115" s="17" t="n">
         <f aca="false">B111+Assumptions!$B$78*12</f>
@@ -15334,7 +19252,7 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="20" t="s">
-        <v>466</v>
+        <v>504</v>
       </c>
       <c r="B116" s="17" t="n">
         <f aca="false">MAX(0,B115)*2.46</f>
@@ -15358,7 +19276,7 @@
       </c>
       <c r="G116" s="3"/>
       <c r="H116" s="8" t="s">
-        <v>467</v>
+        <v>505</v>
       </c>
     </row>
   </sheetData>
@@ -15388,7 +19306,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>472</v>
+        <v>510</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -15410,7 +19328,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>473</v>
+        <v>511</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -15452,7 +19370,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>474</v>
+        <v>512</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -15474,25 +19392,25 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>475</v>
+        <v>513</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="8" t="s">
-        <v>476</v>
+        <v>514</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="8" t="s">
-        <v>477</v>
+        <v>515</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="8" t="s">
-        <v>478</v>
+        <v>516</v>
       </c>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
@@ -15534,25 +19452,25 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>479</v>
+        <v>517</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="8" t="s">
-        <v>480</v>
+        <v>518</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="8" t="s">
-        <v>481</v>
+        <v>519</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="8" t="s">
-        <v>482</v>
+        <v>520</v>
       </c>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
@@ -15594,25 +19512,25 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>483</v>
+        <v>521</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="8" t="s">
-        <v>484</v>
+        <v>522</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="8" t="s">
-        <v>485</v>
+        <v>523</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="8" t="s">
-        <v>486</v>
+        <v>524</v>
       </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
@@ -15630,7 +19548,7 @@
       <c r="D10" s="3"/>
       <c r="E10" s="46" t="n">
         <f aca="false">INDEX(B54:P54,Assumptions!$B$39)</f>
-        <v>6020157.22478942</v>
+        <v>5745966.08489174</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
@@ -15644,7 +19562,7 @@
       <c r="L10" s="3"/>
       <c r="M10" s="46" t="n">
         <f aca="false">INDEX(B56:P56,Assumptions!$B$39)</f>
-        <v>1624683.92455597</v>
+        <v>1350492.78465828</v>
       </c>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
@@ -15674,7 +19592,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="40" t="s">
-        <v>487</v>
+        <v>525</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -15736,7 +19654,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>488</v>
+        <v>526</v>
       </c>
       <c r="B15" s="19" t="n">
         <v>1</v>
@@ -15785,12 +19703,12 @@
       </c>
       <c r="Q15" s="3"/>
       <c r="R15" s="18" t="s">
-        <v>347</v>
+        <v>385</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>489</v>
+        <v>527</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -15812,7 +19730,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>476</v>
+        <v>514</v>
       </c>
       <c r="B17" s="16" t="n">
         <f aca="false">'5-year plan'!C7</f>
@@ -15876,12 +19794,12 @@
       </c>
       <c r="Q17" s="3"/>
       <c r="R17" s="8" t="s">
-        <v>490</v>
+        <v>528</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>438</v>
+        <v>476</v>
       </c>
       <c r="B18" s="21" t="n">
         <f aca="false">Assumptions!$B$11</f>
@@ -15945,12 +19863,12 @@
       </c>
       <c r="Q18" s="3"/>
       <c r="R18" s="8" t="s">
-        <v>491</v>
+        <v>529</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>447</v>
+        <v>485</v>
       </c>
       <c r="B19" s="21" t="n">
         <f aca="false">B17*Assumptions!$B$10*12</f>
@@ -16017,7 +19935,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="18" t="s">
-        <v>448</v>
+        <v>486</v>
       </c>
       <c r="B20" s="22" t="n">
         <f aca="false">B19*B18</f>
@@ -16084,7 +20002,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="42" t="s">
-        <v>492</v>
+        <v>530</v>
       </c>
       <c r="B21" s="43"/>
       <c r="C21" s="43"/>
@@ -16106,7 +20024,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="20" t="s">
-        <v>493</v>
+        <v>531</v>
       </c>
       <c r="B22" s="21" t="n">
         <f aca="false">ROUND(B17*Assumptions!$B$26,0)</f>
@@ -16173,7 +20091,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="20" t="s">
-        <v>494</v>
+        <v>532</v>
       </c>
       <c r="B23" s="21" t="n">
         <f aca="false">IF(B17&gt;=2,ROUNDUP(B17/Assumptions!$B$51,0),0)</f>
@@ -16240,7 +20158,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="20" t="s">
-        <v>495</v>
+        <v>533</v>
       </c>
       <c r="B24" s="21" t="n">
         <f aca="false">IF(B17&gt;=3,ROUNDUP(B17/Assumptions!$B$52,0),0)</f>
@@ -16307,7 +20225,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>496</v>
+        <v>534</v>
       </c>
       <c r="B25" s="21" t="n">
         <f aca="false">IF(B17&gt;=4,ROUNDUP(B17/Assumptions!$B$53,0),0)</f>
@@ -16374,7 +20292,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="42" t="s">
-        <v>210</v>
+        <v>248</v>
       </c>
       <c r="B26" s="43"/>
       <c r="C26" s="43"/>
@@ -16396,7 +20314,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>301</v>
+        <v>339</v>
       </c>
       <c r="B27" s="17" t="n">
         <f aca="false">Assumptions!$B$5</f>
@@ -16463,7 +20381,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="20" t="s">
-        <v>449</v>
+        <v>487</v>
       </c>
       <c r="B28" s="17" t="n">
         <f aca="false">B20*B27</f>
@@ -16530,7 +20448,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="20" t="s">
-        <v>497</v>
+        <v>535</v>
       </c>
       <c r="B29" s="21" t="n">
         <f aca="false">B20/Assumptions!$B$17</f>
@@ -16597,7 +20515,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="20" t="s">
-        <v>498</v>
+        <v>536</v>
       </c>
       <c r="B30" s="21" t="n">
         <f aca="false">B29*Assumptions!$B$31</f>
@@ -16664,7 +20582,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="18" t="s">
-        <v>499</v>
+        <v>537</v>
       </c>
       <c r="B31" s="22" t="n">
         <f aca="false">B30</f>
@@ -16728,12 +20646,12 @@
       </c>
       <c r="Q31" s="3"/>
       <c r="R31" s="8" t="s">
-        <v>500</v>
+        <v>538</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>275</v>
+        <v>313</v>
       </c>
       <c r="B32" s="17" t="n">
         <f aca="false">Assumptions!$B$30</f>
@@ -16800,7 +20718,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>501</v>
+        <v>539</v>
       </c>
       <c r="B33" s="21" t="n">
         <f aca="false">ROUNDUP(B31*Assumptions!$B$33/Assumptions!$B$54,0)</f>
@@ -16864,12 +20782,12 @@
       </c>
       <c r="Q33" s="3"/>
       <c r="R33" s="8" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="18" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="B34" s="22" t="n">
         <f aca="false">1+B22+B23+B24+B25+B33</f>
@@ -16936,7 +20854,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="20" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="B35" s="17" t="n">
         <f aca="false">B31*Assumptions!$B$33*B32</f>
@@ -17003,7 +20921,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="18" t="s">
-        <v>217</v>
+        <v>255</v>
       </c>
       <c r="B36" s="24" t="n">
         <f aca="false">B28+B35</f>
@@ -17070,7 +20988,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="42" t="s">
-        <v>505</v>
+        <v>543</v>
       </c>
       <c r="B37" s="43"/>
       <c r="C37" s="43"/>
@@ -17092,7 +21010,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="20" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="B38" s="17" t="n">
         <f aca="false">B17*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12</f>
@@ -17159,7 +21077,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="20" t="s">
-        <v>451</v>
+        <v>489</v>
       </c>
       <c r="B39" s="17" t="n">
         <f aca="false">B28*Assumptions!$B$22+B31*Assumptions!$B$33*Assumptions!$B$37</f>
@@ -17226,7 +21144,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="18" t="s">
-        <v>224</v>
+        <v>262</v>
       </c>
       <c r="B40" s="24" t="n">
         <f aca="false">B36-B38-B39</f>
@@ -17293,7 +21211,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="20" t="s">
-        <v>507</v>
+        <v>545</v>
       </c>
       <c r="B41" s="17" t="n">
         <f aca="false">(B23*Assumptions!$B$55+B24*Assumptions!$B$56+B25*Assumptions!$B$57)</f>
@@ -17360,7 +21278,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="20" t="s">
-        <v>508</v>
+        <v>546</v>
       </c>
       <c r="B42" s="17" t="n">
         <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+B17*22000+B36*0.05+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,B17-1)</f>
@@ -17424,12 +21342,12 @@
       </c>
       <c r="Q42" s="3"/>
       <c r="R42" s="8" t="s">
-        <v>509</v>
+        <v>547</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="18" t="s">
-        <v>510</v>
+        <v>548</v>
       </c>
       <c r="B43" s="24" t="n">
         <f aca="false">B40-B41-B42</f>
@@ -17496,7 +21414,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>511</v>
+        <v>549</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -17518,7 +21436,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="20" t="s">
-        <v>512</v>
+        <v>550</v>
       </c>
       <c r="B45" s="17" t="n">
         <f aca="false">MAX(0,B17-1)*'Equipment plan'!$B$10</f>
@@ -17585,7 +21503,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="20" t="s">
-        <v>513</v>
+        <v>551</v>
       </c>
       <c r="B46" s="17" t="n">
         <f aca="false">Assumptions!$B$45+B45</f>
@@ -17652,7 +21570,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="20" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="B47" s="17" t="n">
         <f aca="false">B46*(1-1/Assumptions!$B$46)</f>
@@ -17716,12 +21634,12 @@
       </c>
       <c r="Q47" s="3"/>
       <c r="R47" s="8" t="s">
-        <v>515</v>
+        <v>553</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="20" t="s">
-        <v>516</v>
+        <v>554</v>
       </c>
       <c r="B48" s="17" t="n">
         <f aca="false">MAX(0,B45*0.8*0.85)</f>
@@ -17785,12 +21703,12 @@
       </c>
       <c r="Q48" s="3"/>
       <c r="R48" s="8" t="s">
-        <v>517</v>
+        <v>555</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="20" t="s">
-        <v>518</v>
+        <v>556</v>
       </c>
       <c r="B49" s="17" t="n">
         <f aca="false">MAX(0,B43)*Assumptions!$B$44</f>
@@ -17854,12 +21772,12 @@
       </c>
       <c r="Q49" s="3"/>
       <c r="R49" s="8" t="s">
-        <v>519</v>
+        <v>557</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="18" t="s">
-        <v>520</v>
+        <v>558</v>
       </c>
       <c r="B50" s="24" t="n">
         <f aca="false">B49</f>
@@ -17923,12 +21841,12 @@
       </c>
       <c r="Q50" s="3"/>
       <c r="R50" s="8" t="s">
-        <v>521</v>
+        <v>559</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="18" t="s">
-        <v>522</v>
+        <v>560</v>
       </c>
       <c r="B51" s="24" t="n">
         <f aca="false">Assumptions!$B$62+B43-B49-B45*0.2</f>
@@ -17992,12 +21910,12 @@
       </c>
       <c r="Q51" s="3"/>
       <c r="R51" s="8" t="s">
-        <v>523</v>
+        <v>561</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="20" t="s">
-        <v>524</v>
+        <v>562</v>
       </c>
       <c r="B52" s="17" t="n">
         <f aca="false">B43+Assumptions!$B$78*12</f>
@@ -18064,7 +21982,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="20" t="s">
-        <v>525</v>
+        <v>563</v>
       </c>
       <c r="B53" s="17" t="n">
         <f aca="false">B52-B35+B31*Assumptions!$B$33*Assumptions!$B$37</f>
@@ -18128,81 +22046,81 @@
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="8" t="s">
-        <v>526</v>
+        <v>564</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="18" t="s">
-        <v>527</v>
+        <v>565</v>
       </c>
       <c r="B54" s="24" t="n">
         <f aca="false">MAX(0,B52)*Assumptions!$B$47+B51-B48</f>
-        <v>848172.826582223</v>
+        <v>785343.611964015</v>
       </c>
       <c r="C54" s="24" t="n">
         <f aca="false">MAX(0,C52)*Assumptions!$B$47+C51-C48</f>
-        <v>983866.464013039</v>
+        <v>920050.784350031</v>
       </c>
       <c r="D54" s="24" t="n">
         <f aca="false">MAX(0,D52)*Assumptions!$B$47+D51-D48</f>
-        <v>1273641.08675493</v>
+        <v>1194714.14816187</v>
       </c>
       <c r="E54" s="24" t="n">
         <f aca="false">MAX(0,E52)*Assumptions!$B$47+E51-E48</f>
-        <v>1805913.17492169</v>
+        <v>1694722.90416859</v>
       </c>
       <c r="F54" s="24" t="n">
         <f aca="false">MAX(0,F52)*Assumptions!$B$47+F51-F48</f>
-        <v>2106406.18341251</v>
+        <v>1987116.23232975</v>
       </c>
       <c r="G54" s="24" t="n">
         <f aca="false">MAX(0,G52)*Assumptions!$B$47+G51-G48</f>
-        <v>2453200.72049738</v>
+        <v>2323946.1520912</v>
       </c>
       <c r="H54" s="24" t="n">
         <f aca="false">MAX(0,H52)*Assumptions!$B$47+H51-H48</f>
-        <v>3235902.04643527</v>
+        <v>3069903.45291162</v>
       </c>
       <c r="I54" s="24" t="n">
         <f aca="false">MAX(0,I52)*Assumptions!$B$47+I51-I48</f>
-        <v>4137684.20197118</v>
+        <v>3932043.50401945</v>
       </c>
       <c r="J54" s="24" t="n">
         <f aca="false">MAX(0,J52)*Assumptions!$B$47+J51-J48</f>
-        <v>5166083.09692846</v>
+        <v>4917779.1256436</v>
       </c>
       <c r="K54" s="24" t="n">
         <f aca="false">MAX(0,K52)*Assumptions!$B$47+K51-K48</f>
-        <v>6020157.22478942</v>
+        <v>5745966.08489174</v>
       </c>
       <c r="L54" s="24" t="n">
         <f aca="false">MAX(0,L52)*Assumptions!$B$47+L51-L48</f>
-        <v>7305752.34835174</v>
+        <v>6981192.56071712</v>
       </c>
       <c r="M54" s="24" t="n">
         <f aca="false">MAX(0,M52)*Assumptions!$B$47+M51-M48</f>
-        <v>8745294.29428168</v>
+        <v>8366946.71517755</v>
       </c>
       <c r="N54" s="24" t="n">
         <f aca="false">MAX(0,N52)*Assumptions!$B$47+N51-N48</f>
-        <v>10347784.2141334</v>
+        <v>9912086.72796597</v>
       </c>
       <c r="O54" s="24" t="n">
         <f aca="false">MAX(0,O52)*Assumptions!$B$47+O51-O48</f>
-        <v>11722008.1632004</v>
+        <v>11255026.9302516</v>
       </c>
       <c r="P54" s="24" t="n">
         <f aca="false">MAX(0,P52)*Assumptions!$B$47+P51-P48</f>
-        <v>13155112.6242932</v>
+        <v>12656331.7901201</v>
       </c>
       <c r="Q54" s="3"/>
       <c r="R54" s="8" t="s">
-        <v>528</v>
+        <v>566</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="18" t="s">
-        <v>529</v>
+        <v>567</v>
       </c>
       <c r="B55" s="24" t="n">
         <f aca="false">MAX(0,B53)*Assumptions!$B$48+B51-B48</f>
@@ -18269,76 +22187,76 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="18" t="s">
-        <v>530</v>
+        <v>568</v>
       </c>
       <c r="B56" s="24" t="n">
         <f aca="false">B54-B55</f>
-        <v>225146.915454624</v>
+        <v>162317.700836416</v>
       </c>
       <c r="C56" s="24" t="n">
         <f aca="false">C54-C55</f>
-        <v>261832.840461024</v>
+        <v>198017.160798016</v>
       </c>
       <c r="D56" s="24" t="n">
         <f aca="false">D54-D55</f>
-        <v>351974.509284837</v>
+        <v>273047.570691772</v>
       </c>
       <c r="E56" s="24" t="n">
         <f aca="false">E54-E55</f>
-        <v>513510.417758248</v>
+        <v>402320.147005142</v>
       </c>
       <c r="F56" s="24" t="n">
         <f aca="false">F54-F55</f>
-        <v>612946.910267343</v>
+        <v>493656.959184586</v>
       </c>
       <c r="G56" s="24" t="n">
         <f aca="false">G54-G55</f>
-        <v>728797.467322062</v>
+        <v>599542.898915879</v>
       </c>
       <c r="H56" s="24" t="n">
         <f aca="false">H54-H55</f>
-        <v>936246.880060556</v>
+        <v>770248.286536899</v>
       </c>
       <c r="I56" s="24" t="n">
         <f aca="false">I54-I55</f>
-        <v>1164107.39911487</v>
+        <v>958466.701163144</v>
       </c>
       <c r="J56" s="24" t="n">
         <f aca="false">J54-J55</f>
-        <v>1413220.54937234</v>
+        <v>1164916.57808747</v>
       </c>
       <c r="K56" s="24" t="n">
         <f aca="false">K54-K55</f>
-        <v>1624683.92455597</v>
+        <v>1350492.78465828</v>
       </c>
       <c r="L56" s="24" t="n">
         <f aca="false">L54-L55</f>
-        <v>1922777.96893435</v>
+        <v>1598218.18129973</v>
       </c>
       <c r="M56" s="24" t="n">
         <f aca="false">M54-M55</f>
-        <v>2244842.75302125</v>
+        <v>1866495.17391712</v>
       </c>
       <c r="N56" s="24" t="n">
         <f aca="false">N54-N55</f>
-        <v>2591854.74971893</v>
+        <v>2156157.26355151</v>
       </c>
       <c r="O56" s="24" t="n">
         <f aca="false">O54-O55</f>
-        <v>2860905.49237857</v>
+        <v>2393924.25942985</v>
       </c>
       <c r="P56" s="24" t="n">
         <f aca="false">P54-P55</f>
-        <v>3131907.95484385</v>
+        <v>2633127.12067067</v>
       </c>
       <c r="Q56" s="3"/>
       <c r="R56" s="8" t="s">
-        <v>531</v>
+        <v>569</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="20" t="s">
-        <v>532</v>
+        <v>570</v>
       </c>
       <c r="B57" s="17" t="n">
         <f aca="false">B35*Assumptions!$B$49</f>
@@ -18420,129 +22338,543 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="90"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="78"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>533</v>
+        <v>571</v>
       </c>
       <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3"/>
+      <c r="A2" s="4" t="s">
+        <v>572</v>
+      </c>
       <c r="B2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="47" t="s">
-        <v>534</v>
-      </c>
-      <c r="B3" s="48" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="47" t="s">
-        <v>536</v>
-      </c>
-      <c r="B4" s="48" t="s">
-        <v>537</v>
-      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="18" t="s">
+        <v>573</v>
+      </c>
+      <c r="B4" s="46" t="n">
+        <f aca="false">Assumptions!$B$110</f>
+        <v>150000</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="40" t="s">
+        <v>574</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="47" t="s">
-        <v>538</v>
-      </c>
-      <c r="B5" s="48" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="47" t="s">
-        <v>540</v>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="47" t="s">
+        <v>575</v>
+      </c>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
+    </row>
+    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="48" t="s">
+        <v>576</v>
       </c>
       <c r="B6" s="48" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="47" t="s">
-        <v>542</v>
-      </c>
-      <c r="B7" s="48" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="47" t="s">
-        <v>544</v>
-      </c>
-      <c r="B8" s="48" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="47" t="s">
-        <v>546</v>
-      </c>
-      <c r="B9" s="48" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="47" t="s">
-        <v>548</v>
-      </c>
-      <c r="B10" s="48" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="47" t="s">
-        <v>550</v>
-      </c>
-      <c r="B11" s="48" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="47" t="s">
-        <v>552</v>
-      </c>
-      <c r="B12" s="48" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="47" t="s">
-        <v>554</v>
-      </c>
-      <c r="B13" s="48" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="47" t="s">
-        <v>556</v>
-      </c>
-      <c r="B14" s="48" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="47" t="s">
-        <v>558</v>
-      </c>
-      <c r="B15" s="48" t="s">
-        <v>559</v>
-      </c>
+        <v>577</v>
+      </c>
+      <c r="C6" s="48" t="s">
+        <v>578</v>
+      </c>
+      <c r="D6" s="48" t="s">
+        <v>579</v>
+      </c>
+      <c r="E6" s="48" t="s">
+        <v>580</v>
+      </c>
+      <c r="F6" s="48" t="s">
+        <v>581</v>
+      </c>
+      <c r="G6" s="48" t="s">
+        <v>582</v>
+      </c>
+      <c r="H6" s="48" t="s">
+        <v>583</v>
+      </c>
+      <c r="I6" s="48" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="20" t="s">
+        <v>585</v>
+      </c>
+      <c r="B7" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D7" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="50" t="n">
+        <f aca="false">IF(B7=0,$B$4/(C7*12),PMT(B7/12,C7*12,-$B$4))</f>
+        <v>25000</v>
+      </c>
+      <c r="F7" s="50" t="n">
+        <f aca="false">E7*C7*12+$B$4*D7</f>
+        <v>150000</v>
+      </c>
+      <c r="G7" s="50" t="n">
+        <f aca="false">F7-$B$4</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="24" t="n">
+        <f aca="false">G7/C7</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="51" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="20" t="s">
+        <v>587</v>
+      </c>
+      <c r="B8" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="50" t="n">
+        <f aca="false">IF(B8=0,$B$4/(C8*12),PMT(B8/12,C8*12,-$B$4))</f>
+        <v>3125</v>
+      </c>
+      <c r="F8" s="50" t="n">
+        <f aca="false">E8*C8*12+$B$4*D8</f>
+        <v>150000</v>
+      </c>
+      <c r="G8" s="50" t="n">
+        <f aca="false">F8-$B$4</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="24" t="n">
+        <f aca="false">G8/C8</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="51" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="20" t="s">
+        <v>589</v>
+      </c>
+      <c r="B9" s="49" t="n">
+        <v>0.085</v>
+      </c>
+      <c r="C9" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="50" t="n">
+        <f aca="false">IF(B9=0,$B$4/(C9*12),PMT(B9/12,C9*12,-$B$4))</f>
+        <v>3077.47969905769</v>
+      </c>
+      <c r="F9" s="50" t="n">
+        <f aca="false">E9*C9*12+$B$4*D9</f>
+        <v>184648.781943461</v>
+      </c>
+      <c r="G9" s="50" t="n">
+        <f aca="false">F9-$B$4</f>
+        <v>34648.7819434613</v>
+      </c>
+      <c r="H9" s="24" t="n">
+        <f aca="false">G9/C9</f>
+        <v>6929.75638869225</v>
+      </c>
+      <c r="I9" s="51" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="20" t="s">
+        <v>591</v>
+      </c>
+      <c r="B10" s="49" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="C10" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" s="49" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E10" s="50" t="n">
+        <f aca="false">IF(B10=0,$B$4/(C10*12),PMT(B10/12,C10*12,-$B$4))</f>
+        <v>1940.96336341166</v>
+      </c>
+      <c r="F10" s="50" t="n">
+        <f aca="false">E10*C10*12+$B$4*D10</f>
+        <v>234415.603609399</v>
+      </c>
+      <c r="G10" s="50" t="n">
+        <f aca="false">F10-$B$4</f>
+        <v>84415.6036093987</v>
+      </c>
+      <c r="H10" s="24" t="n">
+        <f aca="false">G10/C10</f>
+        <v>8441.56036093986</v>
+      </c>
+      <c r="I10" s="51" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20" t="s">
+        <v>593</v>
+      </c>
+      <c r="B11" s="49" t="n">
+        <v>0.1275</v>
+      </c>
+      <c r="C11" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" s="49" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E11" s="50" t="n">
+        <f aca="false">IF(B11=0,$B$4/(C11*12),PMT(B11/12,C11*12,-$B$4))</f>
+        <v>2217.59712870933</v>
+      </c>
+      <c r="F11" s="50" t="n">
+        <f aca="false">E11*C11*12+$B$4*D11</f>
+        <v>269111.65544512</v>
+      </c>
+      <c r="G11" s="50" t="n">
+        <f aca="false">F11-$B$4</f>
+        <v>119111.65544512</v>
+      </c>
+      <c r="H11" s="24" t="n">
+        <f aca="false">G11/C11</f>
+        <v>11911.165544512</v>
+      </c>
+      <c r="I11" s="51" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="s">
+        <v>595</v>
+      </c>
+      <c r="B12" s="49" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="C12" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" s="49" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E12" s="50" t="n">
+        <f aca="false">IF(B12=0,$B$4/(C12*12),PMT(B12/12,C12*12,-$B$4))</f>
+        <v>2568.36546523481</v>
+      </c>
+      <c r="F12" s="50" t="n">
+        <f aca="false">E12*C12*12+$B$4*D12</f>
+        <v>217242.699079724</v>
+      </c>
+      <c r="G12" s="50" t="n">
+        <f aca="false">F12-$B$4</f>
+        <v>67242.6990797244</v>
+      </c>
+      <c r="H12" s="24" t="n">
+        <f aca="false">G12/C12</f>
+        <v>9606.09986853206</v>
+      </c>
+      <c r="I12" s="51" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="20" t="s">
+        <v>597</v>
+      </c>
+      <c r="B13" s="49" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="C13" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="50" t="n">
+        <f aca="false">IF(B13=0,$B$4/(C13*12),PMT(B13/12,C13*12,-$B$4))</f>
+        <v>4910.80756755031</v>
+      </c>
+      <c r="F13" s="50" t="n">
+        <f aca="false">E13*C13*12+$B$4*D13</f>
+        <v>176789.072431811</v>
+      </c>
+      <c r="G13" s="50" t="n">
+        <f aca="false">F13-$B$4</f>
+        <v>26789.072431811</v>
+      </c>
+      <c r="H13" s="24" t="n">
+        <f aca="false">G13/C13</f>
+        <v>8929.69081060367</v>
+      </c>
+      <c r="I13" s="51" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="52" t="s">
+        <v>599</v>
+      </c>
+      <c r="B14" s="53" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="C14" s="54" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D14" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="55" t="n">
+        <f aca="false">IF(B14=0,$B$4/(C14*12),PMT(B14/12,C14*12,-$B$4))</f>
+        <v>23022.9705207633</v>
+      </c>
+      <c r="F14" s="55" t="n">
+        <f aca="false">E14*C14*12+$B$4*D14</f>
+        <v>207206.73468687</v>
+      </c>
+      <c r="G14" s="55" t="n">
+        <f aca="false">F14-$B$4</f>
+        <v>57206.7346868697</v>
+      </c>
+      <c r="H14" s="56" t="n">
+        <f aca="false">G14/C14</f>
+        <v>76275.6462491595</v>
+      </c>
+      <c r="I14" s="51" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+    </row>
+    <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="57" t="s">
+        <v>602</v>
+      </c>
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
+    </row>
+    <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="57" t="s">
+        <v>603</v>
+      </c>
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="57"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="57"/>
+    </row>
+    <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="57" t="s">
+        <v>604</v>
+      </c>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+    </row>
+    <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="57" t="s">
+        <v>605</v>
+      </c>
+      <c r="B20" s="57"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="57"/>
+    </row>
+    <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="57" t="s">
+        <v>606</v>
+      </c>
+      <c r="B21" s="57"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="57"/>
+      <c r="H21" s="57"/>
+      <c r="I21" s="57"/>
+    </row>
+    <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="57" t="s">
+        <v>607</v>
+      </c>
+      <c r="B22" s="57"/>
+      <c r="C22" s="57"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="57"/>
+      <c r="H22" s="57"/>
+      <c r="I22" s="57"/>
+    </row>
+    <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="57" t="s">
+        <v>608</v>
+      </c>
+      <c r="B23" s="57"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="57"/>
+      <c r="I23" s="57"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+    </row>
+    <row r="26" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="58" t="s">
+        <v>610</v>
+      </c>
+      <c r="B26" s="58"/>
+      <c r="C26" s="58"/>
+      <c r="D26" s="58"/>
+      <c r="E26" s="58"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="58"/>
+      <c r="I26" s="58"/>
     </row>
   </sheetData>
   <sheetProtection sheet="true" password="ef11" formatCells="false" formatColumns="false" formatRows="false"/>
+  <mergeCells count="9">
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A26:I26"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/docs/Scag-Scapes-Proforma.xlsx
+++ b/docs/Scag-Scapes-Proforma.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="963">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="964">
   <si>
     <t xml:space="preserve">Scag Scapes LLC - Growth Proforma - Assumptions</t>
   </si>
@@ -1519,7 +1519,10 @@
     <t xml:space="preserve">OVERHEAD - the layers that let the company handle the volume</t>
   </si>
   <si>
-    <t xml:space="preserve">Charlie's pay rises with the company. Before write-offs - see the Write-offs and taxes tab for what this actually costs him after deductions.</t>
+    <t xml:space="preserve">Owner draw (years 3-5 step up with the company, proportional to the year-1 draw)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charlie's pay rises with the company - change the Owner draw cell on Assumptions and all six years move together, in the same proportion. Before write-offs - see the Write-offs and taxes tab for what this actually costs him after deductions.</t>
   </si>
   <si>
     <t xml:space="preserve">Office admin / bookkeeper (part-time year 2, full-time year 3)</t>
@@ -1600,13 +1603,13 @@
     <t xml:space="preserve">Base ($/yr) - fractional, about 25 hours a week</t>
   </si>
   <si>
-    <t xml:space="preserve">For scale: Baton Rouge general/operations managers average $129,840 full-time (BLS OEWS). Set to 0 to see the plan without it.</t>
+    <t xml:space="preserve">Pulled straight from the Ned assumptions above - change those cells and this tab and the Ned proforma tab move together. For scale: Baton Rouge general/operations managers average $129,840 full-time (BLS OEWS).</t>
   </si>
   <si>
     <t xml:space="preserve">Growth share - % of operating profit above the baseline year</t>
   </si>
   <si>
-    <t xml:space="preserve">Paid only on profit above what the business makes today; nothing on the baseline.</t>
+    <t xml:space="preserve">Paid only on profit above what the business makes today; nothing on the baseline. Same cell as the Ned proforma tab.</t>
   </si>
   <si>
     <t xml:space="preserve">Baseline operating profit (today's run rate after owner draw, floored at 0)</t>
@@ -3126,7 +3129,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3278,6 +3281,10 @@
     <xf numFmtId="169" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="true"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="170" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -5514,7 +5521,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5536,7 +5543,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5578,7 +5585,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -5600,25 +5607,25 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="7" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="7" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="7" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -5627,28 +5634,28 @@
       <c r="R5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="43" t="n">
+      <c r="A6" s="44" t="n">
         <f aca="false">Assumptions!$B$39</f>
         <v>10</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
-      <c r="E6" s="45" t="n">
+      <c r="E6" s="46" t="n">
         <f aca="false">INDEX(B16:P16,Assumptions!$B$39)</f>
         <v>4551505.48237858</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="45" t="n">
+      <c r="I6" s="46" t="n">
         <f aca="false">INDEX(B21:P21,Assumptions!$B$39)</f>
         <v>910301.096475715</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
-      <c r="M6" s="45" t="n">
+      <c r="M6" s="46" t="n">
         <f aca="false">INDEX(B22:P22,Assumptions!$B$39)</f>
         <v>3641204.38590286</v>
       </c>
@@ -5660,25 +5667,25 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="7" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="7" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="7" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -5687,28 +5694,28 @@
       <c r="R7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="45" t="n">
+      <c r="A8" s="46" t="n">
         <f aca="false">INDEX(B24:P24,Assumptions!$B$39)</f>
         <v>30000</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="45" t="n">
+      <c r="E8" s="46" t="n">
         <f aca="false">INDEX(B25:P25,Assumptions!$B$39)</f>
         <v>240975</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
-      <c r="I8" s="45" t="n">
+      <c r="I8" s="46" t="n">
         <f aca="false">INDEX(B26:P26,Assumptions!$B$39)</f>
         <v>4280530.48237858</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
-      <c r="M8" s="45" t="n">
+      <c r="M8" s="46" t="n">
         <f aca="false">INDEX(B28:P28,Assumptions!$B$39)</f>
         <v>639326.096475715</v>
       </c>
@@ -5739,8 +5746,8 @@
       <c r="R9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="39" t="s">
-        <v>727</v>
+      <c r="A10" s="40" t="s">
+        <v>728</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -5802,7 +5809,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B13" s="18" t="n">
         <v>1</v>
@@ -5856,7 +5863,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -5878,7 +5885,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B15" s="16" t="n">
         <f aca="false">'Long range 15-yr'!B36</f>
@@ -5945,7 +5952,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B16" s="23" t="n">
         <f aca="false">'Buyout &amp; exit'!B23</f>
@@ -6011,30 +6018,30 @@
       <c r="R16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="41" t="s">
-        <v>731</v>
-      </c>
-      <c r="B17" s="42"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="42"/>
-      <c r="K17" s="42"/>
-      <c r="L17" s="42"/>
-      <c r="M17" s="42"/>
-      <c r="N17" s="42"/>
-      <c r="O17" s="42"/>
-      <c r="P17" s="42"/>
+      <c r="A17" s="42" t="s">
+        <v>732</v>
+      </c>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="43"/>
+      <c r="L17" s="43"/>
+      <c r="M17" s="43"/>
+      <c r="N17" s="43"/>
+      <c r="O17" s="43"/>
+      <c r="P17" s="43"/>
       <c r="Q17" s="2"/>
-      <c r="R17" s="42"/>
+      <c r="R17" s="43"/>
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B18" s="16" t="n">
         <f aca="false">IF(1=Assumptions!$B$118,Assumptions!$B$116,0)</f>
@@ -6097,13 +6104,13 @@
         <v>0</v>
       </c>
       <c r="Q18" s="2"/>
-      <c r="R18" s="51" t="s">
-        <v>733</v>
+      <c r="R18" s="52" t="s">
+        <v>734</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B19" s="16" t="n">
         <f aca="false">IF(1&lt;Assumptions!$B$118,0,Assumptions!$B$116*(1+Assumptions!$B$119)^(1-Assumptions!$B$118+1))</f>
@@ -6166,13 +6173,13 @@
         <v>881158.087277298</v>
       </c>
       <c r="Q19" s="2"/>
-      <c r="R19" s="51" t="s">
-        <v>735</v>
+      <c r="R19" s="52" t="s">
+        <v>736</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B20" s="16" t="n">
         <f aca="false">IF(OR(Assumptions!$B$116=0,1&lt;Assumptions!$B$118),0,B16*Assumptions!$B$117)</f>
@@ -6239,7 +6246,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B21" s="23" t="n">
         <f aca="false">MAX(B19,B20)</f>
@@ -6306,7 +6313,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B22" s="23" t="n">
         <f aca="false">B16-B21</f>
@@ -6373,7 +6380,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -6395,7 +6402,7 @@
     </row>
     <row r="24" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B24" s="16" t="n">
         <f aca="false">IF(OR(Assumptions!$B$116=0,1&lt;Assumptions!$B$118),0,MAX(0,Assumptions!$B$116*(1-1/Assumptions!$B$112)))</f>
@@ -6458,13 +6465,13 @@
         <v>0</v>
       </c>
       <c r="Q24" s="2"/>
-      <c r="R24" s="51" t="s">
-        <v>741</v>
+      <c r="R24" s="52" t="s">
+        <v>742</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B25" s="16" t="n">
         <f aca="false">IF(OR(Assumptions!$B$116=0,1&lt;Assumptions!$B$118),0,Assumptions!$B$116*Assumptions!$B$111)</f>
@@ -6527,13 +6534,13 @@
         <v>252450</v>
       </c>
       <c r="Q25" s="2"/>
-      <c r="R25" s="51" t="s">
-        <v>743</v>
+      <c r="R25" s="52" t="s">
+        <v>744</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="17" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B26" s="23" t="n">
         <f aca="false">B16-B24-B25</f>
@@ -6596,35 +6603,35 @@
         <v>12237740.7073309</v>
       </c>
       <c r="Q26" s="2"/>
-      <c r="R26" s="51" t="s">
-        <v>745</v>
+      <c r="R26" s="52" t="s">
+        <v>746</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="41" t="s">
-        <v>746</v>
-      </c>
-      <c r="B27" s="42"/>
-      <c r="C27" s="42"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="42"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="42"/>
-      <c r="K27" s="42"/>
-      <c r="L27" s="42"/>
-      <c r="M27" s="42"/>
-      <c r="N27" s="42"/>
-      <c r="O27" s="42"/>
-      <c r="P27" s="42"/>
+      <c r="A27" s="42" t="s">
+        <v>747</v>
+      </c>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="43"/>
+      <c r="L27" s="43"/>
+      <c r="M27" s="43"/>
+      <c r="N27" s="43"/>
+      <c r="O27" s="43"/>
+      <c r="P27" s="43"/>
       <c r="Q27" s="2"/>
-      <c r="R27" s="42"/>
+      <c r="R27" s="43"/>
     </row>
     <row r="28" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="17" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B28" s="23" t="n">
         <f aca="false">B26-B22</f>
@@ -6687,13 +6694,13 @@
         <v>2245588.14146618</v>
       </c>
       <c r="Q28" s="2"/>
-      <c r="R28" s="51" t="s">
-        <v>748</v>
+      <c r="R28" s="52" t="s">
+        <v>749</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B29" s="16" t="n">
         <f aca="false">IF(Assumptions!$B$117=0,0,(B24+B25)/Assumptions!$B$117)</f>
@@ -6756,8 +6763,8 @@
         <v>1262250</v>
       </c>
       <c r="Q29" s="2"/>
-      <c r="R29" s="51" t="s">
-        <v>750</v>
+      <c r="R29" s="52" t="s">
+        <v>751</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6782,7 +6789,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -6804,7 +6811,7 @@
     </row>
     <row r="32" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="32" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B32" s="32"/>
       <c r="C32" s="32"/>
@@ -6854,7 +6861,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6876,7 +6883,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6918,7 +6925,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -6940,25 +6947,25 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="7" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="7" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="7" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -6967,28 +6974,28 @@
       <c r="R5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="43" t="n">
+      <c r="A6" s="44" t="n">
         <f aca="false">Assumptions!$B$39</f>
         <v>10</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
-      <c r="E6" s="45" t="n">
+      <c r="E6" s="46" t="n">
         <f aca="false">INDEX(B17:P17,Assumptions!$B$39)</f>
         <v>4952082.94628947</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="45" t="n">
+      <c r="I6" s="46" t="n">
         <f aca="false">INDEX(B22:P22,Assumptions!$B$39)</f>
         <v>813428.470548401</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
-      <c r="M6" s="44" t="n">
+      <c r="M6" s="45" t="n">
         <f aca="false">INDEX(B21:P21,Assumptions!$B$39)</f>
         <v>4</v>
       </c>
@@ -7000,25 +7007,25 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="7" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="7" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="7" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -7027,28 +7034,28 @@
       <c r="R7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="45" t="n">
+      <c r="A8" s="46" t="n">
         <f aca="false">INDEX(B23:P23,Assumptions!$B$39)</f>
         <v>4551505.48237858</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="45" t="n">
+      <c r="E8" s="46" t="n">
         <f aca="false">INDEX(B24:P24,Assumptions!$B$39)</f>
         <v>3459144.16660772</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
-      <c r="I8" s="45" t="n">
+      <c r="I8" s="46" t="n">
         <f aca="false">INDEX(B27:P27,Assumptions!$B$39)</f>
         <v>657225.822356787</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
-      <c r="M8" s="45" t="n">
+      <c r="M8" s="46" t="n">
         <f aca="false">INDEX(B28:P28,Assumptions!$B$39)</f>
         <v>3894279.66002179</v>
       </c>
@@ -7079,8 +7086,8 @@
       <c r="R9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="39" t="s">
-        <v>760</v>
+      <c r="A10" s="40" t="s">
+        <v>761</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -7182,7 +7189,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B15" s="18" t="n">
         <v>1</v>
@@ -7236,7 +7243,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -7258,7 +7265,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B17" s="23" t="n">
         <f aca="false">'Long range 15-yr'!B36</f>
@@ -7325,7 +7332,7 @@
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B18" s="16" t="n">
         <f aca="false">'Long range 15-yr'!B59</f>
@@ -7388,13 +7395,13 @@
         <v>1544843.49387317</v>
       </c>
       <c r="Q18" s="2"/>
-      <c r="R18" s="51" t="s">
-        <v>763</v>
+      <c r="R18" s="52" t="s">
+        <v>764</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B19" s="16" t="n">
         <f aca="false">'Long range 15-yr'!B59-Assumptions!$B$128</f>
@@ -7457,104 +7464,104 @@
         <v>1459843.49387317</v>
       </c>
       <c r="Q19" s="2"/>
-      <c r="R19" s="51" t="s">
-        <v>765</v>
+      <c r="R19" s="52" t="s">
+        <v>766</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="41" t="s">
-        <v>766</v>
-      </c>
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="42"/>
-      <c r="K20" s="42"/>
-      <c r="L20" s="42"/>
-      <c r="M20" s="42"/>
-      <c r="N20" s="42"/>
-      <c r="O20" s="42"/>
-      <c r="P20" s="42"/>
+      <c r="A20" s="42" t="s">
+        <v>767</v>
+      </c>
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+      <c r="L20" s="43"/>
+      <c r="M20" s="43"/>
+      <c r="N20" s="43"/>
+      <c r="O20" s="43"/>
+      <c r="P20" s="43"/>
       <c r="Q20" s="2"/>
-      <c r="R20" s="42"/>
+      <c r="R20" s="43"/>
     </row>
     <row r="21" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>767</v>
-      </c>
-      <c r="B21" s="59" t="n">
+        <v>768</v>
+      </c>
+      <c r="B21" s="60" t="n">
         <f aca="false">IF(B17&gt;=5000000,Assumptions!$B$127,IF(B17&gt;=2000000,Assumptions!$B$126,Assumptions!$B$125))</f>
         <v>2.3</v>
       </c>
-      <c r="C21" s="59" t="n">
+      <c r="C21" s="60" t="n">
         <f aca="false">IF(C17&gt;=5000000,Assumptions!$B$127,IF(C17&gt;=2000000,Assumptions!$B$126,Assumptions!$B$125))</f>
         <v>2.3</v>
       </c>
-      <c r="D21" s="59" t="n">
+      <c r="D21" s="60" t="n">
         <f aca="false">IF(D17&gt;=5000000,Assumptions!$B$127,IF(D17&gt;=2000000,Assumptions!$B$126,Assumptions!$B$125))</f>
         <v>2.3</v>
       </c>
-      <c r="E21" s="59" t="n">
+      <c r="E21" s="60" t="n">
         <f aca="false">IF(E17&gt;=5000000,Assumptions!$B$127,IF(E17&gt;=2000000,Assumptions!$B$126,Assumptions!$B$125))</f>
         <v>4</v>
       </c>
-      <c r="F21" s="59" t="n">
+      <c r="F21" s="60" t="n">
         <f aca="false">IF(F17&gt;=5000000,Assumptions!$B$127,IF(F17&gt;=2000000,Assumptions!$B$126,Assumptions!$B$125))</f>
         <v>4</v>
       </c>
-      <c r="G21" s="59" t="n">
+      <c r="G21" s="60" t="n">
         <f aca="false">IF(G17&gt;=5000000,Assumptions!$B$127,IF(G17&gt;=2000000,Assumptions!$B$126,Assumptions!$B$125))</f>
         <v>4</v>
       </c>
-      <c r="H21" s="59" t="n">
+      <c r="H21" s="60" t="n">
         <f aca="false">IF(H17&gt;=5000000,Assumptions!$B$127,IF(H17&gt;=2000000,Assumptions!$B$126,Assumptions!$B$125))</f>
         <v>4</v>
       </c>
-      <c r="I21" s="59" t="n">
+      <c r="I21" s="60" t="n">
         <f aca="false">IF(I17&gt;=5000000,Assumptions!$B$127,IF(I17&gt;=2000000,Assumptions!$B$126,Assumptions!$B$125))</f>
         <v>4</v>
       </c>
-      <c r="J21" s="59" t="n">
+      <c r="J21" s="60" t="n">
         <f aca="false">IF(J17&gt;=5000000,Assumptions!$B$127,IF(J17&gt;=2000000,Assumptions!$B$126,Assumptions!$B$125))</f>
         <v>4</v>
       </c>
-      <c r="K21" s="59" t="n">
+      <c r="K21" s="60" t="n">
         <f aca="false">IF(K17&gt;=5000000,Assumptions!$B$127,IF(K17&gt;=2000000,Assumptions!$B$126,Assumptions!$B$125))</f>
         <v>4</v>
       </c>
-      <c r="L21" s="59" t="n">
+      <c r="L21" s="60" t="n">
         <f aca="false">IF(L17&gt;=5000000,Assumptions!$B$127,IF(L17&gt;=2000000,Assumptions!$B$126,Assumptions!$B$125))</f>
         <v>6</v>
       </c>
-      <c r="M21" s="59" t="n">
+      <c r="M21" s="60" t="n">
         <f aca="false">IF(M17&gt;=5000000,Assumptions!$B$127,IF(M17&gt;=2000000,Assumptions!$B$126,Assumptions!$B$125))</f>
         <v>6</v>
       </c>
-      <c r="N21" s="59" t="n">
+      <c r="N21" s="60" t="n">
         <f aca="false">IF(N17&gt;=5000000,Assumptions!$B$127,IF(N17&gt;=2000000,Assumptions!$B$126,Assumptions!$B$125))</f>
         <v>6</v>
       </c>
-      <c r="O21" s="59" t="n">
+      <c r="O21" s="60" t="n">
         <f aca="false">IF(O17&gt;=5000000,Assumptions!$B$127,IF(O17&gt;=2000000,Assumptions!$B$126,Assumptions!$B$125))</f>
         <v>6</v>
       </c>
-      <c r="P21" s="59" t="n">
+      <c r="P21" s="60" t="n">
         <f aca="false">IF(P17&gt;=5000000,Assumptions!$B$127,IF(P17&gt;=2000000,Assumptions!$B$126,Assumptions!$B$125))</f>
         <v>6</v>
       </c>
       <c r="Q21" s="2"/>
-      <c r="R21" s="51" t="s">
-        <v>768</v>
+      <c r="R21" s="52" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B22" s="16" t="n">
         <f aca="false">IF(B17&gt;=2000000,B19,B18)</f>
@@ -7621,7 +7628,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B23" s="23" t="n">
         <f aca="false">MAX(0,B22)*B21+'Long range 15-yr'!B58-'Long range 15-yr'!B55</f>
@@ -7684,13 +7691,13 @@
         <v>12490190.7073309</v>
       </c>
       <c r="Q23" s="2"/>
-      <c r="R23" s="51" t="s">
-        <v>771</v>
+      <c r="R23" s="52" t="s">
+        <v>772</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="17" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B24" s="23" t="n">
         <f aca="false">B23*Assumptions!$B$129</f>
@@ -7753,13 +7760,13 @@
         <v>9492544.93757147</v>
       </c>
       <c r="Q24" s="2"/>
-      <c r="R24" s="51" t="s">
-        <v>773</v>
+      <c r="R24" s="52" t="s">
+        <v>774</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -7781,7 +7788,7 @@
     </row>
     <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B26" s="16" t="n">
         <f aca="false">MAX(0,B23-Assumptions!$B$123)</f>
@@ -7844,13 +7851,13 @@
         <v>12320190.7073309</v>
       </c>
       <c r="Q26" s="2"/>
-      <c r="R26" s="51" t="s">
-        <v>776</v>
+      <c r="R26" s="52" t="s">
+        <v>777</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="17" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B27" s="23" t="n">
         <f aca="false">B26*Assumptions!$B$122</f>
@@ -7917,7 +7924,7 @@
     </row>
     <row r="28" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="17" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B28" s="23" t="n">
         <f aca="false">B23-B27</f>
@@ -7980,13 +7987,13 @@
         <v>10642162.1012313</v>
       </c>
       <c r="Q28" s="2"/>
-      <c r="R28" s="51" t="s">
-        <v>779</v>
+      <c r="R28" s="52" t="s">
+        <v>780</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B29" s="16" t="n">
         <f aca="false">Assumptions!$B$123</f>
@@ -8049,13 +8056,13 @@
         <v>170000</v>
       </c>
       <c r="Q29" s="2"/>
-      <c r="R29" s="51" t="s">
-        <v>781</v>
+      <c r="R29" s="52" t="s">
+        <v>782</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="17" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B30" s="23" t="n">
         <f aca="false">B28-B29</f>
@@ -8121,30 +8128,30 @@
       <c r="R30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="41" t="s">
-        <v>783</v>
-      </c>
-      <c r="B31" s="42"/>
-      <c r="C31" s="42"/>
-      <c r="D31" s="42"/>
-      <c r="E31" s="42"/>
-      <c r="F31" s="42"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="42"/>
-      <c r="I31" s="42"/>
-      <c r="J31" s="42"/>
-      <c r="K31" s="42"/>
-      <c r="L31" s="42"/>
-      <c r="M31" s="42"/>
-      <c r="N31" s="42"/>
-      <c r="O31" s="42"/>
-      <c r="P31" s="42"/>
+      <c r="A31" s="42" t="s">
+        <v>784</v>
+      </c>
+      <c r="B31" s="43"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="43"/>
+      <c r="L31" s="43"/>
+      <c r="M31" s="43"/>
+      <c r="N31" s="43"/>
+      <c r="O31" s="43"/>
+      <c r="P31" s="43"/>
       <c r="Q31" s="2"/>
-      <c r="R31" s="42"/>
+      <c r="R31" s="43"/>
     </row>
     <row r="32" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="17" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B32" s="23" t="n">
         <f aca="false">B27</f>
@@ -8207,13 +8214,13 @@
         <v>1848028.60609963</v>
       </c>
       <c r="Q32" s="2"/>
-      <c r="R32" s="51" t="s">
-        <v>785</v>
+      <c r="R32" s="52" t="s">
+        <v>786</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B33" s="16" t="n">
         <f aca="false">IF(B32=0,0,PMT(Assumptions!$B$111/12,60,-B32))</f>
@@ -8276,8 +8283,8 @@
         <v>41812.2025064305</v>
       </c>
       <c r="Q33" s="2"/>
-      <c r="R33" s="51" t="s">
-        <v>787</v>
+      <c r="R33" s="52" t="s">
+        <v>788</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8302,7 +8309,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -8324,7 +8331,7 @@
     </row>
     <row r="36" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="32" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B36" s="32"/>
       <c r="C36" s="32"/>
@@ -8374,7 +8381,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8396,7 +8403,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8438,7 +8445,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -8460,25 +8467,25 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="7" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="7" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="7" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -8487,28 +8494,28 @@
       <c r="R5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="43" t="n">
+      <c r="A6" s="44" t="n">
         <f aca="false">Assumptions!$B$39</f>
         <v>10</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
-      <c r="E6" s="45" t="n">
+      <c r="E6" s="46" t="n">
         <f aca="false">INDEX(B18:P18,Assumptions!$B$39)</f>
         <v>82459.6807714524</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="45" t="n">
+      <c r="I6" s="46" t="n">
         <f aca="false">INDEX(B20:P20,Assumptions!$B$39)</f>
         <v>74842.8470548401</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
-      <c r="M6" s="45" t="n">
+      <c r="M6" s="46" t="n">
         <f aca="false">INDEX(B21:P21,Assumptions!$B$39)</f>
         <v>157302.527826292</v>
       </c>
@@ -8520,25 +8527,25 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="7" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="7" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="7" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -8547,28 +8554,28 @@
       <c r="R7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="45" t="n">
+      <c r="A8" s="46" t="n">
         <f aca="false">INDEX(B22:P22,Assumptions!$B$39)</f>
         <v>1123335.91271496</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="60" t="n">
+      <c r="E8" s="61" t="n">
         <f aca="false">INDEX(B23:P23,Assumptions!$B$39)</f>
         <v>0.0317649218586205</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
-      <c r="I8" s="45" t="n">
+      <c r="I8" s="46" t="n">
         <f aca="false">INDEX(B29:P29,Assumptions!$B$39)</f>
         <v>657225.822356787</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
-      <c r="M8" s="45" t="n">
+      <c r="M8" s="46" t="n">
         <f aca="false">INDEX(B30:P30,Assumptions!$B$39)</f>
         <v>1780561.73507175</v>
       </c>
@@ -8660,7 +8667,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B13" s="18" t="n">
         <v>1</v>
@@ -8714,7 +8721,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -8736,7 +8743,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B15" s="16" t="n">
         <f aca="false">'Long range 15-yr'!B36</f>
@@ -8803,7 +8810,7 @@
     </row>
     <row r="16" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B16" s="23" t="n">
         <f aca="false">'Long range 15-yr'!B50</f>
@@ -8866,35 +8873,35 @@
         <v>1394843.49387317</v>
       </c>
       <c r="Q16" s="2"/>
-      <c r="R16" s="51" t="s">
-        <v>801</v>
+      <c r="R16" s="52" t="s">
+        <v>802</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="41" t="s">
-        <v>802</v>
-      </c>
-      <c r="B17" s="42"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="42"/>
-      <c r="K17" s="42"/>
-      <c r="L17" s="42"/>
-      <c r="M17" s="42"/>
-      <c r="N17" s="42"/>
-      <c r="O17" s="42"/>
-      <c r="P17" s="42"/>
+      <c r="A17" s="42" t="s">
+        <v>803</v>
+      </c>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="43"/>
+      <c r="L17" s="43"/>
+      <c r="M17" s="43"/>
+      <c r="N17" s="43"/>
+      <c r="O17" s="43"/>
+      <c r="P17" s="43"/>
       <c r="Q17" s="2"/>
-      <c r="R17" s="42"/>
+      <c r="R17" s="43"/>
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B18" s="16" t="n">
         <f aca="false">Assumptions!$B$144</f>
@@ -8957,13 +8964,13 @@
         <v>94438.8743462477</v>
       </c>
       <c r="Q18" s="2"/>
-      <c r="R18" s="51" t="s">
-        <v>803</v>
+      <c r="R18" s="52" t="s">
+        <v>804</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B19" s="16" t="n">
         <f aca="false">MAX(0,B16-Assumptions!$B$148)</f>
@@ -9026,13 +9033,13 @@
         <v>1394843.49387317</v>
       </c>
       <c r="Q19" s="2"/>
-      <c r="R19" s="51" t="s">
-        <v>805</v>
+      <c r="R19" s="52" t="s">
+        <v>806</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B20" s="16" t="n">
         <f aca="false">B19*Assumptions!$B$121</f>
@@ -9099,7 +9106,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B21" s="23" t="n">
         <f aca="false">B18+B20</f>
@@ -9166,7 +9173,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B22" s="23" t="n">
         <f aca="false">B21</f>
@@ -9233,7 +9240,7 @@
     </row>
     <row r="23" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B23" s="22" t="n">
         <f aca="false">B21/B15</f>
@@ -9296,13 +9303,13 @@
         <v>0.0319198890336663</v>
       </c>
       <c r="Q23" s="2"/>
-      <c r="R23" s="51" t="s">
-        <v>810</v>
+      <c r="R23" s="52" t="s">
+        <v>811</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -9324,7 +9331,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="17" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B25" s="23" t="n">
         <f aca="false">B16-B21</f>
@@ -9391,7 +9398,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="17" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B26" s="23" t="n">
         <f aca="false">B25+'Long range 15-yr'!B48</f>
@@ -9457,30 +9464,30 @@
       <c r="R26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="41" t="s">
-        <v>814</v>
-      </c>
-      <c r="B27" s="42"/>
-      <c r="C27" s="42"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="42"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="42"/>
-      <c r="K27" s="42"/>
-      <c r="L27" s="42"/>
-      <c r="M27" s="42"/>
-      <c r="N27" s="42"/>
-      <c r="O27" s="42"/>
-      <c r="P27" s="42"/>
+      <c r="A27" s="42" t="s">
+        <v>815</v>
+      </c>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="43"/>
+      <c r="L27" s="43"/>
+      <c r="M27" s="43"/>
+      <c r="N27" s="43"/>
+      <c r="O27" s="43"/>
+      <c r="P27" s="43"/>
       <c r="Q27" s="2"/>
-      <c r="R27" s="42"/>
+      <c r="R27" s="43"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B28" s="16" t="n">
         <f aca="false">'Buyout &amp; exit'!B23</f>
@@ -9547,7 +9554,7 @@
     </row>
     <row r="29" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="17" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B29" s="23" t="n">
         <f aca="false">'Buyout &amp; exit'!B27</f>
@@ -9610,13 +9617,13 @@
         <v>1848028.60609963</v>
       </c>
       <c r="Q29" s="2"/>
-      <c r="R29" s="51" t="s">
-        <v>817</v>
+      <c r="R29" s="52" t="s">
+        <v>818</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="17" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B30" s="23" t="n">
         <f aca="false">B22+B29</f>
@@ -9679,8 +9686,8 @@
         <v>4017720.11576743</v>
       </c>
       <c r="Q30" s="2"/>
-      <c r="R30" s="51" t="s">
-        <v>819</v>
+      <c r="R30" s="52" t="s">
+        <v>820</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9705,7 +9712,7 @@
     </row>
     <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="32" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B32" s="32"/>
       <c r="C32" s="32"/>
@@ -9755,7 +9762,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -9777,7 +9784,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -9819,7 +9826,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -9841,25 +9848,25 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="7" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="7" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="7" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -9868,28 +9875,28 @@
       <c r="R5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="43" t="n">
+      <c r="A6" s="44" t="n">
         <f aca="false">Assumptions!$B$39</f>
         <v>10</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
-      <c r="E6" s="45" t="n">
+      <c r="E6" s="46" t="n">
         <f aca="false">INDEX(B19:P19,Assumptions!$B$39)</f>
         <v>155000</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="45" t="n">
+      <c r="I6" s="46" t="n">
         <f aca="false">INDEX(B20:P20,Assumptions!$B$39)</f>
         <v>34100</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
-      <c r="M6" s="45" t="n">
+      <c r="M6" s="46" t="n">
         <f aca="false">INDEX(B21:P21,Assumptions!$B$39)</f>
         <v>189100</v>
       </c>
@@ -9901,25 +9908,25 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="7" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="7" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="7" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -9928,28 +9935,28 @@
       <c r="R7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="60" t="n">
+      <c r="A8" s="61" t="n">
         <f aca="false">INDEX(B27:P27,Assumptions!$B$39)</f>
         <v>0.12</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="45" t="n">
+      <c r="E8" s="46" t="n">
         <f aca="false">INDEX(B32:P32,Assumptions!$B$39)</f>
         <v>463222.930203932</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
-      <c r="I8" s="45" t="n">
+      <c r="I8" s="46" t="n">
         <f aca="false">INDEX(B36:P36,Assumptions!$B$39)</f>
         <v>42096.3160608399</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
-      <c r="M8" s="45" t="n">
+      <c r="M8" s="46" t="n">
         <f aca="false">INDEX(B37:P37,Assumptions!$B$39)</f>
         <v>505319.246264772</v>
       </c>
@@ -10041,7 +10048,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B13" s="18" t="n">
         <v>1</v>
@@ -10095,7 +10102,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -10117,7 +10124,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B15" s="16" t="n">
         <f aca="false">'Long range 15-yr'!B36</f>
@@ -10184,7 +10191,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B16" s="15" t="n">
         <f aca="false">'Long range 15-yr'!B17</f>
@@ -10251,7 +10258,7 @@
     </row>
     <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B17" s="20" t="n">
         <f aca="false">'Long range 15-yr'!B34</f>
@@ -10314,35 +10321,35 @@
         <v>37</v>
       </c>
       <c r="Q17" s="2"/>
-      <c r="R17" s="51" t="s">
-        <v>832</v>
+      <c r="R17" s="52" t="s">
+        <v>833</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="41" t="s">
-        <v>833</v>
-      </c>
-      <c r="B18" s="42"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="42"/>
-      <c r="K18" s="42"/>
-      <c r="L18" s="42"/>
-      <c r="M18" s="42"/>
-      <c r="N18" s="42"/>
-      <c r="O18" s="42"/>
-      <c r="P18" s="42"/>
+      <c r="A18" s="42" t="s">
+        <v>834</v>
+      </c>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+      <c r="L18" s="43"/>
+      <c r="M18" s="43"/>
+      <c r="N18" s="43"/>
+      <c r="O18" s="43"/>
+      <c r="P18" s="43"/>
       <c r="Q18" s="2"/>
-      <c r="R18" s="42"/>
+      <c r="R18" s="43"/>
     </row>
     <row r="19" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B19" s="16" t="n">
         <f aca="false">IF(1&lt;Assumptions!$B$150,0,(IF(B15&gt;=6000000,Assumptions!$B$154,IF(B15&gt;=3000000,Assumptions!$B$153,IF(B15&gt;=1500000,Assumptions!$B$152,Assumptions!$B$151))))*IF(1&gt;=Assumptions!$B$165,1,Assumptions!$B$164))</f>
@@ -10405,13 +10412,13 @@
         <v>185000</v>
       </c>
       <c r="Q19" s="2"/>
-      <c r="R19" s="51" t="s">
-        <v>835</v>
+      <c r="R19" s="52" t="s">
+        <v>836</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B20" s="16" t="n">
         <f aca="false">B19*Assumptions!$B$155*Assumptions!$B$156</f>
@@ -10474,13 +10481,13 @@
         <v>40700</v>
       </c>
       <c r="Q20" s="2"/>
-      <c r="R20" s="51" t="s">
-        <v>837</v>
+      <c r="R20" s="52" t="s">
+        <v>838</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B21" s="23" t="n">
         <f aca="false">B19+B20</f>
@@ -10547,7 +10554,7 @@
     </row>
     <row r="22" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B22" s="16" t="n">
         <f aca="false">IF(1&lt;Assumptions!$B$150,0,MIN(1,'Long range 15-yr'!B24)*Assumptions!$B$56)</f>
@@ -10610,13 +10617,13 @@
         <v>116546.005617542</v>
       </c>
       <c r="Q22" s="2"/>
-      <c r="R22" s="51" t="s">
-        <v>840</v>
+      <c r="R22" s="52" t="s">
+        <v>841</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B23" s="23" t="n">
         <f aca="false">B21-B22</f>
@@ -10679,13 +10686,13 @@
         <v>109153.994382458</v>
       </c>
       <c r="Q23" s="2"/>
-      <c r="R23" s="51" t="s">
-        <v>842</v>
+      <c r="R23" s="52" t="s">
+        <v>843</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B24" s="22" t="n">
         <f aca="false">IF(B15=0,0,B23/B15)</f>
@@ -10748,13 +10755,13 @@
         <v>0.0148945595595841</v>
       </c>
       <c r="Q24" s="2"/>
-      <c r="R24" s="51" t="s">
-        <v>844</v>
+      <c r="R24" s="52" t="s">
+        <v>845</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -10776,7 +10783,7 @@
     </row>
     <row r="26" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B26" s="22" t="n">
         <f aca="false">IF(1&lt;Assumptions!$B$150,0,MIN(1,MAX(0,(1-Assumptions!$B$150+1)/Assumptions!$B$158)))</f>
@@ -10839,71 +10846,71 @@
         <v>1</v>
       </c>
       <c r="Q26" s="2"/>
-      <c r="R26" s="51" t="s">
-        <v>847</v>
+      <c r="R26" s="52" t="s">
+        <v>848</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="17" t="s">
-        <v>848</v>
-      </c>
-      <c r="B27" s="46" t="n">
+        <v>849</v>
+      </c>
+      <c r="B27" s="47" t="n">
         <f aca="false">B26*Assumptions!$B$157</f>
         <v>0.03</v>
       </c>
-      <c r="C27" s="46" t="n">
+      <c r="C27" s="47" t="n">
         <f aca="false">C26*Assumptions!$B$157</f>
         <v>0.06</v>
       </c>
-      <c r="D27" s="46" t="n">
+      <c r="D27" s="47" t="n">
         <f aca="false">D26*Assumptions!$B$157</f>
         <v>0.09</v>
       </c>
-      <c r="E27" s="46" t="n">
+      <c r="E27" s="47" t="n">
         <f aca="false">E26*Assumptions!$B$157</f>
         <v>0.12</v>
       </c>
-      <c r="F27" s="46" t="n">
+      <c r="F27" s="47" t="n">
         <f aca="false">F26*Assumptions!$B$157</f>
         <v>0.12</v>
       </c>
-      <c r="G27" s="46" t="n">
+      <c r="G27" s="47" t="n">
         <f aca="false">G26*Assumptions!$B$157</f>
         <v>0.12</v>
       </c>
-      <c r="H27" s="46" t="n">
+      <c r="H27" s="47" t="n">
         <f aca="false">H26*Assumptions!$B$157</f>
         <v>0.12</v>
       </c>
-      <c r="I27" s="46" t="n">
+      <c r="I27" s="47" t="n">
         <f aca="false">I26*Assumptions!$B$157</f>
         <v>0.12</v>
       </c>
-      <c r="J27" s="46" t="n">
+      <c r="J27" s="47" t="n">
         <f aca="false">J26*Assumptions!$B$157</f>
         <v>0.12</v>
       </c>
-      <c r="K27" s="46" t="n">
+      <c r="K27" s="47" t="n">
         <f aca="false">K26*Assumptions!$B$157</f>
         <v>0.12</v>
       </c>
-      <c r="L27" s="46" t="n">
+      <c r="L27" s="47" t="n">
         <f aca="false">L26*Assumptions!$B$157</f>
         <v>0.12</v>
       </c>
-      <c r="M27" s="46" t="n">
+      <c r="M27" s="47" t="n">
         <f aca="false">M26*Assumptions!$B$157</f>
         <v>0.12</v>
       </c>
-      <c r="N27" s="46" t="n">
+      <c r="N27" s="47" t="n">
         <f aca="false">N26*Assumptions!$B$157</f>
         <v>0.12</v>
       </c>
-      <c r="O27" s="46" t="n">
+      <c r="O27" s="47" t="n">
         <f aca="false">O26*Assumptions!$B$157</f>
         <v>0.12</v>
       </c>
-      <c r="P27" s="46" t="n">
+      <c r="P27" s="47" t="n">
         <f aca="false">P26*Assumptions!$B$157</f>
         <v>0.12</v>
       </c>
@@ -10912,7 +10919,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B28" s="16" t="n">
         <f aca="false">'Buyout &amp; exit'!B23</f>
@@ -10979,7 +10986,7 @@
     </row>
     <row r="29" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B29" s="16" t="n">
         <f aca="false">MAX(0,B28-INDEX('Buyout &amp; exit'!$B$23:$P$23,Assumptions!$B$150))</f>
@@ -11042,13 +11049,13 @@
         <v>11798876.3099851</v>
       </c>
       <c r="Q29" s="2"/>
-      <c r="R29" s="51" t="s">
-        <v>850</v>
+      <c r="R29" s="52" t="s">
+        <v>851</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="17" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B30" s="23" t="n">
         <f aca="false">B27*B29</f>
@@ -11115,7 +11122,7 @@
     </row>
     <row r="31" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B31" s="16" t="n">
         <f aca="false">IF(OR(Assumptions!$B$159=0,1&lt;Assumptions!$B$150),0,Assumptions!$B$159/(1-Assumptions!$B$160)/MAX(1,INDEX('Buyout &amp; exit'!$B$23:$P$23,Assumptions!$B$150))*B28)</f>
@@ -11178,13 +11185,13 @@
         <v>0</v>
       </c>
       <c r="Q31" s="2"/>
-      <c r="R31" s="51" t="s">
-        <v>853</v>
+      <c r="R31" s="52" t="s">
+        <v>854</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="17" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B32" s="23" t="n">
         <f aca="false">B30+B31</f>
@@ -11250,30 +11257,30 @@
       <c r="R32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="41" t="s">
-        <v>855</v>
-      </c>
-      <c r="B33" s="42"/>
-      <c r="C33" s="42"/>
-      <c r="D33" s="42"/>
-      <c r="E33" s="42"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="42"/>
-      <c r="H33" s="42"/>
-      <c r="I33" s="42"/>
-      <c r="J33" s="42"/>
-      <c r="K33" s="42"/>
-      <c r="L33" s="42"/>
-      <c r="M33" s="42"/>
-      <c r="N33" s="42"/>
-      <c r="O33" s="42"/>
-      <c r="P33" s="42"/>
+      <c r="A33" s="42" t="s">
+        <v>856</v>
+      </c>
+      <c r="B33" s="43"/>
+      <c r="C33" s="43"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="43"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="43"/>
+      <c r="H33" s="43"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="43"/>
+      <c r="K33" s="43"/>
+      <c r="L33" s="43"/>
+      <c r="M33" s="43"/>
+      <c r="N33" s="43"/>
+      <c r="O33" s="43"/>
+      <c r="P33" s="43"/>
       <c r="Q33" s="2"/>
-      <c r="R33" s="42"/>
+      <c r="R33" s="43"/>
     </row>
     <row r="34" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B34" s="16" t="n">
         <f aca="false">Assumptions!$B$161</f>
@@ -11336,13 +11343,13 @@
         <v>187683.495906459</v>
       </c>
       <c r="Q34" s="2"/>
-      <c r="R34" s="51" t="s">
-        <v>857</v>
+      <c r="R34" s="52" t="s">
+        <v>858</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="17" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B35" s="23" t="n">
         <f aca="false">B21-B34</f>
@@ -11405,13 +11412,13 @@
         <v>38016.5040935409</v>
       </c>
       <c r="Q35" s="2"/>
-      <c r="R35" s="51" t="s">
-        <v>859</v>
+      <c r="R35" s="52" t="s">
+        <v>860</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="17" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B36" s="23" t="n">
         <f aca="false">B35</f>
@@ -11478,7 +11485,7 @@
     </row>
     <row r="37" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="17" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B37" s="23" t="n">
         <f aca="false">B36+B32</f>
@@ -11541,13 +11548,13 @@
         <v>1660349.08287506</v>
       </c>
       <c r="Q37" s="2"/>
-      <c r="R37" s="51" t="s">
-        <v>862</v>
+      <c r="R37" s="52" t="s">
+        <v>863</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="19" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B38" s="20" t="str">
         <f aca="false">IF(B37&gt;0,"AHEAD","behind")</f>
@@ -11633,30 +11640,30 @@
       <c r="R39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="61" t="s">
-        <v>864</v>
-      </c>
-      <c r="B40" s="62"/>
-      <c r="C40" s="62"/>
-      <c r="D40" s="62"/>
-      <c r="E40" s="62"/>
-      <c r="F40" s="62"/>
-      <c r="G40" s="62"/>
-      <c r="H40" s="62"/>
-      <c r="I40" s="62"/>
-      <c r="J40" s="62"/>
-      <c r="K40" s="62"/>
-      <c r="L40" s="62"/>
-      <c r="M40" s="62"/>
-      <c r="N40" s="62"/>
-      <c r="O40" s="62"/>
-      <c r="P40" s="62"/>
+      <c r="A40" s="62" t="s">
+        <v>865</v>
+      </c>
+      <c r="B40" s="63"/>
+      <c r="C40" s="63"/>
+      <c r="D40" s="63"/>
+      <c r="E40" s="63"/>
+      <c r="F40" s="63"/>
+      <c r="G40" s="63"/>
+      <c r="H40" s="63"/>
+      <c r="I40" s="63"/>
+      <c r="J40" s="63"/>
+      <c r="K40" s="63"/>
+      <c r="L40" s="63"/>
+      <c r="M40" s="63"/>
+      <c r="N40" s="63"/>
+      <c r="O40" s="63"/>
+      <c r="P40" s="63"/>
       <c r="Q40" s="2"/>
-      <c r="R40" s="62"/>
+      <c r="R40" s="63"/>
     </row>
     <row r="41" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="32" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B41" s="32"/>
       <c r="C41" s="32"/>
@@ -11706,7 +11713,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -11728,7 +11735,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -11870,7 +11877,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B9" s="18" t="n">
         <v>1</v>
@@ -11924,7 +11931,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B10" s="23" t="n">
         <f aca="false">'Long range 15-yr'!B36</f>
@@ -11991,7 +11998,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B11" s="16" t="n">
         <f aca="false">'Long range 15-yr'!B45</f>
@@ -12058,7 +12065,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B12" s="23" t="n">
         <f aca="false">'Long range 15-yr'!B50+'Long range 15-yr'!B48</f>
@@ -12121,13 +12128,13 @@
         <v>1544843.49387317</v>
       </c>
       <c r="Q12" s="2"/>
-      <c r="R12" s="51" t="s">
-        <v>870</v>
+      <c r="R12" s="52" t="s">
+        <v>871</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B13" s="16" t="n">
         <f aca="false">'Long range 15-yr'!B48</f>
@@ -12194,7 +12201,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B14" s="16" t="n">
         <f aca="false">'Ned - proforma'!B21</f>
@@ -12261,7 +12268,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B15" s="16" t="n">
         <f aca="false">'Bryan - COO proforma'!B21</f>
@@ -12328,7 +12335,7 @@
     </row>
     <row r="16" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B16" s="16" t="n">
         <f aca="false">-'Bryan - COO proforma'!B22</f>
@@ -12391,13 +12398,13 @@
         <v>-116546.005617542</v>
       </c>
       <c r="Q16" s="2"/>
-      <c r="R16" s="51" t="s">
-        <v>875</v>
+      <c r="R16" s="52" t="s">
+        <v>876</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B17" s="23" t="n">
         <f aca="false">B13+B14+B15+B16</f>
@@ -12464,76 +12471,76 @@
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>809</v>
-      </c>
-      <c r="B18" s="46" t="n">
+        <v>810</v>
+      </c>
+      <c r="B18" s="47" t="n">
         <f aca="false">B17/B10</f>
         <v>0.267135139859333</v>
       </c>
-      <c r="C18" s="46" t="n">
+      <c r="C18" s="47" t="n">
         <f aca="false">C17/C10</f>
         <v>0.301951242861078</v>
       </c>
-      <c r="D18" s="46" t="n">
+      <c r="D18" s="47" t="n">
         <f aca="false">D17/D10</f>
         <v>0.240056049255304</v>
       </c>
-      <c r="E18" s="46" t="n">
+      <c r="E18" s="47" t="n">
         <f aca="false">E17/E10</f>
         <v>0.151433631256138</v>
       </c>
-      <c r="F18" s="46" t="n">
+      <c r="F18" s="47" t="n">
         <f aca="false">F17/F10</f>
         <v>0.125913709313645</v>
       </c>
-      <c r="G18" s="46" t="n">
+      <c r="G18" s="47" t="n">
         <f aca="false">G17/G10</f>
         <v>0.106896887910453</v>
       </c>
-      <c r="H18" s="46" t="n">
+      <c r="H18" s="47" t="n">
         <f aca="false">H17/H10</f>
         <v>0.108703379464591</v>
       </c>
-      <c r="I18" s="46" t="n">
+      <c r="I18" s="47" t="n">
         <f aca="false">I17/I10</f>
         <v>0.0985302874798641</v>
       </c>
-      <c r="J18" s="46" t="n">
+      <c r="J18" s="47" t="n">
         <f aca="false">J17/J10</f>
         <v>0.0901668281931212</v>
       </c>
-      <c r="K18" s="46" t="n">
+      <c r="K18" s="47" t="n">
         <f aca="false">K17/K10</f>
         <v>0.0804255346106835</v>
       </c>
-      <c r="L18" s="46" t="n">
+      <c r="L18" s="47" t="n">
         <f aca="false">L17/L10</f>
         <v>0.0748537905524239</v>
       </c>
-      <c r="M18" s="46" t="n">
+      <c r="M18" s="47" t="n">
         <f aca="false">M17/M10</f>
         <v>0.0760472486957636</v>
       </c>
-      <c r="N18" s="46" t="n">
+      <c r="N18" s="47" t="n">
         <f aca="false">N17/N10</f>
         <v>0.0713429512554777</v>
       </c>
-      <c r="O18" s="46" t="n">
+      <c r="O18" s="47" t="n">
         <f aca="false">O17/O10</f>
         <v>0.0692735120892928</v>
       </c>
-      <c r="P18" s="46" t="n">
+      <c r="P18" s="47" t="n">
         <f aca="false">P17/P10</f>
         <v>0.067282631609159</v>
       </c>
       <c r="Q18" s="2"/>
-      <c r="R18" s="51" t="s">
-        <v>877</v>
+      <c r="R18" s="52" t="s">
+        <v>878</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B19" s="23" t="n">
         <f aca="false">B12-B17</f>
@@ -12596,13 +12603,13 @@
         <v>1051766.27575715</v>
       </c>
       <c r="Q19" s="2"/>
-      <c r="R19" s="51" t="s">
-        <v>879</v>
+      <c r="R19" s="52" t="s">
+        <v>880</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B20" s="20" t="str">
         <f aca="false">IF(ABS(B12-B17-B19)&lt;1,"OK","CHECK")</f>
@@ -12689,7 +12696,7 @@
     </row>
     <row r="22" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="32" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B22" s="32"/>
       <c r="C22" s="32"/>
@@ -12739,7 +12746,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -12761,7 +12768,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -12983,7 +12990,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B13" s="18" t="n">
         <v>1</v>
@@ -13037,7 +13044,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -13122,35 +13129,35 @@
         <v>150000</v>
       </c>
       <c r="Q15" s="2"/>
-      <c r="R15" s="51" t="s">
-        <v>885</v>
+      <c r="R15" s="52" t="s">
+        <v>886</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="41" t="s">
-        <v>886</v>
-      </c>
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="42"/>
-      <c r="J16" s="42"/>
-      <c r="K16" s="42"/>
-      <c r="L16" s="42"/>
-      <c r="M16" s="42"/>
-      <c r="N16" s="42"/>
-      <c r="O16" s="42"/>
-      <c r="P16" s="42"/>
+      <c r="A16" s="42" t="s">
+        <v>887</v>
+      </c>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
+      <c r="L16" s="43"/>
+      <c r="M16" s="43"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="43"/>
+      <c r="P16" s="43"/>
       <c r="Q16" s="2"/>
-      <c r="R16" s="42"/>
+      <c r="R16" s="43"/>
     </row>
     <row r="17" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B17" s="16" t="n">
         <f aca="false">Assumptions!$B$167*Assumptions!$B$168</f>
@@ -13213,13 +13220,13 @@
         <v>13374</v>
       </c>
       <c r="Q17" s="2"/>
-      <c r="R17" s="51" t="s">
-        <v>888</v>
+      <c r="R17" s="52" t="s">
+        <v>889</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B18" s="16" t="n">
         <f aca="false">Assumptions!$B$170*0.5</f>
@@ -13282,13 +13289,13 @@
         <v>1200</v>
       </c>
       <c r="Q18" s="2"/>
-      <c r="R18" s="51" t="s">
-        <v>890</v>
+      <c r="R18" s="52" t="s">
+        <v>891</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B19" s="16" t="n">
         <f aca="false">Assumptions!$B$171</f>
@@ -13351,13 +13358,13 @@
         <v>1500</v>
       </c>
       <c r="Q19" s="2"/>
-      <c r="R19" s="51" t="s">
-        <v>892</v>
+      <c r="R19" s="52" t="s">
+        <v>893</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B20" s="16" t="n">
         <f aca="false">Assumptions!$B$172</f>
@@ -13420,13 +13427,13 @@
         <v>9600</v>
       </c>
       <c r="Q20" s="2"/>
-      <c r="R20" s="51" t="s">
-        <v>894</v>
+      <c r="R20" s="52" t="s">
+        <v>895</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="19" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B21" s="16" t="n">
         <f aca="false">Assumptions!$B$174</f>
@@ -13493,7 +13500,7 @@
     </row>
     <row r="22" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B22" s="16" t="n">
         <f aca="false">B15*Assumptions!$B$173</f>
@@ -13556,13 +13563,13 @@
         <v>22500</v>
       </c>
       <c r="Q22" s="2"/>
-      <c r="R22" s="51" t="s">
-        <v>897</v>
+      <c r="R22" s="52" t="s">
+        <v>898</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B23" s="23" t="n">
         <f aca="false">B17+B18+B19+B20+B21+B22</f>
@@ -13629,7 +13636,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -13651,7 +13658,7 @@
     </row>
     <row r="25" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="17" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B25" s="23" t="n">
         <f aca="false">B23*Assumptions!$B$175</f>
@@ -13714,35 +13721,35 @@
         <v>16567.68</v>
       </c>
       <c r="Q25" s="2"/>
-      <c r="R25" s="51" t="s">
-        <v>901</v>
+      <c r="R25" s="52" t="s">
+        <v>902</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="41" t="s">
-        <v>902</v>
-      </c>
-      <c r="B26" s="42"/>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="42"/>
-      <c r="I26" s="42"/>
-      <c r="J26" s="42"/>
-      <c r="K26" s="42"/>
-      <c r="L26" s="42"/>
-      <c r="M26" s="42"/>
-      <c r="N26" s="42"/>
-      <c r="O26" s="42"/>
-      <c r="P26" s="42"/>
+      <c r="A26" s="42" t="s">
+        <v>903</v>
+      </c>
+      <c r="B26" s="43"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="43"/>
+      <c r="L26" s="43"/>
+      <c r="M26" s="43"/>
+      <c r="N26" s="43"/>
+      <c r="O26" s="43"/>
+      <c r="P26" s="43"/>
       <c r="Q26" s="2"/>
-      <c r="R26" s="42"/>
+      <c r="R26" s="43"/>
     </row>
     <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B27" s="16" t="n">
         <f aca="false">Assumptions!$B$177*'Long range 15-yr'!B36/'Long range 15-yr'!B36</f>
@@ -13805,13 +13812,13 @@
         <v>1653704.43540605</v>
       </c>
       <c r="Q27" s="2"/>
-      <c r="R27" s="51" t="s">
-        <v>904</v>
+      <c r="R27" s="52" t="s">
+        <v>905</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="17" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B28" s="23" t="n">
         <f aca="false">B27*Assumptions!$B$178</f>
@@ -13874,13 +13881,13 @@
         <v>33074.0887081209</v>
       </c>
       <c r="Q28" s="2"/>
-      <c r="R28" s="51" t="s">
-        <v>906</v>
+      <c r="R28" s="52" t="s">
+        <v>907</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="17" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B29" s="23" t="n">
         <f aca="false">B25+B28</f>
@@ -13967,7 +13974,7 @@
     </row>
     <row r="31" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="32" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B31" s="32"/>
       <c r="C31" s="32"/>
@@ -13989,7 +13996,7 @@
     </row>
     <row r="32" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="32" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B32" s="32"/>
       <c r="C32" s="32"/>
@@ -14039,7 +14046,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B1" s="2"/>
     </row>
@@ -14048,211 +14055,211 @@
       <c r="B2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="63" t="s">
-        <v>911</v>
-      </c>
-      <c r="B3" s="64" t="s">
+      <c r="A3" s="64" t="s">
         <v>912</v>
       </c>
+      <c r="B3" s="65" t="s">
+        <v>913</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="63" t="s">
-        <v>913</v>
-      </c>
-      <c r="B4" s="64" t="s">
+      <c r="A4" s="64" t="s">
         <v>914</v>
       </c>
+      <c r="B4" s="65" t="s">
+        <v>915</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="63" t="s">
-        <v>915</v>
-      </c>
-      <c r="B5" s="64" t="s">
+      <c r="A5" s="64" t="s">
         <v>916</v>
       </c>
+      <c r="B5" s="65" t="s">
+        <v>917</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="63" t="s">
-        <v>917</v>
-      </c>
-      <c r="B6" s="64" t="s">
+      <c r="A6" s="64" t="s">
         <v>918</v>
       </c>
+      <c r="B6" s="65" t="s">
+        <v>919</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="63" t="s">
-        <v>919</v>
-      </c>
-      <c r="B7" s="64" t="s">
+      <c r="A7" s="64" t="s">
         <v>920</v>
       </c>
+      <c r="B7" s="65" t="s">
+        <v>921</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="63" t="s">
-        <v>921</v>
-      </c>
-      <c r="B8" s="64" t="s">
+      <c r="A8" s="64" t="s">
         <v>922</v>
       </c>
+      <c r="B8" s="65" t="s">
+        <v>923</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="63" t="s">
-        <v>923</v>
-      </c>
-      <c r="B9" s="64" t="s">
+      <c r="A9" s="64" t="s">
         <v>924</v>
       </c>
+      <c r="B9" s="65" t="s">
+        <v>925</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="63" t="s">
-        <v>925</v>
-      </c>
-      <c r="B10" s="64" t="s">
+      <c r="A10" s="64" t="s">
         <v>926</v>
       </c>
+      <c r="B10" s="65" t="s">
+        <v>927</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="63" t="s">
-        <v>927</v>
-      </c>
-      <c r="B11" s="64" t="s">
+      <c r="A11" s="64" t="s">
         <v>928</v>
       </c>
+      <c r="B11" s="65" t="s">
+        <v>929</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="63" t="s">
-        <v>929</v>
-      </c>
-      <c r="B12" s="64" t="s">
+      <c r="A12" s="64" t="s">
         <v>930</v>
       </c>
+      <c r="B12" s="65" t="s">
+        <v>931</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="63" t="s">
-        <v>931</v>
-      </c>
-      <c r="B13" s="64" t="s">
+      <c r="A13" s="64" t="s">
         <v>932</v>
       </c>
+      <c r="B13" s="65" t="s">
+        <v>933</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="63" t="s">
-        <v>933</v>
-      </c>
-      <c r="B14" s="64" t="s">
+      <c r="A14" s="64" t="s">
         <v>934</v>
       </c>
+      <c r="B14" s="65" t="s">
+        <v>935</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="63" t="s">
-        <v>935</v>
-      </c>
-      <c r="B15" s="64" t="s">
+      <c r="A15" s="64" t="s">
         <v>936</v>
       </c>
+      <c r="B15" s="65" t="s">
+        <v>937</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="63" t="s">
-        <v>937</v>
-      </c>
-      <c r="B16" s="64" t="s">
+      <c r="A16" s="64" t="s">
         <v>938</v>
       </c>
+      <c r="B16" s="65" t="s">
+        <v>939</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="63" t="s">
-        <v>939</v>
-      </c>
-      <c r="B17" s="64" t="s">
+      <c r="A17" s="64" t="s">
         <v>940</v>
       </c>
+      <c r="B17" s="65" t="s">
+        <v>941</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="63" t="s">
-        <v>941</v>
-      </c>
-      <c r="B18" s="64" t="s">
+      <c r="A18" s="64" t="s">
         <v>942</v>
       </c>
+      <c r="B18" s="65" t="s">
+        <v>943</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="63" t="s">
-        <v>943</v>
-      </c>
-      <c r="B19" s="64" t="s">
+      <c r="A19" s="64" t="s">
         <v>944</v>
       </c>
+      <c r="B19" s="65" t="s">
+        <v>945</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="63" t="s">
-        <v>945</v>
-      </c>
-      <c r="B20" s="64" t="s">
+      <c r="A20" s="64" t="s">
         <v>946</v>
       </c>
+      <c r="B20" s="65" t="s">
+        <v>947</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="63" t="s">
-        <v>947</v>
-      </c>
-      <c r="B21" s="64" t="s">
+      <c r="A21" s="64" t="s">
         <v>948</v>
       </c>
+      <c r="B21" s="65" t="s">
+        <v>949</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="63" t="s">
-        <v>949</v>
-      </c>
-      <c r="B22" s="64" t="s">
+      <c r="A22" s="64" t="s">
         <v>950</v>
       </c>
+      <c r="B22" s="65" t="s">
+        <v>951</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="63" t="s">
-        <v>951</v>
-      </c>
-      <c r="B23" s="64" t="s">
+      <c r="A23" s="64" t="s">
         <v>952</v>
       </c>
+      <c r="B23" s="65" t="s">
+        <v>953</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="63" t="s">
-        <v>953</v>
-      </c>
-      <c r="B24" s="64" t="s">
+      <c r="A24" s="64" t="s">
         <v>954</v>
       </c>
+      <c r="B24" s="65" t="s">
+        <v>955</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="63" t="s">
-        <v>955</v>
-      </c>
-      <c r="B25" s="64" t="s">
+      <c r="A25" s="64" t="s">
         <v>956</v>
       </c>
+      <c r="B25" s="65" t="s">
+        <v>957</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="63" t="s">
-        <v>957</v>
-      </c>
-      <c r="B26" s="64" t="s">
+      <c r="A26" s="64" t="s">
         <v>958</v>
       </c>
+      <c r="B26" s="65" t="s">
+        <v>959</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="63" t="s">
-        <v>959</v>
-      </c>
-      <c r="B27" s="64" t="s">
+      <c r="A27" s="64" t="s">
         <v>960</v>
       </c>
+      <c r="B27" s="65" t="s">
+        <v>961</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="63" t="s">
-        <v>961</v>
-      </c>
-      <c r="B28" s="64" t="s">
+      <c r="A28" s="64" t="s">
         <v>962</v>
+      </c>
+      <c r="B28" s="65" t="s">
+        <v>963</v>
       </c>
     </row>
   </sheetData>
@@ -22508,7 +22515,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>355</v>
+        <v>494</v>
       </c>
       <c r="B23" s="26" t="n">
         <f aca="false">Assumptions!$B$78*12</f>
@@ -22522,22 +22529,25 @@
         <f aca="false">Assumptions!$B$78*12</f>
         <v>150000</v>
       </c>
-      <c r="E23" s="10" t="n">
-        <v>175000</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>200000</v>
-      </c>
-      <c r="G23" s="10" t="n">
+      <c r="E23" s="26" t="n">
+        <f aca="false">Assumptions!$B$78*12*1.16667</f>
+        <v>175000.5</v>
+      </c>
+      <c r="F23" s="26" t="n">
+        <f aca="false">Assumptions!$B$78*12*1.33333</f>
+        <v>199999.5</v>
+      </c>
+      <c r="G23" s="26" t="n">
+        <f aca="false">Assumptions!$B$78*12*1.5</f>
         <v>225000</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B24" s="10" t="n">
         <v>0</v>
@@ -22558,12 +22568,12 @@
         <v>50000</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B25" s="10" t="n">
         <v>0</v>
@@ -22584,12 +22594,12 @@
         <v>72000</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B26" s="10" t="n">
         <v>0</v>
@@ -22610,12 +22620,12 @@
         <v>58000</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B27" s="10" t="n">
         <v>0</v>
@@ -22636,12 +22646,12 @@
         <v>20000</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B28" s="26" t="n">
         <f aca="false">Assumptions!$B$79*12</f>
@@ -22668,12 +22678,12 @@
         <v>37800</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B29" s="26" t="n">
         <f aca="false">Assumptions!$B$80*12</f>
@@ -22700,12 +22710,12 @@
         <v>104400.927326881</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B30" s="12" t="n">
         <v>0</v>
@@ -22728,7 +22738,7 @@
         <v>4000</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22759,12 +22769,12 @@
         <v>0.98398125</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="19" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B32" s="16" t="n">
         <f aca="false">B30*B31*12</f>
@@ -22791,12 +22801,12 @@
         <v>47231.1</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B33" s="26" t="n">
         <f aca="false">Assumptions!$B$81*12</f>
@@ -22826,7 +22836,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B34" s="26" t="n">
         <f aca="false">Assumptions!$B$82*12</f>
@@ -22850,12 +22860,12 @@
         <v>9600</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="19" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B35" s="26" t="n">
         <f aca="false">(Assumptions!$B$64+Assumptions!$B$67+Assumptions!$B$76)*12</f>
@@ -22882,12 +22892,12 @@
         <v>108533.57643</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="19" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B36" s="26" t="n">
         <f aca="false">Assumptions!$B$83*12</f>
@@ -22917,7 +22927,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="19" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B37" s="34" t="n">
         <v>0</v>
@@ -22946,7 +22956,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -22958,59 +22968,69 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="19" t="s">
-        <v>520</v>
-      </c>
-      <c r="B39" s="10" t="n">
+        <v>521</v>
+      </c>
+      <c r="B39" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="C39" s="10" t="n">
+      <c r="C39" s="26" t="n">
+        <f aca="false">Assumptions!$B$144</f>
         <v>60000</v>
       </c>
-      <c r="D39" s="10" t="n">
+      <c r="D39" s="26" t="n">
+        <f aca="false">Assumptions!$B$144</f>
         <v>60000</v>
       </c>
-      <c r="E39" s="10" t="n">
+      <c r="E39" s="26" t="n">
+        <f aca="false">Assumptions!$B$145</f>
         <v>66000</v>
       </c>
-      <c r="F39" s="10" t="n">
+      <c r="F39" s="26" t="n">
+        <f aca="false">Assumptions!$B$146</f>
         <v>72000</v>
       </c>
-      <c r="G39" s="10" t="n">
+      <c r="G39" s="26" t="n">
+        <f aca="false">Assumptions!$B$146</f>
         <v>72000</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="19" t="s">
-        <v>522</v>
-      </c>
-      <c r="B40" s="13" t="n">
+        <v>523</v>
+      </c>
+      <c r="B40" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="C40" s="13" t="n">
+      <c r="C40" s="28" t="n">
+        <f aca="false">Assumptions!$B$121</f>
         <v>0.1</v>
       </c>
-      <c r="D40" s="13" t="n">
+      <c r="D40" s="28" t="n">
+        <f aca="false">Assumptions!$B$121</f>
         <v>0.1</v>
       </c>
-      <c r="E40" s="13" t="n">
+      <c r="E40" s="28" t="n">
+        <f aca="false">Assumptions!$B$121</f>
         <v>0.1</v>
       </c>
-      <c r="F40" s="13" t="n">
+      <c r="F40" s="28" t="n">
+        <f aca="false">Assumptions!$B$121</f>
         <v>0.1</v>
       </c>
-      <c r="G40" s="13" t="n">
+      <c r="G40" s="28" t="n">
+        <f aca="false">Assumptions!$B$121</f>
         <v>0.1</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B41" s="16" t="n">
         <f aca="false">MAX(0,B45)</f>
@@ -23037,12 +23057,12 @@
         <v>0</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="19" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B42" s="34" t="n">
         <v>0</v>
@@ -23057,23 +23077,23 @@
       </c>
       <c r="E42" s="16" t="n">
         <f aca="false">E39+E40*MAX(0,E44-E41)</f>
-        <v>80773.8891282318</v>
+        <v>80773.8391282318</v>
       </c>
       <c r="F42" s="16" t="n">
         <f aca="false">F39+F40*MAX(0,F44-F41)</f>
-        <v>97582.6247145119</v>
+        <v>97582.6747145119</v>
       </c>
       <c r="G42" s="16" t="n">
         <f aca="false">G39+G40*MAX(0,G44-G41)</f>
         <v>114838.370695016</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="17" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B43" s="23" t="n">
         <f aca="false">SUM(B23:B37)-B30-B31</f>
@@ -23089,11 +23109,11 @@
       </c>
       <c r="E43" s="23" t="n">
         <f aca="false">SUM(E23:E37)-E30-E31</f>
-        <v>531986.414137032</v>
+        <v>531986.914137032</v>
       </c>
       <c r="F43" s="23" t="n">
         <f aca="false">SUM(F23:F37)-F30-F31</f>
-        <v>731963.741076881</v>
+        <v>731963.241076881</v>
       </c>
       <c r="G43" s="23" t="n">
         <f aca="false">SUM(G23:G37)-G30-G31</f>
@@ -23103,7 +23123,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="17" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B44" s="23" t="n">
         <f aca="false">B20-B43</f>
@@ -23119,11 +23139,11 @@
       </c>
       <c r="E44" s="23" t="n">
         <f aca="false">E20-E43</f>
-        <v>147738.891282318</v>
+        <v>147738.391282318</v>
       </c>
       <c r="F44" s="23" t="n">
         <f aca="false">F20-F43</f>
-        <v>255826.247145119</v>
+        <v>255826.747145119</v>
       </c>
       <c r="G44" s="23" t="n">
         <f aca="false">G20-G43</f>
@@ -23133,7 +23153,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="17" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B45" s="23" t="n">
         <f aca="false">B44-B42</f>
@@ -23149,11 +23169,11 @@
       </c>
       <c r="E45" s="23" t="n">
         <f aca="false">E44-E42</f>
-        <v>66965.0021540859</v>
+        <v>66964.5521540859</v>
       </c>
       <c r="F45" s="23" t="n">
         <f aca="false">F44-F42</f>
-        <v>158243.622430607</v>
+        <v>158244.072430607</v>
       </c>
       <c r="G45" s="23" t="n">
         <f aca="false">G44-G42</f>
@@ -23179,11 +23199,11 @@
       </c>
       <c r="E46" s="22" t="n">
         <f aca="false">IF(E15=0,0,E45/E15)</f>
-        <v>0.0480340273510357</v>
+        <v>0.0480337045658253</v>
       </c>
       <c r="F46" s="22" t="n">
         <f aca="false">IF(F15=0,0,F45/F15)</f>
-        <v>0.0783533111658091</v>
+        <v>0.0783535339804128</v>
       </c>
       <c r="G46" s="22" t="n">
         <f aca="false">IF(G15=0,0,G45/G15)</f>
@@ -23193,7 +23213,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -23205,7 +23225,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="19" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B48" s="34" t="n">
         <v>0</v>
@@ -23234,7 +23254,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="17" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B49" s="26" t="n">
         <f aca="false">Assumptions!$B$62</f>
@@ -23250,7 +23270,7 @@
       </c>
       <c r="E49" s="23" t="n">
         <f aca="false">D49+E45-E48</f>
-        <v>255984.440417361</v>
+        <v>255983.990417361</v>
       </c>
       <c r="F49" s="23" t="n">
         <f aca="false">E49+F45-F48</f>
@@ -23261,12 +23281,12 @@
         <v>700073.399103112</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="19" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B50" s="16" t="n">
         <f aca="false">B43/6</f>
@@ -23282,45 +23302,45 @@
       </c>
       <c r="E50" s="16" t="n">
         <f aca="false">E43/6</f>
-        <v>88664.402356172</v>
+        <v>88664.4856895053</v>
       </c>
       <c r="F50" s="16" t="n">
         <f aca="false">F43/6</f>
-        <v>121993.956846147</v>
+        <v>121993.873512813</v>
       </c>
       <c r="G50" s="16" t="n">
         <f aca="false">G43/6</f>
         <v>126794.267292813</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="19" t="s">
-        <v>537</v>
-      </c>
-      <c r="B51" s="38" t="str">
+        <v>538</v>
+      </c>
+      <c r="B51" s="39" t="str">
         <f aca="false">IF(B49&gt;=B50,"yes","NO")</f>
         <v>NO</v>
       </c>
-      <c r="C51" s="38" t="str">
+      <c r="C51" s="39" t="str">
         <f aca="false">IF(C49&gt;=C50,"yes","NO")</f>
         <v>yes</v>
       </c>
-      <c r="D51" s="38" t="str">
+      <c r="D51" s="39" t="str">
         <f aca="false">IF(D49&gt;=D50,"yes","NO")</f>
         <v>yes</v>
       </c>
-      <c r="E51" s="38" t="str">
+      <c r="E51" s="39" t="str">
         <f aca="false">IF(E49&gt;=E50,"yes","NO")</f>
         <v>yes</v>
       </c>
-      <c r="F51" s="38" t="str">
+      <c r="F51" s="39" t="str">
         <f aca="false">IF(F49&gt;=F50,"yes","NO")</f>
         <v>yes</v>
       </c>
-      <c r="G51" s="38" t="str">
+      <c r="G51" s="39" t="str">
         <f aca="false">IF(G49&gt;=G50,"yes","NO")</f>
         <v>yes</v>
       </c>
@@ -23328,7 +23348,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -23340,7 +23360,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="19" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B53" s="16" t="n">
         <f aca="false">B45+B23</f>
@@ -23356,11 +23376,11 @@
       </c>
       <c r="E53" s="16" t="n">
         <f aca="false">E45+E23</f>
-        <v>241965.002154086</v>
+        <v>241965.052154086</v>
       </c>
       <c r="F53" s="16" t="n">
         <f aca="false">F45+F23</f>
-        <v>358243.622430607</v>
+        <v>358243.572430607</v>
       </c>
       <c r="G53" s="16" t="n">
         <f aca="false">G45+G23</f>
@@ -23370,7 +23390,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="19" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B54" s="33" t="n">
         <v>2.46</v>
@@ -23391,12 +23411,12 @@
         <v>2.46</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="17" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B55" s="23" t="n">
         <f aca="false">B53*B54</f>
@@ -23412,18 +23432,18 @@
       </c>
       <c r="E55" s="23" t="n">
         <f aca="false">E53*E54</f>
-        <v>595233.905299051</v>
+        <v>595234.028299051</v>
       </c>
       <c r="F55" s="23" t="n">
         <f aca="false">F53*F54</f>
-        <v>881279.311179294</v>
+        <v>881279.188179294</v>
       </c>
       <c r="G55" s="23" t="n">
         <f aca="false">G53*G54</f>
         <v>1324821.52718765</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
   </sheetData>
@@ -23454,7 +23474,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -23466,7 +23486,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -23488,7 +23508,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -23501,13 +23521,13 @@
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="17"/>
       <c r="B5" s="29" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C5" s="29" t="s">
         <v>424</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -23516,7 +23536,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B6" s="16" t="n">
         <f aca="false">B37</f>
@@ -23537,7 +23557,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B7" s="16" t="n">
         <f aca="false">F37</f>
@@ -23558,7 +23578,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B8" s="20" t="n">
         <f aca="false">F34</f>
@@ -23579,7 +23599,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B9" s="22" t="n">
         <f aca="false">F41</f>
@@ -23600,7 +23620,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B10" s="16" t="n">
         <f aca="false">B43</f>
@@ -23621,7 +23641,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B11" s="23" t="n">
         <f aca="false">B47</f>
@@ -23642,7 +23662,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B12" s="23" t="n">
         <f aca="false">F47</f>
@@ -23663,7 +23683,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B13" s="16" t="n">
         <f aca="false">B46</f>
@@ -23684,7 +23704,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B14" s="16" t="n">
         <f aca="false">F46</f>
@@ -23705,7 +23725,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B15" s="23" t="n">
         <f aca="false">F51</f>
@@ -23726,7 +23746,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B16" s="16" t="n">
         <f aca="false">F50</f>
@@ -23747,7 +23767,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B17" s="23" t="n">
         <f aca="false">F52</f>
@@ -23777,8 +23797,8 @@
       <c r="H18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="39" t="s">
-        <v>561</v>
+      <c r="A19" s="40" t="s">
+        <v>562</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -23810,7 +23830,7 @@
     </row>
     <row r="22" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -23818,13 +23838,13 @@
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="2"/>
-      <c r="H22" s="40" t="s">
-        <v>563</v>
+      <c r="H22" s="41" t="s">
+        <v>564</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="29" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B23" s="29" t="s">
         <v>320</v>
@@ -23865,12 +23885,12 @@
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="7" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B25" s="12" t="n">
         <v>36</v>
@@ -23889,7 +23909,7 @@
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="7" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23920,7 +23940,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B27" s="13" t="n">
         <v>0</v>
@@ -23942,7 +23962,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B28" s="12" t="n">
         <v>45</v>
@@ -23964,7 +23984,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B29" s="13" t="n">
         <v>0.075</v>
@@ -23986,7 +24006,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B30" s="10" t="n">
         <v>24000</v>
@@ -24008,7 +24028,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B31" s="10" t="n">
         <v>0</v>
@@ -24027,24 +24047,24 @@
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="7" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="41" t="s">
-        <v>574</v>
-      </c>
-      <c r="B32" s="42"/>
-      <c r="C32" s="42"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="42"/>
+      <c r="A32" s="42" t="s">
+        <v>575</v>
+      </c>
+      <c r="B32" s="43"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="43"/>
       <c r="G32" s="2"/>
-      <c r="H32" s="42"/>
+      <c r="H32" s="43"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B33" s="20" t="n">
         <f aca="false">B24*Assumptions!$B$10*12</f>
@@ -24071,7 +24091,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="17" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B34" s="21" t="n">
         <f aca="false">B33*B25</f>
@@ -24098,7 +24118,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="19" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B35" s="16" t="n">
         <f aca="false">B34*B26</f>
@@ -24179,7 +24199,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="19" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B38" s="16" t="n">
         <f aca="false">B24*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(B1)-2)</f>
@@ -24206,7 +24226,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="19" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B39" s="16" t="n">
         <f aca="false">B35*Assumptions!$B$22+B28*Assumptions!$B$33*Assumptions!$B$37</f>
@@ -24287,7 +24307,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="19" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B42" s="16" t="n">
         <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+B24*B30+B31+B37*B29+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,B24-1)</f>
@@ -24311,12 +24331,12 @@
       </c>
       <c r="G42" s="2"/>
       <c r="H42" s="7" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="17" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B43" s="23" t="n">
         <f aca="false">B40-B42</f>
@@ -24343,7 +24363,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="19" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B44" s="10" t="n">
         <v>15000</v>
@@ -24362,12 +24382,12 @@
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="19" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B45" s="13" t="n">
         <v>0.1</v>
@@ -24386,12 +24406,12 @@
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="7" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="19" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B46" s="16" t="n">
         <f aca="false">B44+IF(B44=0,0,B45*MAX(0,B43-MAX(0,'5-year plan'!$B$44)))</f>
@@ -24418,7 +24438,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="17" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B47" s="23" t="n">
         <f aca="false">B43-B46</f>
@@ -24445,7 +24465,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="19" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B48" s="22" t="n">
         <f aca="false">IF(B37=0,0,B47/B37)</f>
@@ -24472,7 +24492,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="19" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B49" s="16" t="n">
         <f aca="false">MAX(0,B24-1)*'Equipment plan'!$G$10</f>
@@ -24499,7 +24519,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="17" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B50" s="23" t="n">
         <f aca="false">Assumptions!$B$62+B47-B49</f>
@@ -24523,12 +24543,12 @@
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="7" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="19" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B51" s="16" t="n">
         <f aca="false">B47+Assumptions!$B$78*12</f>
@@ -24555,7 +24575,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="19" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B52" s="16" t="n">
         <f aca="false">MAX(0,B51)*2.46</f>
@@ -24579,7 +24599,7 @@
       </c>
       <c r="G52" s="2"/>
       <c r="H52" s="7" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24594,7 +24614,7 @@
     </row>
     <row r="54" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -24602,13 +24622,13 @@
       <c r="E54" s="5"/>
       <c r="F54" s="5"/>
       <c r="G54" s="2"/>
-      <c r="H54" s="40" t="s">
-        <v>597</v>
+      <c r="H54" s="41" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="29" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B55" s="29" t="s">
         <v>320</v>
@@ -24649,12 +24669,12 @@
       </c>
       <c r="G56" s="2"/>
       <c r="H56" s="7" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="19" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B57" s="12" t="n">
         <v>43</v>
@@ -24673,7 +24693,7 @@
       </c>
       <c r="G57" s="2"/>
       <c r="H57" s="7" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24704,7 +24724,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="19" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B59" s="13" t="n">
         <v>0.03</v>
@@ -24726,7 +24746,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="19" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B60" s="12" t="n">
         <v>94</v>
@@ -24748,7 +24768,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="19" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B61" s="13" t="n">
         <v>0.05</v>
@@ -24770,7 +24790,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="19" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B62" s="10" t="n">
         <v>22000</v>
@@ -24792,7 +24812,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="19" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B63" s="10" t="n">
         <v>0</v>
@@ -24811,24 +24831,24 @@
       </c>
       <c r="G63" s="2"/>
       <c r="H63" s="7" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="41" t="s">
-        <v>574</v>
-      </c>
-      <c r="B64" s="42"/>
-      <c r="C64" s="42"/>
-      <c r="D64" s="42"/>
-      <c r="E64" s="42"/>
-      <c r="F64" s="42"/>
+      <c r="A64" s="42" t="s">
+        <v>575</v>
+      </c>
+      <c r="B64" s="43"/>
+      <c r="C64" s="43"/>
+      <c r="D64" s="43"/>
+      <c r="E64" s="43"/>
+      <c r="F64" s="43"/>
       <c r="G64" s="2"/>
-      <c r="H64" s="42"/>
+      <c r="H64" s="43"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="19" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B65" s="20" t="n">
         <f aca="false">B56*Assumptions!$B$10*12</f>
@@ -24855,7 +24875,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="17" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B66" s="21" t="n">
         <f aca="false">B65*B57</f>
@@ -24882,7 +24902,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="19" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B67" s="16" t="n">
         <f aca="false">B66*B58</f>
@@ -24963,7 +24983,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="19" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B70" s="16" t="n">
         <f aca="false">B56*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(B1)-2)</f>
@@ -24990,7 +25010,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="19" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B71" s="16" t="n">
         <f aca="false">B67*Assumptions!$B$22+B60*Assumptions!$B$33*Assumptions!$B$37</f>
@@ -25071,7 +25091,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="19" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B74" s="16" t="n">
         <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+B56*B62+B63+B69*B61+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,B56-1)</f>
@@ -25095,12 +25115,12 @@
       </c>
       <c r="G74" s="2"/>
       <c r="H74" s="7" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="17" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B75" s="23" t="n">
         <f aca="false">B72-B74</f>
@@ -25127,7 +25147,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="19" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B76" s="10" t="n">
         <v>60000</v>
@@ -25146,12 +25166,12 @@
       </c>
       <c r="G76" s="2"/>
       <c r="H76" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="19" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B77" s="13" t="n">
         <v>0.1</v>
@@ -25170,12 +25190,12 @@
       </c>
       <c r="G77" s="2"/>
       <c r="H77" s="7" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="19" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B78" s="16" t="n">
         <f aca="false">B76+IF(B76=0,0,B77*MAX(0,B75-MAX(0,'5-year plan'!$B$44)))</f>
@@ -25202,7 +25222,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="17" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B79" s="23" t="n">
         <f aca="false">B75-B78</f>
@@ -25229,7 +25249,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="19" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B80" s="22" t="n">
         <f aca="false">IF(B69=0,0,B79/B69)</f>
@@ -25256,7 +25276,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="19" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B81" s="16" t="n">
         <f aca="false">MAX(0,B56-1)*'Equipment plan'!$G$10</f>
@@ -25283,7 +25303,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="17" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B82" s="23" t="n">
         <f aca="false">Assumptions!$B$62+B79-B81</f>
@@ -25307,12 +25327,12 @@
       </c>
       <c r="G82" s="2"/>
       <c r="H82" s="7" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="19" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B83" s="16" t="n">
         <f aca="false">B79+Assumptions!$B$78*12</f>
@@ -25339,7 +25359,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="19" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B84" s="16" t="n">
         <f aca="false">MAX(0,B83)*2.46</f>
@@ -25363,7 +25383,7 @@
       </c>
       <c r="G84" s="2"/>
       <c r="H84" s="7" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25378,7 +25398,7 @@
     </row>
     <row r="86" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="4" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
@@ -25386,13 +25406,13 @@
       <c r="E86" s="5"/>
       <c r="F86" s="5"/>
       <c r="G86" s="2"/>
-      <c r="H86" s="40" t="s">
-        <v>599</v>
+      <c r="H86" s="41" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="29" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B87" s="29" t="s">
         <v>320</v>
@@ -25433,12 +25453,12 @@
       </c>
       <c r="G88" s="2"/>
       <c r="H88" s="7" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="19" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B89" s="12" t="n">
         <v>48</v>
@@ -25457,7 +25477,7 @@
       </c>
       <c r="G89" s="2"/>
       <c r="H89" s="7" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25488,7 +25508,7 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="19" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B91" s="13" t="n">
         <v>0.03</v>
@@ -25510,7 +25530,7 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="19" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B92" s="12" t="n">
         <v>130</v>
@@ -25532,7 +25552,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="19" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B93" s="13" t="n">
         <v>0.045</v>
@@ -25554,7 +25574,7 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="19" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B94" s="10" t="n">
         <v>22000</v>
@@ -25576,7 +25596,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="19" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B95" s="10" t="n">
         <v>12000</v>
@@ -25595,24 +25615,24 @@
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="7" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="41" t="s">
-        <v>574</v>
-      </c>
-      <c r="B96" s="42"/>
-      <c r="C96" s="42"/>
-      <c r="D96" s="42"/>
-      <c r="E96" s="42"/>
-      <c r="F96" s="42"/>
+      <c r="A96" s="42" t="s">
+        <v>575</v>
+      </c>
+      <c r="B96" s="43"/>
+      <c r="C96" s="43"/>
+      <c r="D96" s="43"/>
+      <c r="E96" s="43"/>
+      <c r="F96" s="43"/>
       <c r="G96" s="2"/>
-      <c r="H96" s="42"/>
+      <c r="H96" s="43"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="19" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B97" s="20" t="n">
         <f aca="false">B88*Assumptions!$B$10*12</f>
@@ -25639,7 +25659,7 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="17" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B98" s="21" t="n">
         <f aca="false">B97*B89</f>
@@ -25666,7 +25686,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="19" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B99" s="16" t="n">
         <f aca="false">B98*B90</f>
@@ -25747,7 +25767,7 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="19" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B102" s="16" t="n">
         <f aca="false">B88*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12*1.03^MAX(0,COLUMN(B1)-2)</f>
@@ -25774,7 +25794,7 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="19" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B103" s="16" t="n">
         <f aca="false">B99*Assumptions!$B$22+B92*Assumptions!$B$33*Assumptions!$B$37</f>
@@ -25855,7 +25875,7 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="19" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B106" s="16" t="n">
         <f aca="false">(Assumptions!$B$78+Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+B88*B94+B95+B101*B93+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,B88-1)</f>
@@ -25879,12 +25899,12 @@
       </c>
       <c r="G106" s="2"/>
       <c r="H106" s="7" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="17" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B107" s="23" t="n">
         <f aca="false">B104-B106</f>
@@ -25911,7 +25931,7 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="19" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B108" s="10" t="n">
         <v>60000</v>
@@ -25930,12 +25950,12 @@
       </c>
       <c r="G108" s="2"/>
       <c r="H108" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="19" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B109" s="13" t="n">
         <v>0.1</v>
@@ -25954,12 +25974,12 @@
       </c>
       <c r="G109" s="2"/>
       <c r="H109" s="7" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="19" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B110" s="16" t="n">
         <f aca="false">B108+IF(B108=0,0,B109*MAX(0,B107-MAX(0,'5-year plan'!$B$44)))</f>
@@ -25986,7 +26006,7 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="17" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B111" s="23" t="n">
         <f aca="false">B107-B110</f>
@@ -26013,7 +26033,7 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="19" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B112" s="22" t="n">
         <f aca="false">IF(B101=0,0,B111/B101)</f>
@@ -26040,7 +26060,7 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="19" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B113" s="16" t="n">
         <f aca="false">MAX(0,B88-1)*'Equipment plan'!$G$10</f>
@@ -26067,7 +26087,7 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="17" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B114" s="23" t="n">
         <f aca="false">Assumptions!$B$62+B111-B113</f>
@@ -26091,12 +26111,12 @@
       </c>
       <c r="G114" s="2"/>
       <c r="H114" s="7" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="19" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B115" s="16" t="n">
         <f aca="false">B111+Assumptions!$B$78*12</f>
@@ -26123,7 +26143,7 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="19" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B116" s="16" t="n">
         <f aca="false">MAX(0,B115)*2.46</f>
@@ -26147,7 +26167,7 @@
       </c>
       <c r="G116" s="2"/>
       <c r="H116" s="7" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
   </sheetData>
@@ -26177,7 +26197,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -26199,7 +26219,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -26241,7 +26261,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -26263,25 +26283,25 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="7" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="7" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="7" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -26290,28 +26310,28 @@
       <c r="R5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="43" t="n">
+      <c r="A6" s="44" t="n">
         <f aca="false">Assumptions!$B$39</f>
         <v>10</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
-      <c r="E6" s="44" t="n">
+      <c r="E6" s="45" t="n">
         <f aca="false">INDEX(B17:P17,Assumptions!$B$39)</f>
         <v>6.5</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="43" t="n">
+      <c r="I6" s="44" t="n">
         <f aca="false">INDEX(B34:P34,Assumptions!$B$39)</f>
         <v>32</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
-      <c r="M6" s="45" t="n">
+      <c r="M6" s="46" t="n">
         <f aca="false">INDEX(B36:P36,Assumptions!$B$39)</f>
         <v>4952082.94628947</v>
       </c>
@@ -26323,25 +26343,25 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="7" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="7" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="7" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -26350,28 +26370,28 @@
       <c r="R7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="43" t="n">
+      <c r="A8" s="44" t="n">
         <f aca="false">INDEX(B31:P31,Assumptions!$B$39)</f>
         <v>2075.07366473612</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="45" t="n">
+      <c r="E8" s="46" t="n">
         <f aca="false">INDEX(B50:P50,Assumptions!$B$39)</f>
         <v>748428.470548401</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
-      <c r="I8" s="45" t="n">
+      <c r="I8" s="46" t="n">
         <f aca="false">INDEX(B58:P58,Assumptions!$B$39)</f>
         <v>1482746.81556278</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
-      <c r="M8" s="45" t="n">
+      <c r="M8" s="46" t="n">
         <f aca="false">INDEX(B54:P54,Assumptions!$B$39)</f>
         <v>360470.908966258</v>
       </c>
@@ -26383,25 +26403,25 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="7" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="7" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="7" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -26410,28 +26430,28 @@
       <c r="R9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="45" t="n">
+      <c r="A10" s="46" t="n">
         <f aca="false">INDEX(B57:P57,Assumptions!$B$39)</f>
         <v>2415145.22334417</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="45" t="n">
+      <c r="E10" s="46" t="n">
         <f aca="false">INDEX(B61:P61,Assumptions!$B$39)</f>
         <v>3543862.77655598</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
-      <c r="I10" s="45" t="n">
+      <c r="I10" s="46" t="n">
         <f aca="false">INDEX(B62:P62,Assumptions!$B$39)</f>
         <v>2382380.8834737</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
-      <c r="M10" s="45" t="n">
+      <c r="M10" s="46" t="n">
         <f aca="false">INDEX(B63:P63,Assumptions!$B$39)</f>
         <v>1161481.89308228</v>
       </c>
@@ -26462,8 +26482,8 @@
       <c r="R11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="39" t="s">
-        <v>615</v>
+      <c r="A12" s="40" t="s">
+        <v>616</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -26525,7 +26545,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B15" s="18" t="n">
         <v>1</v>
@@ -26579,7 +26599,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -26601,7 +26621,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B17" s="15" t="n">
         <f aca="false">'5-year plan'!C7</f>
@@ -26665,12 +26685,12 @@
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" s="7" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B18" s="20" t="n">
         <f aca="false">Assumptions!$B$11</f>
@@ -26734,12 +26754,12 @@
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" s="7" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B19" s="20" t="n">
         <f aca="false">B17*Assumptions!$B$10*12</f>
@@ -26806,7 +26826,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B20" s="21" t="n">
         <f aca="false">B19*B18</f>
@@ -26872,30 +26892,30 @@
       <c r="R20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="41" t="s">
-        <v>620</v>
-      </c>
-      <c r="B21" s="42"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="42"/>
-      <c r="J21" s="42"/>
-      <c r="K21" s="42"/>
-      <c r="L21" s="42"/>
-      <c r="M21" s="42"/>
-      <c r="N21" s="42"/>
-      <c r="O21" s="42"/>
-      <c r="P21" s="42"/>
+      <c r="A21" s="42" t="s">
+        <v>621</v>
+      </c>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="43"/>
+      <c r="M21" s="43"/>
+      <c r="N21" s="43"/>
+      <c r="O21" s="43"/>
+      <c r="P21" s="43"/>
       <c r="Q21" s="2"/>
-      <c r="R21" s="42"/>
+      <c r="R21" s="43"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B22" s="20" t="n">
         <f aca="false">ROUND(B17*Assumptions!$B$26,0)</f>
@@ -26962,7 +26982,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B23" s="20" t="n">
         <f aca="false">IF(B17&gt;=2,ROUNDUP(B17/Assumptions!$B$51,0),0)</f>
@@ -27029,7 +27049,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B24" s="20" t="n">
         <f aca="false">IF(B17&gt;=3,ROUNDUP(B17/Assumptions!$B$52,0),0)</f>
@@ -27096,7 +27116,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B25" s="20" t="n">
         <f aca="false">IF(B17&gt;=4,ROUNDUP(B17/Assumptions!$B$53,0),0)</f>
@@ -27162,26 +27182,26 @@
       <c r="R25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="41" t="s">
+      <c r="A26" s="42" t="s">
         <v>338</v>
       </c>
-      <c r="B26" s="42"/>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="42"/>
-      <c r="I26" s="42"/>
-      <c r="J26" s="42"/>
-      <c r="K26" s="42"/>
-      <c r="L26" s="42"/>
-      <c r="M26" s="42"/>
-      <c r="N26" s="42"/>
-      <c r="O26" s="42"/>
-      <c r="P26" s="42"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="43"/>
+      <c r="L26" s="43"/>
+      <c r="M26" s="43"/>
+      <c r="N26" s="43"/>
+      <c r="O26" s="43"/>
+      <c r="P26" s="43"/>
       <c r="Q26" s="2"/>
-      <c r="R26" s="42"/>
+      <c r="R26" s="43"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
@@ -27249,12 +27269,12 @@
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" s="7" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B28" s="16" t="n">
         <f aca="false">B20*B27</f>
@@ -27321,7 +27341,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B29" s="20" t="n">
         <f aca="false">B20/Assumptions!$B$17</f>
@@ -27388,7 +27408,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B30" s="20" t="n">
         <f aca="false">B29*Assumptions!$B$31</f>
@@ -27455,7 +27475,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="17" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B31" s="21" t="n">
         <f aca="false">B30</f>
@@ -27519,7 +27539,7 @@
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" s="7" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27591,7 +27611,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B33" s="20" t="n">
         <f aca="false">ROUNDUP(B31*Assumptions!$B$33/Assumptions!$B$54,0)</f>
@@ -27655,12 +27675,12 @@
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" s="7" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="17" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B34" s="21" t="n">
         <f aca="false">1+B22+B23+B24+B25+B33</f>
@@ -27727,7 +27747,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="19" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B35" s="16" t="n">
         <f aca="false">B31*Assumptions!$B$33*B32</f>
@@ -27860,30 +27880,30 @@
       <c r="R36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="41" t="s">
-        <v>634</v>
-      </c>
-      <c r="B37" s="42"/>
-      <c r="C37" s="42"/>
-      <c r="D37" s="42"/>
-      <c r="E37" s="42"/>
-      <c r="F37" s="42"/>
-      <c r="G37" s="42"/>
-      <c r="H37" s="42"/>
-      <c r="I37" s="42"/>
-      <c r="J37" s="42"/>
-      <c r="K37" s="42"/>
-      <c r="L37" s="42"/>
-      <c r="M37" s="42"/>
-      <c r="N37" s="42"/>
-      <c r="O37" s="42"/>
-      <c r="P37" s="42"/>
+      <c r="A37" s="42" t="s">
+        <v>635</v>
+      </c>
+      <c r="B37" s="43"/>
+      <c r="C37" s="43"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="43"/>
+      <c r="I37" s="43"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="43"/>
+      <c r="L37" s="43"/>
+      <c r="M37" s="43"/>
+      <c r="N37" s="43"/>
+      <c r="O37" s="43"/>
+      <c r="P37" s="43"/>
       <c r="Q37" s="2"/>
-      <c r="R37" s="42"/>
+      <c r="R37" s="43"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="19" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B38" s="16" t="n">
         <f aca="false">B17*(Assumptions!$B$26*Assumptions!$B$27*Assumptions!$B$23+Assumptions!$B$27*Assumptions!$B$24)*(1+Assumptions!$B$25)*12</f>
@@ -27947,12 +27967,12 @@
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" s="7" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="19" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B39" s="16" t="n">
         <f aca="false">B20*(Assumptions!$B$5*Assumptions!$B$22)*(1-Assumptions!$B$135)*Assumptions!$B$134</f>
@@ -28016,12 +28036,12 @@
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" s="7" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="19" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B40" s="16" t="n">
         <f aca="false">B20*(Assumptions!$B$5*Assumptions!$B$22)*(1-Assumptions!$B$135)*(1-Assumptions!$B$134)</f>
@@ -28088,7 +28108,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B41" s="16" t="n">
         <f aca="false">B20*(Assumptions!$B$5*Assumptions!$B$22)*Assumptions!$B$135</f>
@@ -28152,12 +28172,12 @@
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" s="7" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="19" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B42" s="16" t="n">
         <f aca="false">B31*Assumptions!$B$33*Assumptions!$B$37</f>
@@ -28221,12 +28241,12 @@
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" s="7" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="19" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B43" s="16" t="n">
         <f aca="false">B39+B40+B41+B42</f>
@@ -28293,7 +28313,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="19" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B44" s="22" t="n">
         <f aca="false">B43/B36</f>
@@ -28357,7 +28377,7 @@
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" s="7" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28431,74 +28451,74 @@
       <c r="A46" s="17" t="s">
         <v>393</v>
       </c>
-      <c r="B46" s="46" t="n">
+      <c r="B46" s="47" t="n">
         <f aca="false">B45/B36</f>
         <v>0.497020280497441</v>
       </c>
-      <c r="C46" s="46" t="n">
+      <c r="C46" s="47" t="n">
         <f aca="false">C45/C36</f>
         <v>0.483456272911969</v>
       </c>
-      <c r="D46" s="46" t="n">
+      <c r="D46" s="47" t="n">
         <f aca="false">D45/D36</f>
         <v>0.482795966339531</v>
       </c>
-      <c r="E46" s="46" t="n">
+      <c r="E46" s="47" t="n">
         <f aca="false">E45/E36</f>
         <v>0.480547689442316</v>
       </c>
-      <c r="F46" s="46" t="n">
+      <c r="F46" s="47" t="n">
         <f aca="false">F45/F36</f>
         <v>0.479787942540471</v>
       </c>
-      <c r="G46" s="46" t="n">
+      <c r="G46" s="47" t="n">
         <f aca="false">G45/G36</f>
         <v>0.478695342830608</v>
       </c>
-      <c r="H46" s="46" t="n">
+      <c r="H46" s="47" t="n">
         <f aca="false">H45/H36</f>
         <v>0.477340914435507</v>
       </c>
-      <c r="I46" s="46" t="n">
+      <c r="I46" s="47" t="n">
         <f aca="false">I45/I36</f>
         <v>0.475770505525686</v>
       </c>
-      <c r="J46" s="46" t="n">
+      <c r="J46" s="47" t="n">
         <f aca="false">J45/J36</f>
         <v>0.474015311576121</v>
       </c>
-      <c r="K46" s="46" t="n">
+      <c r="K46" s="47" t="n">
         <f aca="false">K45/K36</f>
         <v>0.47209747484362</v>
       </c>
-      <c r="L46" s="46" t="n">
+      <c r="L46" s="47" t="n">
         <f aca="false">L45/L36</f>
         <v>0.470033259800397</v>
       </c>
-      <c r="M46" s="46" t="n">
+      <c r="M46" s="47" t="n">
         <f aca="false">M45/M36</f>
         <v>0.467834951007119</v>
       </c>
-      <c r="N46" s="46" t="n">
+      <c r="N46" s="47" t="n">
         <f aca="false">N45/N36</f>
         <v>0.465512038742625</v>
       </c>
-      <c r="O46" s="46" t="n">
+      <c r="O46" s="47" t="n">
         <f aca="false">O45/O36</f>
         <v>0.464460123023597</v>
       </c>
-      <c r="P46" s="46" t="n">
+      <c r="P46" s="47" t="n">
         <f aca="false">P45/P36</f>
         <v>0.46314900589515</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" s="7" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="19" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B47" s="16" t="n">
         <f aca="false">(B23*Assumptions!$B$55+B24*Assumptions!$B$56+B25*Assumptions!$B$57)</f>
@@ -28562,7 +28582,7 @@
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" s="7" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28631,12 +28651,12 @@
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="19" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B49" s="16" t="n">
         <f aca="false">(Assumptions!$B$80+Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)*12+B17*22000+B36*0.05+Assumptions!$B$84*Assumptions!$B$85*12+'Equipment plan'!$H$10*12*MAX(0,B17-1)</f>
@@ -28700,12 +28720,12 @@
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" s="7" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="17" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B50" s="23" t="n">
         <f aca="false">B45-B47-B49-B48</f>
@@ -28769,12 +28789,12 @@
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" s="7" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -28796,7 +28816,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="19" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B52" s="16" t="n">
         <f aca="false">MAX(0,B17-1)*'Equipment plan'!$B$10</f>
@@ -28863,7 +28883,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="19" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B53" s="16" t="n">
         <f aca="false">Assumptions!$B$45+B52</f>
@@ -28930,7 +28950,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="19" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B54" s="16" t="n">
         <f aca="false">B53*(1-1/Assumptions!$B$46)</f>
@@ -28994,12 +29014,12 @@
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" s="7" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="19" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B55" s="16" t="n">
         <f aca="false">MAX(0,B52*0.8*0.85)</f>
@@ -29063,12 +29083,12 @@
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" s="7" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="19" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B56" s="16" t="n">
         <f aca="false">MAX(0,B50)*Assumptions!$B$44</f>
@@ -29132,12 +29152,12 @@
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" s="7" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="17" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B57" s="23" t="n">
         <f aca="false">B56</f>
@@ -29201,12 +29221,12 @@
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" s="7" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="17" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B58" s="23" t="n">
         <f aca="false">Assumptions!$B$62+B50-B56-B52*0.2</f>
@@ -29270,12 +29290,12 @@
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" s="7" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="19" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B59" s="16" t="n">
         <f aca="false">B50+Assumptions!$B$78*12</f>
@@ -29342,7 +29362,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="19" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B60" s="16" t="n">
         <f aca="false">B59-B35+B31*Assumptions!$B$33*Assumptions!$B$37</f>
@@ -29406,12 +29426,12 @@
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" s="7" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="17" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B61" s="23" t="n">
         <f aca="false">MAX(0,B59)*Assumptions!$B$47+B58-B55</f>
@@ -29475,12 +29495,12 @@
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" s="7" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="17" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B62" s="23" t="n">
         <f aca="false">MAX(0,B60)*Assumptions!$B$48+B58-B55</f>
@@ -29547,7 +29567,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="17" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B63" s="23" t="n">
         <f aca="false">B61-B62</f>
@@ -29611,12 +29631,12 @@
       </c>
       <c r="Q63" s="2"/>
       <c r="R63" s="7" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="19" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B64" s="16" t="n">
         <f aca="false">B35*Assumptions!$B$49</f>
@@ -29711,7 +29731,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -29724,7 +29744,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -29748,15 +29768,15 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>679</v>
-      </c>
-      <c r="B4" s="45" t="n">
+        <v>680</v>
+      </c>
+      <c r="B4" s="46" t="n">
         <f aca="false">Assumptions!$B$110</f>
         <v>150000</v>
       </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="39" t="s">
-        <v>680</v>
+      <c r="D4" s="40" t="s">
+        <v>681</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -29771,63 +29791,63 @@
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
-      <c r="G5" s="47" t="s">
-        <v>681</v>
-      </c>
-      <c r="H5" s="47"/>
-      <c r="I5" s="47"/>
+      <c r="G5" s="48" t="s">
+        <v>682</v>
+      </c>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="48" t="s">
-        <v>682</v>
-      </c>
-      <c r="B6" s="48" t="s">
+      <c r="A6" s="49" t="s">
         <v>683</v>
       </c>
-      <c r="C6" s="48" t="s">
+      <c r="B6" s="49" t="s">
         <v>684</v>
       </c>
-      <c r="D6" s="48" t="s">
+      <c r="C6" s="49" t="s">
         <v>685</v>
       </c>
-      <c r="E6" s="48" t="s">
+      <c r="D6" s="49" t="s">
         <v>686</v>
       </c>
-      <c r="F6" s="48" t="s">
+      <c r="E6" s="49" t="s">
         <v>687</v>
       </c>
-      <c r="G6" s="48" t="s">
+      <c r="F6" s="49" t="s">
         <v>688</v>
       </c>
-      <c r="H6" s="48" t="s">
+      <c r="G6" s="49" t="s">
         <v>689</v>
       </c>
-      <c r="I6" s="48" t="s">
+      <c r="H6" s="49" t="s">
         <v>690</v>
+      </c>
+      <c r="I6" s="49" t="s">
+        <v>691</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>691</v>
-      </c>
-      <c r="B7" s="49" t="n">
+        <v>692</v>
+      </c>
+      <c r="B7" s="50" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="33" t="n">
         <v>0.5</v>
       </c>
-      <c r="D7" s="49" t="n">
+      <c r="D7" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="50" t="n">
+      <c r="E7" s="51" t="n">
         <f aca="false">IF(B7=0,$B$4/(C7*12),PMT(B7/12,C7*12,-$B$4))</f>
         <v>25000</v>
       </c>
-      <c r="F7" s="50" t="n">
+      <c r="F7" s="51" t="n">
         <f aca="false">E7*C7*12+$B$4*D7</f>
         <v>150000</v>
       </c>
-      <c r="G7" s="50" t="n">
+      <c r="G7" s="51" t="n">
         <f aca="false">F7-$B$4</f>
         <v>0</v>
       </c>
@@ -29835,32 +29855,32 @@
         <f aca="false">G7/C7</f>
         <v>0</v>
       </c>
-      <c r="I7" s="51" t="s">
-        <v>692</v>
+      <c r="I7" s="52" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>693</v>
-      </c>
-      <c r="B8" s="49" t="n">
+        <v>694</v>
+      </c>
+      <c r="B8" s="50" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="D8" s="49" t="n">
+      <c r="D8" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="50" t="n">
+      <c r="E8" s="51" t="n">
         <f aca="false">IF(B8=0,$B$4/(C8*12),PMT(B8/12,C8*12,-$B$4))</f>
         <v>3125</v>
       </c>
-      <c r="F8" s="50" t="n">
+      <c r="F8" s="51" t="n">
         <f aca="false">E8*C8*12+$B$4*D8</f>
         <v>150000</v>
       </c>
-      <c r="G8" s="50" t="n">
+      <c r="G8" s="51" t="n">
         <f aca="false">F8-$B$4</f>
         <v>0</v>
       </c>
@@ -29868,32 +29888,32 @@
         <f aca="false">G8/C8</f>
         <v>0</v>
       </c>
-      <c r="I8" s="51" t="s">
-        <v>694</v>
+      <c r="I8" s="52" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>695</v>
-      </c>
-      <c r="B9" s="49" t="n">
+        <v>696</v>
+      </c>
+      <c r="B9" s="50" t="n">
         <v>0.085</v>
       </c>
       <c r="C9" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="D9" s="49" t="n">
+      <c r="D9" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="50" t="n">
+      <c r="E9" s="51" t="n">
         <f aca="false">IF(B9=0,$B$4/(C9*12),PMT(B9/12,C9*12,-$B$4))</f>
         <v>3077.47969905769</v>
       </c>
-      <c r="F9" s="50" t="n">
+      <c r="F9" s="51" t="n">
         <f aca="false">E9*C9*12+$B$4*D9</f>
         <v>184648.781943461</v>
       </c>
-      <c r="G9" s="50" t="n">
+      <c r="G9" s="51" t="n">
         <f aca="false">F9-$B$4</f>
         <v>34648.7819434613</v>
       </c>
@@ -29901,32 +29921,32 @@
         <f aca="false">G9/C9</f>
         <v>6929.75638869225</v>
       </c>
-      <c r="I9" s="51" t="s">
-        <v>696</v>
+      <c r="I9" s="52" t="s">
+        <v>697</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>697</v>
-      </c>
-      <c r="B10" s="49" t="n">
+        <v>698</v>
+      </c>
+      <c r="B10" s="50" t="n">
         <v>0.095</v>
       </c>
       <c r="C10" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="D10" s="49" t="n">
+      <c r="D10" s="50" t="n">
         <v>0.01</v>
       </c>
-      <c r="E10" s="50" t="n">
+      <c r="E10" s="51" t="n">
         <f aca="false">IF(B10=0,$B$4/(C10*12),PMT(B10/12,C10*12,-$B$4))</f>
         <v>1940.96336341166</v>
       </c>
-      <c r="F10" s="50" t="n">
+      <c r="F10" s="51" t="n">
         <f aca="false">E10*C10*12+$B$4*D10</f>
         <v>234415.603609399</v>
       </c>
-      <c r="G10" s="50" t="n">
+      <c r="G10" s="51" t="n">
         <f aca="false">F10-$B$4</f>
         <v>84415.6036093987</v>
       </c>
@@ -29934,32 +29954,32 @@
         <f aca="false">G10/C10</f>
         <v>8441.56036093986</v>
       </c>
-      <c r="I10" s="51" t="s">
-        <v>698</v>
+      <c r="I10" s="52" t="s">
+        <v>699</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>699</v>
-      </c>
-      <c r="B11" s="49" t="n">
+        <v>700</v>
+      </c>
+      <c r="B11" s="50" t="n">
         <v>0.1275</v>
       </c>
       <c r="C11" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="D11" s="49" t="n">
+      <c r="D11" s="50" t="n">
         <v>0.02</v>
       </c>
-      <c r="E11" s="50" t="n">
+      <c r="E11" s="51" t="n">
         <f aca="false">IF(B11=0,$B$4/(C11*12),PMT(B11/12,C11*12,-$B$4))</f>
         <v>2217.59712870933</v>
       </c>
-      <c r="F11" s="50" t="n">
+      <c r="F11" s="51" t="n">
         <f aca="false">E11*C11*12+$B$4*D11</f>
         <v>269111.65544512</v>
       </c>
-      <c r="G11" s="50" t="n">
+      <c r="G11" s="51" t="n">
         <f aca="false">F11-$B$4</f>
         <v>119111.65544512</v>
       </c>
@@ -29967,32 +29987,32 @@
         <f aca="false">G11/C11</f>
         <v>11911.165544512</v>
       </c>
-      <c r="I11" s="51" t="s">
-        <v>700</v>
+      <c r="I11" s="52" t="s">
+        <v>701</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>701</v>
-      </c>
-      <c r="B12" s="49" t="n">
+        <v>702</v>
+      </c>
+      <c r="B12" s="50" t="n">
         <v>0.11</v>
       </c>
       <c r="C12" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="D12" s="49" t="n">
+      <c r="D12" s="50" t="n">
         <v>0.01</v>
       </c>
-      <c r="E12" s="50" t="n">
+      <c r="E12" s="51" t="n">
         <f aca="false">IF(B12=0,$B$4/(C12*12),PMT(B12/12,C12*12,-$B$4))</f>
         <v>2568.36546523481</v>
       </c>
-      <c r="F12" s="50" t="n">
+      <c r="F12" s="51" t="n">
         <f aca="false">E12*C12*12+$B$4*D12</f>
         <v>217242.699079724</v>
       </c>
-      <c r="G12" s="50" t="n">
+      <c r="G12" s="51" t="n">
         <f aca="false">F12-$B$4</f>
         <v>67242.6990797244</v>
       </c>
@@ -30000,32 +30020,32 @@
         <f aca="false">G12/C12</f>
         <v>9606.09986853206</v>
       </c>
-      <c r="I12" s="51" t="s">
-        <v>702</v>
+      <c r="I12" s="52" t="s">
+        <v>703</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>703</v>
-      </c>
-      <c r="B13" s="49" t="n">
+        <v>704</v>
+      </c>
+      <c r="B13" s="50" t="n">
         <v>0.11</v>
       </c>
       <c r="C13" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="49" t="n">
+      <c r="D13" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="50" t="n">
+      <c r="E13" s="51" t="n">
         <f aca="false">IF(B13=0,$B$4/(C13*12),PMT(B13/12,C13*12,-$B$4))</f>
         <v>4910.80756755031</v>
       </c>
-      <c r="F13" s="50" t="n">
+      <c r="F13" s="51" t="n">
         <f aca="false">E13*C13*12+$B$4*D13</f>
         <v>176789.072431811</v>
       </c>
-      <c r="G13" s="50" t="n">
+      <c r="G13" s="51" t="n">
         <f aca="false">F13-$B$4</f>
         <v>26789.072431811</v>
       </c>
@@ -30033,41 +30053,41 @@
         <f aca="false">G13/C13</f>
         <v>8929.69081060367</v>
       </c>
-      <c r="I13" s="51" t="s">
-        <v>704</v>
+      <c r="I13" s="52" t="s">
+        <v>705</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="52" t="s">
-        <v>705</v>
-      </c>
-      <c r="B14" s="53" t="n">
+      <c r="A14" s="53" t="s">
+        <v>706</v>
+      </c>
+      <c r="B14" s="54" t="n">
         <v>0.84</v>
       </c>
-      <c r="C14" s="54" t="n">
+      <c r="C14" s="55" t="n">
         <v>0.75</v>
       </c>
-      <c r="D14" s="53" t="n">
+      <c r="D14" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="55" t="n">
+      <c r="E14" s="56" t="n">
         <f aca="false">IF(B14=0,$B$4/(C14*12),PMT(B14/12,C14*12,-$B$4))</f>
         <v>23022.9705207633</v>
       </c>
-      <c r="F14" s="55" t="n">
+      <c r="F14" s="56" t="n">
         <f aca="false">E14*C14*12+$B$4*D14</f>
         <v>207206.73468687</v>
       </c>
-      <c r="G14" s="55" t="n">
+      <c r="G14" s="56" t="n">
         <f aca="false">F14-$B$4</f>
         <v>57206.7346868697</v>
       </c>
-      <c r="H14" s="56" t="n">
+      <c r="H14" s="57" t="n">
         <f aca="false">G14/C14</f>
         <v>76275.6462491595</v>
       </c>
-      <c r="I14" s="51" t="s">
-        <v>706</v>
+      <c r="I14" s="52" t="s">
+        <v>707</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30083,7 +30103,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -30095,95 +30115,95 @@
       <c r="I16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="57" t="s">
-        <v>708</v>
-      </c>
-      <c r="B17" s="57"/>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="57"/>
-      <c r="H17" s="57"/>
-      <c r="I17" s="57"/>
+      <c r="A17" s="58" t="s">
+        <v>709</v>
+      </c>
+      <c r="B17" s="58"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
+      <c r="H17" s="58"/>
+      <c r="I17" s="58"/>
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="57" t="s">
-        <v>709</v>
-      </c>
-      <c r="B18" s="57"/>
-      <c r="C18" s="57"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="57"/>
-      <c r="G18" s="57"/>
-      <c r="H18" s="57"/>
-      <c r="I18" s="57"/>
+      <c r="A18" s="58" t="s">
+        <v>710</v>
+      </c>
+      <c r="B18" s="58"/>
+      <c r="C18" s="58"/>
+      <c r="D18" s="58"/>
+      <c r="E18" s="58"/>
+      <c r="F18" s="58"/>
+      <c r="G18" s="58"/>
+      <c r="H18" s="58"/>
+      <c r="I18" s="58"/>
     </row>
     <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="57" t="s">
-        <v>710</v>
-      </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="57"/>
+      <c r="A19" s="58" t="s">
+        <v>711</v>
+      </c>
+      <c r="B19" s="58"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="58"/>
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="57" t="s">
-        <v>711</v>
-      </c>
-      <c r="B20" s="57"/>
-      <c r="C20" s="57"/>
-      <c r="D20" s="57"/>
-      <c r="E20" s="57"/>
-      <c r="F20" s="57"/>
-      <c r="G20" s="57"/>
-      <c r="H20" s="57"/>
-      <c r="I20" s="57"/>
+      <c r="A20" s="58" t="s">
+        <v>712</v>
+      </c>
+      <c r="B20" s="58"/>
+      <c r="C20" s="58"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="58"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="58"/>
+      <c r="I20" s="58"/>
     </row>
     <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="57" t="s">
-        <v>712</v>
-      </c>
-      <c r="B21" s="57"/>
-      <c r="C21" s="57"/>
-      <c r="D21" s="57"/>
-      <c r="E21" s="57"/>
-      <c r="F21" s="57"/>
-      <c r="G21" s="57"/>
-      <c r="H21" s="57"/>
-      <c r="I21" s="57"/>
+      <c r="A21" s="58" t="s">
+        <v>713</v>
+      </c>
+      <c r="B21" s="58"/>
+      <c r="C21" s="58"/>
+      <c r="D21" s="58"/>
+      <c r="E21" s="58"/>
+      <c r="F21" s="58"/>
+      <c r="G21" s="58"/>
+      <c r="H21" s="58"/>
+      <c r="I21" s="58"/>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="57" t="s">
-        <v>713</v>
-      </c>
-      <c r="B22" s="57"/>
-      <c r="C22" s="57"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="57"/>
-      <c r="F22" s="57"/>
-      <c r="G22" s="57"/>
-      <c r="H22" s="57"/>
-      <c r="I22" s="57"/>
+      <c r="A22" s="58" t="s">
+        <v>714</v>
+      </c>
+      <c r="B22" s="58"/>
+      <c r="C22" s="58"/>
+      <c r="D22" s="58"/>
+      <c r="E22" s="58"/>
+      <c r="F22" s="58"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="58"/>
+      <c r="I22" s="58"/>
     </row>
     <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="57" t="s">
-        <v>714</v>
-      </c>
-      <c r="B23" s="57"/>
-      <c r="C23" s="57"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="57"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="57"/>
-      <c r="H23" s="57"/>
-      <c r="I23" s="57"/>
+      <c r="A23" s="58" t="s">
+        <v>715</v>
+      </c>
+      <c r="B23" s="58"/>
+      <c r="C23" s="58"/>
+      <c r="D23" s="58"/>
+      <c r="E23" s="58"/>
+      <c r="F23" s="58"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="58"/>
+      <c r="I23" s="58"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
@@ -30198,7 +30218,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -30210,17 +30230,17 @@
       <c r="I25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="58" t="s">
-        <v>716</v>
-      </c>
-      <c r="B26" s="58"/>
-      <c r="C26" s="58"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="58"/>
+      <c r="A26" s="59" t="s">
+        <v>717</v>
+      </c>
+      <c r="B26" s="59"/>
+      <c r="C26" s="59"/>
+      <c r="D26" s="59"/>
+      <c r="E26" s="59"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="59"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="59"/>
     </row>
   </sheetData>
   <sheetProtection sheet="true" password="ef11" formatCells="false" formatColumns="false" formatRows="false"/>
